--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA554"/>
+  <dimension ref="A1:AA559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25071,10 +25071,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="R256" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr"/>
@@ -37283,22 +37283,30 @@
         <v>46215</v>
       </c>
       <c r="O386" t="inlineStr"/>
-      <c r="P386" t="inlineStr"/>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
       <c r="Q386" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="R386" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S386" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T386" t="inlineStr"/>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="U386" t="inlineStr">
         <is>
-          <t>Cedeu conjunto de freio para o 2738 em 19/07/2025. Ramon 30/06/26.</t>
+          <t>Cedeu conjunto de freio para o 2738 em 19/07/2025. Ramon 30/06/26. Recibo não se encontra na Pasta do DRIVE. Godoy 08/07/2026. Recibo 529/FAB/26 assinado em 07/07. Ramon 08/07/26.</t>
         </is>
       </c>
       <c r="V386" t="inlineStr">
@@ -37315,7 +37323,7 @@
       <c r="Y386" t="inlineStr"/>
       <c r="Z386" t="inlineStr"/>
       <c r="AA386" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -39229,10 +39237,10 @@
       <c r="O406" t="inlineStr"/>
       <c r="P406" t="inlineStr"/>
       <c r="Q406" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R406" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -47057,7 +47065,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -47089,10 +47097,10 @@
         </is>
       </c>
       <c r="Q484" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="R484" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="S484" t="inlineStr">
         <is>
@@ -47109,11 +47117,7 @@
           <t>AWB 12738616480 Volume retirado na loja GOLLOG - QMA por Francisca keltlen em 02/06 - Godoy 10/06/26.Não localizado recibo no Drive.Wallace 30/06/26. ITEM ATENDIDO PELA VEE ONE  NO PN ALTERNADO 124K001-3CR-0146 CONFORME RECEBIDO 432/FAB/2026. Godoy 06/07/2026.</t>
         </is>
       </c>
-      <c r="V484" t="inlineStr">
-        <is>
-          <t>Colocado pedido junto ao fornecedor I800035 dia 30/04. ENTREGUE EM MIAMI 14/05. Carga recepcionada VCP dia 23/05. Em processo de desembaraço aduaneiro. ATZ 28/05 - MATERIAL EM RECEBIMENTO V1 AMA 29/05/2026 RC 12:06 - MATERIAL ENVIADO PELA AWB 12738616480 - DPE 02/06/2026 - MATERIAL RECEBIDO DIA 02/06/2026 3S SARA RECIBO ASSINADO 432-fab-26 EM 313260018247 313260018248 ATZ RC 03/06/2026 14:18 - RECIBO NO DRIVE COMPARTILHADO - 432-fab-26 EM 313260018247 313260018248</t>
-        </is>
-      </c>
+      <c r="V484" t="inlineStr"/>
       <c r="W484" t="inlineStr">
         <is>
           <t>VEE ONE</t>
@@ -47261,7 +47265,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -47286,19 +47290,17 @@
       <c r="N486" s="2" t="n">
         <v>46172</v>
       </c>
-      <c r="O486" s="2" t="n">
-        <v>46177</v>
-      </c>
+      <c r="O486" t="inlineStr"/>
       <c r="P486" t="inlineStr">
         <is>
           <t>2026-06-02 00:00:00</t>
         </is>
       </c>
       <c r="Q486" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="R486" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="S486" t="inlineStr">
         <is>
@@ -47315,11 +47317,7 @@
           <t>AWB 12738616480 Volume retirado na loja GOLLOG - QMA por Francisca keltlen em 02/06 - Godoy 10/06/26..Não localizado recibo no Drive.Wallace 30/06/26. ITEM ATENDIDO PELA VEE ONE  NO PN ALTERNADO 124K001-3CR-0132 CONFORME RECEBIDO 432/FAB/2026. Godoy 06/07/2026.</t>
         </is>
       </c>
-      <c r="V486" t="inlineStr">
-        <is>
-          <t>Colocado pedido junto ao fornecedor I800035 dia 30/04. ENTREGUE EM MIAMI 14/05. Carga recepcionada VCP dia 23/05. Em processo de desembaraço aduaneiro. ATZ 28/05 - MATERIAL EM RECEBIMENTO V1 AMA 29/05/2026 RC 12:06 - MATERIAL ENVIADO PELA AWB 12738616480 - DPE 02/06/2026 - MATERIAL RECEBIDO DIA 02/06/2026 3S SARA RECIBO ASSINADO 432-fab-26 EM 313260018247 313260018248 ATZ RC 03/06/2026 14:18 - RECIBO NO DRIVE COMPARTILHADO - 432-fab-26 EM 313260018247 313260018248</t>
-        </is>
-      </c>
+      <c r="V486" t="inlineStr"/>
       <c r="W486" t="inlineStr">
         <is>
           <t>VEE ONE</t>
@@ -47695,14 +47693,18 @@
         <v>46184</v>
       </c>
       <c r="O490" s="2" t="n">
-        <v>46178</v>
-      </c>
-      <c r="P490" t="inlineStr"/>
+        <v>46148</v>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
+      </c>
       <c r="Q490" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R490" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="S490" t="inlineStr">
         <is>
@@ -47716,12 +47718,12 @@
       </c>
       <c r="U490" t="inlineStr">
         <is>
-          <t>O item em estoque na BANT foi enviado pela própria Vee One em 08/05. A intenção realmente é pegar o item de volta?</t>
+          <t>O item em estoque na BANT foi enviado pela própria Vee One em 08/05. A intenção realmente é pegar o item de volta? Recibo 432/FAB/26 é referente a atendimento de emergência do 2741 em Manaus. Ramon 07/07/26. NF 1777 assinado em 03/06/26. Ramon 08/07/26.</t>
         </is>
       </c>
       <c r="V490" t="inlineStr">
         <is>
-          <t>Colocado pedido junto ao fornecedor I800035 dia 30/04. ENTREGUE EM MIAMI 14/05. Carga recepcionada VCP dia 23/05. Em processo de desembaraço aduaneiro. ATZ 28/05 - MATERIAL EM RECEBIMENTO V1 AMA 29/05/2026 RC 12:06 - MATERIAL ENVIADO PELA AWB 12738616480 - DPE 02/06/2026 - MATERIAL RECEBIDO DIA 02/06/2026 3S SARA RECIBO ASSINADO 432-fab-26 EM 313260018247 313260018248 ATZ RC 03/06/2026 14:18 - RECIBO NO DRIVE COMPARTILHADO - 432-fab-26 EM 313260018247 313260018248</t>
+          <t>ESTOQUE DE 1 EA NA BANT- CLA-11-05 NAO DISPONIBILIZADO PARA A APLICACAO. OUTRO ITEM AGUARDANDO A WILLIAM FAZER O RECOLHIMENTO - CLA-12-05 - DPE DA WILLIAM - 29/05/2026 (REZ) - ENVIADO NO DIA 01-06-26 AWB 12738926716 - MATERIAL DISPONIVEL PARA RETIRADA DIA 02/06/2026 RC atz 09:19 - RECIBO NO DRIVE 435-c98-26 - EM 329260019106</t>
         </is>
       </c>
       <c r="W490" t="inlineStr">
@@ -47739,7 +47741,7 @@
         </is>
       </c>
       <c r="AA490" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491">
@@ -49032,12 +49034,16 @@
       <c r="O503" s="2" t="n">
         <v>-620019</v>
       </c>
-      <c r="P503" t="inlineStr"/>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>2026-07-01 00:00:00</t>
+        </is>
+      </c>
       <c r="Q503" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R503" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S503" t="inlineStr">
         <is>
@@ -49051,7 +49057,7 @@
       </c>
       <c r="U503" t="inlineStr">
         <is>
-          <t>Recibo não se encontra na Pasta do DRIVE. Godoy 30/06/2026.Como não tem AWB vou cobrar o recibo Wallace 30/06/2026</t>
+          <t>Recibo não se encontra na Pasta do DRIVE. Godoy 30/06/2026.Como não tem AWB vou cobrar o recibo Wallace 30/06/2026. Recibo 511/FAB/26 assinado em 01/07. Ramon 08/07/26</t>
         </is>
       </c>
       <c r="V503" t="inlineStr">
@@ -49068,7 +49074,7 @@
       <c r="Y503" t="inlineStr"/>
       <c r="Z503" t="inlineStr"/>
       <c r="AA503" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504">
@@ -49818,7 +49824,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -49843,19 +49849,17 @@
       <c r="N511" s="2" t="n">
         <v>46199</v>
       </c>
-      <c r="O511" s="2" t="n">
-        <v>46203</v>
-      </c>
+      <c r="O511" t="inlineStr"/>
       <c r="P511" t="inlineStr">
         <is>
           <t>2026-06-20 00:00:00</t>
         </is>
       </c>
       <c r="Q511" t="n">
-        <v>10</v>
+        <v>-6</v>
       </c>
       <c r="R511" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="S511" t="inlineStr">
         <is>
@@ -49872,11 +49876,7 @@
           <t>AWB 12743528074 -  volume retirado na loja GOLLOG - QMA por kleyton. Godoy 30/06/2026.  ITEM ATENDIDO PELA VEE ONE CONFORME RECEBIDO 507/FAB/2026. Godoy 06/07/2026.</t>
         </is>
       </c>
-      <c r="V511" t="inlineStr">
-        <is>
-          <t>Colocado pedido Textron IJ17463339. Entregue em Miami 29/05. Chegada em VCP 04/06 (voo 3906). Canal amarelo dia 10/06. Carga liberada para entrega em Campinas 25/06 - MATERIAL EM TRANSITO 0 DIA 25/05/2026 VIA AWB 12743528074 RECIBO 507/FAB/26 - DPE 01/07/2026 ATZ RC 14:21 26/06/2026</t>
-        </is>
-      </c>
+      <c r="V511" t="inlineStr"/>
       <c r="W511" t="inlineStr">
         <is>
           <t>VEE ONE</t>
@@ -49923,7 +49923,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -49948,19 +49948,17 @@
       <c r="N512" s="2" t="n">
         <v>46199</v>
       </c>
-      <c r="O512" s="2" t="n">
-        <v>46203</v>
-      </c>
+      <c r="O512" t="inlineStr"/>
       <c r="P512" t="inlineStr">
         <is>
           <t>2026-06-25 00:00:00</t>
         </is>
       </c>
       <c r="Q512" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="R512" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="S512" t="inlineStr">
         <is>
@@ -49977,11 +49975,7 @@
           <t>AWB 12743092324 - volume retirado na loja GOLLOG - CWB por Brendon. Godoy 30/06/2026. ITEM ATENDIDO PELA VEE ONE CONFORME NF-e N° 1864 em 25/06/2026. Godoy 06/07/2026.</t>
         </is>
       </c>
-      <c r="V512" t="inlineStr">
-        <is>
-          <t>Colocado pedido no fornecedor I807209 dia 03/06. Previsão de entrega Miami 16/06. Previsão de chegada em GIG 18/06 - MATERIAL EM PROCESSO DE RECEBIMENTO STK V1 23/06/2026 - MATERIAL ENVIADO VIA RECIBO 501/FAB/26 AWB 12743092324 - MATERIAL DISPONIVEL PARA RETIRADA, CONTATO REALIZADO PARA RETIRADA 25/06/2026 - MATERIAL ENTREGUE DIA 25/06/2026 NOTA FISCAL ENVIADA DIA 25/06/2026 RC ATZ RC 14:21 26/06/2026</t>
-        </is>
-      </c>
+      <c r="V512" t="inlineStr"/>
       <c r="W512" t="inlineStr">
         <is>
           <t>VEE ONE</t>
@@ -51471,9 +51465,7 @@
       <c r="N527" s="2" t="n">
         <v>46207</v>
       </c>
-      <c r="O527" s="2" t="n">
-        <v>46196</v>
-      </c>
+      <c r="O527" t="inlineStr"/>
       <c r="P527" t="inlineStr">
         <is>
           <t>2026-06-23 00:00:00</t>
@@ -51500,11 +51492,7 @@
           <t>AWB 12742260142 volume retirado na loja GOLLOG - MAO por José silva em 23/06/2026 - Godoy 23/06/2026. Aguardando recibo 490/FAB/26 no drive. Enviada a NF 1844 e inserida no drive assinada em 23/06. Ramon 06/07/26.</t>
         </is>
       </c>
-      <c r="V527" t="inlineStr">
-        <is>
-          <t>CHECADO O ESTOQUE FAB QUE CONSTAVA NO SISTEMA O ESTOQUE, PORÉM É VIRTUAL. SOLICITADO APRESSAMENTO PARA A OFICINA REPARADORA ATZ 09/06/2026 - DPE de 01 ea para 18/06/2026 (REZ- 11/06/2026). - AWB 127-4226 0142 CLA 19-06 - MATERIAL DISPONIVEL PARA RETIRADA, DPE 23/06/2026 - RECIBO NO DRIVE E ENVIADO AO FISCAL</t>
-        </is>
-      </c>
+      <c r="V527" t="inlineStr"/>
       <c r="W527" t="inlineStr">
         <is>
           <t>VEE ONE</t>
@@ -52317,7 +52305,7 @@
       </c>
       <c r="U535" t="inlineStr">
         <is>
-          <t>Informar o número do Recibo. Godoy 30/06/2026. Item recebido em 26/06 através do termo 020/GLOG-BE/2026, porém foram identificadas discrepância, foi aberto AT para o PAMA-SP para verificar a possibilidade de uso ou não da FCU. No dia 30/06 a emergência foi dada como atendida, porém ainda sem resposta se será necessário atendimento de outra FCU ou não. Ramon 01/07/26.</t>
+          <t>Informar o número do Recibo. Godoy 30/06/2026. Item recebido em 26/06 através do termo 020/GLOG-BE/2026, porém foram identificadas discrepância, foi aberto AT para o PAMA-SP para verificar a possibilidade de uso ou não da FCU. No dia 30/06 a emergência foi dada como atendida, porém ainda sem resposta se será necessário atendimento de outra FCU ou não. Ramon 01/07/26. Como foi aberto FCU para verificar a possibilidade de utlizar e a empresa ficou aguardando resposta da Engenharia junto ao operador vou considerar montado da entrega até a resposta da engenharia.Foi enviado a resposta do assessormanto a empresa e considerar desmontada a partir do dia 07/07/26. 1T Wallace</t>
         </is>
       </c>
       <c r="V535" t="inlineStr"/>
@@ -52395,10 +52383,10 @@
       <c r="O536" t="inlineStr"/>
       <c r="P536" t="inlineStr"/>
       <c r="Q536" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R536" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S536" t="inlineStr">
         <is>
@@ -52413,7 +52401,7 @@
       </c>
       <c r="V536" t="inlineStr">
         <is>
-          <t>Material Liberado Canal Verde em 01/7/2026 - HAWB: 00125552354 00004021 , Invoice PPSPI01534 PO 696/JPA/2026, aguardando ICMS GIGRJ. ATZ Marcio 01/7/2026 16:13</t>
+          <t>Material Liberado Canal Verde em 01/7/2026 - HAWB: 00125552354 00004021 , Invoice PPSPI01534 PO 696/JPA/2026, aguardando ICMS GIGRJ. ATZ Marcio 01/7/2026 16:13 - material em processo de envio 06/07/2026 - AWB 12744955875 dpe 10/07/2026</t>
         </is>
       </c>
       <c r="W536" t="inlineStr">
@@ -52601,12 +52589,16 @@
       <c r="O538" s="2" t="n">
         <v>46216</v>
       </c>
-      <c r="P538" t="inlineStr"/>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
       <c r="Q538" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="R538" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S538" t="inlineStr">
         <is>
@@ -52618,7 +52610,11 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr"/>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>Recibo 536/FAB/26 assinado em 07/07. Ramon 08/07/26.</t>
+        </is>
+      </c>
       <c r="V538" t="inlineStr">
         <is>
           <t>ENVIADO PARA O OPERADDOR DIA 02/0726, AWB 127-4481 4663- (REZ-02/07/26)</t>
@@ -52633,7 +52629,7 @@
       <c r="Y538" t="inlineStr"/>
       <c r="Z538" t="inlineStr"/>
       <c r="AA538" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539">
@@ -52700,10 +52696,10 @@
       </c>
       <c r="P539" t="inlineStr"/>
       <c r="Q539" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="R539" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S539" t="inlineStr">
         <is>
@@ -52715,10 +52711,14 @@
           <t>Não</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr"/>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>Volume retirado na loja GOLLOG - BSB por tanise Assis em 03/07/2026 - Godoy 08/07/2026. Recibo não se encontra na Pasta do DRIVE. Godoy 08/07/2026.</t>
+        </is>
+      </c>
       <c r="V539" t="inlineStr">
         <is>
-          <t>Colocado pedido na Textron IJ17507011. Previsão de entrega em Miami 17/06. Carga recepcionada no GIG 24/06. Canal verde dia 26/06. DPE V1 29/06. Verificar entrega do item. ATZ 30/06 - MATERIAL EM RECEBIMENTO V1 30-06-2026 - MATERIAL EM PROCESSO DE ENVIO RECIBO 524/FAB/26 ATZ RC 30-06-2026 - MATERIAL EM TRANSITO - AWB 12744330731 DPE 03/07/2026</t>
+          <t>Colocado pedido na Textron IJ17507011. Previsão de entrega em Miami 17/06. Carga recepcionada no GIG 24/06. Canal verde dia 26/06. DPE V1 29/06. Verificar entrega do item. ATZ 30/06 - MATERIAL EM RECEBIMENTO V1 30-06-2026 - MATERIAL EM PROCESSO DE ENVIO RECIBO 524/FAB/26 ATZ RC 30-06-2026 - MATERIAL EM TRANSITO - AWB 12744330731 DPE 03/07/2026 - MATERIAL RECEBIDO POR tanise Assis RG 14807641751 DIA 03/07/2026</t>
         </is>
       </c>
       <c r="W539" t="inlineStr">
@@ -52795,10 +52795,10 @@
       <c r="O540" t="inlineStr"/>
       <c r="P540" t="inlineStr"/>
       <c r="Q540" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R540" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S540" t="inlineStr">
         <is>
@@ -52813,7 +52813,7 @@
       </c>
       <c r="V540" t="inlineStr">
         <is>
-          <t>04 ea recolhidos para a V1, chegada dos itens dia 23/06/2026. Itens não tem oficina no Brasil, terá que ser feito Exchange rc 23/06 - MATERIAL ADQUIRIDO FORNECEDOR TEXTRON -WB0003073549 DPE AGS Miami 29/6/2026 ate 10 30AM - ATZ Marcio 26/6/26 17 23PM</t>
+          <t>04 ea recolhidos para a V1, chegada dos itens dia 23/06/2026. Itens não tem oficina no Brasil, terá que ser feito Exchange rc 23/06 - MATERIAL ADQUIRIDO FORNECEDOR TEXTRON -WB0003073549 Inovice IJ17534800 DPE AGS Miami 29/6/2026 ate 10 30AM - AIR EXPORT HOUSE: 00004046 de 30/6/2026 Chegou no GIGRJ em 01/7/26 para Desembaraço - ATZ Marcio 3/7/2614:35</t>
         </is>
       </c>
       <c r="W540" t="inlineStr">
@@ -53310,14 +53310,14 @@
       <c r="O545" t="inlineStr"/>
       <c r="P545" t="inlineStr">
         <is>
-          <t>2026-06-30 00:00:00</t>
+          <t>2026-06-24 00:00:00</t>
         </is>
       </c>
       <c r="Q545" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="R545" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
@@ -53406,9 +53406,7 @@
       <c r="N546" s="2" t="n">
         <v>46207</v>
       </c>
-      <c r="O546" s="2" t="n">
-        <v>46119</v>
-      </c>
+      <c r="O546" t="inlineStr"/>
       <c r="P546" t="inlineStr">
         <is>
           <t>2026-07-02 00:00:00</t>
@@ -53435,11 +53433,7 @@
           <t>Recibo 532/FAB/26 assinado em 02/07. Ramon 06/07/26.</t>
         </is>
       </c>
-      <c r="V546" t="inlineStr">
-        <is>
-          <t>MATERIAL EM BANCADA COM DPE INICIAL NA V1 DIA 01/07/26 - SOLICITAÇÃO EPM A26619 - PO 726/JPA/2026 de 30/6/2026 ATZ Marcio 30/6 - MATERIAL EM TRANSITO - RECIBO 532/FAB/26 AWB 12744595530 DPE 04/07/2026</t>
-        </is>
-      </c>
+      <c r="V546" t="inlineStr"/>
       <c r="W546" t="inlineStr">
         <is>
           <t>VEE ONE</t>
@@ -53811,10 +53805,10 @@
       <c r="O550" t="inlineStr"/>
       <c r="P550" t="inlineStr"/>
       <c r="Q550" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="R550" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S550" t="inlineStr">
         <is>
@@ -53833,7 +53827,7 @@
       </c>
       <c r="V550" t="inlineStr">
         <is>
-          <t>Efetuada a Compra em SP na Jet Avionics, aguardando confirmar unidade em estoque para liberação do item para a Veeone 01/7/2026 14:15 Marcio - DECLINADO pela JET AVIONICS, colocado Pedido TEXTRON Confirmation Number: WB0003077522 de 01/7/2026 Invoice IJ17546081 as 15:08PM Previsao DPE AGS Miami 02/7/2026 - ATZ Marcio 1/7/26 15:09</t>
+          <t>Efetuada a Compra em SP na Jet Avionics, aguardando confirmar unidade em estoque para liberação do item para a Veeone 01/7/2026 14:15 Marcio - DECLINADO pela JET AVIONICS, colocado Pedido TEXTRON Confirmation Number: WB0003077522 de 01/7/2026 Invoice IJ17546081 as 15:08PM Previsao DPE AGS Miami 02/7/2026 - PRE ALERTA do VOO de 3/7/2026 HAWB4065 - CANAL VERDE - ATZ Mayara 7/7/26 14:34 (MATERIAL EM SEPARAÇÃO - SUP V1 JPA) Atlz Lucas 08/07 14:01</t>
         </is>
       </c>
       <c r="W550" t="inlineStr">
@@ -53910,10 +53904,10 @@
       <c r="O551" t="inlineStr"/>
       <c r="P551" t="inlineStr"/>
       <c r="Q551" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="R551" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -53923,12 +53917,12 @@
       <c r="T551" t="inlineStr"/>
       <c r="U551" t="inlineStr">
         <is>
-          <t>Cedeu o item para o C-98 2738</t>
+          <t>Cedeu o item para o C-98 2738. Pedido será atendido pelo estoque FAB pedido n° 17874678 - Godoy 07/07/2026.</t>
         </is>
       </c>
       <c r="V551" t="inlineStr">
         <is>
-          <t>PEDIDO NO EPM - FOI SOLICITADO ATENDIMENTO COM ESTOUE FAB - CLA-02-07</t>
+          <t>PEDIDO NO EPM - FOI SOLICITADO ATENDIMENTO COM ESTOUE FAB - CLA-02-07 - AWB 12744814663 DPE 07/07/2026</t>
         </is>
       </c>
       <c r="W551" t="inlineStr">
@@ -54003,27 +53997,35 @@
         <v>46216</v>
       </c>
       <c r="O552" t="inlineStr"/>
-      <c r="P552" t="inlineStr"/>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>2026-07-07 00:00:00</t>
+        </is>
+      </c>
       <c r="Q552" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="R552" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S552" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="T552" t="inlineStr"/>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
       <c r="U552" t="inlineStr">
         <is>
-          <t>Cedeu o item para o C-98 2738</t>
+          <t>Cedeu o item para o C-98 2738. Recibo 540/FAB/26 assinado em 07/07. Ramon 08/07/26.</t>
         </is>
       </c>
       <c r="V552" t="inlineStr">
         <is>
-          <t>Colocado pedido fornecedor nacional. Previsão de entrega V1 Campinas 03/07</t>
+          <t>Colocado pedido fornecedor nacional. Previsão de entrega V1 Campinas 03/07. Em processo de envio para Manaus. ATZ 06/07 - AWB 12745010442 DPE 07/07/2026</t>
         </is>
       </c>
       <c r="W552" t="inlineStr">
@@ -54035,7 +54037,7 @@
       <c r="Y552" t="inlineStr"/>
       <c r="Z552" t="inlineStr"/>
       <c r="AA552" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="553">
@@ -54100,10 +54102,10 @@
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="inlineStr"/>
       <c r="Q553" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="R553" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S553" t="inlineStr">
         <is>
@@ -54113,12 +54115,12 @@
       <c r="T553" t="inlineStr"/>
       <c r="U553" t="inlineStr">
         <is>
-          <t>Cedeu o item para o C-98 2738</t>
+          <t>Cedeu o item para o C-98 2738. Pedido será atendido pelo estoque FAB pedido n° 17875036 - Godoy 07/07/2026.</t>
         </is>
       </c>
       <c r="V553" t="inlineStr">
         <is>
-          <t>PEDIDO NO EPM - FOI SOLICITADO ATENDIMENTO COM ESTOUE FAB - CLA-02-07</t>
+          <t>PEDIDO NO EPM - FOI SOLICITADO ATENDIMENTO COM ESTOUE FAB - CLA-02-07 - AWB 12744814663 DPE 07/07/2026</t>
         </is>
       </c>
       <c r="W553" t="inlineStr">
@@ -54195,10 +54197,10 @@
       <c r="O554" t="inlineStr"/>
       <c r="P554" t="inlineStr"/>
       <c r="Q554" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="R554" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S554" t="inlineStr">
         <is>
@@ -54206,8 +54208,16 @@
         </is>
       </c>
       <c r="T554" t="inlineStr"/>
-      <c r="U554" t="inlineStr"/>
-      <c r="V554" t="inlineStr"/>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>Recibo não se encontra na Pasta do DRIVE. Godoy 08/07/2026.</t>
+        </is>
+      </c>
+      <c r="V554" t="inlineStr">
+        <is>
+          <t>Item estara disponivel no RJ na oficina para coleta dia 6/7 apos as 14 horas ATZ Marcio 3/7/ 14:25PM/ MATERIAL EM TRANSITO- RECIBO 548/FAB/26- AWB 12745474752 DPE 08/07 - Atlz Lucas- JPA (07/07)</t>
+        </is>
+      </c>
       <c r="W554" t="inlineStr">
         <is>
           <t>VEE ONE</t>
@@ -54220,6 +54230,453 @@
         <v>1</v>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>329</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>BABR</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>329260019180</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>C145-00-46</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>TRANSMISSION ASSY</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G555" t="n">
+        <v>2709</v>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>AIFP</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="K555" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="L555" t="n">
+        <v>1</v>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N555" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O555" t="inlineStr"/>
+      <c r="P555" t="inlineStr"/>
+      <c r="Q555" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R555" t="n">
+        <v>1</v>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr"/>
+      <c r="U555" t="inlineStr"/>
+      <c r="V555" t="inlineStr">
+        <is>
+          <t>Colocado pedido AOG Textron WB0003081885 - previsão de entrega em Miami 08/07</t>
+        </is>
+      </c>
+      <c r="W555" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X555" t="inlineStr"/>
+      <c r="Y555" t="inlineStr"/>
+      <c r="Z555" t="inlineStr"/>
+      <c r="AA555" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>329</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>BABR</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>329260019181</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>C145-00-46</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>TRANSMISSION ASSY</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G556" t="n">
+        <v>2721</v>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>AIFP</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="K556" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="L556" t="n">
+        <v>1</v>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N556" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="O556" t="inlineStr"/>
+      <c r="P556" t="inlineStr"/>
+      <c r="Q556" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R556" t="n">
+        <v>1</v>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr"/>
+      <c r="U556" t="inlineStr"/>
+      <c r="V556" t="inlineStr">
+        <is>
+          <t>Colocado pedido AOG Textron WB0003081885 - previsão de entrega em Miami 08/07</t>
+        </is>
+      </c>
+      <c r="W556" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X556" t="inlineStr"/>
+      <c r="Y556" t="inlineStr"/>
+      <c r="Z556" t="inlineStr"/>
+      <c r="AA556" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>685</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>BANT</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>685260012303</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>065-0065-01</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>SELECTOR ALT</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G557" t="n">
+        <v>2719</v>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>ANCE</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="K557" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="L557" t="n">
+        <v>1</v>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N557" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="O557" t="inlineStr"/>
+      <c r="P557" t="inlineStr"/>
+      <c r="Q557" t="n">
+        <v>-30</v>
+      </c>
+      <c r="R557" t="n">
+        <v>1</v>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr"/>
+      <c r="U557" t="inlineStr"/>
+      <c r="V557" t="inlineStr"/>
+      <c r="W557" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X557" t="inlineStr"/>
+      <c r="Y557" t="inlineStr"/>
+      <c r="Z557" t="inlineStr"/>
+      <c r="AA557" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>419</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>419260000556</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>066-3046-07</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>CONTROL,INDICATOR</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G558" t="n">
+        <v>2723</v>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>AIFP</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="K558" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="L558" t="n">
+        <v>1</v>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N558" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="O558" t="inlineStr"/>
+      <c r="P558" t="inlineStr"/>
+      <c r="Q558" t="n">
+        <v>-7</v>
+      </c>
+      <c r="R558" t="n">
+        <v>0</v>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr"/>
+      <c r="U558" t="inlineStr"/>
+      <c r="V558" t="inlineStr">
+        <is>
+          <t>MATERIAL EM TRANSITO - AWB 12745918331 dpe 11/07/2026 - atz rc 08/07/2026</t>
+        </is>
+      </c>
+      <c r="W558" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X558" t="inlineStr"/>
+      <c r="Y558" t="inlineStr"/>
+      <c r="Z558" t="inlineStr"/>
+      <c r="AA558" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>396</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>BABE</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>396260016563</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>3244809-4</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>FUEL CONTROL,MAIN,TU</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G559" t="n">
+        <v>2733</v>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>IPLR</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="K559" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="L559" t="n">
+        <v>1</v>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N559" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="O559" t="inlineStr"/>
+      <c r="P559" t="inlineStr"/>
+      <c r="Q559" t="n">
+        <v>-11</v>
+      </c>
+      <c r="R559" t="n">
+        <v>0</v>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr"/>
+      <c r="U559" t="inlineStr"/>
+      <c r="V559" t="inlineStr"/>
+      <c r="W559" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X559" t="inlineStr"/>
+      <c r="Y559" t="inlineStr"/>
+      <c r="Z559" t="inlineStr"/>
+      <c r="AA559" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -25071,10 +25071,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="R256" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr"/>
@@ -37289,10 +37289,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R386" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S386" t="inlineStr">
         <is>
@@ -39237,10 +39237,10 @@
       <c r="O406" t="inlineStr"/>
       <c r="P406" t="inlineStr"/>
       <c r="Q406" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R406" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -47701,10 +47701,10 @@
         </is>
       </c>
       <c r="Q490" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R490" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S490" t="inlineStr">
         <is>
@@ -49040,10 +49040,10 @@
         </is>
       </c>
       <c r="Q503" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R503" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S503" t="inlineStr">
         <is>
@@ -52383,10 +52383,10 @@
       <c r="O536" t="inlineStr"/>
       <c r="P536" t="inlineStr"/>
       <c r="Q536" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R536" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S536" t="inlineStr">
         <is>
@@ -52595,10 +52595,10 @@
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R538" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S538" t="inlineStr">
         <is>
@@ -52696,10 +52696,10 @@
       </c>
       <c r="P539" t="inlineStr"/>
       <c r="Q539" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R539" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S539" t="inlineStr">
         <is>
@@ -52795,10 +52795,10 @@
       <c r="O540" t="inlineStr"/>
       <c r="P540" t="inlineStr"/>
       <c r="Q540" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R540" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S540" t="inlineStr">
         <is>
@@ -53805,10 +53805,10 @@
       <c r="O550" t="inlineStr"/>
       <c r="P550" t="inlineStr"/>
       <c r="Q550" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R550" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S550" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
       <c r="O551" t="inlineStr"/>
       <c r="P551" t="inlineStr"/>
       <c r="Q551" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R551" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S551" t="inlineStr">
         <is>
@@ -54003,10 +54003,10 @@
         </is>
       </c>
       <c r="Q552" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R552" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S552" t="inlineStr">
         <is>
@@ -54102,10 +54102,10 @@
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="inlineStr"/>
       <c r="Q553" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R553" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S553" t="inlineStr">
         <is>
@@ -54197,10 +54197,10 @@
       <c r="O554" t="inlineStr"/>
       <c r="P554" t="inlineStr"/>
       <c r="Q554" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R554" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S554" t="inlineStr">
         <is>
@@ -54292,10 +54292,10 @@
       <c r="O555" t="inlineStr"/>
       <c r="P555" t="inlineStr"/>
       <c r="Q555" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R555" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S555" t="inlineStr">
         <is>
@@ -54383,10 +54383,10 @@
       <c r="O556" t="inlineStr"/>
       <c r="P556" t="inlineStr"/>
       <c r="Q556" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R556" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S556" t="inlineStr">
         <is>
@@ -54474,10 +54474,10 @@
       <c r="O557" t="inlineStr"/>
       <c r="P557" t="inlineStr"/>
       <c r="Q557" t="n">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R557" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S557" t="inlineStr">
         <is>
@@ -54561,10 +54561,10 @@
       <c r="O558" t="inlineStr"/>
       <c r="P558" t="inlineStr"/>
       <c r="Q558" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R558" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S558" t="inlineStr">
         <is>
@@ -54652,10 +54652,10 @@
       <c r="O559" t="inlineStr"/>
       <c r="P559" t="inlineStr"/>
       <c r="Q559" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S559" t="inlineStr">
         <is>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA559"/>
+  <dimension ref="A1:AA562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37257,7 +37257,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Aguardando solução</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -47667,7 +47667,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -47701,10 +47701,10 @@
         </is>
       </c>
       <c r="Q490" t="n">
-        <v>28</v>
+        <v>-8</v>
       </c>
       <c r="R490" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="S490" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -52595,10 +52595,10 @@
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="R538" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S538" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -53902,7 +53902,11 @@
         <v>46216</v>
       </c>
       <c r="O551" t="inlineStr"/>
-      <c r="P551" t="inlineStr"/>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>2026-07-09 00:00:00</t>
+        </is>
+      </c>
       <c r="Q551" t="n">
         <v>-4</v>
       </c>
@@ -53917,7 +53921,7 @@
       <c r="T551" t="inlineStr"/>
       <c r="U551" t="inlineStr">
         <is>
-          <t>Cedeu o item para o C-98 2738. Pedido será atendido pelo estoque FAB pedido n° 17874678 - Godoy 07/07/2026.</t>
+          <t>Cedeu o item para o C-98 2738. Pedido será atendido pelo estoque FAB pedido n° 17874678 - Godoy 07/07/2026. Movimento recebido no SILOMS em 09/07. Ramon 09/07/26</t>
         </is>
       </c>
       <c r="V551" t="inlineStr">
@@ -53934,7 +53938,7 @@
       <c r="Y551" t="inlineStr"/>
       <c r="Z551" t="inlineStr"/>
       <c r="AA551" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552">
@@ -53971,7 +53975,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -54003,10 +54007,10 @@
         </is>
       </c>
       <c r="Q552" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="R552" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S552" t="inlineStr">
         <is>
@@ -54074,7 +54078,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Providência tomada</t>
+          <t>Emg concluída</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -54100,7 +54104,11 @@
         <v>46216</v>
       </c>
       <c r="O553" t="inlineStr"/>
-      <c r="P553" t="inlineStr"/>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>2026-07-09 00:00:00</t>
+        </is>
+      </c>
       <c r="Q553" t="n">
         <v>-4</v>
       </c>
@@ -54115,7 +54123,7 @@
       <c r="T553" t="inlineStr"/>
       <c r="U553" t="inlineStr">
         <is>
-          <t>Cedeu o item para o C-98 2738. Pedido será atendido pelo estoque FAB pedido n° 17875036 - Godoy 07/07/2026.</t>
+          <t>Cedeu o item para o C-98 2738. Pedido será atendido pelo estoque FAB pedido n° 17875036 - Godoy 07/07/2026. Movimento recebido no SILOMS em 09/07. Ramon 09/07/26</t>
         </is>
       </c>
       <c r="V553" t="inlineStr">
@@ -54132,7 +54140,7 @@
       <c r="Y553" t="inlineStr"/>
       <c r="Z553" t="inlineStr"/>
       <c r="AA553" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="554">
@@ -54264,7 +54272,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -54355,7 +54363,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -54446,7 +54454,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -54533,7 +54541,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -54624,7 +54632,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -54677,6 +54685,271 @@
         <v>1</v>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>396</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>BABE</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>396260016566</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>060-0015-00</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>CONTROL,DIRECTIONAL,</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G560" t="n">
+        <v>2726</v>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>AIFP</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="K560" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="L560" t="n">
+        <v>1</v>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N560" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="O560" t="inlineStr"/>
+      <c r="P560" t="inlineStr"/>
+      <c r="Q560" t="n">
+        <v>-7</v>
+      </c>
+      <c r="R560" t="n">
+        <v>0</v>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr"/>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>Cedeu o item para o C-98 2721. Ramon 09/07/26.</t>
+        </is>
+      </c>
+      <c r="V560" t="inlineStr"/>
+      <c r="W560" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X560" t="inlineStr"/>
+      <c r="Y560" t="inlineStr"/>
+      <c r="Z560" t="inlineStr"/>
+      <c r="AA560" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>419</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>CLA</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>419260000557</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>3244897-4</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>FUEL CONTROL UNIT</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G561" t="n">
+        <v>2723</v>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>AIFP</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="K561" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="L561" t="n">
+        <v>1</v>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N561" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="O561" t="inlineStr"/>
+      <c r="P561" t="inlineStr"/>
+      <c r="Q561" t="n">
+        <v>-7</v>
+      </c>
+      <c r="R561" t="n">
+        <v>0</v>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr"/>
+      <c r="U561" t="inlineStr"/>
+      <c r="V561" t="inlineStr"/>
+      <c r="W561" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X561" t="inlineStr"/>
+      <c r="Y561" t="inlineStr"/>
+      <c r="Z561" t="inlineStr"/>
+      <c r="AA561" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>685</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>BANT</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>685260012350</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>030-1094-58</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>CONNECTOR</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G562" t="n">
+        <v>2702</v>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>ANCE</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="K562" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="L562" t="n">
+        <v>1</v>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N562" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="O562" t="inlineStr"/>
+      <c r="P562" t="inlineStr"/>
+      <c r="Q562" t="n">
+        <v>-31</v>
+      </c>
+      <c r="R562" t="n">
+        <v>0</v>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr"/>
+      <c r="U562" t="inlineStr"/>
+      <c r="V562" t="inlineStr"/>
+      <c r="W562" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X562" t="inlineStr"/>
+      <c r="Y562" t="inlineStr"/>
+      <c r="Z562" t="inlineStr"/>
+      <c r="AA562" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -37257,7 +37257,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -54693,7 +54693,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -54788,7 +54788,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -54879,7 +54879,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -25059,10 +25059,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R256" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="S256" t="inlineStr"/>
       <c r="T256" t="inlineStr"/>
@@ -37277,10 +37277,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R386" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S386" t="inlineStr">
         <is>
@@ -39221,10 +39221,10 @@
       <c r="O406" t="inlineStr"/>
       <c r="P406" t="inlineStr"/>
       <c r="Q406" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R406" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -49016,10 +49016,10 @@
         </is>
       </c>
       <c r="Q503" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R503" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S503" t="inlineStr">
         <is>
@@ -52355,10 +52355,10 @@
       <c r="O536" t="inlineStr"/>
       <c r="P536" t="inlineStr"/>
       <c r="Q536" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R536" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S536" t="inlineStr">
         <is>
@@ -52662,10 +52662,10 @@
       </c>
       <c r="P539" t="inlineStr"/>
       <c r="Q539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R539" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S539" t="inlineStr">
         <is>
@@ -52761,10 +52761,10 @@
       <c r="O540" t="inlineStr"/>
       <c r="P540" t="inlineStr"/>
       <c r="Q540" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R540" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S540" t="inlineStr">
         <is>
@@ -53771,10 +53771,10 @@
       <c r="O550" t="inlineStr"/>
       <c r="P550" t="inlineStr"/>
       <c r="Q550" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R550" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S550" t="inlineStr">
         <is>
@@ -54159,10 +54159,10 @@
       <c r="O554" t="inlineStr"/>
       <c r="P554" t="inlineStr"/>
       <c r="Q554" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R554" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S554" t="inlineStr">
         <is>
@@ -54254,10 +54254,10 @@
       <c r="O555" t="inlineStr"/>
       <c r="P555" t="inlineStr"/>
       <c r="Q555" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R555" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S555" t="inlineStr">
         <is>
@@ -54345,10 +54345,10 @@
       <c r="O556" t="inlineStr"/>
       <c r="P556" t="inlineStr"/>
       <c r="Q556" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R556" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S556" t="inlineStr">
         <is>
@@ -54436,10 +54436,10 @@
       <c r="O557" t="inlineStr"/>
       <c r="P557" t="inlineStr"/>
       <c r="Q557" t="n">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R557" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S557" t="inlineStr">
         <is>
@@ -54527,10 +54527,10 @@
       <c r="O558" t="inlineStr"/>
       <c r="P558" t="inlineStr"/>
       <c r="Q558" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R558" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S558" t="inlineStr">
         <is>
@@ -54622,10 +54622,10 @@
       <c r="O559" t="inlineStr"/>
       <c r="P559" t="inlineStr"/>
       <c r="Q559" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R559" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S559" t="inlineStr">
         <is>
@@ -54713,10 +54713,10 @@
       <c r="O560" t="inlineStr"/>
       <c r="P560" t="inlineStr"/>
       <c r="Q560" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R560" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S560" t="inlineStr">
         <is>
@@ -54808,10 +54808,10 @@
       <c r="O561" t="inlineStr"/>
       <c r="P561" t="inlineStr"/>
       <c r="Q561" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R561" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S561" t="inlineStr">
         <is>
@@ -54899,10 +54899,10 @@
       <c r="O562" t="inlineStr"/>
       <c r="P562" t="inlineStr"/>
       <c r="Q562" t="n">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R562" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S562" t="inlineStr">
         <is>
@@ -54990,10 +54990,10 @@
       <c r="O563" t="inlineStr"/>
       <c r="P563" t="inlineStr"/>
       <c r="Q563" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="R563" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S563" t="inlineStr">
         <is>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA563"/>
+  <dimension ref="A1:AA566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30616,11 +30616,15 @@
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
-          <t>verificar data</t>
-        </is>
-      </c>
-      <c r="Q315" t="inlineStr"/>
-      <c r="R315" t="inlineStr"/>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q315" t="n">
+        <v>-7</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0</v>
+      </c>
       <c r="S315" t="inlineStr"/>
       <c r="T315" t="inlineStr"/>
       <c r="U315" t="inlineStr">
@@ -52779,7 +52783,7 @@
       </c>
       <c r="V540" t="inlineStr">
         <is>
-          <t>"04 ea recolhidos para a V1, chegada dos itens dia 23/06/2026. Itens não tem oficina no Brasil, terá que ser feito  Exchange rc 23/06 - MATERIAL ADQUIRIDO FORNECEDOR TEXTRON -WB0003073549 Inovice IJ17534800 DPE AGS  Miami 29/6/2026 ate 10 30AM - AIR EXPORT HOUSE: 00004046 de 30/6/2026 Chegou no GIGRJ em 01/7/26 para  Desembaraço - ATZ Marcio 3/7/26 CANAL VERDE EM 7/7/26 entregue V1 em 8/7/26 ATZ Marcio 9/7/26"</t>
+          <t>04 ea recolhidos para a V1, chegada dos itens dia 23/06/2026. Itens não tem oficina no Brasil, terá que ser feito Exchange rc 23/06 - MATERIAL ADQUIRIDO FORNECEDOR TEXTRON -WB0003073549 Inovice IJ17534800 DPE AGS Miami 29/6/2026 ate 10 30AM - AIR EXPORT HOUSE: 00004046 de 30/6/2026 Chegou no GIGRJ em 01/7/26 para Desembaraço - ATZ Marcio 3/7/26 CANAL VERDE EM 7/7/26 entregue V1 em 8/7/26 ATZ Marcio 9/7/26 - MATERIAL EM TRANSITO - RECIBO 560/FAB/26 AWB - 12746187256 DPE 13/07/2026</t>
         </is>
       </c>
       <c r="W540" t="inlineStr">
@@ -54177,7 +54181,7 @@
       </c>
       <c r="V554" t="inlineStr">
         <is>
-          <t>Item estara disponivel no RJ na oficina para coleta dia 6/7 apos as 14 horas ATZ Marcio 3/7/ 14:25PM/ MATERIAL EM TRANSITO- RECIBO 548/FAB/26- AWB 12745474752 DPE 08/07 - Atlz Lucas- JPA (07/07) - MATERIAL DISPONIVEL PRA RETIRADA DIA 09/07/2026 ATZ RC</t>
+          <t>Item estara disponivel no RJ na oficina para coleta dia 6/7 apos as 14 horas ATZ Marcio 3/7/ 14:25PM/ MATERIAL EM TRANSITO- RECIBO 548/FAB/26- AWB 12745474752 DPE 08/07 - Atlz Lucas- JPA (07/07) - MATERIAL DISPONIVEL PRA RETIRADA DIA 09/07/2026 ATZ RC - MATERIAL RETIRADO DIA 09/07/2026 POR KÉSIA SANTOS</t>
         </is>
       </c>
       <c r="W554" t="inlineStr">
@@ -54231,7 +54235,7 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>AIFP</t>
+          <t>ANCE</t>
         </is>
       </c>
       <c r="J555" s="1" t="n">
@@ -54249,12 +54253,12 @@
         </is>
       </c>
       <c r="N555" s="1" t="n">
-        <v>46217</v>
+        <v>46241</v>
       </c>
       <c r="O555" t="inlineStr"/>
       <c r="P555" t="inlineStr"/>
       <c r="Q555" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="R555" t="n">
         <v>7</v>
@@ -54268,7 +54272,7 @@
       <c r="U555" t="inlineStr"/>
       <c r="V555" t="inlineStr">
         <is>
-          <t>Colocado pedido AOG Textron IJ17557538 - previsão de entrega em Miami 08/07. Previsão de chegada GIG 09/07 - MATERIAL EM TRANSITO - RECIBO 551/FAB/26 - ENVIADO PN COMPLETO PARA SANAR A EMERGENCIA DO 2709, ENVIADO MODAL TERRESTRE, DPE 09/07/2026</t>
+          <t>Colocado pedido AOG Textron IJ17557538 - previsão de entrega em Miami 08/07. Previsão de chegada GIG 09/07 - MATERIAL EM TRANSITO - RECIBO 551/FAB/26 - ENVIADO PN COMPLETO PARA SANAR A EMERGENCIA DO 2709, ENVIADO MODAL TERRESTRE, DPE 13/07/2026</t>
         </is>
       </c>
       <c r="W555" t="inlineStr">
@@ -54359,7 +54363,7 @@
       <c r="U556" t="inlineStr"/>
       <c r="V556" t="inlineStr">
         <is>
-          <t>Colocado pedido AOG Textron IJ17557538 - previsão de entrega em Miami 08/07. Previsão de chegada GIG 09/07 (voo 4093)</t>
+          <t>Colocado pedido AOG Textron IJ17557538 - previsão de entrega em Miami 08/07. HAWB4093 - CANAL VERDE - ENTREGUE NA VEE ONE 13/07. ATZ MAYARA 13/07/26</t>
         </is>
       </c>
       <c r="W556" t="inlineStr">
@@ -54962,7 +54966,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Aguardando solução</t>
+          <t>Providência tomada</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -55019,6 +55023,267 @@
         <v>1</v>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>313</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>BAMN</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>313260018674</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>205842-1</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>CONNECTOR</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G564" t="n">
+        <v>2736</v>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>ANCE</t>
+        </is>
+      </c>
+      <c r="J564" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="K564" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="L564" t="n">
+        <v>1</v>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N564" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="O564" t="inlineStr"/>
+      <c r="P564" t="inlineStr"/>
+      <c r="Q564" t="n">
+        <v>-31</v>
+      </c>
+      <c r="R564" t="n">
+        <v>0</v>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr"/>
+      <c r="U564" t="inlineStr"/>
+      <c r="V564" t="inlineStr"/>
+      <c r="W564" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X564" t="inlineStr"/>
+      <c r="Y564" t="inlineStr"/>
+      <c r="Z564" t="inlineStr"/>
+      <c r="AA564" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>685</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>BANT</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>685260012368</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>C611008-0101</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>ALTERNATOR CONTROL U</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G565" t="n">
+        <v>2729</v>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>ANCE</t>
+        </is>
+      </c>
+      <c r="J565" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="K565" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="L565" t="n">
+        <v>1</v>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N565" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="O565" t="inlineStr"/>
+      <c r="P565" t="inlineStr"/>
+      <c r="Q565" t="n">
+        <v>-31</v>
+      </c>
+      <c r="R565" t="n">
+        <v>0</v>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr"/>
+      <c r="U565" t="inlineStr"/>
+      <c r="V565" t="inlineStr"/>
+      <c r="W565" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X565" t="inlineStr"/>
+      <c r="Y565" t="inlineStr"/>
+      <c r="Z565" t="inlineStr"/>
+      <c r="AA565" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>386</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>BACO</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>386260013445</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>C611008-0101</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>ALTERNATOR CONTROL U</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G566" t="n">
+        <v>2743</v>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Aguardando solução</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>IPLR</t>
+        </is>
+      </c>
+      <c r="J566" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="K566" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="L566" t="n">
+        <v>1</v>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="N566" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="O566" t="inlineStr"/>
+      <c r="P566" t="inlineStr"/>
+      <c r="Q566" t="n">
+        <v>-11</v>
+      </c>
+      <c r="R566" t="n">
+        <v>0</v>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T566" t="inlineStr"/>
+      <c r="U566" t="inlineStr"/>
+      <c r="V566" t="inlineStr"/>
+      <c r="W566" t="inlineStr">
+        <is>
+          <t>VEE ONE</t>
+        </is>
+      </c>
+      <c r="X566" t="inlineStr"/>
+      <c r="Y566" t="inlineStr"/>
+      <c r="Z566" t="inlineStr"/>
+      <c r="AA566" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32372,10 +32372,10 @@
         <v>1374</v>
       </c>
       <c r="Q386">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R386">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S386" t="s">
         <v>1442</v>
@@ -33708,10 +33708,10 @@
         <v>46091</v>
       </c>
       <c r="Q406">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="R406">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="S406" t="s">
         <v>1441</v>
@@ -42968,10 +42968,10 @@
         <v>46216</v>
       </c>
       <c r="Q539">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R539">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S539" t="s">
         <v>1441</v>
@@ -43039,10 +43039,10 @@
         <v>46216</v>
       </c>
       <c r="Q540">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R540">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S540" t="s">
         <v>1441</v>
@@ -43734,10 +43734,10 @@
         <v>46214</v>
       </c>
       <c r="Q550">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R550">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S550" t="s">
         <v>1441</v>
@@ -44003,10 +44003,10 @@
         <v>46212</v>
       </c>
       <c r="Q554">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R554">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S554" t="s">
         <v>1441</v>
@@ -44136,10 +44136,10 @@
         <v>46216</v>
       </c>
       <c r="Q556">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R556">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S556" t="s">
         <v>1441</v>
@@ -44201,10 +44201,10 @@
         <v>46238</v>
       </c>
       <c r="Q557">
-        <v>-21</v>
+        <v>-18</v>
       </c>
       <c r="R557">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S557" t="s">
         <v>1441</v>
@@ -44266,10 +44266,10 @@
         <v>46213</v>
       </c>
       <c r="Q558">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R558">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S558" t="s">
         <v>1441</v>
@@ -44334,10 +44334,10 @@
         <v>46237</v>
       </c>
       <c r="Q559">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="R559">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S559" t="s">
         <v>1441</v>
@@ -44399,10 +44399,10 @@
         <v>46216</v>
       </c>
       <c r="Q560">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R560">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S560" t="s">
         <v>1442</v>
@@ -44467,10 +44467,10 @@
         <v>46237</v>
       </c>
       <c r="Q561">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R561">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S561" t="s">
         <v>1441</v>
@@ -44529,10 +44529,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-23</v>
+        <v>-20</v>
       </c>
       <c r="R562">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S562" t="s">
         <v>1441</v>
@@ -44594,10 +44594,10 @@
         <v>46219</v>
       </c>
       <c r="Q563">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="R563">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S563" t="s">
         <v>1441</v>
@@ -44659,10 +44659,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="R564">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S564" t="s">
         <v>1441</v>
@@ -44718,10 +44718,10 @@
         <v>46228</v>
       </c>
       <c r="Q565">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="R565">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S565" t="s">
         <v>1441</v>
@@ -44780,10 +44780,10 @@
         <v>46218</v>
       </c>
       <c r="Q566">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="R566">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S566" t="s">
         <v>1441</v>
@@ -44842,10 +44842,10 @@
         <v>46229</v>
       </c>
       <c r="Q567">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="R567">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S567" t="s">
         <v>1441</v>
@@ -44901,10 +44901,10 @@
         <v>46229</v>
       </c>
       <c r="Q568">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="R568">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S568" t="s">
         <v>1441</v>
@@ -44960,10 +44960,10 @@
         <v>46230</v>
       </c>
       <c r="Q569">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="R569">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S569" t="s">
         <v>1441</v>
@@ -45019,10 +45019,10 @@
         <v>46251</v>
       </c>
       <c r="Q570">
-        <v>-31</v>
+        <v>-28</v>
       </c>
       <c r="R570">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S570" t="s">
         <v>1442</v>
@@ -45078,10 +45078,10 @@
         <v>46228</v>
       </c>
       <c r="Q571">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="R571">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S571" t="s">
         <v>1442</v>
@@ -45140,10 +45140,10 @@
         <v>46232</v>
       </c>
       <c r="Q572">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="R572">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S572" t="s">
         <v>1441</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32459,10 +32459,10 @@
         <v>1387</v>
       </c>
       <c r="Q386">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R386">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S386" t="s">
         <v>1459</v>
@@ -33795,10 +33795,10 @@
         <v>46091</v>
       </c>
       <c r="Q406">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R406">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S406" t="s">
         <v>1458</v>
@@ -43055,10 +43055,10 @@
         <v>46216</v>
       </c>
       <c r="Q539">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R539">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S539" t="s">
         <v>1458</v>
@@ -44096,10 +44096,10 @@
         <v>1453</v>
       </c>
       <c r="Q554">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R554">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S554" t="s">
         <v>1458</v>
@@ -44235,10 +44235,10 @@
         <v>46216</v>
       </c>
       <c r="Q556">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R556">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S556" t="s">
         <v>1458</v>
@@ -44303,10 +44303,10 @@
         <v>46238</v>
       </c>
       <c r="Q557">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R557">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S557" t="s">
         <v>1458</v>
@@ -44368,10 +44368,10 @@
         <v>46213</v>
       </c>
       <c r="Q558">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R558">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S558" t="s">
         <v>1458</v>
@@ -44439,10 +44439,10 @@
         <v>46237</v>
       </c>
       <c r="Q559">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R559">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S559" t="s">
         <v>1458</v>
@@ -44507,10 +44507,10 @@
         <v>46216</v>
       </c>
       <c r="Q560">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R560">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S560" t="s">
         <v>1459</v>
@@ -44575,10 +44575,10 @@
         <v>46237</v>
       </c>
       <c r="Q561">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R561">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S561" t="s">
         <v>1458</v>
@@ -44643,10 +44643,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="R562">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S562" t="s">
         <v>1458</v>
@@ -44773,10 +44773,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="R564">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S564" t="s">
         <v>1458</v>
@@ -44835,10 +44835,10 @@
         <v>46228</v>
       </c>
       <c r="Q565">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R565">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S565" t="s">
         <v>1458</v>
@@ -45042,10 +45042,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R568">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S568" t="s">
         <v>1458</v>
@@ -45110,10 +45110,10 @@
         <v>46230</v>
       </c>
       <c r="Q569">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R569">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S569" t="s">
         <v>1458</v>
@@ -45175,10 +45175,10 @@
         <v>46251</v>
       </c>
       <c r="Q570">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R570">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S570" t="s">
         <v>1459</v>
@@ -45308,10 +45308,10 @@
         <v>46232</v>
       </c>
       <c r="Q572">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R572">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S572" t="s">
         <v>1458</v>
@@ -45373,10 +45373,10 @@
         <v>46228</v>
       </c>
       <c r="Q573">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R573">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S573" t="s">
         <v>1458</v>
@@ -45438,10 +45438,10 @@
         <v>46229</v>
       </c>
       <c r="Q574">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R574">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S574" t="s">
         <v>1458</v>
@@ -45503,10 +45503,10 @@
         <v>46254</v>
       </c>
       <c r="Q575">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R575">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S575" t="s">
         <v>1458</v>
@@ -45568,10 +45568,10 @@
         <v>46255</v>
       </c>
       <c r="Q576">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R576">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S576" t="s">
         <v>1458</v>
@@ -45630,10 +45630,10 @@
         <v>46256</v>
       </c>
       <c r="Q577">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R577">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S577" t="s">
         <v>1459</v>
@@ -45692,10 +45692,10 @@
         <v>46233</v>
       </c>
       <c r="Q578">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="R578">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S578" t="s">
         <v>1458</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7245" uniqueCount="2299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7246" uniqueCount="2300">
   <si>
     <t>om_emg</t>
   </si>
@@ -5723,6 +5723,9 @@
   </si>
   <si>
     <t>Alterado o tipo da emerg. de IPLR para ANCE. Godoy 22/07/26</t>
+  </si>
+  <si>
+    <t>Será atendido com o estoque FAB pedido 17963489. Godoy 23/07/2026</t>
   </si>
   <si>
     <t>Vee One preferiu atender a demanda com estoque da empresa. Godoy 16/07/26. AWB 12747645135 - volume retirados na loja GOLLOG - CGR por givanildo em 20/07. Godoy 21/07/26. item atendido pela NF-e 1971 em 20/07/2026. Godoy 21/07/2026.</t>
@@ -7388,7 +7391,7 @@
         <v>1463</v>
       </c>
       <c r="W2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7450,16 +7453,16 @@
         <v>1464</v>
       </c>
       <c r="W3" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X3" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="Y3" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z3" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7521,7 +7524,7 @@
         <v>1463</v>
       </c>
       <c r="W4" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7583,7 +7586,7 @@
         <v>1465</v>
       </c>
       <c r="W5" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7645,7 +7648,7 @@
         <v>1466</v>
       </c>
       <c r="W6" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7707,7 +7710,7 @@
         <v>1467</v>
       </c>
       <c r="W7" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7769,7 +7772,7 @@
         <v>1468</v>
       </c>
       <c r="W8" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7831,7 +7834,7 @@
         <v>1469</v>
       </c>
       <c r="W9" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -7893,7 +7896,7 @@
         <v>1470</v>
       </c>
       <c r="W10" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -7955,7 +7958,7 @@
         <v>1471</v>
       </c>
       <c r="W11" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8017,7 +8020,7 @@
         <v>1472</v>
       </c>
       <c r="W12" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8079,7 +8082,7 @@
         <v>1468</v>
       </c>
       <c r="W13" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8141,16 +8144,16 @@
         <v>1473</v>
       </c>
       <c r="W14" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X14" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="Y14" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z14" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8209,7 +8212,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8274,7 +8277,7 @@
         <v>1474</v>
       </c>
       <c r="W16" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8336,7 +8339,7 @@
         <v>1475</v>
       </c>
       <c r="W17" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8398,7 +8401,7 @@
         <v>1466</v>
       </c>
       <c r="W18" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8460,7 +8463,7 @@
         <v>1466</v>
       </c>
       <c r="W19" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8522,7 +8525,7 @@
         <v>1476</v>
       </c>
       <c r="W20" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8584,7 +8587,7 @@
         <v>1477</v>
       </c>
       <c r="W21" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8646,7 +8649,7 @@
         <v>1477</v>
       </c>
       <c r="W22" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8708,7 +8711,7 @@
         <v>1478</v>
       </c>
       <c r="W23" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8767,7 +8770,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -8826,7 +8829,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -8888,7 +8891,7 @@
         <v>1466</v>
       </c>
       <c r="W26" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -8947,7 +8950,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9006,7 +9009,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9068,7 +9071,7 @@
         <v>1479</v>
       </c>
       <c r="W29" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9127,7 +9130,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9189,7 +9192,7 @@
         <v>1480</v>
       </c>
       <c r="W31" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9251,7 +9254,7 @@
         <v>1481</v>
       </c>
       <c r="W32" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9313,7 +9316,7 @@
         <v>1482</v>
       </c>
       <c r="W33" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9375,7 +9378,7 @@
         <v>1483</v>
       </c>
       <c r="W34" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9437,7 +9440,7 @@
         <v>1484</v>
       </c>
       <c r="W35" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9499,7 +9502,7 @@
         <v>1480</v>
       </c>
       <c r="W36" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9561,7 +9564,7 @@
         <v>1485</v>
       </c>
       <c r="W37" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9623,7 +9626,7 @@
         <v>1463</v>
       </c>
       <c r="W38" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9685,7 +9688,7 @@
         <v>1482</v>
       </c>
       <c r="W39" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9747,7 +9750,7 @@
         <v>1486</v>
       </c>
       <c r="W40" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -9809,7 +9812,7 @@
         <v>1487</v>
       </c>
       <c r="W41" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -9871,16 +9874,16 @@
         <v>1488</v>
       </c>
       <c r="W42" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X42" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="Y42" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z42" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -9942,7 +9945,7 @@
         <v>1482</v>
       </c>
       <c r="W43" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10004,7 +10007,7 @@
         <v>1489</v>
       </c>
       <c r="W44" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10066,7 +10069,7 @@
         <v>1482</v>
       </c>
       <c r="W45" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10128,7 +10131,7 @@
         <v>1482</v>
       </c>
       <c r="W46" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10190,7 +10193,7 @@
         <v>1490</v>
       </c>
       <c r="W47" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10252,7 +10255,7 @@
         <v>1491</v>
       </c>
       <c r="W48" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10314,7 +10317,7 @@
         <v>1492</v>
       </c>
       <c r="W49" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10376,7 +10379,7 @@
         <v>1493</v>
       </c>
       <c r="W50" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10438,7 +10441,7 @@
         <v>1494</v>
       </c>
       <c r="W51" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10500,7 +10503,7 @@
         <v>1483</v>
       </c>
       <c r="W52" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10562,7 +10565,7 @@
         <v>1477</v>
       </c>
       <c r="W53" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10624,7 +10627,7 @@
         <v>1477</v>
       </c>
       <c r="W54" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10686,7 +10689,7 @@
         <v>1477</v>
       </c>
       <c r="W55" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10748,7 +10751,7 @@
         <v>1495</v>
       </c>
       <c r="W56" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -10810,7 +10813,7 @@
         <v>1496</v>
       </c>
       <c r="W57" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -10872,16 +10875,16 @@
         <v>1497</v>
       </c>
       <c r="W58" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X58" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="Y58" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z58" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -10943,7 +10946,7 @@
         <v>1498</v>
       </c>
       <c r="W59" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11005,7 +11008,7 @@
         <v>1499</v>
       </c>
       <c r="W60" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11067,7 +11070,7 @@
         <v>1477</v>
       </c>
       <c r="W61" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11129,7 +11132,7 @@
         <v>1500</v>
       </c>
       <c r="W62" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11188,7 +11191,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11247,7 +11250,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11306,7 +11309,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11365,7 +11368,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11424,7 +11427,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11483,7 +11486,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11545,7 +11548,7 @@
         <v>1501</v>
       </c>
       <c r="W69" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11607,7 +11610,7 @@
         <v>1499</v>
       </c>
       <c r="W70" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11669,7 +11672,7 @@
         <v>1484</v>
       </c>
       <c r="W71" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11731,7 +11734,7 @@
         <v>1502</v>
       </c>
       <c r="W72" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -11793,7 +11796,7 @@
         <v>1503</v>
       </c>
       <c r="W73" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -11855,16 +11858,16 @@
         <v>1504</v>
       </c>
       <c r="W74" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X74" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="Y74" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z74" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -11926,16 +11929,16 @@
         <v>1505</v>
       </c>
       <c r="W75" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X75" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="Y75" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z75" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -11997,7 +12000,7 @@
         <v>1484</v>
       </c>
       <c r="W76" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12059,7 +12062,7 @@
         <v>1484</v>
       </c>
       <c r="W77" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12121,10 +12124,10 @@
         <v>1506</v>
       </c>
       <c r="W78" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="Z78" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12189,7 +12192,7 @@
         <v>1507</v>
       </c>
       <c r="W79" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12248,7 +12251,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12307,7 +12310,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12369,7 +12372,7 @@
         <v>1508</v>
       </c>
       <c r="W82" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12431,7 +12434,7 @@
         <v>1509</v>
       </c>
       <c r="W83" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12493,7 +12496,7 @@
         <v>1510</v>
       </c>
       <c r="W84" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12552,7 +12555,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12614,7 +12617,7 @@
         <v>1511</v>
       </c>
       <c r="W86" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12676,7 +12679,7 @@
         <v>1512</v>
       </c>
       <c r="W87" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12738,7 +12741,7 @@
         <v>1512</v>
       </c>
       <c r="W88" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -12800,7 +12803,7 @@
         <v>1477</v>
       </c>
       <c r="W89" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -12862,16 +12865,16 @@
         <v>1513</v>
       </c>
       <c r="W90" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X90" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="Y90" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z90" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -12933,16 +12936,16 @@
         <v>1514</v>
       </c>
       <c r="W91" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X91" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="Y91" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z91" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13004,7 +13007,7 @@
         <v>1515</v>
       </c>
       <c r="W92" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13066,7 +13069,7 @@
         <v>1516</v>
       </c>
       <c r="W93" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13128,7 +13131,7 @@
         <v>1516</v>
       </c>
       <c r="W94" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13190,7 +13193,7 @@
         <v>1517</v>
       </c>
       <c r="W95" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13252,16 +13255,16 @@
         <v>1518</v>
       </c>
       <c r="W96" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X96" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="Y96" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z96" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13323,7 +13326,7 @@
         <v>1519</v>
       </c>
       <c r="W97" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13385,7 +13388,7 @@
         <v>1520</v>
       </c>
       <c r="W98" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13447,7 +13450,7 @@
         <v>1521</v>
       </c>
       <c r="W99" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13509,7 +13512,7 @@
         <v>1522</v>
       </c>
       <c r="W100" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13571,16 +13574,16 @@
         <v>1523</v>
       </c>
       <c r="W101" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X101" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="Y101" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z101" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13642,7 +13645,7 @@
         <v>1524</v>
       </c>
       <c r="W102" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13704,7 +13707,7 @@
         <v>1524</v>
       </c>
       <c r="W103" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13766,7 +13769,7 @@
         <v>1525</v>
       </c>
       <c r="W104" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -13828,16 +13831,16 @@
         <v>1526</v>
       </c>
       <c r="W105" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X105" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="Y105" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z105" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -13899,16 +13902,16 @@
         <v>1527</v>
       </c>
       <c r="W106" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X106" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="Y106" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z106" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -13970,7 +13973,7 @@
         <v>1528</v>
       </c>
       <c r="W107" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14032,16 +14035,16 @@
         <v>1529</v>
       </c>
       <c r="W108" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X108" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="Y108" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z108" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14103,16 +14106,16 @@
         <v>1530</v>
       </c>
       <c r="W109" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X109" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="Y109" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z109" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14171,7 +14174,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14233,16 +14236,16 @@
         <v>1531</v>
       </c>
       <c r="W111" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X111" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="Y111" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z111" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14304,16 +14307,16 @@
         <v>1532</v>
       </c>
       <c r="W112" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X112" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="Y112" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z112" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14375,16 +14378,16 @@
         <v>1533</v>
       </c>
       <c r="W113" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X113" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="Y113" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z113" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14446,16 +14449,16 @@
         <v>1534</v>
       </c>
       <c r="W114" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X114" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="Y114" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z114" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14517,16 +14520,16 @@
         <v>1530</v>
       </c>
       <c r="W115" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X115" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="Y115" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z115" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14588,16 +14591,16 @@
         <v>1530</v>
       </c>
       <c r="W116" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X116" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="Y116" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z116" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14659,16 +14662,16 @@
         <v>1535</v>
       </c>
       <c r="W117" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X117" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="Y117" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z117" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14730,16 +14733,16 @@
         <v>1536</v>
       </c>
       <c r="W118" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X118" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="Y118" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z118" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -14801,7 +14804,7 @@
         <v>1537</v>
       </c>
       <c r="W119" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -14863,16 +14866,16 @@
         <v>1538</v>
       </c>
       <c r="W120" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X120" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y120" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z120" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -14934,16 +14937,16 @@
         <v>1538</v>
       </c>
       <c r="W121" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X121" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y121" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z121" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15005,16 +15008,16 @@
         <v>1538</v>
       </c>
       <c r="W122" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X122" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y122" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z122" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15076,16 +15079,16 @@
         <v>1538</v>
       </c>
       <c r="W123" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X123" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y123" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z123" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15147,16 +15150,16 @@
         <v>1538</v>
       </c>
       <c r="W124" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X124" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y124" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z124" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15218,16 +15221,16 @@
         <v>1538</v>
       </c>
       <c r="W125" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X125" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y125" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z125" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15289,16 +15292,16 @@
         <v>1538</v>
       </c>
       <c r="W126" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X126" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y126" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z126" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15360,16 +15363,16 @@
         <v>1539</v>
       </c>
       <c r="W127" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X127" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="Y127" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z127" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15431,16 +15434,16 @@
         <v>1540</v>
       </c>
       <c r="W128" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X128" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="Y128" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z128" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15502,16 +15505,16 @@
         <v>1538</v>
       </c>
       <c r="W129" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X129" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y129" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z129" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15573,16 +15576,16 @@
         <v>1538</v>
       </c>
       <c r="W130" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X130" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y130" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z130" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15644,7 +15647,7 @@
         <v>1541</v>
       </c>
       <c r="W131" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15703,7 +15706,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15762,7 +15765,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -15824,16 +15827,16 @@
         <v>1538</v>
       </c>
       <c r="W134" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X134" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y134" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z134" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -15895,16 +15898,16 @@
         <v>1538</v>
       </c>
       <c r="W135" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X135" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y135" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z135" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -15966,7 +15969,7 @@
         <v>1537</v>
       </c>
       <c r="W136" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16025,7 +16028,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16087,16 +16090,16 @@
         <v>1542</v>
       </c>
       <c r="W138" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X138" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="Y138" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z138" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16158,16 +16161,16 @@
         <v>1530</v>
       </c>
       <c r="W139" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X139" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="Y139" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z139" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16229,16 +16232,16 @@
         <v>1538</v>
       </c>
       <c r="W140" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X140" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y140" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z140" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16297,7 +16300,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16356,7 +16359,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16418,16 +16421,16 @@
         <v>1543</v>
       </c>
       <c r="W143" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X143" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="Y143" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z143" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16489,16 +16492,16 @@
         <v>1544</v>
       </c>
       <c r="W144" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X144" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="Y144" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z144" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16560,16 +16563,16 @@
         <v>1545</v>
       </c>
       <c r="W145" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X145" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="Y145" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z145" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16631,16 +16634,16 @@
         <v>1546</v>
       </c>
       <c r="W146" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X146" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="Y146" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z146" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16699,7 +16702,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16761,7 +16764,7 @@
         <v>1547</v>
       </c>
       <c r="W148" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -16823,16 +16826,16 @@
         <v>1548</v>
       </c>
       <c r="W149" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X149" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y149" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z149" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -16894,7 +16897,7 @@
         <v>1549</v>
       </c>
       <c r="W150" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -16956,16 +16959,16 @@
         <v>1550</v>
       </c>
       <c r="W151" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X151" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="Y151" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z151" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17027,7 +17030,7 @@
         <v>1549</v>
       </c>
       <c r="W152" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17089,7 +17092,7 @@
         <v>1547</v>
       </c>
       <c r="W153" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17151,7 +17154,7 @@
         <v>1549</v>
       </c>
       <c r="W154" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17213,7 +17216,7 @@
         <v>1549</v>
       </c>
       <c r="W155" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17275,16 +17278,16 @@
         <v>1551</v>
       </c>
       <c r="W156" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X156" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="Y156" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z156" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17346,7 +17349,7 @@
         <v>1547</v>
       </c>
       <c r="W157" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17408,16 +17411,16 @@
         <v>1552</v>
       </c>
       <c r="W158" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X158" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Y158" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z158" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17479,16 +17482,16 @@
         <v>1553</v>
       </c>
       <c r="W159" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X159" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="Y159" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z159" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17550,16 +17553,16 @@
         <v>1552</v>
       </c>
       <c r="W160" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X160" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Y160" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z160" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17621,16 +17624,16 @@
         <v>1552</v>
       </c>
       <c r="W161" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X161" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Y161" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z161" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17692,16 +17695,16 @@
         <v>1552</v>
       </c>
       <c r="W162" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X162" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Y162" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z162" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17763,16 +17766,16 @@
         <v>1554</v>
       </c>
       <c r="W163" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X163" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="Y163" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z163" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -17834,16 +17837,16 @@
         <v>1555</v>
       </c>
       <c r="W164" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X164" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="Y164" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z164" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -17905,16 +17908,16 @@
         <v>1556</v>
       </c>
       <c r="W165" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X165" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="Y165" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z165" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -17976,16 +17979,16 @@
         <v>1557</v>
       </c>
       <c r="W166" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X166" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="Y166" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z166" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18047,16 +18050,16 @@
         <v>1535</v>
       </c>
       <c r="W167" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X167" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="Y167" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z167" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18118,16 +18121,16 @@
         <v>1538</v>
       </c>
       <c r="W168" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X168" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y168" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z168" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18189,7 +18192,7 @@
         <v>1558</v>
       </c>
       <c r="W169" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18251,16 +18254,16 @@
         <v>1538</v>
       </c>
       <c r="W170" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X170" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y170" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z170" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18322,16 +18325,16 @@
         <v>1559</v>
       </c>
       <c r="W171" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X171" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Y171" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z171" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18393,16 +18396,16 @@
         <v>1560</v>
       </c>
       <c r="W172" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X172" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="Y172" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z172" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18464,16 +18467,16 @@
         <v>1561</v>
       </c>
       <c r="W173" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X173" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="Y173" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z173" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18535,16 +18538,16 @@
         <v>1562</v>
       </c>
       <c r="W174" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X174" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y174" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z174" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18606,16 +18609,16 @@
         <v>1563</v>
       </c>
       <c r="W175" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X175" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="Y175" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z175" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18677,16 +18680,16 @@
         <v>1564</v>
       </c>
       <c r="W176" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X176" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="Y176" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z176" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18748,7 +18751,7 @@
         <v>1558</v>
       </c>
       <c r="W177" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -18810,16 +18813,16 @@
         <v>1565</v>
       </c>
       <c r="W178" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X178" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="Y178" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z178" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -18881,16 +18884,16 @@
         <v>1566</v>
       </c>
       <c r="W179" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X179" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Y179" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z179" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -18952,7 +18955,7 @@
         <v>1567</v>
       </c>
       <c r="W180" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19014,16 +19017,16 @@
         <v>1568</v>
       </c>
       <c r="W181" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X181" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="Y181" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z181" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19085,16 +19088,16 @@
         <v>1568</v>
       </c>
       <c r="W182" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X182" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="Y182" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z182" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19156,16 +19159,16 @@
         <v>1569</v>
       </c>
       <c r="W183" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X183" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="Y183" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z183" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19227,16 +19230,16 @@
         <v>1570</v>
       </c>
       <c r="W184" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X184" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="Y184" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z184" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19298,16 +19301,16 @@
         <v>1571</v>
       </c>
       <c r="W185" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X185" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="Y185" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z185" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19369,7 +19372,7 @@
         <v>1572</v>
       </c>
       <c r="W186" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19431,7 +19434,7 @@
         <v>1573</v>
       </c>
       <c r="W187" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19493,7 +19496,7 @@
         <v>1574</v>
       </c>
       <c r="W188" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19555,7 +19558,7 @@
         <v>1575</v>
       </c>
       <c r="W189" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19617,16 +19620,16 @@
         <v>1576</v>
       </c>
       <c r="W190" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X190" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="Y190" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z190" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19688,16 +19691,16 @@
         <v>1577</v>
       </c>
       <c r="W191" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X191" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="Y191" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z191" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19759,7 +19762,7 @@
         <v>1578</v>
       </c>
       <c r="W192" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -19821,7 +19824,7 @@
         <v>1578</v>
       </c>
       <c r="W193" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -19883,16 +19886,16 @@
         <v>1579</v>
       </c>
       <c r="W194" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X194" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="Y194" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z194" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -19954,16 +19957,16 @@
         <v>1580</v>
       </c>
       <c r="W195" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X195" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="Y195" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z195" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20025,16 +20028,16 @@
         <v>1581</v>
       </c>
       <c r="W196" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X196" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="Y196" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z196" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20096,16 +20099,16 @@
         <v>1577</v>
       </c>
       <c r="W197" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X197" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="Y197" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z197" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20167,7 +20170,7 @@
         <v>1582</v>
       </c>
       <c r="W198" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20229,7 +20232,7 @@
         <v>1583</v>
       </c>
       <c r="W199" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20291,16 +20294,16 @@
         <v>1584</v>
       </c>
       <c r="W200" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X200" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="Y200" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z200" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20362,16 +20365,16 @@
         <v>1584</v>
       </c>
       <c r="W201" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X201" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="Y201" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z201" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20433,16 +20436,16 @@
         <v>1585</v>
       </c>
       <c r="W202" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X202" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="Y202" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z202" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20504,16 +20507,16 @@
         <v>1586</v>
       </c>
       <c r="W203" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X203" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="Y203" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z203" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20575,16 +20578,16 @@
         <v>1587</v>
       </c>
       <c r="W204" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X204" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="Y204" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z204" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20646,16 +20649,16 @@
         <v>1588</v>
       </c>
       <c r="W205" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X205" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="Y205" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z205" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20717,16 +20720,16 @@
         <v>1589</v>
       </c>
       <c r="W206" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X206" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="Y206" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z206" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -20788,16 +20791,16 @@
         <v>1590</v>
       </c>
       <c r="W207" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X207" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="Y207" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z207" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -20859,16 +20862,16 @@
         <v>1591</v>
       </c>
       <c r="W208" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X208" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="Y208" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z208" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -20930,7 +20933,7 @@
         <v>1592</v>
       </c>
       <c r="W209" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -20992,16 +20995,16 @@
         <v>1593</v>
       </c>
       <c r="W210" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X210" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="Y210" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z210" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21063,16 +21066,16 @@
         <v>1594</v>
       </c>
       <c r="W211" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X211" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="Y211" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z211" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21134,16 +21137,16 @@
         <v>1595</v>
       </c>
       <c r="W212" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X212" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Y212" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z212" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21205,16 +21208,16 @@
         <v>1596</v>
       </c>
       <c r="W213" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X213" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="Y213" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z213" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21276,7 +21279,7 @@
         <v>1597</v>
       </c>
       <c r="W214" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21338,16 +21341,16 @@
         <v>1562</v>
       </c>
       <c r="W215" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X215" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y215" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z215" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21409,16 +21412,16 @@
         <v>1598</v>
       </c>
       <c r="W216" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X216" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="Y216" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z216" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21480,7 +21483,7 @@
         <v>1599</v>
       </c>
       <c r="W217" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21542,16 +21545,16 @@
         <v>1600</v>
       </c>
       <c r="W218" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X218" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="Y218" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z218" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21613,16 +21616,16 @@
         <v>1601</v>
       </c>
       <c r="W219" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X219" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="Y219" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z219" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21684,7 +21687,7 @@
         <v>1602</v>
       </c>
       <c r="W220" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21746,7 +21749,7 @@
         <v>1603</v>
       </c>
       <c r="W221" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -21808,7 +21811,7 @@
         <v>1602</v>
       </c>
       <c r="W222" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -21870,7 +21873,7 @@
         <v>1603</v>
       </c>
       <c r="W223" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -21932,16 +21935,16 @@
         <v>1604</v>
       </c>
       <c r="W224" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X224" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="Y224" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z224" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22003,16 +22006,16 @@
         <v>1605</v>
       </c>
       <c r="W225" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X225" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="Y225" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z225" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22074,7 +22077,7 @@
         <v>1606</v>
       </c>
       <c r="W226" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22136,7 +22139,7 @@
         <v>1607</v>
       </c>
       <c r="W227" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22198,7 +22201,7 @@
         <v>1608</v>
       </c>
       <c r="W228" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22260,16 +22263,16 @@
         <v>1609</v>
       </c>
       <c r="W229" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X229" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="Y229" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z229" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22331,16 +22334,16 @@
         <v>1610</v>
       </c>
       <c r="W230" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X230" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="Y230" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z230" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22402,16 +22405,16 @@
         <v>1611</v>
       </c>
       <c r="W231" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X231" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="Y231" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z231" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22476,16 +22479,16 @@
         <v>1612</v>
       </c>
       <c r="W232" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X232" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="Y232" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z232" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22547,16 +22550,16 @@
         <v>1613</v>
       </c>
       <c r="W233" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X233" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="Y233" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z233" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22618,16 +22621,16 @@
         <v>1614</v>
       </c>
       <c r="W234" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X234" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y234" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z234" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22689,16 +22692,16 @@
         <v>1614</v>
       </c>
       <c r="W235" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X235" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y235" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z235" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22760,16 +22763,16 @@
         <v>1615</v>
       </c>
       <c r="W236" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X236" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y236" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z236" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -22831,7 +22834,7 @@
         <v>1616</v>
       </c>
       <c r="W237" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -22893,7 +22896,7 @@
         <v>1617</v>
       </c>
       <c r="W238" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -22955,16 +22958,16 @@
         <v>1618</v>
       </c>
       <c r="W239" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X239" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="Y239" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z239" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23026,16 +23029,16 @@
         <v>1619</v>
       </c>
       <c r="W240" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X240" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="Y240" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z240" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23097,7 +23100,7 @@
         <v>1620</v>
       </c>
       <c r="W241" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23159,16 +23162,16 @@
         <v>1621</v>
       </c>
       <c r="W242" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X242" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="Y242" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z242" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23230,16 +23233,16 @@
         <v>1622</v>
       </c>
       <c r="W243" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X243" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="Y243" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z243" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23301,16 +23304,16 @@
         <v>1621</v>
       </c>
       <c r="W244" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X244" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="Y244" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z244" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23372,16 +23375,16 @@
         <v>1623</v>
       </c>
       <c r="W245" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X245" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y245" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z245" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23443,16 +23446,16 @@
         <v>1622</v>
       </c>
       <c r="W246" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X246" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="Y246" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z246" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23514,16 +23517,16 @@
         <v>1623</v>
       </c>
       <c r="W247" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X247" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y247" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z247" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23585,16 +23588,16 @@
         <v>1624</v>
       </c>
       <c r="W248" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X248" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="Y248" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z248" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23656,16 +23659,16 @@
         <v>1614</v>
       </c>
       <c r="W249" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X249" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y249" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z249" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23727,7 +23730,7 @@
         <v>1625</v>
       </c>
       <c r="W250" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -23789,7 +23792,7 @@
         <v>1626</v>
       </c>
       <c r="W251" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -23851,16 +23854,16 @@
         <v>1627</v>
       </c>
       <c r="W252" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X252" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="Y252" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z252" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -23922,16 +23925,16 @@
         <v>1628</v>
       </c>
       <c r="W253" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X253" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Y253" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z253" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -23993,7 +23996,7 @@
         <v>1629</v>
       </c>
       <c r="W254" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24055,16 +24058,16 @@
         <v>1630</v>
       </c>
       <c r="W255" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X255" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="Y255" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z255" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24126,7 +24129,7 @@
         <v>1631</v>
       </c>
       <c r="W256" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24191,7 +24194,7 @@
         <v>1632</v>
       </c>
       <c r="W257" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24253,7 +24256,7 @@
         <v>1633</v>
       </c>
       <c r="W258" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24315,7 +24318,7 @@
         <v>1633</v>
       </c>
       <c r="W259" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24377,7 +24380,7 @@
         <v>1634</v>
       </c>
       <c r="W260" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24439,16 +24442,16 @@
         <v>1635</v>
       </c>
       <c r="W261" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X261" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="Y261" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z261" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24510,13 +24513,13 @@
         <v>1636</v>
       </c>
       <c r="W262" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X262" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="Y262" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24578,16 +24581,16 @@
         <v>1637</v>
       </c>
       <c r="W263" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X263" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y263" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z263" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24649,7 +24652,7 @@
         <v>1638</v>
       </c>
       <c r="W264" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24711,7 +24714,7 @@
         <v>1638</v>
       </c>
       <c r="W265" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24773,7 +24776,7 @@
         <v>1639</v>
       </c>
       <c r="W266" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -24835,16 +24838,16 @@
         <v>1640</v>
       </c>
       <c r="W267" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X267" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="Y267" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z267" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -24906,16 +24909,16 @@
         <v>1641</v>
       </c>
       <c r="W268" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X268" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="Y268" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z268" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -24977,7 +24980,7 @@
         <v>1482</v>
       </c>
       <c r="W269" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25039,7 +25042,7 @@
         <v>1642</v>
       </c>
       <c r="W270" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25101,7 +25104,7 @@
         <v>1643</v>
       </c>
       <c r="W271" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25163,16 +25166,16 @@
         <v>1644</v>
       </c>
       <c r="W272" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X272" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="Y272" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z272" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25231,7 +25234,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25293,7 +25296,7 @@
         <v>1645</v>
       </c>
       <c r="W274" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25352,7 +25355,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25414,7 +25417,7 @@
         <v>1646</v>
       </c>
       <c r="W276" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25476,7 +25479,7 @@
         <v>1647</v>
       </c>
       <c r="W277" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25538,16 +25541,16 @@
         <v>1648</v>
       </c>
       <c r="W278" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X278" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="Y278" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z278" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25609,16 +25612,16 @@
         <v>1649</v>
       </c>
       <c r="W279" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X279" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="Y279" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z279" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25680,16 +25683,16 @@
         <v>1649</v>
       </c>
       <c r="W280" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X280" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="Y280" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z280" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25751,16 +25754,16 @@
         <v>1650</v>
       </c>
       <c r="W281" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X281" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="Y281" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z281" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -25822,7 +25825,7 @@
         <v>1651</v>
       </c>
       <c r="W282" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -25884,7 +25887,7 @@
         <v>1652</v>
       </c>
       <c r="W283" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -25946,7 +25949,7 @@
         <v>1653</v>
       </c>
       <c r="W284" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26008,16 +26011,16 @@
         <v>1654</v>
       </c>
       <c r="W285" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X285" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="Y285" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z285" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26079,7 +26082,7 @@
         <v>1655</v>
       </c>
       <c r="W286" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26141,16 +26144,16 @@
         <v>1649</v>
       </c>
       <c r="W287" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X287" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="Y287" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z287" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26212,16 +26215,16 @@
         <v>1656</v>
       </c>
       <c r="W288" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X288" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y288" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z288" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26283,7 +26286,7 @@
         <v>1657</v>
       </c>
       <c r="W289" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26345,16 +26348,16 @@
         <v>1658</v>
       </c>
       <c r="W290" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X290" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="Y290" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z290" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26416,16 +26419,16 @@
         <v>1659</v>
       </c>
       <c r="W291" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X291" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="Y291" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z291" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26487,7 +26490,7 @@
         <v>1660</v>
       </c>
       <c r="W292" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26546,7 +26549,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26608,7 +26611,7 @@
         <v>1661</v>
       </c>
       <c r="W294" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26670,7 +26673,7 @@
         <v>1662</v>
       </c>
       <c r="W295" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26732,7 +26735,7 @@
         <v>1663</v>
       </c>
       <c r="W296" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -26794,13 +26797,13 @@
         <v>1664</v>
       </c>
       <c r="W297" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X297" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="Z297" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -26862,7 +26865,7 @@
         <v>1665</v>
       </c>
       <c r="W298" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -26924,7 +26927,7 @@
         <v>1666</v>
       </c>
       <c r="W299" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -26986,7 +26989,7 @@
         <v>1667</v>
       </c>
       <c r="W300" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27048,7 +27051,7 @@
         <v>1668</v>
       </c>
       <c r="W301" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27110,7 +27113,7 @@
         <v>1669</v>
       </c>
       <c r="W302" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27172,16 +27175,16 @@
         <v>1670</v>
       </c>
       <c r="W303" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X303" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="Y303" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z303" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27243,7 +27246,7 @@
         <v>1671</v>
       </c>
       <c r="W304" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27305,7 +27308,7 @@
         <v>1672</v>
       </c>
       <c r="W305" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27367,7 +27370,7 @@
         <v>1673</v>
       </c>
       <c r="W306" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27429,7 +27432,7 @@
         <v>1674</v>
       </c>
       <c r="W307" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27491,7 +27494,7 @@
         <v>1667</v>
       </c>
       <c r="W308" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27553,7 +27556,7 @@
         <v>1675</v>
       </c>
       <c r="W309" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27615,7 +27618,7 @@
         <v>1676</v>
       </c>
       <c r="W310" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27677,7 +27680,7 @@
         <v>1677</v>
       </c>
       <c r="W311" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27739,7 +27742,7 @@
         <v>1678</v>
       </c>
       <c r="W312" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -27801,7 +27804,7 @@
         <v>1679</v>
       </c>
       <c r="W313" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -27863,7 +27866,7 @@
         <v>1680</v>
       </c>
       <c r="W314" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -27925,7 +27928,7 @@
         <v>1681</v>
       </c>
       <c r="W315" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -27987,7 +27990,7 @@
         <v>1682</v>
       </c>
       <c r="W316" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28049,7 +28052,7 @@
         <v>1683</v>
       </c>
       <c r="W317" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28111,7 +28114,7 @@
         <v>1684</v>
       </c>
       <c r="W318" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28173,7 +28176,7 @@
         <v>1685</v>
       </c>
       <c r="W319" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28232,13 +28235,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X320" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Z320" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28297,7 +28300,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28356,7 +28359,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28415,7 +28418,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28477,7 +28480,7 @@
         <v>1686</v>
       </c>
       <c r="W324" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28539,7 +28542,7 @@
         <v>1687</v>
       </c>
       <c r="W325" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28601,7 +28604,7 @@
         <v>1688</v>
       </c>
       <c r="W326" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28663,7 +28666,7 @@
         <v>1689</v>
       </c>
       <c r="W327" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28722,7 +28725,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -28784,7 +28787,7 @@
         <v>1689</v>
       </c>
       <c r="W329" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -28846,7 +28849,7 @@
         <v>1690</v>
       </c>
       <c r="W330" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -28908,7 +28911,7 @@
         <v>1691</v>
       </c>
       <c r="W331" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -28970,7 +28973,7 @@
         <v>1691</v>
       </c>
       <c r="W332" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29032,7 +29035,7 @@
         <v>1692</v>
       </c>
       <c r="W333" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29094,7 +29097,7 @@
         <v>1693</v>
       </c>
       <c r="W334" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29156,7 +29159,7 @@
         <v>1694</v>
       </c>
       <c r="W335" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29215,13 +29218,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X336" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Z336" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29283,7 +29286,7 @@
         <v>1695</v>
       </c>
       <c r="W337" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29345,13 +29348,13 @@
         <v>1696</v>
       </c>
       <c r="W338" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X338" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="Z338" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29413,13 +29416,13 @@
         <v>1697</v>
       </c>
       <c r="W339" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X339" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="Z339" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29481,7 +29484,7 @@
         <v>1698</v>
       </c>
       <c r="W340" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29543,7 +29546,7 @@
         <v>1699</v>
       </c>
       <c r="W341" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29605,10 +29608,10 @@
         <v>1700</v>
       </c>
       <c r="W342" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X342" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29670,7 +29673,7 @@
         <v>1701</v>
       </c>
       <c r="W343" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29732,7 +29735,7 @@
         <v>1702</v>
       </c>
       <c r="W344" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -29794,13 +29797,13 @@
         <v>1703</v>
       </c>
       <c r="W345" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X345" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Z345" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -29862,7 +29865,7 @@
         <v>1667</v>
       </c>
       <c r="W346" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -29924,7 +29927,7 @@
         <v>1704</v>
       </c>
       <c r="W347" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -29986,16 +29989,16 @@
         <v>1705</v>
       </c>
       <c r="W348" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X348" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y348" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z348" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30060,13 +30063,13 @@
         <v>1706</v>
       </c>
       <c r="W349" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X349" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Z349" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30128,7 +30131,7 @@
         <v>1707</v>
       </c>
       <c r="W350" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30190,16 +30193,16 @@
         <v>1708</v>
       </c>
       <c r="W351" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X351" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="Y351" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z351" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30261,13 +30264,13 @@
         <v>1709</v>
       </c>
       <c r="W352" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X352" t="s">
         <v>1709</v>
       </c>
       <c r="Z352" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30329,16 +30332,16 @@
         <v>1710</v>
       </c>
       <c r="W353" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X353" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="Y353" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z353" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30400,7 +30403,7 @@
         <v>1711</v>
       </c>
       <c r="W354" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30462,7 +30465,7 @@
         <v>1712</v>
       </c>
       <c r="W355" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30521,7 +30524,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30580,7 +30583,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30639,7 +30642,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30701,7 +30704,7 @@
         <v>1713</v>
       </c>
       <c r="W359" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30766,7 +30769,7 @@
         <v>1714</v>
       </c>
       <c r="W360" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -30831,7 +30834,7 @@
         <v>1715</v>
       </c>
       <c r="W361" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -30893,16 +30896,16 @@
         <v>1716</v>
       </c>
       <c r="W362" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X362" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="Y362" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z362" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -30964,16 +30967,16 @@
         <v>1717</v>
       </c>
       <c r="W363" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X363" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="Y363" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z363" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31035,7 +31038,7 @@
         <v>1718</v>
       </c>
       <c r="W364" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31097,7 +31100,7 @@
         <v>1719</v>
       </c>
       <c r="W365" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31162,7 +31165,7 @@
         <v>1720</v>
       </c>
       <c r="W366" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31224,7 +31227,7 @@
         <v>1721</v>
       </c>
       <c r="W367" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31286,7 +31289,7 @@
         <v>1722</v>
       </c>
       <c r="W368" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31351,13 +31354,13 @@
         <v>1723</v>
       </c>
       <c r="W369" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X369" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="Z369" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31419,7 +31422,7 @@
         <v>1724</v>
       </c>
       <c r="W370" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31481,16 +31484,16 @@
         <v>1725</v>
       </c>
       <c r="W371" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X371" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="Y371" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z371" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31555,7 +31558,7 @@
         <v>1726</v>
       </c>
       <c r="W372" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31620,16 +31623,16 @@
         <v>1727</v>
       </c>
       <c r="W373" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X373" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="Y373" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z373" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31691,7 +31694,7 @@
         <v>1728</v>
       </c>
       <c r="W374" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31756,7 +31759,7 @@
         <v>1729</v>
       </c>
       <c r="W375" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -31821,7 +31824,7 @@
         <v>1730</v>
       </c>
       <c r="W376" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -31886,7 +31889,7 @@
         <v>1730</v>
       </c>
       <c r="W377" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -31951,13 +31954,13 @@
         <v>1731</v>
       </c>
       <c r="W378" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X378" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="Z378" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32019,16 +32022,16 @@
         <v>1732</v>
       </c>
       <c r="W379" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X379" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="Y379" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z379" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32093,7 +32096,7 @@
         <v>1733</v>
       </c>
       <c r="W380" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32155,7 +32158,7 @@
         <v>1734</v>
       </c>
       <c r="W381" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32220,7 +32223,7 @@
         <v>1735</v>
       </c>
       <c r="W382" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32282,7 +32285,7 @@
         <v>1736</v>
       </c>
       <c r="W383" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32347,7 +32350,7 @@
         <v>1735</v>
       </c>
       <c r="W384" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32409,16 +32412,16 @@
         <v>1737</v>
       </c>
       <c r="W385" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X385" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Y385" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z385" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32486,7 +32489,7 @@
         <v>1738</v>
       </c>
       <c r="W386" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32548,7 +32551,7 @@
         <v>1739</v>
       </c>
       <c r="W387" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32610,7 +32613,7 @@
         <v>1740</v>
       </c>
       <c r="W388" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32672,16 +32675,16 @@
         <v>1741</v>
       </c>
       <c r="W389" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X389" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="Y389" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z389" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32746,16 +32749,16 @@
         <v>1742</v>
       </c>
       <c r="W390" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X390" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y390" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z390" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -32820,7 +32823,7 @@
         <v>1743</v>
       </c>
       <c r="W391" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -32882,7 +32885,7 @@
         <v>1744</v>
       </c>
       <c r="W392" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -32944,16 +32947,16 @@
         <v>1745</v>
       </c>
       <c r="W393" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X393" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="Y393" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z393" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33015,7 +33018,7 @@
         <v>1746</v>
       </c>
       <c r="W394" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33080,16 +33083,16 @@
         <v>1747</v>
       </c>
       <c r="W395" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X395" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="Y395" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z395" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33154,13 +33157,13 @@
         <v>1748</v>
       </c>
       <c r="W396" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X396" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="Y396" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33222,7 +33225,7 @@
         <v>1749</v>
       </c>
       <c r="W397" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33284,7 +33287,7 @@
         <v>1750</v>
       </c>
       <c r="W398" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33349,7 +33352,7 @@
         <v>1751</v>
       </c>
       <c r="W399" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33414,16 +33417,16 @@
         <v>1752</v>
       </c>
       <c r="W400" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X400" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="Y400" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z400" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33488,7 +33491,7 @@
         <v>1753</v>
       </c>
       <c r="W401" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33553,7 +33556,7 @@
         <v>1754</v>
       </c>
       <c r="W402" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33618,16 +33621,16 @@
         <v>1755</v>
       </c>
       <c r="W403" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X403" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="Y403" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z403" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33692,7 +33695,7 @@
         <v>1756</v>
       </c>
       <c r="W404" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33757,7 +33760,7 @@
         <v>1757</v>
       </c>
       <c r="W405" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -33822,10 +33825,10 @@
         <v>1758</v>
       </c>
       <c r="V406" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="W406" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA406" t="b">
         <v>1</v>
@@ -33887,16 +33890,16 @@
         <v>1759</v>
       </c>
       <c r="W407" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X407" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="Y407" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z407" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -33961,13 +33964,13 @@
         <v>1760</v>
       </c>
       <c r="W408" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X408" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Z408" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34032,7 +34035,7 @@
         <v>1761</v>
       </c>
       <c r="W409" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34097,7 +34100,7 @@
         <v>1762</v>
       </c>
       <c r="W410" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34162,7 +34165,7 @@
         <v>1763</v>
       </c>
       <c r="W411" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34227,7 +34230,7 @@
         <v>1764</v>
       </c>
       <c r="W412" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34292,7 +34295,7 @@
         <v>1765</v>
       </c>
       <c r="W413" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34357,7 +34360,7 @@
         <v>1765</v>
       </c>
       <c r="W414" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34422,7 +34425,7 @@
         <v>1766</v>
       </c>
       <c r="W415" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34487,7 +34490,7 @@
         <v>1767</v>
       </c>
       <c r="W416" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34552,7 +34555,7 @@
         <v>1765</v>
       </c>
       <c r="W417" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34617,7 +34620,7 @@
         <v>1768</v>
       </c>
       <c r="W418" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34682,7 +34685,7 @@
         <v>1769</v>
       </c>
       <c r="W419" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34747,16 +34750,16 @@
         <v>1770</v>
       </c>
       <c r="W420" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X420" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Y420" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z420" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -34821,7 +34824,7 @@
         <v>1771</v>
       </c>
       <c r="W421" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -34886,7 +34889,7 @@
         <v>1772</v>
       </c>
       <c r="W422" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -34951,7 +34954,7 @@
         <v>1773</v>
       </c>
       <c r="W423" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35016,16 +35019,16 @@
         <v>1774</v>
       </c>
       <c r="W424" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X424" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="Y424" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z424" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35090,7 +35093,7 @@
         <v>1773</v>
       </c>
       <c r="W425" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35155,7 +35158,7 @@
         <v>1775</v>
       </c>
       <c r="W426" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35220,7 +35223,7 @@
         <v>1776</v>
       </c>
       <c r="W427" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35285,13 +35288,13 @@
         <v>1777</v>
       </c>
       <c r="W428" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X428" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="Y428" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35356,16 +35359,16 @@
         <v>1778</v>
       </c>
       <c r="W429" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X429" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="Y429" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z429" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35430,7 +35433,7 @@
         <v>1779</v>
       </c>
       <c r="W430" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35495,16 +35498,16 @@
         <v>1780</v>
       </c>
       <c r="W431" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X431" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="Y431" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z431" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35569,7 +35572,7 @@
         <v>1781</v>
       </c>
       <c r="W432" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35634,7 +35637,7 @@
         <v>1782</v>
       </c>
       <c r="W433" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35699,7 +35702,7 @@
         <v>1783</v>
       </c>
       <c r="W434" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35764,7 +35767,7 @@
         <v>1784</v>
       </c>
       <c r="W435" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -35829,7 +35832,7 @@
         <v>1785</v>
       </c>
       <c r="W436" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -35894,7 +35897,7 @@
         <v>1786</v>
       </c>
       <c r="W437" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -35959,7 +35962,7 @@
         <v>1787</v>
       </c>
       <c r="W438" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36024,7 +36027,7 @@
         <v>1788</v>
       </c>
       <c r="W439" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36089,16 +36092,16 @@
         <v>1789</v>
       </c>
       <c r="W440" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X440" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Y440" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z440" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36163,16 +36166,16 @@
         <v>1790</v>
       </c>
       <c r="W441" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X441" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y441" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z441" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36237,16 +36240,16 @@
         <v>1791</v>
       </c>
       <c r="W442" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X442" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="Y442" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z442" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36311,7 +36314,7 @@
         <v>1792</v>
       </c>
       <c r="W443" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36376,7 +36379,7 @@
         <v>1793</v>
       </c>
       <c r="W444" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36441,16 +36444,16 @@
         <v>1790</v>
       </c>
       <c r="W445" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X445" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y445" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z445" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36515,16 +36518,16 @@
         <v>1790</v>
       </c>
       <c r="W446" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X446" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y446" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z446" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36589,16 +36592,16 @@
         <v>1794</v>
       </c>
       <c r="W447" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X447" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="Y447" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z447" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36663,16 +36666,16 @@
         <v>1790</v>
       </c>
       <c r="W448" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X448" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y448" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z448" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36737,16 +36740,16 @@
         <v>1790</v>
       </c>
       <c r="W449" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X449" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y449" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z449" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -36811,16 +36814,16 @@
         <v>1795</v>
       </c>
       <c r="W450" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X450" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="Y450" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z450" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -36885,16 +36888,16 @@
         <v>1796</v>
       </c>
       <c r="W451" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X451" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="Y451" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z451" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -36959,7 +36962,7 @@
         <v>1797</v>
       </c>
       <c r="W452" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37024,16 +37027,16 @@
         <v>1798</v>
       </c>
       <c r="W453" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X453" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="Y453" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z453" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37098,16 +37101,16 @@
         <v>1799</v>
       </c>
       <c r="W454" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X454" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y454" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z454" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37172,16 +37175,16 @@
         <v>1800</v>
       </c>
       <c r="W455" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X455" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="Y455" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z455" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37246,16 +37249,16 @@
         <v>1801</v>
       </c>
       <c r="W456" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X456" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y456" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z456" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37320,7 +37323,7 @@
         <v>1802</v>
       </c>
       <c r="W457" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37385,7 +37388,7 @@
         <v>1802</v>
       </c>
       <c r="W458" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37450,16 +37453,16 @@
         <v>1800</v>
       </c>
       <c r="W459" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X459" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="Y459" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z459" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37524,16 +37527,16 @@
         <v>1803</v>
       </c>
       <c r="W460" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X460" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="Y460" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z460" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37598,16 +37601,16 @@
         <v>1804</v>
       </c>
       <c r="W461" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X461" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y461" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z461" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37672,7 +37675,7 @@
         <v>1805</v>
       </c>
       <c r="W462" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37737,16 +37740,16 @@
         <v>1806</v>
       </c>
       <c r="W463" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X463" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="Y463" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z463" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -37811,16 +37814,16 @@
         <v>1807</v>
       </c>
       <c r="W464" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X464" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="Y464" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z464" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -37885,16 +37888,16 @@
         <v>1808</v>
       </c>
       <c r="W465" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X465" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="Y465" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z465" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -37959,7 +37962,7 @@
         <v>1809</v>
       </c>
       <c r="W466" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38024,16 +38027,16 @@
         <v>1810</v>
       </c>
       <c r="W467" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X467" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="Y467" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z467" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38098,16 +38101,16 @@
         <v>1811</v>
       </c>
       <c r="W468" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X468" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="Y468" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z468" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38172,16 +38175,16 @@
         <v>1812</v>
       </c>
       <c r="W469" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X469" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="Y469" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z469" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38246,16 +38249,16 @@
         <v>1813</v>
       </c>
       <c r="W470" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X470" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y470" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z470" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38320,7 +38323,7 @@
         <v>1814</v>
       </c>
       <c r="W471" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38385,16 +38388,16 @@
         <v>1815</v>
       </c>
       <c r="W472" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X472" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="Y472" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z472" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38459,16 +38462,16 @@
         <v>1815</v>
       </c>
       <c r="W473" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X473" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="Y473" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z473" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38533,7 +38536,7 @@
         <v>1816</v>
       </c>
       <c r="W474" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38598,16 +38601,16 @@
         <v>1817</v>
       </c>
       <c r="W475" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X475" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="Y475" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z475" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38672,16 +38675,16 @@
         <v>1818</v>
       </c>
       <c r="W476" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X476" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="Y476" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z476" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38746,7 +38749,7 @@
         <v>1819</v>
       </c>
       <c r="W477" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -38811,7 +38814,7 @@
         <v>1820</v>
       </c>
       <c r="W478" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -38876,16 +38879,16 @@
         <v>1821</v>
       </c>
       <c r="W479" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X479" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="Y479" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z479" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -38950,16 +38953,16 @@
         <v>1822</v>
       </c>
       <c r="W480" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X480" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="Y480" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z480" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39024,16 +39027,16 @@
         <v>1823</v>
       </c>
       <c r="W481" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X481" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="Y481" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z481" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39098,7 +39101,7 @@
         <v>1824</v>
       </c>
       <c r="W482" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39163,7 +39166,7 @@
         <v>1825</v>
       </c>
       <c r="W483" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39231,13 +39234,13 @@
         <v>1826</v>
       </c>
       <c r="W484" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39302,7 +39305,7 @@
         <v>1827</v>
       </c>
       <c r="W485" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39370,13 +39373,13 @@
         <v>1828</v>
       </c>
       <c r="W486" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39441,7 +39444,7 @@
         <v>1829</v>
       </c>
       <c r="W487" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39506,16 +39509,16 @@
         <v>1830</v>
       </c>
       <c r="W488" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X488" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="Y488" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z488" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39580,7 +39583,7 @@
         <v>1831</v>
       </c>
       <c r="W489" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39648,13 +39651,13 @@
         <v>1832</v>
       </c>
       <c r="W490" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39719,16 +39722,16 @@
         <v>1833</v>
       </c>
       <c r="W491" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X491" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="Y491" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z491" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -39793,16 +39796,16 @@
         <v>1834</v>
       </c>
       <c r="W492" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X492" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="Y492" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z492" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -39867,16 +39870,16 @@
         <v>1835</v>
       </c>
       <c r="W493" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X493" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="Y493" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z493" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -39941,13 +39944,13 @@
         <v>1836</v>
       </c>
       <c r="W494" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X494" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="Y494" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40012,16 +40015,16 @@
         <v>1837</v>
       </c>
       <c r="W495" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X495" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="Y495" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z495" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40086,7 +40089,7 @@
         <v>1838</v>
       </c>
       <c r="W496" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40154,7 +40157,7 @@
         <v>1839</v>
       </c>
       <c r="W497" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40219,7 +40222,7 @@
         <v>1840</v>
       </c>
       <c r="W498" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40287,7 +40290,7 @@
         <v>1841</v>
       </c>
       <c r="W499" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40352,16 +40355,16 @@
         <v>1842</v>
       </c>
       <c r="W500" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X500" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="Y500" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z500" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40426,16 +40429,16 @@
         <v>1843</v>
       </c>
       <c r="W501" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X501" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Y501" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z501" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40500,7 +40503,7 @@
         <v>1844</v>
       </c>
       <c r="W502" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40568,7 +40571,7 @@
         <v>1845</v>
       </c>
       <c r="W503" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40636,16 +40639,16 @@
         <v>1846</v>
       </c>
       <c r="W504" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X504" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="Y504" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z504" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40710,7 +40713,7 @@
         <v>1847</v>
       </c>
       <c r="W505" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40775,16 +40778,16 @@
         <v>1848</v>
       </c>
       <c r="W506" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X506" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Y506" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z506" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -40849,7 +40852,7 @@
         <v>1849</v>
       </c>
       <c r="W507" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -40914,7 +40917,7 @@
         <v>1850</v>
       </c>
       <c r="W508" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -40979,16 +40982,16 @@
         <v>1851</v>
       </c>
       <c r="W509" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X509" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="Y509" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z509" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41053,16 +41056,16 @@
         <v>1852</v>
       </c>
       <c r="W510" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X510" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="Y510" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z510" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41130,7 +41133,7 @@
         <v>1853</v>
       </c>
       <c r="W511" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41198,7 +41201,7 @@
         <v>1854</v>
       </c>
       <c r="W512" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41266,7 +41269,7 @@
         <v>1855</v>
       </c>
       <c r="W513" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41334,7 +41337,7 @@
         <v>1855</v>
       </c>
       <c r="W514" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41402,7 +41405,7 @@
         <v>1855</v>
       </c>
       <c r="W515" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41470,13 +41473,13 @@
         <v>1856</v>
       </c>
       <c r="W516" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41544,13 +41547,13 @@
         <v>1857</v>
       </c>
       <c r="W517" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41618,16 +41621,16 @@
         <v>1858</v>
       </c>
       <c r="W518" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X518" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="Y518" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z518" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41695,16 +41698,16 @@
         <v>1859</v>
       </c>
       <c r="W519" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X519" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="Y519" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z519" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41769,7 +41772,7 @@
         <v>1462</v>
       </c>
       <c r="W520" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -41837,7 +41840,7 @@
         <v>1860</v>
       </c>
       <c r="W521" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -41905,7 +41908,7 @@
         <v>1860</v>
       </c>
       <c r="W522" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -41973,7 +41976,7 @@
         <v>1861</v>
       </c>
       <c r="W523" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42041,7 +42044,7 @@
         <v>1862</v>
       </c>
       <c r="W524" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42109,7 +42112,7 @@
         <v>1863</v>
       </c>
       <c r="W525" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42177,7 +42180,7 @@
         <v>1864</v>
       </c>
       <c r="W526" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42245,7 +42248,7 @@
         <v>1865</v>
       </c>
       <c r="W527" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42310,7 +42313,7 @@
         <v>1866</v>
       </c>
       <c r="W528" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42378,7 +42381,7 @@
         <v>1867</v>
       </c>
       <c r="W529" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42446,16 +42449,16 @@
         <v>1868</v>
       </c>
       <c r="W530" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X530" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="Y530" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z530" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42523,7 +42526,7 @@
         <v>1869</v>
       </c>
       <c r="W531" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42588,7 +42591,7 @@
         <v>1870</v>
       </c>
       <c r="W532" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42656,16 +42659,16 @@
         <v>1871</v>
       </c>
       <c r="W533" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X533" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="Y533" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z533" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42733,13 +42736,13 @@
         <v>1872</v>
       </c>
       <c r="W534" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -42807,7 +42810,7 @@
         <v>1873</v>
       </c>
       <c r="W535" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -42872,7 +42875,7 @@
         <v>1874</v>
       </c>
       <c r="W536" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -42940,16 +42943,16 @@
         <v>1875</v>
       </c>
       <c r="W537" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X537" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="Y537" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z537" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43017,7 +43020,7 @@
         <v>1876</v>
       </c>
       <c r="W538" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43085,10 +43088,10 @@
         <v>1877</v>
       </c>
       <c r="V539" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="W539" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA539" t="b">
         <v>1</v>
@@ -43153,7 +43156,7 @@
         <v>1878</v>
       </c>
       <c r="W540" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43221,7 +43224,7 @@
         <v>1879</v>
       </c>
       <c r="W541" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43289,16 +43292,16 @@
         <v>1880</v>
       </c>
       <c r="W542" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X542" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="Y542" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z542" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43366,7 +43369,7 @@
         <v>1881</v>
       </c>
       <c r="W543" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43434,16 +43437,16 @@
         <v>1882</v>
       </c>
       <c r="W544" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="X544" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="Y544" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z544" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43511,7 +43514,7 @@
         <v>1883</v>
       </c>
       <c r="W545" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43579,7 +43582,7 @@
         <v>1884</v>
       </c>
       <c r="W546" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43647,7 +43650,7 @@
         <v>1885</v>
       </c>
       <c r="W547" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43715,7 +43718,7 @@
         <v>1886</v>
       </c>
       <c r="W548" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -43783,7 +43786,7 @@
         <v>1886</v>
       </c>
       <c r="W549" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -43851,7 +43854,7 @@
         <v>1887</v>
       </c>
       <c r="W550" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -43916,7 +43919,7 @@
         <v>1888</v>
       </c>
       <c r="W551" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -43984,7 +43987,7 @@
         <v>1889</v>
       </c>
       <c r="W552" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44049,7 +44052,7 @@
         <v>1890</v>
       </c>
       <c r="W553" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44120,10 +44123,10 @@
         <v>1891</v>
       </c>
       <c r="V554" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="W554" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44191,7 +44194,7 @@
         <v>1892</v>
       </c>
       <c r="W555" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44259,10 +44262,10 @@
         <v>1893</v>
       </c>
       <c r="V556" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="W556" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA556" t="b">
         <v>1</v>
@@ -44324,10 +44327,10 @@
         <v>1459</v>
       </c>
       <c r="V557" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="W557" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA557" t="b">
         <v>1</v>
@@ -44395,10 +44398,10 @@
         <v>1894</v>
       </c>
       <c r="V558" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="W558" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA558" t="b">
         <v>1</v>
@@ -44469,10 +44472,10 @@
         <v>1895</v>
       </c>
       <c r="V559" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="W559" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44537,10 +44540,10 @@
         <v>1896</v>
       </c>
       <c r="V560" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="W560" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA560" t="b">
         <v>1</v>
@@ -44608,10 +44611,10 @@
         <v>1897</v>
       </c>
       <c r="V561" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="W561" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA561" t="b">
         <v>1</v>
@@ -44670,10 +44673,10 @@
         <v>1459</v>
       </c>
       <c r="V562" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="W562" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44738,7 +44741,7 @@
         <v>1898</v>
       </c>
       <c r="W563" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -44800,10 +44803,10 @@
         <v>1459</v>
       </c>
       <c r="V564" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="W564" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA564" t="b">
         <v>1</v>
@@ -44871,10 +44874,10 @@
         <v>1899</v>
       </c>
       <c r="V565" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="W565" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -44942,7 +44945,7 @@
         <v>1900</v>
       </c>
       <c r="W566" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45010,7 +45013,7 @@
         <v>1901</v>
       </c>
       <c r="W567" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45075,10 +45078,10 @@
         <v>1902</v>
       </c>
       <c r="V568" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="W568" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA568" t="b">
         <v>1</v>
@@ -45140,10 +45143,10 @@
         <v>1460</v>
       </c>
       <c r="V569" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="W569" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA569" t="b">
         <v>1</v>
@@ -45201,11 +45204,14 @@
       <c r="S570" t="s">
         <v>1460</v>
       </c>
+      <c r="U570" t="s">
+        <v>1903</v>
+      </c>
       <c r="V570" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="W570" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA570" t="b">
         <v>1</v>
@@ -45267,10 +45273,10 @@
         <v>1460</v>
       </c>
       <c r="U571" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="W571" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45332,10 +45338,10 @@
         <v>1460</v>
       </c>
       <c r="V572" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="W572" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA572" t="b">
         <v>1</v>
@@ -45400,13 +45406,13 @@
         <v>1460</v>
       </c>
       <c r="U573" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="V573" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="W573" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA573" t="b">
         <v>1</v>
@@ -45468,10 +45474,10 @@
         <v>1460</v>
       </c>
       <c r="V574" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="W574" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA574" t="b">
         <v>1</v>
@@ -45533,10 +45539,10 @@
         <v>1459</v>
       </c>
       <c r="V575" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="W575" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA575" t="b">
         <v>1</v>
@@ -45598,13 +45604,13 @@
         <v>1459</v>
       </c>
       <c r="U576" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="V576" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="W576" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA576" t="b">
         <v>1</v>
@@ -45666,13 +45672,13 @@
         <v>1459</v>
       </c>
       <c r="U577" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="V577" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="W577" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA577" t="b">
         <v>1</v>
@@ -45734,7 +45740,7 @@
         <v>1459</v>
       </c>
       <c r="W578" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="AA578" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32483,10 +32483,10 @@
         <v>1386</v>
       </c>
       <c r="Q386">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R386">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S386" t="s">
         <v>1463</v>
@@ -33822,10 +33822,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R406">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S406" t="s">
         <v>1462</v>
@@ -44259,10 +44259,10 @@
         <v>46216</v>
       </c>
       <c r="Q556">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R556">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S556" t="s">
         <v>1462</v>
@@ -44330,10 +44330,10 @@
         <v>46238</v>
       </c>
       <c r="Q557">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="R557">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S557" t="s">
         <v>1462</v>
@@ -44608,10 +44608,10 @@
         <v>46237</v>
       </c>
       <c r="Q561">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R561">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S561" t="s">
         <v>1462</v>
@@ -44676,10 +44676,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S562" t="s">
         <v>1462</v>
@@ -44806,10 +44806,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="R564">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S564" t="s">
         <v>1462</v>
@@ -45072,10 +45072,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="R568">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S568" t="s">
         <v>1462</v>
@@ -45143,10 +45143,10 @@
         <v>46227</v>
       </c>
       <c r="Q569">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R569">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S569" t="s">
         <v>1462</v>
@@ -45208,10 +45208,10 @@
         <v>46251</v>
       </c>
       <c r="Q570">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R570">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S570" t="s">
         <v>1463</v>
@@ -45338,10 +45338,10 @@
         <v>46232</v>
       </c>
       <c r="Q572">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R572">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S572" t="s">
         <v>1462</v>
@@ -45406,10 +45406,10 @@
         <v>46228</v>
       </c>
       <c r="Q573">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R573">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S573" t="s">
         <v>1462</v>
@@ -45474,10 +45474,10 @@
         <v>46229</v>
       </c>
       <c r="Q574">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R574">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S574" t="s">
         <v>1462</v>
@@ -45539,10 +45539,10 @@
         <v>46254</v>
       </c>
       <c r="Q575">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R575">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S575" t="s">
         <v>1462</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32483,10 +32483,10 @@
         <v>1386</v>
       </c>
       <c r="Q386">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R386">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S386" t="s">
         <v>1465</v>
@@ -33822,10 +33822,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R406">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S406" t="s">
         <v>1464</v>
@@ -44247,10 +44247,10 @@
         <v>46216</v>
       </c>
       <c r="Q556">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R556">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S556" t="s">
         <v>1464</v>
@@ -44593,10 +44593,10 @@
         <v>1458</v>
       </c>
       <c r="Q561">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R561">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S561" t="s">
         <v>1464</v>
@@ -44661,10 +44661,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="R562">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S562" t="s">
         <v>1464</v>
@@ -44791,10 +44791,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="R564">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S564" t="s">
         <v>1464</v>
@@ -45057,10 +45057,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="R568">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S568" t="s">
         <v>1464</v>
@@ -45199,10 +45199,10 @@
         <v>46251</v>
       </c>
       <c r="Q570">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="R570">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S570" t="s">
         <v>1465</v>
@@ -45403,10 +45403,10 @@
         <v>46228</v>
       </c>
       <c r="Q573">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R573">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S573" t="s">
         <v>1464</v>
@@ -45471,10 +45471,10 @@
         <v>46229</v>
       </c>
       <c r="Q574">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R574">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S574" t="s">
         <v>1464</v>
@@ -45539,10 +45539,10 @@
         <v>46254</v>
       </c>
       <c r="Q575">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R575">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S575" t="s">
         <v>1464</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7267" uniqueCount="2306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7272" uniqueCount="2306">
   <si>
     <t>om_emg</t>
   </si>
@@ -5761,7 +5761,7 @@
     <t>Recibo 605/FAB/26 assinado em 27/07. Ramon 27/07/26.</t>
   </si>
   <si>
-    <t>Cedeu o item para o C-98 2737. Godoy 21/07/26.  AWB 127-4857 9742volume retirado na loja GOLLOG - QMA por Kleyton em 27/07. Godoy 28/07/26.</t>
+    <t>Cedeu o item para o C-98 2737. Godoy 21/07/26.  AWB 127-4857 9742volume retirado na loja GOLLOG - QMA por Kleyton em 27/07. Godoy 28/07/26. Item recebido na NF-e em 27/07/2026 por 3S Lazaro. Godoy 28/07/2026.</t>
   </si>
   <si>
     <t>AWB 127-4858 1702 retirado em 27/07. Recibo 592/FAB/26 assinado em 27/07. Ramon 28/07/26</t>
@@ -33839,6 +33839,9 @@
       <c r="S406" t="s">
         <v>1466</v>
       </c>
+      <c r="T406" t="s">
+        <v>1467</v>
+      </c>
       <c r="U406" t="s">
         <v>1765</v>
       </c>
@@ -42889,6 +42892,9 @@
       <c r="S536" t="s">
         <v>1466</v>
       </c>
+      <c r="T536" t="s">
+        <v>1467</v>
+      </c>
       <c r="U536" t="s">
         <v>1881</v>
       </c>
@@ -43167,6 +43173,9 @@
       <c r="S540" t="s">
         <v>1466</v>
       </c>
+      <c r="T540" t="s">
+        <v>1467</v>
+      </c>
       <c r="U540" t="s">
         <v>1885</v>
       </c>
@@ -45420,6 +45429,9 @@
       <c r="O573" s="1">
         <v>46228</v>
       </c>
+      <c r="P573" t="s">
+        <v>1457</v>
+      </c>
       <c r="Q573">
         <v>-1</v>
       </c>
@@ -45442,7 +45454,7 @@
         <v>1933</v>
       </c>
       <c r="AA573" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="574" spans="1:27">
@@ -45835,6 +45847,9 @@
         <v>0</v>
       </c>
       <c r="S579" t="s">
+        <v>1466</v>
+      </c>
+      <c r="T579" t="s">
         <v>1466</v>
       </c>
       <c r="W579" t="s">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -45370,7 +45370,7 @@
         <v>46220</v>
       </c>
       <c r="K573" s="1">
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="L573">
         <v>1</v>
@@ -45379,7 +45379,7 @@
         <v>1237</v>
       </c>
       <c r="N573" s="1">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="O573" s="1">
         <v>46228</v>
@@ -45388,10 +45388,10 @@
         <v>1458</v>
       </c>
       <c r="Q573">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="R573">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S573" t="s">
         <v>1467</v>
@@ -45444,7 +45444,7 @@
         <v>46224</v>
       </c>
       <c r="K574" s="1">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="L574">
         <v>1</v>
@@ -45453,16 +45453,16 @@
         <v>1237</v>
       </c>
       <c r="N574" s="1">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="P574" t="s">
         <v>1458</v>
       </c>
       <c r="Q574">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R574">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S574" t="s">
         <v>1467</v>
@@ -45512,7 +45512,7 @@
         <v>46220</v>
       </c>
       <c r="K575" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="L575">
         <v>10</v>
@@ -45521,13 +45521,13 @@
         <v>1237</v>
       </c>
       <c r="N575" s="1">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="Q575">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="R575">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S575" t="s">
         <v>1467</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32495,10 +32495,10 @@
         <v>1393</v>
       </c>
       <c r="Q386">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R386">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S386" t="s">
         <v>1473</v>
@@ -33834,10 +33834,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R406">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S406" t="s">
         <v>1472</v>
@@ -44667,10 +44667,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R562">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S562" t="s">
         <v>1472</v>
@@ -44800,10 +44800,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="R564">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S564" t="s">
         <v>1472</v>
@@ -45069,10 +45069,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R568">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S568" t="s">
         <v>1472</v>
@@ -45539,10 +45539,10 @@
         <v>46255</v>
       </c>
       <c r="Q575">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="R575">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S575" t="s">
         <v>1472</v>
@@ -45885,10 +45885,10 @@
         <v>1471</v>
       </c>
       <c r="Q580">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R580">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S580" t="s">
         <v>1472</v>
@@ -45953,10 +45953,10 @@
         <v>46265</v>
       </c>
       <c r="Q581">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="R581">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S581" t="s">
         <v>1472</v>
@@ -46012,10 +46012,10 @@
         <v>46265</v>
       </c>
       <c r="Q582">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="R582">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S582" t="s">
         <v>1472</v>
@@ -46071,10 +46071,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="R583">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S583" t="s">
         <v>1472</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7312" uniqueCount="2307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7315" uniqueCount="2307">
   <si>
     <t>om_emg</t>
   </si>
@@ -45961,6 +45961,9 @@
       <c r="S581" t="s">
         <v>1472</v>
       </c>
+      <c r="T581" t="s">
+        <v>1473</v>
+      </c>
       <c r="W581" t="s">
         <v>1934</v>
       </c>
@@ -46020,6 +46023,9 @@
       <c r="S582" t="s">
         <v>1472</v>
       </c>
+      <c r="T582" t="s">
+        <v>1473</v>
+      </c>
       <c r="W582" t="s">
         <v>1934</v>
       </c>
@@ -46078,6 +46084,9 @@
       </c>
       <c r="S583" t="s">
         <v>1472</v>
+      </c>
+      <c r="T583" t="s">
+        <v>1473</v>
       </c>
       <c r="W583" t="s">
         <v>1934</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7315" uniqueCount="2307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7316" uniqueCount="2308">
   <si>
     <t>om_emg</t>
   </si>
@@ -5797,25 +5797,28 @@
     <t>Cedeu o item para o 2704. Ramon 29/07/26. Recibo 634/FAB/26 entregue em 30/07. Ramon 30/07/26.</t>
   </si>
   <si>
+    <t>Atendido 01 EA através da TSP 18122931. Outros 02 EA serão enviados pela empresa. Ramon 03/08/26.</t>
+  </si>
+  <si>
     <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron WB0003068789 - previsão de entrega 60 dias em média. Os demais fornecedores informaram não ter em estoque ou não possuírem a certificação necessária da peça.</t>
   </si>
   <si>
-    <t>Colocado pedido junto ao fornecedor LEGACY PARTS, validando prazo de entrega em Miami. ATZ 28/07</t>
-  </si>
-  <si>
-    <t>Colocado pedido Textron IJ17575583 - entregue em Miami 15/07. Carga rercepcionada GIG 19/07 - Aguardando liberação do SEFAZ. ATZ 21/07 - material em processo de expedição RC 23/07/2026</t>
+    <t>Colocado pedido junto ao fornecedor LEGACY PARTS, previsão de entrega em Miami 05/08</t>
+  </si>
+  <si>
+    <t>Colocado pedido Textron IJ17575583 - entregue em Miami 15/07. Carga rercepcionada GIG 19/07 - Aguardando liberação do SEFAZ. ATZ 21/07 - material em processo de expedição RC 23/07/2026 - MATERIAL ENVIADO PELO RECIBO 639/FAB/26 AWB A SER GERADA NA GOLLOG</t>
   </si>
   <si>
     <t>Item em bancada porem em pessimo estado, foi solicitado recolhimento de mais unidades para envio a oficina para tentativa de reparo ATZ Marcio 17/7/26. Solicitado abertura de O.S. para 3EA do item no dia 16-07-26 via Email para a Coordenadoria - CLA-21-07-26</t>
   </si>
   <si>
-    <t>Pedido I816822 entregue em Miami 27/07. Consolidando próximo embarque GIG. ATZ 28/07</t>
-  </si>
-  <si>
-    <t>ITEM ENVIADO NO DIA 28-07-26 AWB 127-4985 2891 - CLA -29-07</t>
-  </si>
-  <si>
-    <t>Será atendido via estoque V1. ATZ 29/07</t>
+    <t>Pedido I816822 entregue em Miami 27/07. Previsão de chegada GIG 30/07 (voo 4208). Previsão de canal 31/07</t>
+  </si>
+  <si>
+    <t>Enviado para o Operador(02 EA), atendimento parcial, em 31/07/2026 - REZ - o outro 1 EA será atendido pelo estoque FAB. conforme solicitado por Email- CLA-03-08</t>
+  </si>
+  <si>
+    <t>Temos 4 EA em manutenção na William, será pedido prioridade. CLA-03-08</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7412,7 +7415,7 @@
         <v>1476</v>
       </c>
       <c r="W2" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7474,16 +7477,16 @@
         <v>1477</v>
       </c>
       <c r="W3" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X3" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="Y3" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z3" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7545,7 +7548,7 @@
         <v>1476</v>
       </c>
       <c r="W4" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7607,7 +7610,7 @@
         <v>1478</v>
       </c>
       <c r="W5" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7669,7 +7672,7 @@
         <v>1479</v>
       </c>
       <c r="W6" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7731,7 +7734,7 @@
         <v>1480</v>
       </c>
       <c r="W7" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7793,7 +7796,7 @@
         <v>1481</v>
       </c>
       <c r="W8" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7855,7 +7858,7 @@
         <v>1482</v>
       </c>
       <c r="W9" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -7917,7 +7920,7 @@
         <v>1483</v>
       </c>
       <c r="W10" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -7979,7 +7982,7 @@
         <v>1484</v>
       </c>
       <c r="W11" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8041,7 +8044,7 @@
         <v>1485</v>
       </c>
       <c r="W12" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8103,7 +8106,7 @@
         <v>1481</v>
       </c>
       <c r="W13" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8165,16 +8168,16 @@
         <v>1486</v>
       </c>
       <c r="W14" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X14" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="Y14" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z14" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8233,7 +8236,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8298,7 +8301,7 @@
         <v>1487</v>
       </c>
       <c r="W16" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8360,7 +8363,7 @@
         <v>1488</v>
       </c>
       <c r="W17" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8422,7 +8425,7 @@
         <v>1479</v>
       </c>
       <c r="W18" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8484,7 +8487,7 @@
         <v>1479</v>
       </c>
       <c r="W19" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8546,7 +8549,7 @@
         <v>1489</v>
       </c>
       <c r="W20" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8608,7 +8611,7 @@
         <v>1490</v>
       </c>
       <c r="W21" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8670,7 +8673,7 @@
         <v>1490</v>
       </c>
       <c r="W22" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8732,7 +8735,7 @@
         <v>1491</v>
       </c>
       <c r="W23" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8791,7 +8794,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -8850,7 +8853,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -8912,7 +8915,7 @@
         <v>1479</v>
       </c>
       <c r="W26" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -8971,7 +8974,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9030,7 +9033,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9092,7 +9095,7 @@
         <v>1492</v>
       </c>
       <c r="W29" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9151,7 +9154,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9213,7 +9216,7 @@
         <v>1493</v>
       </c>
       <c r="W31" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9275,7 +9278,7 @@
         <v>1494</v>
       </c>
       <c r="W32" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9337,7 +9340,7 @@
         <v>1495</v>
       </c>
       <c r="W33" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9399,7 +9402,7 @@
         <v>1496</v>
       </c>
       <c r="W34" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9461,7 +9464,7 @@
         <v>1497</v>
       </c>
       <c r="W35" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9523,7 +9526,7 @@
         <v>1493</v>
       </c>
       <c r="W36" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9585,7 +9588,7 @@
         <v>1498</v>
       </c>
       <c r="W37" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9647,7 +9650,7 @@
         <v>1476</v>
       </c>
       <c r="W38" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9709,7 +9712,7 @@
         <v>1495</v>
       </c>
       <c r="W39" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9771,7 +9774,7 @@
         <v>1499</v>
       </c>
       <c r="W40" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -9833,7 +9836,7 @@
         <v>1500</v>
       </c>
       <c r="W41" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -9895,16 +9898,16 @@
         <v>1501</v>
       </c>
       <c r="W42" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X42" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="Y42" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z42" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -9966,7 +9969,7 @@
         <v>1495</v>
       </c>
       <c r="W43" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10028,7 +10031,7 @@
         <v>1502</v>
       </c>
       <c r="W44" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10090,7 +10093,7 @@
         <v>1495</v>
       </c>
       <c r="W45" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10152,7 +10155,7 @@
         <v>1495</v>
       </c>
       <c r="W46" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10214,7 +10217,7 @@
         <v>1503</v>
       </c>
       <c r="W47" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10276,7 +10279,7 @@
         <v>1504</v>
       </c>
       <c r="W48" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10338,7 +10341,7 @@
         <v>1505</v>
       </c>
       <c r="W49" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10400,7 +10403,7 @@
         <v>1506</v>
       </c>
       <c r="W50" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10462,7 +10465,7 @@
         <v>1507</v>
       </c>
       <c r="W51" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10524,7 +10527,7 @@
         <v>1496</v>
       </c>
       <c r="W52" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10586,7 +10589,7 @@
         <v>1490</v>
       </c>
       <c r="W53" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10648,7 +10651,7 @@
         <v>1490</v>
       </c>
       <c r="W54" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10710,7 +10713,7 @@
         <v>1490</v>
       </c>
       <c r="W55" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10772,7 +10775,7 @@
         <v>1508</v>
       </c>
       <c r="W56" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -10834,7 +10837,7 @@
         <v>1509</v>
       </c>
       <c r="W57" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -10896,16 +10899,16 @@
         <v>1510</v>
       </c>
       <c r="W58" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X58" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="Y58" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z58" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -10967,7 +10970,7 @@
         <v>1511</v>
       </c>
       <c r="W59" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11029,7 +11032,7 @@
         <v>1512</v>
       </c>
       <c r="W60" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11091,7 +11094,7 @@
         <v>1490</v>
       </c>
       <c r="W61" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11153,7 +11156,7 @@
         <v>1513</v>
       </c>
       <c r="W62" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11212,7 +11215,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11271,7 +11274,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11330,7 +11333,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11389,7 +11392,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11448,7 +11451,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11507,7 +11510,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11569,7 +11572,7 @@
         <v>1514</v>
       </c>
       <c r="W69" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11631,7 +11634,7 @@
         <v>1512</v>
       </c>
       <c r="W70" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11693,7 +11696,7 @@
         <v>1497</v>
       </c>
       <c r="W71" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11755,7 +11758,7 @@
         <v>1515</v>
       </c>
       <c r="W72" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -11817,7 +11820,7 @@
         <v>1516</v>
       </c>
       <c r="W73" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -11879,16 +11882,16 @@
         <v>1517</v>
       </c>
       <c r="W74" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X74" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="Y74" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z74" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -11950,16 +11953,16 @@
         <v>1518</v>
       </c>
       <c r="W75" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X75" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="Y75" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z75" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12021,7 +12024,7 @@
         <v>1497</v>
       </c>
       <c r="W76" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12083,7 +12086,7 @@
         <v>1497</v>
       </c>
       <c r="W77" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12145,10 +12148,10 @@
         <v>1519</v>
       </c>
       <c r="W78" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="Z78" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12213,7 +12216,7 @@
         <v>1520</v>
       </c>
       <c r="W79" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12272,7 +12275,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12331,7 +12334,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12393,7 +12396,7 @@
         <v>1521</v>
       </c>
       <c r="W82" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12455,7 +12458,7 @@
         <v>1522</v>
       </c>
       <c r="W83" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12517,7 +12520,7 @@
         <v>1523</v>
       </c>
       <c r="W84" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12576,7 +12579,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12638,7 +12641,7 @@
         <v>1524</v>
       </c>
       <c r="W86" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12700,7 +12703,7 @@
         <v>1525</v>
       </c>
       <c r="W87" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12762,7 +12765,7 @@
         <v>1525</v>
       </c>
       <c r="W88" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -12824,7 +12827,7 @@
         <v>1490</v>
       </c>
       <c r="W89" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -12886,16 +12889,16 @@
         <v>1526</v>
       </c>
       <c r="W90" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X90" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="Y90" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z90" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -12957,16 +12960,16 @@
         <v>1527</v>
       </c>
       <c r="W91" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X91" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="Y91" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z91" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13028,7 +13031,7 @@
         <v>1528</v>
       </c>
       <c r="W92" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13090,7 +13093,7 @@
         <v>1529</v>
       </c>
       <c r="W93" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13152,7 +13155,7 @@
         <v>1529</v>
       </c>
       <c r="W94" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13214,7 +13217,7 @@
         <v>1530</v>
       </c>
       <c r="W95" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13276,16 +13279,16 @@
         <v>1531</v>
       </c>
       <c r="W96" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X96" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="Y96" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z96" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13347,7 +13350,7 @@
         <v>1532</v>
       </c>
       <c r="W97" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13409,7 +13412,7 @@
         <v>1533</v>
       </c>
       <c r="W98" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13471,7 +13474,7 @@
         <v>1534</v>
       </c>
       <c r="W99" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13533,7 +13536,7 @@
         <v>1535</v>
       </c>
       <c r="W100" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13595,16 +13598,16 @@
         <v>1536</v>
       </c>
       <c r="W101" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X101" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="Y101" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z101" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13666,7 +13669,7 @@
         <v>1537</v>
       </c>
       <c r="W102" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13728,7 +13731,7 @@
         <v>1537</v>
       </c>
       <c r="W103" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13790,7 +13793,7 @@
         <v>1538</v>
       </c>
       <c r="W104" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -13852,16 +13855,16 @@
         <v>1539</v>
       </c>
       <c r="W105" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X105" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="Y105" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z105" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -13923,16 +13926,16 @@
         <v>1540</v>
       </c>
       <c r="W106" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X106" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="Y106" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z106" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -13994,7 +13997,7 @@
         <v>1541</v>
       </c>
       <c r="W107" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14056,16 +14059,16 @@
         <v>1542</v>
       </c>
       <c r="W108" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X108" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="Y108" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z108" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14127,16 +14130,16 @@
         <v>1543</v>
       </c>
       <c r="W109" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X109" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="Y109" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z109" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14195,7 +14198,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14257,16 +14260,16 @@
         <v>1544</v>
       </c>
       <c r="W111" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X111" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="Y111" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z111" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14328,16 +14331,16 @@
         <v>1545</v>
       </c>
       <c r="W112" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X112" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="Y112" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z112" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14399,16 +14402,16 @@
         <v>1546</v>
       </c>
       <c r="W113" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X113" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="Y113" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z113" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14470,16 +14473,16 @@
         <v>1547</v>
       </c>
       <c r="W114" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X114" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="Y114" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z114" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14541,16 +14544,16 @@
         <v>1543</v>
       </c>
       <c r="W115" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X115" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="Y115" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z115" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14612,16 +14615,16 @@
         <v>1543</v>
       </c>
       <c r="W116" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X116" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="Y116" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z116" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14683,16 +14686,16 @@
         <v>1548</v>
       </c>
       <c r="W117" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X117" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="Y117" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z117" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14754,16 +14757,16 @@
         <v>1549</v>
       </c>
       <c r="W118" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X118" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="Y118" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z118" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -14825,7 +14828,7 @@
         <v>1550</v>
       </c>
       <c r="W119" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -14887,16 +14890,16 @@
         <v>1551</v>
       </c>
       <c r="W120" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X120" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y120" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z120" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -14958,16 +14961,16 @@
         <v>1551</v>
       </c>
       <c r="W121" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X121" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y121" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z121" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15029,16 +15032,16 @@
         <v>1551</v>
       </c>
       <c r="W122" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X122" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y122" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z122" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15100,16 +15103,16 @@
         <v>1551</v>
       </c>
       <c r="W123" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X123" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y123" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z123" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15171,16 +15174,16 @@
         <v>1551</v>
       </c>
       <c r="W124" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X124" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y124" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z124" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15242,16 +15245,16 @@
         <v>1551</v>
       </c>
       <c r="W125" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X125" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y125" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z125" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15313,16 +15316,16 @@
         <v>1551</v>
       </c>
       <c r="W126" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X126" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y126" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z126" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15384,16 +15387,16 @@
         <v>1552</v>
       </c>
       <c r="W127" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X127" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="Y127" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z127" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15455,16 +15458,16 @@
         <v>1553</v>
       </c>
       <c r="W128" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X128" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="Y128" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z128" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15526,16 +15529,16 @@
         <v>1551</v>
       </c>
       <c r="W129" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X129" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y129" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z129" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15597,16 +15600,16 @@
         <v>1551</v>
       </c>
       <c r="W130" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X130" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y130" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z130" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15668,7 +15671,7 @@
         <v>1554</v>
       </c>
       <c r="W131" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15727,7 +15730,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15786,7 +15789,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -15848,16 +15851,16 @@
         <v>1551</v>
       </c>
       <c r="W134" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X134" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y134" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z134" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -15919,16 +15922,16 @@
         <v>1551</v>
       </c>
       <c r="W135" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X135" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y135" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z135" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -15990,7 +15993,7 @@
         <v>1550</v>
       </c>
       <c r="W136" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16049,7 +16052,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16111,16 +16114,16 @@
         <v>1555</v>
       </c>
       <c r="W138" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X138" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="Y138" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z138" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16182,16 +16185,16 @@
         <v>1543</v>
       </c>
       <c r="W139" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X139" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="Y139" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z139" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16253,16 +16256,16 @@
         <v>1551</v>
       </c>
       <c r="W140" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X140" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y140" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z140" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16321,7 +16324,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16380,7 +16383,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16442,16 +16445,16 @@
         <v>1556</v>
       </c>
       <c r="W143" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X143" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="Y143" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z143" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16513,16 +16516,16 @@
         <v>1557</v>
       </c>
       <c r="W144" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X144" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="Y144" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z144" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16584,16 +16587,16 @@
         <v>1558</v>
       </c>
       <c r="W145" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X145" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="Y145" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z145" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16655,16 +16658,16 @@
         <v>1559</v>
       </c>
       <c r="W146" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X146" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="Y146" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z146" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16723,7 +16726,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16785,7 +16788,7 @@
         <v>1560</v>
       </c>
       <c r="W148" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -16847,16 +16850,16 @@
         <v>1561</v>
       </c>
       <c r="W149" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X149" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="Y149" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z149" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -16918,7 +16921,7 @@
         <v>1562</v>
       </c>
       <c r="W150" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -16980,16 +16983,16 @@
         <v>1563</v>
       </c>
       <c r="W151" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X151" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="Y151" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z151" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17051,7 +17054,7 @@
         <v>1562</v>
       </c>
       <c r="W152" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17113,7 +17116,7 @@
         <v>1560</v>
       </c>
       <c r="W153" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17175,7 +17178,7 @@
         <v>1562</v>
       </c>
       <c r="W154" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17237,7 +17240,7 @@
         <v>1562</v>
       </c>
       <c r="W155" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17299,16 +17302,16 @@
         <v>1564</v>
       </c>
       <c r="W156" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X156" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="Y156" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z156" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17370,7 +17373,7 @@
         <v>1560</v>
       </c>
       <c r="W157" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17432,16 +17435,16 @@
         <v>1565</v>
       </c>
       <c r="W158" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X158" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y158" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z158" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17503,16 +17506,16 @@
         <v>1566</v>
       </c>
       <c r="W159" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X159" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="Y159" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z159" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17574,16 +17577,16 @@
         <v>1565</v>
       </c>
       <c r="W160" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X160" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y160" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z160" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17645,16 +17648,16 @@
         <v>1565</v>
       </c>
       <c r="W161" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X161" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y161" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z161" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17716,16 +17719,16 @@
         <v>1565</v>
       </c>
       <c r="W162" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X162" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y162" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z162" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17787,16 +17790,16 @@
         <v>1567</v>
       </c>
       <c r="W163" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X163" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="Y163" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z163" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -17858,16 +17861,16 @@
         <v>1568</v>
       </c>
       <c r="W164" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X164" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="Y164" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z164" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -17929,16 +17932,16 @@
         <v>1569</v>
       </c>
       <c r="W165" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X165" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="Y165" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z165" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18000,16 +18003,16 @@
         <v>1570</v>
       </c>
       <c r="W166" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X166" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="Y166" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z166" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18071,16 +18074,16 @@
         <v>1548</v>
       </c>
       <c r="W167" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X167" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="Y167" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z167" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18142,16 +18145,16 @@
         <v>1551</v>
       </c>
       <c r="W168" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X168" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y168" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z168" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18213,7 +18216,7 @@
         <v>1571</v>
       </c>
       <c r="W169" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18275,16 +18278,16 @@
         <v>1551</v>
       </c>
       <c r="W170" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X170" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="Y170" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z170" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18346,16 +18349,16 @@
         <v>1572</v>
       </c>
       <c r="W171" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X171" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y171" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z171" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18417,16 +18420,16 @@
         <v>1573</v>
       </c>
       <c r="W172" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X172" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="Y172" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z172" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18488,16 +18491,16 @@
         <v>1574</v>
       </c>
       <c r="W173" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X173" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="Y173" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z173" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18559,16 +18562,16 @@
         <v>1575</v>
       </c>
       <c r="W174" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X174" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="Y174" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z174" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18630,16 +18633,16 @@
         <v>1576</v>
       </c>
       <c r="W175" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X175" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="Y175" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z175" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18701,16 +18704,16 @@
         <v>1577</v>
       </c>
       <c r="W176" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X176" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="Y176" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z176" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18772,7 +18775,7 @@
         <v>1571</v>
       </c>
       <c r="W177" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -18834,16 +18837,16 @@
         <v>1578</v>
       </c>
       <c r="W178" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X178" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="Y178" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z178" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -18905,16 +18908,16 @@
         <v>1579</v>
       </c>
       <c r="W179" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X179" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="Y179" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z179" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -18976,7 +18979,7 @@
         <v>1580</v>
       </c>
       <c r="W180" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19038,16 +19041,16 @@
         <v>1581</v>
       </c>
       <c r="W181" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X181" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="Y181" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z181" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19109,16 +19112,16 @@
         <v>1581</v>
       </c>
       <c r="W182" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X182" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="Y182" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z182" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19180,16 +19183,16 @@
         <v>1582</v>
       </c>
       <c r="W183" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X183" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="Y183" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z183" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19251,16 +19254,16 @@
         <v>1583</v>
       </c>
       <c r="W184" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X184" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="Y184" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z184" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19322,16 +19325,16 @@
         <v>1584</v>
       </c>
       <c r="W185" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X185" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="Y185" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z185" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19393,7 +19396,7 @@
         <v>1585</v>
       </c>
       <c r="W186" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19455,7 +19458,7 @@
         <v>1586</v>
       </c>
       <c r="W187" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19517,7 +19520,7 @@
         <v>1587</v>
       </c>
       <c r="W188" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19579,7 +19582,7 @@
         <v>1588</v>
       </c>
       <c r="W189" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19641,16 +19644,16 @@
         <v>1589</v>
       </c>
       <c r="W190" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X190" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="Y190" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z190" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19712,16 +19715,16 @@
         <v>1590</v>
       </c>
       <c r="W191" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X191" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="Y191" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z191" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19783,7 +19786,7 @@
         <v>1591</v>
       </c>
       <c r="W192" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -19845,7 +19848,7 @@
         <v>1591</v>
       </c>
       <c r="W193" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -19907,16 +19910,16 @@
         <v>1592</v>
       </c>
       <c r="W194" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X194" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="Y194" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z194" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -19978,16 +19981,16 @@
         <v>1593</v>
       </c>
       <c r="W195" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X195" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="Y195" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z195" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20049,16 +20052,16 @@
         <v>1594</v>
       </c>
       <c r="W196" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X196" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="Y196" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z196" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20120,16 +20123,16 @@
         <v>1590</v>
       </c>
       <c r="W197" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X197" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="Y197" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z197" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20191,7 +20194,7 @@
         <v>1595</v>
       </c>
       <c r="W198" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20253,7 +20256,7 @@
         <v>1596</v>
       </c>
       <c r="W199" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20315,16 +20318,16 @@
         <v>1597</v>
       </c>
       <c r="W200" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X200" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="Y200" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z200" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20386,16 +20389,16 @@
         <v>1597</v>
       </c>
       <c r="W201" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X201" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="Y201" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z201" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20457,16 +20460,16 @@
         <v>1598</v>
       </c>
       <c r="W202" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X202" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="Y202" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z202" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20528,16 +20531,16 @@
         <v>1599</v>
       </c>
       <c r="W203" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X203" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Y203" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z203" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20599,16 +20602,16 @@
         <v>1600</v>
       </c>
       <c r="W204" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X204" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="Y204" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z204" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20670,16 +20673,16 @@
         <v>1601</v>
       </c>
       <c r="W205" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X205" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="Y205" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z205" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20741,16 +20744,16 @@
         <v>1602</v>
       </c>
       <c r="W206" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X206" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="Y206" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z206" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -20812,16 +20815,16 @@
         <v>1603</v>
       </c>
       <c r="W207" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X207" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="Y207" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z207" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -20883,16 +20886,16 @@
         <v>1604</v>
       </c>
       <c r="W208" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X208" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="Y208" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z208" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -20954,7 +20957,7 @@
         <v>1605</v>
       </c>
       <c r="W209" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21016,16 +21019,16 @@
         <v>1606</v>
       </c>
       <c r="W210" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X210" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="Y210" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z210" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21087,16 +21090,16 @@
         <v>1607</v>
       </c>
       <c r="W211" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X211" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="Y211" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z211" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21158,16 +21161,16 @@
         <v>1608</v>
       </c>
       <c r="W212" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X212" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="Y212" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z212" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21229,16 +21232,16 @@
         <v>1609</v>
       </c>
       <c r="W213" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X213" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="Y213" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z213" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21300,7 +21303,7 @@
         <v>1610</v>
       </c>
       <c r="W214" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21362,16 +21365,16 @@
         <v>1575</v>
       </c>
       <c r="W215" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X215" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="Y215" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z215" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21433,16 +21436,16 @@
         <v>1611</v>
       </c>
       <c r="W216" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X216" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="Y216" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z216" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21504,7 +21507,7 @@
         <v>1612</v>
       </c>
       <c r="W217" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21566,16 +21569,16 @@
         <v>1613</v>
       </c>
       <c r="W218" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X218" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y218" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z218" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21637,16 +21640,16 @@
         <v>1614</v>
       </c>
       <c r="W219" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X219" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="Y219" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z219" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21708,7 +21711,7 @@
         <v>1615</v>
       </c>
       <c r="W220" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21770,7 +21773,7 @@
         <v>1616</v>
       </c>
       <c r="W221" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -21832,7 +21835,7 @@
         <v>1615</v>
       </c>
       <c r="W222" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -21894,7 +21897,7 @@
         <v>1616</v>
       </c>
       <c r="W223" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -21956,16 +21959,16 @@
         <v>1617</v>
       </c>
       <c r="W224" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X224" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="Y224" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z224" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22027,16 +22030,16 @@
         <v>1618</v>
       </c>
       <c r="W225" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X225" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="Y225" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z225" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22098,7 +22101,7 @@
         <v>1619</v>
       </c>
       <c r="W226" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22160,7 +22163,7 @@
         <v>1620</v>
       </c>
       <c r="W227" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22222,7 +22225,7 @@
         <v>1621</v>
       </c>
       <c r="W228" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22284,16 +22287,16 @@
         <v>1622</v>
       </c>
       <c r="W229" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X229" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="Y229" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z229" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22355,16 +22358,16 @@
         <v>1623</v>
       </c>
       <c r="W230" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X230" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="Y230" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z230" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22426,16 +22429,16 @@
         <v>1624</v>
       </c>
       <c r="W231" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X231" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y231" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z231" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22500,16 +22503,16 @@
         <v>1625</v>
       </c>
       <c r="W232" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X232" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="Y232" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z232" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22571,16 +22574,16 @@
         <v>1626</v>
       </c>
       <c r="W233" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X233" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="Y233" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z233" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22642,16 +22645,16 @@
         <v>1627</v>
       </c>
       <c r="W234" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X234" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Y234" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z234" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22713,16 +22716,16 @@
         <v>1627</v>
       </c>
       <c r="W235" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X235" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Y235" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z235" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22784,16 +22787,16 @@
         <v>1628</v>
       </c>
       <c r="W236" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X236" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Y236" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z236" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -22855,7 +22858,7 @@
         <v>1629</v>
       </c>
       <c r="W237" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -22917,7 +22920,7 @@
         <v>1630</v>
       </c>
       <c r="W238" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -22979,16 +22982,16 @@
         <v>1631</v>
       </c>
       <c r="W239" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X239" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="Y239" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z239" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23050,16 +23053,16 @@
         <v>1632</v>
       </c>
       <c r="W240" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X240" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="Y240" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z240" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23121,7 +23124,7 @@
         <v>1633</v>
       </c>
       <c r="W241" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23183,16 +23186,16 @@
         <v>1634</v>
       </c>
       <c r="W242" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X242" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="Y242" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z242" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23254,16 +23257,16 @@
         <v>1635</v>
       </c>
       <c r="W243" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X243" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="Y243" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z243" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23325,16 +23328,16 @@
         <v>1634</v>
       </c>
       <c r="W244" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X244" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="Y244" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z244" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23396,16 +23399,16 @@
         <v>1636</v>
       </c>
       <c r="W245" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X245" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="Y245" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z245" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23467,16 +23470,16 @@
         <v>1635</v>
       </c>
       <c r="W246" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X246" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="Y246" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z246" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23538,16 +23541,16 @@
         <v>1636</v>
       </c>
       <c r="W247" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X247" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="Y247" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z247" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23609,16 +23612,16 @@
         <v>1637</v>
       </c>
       <c r="W248" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X248" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="Y248" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z248" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23680,16 +23683,16 @@
         <v>1627</v>
       </c>
       <c r="W249" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X249" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Y249" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z249" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23751,7 +23754,7 @@
         <v>1638</v>
       </c>
       <c r="W250" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -23813,7 +23816,7 @@
         <v>1639</v>
       </c>
       <c r="W251" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -23875,16 +23878,16 @@
         <v>1640</v>
       </c>
       <c r="W252" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X252" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="Y252" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z252" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -23946,16 +23949,16 @@
         <v>1641</v>
       </c>
       <c r="W253" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X253" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y253" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z253" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24017,7 +24020,7 @@
         <v>1642</v>
       </c>
       <c r="W254" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24079,16 +24082,16 @@
         <v>1643</v>
       </c>
       <c r="W255" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X255" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="Y255" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z255" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24150,7 +24153,7 @@
         <v>1644</v>
       </c>
       <c r="W256" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24215,7 +24218,7 @@
         <v>1645</v>
       </c>
       <c r="W257" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24277,7 +24280,7 @@
         <v>1646</v>
       </c>
       <c r="W258" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24339,7 +24342,7 @@
         <v>1646</v>
       </c>
       <c r="W259" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24401,7 +24404,7 @@
         <v>1647</v>
       </c>
       <c r="W260" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24463,16 +24466,16 @@
         <v>1648</v>
       </c>
       <c r="W261" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X261" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="Y261" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z261" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24534,13 +24537,13 @@
         <v>1649</v>
       </c>
       <c r="W262" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X262" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="Y262" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24602,16 +24605,16 @@
         <v>1650</v>
       </c>
       <c r="W263" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X263" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Y263" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z263" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24673,7 +24676,7 @@
         <v>1651</v>
       </c>
       <c r="W264" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24735,7 +24738,7 @@
         <v>1651</v>
       </c>
       <c r="W265" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24797,7 +24800,7 @@
         <v>1652</v>
       </c>
       <c r="W266" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -24859,16 +24862,16 @@
         <v>1653</v>
       </c>
       <c r="W267" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X267" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="Y267" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z267" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -24930,16 +24933,16 @@
         <v>1654</v>
       </c>
       <c r="W268" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X268" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="Y268" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z268" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25001,7 +25004,7 @@
         <v>1495</v>
       </c>
       <c r="W269" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25063,7 +25066,7 @@
         <v>1655</v>
       </c>
       <c r="W270" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25125,7 +25128,7 @@
         <v>1656</v>
       </c>
       <c r="W271" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25187,16 +25190,16 @@
         <v>1657</v>
       </c>
       <c r="W272" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X272" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="Y272" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z272" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25255,7 +25258,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25317,7 +25320,7 @@
         <v>1658</v>
       </c>
       <c r="W274" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25376,7 +25379,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25438,7 +25441,7 @@
         <v>1659</v>
       </c>
       <c r="W276" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25500,7 +25503,7 @@
         <v>1660</v>
       </c>
       <c r="W277" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25562,16 +25565,16 @@
         <v>1661</v>
       </c>
       <c r="W278" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X278" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Y278" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z278" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25633,16 +25636,16 @@
         <v>1662</v>
       </c>
       <c r="W279" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X279" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Y279" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z279" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25704,16 +25707,16 @@
         <v>1662</v>
       </c>
       <c r="W280" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X280" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Y280" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z280" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25775,16 +25778,16 @@
         <v>1663</v>
       </c>
       <c r="W281" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X281" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Y281" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z281" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -25846,7 +25849,7 @@
         <v>1664</v>
       </c>
       <c r="W282" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -25908,7 +25911,7 @@
         <v>1665</v>
       </c>
       <c r="W283" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -25970,7 +25973,7 @@
         <v>1666</v>
       </c>
       <c r="W284" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26032,16 +26035,16 @@
         <v>1667</v>
       </c>
       <c r="W285" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X285" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="Y285" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z285" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26103,7 +26106,7 @@
         <v>1668</v>
       </c>
       <c r="W286" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26165,16 +26168,16 @@
         <v>1662</v>
       </c>
       <c r="W287" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X287" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Y287" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z287" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26236,16 +26239,16 @@
         <v>1669</v>
       </c>
       <c r="W288" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X288" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="Y288" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z288" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26307,7 +26310,7 @@
         <v>1670</v>
       </c>
       <c r="W289" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26369,16 +26372,16 @@
         <v>1671</v>
       </c>
       <c r="W290" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X290" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="Y290" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z290" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26440,16 +26443,16 @@
         <v>1672</v>
       </c>
       <c r="W291" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X291" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Y291" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z291" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26511,7 +26514,7 @@
         <v>1673</v>
       </c>
       <c r="W292" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26570,7 +26573,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26632,7 +26635,7 @@
         <v>1674</v>
       </c>
       <c r="W294" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26694,7 +26697,7 @@
         <v>1675</v>
       </c>
       <c r="W295" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26756,7 +26759,7 @@
         <v>1676</v>
       </c>
       <c r="W296" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -26818,13 +26821,13 @@
         <v>1677</v>
       </c>
       <c r="W297" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X297" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Z297" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -26886,7 +26889,7 @@
         <v>1678</v>
       </c>
       <c r="W298" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -26948,7 +26951,7 @@
         <v>1679</v>
       </c>
       <c r="W299" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27010,7 +27013,7 @@
         <v>1680</v>
       </c>
       <c r="W300" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27072,7 +27075,7 @@
         <v>1681</v>
       </c>
       <c r="W301" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27134,7 +27137,7 @@
         <v>1682</v>
       </c>
       <c r="W302" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27196,16 +27199,16 @@
         <v>1683</v>
       </c>
       <c r="W303" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X303" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Y303" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z303" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27267,7 +27270,7 @@
         <v>1684</v>
       </c>
       <c r="W304" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27329,7 +27332,7 @@
         <v>1685</v>
       </c>
       <c r="W305" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27391,7 +27394,7 @@
         <v>1686</v>
       </c>
       <c r="W306" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27453,7 +27456,7 @@
         <v>1687</v>
       </c>
       <c r="W307" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27515,7 +27518,7 @@
         <v>1680</v>
       </c>
       <c r="W308" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27577,7 +27580,7 @@
         <v>1688</v>
       </c>
       <c r="W309" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27639,7 +27642,7 @@
         <v>1689</v>
       </c>
       <c r="W310" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27701,7 +27704,7 @@
         <v>1690</v>
       </c>
       <c r="W311" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27763,7 +27766,7 @@
         <v>1691</v>
       </c>
       <c r="W312" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -27825,7 +27828,7 @@
         <v>1692</v>
       </c>
       <c r="W313" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -27887,7 +27890,7 @@
         <v>1693</v>
       </c>
       <c r="W314" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -27949,7 +27952,7 @@
         <v>1694</v>
       </c>
       <c r="W315" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28011,7 +28014,7 @@
         <v>1695</v>
       </c>
       <c r="W316" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28073,7 +28076,7 @@
         <v>1696</v>
       </c>
       <c r="W317" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28135,7 +28138,7 @@
         <v>1697</v>
       </c>
       <c r="W318" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28197,7 +28200,7 @@
         <v>1698</v>
       </c>
       <c r="W319" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28256,13 +28259,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X320" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="Z320" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28321,7 +28324,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28380,7 +28383,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28439,7 +28442,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28501,7 +28504,7 @@
         <v>1699</v>
       </c>
       <c r="W324" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28563,7 +28566,7 @@
         <v>1700</v>
       </c>
       <c r="W325" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28625,7 +28628,7 @@
         <v>1701</v>
       </c>
       <c r="W326" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28687,7 +28690,7 @@
         <v>1702</v>
       </c>
       <c r="W327" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28746,7 +28749,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -28808,7 +28811,7 @@
         <v>1702</v>
       </c>
       <c r="W329" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -28870,7 +28873,7 @@
         <v>1703</v>
       </c>
       <c r="W330" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -28932,7 +28935,7 @@
         <v>1704</v>
       </c>
       <c r="W331" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -28994,7 +28997,7 @@
         <v>1704</v>
       </c>
       <c r="W332" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29056,7 +29059,7 @@
         <v>1705</v>
       </c>
       <c r="W333" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29118,7 +29121,7 @@
         <v>1706</v>
       </c>
       <c r="W334" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29180,7 +29183,7 @@
         <v>1707</v>
       </c>
       <c r="W335" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29239,13 +29242,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X336" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="Z336" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29307,7 +29310,7 @@
         <v>1708</v>
       </c>
       <c r="W337" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29369,13 +29372,13 @@
         <v>1709</v>
       </c>
       <c r="W338" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X338" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="Z338" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29437,13 +29440,13 @@
         <v>1710</v>
       </c>
       <c r="W339" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X339" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="Z339" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29505,7 +29508,7 @@
         <v>1711</v>
       </c>
       <c r="W340" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29567,7 +29570,7 @@
         <v>1712</v>
       </c>
       <c r="W341" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29629,10 +29632,10 @@
         <v>1713</v>
       </c>
       <c r="W342" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X342" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29694,7 +29697,7 @@
         <v>1714</v>
       </c>
       <c r="W343" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29756,7 +29759,7 @@
         <v>1715</v>
       </c>
       <c r="W344" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -29818,13 +29821,13 @@
         <v>1716</v>
       </c>
       <c r="W345" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X345" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="Z345" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -29886,7 +29889,7 @@
         <v>1680</v>
       </c>
       <c r="W346" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -29948,7 +29951,7 @@
         <v>1717</v>
       </c>
       <c r="W347" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30010,16 +30013,16 @@
         <v>1718</v>
       </c>
       <c r="W348" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X348" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="Y348" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z348" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30084,13 +30087,13 @@
         <v>1719</v>
       </c>
       <c r="W349" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X349" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Z349" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30152,7 +30155,7 @@
         <v>1720</v>
       </c>
       <c r="W350" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30214,16 +30217,16 @@
         <v>1721</v>
       </c>
       <c r="W351" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X351" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="Y351" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z351" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30285,13 +30288,13 @@
         <v>1722</v>
       </c>
       <c r="W352" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X352" t="s">
         <v>1722</v>
       </c>
       <c r="Z352" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30353,16 +30356,16 @@
         <v>1723</v>
       </c>
       <c r="W353" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X353" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y353" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z353" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30424,7 +30427,7 @@
         <v>1724</v>
       </c>
       <c r="W354" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30486,7 +30489,7 @@
         <v>1725</v>
       </c>
       <c r="W355" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30545,7 +30548,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30604,7 +30607,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30663,7 +30666,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30725,7 +30728,7 @@
         <v>1726</v>
       </c>
       <c r="W359" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30790,7 +30793,7 @@
         <v>1727</v>
       </c>
       <c r="W360" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -30855,7 +30858,7 @@
         <v>1728</v>
       </c>
       <c r="W361" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -30917,16 +30920,16 @@
         <v>1729</v>
       </c>
       <c r="W362" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X362" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="Y362" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z362" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -30988,16 +30991,16 @@
         <v>1730</v>
       </c>
       <c r="W363" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X363" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="Y363" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z363" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31059,7 +31062,7 @@
         <v>1731</v>
       </c>
       <c r="W364" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31121,7 +31124,7 @@
         <v>1732</v>
       </c>
       <c r="W365" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31186,7 +31189,7 @@
         <v>1733</v>
       </c>
       <c r="W366" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31248,7 +31251,7 @@
         <v>1734</v>
       </c>
       <c r="W367" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31310,7 +31313,7 @@
         <v>1735</v>
       </c>
       <c r="W368" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31375,13 +31378,13 @@
         <v>1736</v>
       </c>
       <c r="W369" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X369" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="Z369" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31443,7 +31446,7 @@
         <v>1737</v>
       </c>
       <c r="W370" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31505,16 +31508,16 @@
         <v>1738</v>
       </c>
       <c r="W371" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X371" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="Y371" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z371" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31579,7 +31582,7 @@
         <v>1739</v>
       </c>
       <c r="W372" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31644,16 +31647,16 @@
         <v>1740</v>
       </c>
       <c r="W373" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X373" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="Y373" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z373" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31715,7 +31718,7 @@
         <v>1741</v>
       </c>
       <c r="W374" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31780,7 +31783,7 @@
         <v>1742</v>
       </c>
       <c r="W375" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -31845,7 +31848,7 @@
         <v>1743</v>
       </c>
       <c r="W376" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -31910,7 +31913,7 @@
         <v>1743</v>
       </c>
       <c r="W377" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -31975,13 +31978,13 @@
         <v>1744</v>
       </c>
       <c r="W378" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X378" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="Z378" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32043,16 +32046,16 @@
         <v>1745</v>
       </c>
       <c r="W379" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X379" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="Y379" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z379" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32117,7 +32120,7 @@
         <v>1746</v>
       </c>
       <c r="W380" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32179,7 +32182,7 @@
         <v>1747</v>
       </c>
       <c r="W381" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32244,7 +32247,7 @@
         <v>1748</v>
       </c>
       <c r="W382" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32306,7 +32309,7 @@
         <v>1749</v>
       </c>
       <c r="W383" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32371,7 +32374,7 @@
         <v>1748</v>
       </c>
       <c r="W384" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32433,16 +32436,16 @@
         <v>1750</v>
       </c>
       <c r="W385" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X385" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y385" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z385" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32495,10 +32498,10 @@
         <v>1393</v>
       </c>
       <c r="Q386">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R386">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S386" t="s">
         <v>1473</v>
@@ -32510,7 +32513,7 @@
         <v>1751</v>
       </c>
       <c r="W386" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32572,7 +32575,7 @@
         <v>1752</v>
       </c>
       <c r="W387" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32634,7 +32637,7 @@
         <v>1753</v>
       </c>
       <c r="W388" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32696,16 +32699,16 @@
         <v>1754</v>
       </c>
       <c r="W389" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X389" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Y389" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z389" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32770,16 +32773,16 @@
         <v>1755</v>
       </c>
       <c r="W390" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X390" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="Y390" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z390" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -32844,7 +32847,7 @@
         <v>1756</v>
       </c>
       <c r="W391" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -32906,7 +32909,7 @@
         <v>1757</v>
       </c>
       <c r="W392" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -32968,16 +32971,16 @@
         <v>1758</v>
       </c>
       <c r="W393" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X393" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="Y393" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z393" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33039,7 +33042,7 @@
         <v>1759</v>
       </c>
       <c r="W394" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33104,16 +33107,16 @@
         <v>1760</v>
       </c>
       <c r="W395" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X395" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="Y395" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z395" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33178,13 +33181,13 @@
         <v>1761</v>
       </c>
       <c r="W396" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X396" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="Y396" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33246,7 +33249,7 @@
         <v>1762</v>
       </c>
       <c r="W397" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33308,7 +33311,7 @@
         <v>1763</v>
       </c>
       <c r="W398" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33373,7 +33376,7 @@
         <v>1764</v>
       </c>
       <c r="W399" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33438,16 +33441,16 @@
         <v>1765</v>
       </c>
       <c r="W400" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X400" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Y400" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z400" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33512,7 +33515,7 @@
         <v>1766</v>
       </c>
       <c r="W401" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33577,7 +33580,7 @@
         <v>1767</v>
       </c>
       <c r="W402" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33642,16 +33645,16 @@
         <v>1768</v>
       </c>
       <c r="W403" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X403" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="Y403" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z403" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33716,7 +33719,7 @@
         <v>1769</v>
       </c>
       <c r="W404" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33781,7 +33784,7 @@
         <v>1770</v>
       </c>
       <c r="W405" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -33834,10 +33837,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="R406">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="S406" t="s">
         <v>1472</v>
@@ -33849,10 +33852,10 @@
         <v>1771</v>
       </c>
       <c r="V406" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="W406" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA406" t="b">
         <v>1</v>
@@ -33914,16 +33917,16 @@
         <v>1772</v>
       </c>
       <c r="W407" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X407" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y407" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z407" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -33988,13 +33991,13 @@
         <v>1773</v>
       </c>
       <c r="W408" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X408" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="Z408" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34059,7 +34062,7 @@
         <v>1774</v>
       </c>
       <c r="W409" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34124,7 +34127,7 @@
         <v>1775</v>
       </c>
       <c r="W410" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34189,7 +34192,7 @@
         <v>1776</v>
       </c>
       <c r="W411" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34254,7 +34257,7 @@
         <v>1777</v>
       </c>
       <c r="W412" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34319,7 +34322,7 @@
         <v>1778</v>
       </c>
       <c r="W413" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34384,7 +34387,7 @@
         <v>1778</v>
       </c>
       <c r="W414" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34449,7 +34452,7 @@
         <v>1779</v>
       </c>
       <c r="W415" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34514,7 +34517,7 @@
         <v>1780</v>
       </c>
       <c r="W416" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34579,7 +34582,7 @@
         <v>1778</v>
       </c>
       <c r="W417" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34644,7 +34647,7 @@
         <v>1781</v>
       </c>
       <c r="W418" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34709,7 +34712,7 @@
         <v>1782</v>
       </c>
       <c r="W419" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34774,16 +34777,16 @@
         <v>1783</v>
       </c>
       <c r="W420" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X420" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="Y420" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z420" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -34848,7 +34851,7 @@
         <v>1784</v>
       </c>
       <c r="W421" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -34913,7 +34916,7 @@
         <v>1785</v>
       </c>
       <c r="W422" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -34978,7 +34981,7 @@
         <v>1786</v>
       </c>
       <c r="W423" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35043,16 +35046,16 @@
         <v>1787</v>
       </c>
       <c r="W424" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X424" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="Y424" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z424" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35117,7 +35120,7 @@
         <v>1786</v>
       </c>
       <c r="W425" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35182,7 +35185,7 @@
         <v>1788</v>
       </c>
       <c r="W426" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35247,7 +35250,7 @@
         <v>1789</v>
       </c>
       <c r="W427" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35312,13 +35315,13 @@
         <v>1790</v>
       </c>
       <c r="W428" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X428" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="Y428" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35383,16 +35386,16 @@
         <v>1791</v>
       </c>
       <c r="W429" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X429" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y429" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z429" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35457,7 +35460,7 @@
         <v>1792</v>
       </c>
       <c r="W430" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35522,16 +35525,16 @@
         <v>1793</v>
       </c>
       <c r="W431" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X431" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="Y431" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z431" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35596,7 +35599,7 @@
         <v>1794</v>
       </c>
       <c r="W432" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35661,7 +35664,7 @@
         <v>1795</v>
       </c>
       <c r="W433" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35726,7 +35729,7 @@
         <v>1796</v>
       </c>
       <c r="W434" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35791,7 +35794,7 @@
         <v>1797</v>
       </c>
       <c r="W435" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -35856,7 +35859,7 @@
         <v>1798</v>
       </c>
       <c r="W436" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -35921,7 +35924,7 @@
         <v>1799</v>
       </c>
       <c r="W437" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -35986,7 +35989,7 @@
         <v>1800</v>
       </c>
       <c r="W438" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36051,7 +36054,7 @@
         <v>1801</v>
       </c>
       <c r="W439" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36116,16 +36119,16 @@
         <v>1802</v>
       </c>
       <c r="W440" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X440" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="Y440" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z440" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36190,16 +36193,16 @@
         <v>1803</v>
       </c>
       <c r="W441" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X441" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y441" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z441" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36264,16 +36267,16 @@
         <v>1804</v>
       </c>
       <c r="W442" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X442" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="Y442" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z442" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36338,7 +36341,7 @@
         <v>1805</v>
       </c>
       <c r="W443" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36403,7 +36406,7 @@
         <v>1806</v>
       </c>
       <c r="W444" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36468,16 +36471,16 @@
         <v>1803</v>
       </c>
       <c r="W445" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X445" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y445" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z445" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36542,16 +36545,16 @@
         <v>1803</v>
       </c>
       <c r="W446" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X446" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y446" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z446" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36616,16 +36619,16 @@
         <v>1807</v>
       </c>
       <c r="W447" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X447" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="Y447" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z447" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36690,16 +36693,16 @@
         <v>1803</v>
       </c>
       <c r="W448" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X448" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y448" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z448" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36764,16 +36767,16 @@
         <v>1803</v>
       </c>
       <c r="W449" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X449" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y449" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z449" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -36838,16 +36841,16 @@
         <v>1808</v>
       </c>
       <c r="W450" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X450" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y450" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z450" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -36912,16 +36915,16 @@
         <v>1809</v>
       </c>
       <c r="W451" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X451" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="Y451" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z451" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -36986,7 +36989,7 @@
         <v>1810</v>
       </c>
       <c r="W452" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37051,16 +37054,16 @@
         <v>1811</v>
       </c>
       <c r="W453" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X453" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="Y453" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z453" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37125,16 +37128,16 @@
         <v>1812</v>
       </c>
       <c r="W454" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X454" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="Y454" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z454" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37199,16 +37202,16 @@
         <v>1813</v>
       </c>
       <c r="W455" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X455" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y455" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z455" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37273,16 +37276,16 @@
         <v>1814</v>
       </c>
       <c r="W456" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X456" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="Y456" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z456" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37347,7 +37350,7 @@
         <v>1815</v>
       </c>
       <c r="W457" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37412,7 +37415,7 @@
         <v>1815</v>
       </c>
       <c r="W458" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37477,16 +37480,16 @@
         <v>1813</v>
       </c>
       <c r="W459" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X459" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y459" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z459" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37551,16 +37554,16 @@
         <v>1816</v>
       </c>
       <c r="W460" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X460" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="Y460" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z460" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37625,16 +37628,16 @@
         <v>1817</v>
       </c>
       <c r="W461" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X461" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="Y461" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z461" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37699,7 +37702,7 @@
         <v>1818</v>
       </c>
       <c r="W462" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37764,16 +37767,16 @@
         <v>1819</v>
       </c>
       <c r="W463" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X463" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="Y463" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z463" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -37838,16 +37841,16 @@
         <v>1820</v>
       </c>
       <c r="W464" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X464" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="Y464" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z464" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -37912,16 +37915,16 @@
         <v>1821</v>
       </c>
       <c r="W465" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X465" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="Y465" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z465" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -37986,7 +37989,7 @@
         <v>1822</v>
       </c>
       <c r="W466" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38051,16 +38054,16 @@
         <v>1823</v>
       </c>
       <c r="W467" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X467" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="Y467" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z467" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38125,16 +38128,16 @@
         <v>1824</v>
       </c>
       <c r="W468" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X468" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="Y468" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z468" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38199,16 +38202,16 @@
         <v>1825</v>
       </c>
       <c r="W469" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X469" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="Y469" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z469" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38273,16 +38276,16 @@
         <v>1826</v>
       </c>
       <c r="W470" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X470" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="Y470" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z470" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38347,7 +38350,7 @@
         <v>1827</v>
       </c>
       <c r="W471" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38412,16 +38415,16 @@
         <v>1828</v>
       </c>
       <c r="W472" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X472" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="Y472" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z472" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38486,16 +38489,16 @@
         <v>1828</v>
       </c>
       <c r="W473" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X473" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="Y473" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z473" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38560,7 +38563,7 @@
         <v>1829</v>
       </c>
       <c r="W474" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38625,16 +38628,16 @@
         <v>1830</v>
       </c>
       <c r="W475" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X475" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="Y475" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z475" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38699,16 +38702,16 @@
         <v>1831</v>
       </c>
       <c r="W476" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X476" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="Y476" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z476" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38773,7 +38776,7 @@
         <v>1832</v>
       </c>
       <c r="W477" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -38838,7 +38841,7 @@
         <v>1833</v>
       </c>
       <c r="W478" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -38903,16 +38906,16 @@
         <v>1834</v>
       </c>
       <c r="W479" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X479" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="Y479" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z479" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -38977,16 +38980,16 @@
         <v>1835</v>
       </c>
       <c r="W480" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X480" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Y480" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z480" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39051,16 +39054,16 @@
         <v>1836</v>
       </c>
       <c r="W481" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X481" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="Y481" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z481" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39125,7 +39128,7 @@
         <v>1837</v>
       </c>
       <c r="W482" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39190,7 +39193,7 @@
         <v>1838</v>
       </c>
       <c r="W483" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39258,13 +39261,13 @@
         <v>1839</v>
       </c>
       <c r="W484" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39329,7 +39332,7 @@
         <v>1840</v>
       </c>
       <c r="W485" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39397,13 +39400,13 @@
         <v>1841</v>
       </c>
       <c r="W486" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39468,7 +39471,7 @@
         <v>1842</v>
       </c>
       <c r="W487" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39533,16 +39536,16 @@
         <v>1843</v>
       </c>
       <c r="W488" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X488" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Y488" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z488" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39607,7 +39610,7 @@
         <v>1844</v>
       </c>
       <c r="W489" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39675,13 +39678,13 @@
         <v>1845</v>
       </c>
       <c r="W490" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39746,16 +39749,16 @@
         <v>1846</v>
       </c>
       <c r="W491" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X491" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="Y491" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z491" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -39820,16 +39823,16 @@
         <v>1847</v>
       </c>
       <c r="W492" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X492" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="Y492" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z492" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -39894,16 +39897,16 @@
         <v>1848</v>
       </c>
       <c r="W493" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X493" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="Y493" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z493" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -39968,13 +39971,13 @@
         <v>1849</v>
       </c>
       <c r="W494" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X494" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="Y494" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40039,16 +40042,16 @@
         <v>1850</v>
       </c>
       <c r="W495" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X495" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="Y495" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z495" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40113,7 +40116,7 @@
         <v>1851</v>
       </c>
       <c r="W496" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40181,7 +40184,7 @@
         <v>1852</v>
       </c>
       <c r="W497" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40246,7 +40249,7 @@
         <v>1853</v>
       </c>
       <c r="W498" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40314,7 +40317,7 @@
         <v>1854</v>
       </c>
       <c r="W499" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40379,16 +40382,16 @@
         <v>1855</v>
       </c>
       <c r="W500" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X500" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="Y500" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z500" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40453,16 +40456,16 @@
         <v>1856</v>
       </c>
       <c r="W501" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X501" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="Y501" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z501" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40527,7 +40530,7 @@
         <v>1857</v>
       </c>
       <c r="W502" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40595,7 +40598,7 @@
         <v>1858</v>
       </c>
       <c r="W503" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40663,16 +40666,16 @@
         <v>1859</v>
       </c>
       <c r="W504" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X504" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="Y504" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z504" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40737,7 +40740,7 @@
         <v>1860</v>
       </c>
       <c r="W505" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40802,16 +40805,16 @@
         <v>1861</v>
       </c>
       <c r="W506" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X506" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="Y506" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z506" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -40876,7 +40879,7 @@
         <v>1862</v>
       </c>
       <c r="W507" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -40941,7 +40944,7 @@
         <v>1863</v>
       </c>
       <c r="W508" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41006,16 +41009,16 @@
         <v>1864</v>
       </c>
       <c r="W509" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X509" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="Y509" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z509" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41080,16 +41083,16 @@
         <v>1865</v>
       </c>
       <c r="W510" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X510" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Y510" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z510" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41157,7 +41160,7 @@
         <v>1866</v>
       </c>
       <c r="W511" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41225,7 +41228,7 @@
         <v>1867</v>
       </c>
       <c r="W512" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41293,7 +41296,7 @@
         <v>1868</v>
       </c>
       <c r="W513" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41361,7 +41364,7 @@
         <v>1868</v>
       </c>
       <c r="W514" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41429,7 +41432,7 @@
         <v>1868</v>
       </c>
       <c r="W515" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41497,13 +41500,13 @@
         <v>1869</v>
       </c>
       <c r="W516" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41571,13 +41574,13 @@
         <v>1870</v>
       </c>
       <c r="W517" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41645,16 +41648,16 @@
         <v>1871</v>
       </c>
       <c r="W518" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X518" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="Y518" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z518" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41722,16 +41725,16 @@
         <v>1872</v>
       </c>
       <c r="W519" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X519" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="Y519" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z519" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41796,7 +41799,7 @@
         <v>1475</v>
       </c>
       <c r="W520" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -41864,7 +41867,7 @@
         <v>1873</v>
       </c>
       <c r="W521" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -41932,7 +41935,7 @@
         <v>1873</v>
       </c>
       <c r="W522" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42000,7 +42003,7 @@
         <v>1874</v>
       </c>
       <c r="W523" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42068,7 +42071,7 @@
         <v>1875</v>
       </c>
       <c r="W524" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42136,7 +42139,7 @@
         <v>1876</v>
       </c>
       <c r="W525" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42204,7 +42207,7 @@
         <v>1877</v>
       </c>
       <c r="W526" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42272,7 +42275,7 @@
         <v>1878</v>
       </c>
       <c r="W527" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42337,7 +42340,7 @@
         <v>1879</v>
       </c>
       <c r="W528" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42405,7 +42408,7 @@
         <v>1880</v>
       </c>
       <c r="W529" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42473,16 +42476,16 @@
         <v>1881</v>
       </c>
       <c r="W530" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X530" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="Y530" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z530" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42550,7 +42553,7 @@
         <v>1882</v>
       </c>
       <c r="W531" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42615,7 +42618,7 @@
         <v>1883</v>
       </c>
       <c r="W532" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42683,16 +42686,16 @@
         <v>1884</v>
       </c>
       <c r="W533" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X533" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="Y533" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z533" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42760,13 +42763,13 @@
         <v>1885</v>
       </c>
       <c r="W534" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -42834,7 +42837,7 @@
         <v>1886</v>
       </c>
       <c r="W535" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -42902,7 +42905,7 @@
         <v>1887</v>
       </c>
       <c r="W536" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -42970,16 +42973,16 @@
         <v>1888</v>
       </c>
       <c r="W537" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X537" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="Y537" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z537" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43047,7 +43050,7 @@
         <v>1889</v>
       </c>
       <c r="W538" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43115,7 +43118,7 @@
         <v>1890</v>
       </c>
       <c r="W539" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43183,7 +43186,7 @@
         <v>1891</v>
       </c>
       <c r="W540" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43251,7 +43254,7 @@
         <v>1892</v>
       </c>
       <c r="W541" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43319,16 +43322,16 @@
         <v>1893</v>
       </c>
       <c r="W542" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X542" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="Y542" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z542" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43396,7 +43399,7 @@
         <v>1894</v>
       </c>
       <c r="W543" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43464,16 +43467,16 @@
         <v>1895</v>
       </c>
       <c r="W544" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="X544" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="Y544" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z544" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43541,7 +43544,7 @@
         <v>1896</v>
       </c>
       <c r="W545" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43609,7 +43612,7 @@
         <v>1897</v>
       </c>
       <c r="W546" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43677,7 +43680,7 @@
         <v>1898</v>
       </c>
       <c r="W547" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43745,7 +43748,7 @@
         <v>1899</v>
       </c>
       <c r="W548" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -43813,7 +43816,7 @@
         <v>1899</v>
       </c>
       <c r="W549" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -43881,7 +43884,7 @@
         <v>1900</v>
       </c>
       <c r="W550" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -43946,7 +43949,7 @@
         <v>1901</v>
       </c>
       <c r="W551" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44014,7 +44017,7 @@
         <v>1902</v>
       </c>
       <c r="W552" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44079,7 +44082,7 @@
         <v>1903</v>
       </c>
       <c r="W553" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44147,7 +44150,7 @@
         <v>1904</v>
       </c>
       <c r="W554" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44215,7 +44218,7 @@
         <v>1905</v>
       </c>
       <c r="W555" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44283,7 +44286,7 @@
         <v>1906</v>
       </c>
       <c r="W556" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44348,7 +44351,7 @@
         <v>1907</v>
       </c>
       <c r="W557" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44416,7 +44419,7 @@
         <v>1908</v>
       </c>
       <c r="W558" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44484,7 +44487,7 @@
         <v>1909</v>
       </c>
       <c r="W559" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44549,7 +44552,7 @@
         <v>1910</v>
       </c>
       <c r="W560" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44617,7 +44620,7 @@
         <v>1911</v>
       </c>
       <c r="W561" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44667,10 +44670,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="R562">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="S562" t="s">
         <v>1472</v>
@@ -44679,10 +44682,10 @@
         <v>1473</v>
       </c>
       <c r="V562" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="W562" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44747,7 +44750,7 @@
         <v>1912</v>
       </c>
       <c r="W563" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -44800,10 +44803,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="R564">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S564" t="s">
         <v>1472</v>
@@ -44812,10 +44815,10 @@
         <v>1473</v>
       </c>
       <c r="V564" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="W564" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA564" t="b">
         <v>1</v>
@@ -44883,7 +44886,7 @@
         <v>1913</v>
       </c>
       <c r="W565" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -44951,7 +44954,7 @@
         <v>1914</v>
       </c>
       <c r="W566" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45019,7 +45022,7 @@
         <v>1915</v>
       </c>
       <c r="W567" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45069,10 +45072,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="R568">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S568" t="s">
         <v>1472</v>
@@ -45084,10 +45087,10 @@
         <v>1916</v>
       </c>
       <c r="V568" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="W568" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA568" t="b">
         <v>1</v>
@@ -45155,7 +45158,7 @@
         <v>1917</v>
       </c>
       <c r="W569" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45220,7 +45223,7 @@
         <v>1918</v>
       </c>
       <c r="W570" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45285,7 +45288,7 @@
         <v>1919</v>
       </c>
       <c r="W571" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45353,7 +45356,7 @@
         <v>1920</v>
       </c>
       <c r="W572" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45421,7 +45424,7 @@
         <v>1921</v>
       </c>
       <c r="W573" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45489,7 +45492,7 @@
         <v>1922</v>
       </c>
       <c r="W574" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45539,10 +45542,10 @@
         <v>46255</v>
       </c>
       <c r="Q575">
-        <v>-21</v>
+        <v>-18</v>
       </c>
       <c r="R575">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S575" t="s">
         <v>1472</v>
@@ -45551,10 +45554,10 @@
         <v>1472</v>
       </c>
       <c r="V575" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="W575" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA575" t="b">
         <v>1</v>
@@ -45622,7 +45625,7 @@
         <v>1923</v>
       </c>
       <c r="W576" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45690,7 +45693,7 @@
         <v>1923</v>
       </c>
       <c r="W577" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45758,7 +45761,7 @@
         <v>1924</v>
       </c>
       <c r="W578" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -45807,9 +45810,6 @@
       <c r="N579" s="1">
         <v>46242</v>
       </c>
-      <c r="O579" s="1">
-        <v>46232</v>
-      </c>
       <c r="P579" t="s">
         <v>1471</v>
       </c>
@@ -45828,11 +45828,8 @@
       <c r="U579" t="s">
         <v>1925</v>
       </c>
-      <c r="V579" t="s">
-        <v>1932</v>
-      </c>
       <c r="W579" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -45885,10 +45882,10 @@
         <v>1471</v>
       </c>
       <c r="Q580">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="R580">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S580" t="s">
         <v>1472</v>
@@ -45899,11 +45896,8 @@
       <c r="U580" t="s">
         <v>1926</v>
       </c>
-      <c r="V580" t="s">
-        <v>1933</v>
-      </c>
       <c r="W580" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -45953,10 +45947,10 @@
         <v>46265</v>
       </c>
       <c r="Q581">
-        <v>-31</v>
+        <v>-28</v>
       </c>
       <c r="R581">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S581" t="s">
         <v>1472</v>
@@ -45965,7 +45959,7 @@
         <v>1473</v>
       </c>
       <c r="W581" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA581" t="b">
         <v>1</v>
@@ -46015,10 +46009,10 @@
         <v>46265</v>
       </c>
       <c r="Q582">
-        <v>-31</v>
+        <v>-28</v>
       </c>
       <c r="R582">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S582" t="s">
         <v>1472</v>
@@ -46026,8 +46020,14 @@
       <c r="T582" t="s">
         <v>1473</v>
       </c>
+      <c r="U582" t="s">
+        <v>1927</v>
+      </c>
+      <c r="V582" t="s">
+        <v>1933</v>
+      </c>
       <c r="W582" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA582" t="b">
         <v>1</v>
@@ -46077,10 +46077,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-31</v>
+        <v>-28</v>
       </c>
       <c r="R583">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S583" t="s">
         <v>1472</v>
@@ -46088,8 +46088,11 @@
       <c r="T583" t="s">
         <v>1473</v>
       </c>
+      <c r="V583" t="s">
+        <v>1934</v>
+      </c>
       <c r="W583" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="AA583" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32498,10 +32498,10 @@
         <v>1393</v>
       </c>
       <c r="Q386">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R386">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S386" t="s">
         <v>1473</v>
@@ -33837,10 +33837,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R406">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S406" t="s">
         <v>1472</v>
@@ -44670,10 +44670,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R562">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S562" t="s">
         <v>1472</v>
@@ -44803,10 +44803,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R564">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S564" t="s">
         <v>1472</v>
@@ -45072,10 +45072,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="R568">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S568" t="s">
         <v>1472</v>
@@ -45542,10 +45542,10 @@
         <v>46255</v>
       </c>
       <c r="Q575">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="R575">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S575" t="s">
         <v>1472</v>
@@ -45882,10 +45882,10 @@
         <v>1471</v>
       </c>
       <c r="Q580">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R580">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S580" t="s">
         <v>1472</v>
@@ -45947,10 +45947,10 @@
         <v>46265</v>
       </c>
       <c r="Q581">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="R581">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S581" t="s">
         <v>1472</v>
@@ -46009,10 +46009,10 @@
         <v>46265</v>
       </c>
       <c r="Q582">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="R582">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S582" t="s">
         <v>1472</v>
@@ -46077,10 +46077,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="R583">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S583" t="s">
         <v>1472</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32510,10 +32510,10 @@
         <v>1397</v>
       </c>
       <c r="Q386">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R386">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S386" t="s">
         <v>1477</v>
@@ -33849,10 +33849,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R406">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S406" t="s">
         <v>1476</v>
@@ -44682,10 +44682,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R562">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S562" t="s">
         <v>1476</v>
@@ -44815,10 +44815,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R564">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S564" t="s">
         <v>1476</v>
@@ -45084,10 +45084,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R568">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S568" t="s">
         <v>1476</v>
@@ -45554,10 +45554,10 @@
         <v>46255</v>
       </c>
       <c r="Q575">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="R575">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S575" t="s">
         <v>1476</v>
@@ -45894,10 +45894,10 @@
         <v>1475</v>
       </c>
       <c r="Q580">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R580">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S580" t="s">
         <v>1476</v>
@@ -45959,10 +45959,10 @@
         <v>46265</v>
       </c>
       <c r="Q581">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R581">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S581" t="s">
         <v>1476</v>
@@ -46021,10 +46021,10 @@
         <v>46265</v>
       </c>
       <c r="Q582">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R582">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S582" t="s">
         <v>1476</v>
@@ -46089,10 +46089,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R583">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S583" t="s">
         <v>1476</v>
@@ -46154,10 +46154,10 @@
         <v>46249</v>
       </c>
       <c r="Q584">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R584">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S584" t="s">
         <v>1477</v>
@@ -46216,10 +46216,10 @@
         <v>46245</v>
       </c>
       <c r="Q585">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R585">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S585" t="s">
         <v>1476</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -5824,10 +5824,10 @@
     <t>AWB: 127-5104 0312 entregue em 05/08. Ramon 05/08/26.</t>
   </si>
   <si>
-    <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron WB0003068789 - previsão de entrega 60 dias em média. Os demais fornecedores informaram não ter em estoque ou não possuírem a certificação necessária da peça.</t>
-  </si>
-  <si>
-    <t>Colocado pedido junto ao fornecedor LEGACY PARTS, previsão de entrega em Miami 05/08</t>
+    <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron J17626242 - previsão de entrega em Miami 05/08</t>
+  </si>
+  <si>
+    <t>Colocado pedido junto ao fornecedor LEGACY PARTS, previsão de entrega em Miami 06/08</t>
   </si>
   <si>
     <t>Colocado pedido Textron IJ17575583 - entregue em Miami 15/07. Carga rercepcionada GIG 19/07 - Aguardando liberação do SEFAZ. ATZ 21/07 - material em processo de expedição RC 23/07/2026 - MATERIAL ENVIADO PELO RECIBO 639/FAB/26 AWB A SER GERADA</t>
@@ -46154,7 +46154,7 @@
         <v>2709</v>
       </c>
       <c r="H584" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="I584" t="s">
         <v>1246</v>
@@ -46222,7 +46222,7 @@
         <v>2720</v>
       </c>
       <c r="H585" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="I585" t="s">
         <v>1245</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32522,10 +32522,10 @@
         <v>1399</v>
       </c>
       <c r="Q386">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R386">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S386" t="s">
         <v>1480</v>
@@ -33861,10 +33861,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R406">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S406" t="s">
         <v>1479</v>
@@ -44694,10 +44694,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R562">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S562" t="s">
         <v>1479</v>
@@ -44827,10 +44827,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R564">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S564" t="s">
         <v>1479</v>
@@ -45096,10 +45096,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R568">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S568" t="s">
         <v>1479</v>
@@ -45569,10 +45569,10 @@
         <v>46240</v>
       </c>
       <c r="Q575">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R575">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S575" t="s">
         <v>1479</v>
@@ -45909,10 +45909,10 @@
         <v>1477</v>
       </c>
       <c r="Q580">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R580">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S580" t="s">
         <v>1479</v>
@@ -45977,10 +45977,10 @@
         <v>46239</v>
       </c>
       <c r="Q581">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R581">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S581" t="s">
         <v>1479</v>
@@ -46045,10 +46045,10 @@
         <v>46239</v>
       </c>
       <c r="Q582">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R582">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S582" t="s">
         <v>1479</v>
@@ -46113,10 +46113,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R583">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S583" t="s">
         <v>1479</v>
@@ -46311,10 +46311,10 @@
         <v>46266</v>
       </c>
       <c r="Q586">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R586">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S586" t="s">
         <v>1479</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -46299,7 +46299,7 @@
         <v>46238</v>
       </c>
       <c r="K586" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="L586">
         <v>1</v>
@@ -46308,13 +46308,13 @@
         <v>1247</v>
       </c>
       <c r="N586" s="1">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-26</v>
+        <v>-29</v>
       </c>
       <c r="R586">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S586" t="s">
         <v>1479</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32522,10 +32522,10 @@
         <v>1399</v>
       </c>
       <c r="Q386">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R386">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S386" t="s">
         <v>1480</v>
@@ -33861,10 +33861,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R406">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S406" t="s">
         <v>1479</v>
@@ -44694,10 +44694,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R562">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S562" t="s">
         <v>1479</v>
@@ -44827,10 +44827,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="R564">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S564" t="s">
         <v>1479</v>
@@ -45096,10 +45096,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R568">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S568" t="s">
         <v>1479</v>
@@ -45569,10 +45569,10 @@
         <v>46240</v>
       </c>
       <c r="Q575">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="R575">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S575" t="s">
         <v>1479</v>
@@ -45909,10 +45909,10 @@
         <v>1477</v>
       </c>
       <c r="Q580">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R580">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S580" t="s">
         <v>1479</v>
@@ -45977,10 +45977,10 @@
         <v>46239</v>
       </c>
       <c r="Q581">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R581">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S581" t="s">
         <v>1479</v>
@@ -46045,10 +46045,10 @@
         <v>46239</v>
       </c>
       <c r="Q582">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R582">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S582" t="s">
         <v>1479</v>
@@ -46113,10 +46113,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R583">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S583" t="s">
         <v>1479</v>
@@ -46311,10 +46311,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R586">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S586" t="s">
         <v>1479</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -45885,7 +45885,7 @@
         <v>2728</v>
       </c>
       <c r="H580" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="I580" t="s">
         <v>1246</v>
@@ -45909,10 +45909,10 @@
         <v>1477</v>
       </c>
       <c r="Q580">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="R580">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S580" t="s">
         <v>1479</v>
@@ -46290,7 +46290,7 @@
         <v>2733</v>
       </c>
       <c r="H586" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="I586" t="s">
         <v>1244</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -32528,10 +32528,10 @@
         <v>1401</v>
       </c>
       <c r="Q386">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R386">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S386" t="s">
         <v>1482</v>
@@ -33867,10 +33867,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="R406">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="S406" t="s">
         <v>1481</v>
@@ -44700,10 +44700,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="R562">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S562" t="s">
         <v>1481</v>
@@ -44833,10 +44833,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R564">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S564" t="s">
         <v>1481</v>
@@ -45102,10 +45102,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="R568">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="S568" t="s">
         <v>1481</v>
@@ -45575,10 +45575,10 @@
         <v>46240</v>
       </c>
       <c r="Q575">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="R575">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S575" t="s">
         <v>1481</v>
@@ -45983,10 +45983,10 @@
         <v>46239</v>
       </c>
       <c r="Q581">
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="R581">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S581" t="s">
         <v>1481</v>
@@ -46051,10 +46051,10 @@
         <v>46239</v>
       </c>
       <c r="Q582">
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="R582">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S582" t="s">
         <v>1481</v>
@@ -46119,10 +46119,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="R583">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S583" t="s">
         <v>1481</v>
@@ -46317,10 +46317,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="R586">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S586" t="s">
         <v>1481</v>
@@ -46376,10 +46376,10 @@
         <v>46246</v>
       </c>
       <c r="Q587">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="R587">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S587" t="s">
         <v>1481</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -33882,10 +33882,10 @@
         <v>46287</v>
       </c>
       <c r="Q406">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R406">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S406" t="s">
         <v>1485</v>
@@ -44715,10 +44715,10 @@
         <v>46243</v>
       </c>
       <c r="Q562">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R562">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S562" t="s">
         <v>1485</v>
@@ -44848,10 +44848,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R564">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S564" t="s">
         <v>1485</v>
@@ -45117,10 +45117,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R568">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S568" t="s">
         <v>1485</v>
@@ -45590,10 +45590,10 @@
         <v>46240</v>
       </c>
       <c r="Q575">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R575">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S575" t="s">
         <v>1485</v>
@@ -46072,10 +46072,10 @@
         <v>46239</v>
       </c>
       <c r="Q582">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="R582">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S582" t="s">
         <v>1485</v>
@@ -46140,10 +46140,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="R583">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S583" t="s">
         <v>1485</v>
@@ -46338,10 +46338,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R586">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S586" t="s">
         <v>1485</v>
@@ -46400,10 +46400,10 @@
         <v>46246</v>
       </c>
       <c r="Q587">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R587">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S587" t="s">
         <v>1485</v>
@@ -46459,10 +46459,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R588">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S588" t="s">
         <v>1486</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -5854,7 +5854,7 @@
     <t>AWB: 127-5104 0312 entregue em 05/08. Ramon 05/08/26.</t>
   </si>
   <si>
-    <t>item atendido com o estoque local pedido 18171852 em 10/08. Godoy 11/08.</t>
+    <t>item atendido com o estoque local pedido 18171852 em 10/08. Godoy 11/08. Está sendo definido se o PN está correto. Ramon 11/08/26.</t>
   </si>
   <si>
     <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron J17626242 - previsão de entrega em Miami 05/08 AWB4238 em desembaraço no GIGRJ em 06/8/2026, previsao de CANAL hoje às 18 horas ATZ Marcio 6/8/2026 - MATERIAL EM RECEBIMENTO VEE ONE 07/08/2026 16:31, SERÁ ENVIADO NA SEGUNDA FEIRA</t>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7388" uniqueCount="2327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7391" uniqueCount="2329">
   <si>
     <t>om_emg</t>
   </si>
@@ -5833,6 +5833,9 @@
     <t>AWB 127-4858 1702 retirado em 27/07. Recibo 592/FAB/26 assinado em 27/07. Ramon 28/07/26</t>
   </si>
   <si>
+    <t>AWB 12750991113 volume retirado na loja GOLLOG - BSB por MICHELLIBCRISTINI DE BARROS em 10/08. Godoy 12/08/26.</t>
+  </si>
+  <si>
     <t>AWB 12748301050 - volume retirado na loja GOLLOG - BSB por MARIO JORGE BARRIOLi em 21/07. Godoy 23/07/26.  Emerg atendida pela GMM 202667292001554 no dia 21/07/2026. Godoy 24/07/2026.</t>
   </si>
   <si>
@@ -5848,7 +5851,7 @@
     <t>Atendido pelo recibo 645/FAB/2026 em 06/08/2026. Godoy 10/08/2026.</t>
   </si>
   <si>
-    <t>Atendido 01 EA através da TSP 18122931. Outros 02 EA serão enviados pela empresa. Ramon 03/08/26.</t>
+    <t>Atendido 01 EA através da TSP 18122931. Outros 02 EA serão enviados pela empresa. Ramon 03/08/26. AWB 12750821282 volume retirado na loja GOLLOG - MAO por kleyton EM 06/08. Godoy 12/08/26.</t>
   </si>
   <si>
     <t>AWB: 127-5104 0312 entregue em 05/08. Ramon 05/08/26.</t>
@@ -5857,25 +5860,28 @@
     <t>item atendido com o estoque local pedido 18171852 em 10/08. Godoy 11/08. Está sendo definido se o PN está correto. Ramon 11/08/26.</t>
   </si>
   <si>
-    <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron J17626242 - previsão de entrega em Miami 05/08 AWB4238 em desembaraço no GIGRJ em 06/8/2026, previsao de CANAL hoje às 18 horas ATZ Marcio 6/8/2026 - MATERIAL EM RECEBIMENTO VEE ONE 07/08/2026 16:31, SERÁ ENVIADO NA SEGUNDA FEIRA</t>
-  </si>
-  <si>
-    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - previsão de entrega em Miami 12/08</t>
+    <t>Estoque com 12 EA do Pn LM600-9 (Alternado), Godoy 12/08/26.</t>
+  </si>
+  <si>
+    <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron J17626242 - previsão de entrega em Miami 05/08 AWB4238 em desembaraço no GIGRJ em 06/8/2026, previsao de CANAL hoje às 18 horas ATZ Marcio 6/8/2026 - MATERIAL EM RECEBIMENTO VEE ONE 07/08/2026 16:31, SERÁ ENVIADO NA SEGUNDA FEIRA - AWB 12752106375 dpe 14/08/2026</t>
+  </si>
+  <si>
+    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - previsão de entrega em Miami 11/08</t>
   </si>
   <si>
     <t>Colocado pedido Textron IJ17575583 - entregue em Miami 15/07. Carga rercepcionada GIG 19/07 - Aguardando liberação do SEFAZ. ATZ 21/07 - material em processo de expedição RC 23/07/2026 - MATERIAL ENVIADO PELO RECIBO 639/FAB/26 - AWB 12750389603 DPE 13/08/2026</t>
   </si>
   <si>
-    <t>Item em bancada porem em pessimo estado, foi solicitado recolhimento de mais unidades para envio a oficina para tentativa de reparo ATZ Marcio 17/7/26. Solicitado abertura de O.S. para 3EA do item no dia 16-07-26 via Email para a Coordenadoria - CLA-21-07-26</t>
-  </si>
-  <si>
-    <t>Pedido I816822 entregue em Miami 27/07. Previsão de chegada GIG 30/07 (voo 4208). Previsão de canal 31/07 - MATERIAL RECEBIDO NA VEE ONE, EM PROCESSO DE EXPEDIÇÃO 04/08/2026 - ATZ RC - MATERIAL ENVIADO VIA RECIBO 650/FAB/26 - AWB 12750991113 DPE 06/08/2026, ESTÁ DISPONÍVEL PARA RETIRADA DESDE 04/08/2026</t>
+    <t>Item em bancada porem em pessimo estado, foi solicitado recolhimento de mais unidades para envio a oficina para tentativa de reparo ATZ Marcio 17/7/26. Solicitado abertura de O.S. para 3EA do item no dia 16-07-26 via Email para a Coordenadoria - CLA-21-07-26- SERÁ ENTREGUE PELA WILLIAM DPE DIA 12-08-26 - CLA-11-08</t>
+  </si>
+  <si>
+    <t>Pedido I816822 entregue em Miami 27/07. Previsão de chegada GIG 30/07 (voo 4208). Previsão de canal 31/07 - MATERIAL RECEBIDO NA VEE ONE, EM PROCESSO DE EXPEDIÇÃO 04/08/2026 - ATZ RC - MATERIAL ENVIADO VIA RECIBO 650/FAB/26 - AWB 12750991113 DPE 06/08/2026, ESTÁ DISPONÍVEL PARA RETIRADA DESDE 04/08/2026 - retirado na Gollog dia 10/08/2026</t>
   </si>
   <si>
     <t>Enviado para o Operador(02 EA), atendimento parcial, em 31/07/2026 -AWB 127-5041 6833- REZ - o outro 1 EA será atendido pelo estoque FAB. conforme solicitado por Email- CLA-03-08 - AWB 127-5082 1282 -1 EA ENVIADO ESTOQUE FAB - Material entregue dia 06/08/2026</t>
   </si>
   <si>
-    <t>Temos 4 EA em manutenção na William, será pedido prioridade. CLA-03-08</t>
+    <t>Foi solicitado abertura de O.S. no dia 7 -08-26 de 6 EA. As OSs foram abertas e aguardando recolhimento para reparo. CLA-10-08 - ITEM FOI RECOLHIDO PELA WILLIAM- CLA-11-08</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7472,7 +7478,7 @@
         <v>1492</v>
       </c>
       <c r="W2" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7534,16 +7540,16 @@
         <v>1493</v>
       </c>
       <c r="W3" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X3" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="Y3" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z3" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7605,7 +7611,7 @@
         <v>1492</v>
       </c>
       <c r="W4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7667,7 +7673,7 @@
         <v>1494</v>
       </c>
       <c r="W5" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7729,7 +7735,7 @@
         <v>1495</v>
       </c>
       <c r="W6" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7791,7 +7797,7 @@
         <v>1496</v>
       </c>
       <c r="W7" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7853,7 +7859,7 @@
         <v>1497</v>
       </c>
       <c r="W8" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7915,7 +7921,7 @@
         <v>1498</v>
       </c>
       <c r="W9" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -7977,7 +7983,7 @@
         <v>1499</v>
       </c>
       <c r="W10" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8039,7 +8045,7 @@
         <v>1500</v>
       </c>
       <c r="W11" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8101,7 +8107,7 @@
         <v>1501</v>
       </c>
       <c r="W12" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8163,7 +8169,7 @@
         <v>1497</v>
       </c>
       <c r="W13" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8225,16 +8231,16 @@
         <v>1502</v>
       </c>
       <c r="W14" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X14" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="Y14" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z14" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8293,7 +8299,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8358,7 +8364,7 @@
         <v>1503</v>
       </c>
       <c r="W16" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8420,7 +8426,7 @@
         <v>1504</v>
       </c>
       <c r="W17" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8482,7 +8488,7 @@
         <v>1495</v>
       </c>
       <c r="W18" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8544,7 +8550,7 @@
         <v>1495</v>
       </c>
       <c r="W19" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8606,7 +8612,7 @@
         <v>1505</v>
       </c>
       <c r="W20" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8668,7 +8674,7 @@
         <v>1506</v>
       </c>
       <c r="W21" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8730,7 +8736,7 @@
         <v>1506</v>
       </c>
       <c r="W22" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8792,7 +8798,7 @@
         <v>1507</v>
       </c>
       <c r="W23" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8851,7 +8857,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -8910,7 +8916,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -8972,7 +8978,7 @@
         <v>1495</v>
       </c>
       <c r="W26" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9031,7 +9037,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9090,7 +9096,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9152,7 +9158,7 @@
         <v>1508</v>
       </c>
       <c r="W29" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9211,7 +9217,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9273,7 +9279,7 @@
         <v>1509</v>
       </c>
       <c r="W31" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9335,7 +9341,7 @@
         <v>1510</v>
       </c>
       <c r="W32" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9397,7 +9403,7 @@
         <v>1511</v>
       </c>
       <c r="W33" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9459,7 +9465,7 @@
         <v>1512</v>
       </c>
       <c r="W34" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9521,7 +9527,7 @@
         <v>1513</v>
       </c>
       <c r="W35" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9583,7 +9589,7 @@
         <v>1509</v>
       </c>
       <c r="W36" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9645,7 +9651,7 @@
         <v>1514</v>
       </c>
       <c r="W37" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9707,7 +9713,7 @@
         <v>1492</v>
       </c>
       <c r="W38" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9769,7 +9775,7 @@
         <v>1511</v>
       </c>
       <c r="W39" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9831,7 +9837,7 @@
         <v>1515</v>
       </c>
       <c r="W40" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -9893,7 +9899,7 @@
         <v>1516</v>
       </c>
       <c r="W41" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -9955,16 +9961,16 @@
         <v>1517</v>
       </c>
       <c r="W42" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X42" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="Y42" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z42" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10026,7 +10032,7 @@
         <v>1511</v>
       </c>
       <c r="W43" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10088,7 +10094,7 @@
         <v>1518</v>
       </c>
       <c r="W44" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10150,7 +10156,7 @@
         <v>1511</v>
       </c>
       <c r="W45" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10212,7 +10218,7 @@
         <v>1511</v>
       </c>
       <c r="W46" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10274,7 +10280,7 @@
         <v>1519</v>
       </c>
       <c r="W47" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10336,7 +10342,7 @@
         <v>1520</v>
       </c>
       <c r="W48" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10398,7 +10404,7 @@
         <v>1521</v>
       </c>
       <c r="W49" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10460,7 +10466,7 @@
         <v>1522</v>
       </c>
       <c r="W50" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10522,7 +10528,7 @@
         <v>1523</v>
       </c>
       <c r="W51" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10584,7 +10590,7 @@
         <v>1512</v>
       </c>
       <c r="W52" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10646,7 +10652,7 @@
         <v>1506</v>
       </c>
       <c r="W53" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10708,7 +10714,7 @@
         <v>1506</v>
       </c>
       <c r="W54" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10770,7 +10776,7 @@
         <v>1506</v>
       </c>
       <c r="W55" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10832,7 +10838,7 @@
         <v>1524</v>
       </c>
       <c r="W56" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -10894,7 +10900,7 @@
         <v>1525</v>
       </c>
       <c r="W57" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -10956,16 +10962,16 @@
         <v>1526</v>
       </c>
       <c r="W58" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X58" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="Y58" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z58" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11027,7 +11033,7 @@
         <v>1527</v>
       </c>
       <c r="W59" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11089,7 +11095,7 @@
         <v>1528</v>
       </c>
       <c r="W60" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11151,7 +11157,7 @@
         <v>1506</v>
       </c>
       <c r="W61" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11213,7 +11219,7 @@
         <v>1529</v>
       </c>
       <c r="W62" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11272,7 +11278,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11331,7 +11337,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11390,7 +11396,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11449,7 +11455,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11508,7 +11514,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11567,7 +11573,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11629,7 +11635,7 @@
         <v>1530</v>
       </c>
       <c r="W69" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11691,7 +11697,7 @@
         <v>1528</v>
       </c>
       <c r="W70" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11753,7 +11759,7 @@
         <v>1513</v>
       </c>
       <c r="W71" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11815,7 +11821,7 @@
         <v>1531</v>
       </c>
       <c r="W72" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -11877,7 +11883,7 @@
         <v>1532</v>
       </c>
       <c r="W73" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -11939,16 +11945,16 @@
         <v>1533</v>
       </c>
       <c r="W74" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X74" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="Y74" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z74" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12010,16 +12016,16 @@
         <v>1534</v>
       </c>
       <c r="W75" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X75" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="Y75" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z75" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12081,7 +12087,7 @@
         <v>1513</v>
       </c>
       <c r="W76" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12143,7 +12149,7 @@
         <v>1513</v>
       </c>
       <c r="W77" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12205,10 +12211,10 @@
         <v>1535</v>
       </c>
       <c r="W78" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="Z78" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12273,7 +12279,7 @@
         <v>1536</v>
       </c>
       <c r="W79" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12332,7 +12338,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12391,7 +12397,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12453,7 +12459,7 @@
         <v>1537</v>
       </c>
       <c r="W82" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12515,7 +12521,7 @@
         <v>1538</v>
       </c>
       <c r="W83" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12577,7 +12583,7 @@
         <v>1539</v>
       </c>
       <c r="W84" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12636,7 +12642,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12698,7 +12704,7 @@
         <v>1540</v>
       </c>
       <c r="W86" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12760,7 +12766,7 @@
         <v>1541</v>
       </c>
       <c r="W87" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12822,7 +12828,7 @@
         <v>1541</v>
       </c>
       <c r="W88" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -12884,7 +12890,7 @@
         <v>1506</v>
       </c>
       <c r="W89" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -12946,16 +12952,16 @@
         <v>1542</v>
       </c>
       <c r="W90" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X90" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="Y90" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z90" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13017,16 +13023,16 @@
         <v>1543</v>
       </c>
       <c r="W91" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X91" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="Y91" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z91" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13088,7 +13094,7 @@
         <v>1544</v>
       </c>
       <c r="W92" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13150,7 +13156,7 @@
         <v>1545</v>
       </c>
       <c r="W93" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13212,7 +13218,7 @@
         <v>1545</v>
       </c>
       <c r="W94" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13274,7 +13280,7 @@
         <v>1546</v>
       </c>
       <c r="W95" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13336,16 +13342,16 @@
         <v>1547</v>
       </c>
       <c r="W96" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X96" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="Y96" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z96" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13407,7 +13413,7 @@
         <v>1548</v>
       </c>
       <c r="W97" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13469,7 +13475,7 @@
         <v>1549</v>
       </c>
       <c r="W98" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13531,7 +13537,7 @@
         <v>1550</v>
       </c>
       <c r="W99" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13593,7 +13599,7 @@
         <v>1551</v>
       </c>
       <c r="W100" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13655,16 +13661,16 @@
         <v>1552</v>
       </c>
       <c r="W101" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X101" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="Y101" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z101" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13726,7 +13732,7 @@
         <v>1553</v>
       </c>
       <c r="W102" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13788,7 +13794,7 @@
         <v>1553</v>
       </c>
       <c r="W103" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13850,7 +13856,7 @@
         <v>1554</v>
       </c>
       <c r="W104" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -13912,16 +13918,16 @@
         <v>1555</v>
       </c>
       <c r="W105" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X105" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="Y105" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z105" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -13983,16 +13989,16 @@
         <v>1556</v>
       </c>
       <c r="W106" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X106" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="Y106" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z106" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14054,7 +14060,7 @@
         <v>1557</v>
       </c>
       <c r="W107" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14116,16 +14122,16 @@
         <v>1558</v>
       </c>
       <c r="W108" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X108" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="Y108" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z108" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14187,16 +14193,16 @@
         <v>1559</v>
       </c>
       <c r="W109" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X109" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="Y109" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z109" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14255,7 +14261,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14317,16 +14323,16 @@
         <v>1560</v>
       </c>
       <c r="W111" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X111" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="Y111" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z111" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14388,16 +14394,16 @@
         <v>1561</v>
       </c>
       <c r="W112" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X112" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="Y112" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z112" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14459,16 +14465,16 @@
         <v>1562</v>
       </c>
       <c r="W113" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X113" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="Y113" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z113" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14530,16 +14536,16 @@
         <v>1563</v>
       </c>
       <c r="W114" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X114" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="Y114" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z114" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14601,16 +14607,16 @@
         <v>1559</v>
       </c>
       <c r="W115" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X115" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="Y115" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z115" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14672,16 +14678,16 @@
         <v>1559</v>
       </c>
       <c r="W116" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X116" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="Y116" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z116" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14743,16 +14749,16 @@
         <v>1564</v>
       </c>
       <c r="W117" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X117" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="Y117" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z117" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14814,16 +14820,16 @@
         <v>1565</v>
       </c>
       <c r="W118" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X118" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="Y118" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z118" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -14885,7 +14891,7 @@
         <v>1566</v>
       </c>
       <c r="W119" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -14947,16 +14953,16 @@
         <v>1567</v>
       </c>
       <c r="W120" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X120" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y120" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z120" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15018,16 +15024,16 @@
         <v>1567</v>
       </c>
       <c r="W121" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X121" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y121" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z121" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15089,16 +15095,16 @@
         <v>1567</v>
       </c>
       <c r="W122" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X122" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y122" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z122" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15160,16 +15166,16 @@
         <v>1567</v>
       </c>
       <c r="W123" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X123" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y123" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z123" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15231,16 +15237,16 @@
         <v>1567</v>
       </c>
       <c r="W124" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X124" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y124" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z124" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15302,16 +15308,16 @@
         <v>1567</v>
       </c>
       <c r="W125" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X125" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y125" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z125" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15373,16 +15379,16 @@
         <v>1567</v>
       </c>
       <c r="W126" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X126" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y126" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z126" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15444,16 +15450,16 @@
         <v>1568</v>
       </c>
       <c r="W127" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X127" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="Y127" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z127" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15515,16 +15521,16 @@
         <v>1569</v>
       </c>
       <c r="W128" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X128" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="Y128" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z128" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15586,16 +15592,16 @@
         <v>1567</v>
       </c>
       <c r="W129" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X129" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y129" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z129" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15657,16 +15663,16 @@
         <v>1567</v>
       </c>
       <c r="W130" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X130" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y130" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z130" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15728,7 +15734,7 @@
         <v>1570</v>
       </c>
       <c r="W131" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15787,7 +15793,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15846,7 +15852,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -15908,16 +15914,16 @@
         <v>1567</v>
       </c>
       <c r="W134" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X134" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y134" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z134" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -15979,16 +15985,16 @@
         <v>1567</v>
       </c>
       <c r="W135" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X135" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y135" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z135" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16050,7 +16056,7 @@
         <v>1566</v>
       </c>
       <c r="W136" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16109,7 +16115,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16171,16 +16177,16 @@
         <v>1571</v>
       </c>
       <c r="W138" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X138" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="Y138" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z138" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16242,16 +16248,16 @@
         <v>1559</v>
       </c>
       <c r="W139" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X139" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="Y139" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z139" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16313,16 +16319,16 @@
         <v>1567</v>
       </c>
       <c r="W140" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X140" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y140" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z140" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16381,7 +16387,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16440,7 +16446,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16502,16 +16508,16 @@
         <v>1572</v>
       </c>
       <c r="W143" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X143" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="Y143" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z143" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16573,16 +16579,16 @@
         <v>1573</v>
       </c>
       <c r="W144" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X144" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="Y144" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z144" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16644,16 +16650,16 @@
         <v>1574</v>
       </c>
       <c r="W145" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X145" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="Y145" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z145" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16715,16 +16721,16 @@
         <v>1575</v>
       </c>
       <c r="W146" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X146" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="Y146" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z146" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16783,7 +16789,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16845,7 +16851,7 @@
         <v>1576</v>
       </c>
       <c r="W148" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -16907,16 +16913,16 @@
         <v>1577</v>
       </c>
       <c r="W149" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X149" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="Y149" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z149" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -16978,7 +16984,7 @@
         <v>1578</v>
       </c>
       <c r="W150" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17040,16 +17046,16 @@
         <v>1579</v>
       </c>
       <c r="W151" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X151" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="Y151" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z151" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17111,7 +17117,7 @@
         <v>1578</v>
       </c>
       <c r="W152" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17173,7 +17179,7 @@
         <v>1576</v>
       </c>
       <c r="W153" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17235,7 +17241,7 @@
         <v>1578</v>
       </c>
       <c r="W154" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17297,7 +17303,7 @@
         <v>1578</v>
       </c>
       <c r="W155" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17359,16 +17365,16 @@
         <v>1580</v>
       </c>
       <c r="W156" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X156" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="Y156" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z156" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17430,7 +17436,7 @@
         <v>1576</v>
       </c>
       <c r="W157" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17492,16 +17498,16 @@
         <v>1581</v>
       </c>
       <c r="W158" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X158" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y158" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z158" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17563,16 +17569,16 @@
         <v>1582</v>
       </c>
       <c r="W159" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X159" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="Y159" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z159" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17634,16 +17640,16 @@
         <v>1581</v>
       </c>
       <c r="W160" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X160" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y160" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z160" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17705,16 +17711,16 @@
         <v>1581</v>
       </c>
       <c r="W161" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X161" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y161" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z161" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17776,16 +17782,16 @@
         <v>1581</v>
       </c>
       <c r="W162" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X162" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y162" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z162" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17847,16 +17853,16 @@
         <v>1583</v>
       </c>
       <c r="W163" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X163" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="Y163" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z163" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -17918,16 +17924,16 @@
         <v>1584</v>
       </c>
       <c r="W164" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X164" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="Y164" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z164" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -17989,16 +17995,16 @@
         <v>1585</v>
       </c>
       <c r="W165" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X165" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="Y165" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z165" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18060,16 +18066,16 @@
         <v>1586</v>
       </c>
       <c r="W166" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X166" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="Y166" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z166" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18131,16 +18137,16 @@
         <v>1564</v>
       </c>
       <c r="W167" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X167" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="Y167" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z167" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18202,16 +18208,16 @@
         <v>1567</v>
       </c>
       <c r="W168" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X168" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y168" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z168" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18273,7 +18279,7 @@
         <v>1587</v>
       </c>
       <c r="W169" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18335,16 +18341,16 @@
         <v>1567</v>
       </c>
       <c r="W170" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X170" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="Y170" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z170" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18406,16 +18412,16 @@
         <v>1588</v>
       </c>
       <c r="W171" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X171" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y171" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z171" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18477,16 +18483,16 @@
         <v>1589</v>
       </c>
       <c r="W172" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X172" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="Y172" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z172" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18548,16 +18554,16 @@
         <v>1590</v>
       </c>
       <c r="W173" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X173" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="Y173" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z173" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18619,16 +18625,16 @@
         <v>1591</v>
       </c>
       <c r="W174" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X174" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="Y174" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z174" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18690,16 +18696,16 @@
         <v>1592</v>
       </c>
       <c r="W175" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X175" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="Y175" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z175" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18761,16 +18767,16 @@
         <v>1593</v>
       </c>
       <c r="W176" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X176" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="Y176" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z176" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18832,7 +18838,7 @@
         <v>1587</v>
       </c>
       <c r="W177" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -18894,16 +18900,16 @@
         <v>1594</v>
       </c>
       <c r="W178" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X178" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="Y178" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z178" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -18965,16 +18971,16 @@
         <v>1595</v>
       </c>
       <c r="W179" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X179" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y179" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z179" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19036,7 +19042,7 @@
         <v>1596</v>
       </c>
       <c r="W180" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19098,16 +19104,16 @@
         <v>1597</v>
       </c>
       <c r="W181" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X181" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="Y181" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z181" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19169,16 +19175,16 @@
         <v>1597</v>
       </c>
       <c r="W182" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X182" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="Y182" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z182" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19240,16 +19246,16 @@
         <v>1598</v>
       </c>
       <c r="W183" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X183" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="Y183" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z183" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19311,16 +19317,16 @@
         <v>1599</v>
       </c>
       <c r="W184" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X184" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="Y184" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z184" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19382,16 +19388,16 @@
         <v>1600</v>
       </c>
       <c r="W185" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X185" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="Y185" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z185" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19453,7 +19459,7 @@
         <v>1601</v>
       </c>
       <c r="W186" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19515,7 +19521,7 @@
         <v>1602</v>
       </c>
       <c r="W187" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19577,7 +19583,7 @@
         <v>1603</v>
       </c>
       <c r="W188" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19639,7 +19645,7 @@
         <v>1604</v>
       </c>
       <c r="W189" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19701,16 +19707,16 @@
         <v>1605</v>
       </c>
       <c r="W190" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X190" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="Y190" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z190" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19772,16 +19778,16 @@
         <v>1606</v>
       </c>
       <c r="W191" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X191" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="Y191" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z191" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19843,7 +19849,7 @@
         <v>1607</v>
       </c>
       <c r="W192" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -19905,7 +19911,7 @@
         <v>1607</v>
       </c>
       <c r="W193" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -19967,16 +19973,16 @@
         <v>1608</v>
       </c>
       <c r="W194" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X194" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="Y194" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z194" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20038,16 +20044,16 @@
         <v>1609</v>
       </c>
       <c r="W195" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X195" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="Y195" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z195" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20109,16 +20115,16 @@
         <v>1610</v>
       </c>
       <c r="W196" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X196" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="Y196" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z196" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20180,16 +20186,16 @@
         <v>1606</v>
       </c>
       <c r="W197" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X197" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="Y197" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z197" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20251,7 +20257,7 @@
         <v>1611</v>
       </c>
       <c r="W198" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20313,7 +20319,7 @@
         <v>1612</v>
       </c>
       <c r="W199" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20375,16 +20381,16 @@
         <v>1613</v>
       </c>
       <c r="W200" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X200" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="Y200" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z200" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20446,16 +20452,16 @@
         <v>1613</v>
       </c>
       <c r="W201" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X201" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="Y201" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z201" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20517,16 +20523,16 @@
         <v>1614</v>
       </c>
       <c r="W202" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X202" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="Y202" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z202" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20588,16 +20594,16 @@
         <v>1615</v>
       </c>
       <c r="W203" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X203" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="Y203" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z203" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20659,16 +20665,16 @@
         <v>1616</v>
       </c>
       <c r="W204" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X204" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="Y204" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z204" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20730,16 +20736,16 @@
         <v>1617</v>
       </c>
       <c r="W205" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X205" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="Y205" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z205" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20801,16 +20807,16 @@
         <v>1618</v>
       </c>
       <c r="W206" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X206" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="Y206" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z206" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -20872,16 +20878,16 @@
         <v>1619</v>
       </c>
       <c r="W207" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X207" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="Y207" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z207" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -20943,16 +20949,16 @@
         <v>1620</v>
       </c>
       <c r="W208" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X208" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="Y208" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z208" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21014,7 +21020,7 @@
         <v>1621</v>
       </c>
       <c r="W209" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21076,16 +21082,16 @@
         <v>1622</v>
       </c>
       <c r="W210" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X210" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="Y210" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z210" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21147,16 +21153,16 @@
         <v>1623</v>
       </c>
       <c r="W211" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X211" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="Y211" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z211" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21218,16 +21224,16 @@
         <v>1624</v>
       </c>
       <c r="W212" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X212" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="Y212" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z212" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21289,16 +21295,16 @@
         <v>1625</v>
       </c>
       <c r="W213" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X213" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="Y213" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z213" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21360,7 +21366,7 @@
         <v>1626</v>
       </c>
       <c r="W214" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21422,16 +21428,16 @@
         <v>1591</v>
       </c>
       <c r="W215" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X215" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="Y215" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z215" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21493,16 +21499,16 @@
         <v>1627</v>
       </c>
       <c r="W216" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X216" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="Y216" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z216" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21564,7 +21570,7 @@
         <v>1628</v>
       </c>
       <c r="W217" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21626,16 +21632,16 @@
         <v>1629</v>
       </c>
       <c r="W218" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X218" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="Y218" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z218" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21697,16 +21703,16 @@
         <v>1630</v>
       </c>
       <c r="W219" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X219" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="Y219" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z219" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21768,7 +21774,7 @@
         <v>1631</v>
       </c>
       <c r="W220" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21830,7 +21836,7 @@
         <v>1632</v>
       </c>
       <c r="W221" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -21892,7 +21898,7 @@
         <v>1631</v>
       </c>
       <c r="W222" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -21954,7 +21960,7 @@
         <v>1632</v>
       </c>
       <c r="W223" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22016,16 +22022,16 @@
         <v>1633</v>
       </c>
       <c r="W224" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X224" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="Y224" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z224" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22087,16 +22093,16 @@
         <v>1634</v>
       </c>
       <c r="W225" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X225" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="Y225" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z225" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22158,7 +22164,7 @@
         <v>1635</v>
       </c>
       <c r="W226" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22220,7 +22226,7 @@
         <v>1636</v>
       </c>
       <c r="W227" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22282,7 +22288,7 @@
         <v>1637</v>
       </c>
       <c r="W228" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22344,16 +22350,16 @@
         <v>1638</v>
       </c>
       <c r="W229" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X229" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="Y229" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z229" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22415,16 +22421,16 @@
         <v>1639</v>
       </c>
       <c r="W230" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X230" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="Y230" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z230" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22486,16 +22492,16 @@
         <v>1640</v>
       </c>
       <c r="W231" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X231" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="Y231" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z231" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22560,16 +22566,16 @@
         <v>1641</v>
       </c>
       <c r="W232" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X232" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y232" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z232" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22631,16 +22637,16 @@
         <v>1642</v>
       </c>
       <c r="W233" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X233" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="Y233" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z233" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22702,16 +22708,16 @@
         <v>1643</v>
       </c>
       <c r="W234" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X234" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="Y234" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z234" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22773,16 +22779,16 @@
         <v>1643</v>
       </c>
       <c r="W235" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X235" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="Y235" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z235" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22844,16 +22850,16 @@
         <v>1644</v>
       </c>
       <c r="W236" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X236" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="Y236" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z236" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -22915,7 +22921,7 @@
         <v>1645</v>
       </c>
       <c r="W237" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -22977,7 +22983,7 @@
         <v>1646</v>
       </c>
       <c r="W238" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23039,16 +23045,16 @@
         <v>1647</v>
       </c>
       <c r="W239" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X239" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="Y239" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z239" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23110,16 +23116,16 @@
         <v>1648</v>
       </c>
       <c r="W240" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X240" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="Y240" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z240" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23181,7 +23187,7 @@
         <v>1649</v>
       </c>
       <c r="W241" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23243,16 +23249,16 @@
         <v>1650</v>
       </c>
       <c r="W242" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X242" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="Y242" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z242" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23314,16 +23320,16 @@
         <v>1651</v>
       </c>
       <c r="W243" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X243" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y243" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z243" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23385,16 +23391,16 @@
         <v>1650</v>
       </c>
       <c r="W244" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X244" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="Y244" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z244" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23456,16 +23462,16 @@
         <v>1652</v>
       </c>
       <c r="W245" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X245" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="Y245" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z245" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23527,16 +23533,16 @@
         <v>1651</v>
       </c>
       <c r="W246" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X246" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y246" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z246" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23598,16 +23604,16 @@
         <v>1652</v>
       </c>
       <c r="W247" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X247" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="Y247" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z247" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23669,16 +23675,16 @@
         <v>1653</v>
       </c>
       <c r="W248" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X248" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="Y248" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z248" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23740,16 +23746,16 @@
         <v>1643</v>
       </c>
       <c r="W249" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X249" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="Y249" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z249" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23811,7 +23817,7 @@
         <v>1654</v>
       </c>
       <c r="W250" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -23873,7 +23879,7 @@
         <v>1655</v>
       </c>
       <c r="W251" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -23935,16 +23941,16 @@
         <v>1656</v>
       </c>
       <c r="W252" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X252" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="Y252" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z252" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24006,16 +24012,16 @@
         <v>1657</v>
       </c>
       <c r="W253" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X253" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="Y253" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z253" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24077,7 +24083,7 @@
         <v>1658</v>
       </c>
       <c r="W254" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24139,16 +24145,16 @@
         <v>1659</v>
       </c>
       <c r="W255" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X255" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="Y255" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z255" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24210,7 +24216,7 @@
         <v>1660</v>
       </c>
       <c r="W256" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24275,7 +24281,7 @@
         <v>1661</v>
       </c>
       <c r="W257" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24337,7 +24343,7 @@
         <v>1662</v>
       </c>
       <c r="W258" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24399,7 +24405,7 @@
         <v>1662</v>
       </c>
       <c r="W259" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24461,7 +24467,7 @@
         <v>1663</v>
       </c>
       <c r="W260" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24523,16 +24529,16 @@
         <v>1664</v>
       </c>
       <c r="W261" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X261" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="Y261" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z261" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24594,13 +24600,13 @@
         <v>1665</v>
       </c>
       <c r="W262" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X262" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="Y262" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24662,16 +24668,16 @@
         <v>1666</v>
       </c>
       <c r="W263" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X263" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="Y263" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z263" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24733,7 +24739,7 @@
         <v>1667</v>
       </c>
       <c r="W264" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24795,7 +24801,7 @@
         <v>1667</v>
       </c>
       <c r="W265" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24857,7 +24863,7 @@
         <v>1668</v>
       </c>
       <c r="W266" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -24919,16 +24925,16 @@
         <v>1669</v>
       </c>
       <c r="W267" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X267" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="Y267" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z267" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -24990,16 +24996,16 @@
         <v>1670</v>
       </c>
       <c r="W268" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X268" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="Y268" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z268" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25061,7 +25067,7 @@
         <v>1511</v>
       </c>
       <c r="W269" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25123,7 +25129,7 @@
         <v>1671</v>
       </c>
       <c r="W270" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25185,7 +25191,7 @@
         <v>1672</v>
       </c>
       <c r="W271" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25247,16 +25253,16 @@
         <v>1673</v>
       </c>
       <c r="W272" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X272" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="Y272" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z272" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25315,7 +25321,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25377,7 +25383,7 @@
         <v>1674</v>
       </c>
       <c r="W274" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25436,7 +25442,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25498,7 +25504,7 @@
         <v>1675</v>
       </c>
       <c r="W276" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25560,7 +25566,7 @@
         <v>1676</v>
       </c>
       <c r="W277" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25622,16 +25628,16 @@
         <v>1677</v>
       </c>
       <c r="W278" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X278" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="Y278" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z278" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25693,16 +25699,16 @@
         <v>1678</v>
       </c>
       <c r="W279" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X279" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="Y279" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z279" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25764,16 +25770,16 @@
         <v>1678</v>
       </c>
       <c r="W280" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X280" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="Y280" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z280" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25835,16 +25841,16 @@
         <v>1679</v>
       </c>
       <c r="W281" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X281" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="Y281" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z281" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -25906,7 +25912,7 @@
         <v>1680</v>
       </c>
       <c r="W282" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -25968,7 +25974,7 @@
         <v>1681</v>
       </c>
       <c r="W283" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26030,7 +26036,7 @@
         <v>1682</v>
       </c>
       <c r="W284" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26092,16 +26098,16 @@
         <v>1683</v>
       </c>
       <c r="W285" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X285" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y285" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z285" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26163,7 +26169,7 @@
         <v>1684</v>
       </c>
       <c r="W286" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26225,16 +26231,16 @@
         <v>1678</v>
       </c>
       <c r="W287" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X287" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="Y287" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z287" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26296,16 +26302,16 @@
         <v>1685</v>
       </c>
       <c r="W288" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X288" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="Y288" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z288" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26367,7 +26373,7 @@
         <v>1686</v>
       </c>
       <c r="W289" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26429,16 +26435,16 @@
         <v>1687</v>
       </c>
       <c r="W290" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X290" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="Y290" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z290" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26500,16 +26506,16 @@
         <v>1688</v>
       </c>
       <c r="W291" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X291" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="Y291" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z291" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26571,7 +26577,7 @@
         <v>1689</v>
       </c>
       <c r="W292" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26630,7 +26636,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26692,7 +26698,7 @@
         <v>1690</v>
       </c>
       <c r="W294" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26754,7 +26760,7 @@
         <v>1691</v>
       </c>
       <c r="W295" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26816,7 +26822,7 @@
         <v>1692</v>
       </c>
       <c r="W296" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -26878,13 +26884,13 @@
         <v>1693</v>
       </c>
       <c r="W297" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X297" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="Z297" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -26946,7 +26952,7 @@
         <v>1694</v>
       </c>
       <c r="W298" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27008,7 +27014,7 @@
         <v>1695</v>
       </c>
       <c r="W299" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27070,7 +27076,7 @@
         <v>1696</v>
       </c>
       <c r="W300" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27132,7 +27138,7 @@
         <v>1697</v>
       </c>
       <c r="W301" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27194,7 +27200,7 @@
         <v>1698</v>
       </c>
       <c r="W302" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27256,16 +27262,16 @@
         <v>1699</v>
       </c>
       <c r="W303" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X303" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="Y303" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z303" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27327,7 +27333,7 @@
         <v>1700</v>
       </c>
       <c r="W304" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27389,7 +27395,7 @@
         <v>1701</v>
       </c>
       <c r="W305" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27451,7 +27457,7 @@
         <v>1702</v>
       </c>
       <c r="W306" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27513,7 +27519,7 @@
         <v>1703</v>
       </c>
       <c r="W307" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27575,7 +27581,7 @@
         <v>1696</v>
       </c>
       <c r="W308" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27637,7 +27643,7 @@
         <v>1704</v>
       </c>
       <c r="W309" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27699,7 +27705,7 @@
         <v>1705</v>
       </c>
       <c r="W310" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27761,7 +27767,7 @@
         <v>1706</v>
       </c>
       <c r="W311" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27823,7 +27829,7 @@
         <v>1707</v>
       </c>
       <c r="W312" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -27885,7 +27891,7 @@
         <v>1708</v>
       </c>
       <c r="W313" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -27947,7 +27953,7 @@
         <v>1709</v>
       </c>
       <c r="W314" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28009,7 +28015,7 @@
         <v>1710</v>
       </c>
       <c r="W315" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28071,7 +28077,7 @@
         <v>1711</v>
       </c>
       <c r="W316" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28133,7 +28139,7 @@
         <v>1712</v>
       </c>
       <c r="W317" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28195,7 +28201,7 @@
         <v>1713</v>
       </c>
       <c r="W318" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28257,7 +28263,7 @@
         <v>1714</v>
       </c>
       <c r="W319" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28316,13 +28322,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X320" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="Z320" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28381,7 +28387,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28440,7 +28446,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28499,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28561,7 +28567,7 @@
         <v>1715</v>
       </c>
       <c r="W324" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28623,7 +28629,7 @@
         <v>1716</v>
       </c>
       <c r="W325" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28685,7 +28691,7 @@
         <v>1717</v>
       </c>
       <c r="W326" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28747,7 +28753,7 @@
         <v>1718</v>
       </c>
       <c r="W327" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28806,7 +28812,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -28868,7 +28874,7 @@
         <v>1718</v>
       </c>
       <c r="W329" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -28930,7 +28936,7 @@
         <v>1719</v>
       </c>
       <c r="W330" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -28992,7 +28998,7 @@
         <v>1720</v>
       </c>
       <c r="W331" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29054,7 +29060,7 @@
         <v>1720</v>
       </c>
       <c r="W332" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29116,7 +29122,7 @@
         <v>1721</v>
       </c>
       <c r="W333" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29178,7 +29184,7 @@
         <v>1722</v>
       </c>
       <c r="W334" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29240,7 +29246,7 @@
         <v>1723</v>
       </c>
       <c r="W335" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29299,13 +29305,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X336" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="Z336" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29367,7 +29373,7 @@
         <v>1724</v>
       </c>
       <c r="W337" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29429,13 +29435,13 @@
         <v>1725</v>
       </c>
       <c r="W338" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X338" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="Z338" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29497,13 +29503,13 @@
         <v>1726</v>
       </c>
       <c r="W339" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X339" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="Z339" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29565,7 +29571,7 @@
         <v>1727</v>
       </c>
       <c r="W340" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29627,7 +29633,7 @@
         <v>1728</v>
       </c>
       <c r="W341" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29689,10 +29695,10 @@
         <v>1729</v>
       </c>
       <c r="W342" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X342" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29754,7 +29760,7 @@
         <v>1730</v>
       </c>
       <c r="W343" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29816,7 +29822,7 @@
         <v>1731</v>
       </c>
       <c r="W344" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -29878,13 +29884,13 @@
         <v>1732</v>
       </c>
       <c r="W345" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X345" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="Z345" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -29946,7 +29952,7 @@
         <v>1696</v>
       </c>
       <c r="W346" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30008,7 +30014,7 @@
         <v>1733</v>
       </c>
       <c r="W347" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30070,16 +30076,16 @@
         <v>1734</v>
       </c>
       <c r="W348" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X348" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="Y348" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z348" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30144,13 +30150,13 @@
         <v>1735</v>
       </c>
       <c r="W349" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X349" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="Z349" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30212,7 +30218,7 @@
         <v>1736</v>
       </c>
       <c r="W350" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30274,16 +30280,16 @@
         <v>1737</v>
       </c>
       <c r="W351" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X351" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="Y351" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z351" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30345,13 +30351,13 @@
         <v>1738</v>
       </c>
       <c r="W352" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X352" t="s">
         <v>1738</v>
       </c>
       <c r="Z352" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30413,16 +30419,16 @@
         <v>1739</v>
       </c>
       <c r="W353" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X353" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="Y353" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z353" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30484,7 +30490,7 @@
         <v>1740</v>
       </c>
       <c r="W354" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30546,7 +30552,7 @@
         <v>1741</v>
       </c>
       <c r="W355" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30605,7 +30611,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30664,7 +30670,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30723,7 +30729,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30785,7 +30791,7 @@
         <v>1742</v>
       </c>
       <c r="W359" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30850,7 +30856,7 @@
         <v>1743</v>
       </c>
       <c r="W360" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -30915,7 +30921,7 @@
         <v>1744</v>
       </c>
       <c r="W361" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -30977,16 +30983,16 @@
         <v>1745</v>
       </c>
       <c r="W362" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X362" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="Y362" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z362" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31048,16 +31054,16 @@
         <v>1746</v>
       </c>
       <c r="W363" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X363" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="Y363" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z363" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31119,7 +31125,7 @@
         <v>1747</v>
       </c>
       <c r="W364" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31181,7 +31187,7 @@
         <v>1748</v>
       </c>
       <c r="W365" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31246,7 +31252,7 @@
         <v>1749</v>
       </c>
       <c r="W366" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31308,7 +31314,7 @@
         <v>1750</v>
       </c>
       <c r="W367" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31370,7 +31376,7 @@
         <v>1751</v>
       </c>
       <c r="W368" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31435,13 +31441,13 @@
         <v>1752</v>
       </c>
       <c r="W369" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X369" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="Z369" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31503,7 +31509,7 @@
         <v>1753</v>
       </c>
       <c r="W370" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31565,16 +31571,16 @@
         <v>1754</v>
       </c>
       <c r="W371" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X371" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="Y371" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z371" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31639,7 +31645,7 @@
         <v>1755</v>
       </c>
       <c r="W372" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31704,16 +31710,16 @@
         <v>1756</v>
       </c>
       <c r="W373" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X373" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="Y373" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z373" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31775,7 +31781,7 @@
         <v>1757</v>
       </c>
       <c r="W374" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31840,7 +31846,7 @@
         <v>1758</v>
       </c>
       <c r="W375" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -31905,7 +31911,7 @@
         <v>1759</v>
       </c>
       <c r="W376" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -31970,7 +31976,7 @@
         <v>1759</v>
       </c>
       <c r="W377" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32035,13 +32041,13 @@
         <v>1760</v>
       </c>
       <c r="W378" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X378" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="Z378" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32103,16 +32109,16 @@
         <v>1761</v>
       </c>
       <c r="W379" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X379" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y379" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z379" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32177,7 +32183,7 @@
         <v>1762</v>
       </c>
       <c r="W380" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32239,7 +32245,7 @@
         <v>1763</v>
       </c>
       <c r="W381" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32304,7 +32310,7 @@
         <v>1764</v>
       </c>
       <c r="W382" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32366,7 +32372,7 @@
         <v>1765</v>
       </c>
       <c r="W383" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32431,7 +32437,7 @@
         <v>1764</v>
       </c>
       <c r="W384" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32493,16 +32499,16 @@
         <v>1766</v>
       </c>
       <c r="W385" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X385" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="Y385" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z385" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32570,7 +32576,7 @@
         <v>1767</v>
       </c>
       <c r="W386" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32632,7 +32638,7 @@
         <v>1768</v>
       </c>
       <c r="W387" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32694,7 +32700,7 @@
         <v>1769</v>
       </c>
       <c r="W388" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32756,16 +32762,16 @@
         <v>1770</v>
       </c>
       <c r="W389" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X389" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="Y389" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z389" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32830,16 +32836,16 @@
         <v>1771</v>
       </c>
       <c r="W390" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X390" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="Y390" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z390" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -32904,7 +32910,7 @@
         <v>1772</v>
       </c>
       <c r="W391" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -32966,7 +32972,7 @@
         <v>1773</v>
       </c>
       <c r="W392" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33028,16 +33034,16 @@
         <v>1774</v>
       </c>
       <c r="W393" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X393" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="Y393" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z393" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33099,7 +33105,7 @@
         <v>1775</v>
       </c>
       <c r="W394" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33164,16 +33170,16 @@
         <v>1776</v>
       </c>
       <c r="W395" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X395" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="Y395" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z395" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33238,13 +33244,13 @@
         <v>1777</v>
       </c>
       <c r="W396" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X396" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="Y396" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33306,7 +33312,7 @@
         <v>1778</v>
       </c>
       <c r="W397" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33368,7 +33374,7 @@
         <v>1779</v>
       </c>
       <c r="W398" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33433,7 +33439,7 @@
         <v>1780</v>
       </c>
       <c r="W399" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33498,16 +33504,16 @@
         <v>1781</v>
       </c>
       <c r="W400" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X400" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="Y400" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z400" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33572,7 +33578,7 @@
         <v>1782</v>
       </c>
       <c r="W401" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33637,7 +33643,7 @@
         <v>1783</v>
       </c>
       <c r="W402" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33702,16 +33708,16 @@
         <v>1784</v>
       </c>
       <c r="W403" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X403" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y403" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z403" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33776,7 +33782,7 @@
         <v>1785</v>
       </c>
       <c r="W404" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33841,7 +33847,7 @@
         <v>1786</v>
       </c>
       <c r="W405" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -33891,13 +33897,13 @@
         <v>46091</v>
       </c>
       <c r="O406" s="1">
-        <v>46287</v>
+        <v>46248</v>
       </c>
       <c r="Q406">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R406">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S406" t="s">
         <v>1488</v>
@@ -33909,10 +33915,10 @@
         <v>1787</v>
       </c>
       <c r="V406" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="W406" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA406" t="b">
         <v>1</v>
@@ -33974,16 +33980,16 @@
         <v>1788</v>
       </c>
       <c r="W407" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X407" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="Y407" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z407" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34048,13 +34054,13 @@
         <v>1789</v>
       </c>
       <c r="W408" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X408" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="Z408" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34119,7 +34125,7 @@
         <v>1790</v>
       </c>
       <c r="W409" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34184,7 +34190,7 @@
         <v>1791</v>
       </c>
       <c r="W410" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34249,7 +34255,7 @@
         <v>1792</v>
       </c>
       <c r="W411" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34314,7 +34320,7 @@
         <v>1793</v>
       </c>
       <c r="W412" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34379,7 +34385,7 @@
         <v>1794</v>
       </c>
       <c r="W413" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34444,7 +34450,7 @@
         <v>1794</v>
       </c>
       <c r="W414" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34509,7 +34515,7 @@
         <v>1795</v>
       </c>
       <c r="W415" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34574,7 +34580,7 @@
         <v>1796</v>
       </c>
       <c r="W416" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34639,7 +34645,7 @@
         <v>1794</v>
       </c>
       <c r="W417" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34704,7 +34710,7 @@
         <v>1797</v>
       </c>
       <c r="W418" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34769,7 +34775,7 @@
         <v>1798</v>
       </c>
       <c r="W419" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34834,16 +34840,16 @@
         <v>1799</v>
       </c>
       <c r="W420" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X420" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="Y420" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z420" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -34908,7 +34914,7 @@
         <v>1800</v>
       </c>
       <c r="W421" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -34973,7 +34979,7 @@
         <v>1801</v>
       </c>
       <c r="W422" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35038,7 +35044,7 @@
         <v>1802</v>
       </c>
       <c r="W423" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35103,16 +35109,16 @@
         <v>1803</v>
       </c>
       <c r="W424" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X424" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="Y424" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z424" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35177,7 +35183,7 @@
         <v>1802</v>
       </c>
       <c r="W425" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35242,7 +35248,7 @@
         <v>1804</v>
       </c>
       <c r="W426" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35307,7 +35313,7 @@
         <v>1805</v>
       </c>
       <c r="W427" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35372,13 +35378,13 @@
         <v>1806</v>
       </c>
       <c r="W428" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X428" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="Y428" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35443,16 +35449,16 @@
         <v>1807</v>
       </c>
       <c r="W429" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X429" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="Y429" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z429" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35517,7 +35523,7 @@
         <v>1808</v>
       </c>
       <c r="W430" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35582,16 +35588,16 @@
         <v>1809</v>
       </c>
       <c r="W431" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X431" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="Y431" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z431" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35656,7 +35662,7 @@
         <v>1810</v>
       </c>
       <c r="W432" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35721,7 +35727,7 @@
         <v>1811</v>
       </c>
       <c r="W433" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35786,7 +35792,7 @@
         <v>1812</v>
       </c>
       <c r="W434" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35851,7 +35857,7 @@
         <v>1813</v>
       </c>
       <c r="W435" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -35916,7 +35922,7 @@
         <v>1814</v>
       </c>
       <c r="W436" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -35981,7 +35987,7 @@
         <v>1815</v>
       </c>
       <c r="W437" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36046,7 +36052,7 @@
         <v>1816</v>
       </c>
       <c r="W438" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36111,7 +36117,7 @@
         <v>1817</v>
       </c>
       <c r="W439" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36176,16 +36182,16 @@
         <v>1818</v>
       </c>
       <c r="W440" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X440" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="Y440" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z440" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36250,16 +36256,16 @@
         <v>1819</v>
       </c>
       <c r="W441" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X441" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="Y441" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z441" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36324,16 +36330,16 @@
         <v>1820</v>
       </c>
       <c r="W442" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X442" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="Y442" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z442" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36398,7 +36404,7 @@
         <v>1821</v>
       </c>
       <c r="W443" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36463,7 +36469,7 @@
         <v>1822</v>
       </c>
       <c r="W444" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36528,16 +36534,16 @@
         <v>1819</v>
       </c>
       <c r="W445" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X445" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="Y445" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z445" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36602,16 +36608,16 @@
         <v>1819</v>
       </c>
       <c r="W446" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X446" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="Y446" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z446" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36676,16 +36682,16 @@
         <v>1823</v>
       </c>
       <c r="W447" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X447" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="Y447" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z447" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36750,16 +36756,16 @@
         <v>1819</v>
       </c>
       <c r="W448" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X448" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="Y448" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z448" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36824,16 +36830,16 @@
         <v>1819</v>
       </c>
       <c r="W449" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X449" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="Y449" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z449" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -36898,16 +36904,16 @@
         <v>1824</v>
       </c>
       <c r="W450" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X450" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="Y450" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z450" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -36972,16 +36978,16 @@
         <v>1825</v>
       </c>
       <c r="W451" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X451" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="Y451" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z451" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37046,7 +37052,7 @@
         <v>1826</v>
       </c>
       <c r="W452" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37111,16 +37117,16 @@
         <v>1827</v>
       </c>
       <c r="W453" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X453" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="Y453" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z453" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37185,16 +37191,16 @@
         <v>1828</v>
       </c>
       <c r="W454" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X454" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="Y454" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z454" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37259,16 +37265,16 @@
         <v>1829</v>
       </c>
       <c r="W455" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X455" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="Y455" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z455" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37333,16 +37339,16 @@
         <v>1830</v>
       </c>
       <c r="W456" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X456" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="Y456" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z456" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37407,7 +37413,7 @@
         <v>1831</v>
       </c>
       <c r="W457" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37472,7 +37478,7 @@
         <v>1831</v>
       </c>
       <c r="W458" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37537,16 +37543,16 @@
         <v>1829</v>
       </c>
       <c r="W459" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X459" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="Y459" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z459" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37611,16 +37617,16 @@
         <v>1832</v>
       </c>
       <c r="W460" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X460" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="Y460" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z460" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37685,16 +37691,16 @@
         <v>1833</v>
       </c>
       <c r="W461" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X461" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="Y461" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z461" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37759,7 +37765,7 @@
         <v>1834</v>
       </c>
       <c r="W462" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37824,16 +37830,16 @@
         <v>1835</v>
       </c>
       <c r="W463" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X463" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="Y463" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z463" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -37898,16 +37904,16 @@
         <v>1836</v>
       </c>
       <c r="W464" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X464" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="Y464" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z464" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -37972,16 +37978,16 @@
         <v>1837</v>
       </c>
       <c r="W465" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X465" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="Y465" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z465" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38046,7 +38052,7 @@
         <v>1838</v>
       </c>
       <c r="W466" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38111,16 +38117,16 @@
         <v>1839</v>
       </c>
       <c r="W467" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X467" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="Y467" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z467" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38185,16 +38191,16 @@
         <v>1840</v>
       </c>
       <c r="W468" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X468" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="Y468" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z468" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38259,16 +38265,16 @@
         <v>1841</v>
       </c>
       <c r="W469" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X469" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="Y469" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z469" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38333,16 +38339,16 @@
         <v>1842</v>
       </c>
       <c r="W470" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X470" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="Y470" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z470" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38407,7 +38413,7 @@
         <v>1843</v>
       </c>
       <c r="W471" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38472,16 +38478,16 @@
         <v>1844</v>
       </c>
       <c r="W472" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X472" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="Y472" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z472" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38546,16 +38552,16 @@
         <v>1844</v>
       </c>
       <c r="W473" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X473" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="Y473" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z473" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38620,7 +38626,7 @@
         <v>1845</v>
       </c>
       <c r="W474" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38685,16 +38691,16 @@
         <v>1846</v>
       </c>
       <c r="W475" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X475" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="Y475" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z475" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38759,16 +38765,16 @@
         <v>1847</v>
       </c>
       <c r="W476" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X476" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="Y476" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z476" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38833,7 +38839,7 @@
         <v>1848</v>
       </c>
       <c r="W477" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -38898,7 +38904,7 @@
         <v>1849</v>
       </c>
       <c r="W478" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -38963,16 +38969,16 @@
         <v>1850</v>
       </c>
       <c r="W479" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X479" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Y479" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z479" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39037,16 +39043,16 @@
         <v>1851</v>
       </c>
       <c r="W480" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X480" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="Y480" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z480" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39111,16 +39117,16 @@
         <v>1852</v>
       </c>
       <c r="W481" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X481" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="Y481" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z481" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39185,7 +39191,7 @@
         <v>1853</v>
       </c>
       <c r="W482" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39250,7 +39256,7 @@
         <v>1854</v>
       </c>
       <c r="W483" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39318,13 +39324,13 @@
         <v>1855</v>
       </c>
       <c r="W484" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39389,7 +39395,7 @@
         <v>1856</v>
       </c>
       <c r="W485" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39457,13 +39463,13 @@
         <v>1857</v>
       </c>
       <c r="W486" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39528,7 +39534,7 @@
         <v>1858</v>
       </c>
       <c r="W487" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39593,16 +39599,16 @@
         <v>1859</v>
       </c>
       <c r="W488" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X488" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="Y488" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z488" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39667,7 +39673,7 @@
         <v>1860</v>
       </c>
       <c r="W489" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39735,13 +39741,13 @@
         <v>1861</v>
       </c>
       <c r="W490" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39806,16 +39812,16 @@
         <v>1862</v>
       </c>
       <c r="W491" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X491" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="Y491" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z491" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -39880,16 +39886,16 @@
         <v>1863</v>
       </c>
       <c r="W492" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X492" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="Y492" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z492" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -39954,16 +39960,16 @@
         <v>1864</v>
       </c>
       <c r="W493" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X493" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="Y493" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z493" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40028,13 +40034,13 @@
         <v>1865</v>
       </c>
       <c r="W494" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X494" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="Y494" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40099,16 +40105,16 @@
         <v>1866</v>
       </c>
       <c r="W495" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X495" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="Y495" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z495" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40173,7 +40179,7 @@
         <v>1867</v>
       </c>
       <c r="W496" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40241,7 +40247,7 @@
         <v>1868</v>
       </c>
       <c r="W497" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40306,7 +40312,7 @@
         <v>1869</v>
       </c>
       <c r="W498" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40374,7 +40380,7 @@
         <v>1870</v>
       </c>
       <c r="W499" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40439,16 +40445,16 @@
         <v>1871</v>
       </c>
       <c r="W500" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X500" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="Y500" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z500" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40513,16 +40519,16 @@
         <v>1872</v>
       </c>
       <c r="W501" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X501" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="Y501" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z501" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40587,7 +40593,7 @@
         <v>1873</v>
       </c>
       <c r="W502" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40655,7 +40661,7 @@
         <v>1874</v>
       </c>
       <c r="W503" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40723,16 +40729,16 @@
         <v>1875</v>
       </c>
       <c r="W504" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X504" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="Y504" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z504" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40797,7 +40803,7 @@
         <v>1876</v>
       </c>
       <c r="W505" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40862,16 +40868,16 @@
         <v>1877</v>
       </c>
       <c r="W506" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X506" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="Y506" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z506" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -40936,7 +40942,7 @@
         <v>1878</v>
       </c>
       <c r="W507" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41001,7 +41007,7 @@
         <v>1879</v>
       </c>
       <c r="W508" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41066,16 +41072,16 @@
         <v>1880</v>
       </c>
       <c r="W509" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X509" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y509" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z509" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41140,16 +41146,16 @@
         <v>1881</v>
       </c>
       <c r="W510" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X510" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="Y510" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z510" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41217,7 +41223,7 @@
         <v>1882</v>
       </c>
       <c r="W511" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41285,7 +41291,7 @@
         <v>1883</v>
       </c>
       <c r="W512" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41353,7 +41359,7 @@
         <v>1884</v>
       </c>
       <c r="W513" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41421,7 +41427,7 @@
         <v>1884</v>
       </c>
       <c r="W514" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41489,7 +41495,7 @@
         <v>1884</v>
       </c>
       <c r="W515" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41557,13 +41563,13 @@
         <v>1885</v>
       </c>
       <c r="W516" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41631,13 +41637,13 @@
         <v>1886</v>
       </c>
       <c r="W517" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41705,16 +41711,16 @@
         <v>1887</v>
       </c>
       <c r="W518" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X518" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="Y518" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z518" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41782,16 +41788,16 @@
         <v>1888</v>
       </c>
       <c r="W519" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X519" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="Y519" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z519" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41856,7 +41862,7 @@
         <v>1491</v>
       </c>
       <c r="W520" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -41924,7 +41930,7 @@
         <v>1889</v>
       </c>
       <c r="W521" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -41992,7 +41998,7 @@
         <v>1889</v>
       </c>
       <c r="W522" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42060,7 +42066,7 @@
         <v>1890</v>
       </c>
       <c r="W523" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42128,7 +42134,7 @@
         <v>1891</v>
       </c>
       <c r="W524" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42196,7 +42202,7 @@
         <v>1892</v>
       </c>
       <c r="W525" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42264,7 +42270,7 @@
         <v>1893</v>
       </c>
       <c r="W526" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42332,7 +42338,7 @@
         <v>1894</v>
       </c>
       <c r="W527" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42397,7 +42403,7 @@
         <v>1895</v>
       </c>
       <c r="W528" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42465,7 +42471,7 @@
         <v>1896</v>
       </c>
       <c r="W529" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42533,16 +42539,16 @@
         <v>1897</v>
       </c>
       <c r="W530" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X530" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="Y530" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z530" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42610,7 +42616,7 @@
         <v>1898</v>
       </c>
       <c r="W531" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42675,7 +42681,7 @@
         <v>1899</v>
       </c>
       <c r="W532" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42743,16 +42749,16 @@
         <v>1900</v>
       </c>
       <c r="W533" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X533" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="Y533" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z533" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42820,13 +42826,13 @@
         <v>1901</v>
       </c>
       <c r="W534" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -42894,7 +42900,7 @@
         <v>1902</v>
       </c>
       <c r="W535" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -42962,7 +42968,7 @@
         <v>1903</v>
       </c>
       <c r="W536" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43030,16 +43036,16 @@
         <v>1904</v>
       </c>
       <c r="W537" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X537" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="Y537" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z537" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43107,7 +43113,7 @@
         <v>1905</v>
       </c>
       <c r="W538" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43175,7 +43181,7 @@
         <v>1906</v>
       </c>
       <c r="W539" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43243,7 +43249,7 @@
         <v>1907</v>
       </c>
       <c r="W540" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43311,7 +43317,7 @@
         <v>1908</v>
       </c>
       <c r="W541" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43379,16 +43385,16 @@
         <v>1909</v>
       </c>
       <c r="W542" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X542" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="Y542" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z542" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43456,7 +43462,7 @@
         <v>1910</v>
       </c>
       <c r="W543" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43524,16 +43530,16 @@
         <v>1911</v>
       </c>
       <c r="W544" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="X544" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="Y544" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Z544" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43601,7 +43607,7 @@
         <v>1912</v>
       </c>
       <c r="W545" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43669,7 +43675,7 @@
         <v>1913</v>
       </c>
       <c r="W546" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43737,7 +43743,7 @@
         <v>1914</v>
       </c>
       <c r="W547" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43805,7 +43811,7 @@
         <v>1915</v>
       </c>
       <c r="W548" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -43873,7 +43879,7 @@
         <v>1915</v>
       </c>
       <c r="W549" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -43941,7 +43947,7 @@
         <v>1916</v>
       </c>
       <c r="W550" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44006,7 +44012,7 @@
         <v>1917</v>
       </c>
       <c r="W551" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44074,7 +44080,7 @@
         <v>1918</v>
       </c>
       <c r="W552" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44139,7 +44145,7 @@
         <v>1919</v>
       </c>
       <c r="W553" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44207,7 +44213,7 @@
         <v>1920</v>
       </c>
       <c r="W554" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44275,7 +44281,7 @@
         <v>1921</v>
       </c>
       <c r="W555" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44343,7 +44349,7 @@
         <v>1922</v>
       </c>
       <c r="W556" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44408,7 +44414,7 @@
         <v>1923</v>
       </c>
       <c r="W557" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44476,7 +44482,7 @@
         <v>1924</v>
       </c>
       <c r="W558" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44544,7 +44550,7 @@
         <v>1925</v>
       </c>
       <c r="W559" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44609,7 +44615,7 @@
         <v>1926</v>
       </c>
       <c r="W560" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44677,7 +44683,7 @@
         <v>1927</v>
       </c>
       <c r="W561" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44726,11 +44732,14 @@
       <c r="N562" s="1">
         <v>46243</v>
       </c>
+      <c r="O562" s="1">
+        <v>46251</v>
+      </c>
       <c r="Q562">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R562">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S562" t="s">
         <v>1488</v>
@@ -44739,10 +44748,10 @@
         <v>1489</v>
       </c>
       <c r="V562" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="W562" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44807,7 +44816,7 @@
         <v>1928</v>
       </c>
       <c r="W563" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -44860,10 +44869,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R564">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S564" t="s">
         <v>1488</v>
@@ -44872,10 +44881,10 @@
         <v>1489</v>
       </c>
       <c r="V564" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="W564" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA564" t="b">
         <v>1</v>
@@ -44943,7 +44952,7 @@
         <v>1929</v>
       </c>
       <c r="W565" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45011,7 +45020,7 @@
         <v>1930</v>
       </c>
       <c r="W566" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45079,7 +45088,7 @@
         <v>1931</v>
       </c>
       <c r="W567" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45128,11 +45137,14 @@
       <c r="N568" s="1">
         <v>46249</v>
       </c>
+      <c r="O568" s="1">
+        <v>46249</v>
+      </c>
       <c r="Q568">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R568">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S568" t="s">
         <v>1488</v>
@@ -45144,10 +45156,10 @@
         <v>1932</v>
       </c>
       <c r="V568" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="W568" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA568" t="b">
         <v>1</v>
@@ -45215,7 +45227,7 @@
         <v>1933</v>
       </c>
       <c r="W569" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45280,7 +45292,7 @@
         <v>1934</v>
       </c>
       <c r="W570" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45345,7 +45357,7 @@
         <v>1935</v>
       </c>
       <c r="W571" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45413,7 +45425,7 @@
         <v>1936</v>
       </c>
       <c r="W572" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45481,7 +45493,7 @@
         <v>1937</v>
       </c>
       <c r="W573" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45549,7 +45561,7 @@
         <v>1938</v>
       </c>
       <c r="W574" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45599,13 +45611,13 @@
         <v>46255</v>
       </c>
       <c r="O575" s="1">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="Q575">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R575">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S575" t="s">
         <v>1488</v>
@@ -45613,11 +45625,14 @@
       <c r="T575" t="s">
         <v>1488</v>
       </c>
+      <c r="U575" t="s">
+        <v>1939</v>
+      </c>
       <c r="V575" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="W575" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA575" t="b">
         <v>1</v>
@@ -45682,10 +45697,10 @@
         <v>1488</v>
       </c>
       <c r="U576" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="W576" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45750,10 +45765,10 @@
         <v>1488</v>
       </c>
       <c r="U577" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="W577" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45818,10 +45833,10 @@
         <v>1488</v>
       </c>
       <c r="U578" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="W578" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -45886,10 +45901,10 @@
         <v>1488</v>
       </c>
       <c r="U579" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="W579" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -45954,10 +45969,10 @@
         <v>1489</v>
       </c>
       <c r="U580" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="W580" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46022,10 +46037,10 @@
         <v>1489</v>
       </c>
       <c r="U581" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="W581" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46075,13 +46090,13 @@
         <v>46265</v>
       </c>
       <c r="O582" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="Q582">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="R582">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S582" t="s">
         <v>1488</v>
@@ -46090,13 +46105,13 @@
         <v>1489</v>
       </c>
       <c r="U582" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="V582" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="W582" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA582" t="b">
         <v>1</v>
@@ -46146,10 +46161,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="R583">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S583" t="s">
         <v>1488</v>
@@ -46157,11 +46172,8 @@
       <c r="T583" t="s">
         <v>1489</v>
       </c>
-      <c r="V583" t="s">
-        <v>1953</v>
-      </c>
       <c r="W583" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA583" t="b">
         <v>1</v>
@@ -46226,10 +46238,10 @@
         <v>1488</v>
       </c>
       <c r="U584" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="W584" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46294,10 +46306,10 @@
         <v>1488</v>
       </c>
       <c r="U585" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="W585" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46347,10 +46359,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R586">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S586" t="s">
         <v>1488</v>
@@ -46359,7 +46371,7 @@
         <v>1489</v>
       </c>
       <c r="W586" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46409,16 +46421,19 @@
         <v>46248</v>
       </c>
       <c r="Q587">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R587">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S587" t="s">
         <v>1488</v>
       </c>
+      <c r="V587" t="s">
+        <v>1955</v>
+      </c>
       <c r="W587" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA587" t="b">
         <v>1</v>
@@ -46471,10 +46486,10 @@
         <v>1487</v>
       </c>
       <c r="Q588">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R588">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S588" t="s">
         <v>1489</v>
@@ -46483,10 +46498,10 @@
         <v>1489</v>
       </c>
       <c r="U588" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="W588" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA588" t="b">
         <v>0</v>
@@ -46536,16 +46551,22 @@
         <v>46277</v>
       </c>
       <c r="Q589">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="R589">
-        <v>-1</v>
+        <v>0</v>
+      </c>
+      <c r="S589" t="s">
+        <v>1489</v>
       </c>
       <c r="T589" t="s">
         <v>1488</v>
       </c>
+      <c r="U589" t="s">
+        <v>1948</v>
+      </c>
       <c r="W589" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="AA589" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7435" uniqueCount="2335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7445" uniqueCount="2344">
   <si>
     <t>om_emg</t>
   </si>
@@ -5392,7 +5392,7 @@
     <t>Foram cedidos para o C-98 2733. / FOI GERADO SOLICITAÇÃO DE COMPRA E-C98-26008 - CLAUDIO-02-03-26. Solicitado cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. - MATERIAL EM TRANSITO- RECIBO 174/FAB/26 AWB 12721747386 - MATERIAL EM FISCALIZAÇÃO DIA 14/03/2026 - GUIA DE PAGAMENTO GERADA 16/03/2026 - ATZ RC 16/03/2026 SERÁ ATENDIDO 1EA CONFORME TRATATIVAS DO GESTOR DO CONTRATO 1T Wallace</t>
   </si>
   <si>
-    <t>Foram cedidos para o C-98 2733. / De acordo com o manual da aeronave, o QPA é 02 EA por cadeira. Sendo o total para a aeronave 04 EA.A demanda aberta foi de  4EA, o SO Bispo que intermediou . Wallace 29.05</t>
+    <t>Foram cedidos para o C-98 2733. / De acordo com o manual da aeronave, o QPA é 02 EA por cadeira. Sendo o total para a aeronave 04 EA.A demanda aberta foi de  4EA, o SO Bispo que intermediou . Wallace 29.05 Recibo 672/FAB/26 com 04 EA entregue em 12/08/26. Ramon 13/08/26</t>
   </si>
   <si>
     <t>Há estoque no PAMA do alternado. Recibo 166/FAB/26 , AWB 127-2144 2304 entregue em 17/03/26.</t>
@@ -5818,6 +5818,9 @@
     <t>Cedeu o item para o C-98 2738. Godoy 13/07/26.  Item atendido pelo recibo 568/FAB/26 em 16/07/2026. Godoy 21/07/26.</t>
   </si>
   <si>
+    <t>Recibo 639/FAB/26 entregue em 12/08/26. Ramon 13/08/26</t>
+  </si>
+  <si>
     <t>Atendido conforme NF-e 1996 em 22/07/2026. Godoy 23/07/2026</t>
   </si>
   <si>
@@ -5878,13 +5881,16 @@
     <t>Estoque com 12 EA do Pn LM600-9 (Alternado). Godoy 12/08/26.</t>
   </si>
   <si>
+    <t>AWB 127-5256 7745 com previsão de entrega em 14/08. Ramon 13/08/26</t>
+  </si>
+  <si>
     <t>Estoque no alternado 285K4. Caso use do estoque, verificar validade que consta no item. Ramon 12/08/26.</t>
   </si>
   <si>
     <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron J17626242 - previsão de entrega em Miami 05/08 AWB4238 em desembaraço no GIGRJ em 06/8/2026, previsao de CANAL hoje às 18 horas ATZ Marcio 6/8/2026 - MATERIAL EM RECEBIMENTO VEE ONE 07/08/2026 16:31, SERÁ ENVIADO NA SEGUNDA FEIRA - AWB 12752106375 dpe 14/08/2026</t>
   </si>
   <si>
-    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - previsão de entrega em Miami 11/08</t>
+    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Consolidando embarque próximo voo para o GIG</t>
   </si>
   <si>
     <t>Colocado pedido Textron IJ17575583 - entregue em Miami 15/07. Carga rercepcionada GIG 19/07 - Aguardando liberação do SEFAZ. ATZ 21/07 - material em processo de expedição RC 23/07/2026 - MATERIAL ENVIADO PELO RECIBO 639/FAB/26 - AWB 12750389603 DPE 13/08/2026</t>
@@ -5899,7 +5905,28 @@
     <t>Enviado para o Operador(02 EA), atendimento parcial, em 31/07/2026 -AWB 127-5041 6833- REZ - o outro 1 EA será atendido pelo estoque FAB. conforme solicitado por Email- CLA-03-08 - AWB 127-5082 1282 -1 EA ENVIADO ESTOQUE FAB - Material entregue dia 06/08/2026</t>
   </si>
   <si>
+    <t>Temos 4 EA em manutenção na William, será pedido prioridade. CLA-03-08</t>
+  </si>
+  <si>
+    <t>PEDIDO NO EPM E-C98-26060 - CLA-05-08 , por gentileza, me confirme se está correto a data da informação e prazo de entrega do item.O item solicitado não atende a pane do sistema ARCOND,pôs a pane é de 18/11/2024, anterior ao contrato vigente ,desta forma deve ser feito toda analise do sistema ,devido muito tempo inoperante e sem o item. SO R1 Bispo VEE-ONE-BE em 06/08/26</t>
+  </si>
+  <si>
     <t>Foi solicitado abertura de O.S. no dia 7 -08-26 de 6 EA. As OSs foram abertas e aguardando recolhimento para reparo. CLA-10-08 - ITEM FOI RECOLHIDO PELA WILLIAM- CLA-11-08</t>
+  </si>
+  <si>
+    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08</t>
+  </si>
+  <si>
+    <t>TEM ESTOQUE NA VEEONE</t>
+  </si>
+  <si>
+    <t>Em estoque na V1 JPA 12/8/26 Marcio 13:23</t>
+  </si>
+  <si>
+    <t>Previsao de entrega da oficina do RJ na V1 JPA 13/8/2026 durante o dia, horario comercial, ATZ Marcio 12/8 13:22hs</t>
+  </si>
+  <si>
+    <t>1 Unidade na oficina em BH William, solicitado prioridade na entrega DPE 14/8, aguardando orçamento final ATZ Marcio 12/8 13:24hs</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7496,7 +7523,7 @@
         <v>1497</v>
       </c>
       <c r="W2" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7558,16 +7585,16 @@
         <v>1498</v>
       </c>
       <c r="W3" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X3" t="s">
-        <v>1963</v>
+        <v>1972</v>
       </c>
       <c r="Y3" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z3" t="s">
-        <v>2122</v>
+        <v>2131</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7629,7 +7656,7 @@
         <v>1497</v>
       </c>
       <c r="W4" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7691,7 +7718,7 @@
         <v>1499</v>
       </c>
       <c r="W5" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7753,7 +7780,7 @@
         <v>1500</v>
       </c>
       <c r="W6" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7815,7 +7842,7 @@
         <v>1501</v>
       </c>
       <c r="W7" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7877,7 +7904,7 @@
         <v>1502</v>
       </c>
       <c r="W8" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7939,7 +7966,7 @@
         <v>1503</v>
       </c>
       <c r="W9" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8001,7 +8028,7 @@
         <v>1504</v>
       </c>
       <c r="W10" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8063,7 +8090,7 @@
         <v>1505</v>
       </c>
       <c r="W11" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8125,7 +8152,7 @@
         <v>1506</v>
       </c>
       <c r="W12" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8187,7 +8214,7 @@
         <v>1502</v>
       </c>
       <c r="W13" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8249,16 +8276,16 @@
         <v>1507</v>
       </c>
       <c r="W14" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X14" t="s">
-        <v>1964</v>
+        <v>1973</v>
       </c>
       <c r="Y14" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z14" t="s">
-        <v>2123</v>
+        <v>2132</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8317,7 +8344,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8382,7 +8409,7 @@
         <v>1508</v>
       </c>
       <c r="W16" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8444,7 +8471,7 @@
         <v>1509</v>
       </c>
       <c r="W17" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8506,7 +8533,7 @@
         <v>1500</v>
       </c>
       <c r="W18" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8568,7 +8595,7 @@
         <v>1500</v>
       </c>
       <c r="W19" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8630,7 +8657,7 @@
         <v>1510</v>
       </c>
       <c r="W20" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8692,7 +8719,7 @@
         <v>1511</v>
       </c>
       <c r="W21" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8754,7 +8781,7 @@
         <v>1511</v>
       </c>
       <c r="W22" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8816,7 +8843,7 @@
         <v>1512</v>
       </c>
       <c r="W23" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8875,7 +8902,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -8934,7 +8961,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -8996,7 +9023,7 @@
         <v>1500</v>
       </c>
       <c r="W26" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9055,7 +9082,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9114,7 +9141,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9176,7 +9203,7 @@
         <v>1513</v>
       </c>
       <c r="W29" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9235,7 +9262,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9297,7 +9324,7 @@
         <v>1514</v>
       </c>
       <c r="W31" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9359,7 +9386,7 @@
         <v>1515</v>
       </c>
       <c r="W32" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9421,7 +9448,7 @@
         <v>1516</v>
       </c>
       <c r="W33" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9483,7 +9510,7 @@
         <v>1517</v>
       </c>
       <c r="W34" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9545,7 +9572,7 @@
         <v>1518</v>
       </c>
       <c r="W35" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9607,7 +9634,7 @@
         <v>1514</v>
       </c>
       <c r="W36" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9669,7 +9696,7 @@
         <v>1519</v>
       </c>
       <c r="W37" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9731,7 +9758,7 @@
         <v>1497</v>
       </c>
       <c r="W38" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9793,7 +9820,7 @@
         <v>1516</v>
       </c>
       <c r="W39" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9855,7 +9882,7 @@
         <v>1520</v>
       </c>
       <c r="W40" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -9917,7 +9944,7 @@
         <v>1521</v>
       </c>
       <c r="W41" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -9979,16 +10006,16 @@
         <v>1522</v>
       </c>
       <c r="W42" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X42" t="s">
-        <v>1965</v>
+        <v>1974</v>
       </c>
       <c r="Y42" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z42" t="s">
-        <v>2124</v>
+        <v>2133</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10050,7 +10077,7 @@
         <v>1516</v>
       </c>
       <c r="W43" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10112,7 +10139,7 @@
         <v>1523</v>
       </c>
       <c r="W44" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10174,7 +10201,7 @@
         <v>1516</v>
       </c>
       <c r="W45" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10236,7 +10263,7 @@
         <v>1516</v>
       </c>
       <c r="W46" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10298,7 +10325,7 @@
         <v>1524</v>
       </c>
       <c r="W47" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10360,7 +10387,7 @@
         <v>1525</v>
       </c>
       <c r="W48" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10422,7 +10449,7 @@
         <v>1526</v>
       </c>
       <c r="W49" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10484,7 +10511,7 @@
         <v>1527</v>
       </c>
       <c r="W50" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10546,7 +10573,7 @@
         <v>1528</v>
       </c>
       <c r="W51" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10608,7 +10635,7 @@
         <v>1517</v>
       </c>
       <c r="W52" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10670,7 +10697,7 @@
         <v>1511</v>
       </c>
       <c r="W53" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10732,7 +10759,7 @@
         <v>1511</v>
       </c>
       <c r="W54" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10794,7 +10821,7 @@
         <v>1511</v>
       </c>
       <c r="W55" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10856,7 +10883,7 @@
         <v>1529</v>
       </c>
       <c r="W56" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -10918,7 +10945,7 @@
         <v>1530</v>
       </c>
       <c r="W57" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -10980,16 +11007,16 @@
         <v>1531</v>
       </c>
       <c r="W58" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X58" t="s">
-        <v>1966</v>
+        <v>1975</v>
       </c>
       <c r="Y58" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z58" t="s">
-        <v>2125</v>
+        <v>2134</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11051,7 +11078,7 @@
         <v>1532</v>
       </c>
       <c r="W59" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11113,7 +11140,7 @@
         <v>1533</v>
       </c>
       <c r="W60" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11175,7 +11202,7 @@
         <v>1511</v>
       </c>
       <c r="W61" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11237,7 +11264,7 @@
         <v>1534</v>
       </c>
       <c r="W62" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11296,7 +11323,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11355,7 +11382,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11414,7 +11441,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11473,7 +11500,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11532,7 +11559,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11591,7 +11618,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11653,7 +11680,7 @@
         <v>1535</v>
       </c>
       <c r="W69" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11715,7 +11742,7 @@
         <v>1533</v>
       </c>
       <c r="W70" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11777,7 +11804,7 @@
         <v>1518</v>
       </c>
       <c r="W71" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11839,7 +11866,7 @@
         <v>1536</v>
       </c>
       <c r="W72" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -11901,7 +11928,7 @@
         <v>1537</v>
       </c>
       <c r="W73" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -11963,16 +11990,16 @@
         <v>1538</v>
       </c>
       <c r="W74" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X74" t="s">
-        <v>1967</v>
+        <v>1976</v>
       </c>
       <c r="Y74" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z74" t="s">
-        <v>2126</v>
+        <v>2135</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12034,16 +12061,16 @@
         <v>1539</v>
       </c>
       <c r="W75" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X75" t="s">
-        <v>1968</v>
+        <v>1977</v>
       </c>
       <c r="Y75" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z75" t="s">
-        <v>2127</v>
+        <v>2136</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12105,7 +12132,7 @@
         <v>1518</v>
       </c>
       <c r="W76" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12167,7 +12194,7 @@
         <v>1518</v>
       </c>
       <c r="W77" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12229,10 +12256,10 @@
         <v>1540</v>
       </c>
       <c r="W78" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="Z78" t="s">
-        <v>2128</v>
+        <v>2137</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12297,7 +12324,7 @@
         <v>1541</v>
       </c>
       <c r="W79" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12356,7 +12383,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12415,7 +12442,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12477,7 +12504,7 @@
         <v>1542</v>
       </c>
       <c r="W82" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12539,7 +12566,7 @@
         <v>1543</v>
       </c>
       <c r="W83" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12601,7 +12628,7 @@
         <v>1544</v>
       </c>
       <c r="W84" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12660,7 +12687,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12722,7 +12749,7 @@
         <v>1545</v>
       </c>
       <c r="W86" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12784,7 +12811,7 @@
         <v>1546</v>
       </c>
       <c r="W87" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12846,7 +12873,7 @@
         <v>1546</v>
       </c>
       <c r="W88" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -12908,7 +12935,7 @@
         <v>1511</v>
       </c>
       <c r="W89" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -12970,16 +12997,16 @@
         <v>1547</v>
       </c>
       <c r="W90" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X90" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="Y90" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z90" t="s">
-        <v>2129</v>
+        <v>2138</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13041,16 +13068,16 @@
         <v>1548</v>
       </c>
       <c r="W91" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X91" t="s">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="Y91" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z91" t="s">
-        <v>2130</v>
+        <v>2139</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13112,7 +13139,7 @@
         <v>1549</v>
       </c>
       <c r="W92" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13174,7 +13201,7 @@
         <v>1550</v>
       </c>
       <c r="W93" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13236,7 +13263,7 @@
         <v>1550</v>
       </c>
       <c r="W94" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13298,7 +13325,7 @@
         <v>1551</v>
       </c>
       <c r="W95" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13360,16 +13387,16 @@
         <v>1552</v>
       </c>
       <c r="W96" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X96" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
       <c r="Y96" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z96" t="s">
-        <v>2131</v>
+        <v>2140</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13431,7 +13458,7 @@
         <v>1553</v>
       </c>
       <c r="W97" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13493,7 +13520,7 @@
         <v>1554</v>
       </c>
       <c r="W98" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13555,7 +13582,7 @@
         <v>1555</v>
       </c>
       <c r="W99" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13617,7 +13644,7 @@
         <v>1556</v>
       </c>
       <c r="W100" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13679,16 +13706,16 @@
         <v>1557</v>
       </c>
       <c r="W101" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X101" t="s">
-        <v>1971</v>
+        <v>1980</v>
       </c>
       <c r="Y101" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z101" t="s">
-        <v>2132</v>
+        <v>2141</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13750,7 +13777,7 @@
         <v>1558</v>
       </c>
       <c r="W102" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13812,7 +13839,7 @@
         <v>1558</v>
       </c>
       <c r="W103" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13874,7 +13901,7 @@
         <v>1559</v>
       </c>
       <c r="W104" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -13936,16 +13963,16 @@
         <v>1560</v>
       </c>
       <c r="W105" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X105" t="s">
-        <v>1972</v>
+        <v>1981</v>
       </c>
       <c r="Y105" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z105" t="s">
-        <v>2133</v>
+        <v>2142</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14007,16 +14034,16 @@
         <v>1561</v>
       </c>
       <c r="W106" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X106" t="s">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="Y106" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z106" t="s">
-        <v>2134</v>
+        <v>2143</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14078,7 +14105,7 @@
         <v>1562</v>
       </c>
       <c r="W107" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14140,16 +14167,16 @@
         <v>1563</v>
       </c>
       <c r="W108" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X108" t="s">
-        <v>1974</v>
+        <v>1983</v>
       </c>
       <c r="Y108" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z108" t="s">
-        <v>2135</v>
+        <v>2144</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14211,16 +14238,16 @@
         <v>1564</v>
       </c>
       <c r="W109" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X109" t="s">
-        <v>1975</v>
+        <v>1984</v>
       </c>
       <c r="Y109" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z109" t="s">
-        <v>2136</v>
+        <v>2145</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14279,7 +14306,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14341,16 +14368,16 @@
         <v>1565</v>
       </c>
       <c r="W111" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X111" t="s">
-        <v>1976</v>
+        <v>1985</v>
       </c>
       <c r="Y111" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z111" t="s">
-        <v>2137</v>
+        <v>2146</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14412,16 +14439,16 @@
         <v>1566</v>
       </c>
       <c r="W112" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X112" t="s">
-        <v>1976</v>
+        <v>1985</v>
       </c>
       <c r="Y112" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z112" t="s">
-        <v>2138</v>
+        <v>2147</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14483,16 +14510,16 @@
         <v>1567</v>
       </c>
       <c r="W113" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X113" t="s">
-        <v>1977</v>
+        <v>1986</v>
       </c>
       <c r="Y113" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z113" t="s">
-        <v>2139</v>
+        <v>2148</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14554,16 +14581,16 @@
         <v>1568</v>
       </c>
       <c r="W114" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X114" t="s">
-        <v>1978</v>
+        <v>1987</v>
       </c>
       <c r="Y114" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z114" t="s">
-        <v>2140</v>
+        <v>2149</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14625,16 +14652,16 @@
         <v>1564</v>
       </c>
       <c r="W115" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X115" t="s">
-        <v>1975</v>
+        <v>1984</v>
       </c>
       <c r="Y115" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z115" t="s">
-        <v>2141</v>
+        <v>2150</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14696,16 +14723,16 @@
         <v>1564</v>
       </c>
       <c r="W116" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X116" t="s">
-        <v>1975</v>
+        <v>1984</v>
       </c>
       <c r="Y116" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z116" t="s">
-        <v>2142</v>
+        <v>2151</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14767,16 +14794,16 @@
         <v>1569</v>
       </c>
       <c r="W117" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X117" t="s">
-        <v>1979</v>
+        <v>1988</v>
       </c>
       <c r="Y117" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z117" t="s">
-        <v>2143</v>
+        <v>2152</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14838,16 +14865,16 @@
         <v>1570</v>
       </c>
       <c r="W118" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X118" t="s">
-        <v>1980</v>
+        <v>1989</v>
       </c>
       <c r="Y118" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z118" t="s">
-        <v>2144</v>
+        <v>2153</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -14909,7 +14936,7 @@
         <v>1571</v>
       </c>
       <c r="W119" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -14971,16 +14998,16 @@
         <v>1572</v>
       </c>
       <c r="W120" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X120" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y120" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z120" t="s">
-        <v>2145</v>
+        <v>2154</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15042,16 +15069,16 @@
         <v>1572</v>
       </c>
       <c r="W121" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X121" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y121" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z121" t="s">
-        <v>2146</v>
+        <v>2155</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15113,16 +15140,16 @@
         <v>1572</v>
       </c>
       <c r="W122" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X122" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y122" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z122" t="s">
-        <v>2147</v>
+        <v>2156</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15184,16 +15211,16 @@
         <v>1572</v>
       </c>
       <c r="W123" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X123" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y123" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z123" t="s">
-        <v>2148</v>
+        <v>2157</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15255,16 +15282,16 @@
         <v>1572</v>
       </c>
       <c r="W124" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X124" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y124" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z124" t="s">
-        <v>2149</v>
+        <v>2158</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15326,16 +15353,16 @@
         <v>1572</v>
       </c>
       <c r="W125" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X125" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y125" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z125" t="s">
-        <v>2150</v>
+        <v>2159</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15397,16 +15424,16 @@
         <v>1572</v>
       </c>
       <c r="W126" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X126" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y126" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z126" t="s">
-        <v>2151</v>
+        <v>2160</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15468,16 +15495,16 @@
         <v>1573</v>
       </c>
       <c r="W127" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X127" t="s">
-        <v>1982</v>
+        <v>1991</v>
       </c>
       <c r="Y127" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z127" t="s">
-        <v>2152</v>
+        <v>2161</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15539,16 +15566,16 @@
         <v>1574</v>
       </c>
       <c r="W128" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X128" t="s">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="Y128" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z128" t="s">
-        <v>2153</v>
+        <v>2162</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15610,16 +15637,16 @@
         <v>1572</v>
       </c>
       <c r="W129" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X129" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y129" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z129" t="s">
-        <v>2154</v>
+        <v>2163</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15681,16 +15708,16 @@
         <v>1572</v>
       </c>
       <c r="W130" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X130" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y130" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z130" t="s">
-        <v>2155</v>
+        <v>2164</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15752,7 +15779,7 @@
         <v>1575</v>
       </c>
       <c r="W131" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15811,7 +15838,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15870,7 +15897,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -15932,16 +15959,16 @@
         <v>1572</v>
       </c>
       <c r="W134" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X134" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y134" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z134" t="s">
-        <v>2156</v>
+        <v>2165</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16003,16 +16030,16 @@
         <v>1572</v>
       </c>
       <c r="W135" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X135" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y135" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z135" t="s">
-        <v>2157</v>
+        <v>2166</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16074,7 +16101,7 @@
         <v>1571</v>
       </c>
       <c r="W136" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16133,7 +16160,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16195,16 +16222,16 @@
         <v>1576</v>
       </c>
       <c r="W138" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X138" t="s">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="Y138" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z138" t="s">
-        <v>2158</v>
+        <v>2167</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16266,16 +16293,16 @@
         <v>1564</v>
       </c>
       <c r="W139" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X139" t="s">
-        <v>1975</v>
+        <v>1984</v>
       </c>
       <c r="Y139" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z139" t="s">
-        <v>2159</v>
+        <v>2168</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16337,16 +16364,16 @@
         <v>1572</v>
       </c>
       <c r="W140" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X140" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y140" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z140" t="s">
-        <v>2160</v>
+        <v>2169</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16405,7 +16432,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16464,7 +16491,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16526,16 +16553,16 @@
         <v>1577</v>
       </c>
       <c r="W143" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X143" t="s">
-        <v>1985</v>
+        <v>1994</v>
       </c>
       <c r="Y143" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z143" t="s">
-        <v>2161</v>
+        <v>2170</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16597,16 +16624,16 @@
         <v>1578</v>
       </c>
       <c r="W144" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X144" t="s">
-        <v>1986</v>
+        <v>1995</v>
       </c>
       <c r="Y144" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z144" t="s">
-        <v>2162</v>
+        <v>2171</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16668,16 +16695,16 @@
         <v>1579</v>
       </c>
       <c r="W145" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X145" t="s">
-        <v>1987</v>
+        <v>1996</v>
       </c>
       <c r="Y145" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z145" t="s">
-        <v>2163</v>
+        <v>2172</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16739,16 +16766,16 @@
         <v>1580</v>
       </c>
       <c r="W146" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X146" t="s">
-        <v>1988</v>
+        <v>1997</v>
       </c>
       <c r="Y146" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z146" t="s">
-        <v>2164</v>
+        <v>2173</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16807,7 +16834,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16869,7 +16896,7 @@
         <v>1581</v>
       </c>
       <c r="W148" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -16931,16 +16958,16 @@
         <v>1582</v>
       </c>
       <c r="W149" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X149" t="s">
-        <v>1989</v>
+        <v>1998</v>
       </c>
       <c r="Y149" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z149" t="s">
-        <v>2165</v>
+        <v>2174</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17002,7 +17029,7 @@
         <v>1583</v>
       </c>
       <c r="W150" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17064,16 +17091,16 @@
         <v>1584</v>
       </c>
       <c r="W151" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X151" t="s">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="Y151" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z151" t="s">
-        <v>2166</v>
+        <v>2175</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17135,7 +17162,7 @@
         <v>1583</v>
       </c>
       <c r="W152" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17197,7 +17224,7 @@
         <v>1581</v>
       </c>
       <c r="W153" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17259,7 +17286,7 @@
         <v>1583</v>
       </c>
       <c r="W154" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17321,7 +17348,7 @@
         <v>1583</v>
       </c>
       <c r="W155" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17383,16 +17410,16 @@
         <v>1585</v>
       </c>
       <c r="W156" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X156" t="s">
-        <v>1991</v>
+        <v>2000</v>
       </c>
       <c r="Y156" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z156" t="s">
-        <v>2167</v>
+        <v>2176</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17454,7 +17481,7 @@
         <v>1581</v>
       </c>
       <c r="W157" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17516,16 +17543,16 @@
         <v>1586</v>
       </c>
       <c r="W158" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X158" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="Y158" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z158" t="s">
-        <v>2168</v>
+        <v>2177</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17587,16 +17614,16 @@
         <v>1587</v>
       </c>
       <c r="W159" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X159" t="s">
-        <v>1993</v>
+        <v>2002</v>
       </c>
       <c r="Y159" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z159" t="s">
-        <v>2169</v>
+        <v>2178</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17658,16 +17685,16 @@
         <v>1586</v>
       </c>
       <c r="W160" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X160" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="Y160" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z160" t="s">
-        <v>2170</v>
+        <v>2179</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17729,16 +17756,16 @@
         <v>1586</v>
       </c>
       <c r="W161" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X161" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="Y161" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z161" t="s">
-        <v>2171</v>
+        <v>2180</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17800,16 +17827,16 @@
         <v>1586</v>
       </c>
       <c r="W162" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X162" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="Y162" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z162" t="s">
-        <v>2172</v>
+        <v>2181</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17871,16 +17898,16 @@
         <v>1588</v>
       </c>
       <c r="W163" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X163" t="s">
-        <v>1994</v>
+        <v>2003</v>
       </c>
       <c r="Y163" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z163" t="s">
-        <v>2173</v>
+        <v>2182</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -17942,16 +17969,16 @@
         <v>1589</v>
       </c>
       <c r="W164" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X164" t="s">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="Y164" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z164" t="s">
-        <v>2174</v>
+        <v>2183</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18013,16 +18040,16 @@
         <v>1590</v>
       </c>
       <c r="W165" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X165" t="s">
-        <v>1996</v>
+        <v>2005</v>
       </c>
       <c r="Y165" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z165" t="s">
-        <v>2175</v>
+        <v>2184</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18084,16 +18111,16 @@
         <v>1591</v>
       </c>
       <c r="W166" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X166" t="s">
-        <v>1997</v>
+        <v>2006</v>
       </c>
       <c r="Y166" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z166" t="s">
-        <v>2176</v>
+        <v>2185</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18155,16 +18182,16 @@
         <v>1569</v>
       </c>
       <c r="W167" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X167" t="s">
-        <v>1979</v>
+        <v>1988</v>
       </c>
       <c r="Y167" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z167" t="s">
-        <v>2177</v>
+        <v>2186</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18226,16 +18253,16 @@
         <v>1572</v>
       </c>
       <c r="W168" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X168" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y168" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z168" t="s">
-        <v>2178</v>
+        <v>2187</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18297,7 +18324,7 @@
         <v>1592</v>
       </c>
       <c r="W169" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18359,16 +18386,16 @@
         <v>1572</v>
       </c>
       <c r="W170" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X170" t="s">
-        <v>1981</v>
+        <v>1990</v>
       </c>
       <c r="Y170" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z170" t="s">
-        <v>2179</v>
+        <v>2188</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18430,16 +18457,16 @@
         <v>1593</v>
       </c>
       <c r="W171" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X171" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="Y171" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z171" t="s">
-        <v>2180</v>
+        <v>2189</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18501,16 +18528,16 @@
         <v>1594</v>
       </c>
       <c r="W172" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X172" t="s">
-        <v>1998</v>
+        <v>2007</v>
       </c>
       <c r="Y172" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z172" t="s">
-        <v>2181</v>
+        <v>2190</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18572,16 +18599,16 @@
         <v>1595</v>
       </c>
       <c r="W173" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X173" t="s">
-        <v>1999</v>
+        <v>2008</v>
       </c>
       <c r="Y173" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z173" t="s">
-        <v>2182</v>
+        <v>2191</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18643,16 +18670,16 @@
         <v>1596</v>
       </c>
       <c r="W174" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X174" t="s">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="Y174" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z174" t="s">
-        <v>2183</v>
+        <v>2192</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18714,16 +18741,16 @@
         <v>1597</v>
       </c>
       <c r="W175" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X175" t="s">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="Y175" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z175" t="s">
-        <v>2184</v>
+        <v>2193</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18785,16 +18812,16 @@
         <v>1598</v>
       </c>
       <c r="W176" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X176" t="s">
-        <v>2002</v>
+        <v>2011</v>
       </c>
       <c r="Y176" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z176" t="s">
-        <v>2185</v>
+        <v>2194</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18856,7 +18883,7 @@
         <v>1592</v>
       </c>
       <c r="W177" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -18918,16 +18945,16 @@
         <v>1599</v>
       </c>
       <c r="W178" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X178" t="s">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="Y178" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z178" t="s">
-        <v>2186</v>
+        <v>2195</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -18989,16 +19016,16 @@
         <v>1600</v>
       </c>
       <c r="W179" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X179" t="s">
-        <v>1992</v>
+        <v>2001</v>
       </c>
       <c r="Y179" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z179" t="s">
-        <v>2187</v>
+        <v>2196</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19060,7 +19087,7 @@
         <v>1601</v>
       </c>
       <c r="W180" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19122,16 +19149,16 @@
         <v>1602</v>
       </c>
       <c r="W181" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X181" t="s">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="Y181" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z181" t="s">
-        <v>2188</v>
+        <v>2197</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19193,16 +19220,16 @@
         <v>1602</v>
       </c>
       <c r="W182" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X182" t="s">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="Y182" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z182" t="s">
-        <v>2189</v>
+        <v>2198</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19264,16 +19291,16 @@
         <v>1603</v>
       </c>
       <c r="W183" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X183" t="s">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="Y183" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z183" t="s">
-        <v>2190</v>
+        <v>2199</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19335,16 +19362,16 @@
         <v>1604</v>
       </c>
       <c r="W184" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X184" t="s">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="Y184" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z184" t="s">
-        <v>2191</v>
+        <v>2200</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19406,16 +19433,16 @@
         <v>1605</v>
       </c>
       <c r="W185" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X185" t="s">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="Y185" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z185" t="s">
-        <v>2192</v>
+        <v>2201</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19477,7 +19504,7 @@
         <v>1606</v>
       </c>
       <c r="W186" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19539,7 +19566,7 @@
         <v>1607</v>
       </c>
       <c r="W187" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19601,7 +19628,7 @@
         <v>1608</v>
       </c>
       <c r="W188" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19663,7 +19690,7 @@
         <v>1609</v>
       </c>
       <c r="W189" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19725,16 +19752,16 @@
         <v>1610</v>
       </c>
       <c r="W190" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X190" t="s">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="Y190" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z190" t="s">
-        <v>2193</v>
+        <v>2202</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19796,16 +19823,16 @@
         <v>1611</v>
       </c>
       <c r="W191" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X191" t="s">
-        <v>2009</v>
+        <v>2018</v>
       </c>
       <c r="Y191" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z191" t="s">
-        <v>2194</v>
+        <v>2203</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19867,7 +19894,7 @@
         <v>1612</v>
       </c>
       <c r="W192" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -19929,7 +19956,7 @@
         <v>1612</v>
       </c>
       <c r="W193" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -19991,16 +20018,16 @@
         <v>1613</v>
       </c>
       <c r="W194" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X194" t="s">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="Y194" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z194" t="s">
-        <v>2195</v>
+        <v>2204</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20062,16 +20089,16 @@
         <v>1614</v>
       </c>
       <c r="W195" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X195" t="s">
-        <v>1988</v>
+        <v>1997</v>
       </c>
       <c r="Y195" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z195" t="s">
-        <v>2196</v>
+        <v>2205</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20133,16 +20160,16 @@
         <v>1615</v>
       </c>
       <c r="W196" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X196" t="s">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="Y196" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z196" t="s">
-        <v>2197</v>
+        <v>2206</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20204,16 +20231,16 @@
         <v>1611</v>
       </c>
       <c r="W197" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X197" t="s">
-        <v>2009</v>
+        <v>2018</v>
       </c>
       <c r="Y197" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z197" t="s">
-        <v>2198</v>
+        <v>2207</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20275,7 +20302,7 @@
         <v>1616</v>
       </c>
       <c r="W198" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20337,7 +20364,7 @@
         <v>1617</v>
       </c>
       <c r="W199" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20399,16 +20426,16 @@
         <v>1618</v>
       </c>
       <c r="W200" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X200" t="s">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="Y200" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z200" t="s">
-        <v>2199</v>
+        <v>2208</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20470,16 +20497,16 @@
         <v>1618</v>
       </c>
       <c r="W201" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X201" t="s">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="Y201" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z201" t="s">
-        <v>2200</v>
+        <v>2209</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20541,16 +20568,16 @@
         <v>1619</v>
       </c>
       <c r="W202" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X202" t="s">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="Y202" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z202" t="s">
-        <v>2201</v>
+        <v>2210</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20612,16 +20639,16 @@
         <v>1620</v>
       </c>
       <c r="W203" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X203" t="s">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="Y203" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z203" t="s">
-        <v>2202</v>
+        <v>2211</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20683,16 +20710,16 @@
         <v>1621</v>
       </c>
       <c r="W204" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X204" t="s">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="Y204" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z204" t="s">
-        <v>2203</v>
+        <v>2212</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20754,16 +20781,16 @@
         <v>1622</v>
       </c>
       <c r="W205" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X205" t="s">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="Y205" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z205" t="s">
-        <v>2204</v>
+        <v>2213</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20825,16 +20852,16 @@
         <v>1623</v>
       </c>
       <c r="W206" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X206" t="s">
-        <v>2017</v>
+        <v>2026</v>
       </c>
       <c r="Y206" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z206" t="s">
-        <v>2205</v>
+        <v>2214</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -20896,16 +20923,16 @@
         <v>1624</v>
       </c>
       <c r="W207" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X207" t="s">
-        <v>2018</v>
+        <v>2027</v>
       </c>
       <c r="Y207" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z207" t="s">
-        <v>2206</v>
+        <v>2215</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -20967,16 +20994,16 @@
         <v>1625</v>
       </c>
       <c r="W208" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X208" t="s">
-        <v>2019</v>
+        <v>2028</v>
       </c>
       <c r="Y208" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z208" t="s">
-        <v>2207</v>
+        <v>2216</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21038,7 +21065,7 @@
         <v>1626</v>
       </c>
       <c r="W209" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21100,16 +21127,16 @@
         <v>1627</v>
       </c>
       <c r="W210" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X210" t="s">
-        <v>2020</v>
+        <v>2029</v>
       </c>
       <c r="Y210" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z210" t="s">
-        <v>2208</v>
+        <v>2217</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21171,16 +21198,16 @@
         <v>1628</v>
       </c>
       <c r="W211" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X211" t="s">
-        <v>2021</v>
+        <v>2030</v>
       </c>
       <c r="Y211" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z211" t="s">
-        <v>2209</v>
+        <v>2218</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21242,16 +21269,16 @@
         <v>1629</v>
       </c>
       <c r="W212" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X212" t="s">
-        <v>2022</v>
+        <v>2031</v>
       </c>
       <c r="Y212" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z212" t="s">
-        <v>2210</v>
+        <v>2219</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21313,16 +21340,16 @@
         <v>1630</v>
       </c>
       <c r="W213" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X213" t="s">
-        <v>2019</v>
+        <v>2028</v>
       </c>
       <c r="Y213" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z213" t="s">
-        <v>2211</v>
+        <v>2220</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21384,7 +21411,7 @@
         <v>1631</v>
       </c>
       <c r="W214" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21446,16 +21473,16 @@
         <v>1596</v>
       </c>
       <c r="W215" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X215" t="s">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="Y215" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z215" t="s">
-        <v>2212</v>
+        <v>2221</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21517,16 +21544,16 @@
         <v>1632</v>
       </c>
       <c r="W216" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X216" t="s">
-        <v>2023</v>
+        <v>2032</v>
       </c>
       <c r="Y216" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z216" t="s">
-        <v>2213</v>
+        <v>2222</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21588,7 +21615,7 @@
         <v>1633</v>
       </c>
       <c r="W217" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21650,16 +21677,16 @@
         <v>1634</v>
       </c>
       <c r="W218" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X218" t="s">
-        <v>2024</v>
+        <v>2033</v>
       </c>
       <c r="Y218" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z218" t="s">
-        <v>2214</v>
+        <v>2223</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21721,16 +21748,16 @@
         <v>1635</v>
       </c>
       <c r="W219" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X219" t="s">
-        <v>2025</v>
+        <v>2034</v>
       </c>
       <c r="Y219" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z219" t="s">
-        <v>2215</v>
+        <v>2224</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21792,7 +21819,7 @@
         <v>1636</v>
       </c>
       <c r="W220" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21854,7 +21881,7 @@
         <v>1637</v>
       </c>
       <c r="W221" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -21916,7 +21943,7 @@
         <v>1636</v>
       </c>
       <c r="W222" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -21978,7 +22005,7 @@
         <v>1637</v>
       </c>
       <c r="W223" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22040,16 +22067,16 @@
         <v>1638</v>
       </c>
       <c r="W224" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X224" t="s">
-        <v>2026</v>
+        <v>2035</v>
       </c>
       <c r="Y224" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z224" t="s">
-        <v>2216</v>
+        <v>2225</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22111,16 +22138,16 @@
         <v>1639</v>
       </c>
       <c r="W225" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X225" t="s">
-        <v>2027</v>
+        <v>2036</v>
       </c>
       <c r="Y225" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z225" t="s">
-        <v>2217</v>
+        <v>2226</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22182,7 +22209,7 @@
         <v>1640</v>
       </c>
       <c r="W226" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22244,7 +22271,7 @@
         <v>1641</v>
       </c>
       <c r="W227" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22306,7 +22333,7 @@
         <v>1642</v>
       </c>
       <c r="W228" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22368,16 +22395,16 @@
         <v>1643</v>
       </c>
       <c r="W229" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X229" t="s">
-        <v>2028</v>
+        <v>2037</v>
       </c>
       <c r="Y229" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z229" t="s">
-        <v>2218</v>
+        <v>2227</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22439,16 +22466,16 @@
         <v>1644</v>
       </c>
       <c r="W230" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X230" t="s">
-        <v>2019</v>
+        <v>2028</v>
       </c>
       <c r="Y230" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z230" t="s">
-        <v>2219</v>
+        <v>2228</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22510,16 +22537,16 @@
         <v>1645</v>
       </c>
       <c r="W231" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X231" t="s">
-        <v>2029</v>
+        <v>2038</v>
       </c>
       <c r="Y231" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z231" t="s">
-        <v>2220</v>
+        <v>2229</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22584,16 +22611,16 @@
         <v>1646</v>
       </c>
       <c r="W232" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X232" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="Y232" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z232" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22655,16 +22682,16 @@
         <v>1647</v>
       </c>
       <c r="W233" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X233" t="s">
-        <v>2031</v>
+        <v>2040</v>
       </c>
       <c r="Y233" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z233" t="s">
-        <v>2221</v>
+        <v>2230</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22726,16 +22753,16 @@
         <v>1648</v>
       </c>
       <c r="W234" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X234" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="Y234" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z234" t="s">
-        <v>2222</v>
+        <v>2231</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22797,16 +22824,16 @@
         <v>1648</v>
       </c>
       <c r="W235" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X235" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="Y235" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z235" t="s">
-        <v>2223</v>
+        <v>2232</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22868,16 +22895,16 @@
         <v>1649</v>
       </c>
       <c r="W236" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X236" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="Y236" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z236" t="s">
-        <v>2224</v>
+        <v>2233</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -22939,7 +22966,7 @@
         <v>1650</v>
       </c>
       <c r="W237" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23001,7 +23028,7 @@
         <v>1651</v>
       </c>
       <c r="W238" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23063,16 +23090,16 @@
         <v>1652</v>
       </c>
       <c r="W239" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X239" t="s">
-        <v>2033</v>
+        <v>2042</v>
       </c>
       <c r="Y239" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z239" t="s">
-        <v>2225</v>
+        <v>2234</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23134,16 +23161,16 @@
         <v>1653</v>
       </c>
       <c r="W240" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X240" t="s">
-        <v>2034</v>
+        <v>2043</v>
       </c>
       <c r="Y240" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z240" t="s">
-        <v>2226</v>
+        <v>2235</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23205,7 +23232,7 @@
         <v>1654</v>
       </c>
       <c r="W241" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23267,16 +23294,16 @@
         <v>1655</v>
       </c>
       <c r="W242" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X242" t="s">
-        <v>2035</v>
+        <v>2044</v>
       </c>
       <c r="Y242" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z242" t="s">
-        <v>2227</v>
+        <v>2236</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23338,16 +23365,16 @@
         <v>1656</v>
       </c>
       <c r="W243" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X243" t="s">
-        <v>2036</v>
+        <v>2045</v>
       </c>
       <c r="Y243" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z243" t="s">
-        <v>2228</v>
+        <v>2237</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23409,16 +23436,16 @@
         <v>1655</v>
       </c>
       <c r="W244" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X244" t="s">
-        <v>2035</v>
+        <v>2044</v>
       </c>
       <c r="Y244" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z244" t="s">
-        <v>2229</v>
+        <v>2238</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23480,16 +23507,16 @@
         <v>1657</v>
       </c>
       <c r="W245" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X245" t="s">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="Y245" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z245" t="s">
-        <v>2230</v>
+        <v>2239</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23551,16 +23578,16 @@
         <v>1656</v>
       </c>
       <c r="W246" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X246" t="s">
-        <v>2036</v>
+        <v>2045</v>
       </c>
       <c r="Y246" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z246" t="s">
-        <v>2231</v>
+        <v>2240</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23622,16 +23649,16 @@
         <v>1657</v>
       </c>
       <c r="W247" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X247" t="s">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="Y247" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z247" t="s">
-        <v>2232</v>
+        <v>2241</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23693,16 +23720,16 @@
         <v>1658</v>
       </c>
       <c r="W248" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X248" t="s">
-        <v>2038</v>
+        <v>2047</v>
       </c>
       <c r="Y248" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z248" t="s">
-        <v>2233</v>
+        <v>2242</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23764,16 +23791,16 @@
         <v>1648</v>
       </c>
       <c r="W249" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X249" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="Y249" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z249" t="s">
-        <v>2234</v>
+        <v>2243</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23835,7 +23862,7 @@
         <v>1659</v>
       </c>
       <c r="W250" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -23897,7 +23924,7 @@
         <v>1660</v>
       </c>
       <c r="W251" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -23959,16 +23986,16 @@
         <v>1661</v>
       </c>
       <c r="W252" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X252" t="s">
-        <v>2039</v>
+        <v>2048</v>
       </c>
       <c r="Y252" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z252" t="s">
-        <v>2235</v>
+        <v>2244</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24030,16 +24057,16 @@
         <v>1662</v>
       </c>
       <c r="W253" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X253" t="s">
-        <v>2040</v>
+        <v>2049</v>
       </c>
       <c r="Y253" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z253" t="s">
-        <v>2236</v>
+        <v>2245</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24101,7 +24128,7 @@
         <v>1663</v>
       </c>
       <c r="W254" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24163,16 +24190,16 @@
         <v>1664</v>
       </c>
       <c r="W255" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X255" t="s">
-        <v>2041</v>
+        <v>2050</v>
       </c>
       <c r="Y255" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z255" t="s">
-        <v>2237</v>
+        <v>2246</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24234,7 +24261,7 @@
         <v>1665</v>
       </c>
       <c r="W256" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24299,7 +24326,7 @@
         <v>1666</v>
       </c>
       <c r="W257" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24361,7 +24388,7 @@
         <v>1667</v>
       </c>
       <c r="W258" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24423,7 +24450,7 @@
         <v>1667</v>
       </c>
       <c r="W259" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24485,7 +24512,7 @@
         <v>1668</v>
       </c>
       <c r="W260" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24547,16 +24574,16 @@
         <v>1669</v>
       </c>
       <c r="W261" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X261" t="s">
-        <v>2039</v>
+        <v>2048</v>
       </c>
       <c r="Y261" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z261" t="s">
-        <v>2238</v>
+        <v>2247</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24618,13 +24645,13 @@
         <v>1670</v>
       </c>
       <c r="W262" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X262" t="s">
-        <v>2042</v>
+        <v>2051</v>
       </c>
       <c r="Y262" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24686,16 +24713,16 @@
         <v>1671</v>
       </c>
       <c r="W263" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X263" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="Y263" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z263" t="s">
-        <v>2239</v>
+        <v>2248</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24757,7 +24784,7 @@
         <v>1672</v>
       </c>
       <c r="W264" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24819,7 +24846,7 @@
         <v>1672</v>
       </c>
       <c r="W265" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24881,7 +24908,7 @@
         <v>1673</v>
       </c>
       <c r="W266" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -24943,16 +24970,16 @@
         <v>1674</v>
       </c>
       <c r="W267" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X267" t="s">
-        <v>2023</v>
+        <v>2032</v>
       </c>
       <c r="Y267" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z267" t="s">
-        <v>2240</v>
+        <v>2249</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25014,16 +25041,16 @@
         <v>1675</v>
       </c>
       <c r="W268" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X268" t="s">
-        <v>2043</v>
+        <v>2052</v>
       </c>
       <c r="Y268" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z268" t="s">
-        <v>2241</v>
+        <v>2250</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25085,7 +25112,7 @@
         <v>1516</v>
       </c>
       <c r="W269" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25147,7 +25174,7 @@
         <v>1676</v>
       </c>
       <c r="W270" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25209,7 +25236,7 @@
         <v>1677</v>
       </c>
       <c r="W271" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25271,16 +25298,16 @@
         <v>1678</v>
       </c>
       <c r="W272" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X272" t="s">
-        <v>2044</v>
+        <v>2053</v>
       </c>
       <c r="Y272" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z272" t="s">
-        <v>2242</v>
+        <v>2251</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25339,7 +25366,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25401,7 +25428,7 @@
         <v>1679</v>
       </c>
       <c r="W274" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25460,7 +25487,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25522,7 +25549,7 @@
         <v>1680</v>
       </c>
       <c r="W276" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25584,7 +25611,7 @@
         <v>1681</v>
       </c>
       <c r="W277" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25646,16 +25673,16 @@
         <v>1682</v>
       </c>
       <c r="W278" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X278" t="s">
-        <v>2045</v>
+        <v>2054</v>
       </c>
       <c r="Y278" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z278" t="s">
-        <v>2243</v>
+        <v>2252</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25717,16 +25744,16 @@
         <v>1683</v>
       </c>
       <c r="W279" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X279" t="s">
-        <v>2046</v>
+        <v>2055</v>
       </c>
       <c r="Y279" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z279" t="s">
-        <v>2244</v>
+        <v>2253</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25788,16 +25815,16 @@
         <v>1683</v>
       </c>
       <c r="W280" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X280" t="s">
-        <v>2046</v>
+        <v>2055</v>
       </c>
       <c r="Y280" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z280" t="s">
-        <v>2245</v>
+        <v>2254</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25859,16 +25886,16 @@
         <v>1684</v>
       </c>
       <c r="W281" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X281" t="s">
-        <v>2046</v>
+        <v>2055</v>
       </c>
       <c r="Y281" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z281" t="s">
-        <v>2246</v>
+        <v>2255</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -25930,7 +25957,7 @@
         <v>1685</v>
       </c>
       <c r="W282" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -25992,7 +26019,7 @@
         <v>1686</v>
       </c>
       <c r="W283" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26054,7 +26081,7 @@
         <v>1687</v>
       </c>
       <c r="W284" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26116,16 +26143,16 @@
         <v>1688</v>
       </c>
       <c r="W285" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X285" t="s">
-        <v>2047</v>
+        <v>2056</v>
       </c>
       <c r="Y285" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z285" t="s">
-        <v>2247</v>
+        <v>2256</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26187,7 +26214,7 @@
         <v>1689</v>
       </c>
       <c r="W286" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26249,16 +26276,16 @@
         <v>1683</v>
       </c>
       <c r="W287" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X287" t="s">
-        <v>2046</v>
+        <v>2055</v>
       </c>
       <c r="Y287" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z287" t="s">
-        <v>2248</v>
+        <v>2257</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26320,16 +26347,16 @@
         <v>1690</v>
       </c>
       <c r="W288" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X288" t="s">
-        <v>2048</v>
+        <v>2057</v>
       </c>
       <c r="Y288" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z288" t="s">
-        <v>2249</v>
+        <v>2258</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26391,7 +26418,7 @@
         <v>1691</v>
       </c>
       <c r="W289" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26453,16 +26480,16 @@
         <v>1692</v>
       </c>
       <c r="W290" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X290" t="s">
-        <v>2049</v>
+        <v>2058</v>
       </c>
       <c r="Y290" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z290" t="s">
-        <v>2250</v>
+        <v>2259</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26524,16 +26551,16 @@
         <v>1693</v>
       </c>
       <c r="W291" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X291" t="s">
-        <v>2050</v>
+        <v>2059</v>
       </c>
       <c r="Y291" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z291" t="s">
-        <v>2251</v>
+        <v>2260</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26595,7 +26622,7 @@
         <v>1694</v>
       </c>
       <c r="W292" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26654,7 +26681,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26716,7 +26743,7 @@
         <v>1695</v>
       </c>
       <c r="W294" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26778,7 +26805,7 @@
         <v>1696</v>
       </c>
       <c r="W295" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26840,7 +26867,7 @@
         <v>1697</v>
       </c>
       <c r="W296" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -26902,13 +26929,13 @@
         <v>1698</v>
       </c>
       <c r="W297" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X297" t="s">
-        <v>2051</v>
+        <v>2060</v>
       </c>
       <c r="Z297" t="s">
-        <v>2252</v>
+        <v>2261</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -26970,7 +26997,7 @@
         <v>1699</v>
       </c>
       <c r="W298" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27032,7 +27059,7 @@
         <v>1700</v>
       </c>
       <c r="W299" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27094,7 +27121,7 @@
         <v>1701</v>
       </c>
       <c r="W300" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27156,7 +27183,7 @@
         <v>1702</v>
       </c>
       <c r="W301" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27218,7 +27245,7 @@
         <v>1703</v>
       </c>
       <c r="W302" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27280,16 +27307,16 @@
         <v>1704</v>
       </c>
       <c r="W303" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X303" t="s">
-        <v>2052</v>
+        <v>2061</v>
       </c>
       <c r="Y303" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z303" t="s">
-        <v>2253</v>
+        <v>2262</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27351,7 +27378,7 @@
         <v>1705</v>
       </c>
       <c r="W304" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27413,7 +27440,7 @@
         <v>1706</v>
       </c>
       <c r="W305" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27475,7 +27502,7 @@
         <v>1707</v>
       </c>
       <c r="W306" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27537,7 +27564,7 @@
         <v>1708</v>
       </c>
       <c r="W307" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27599,7 +27626,7 @@
         <v>1701</v>
       </c>
       <c r="W308" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27661,7 +27688,7 @@
         <v>1709</v>
       </c>
       <c r="W309" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27723,7 +27750,7 @@
         <v>1710</v>
       </c>
       <c r="W310" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27785,7 +27812,7 @@
         <v>1711</v>
       </c>
       <c r="W311" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27847,7 +27874,7 @@
         <v>1712</v>
       </c>
       <c r="W312" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -27909,7 +27936,7 @@
         <v>1713</v>
       </c>
       <c r="W313" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -27971,7 +27998,7 @@
         <v>1714</v>
       </c>
       <c r="W314" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28033,7 +28060,7 @@
         <v>1715</v>
       </c>
       <c r="W315" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28095,7 +28122,7 @@
         <v>1716</v>
       </c>
       <c r="W316" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28157,7 +28184,7 @@
         <v>1717</v>
       </c>
       <c r="W317" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28219,7 +28246,7 @@
         <v>1718</v>
       </c>
       <c r="W318" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28281,7 +28308,7 @@
         <v>1719</v>
       </c>
       <c r="W319" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28340,13 +28367,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X320" t="s">
-        <v>2053</v>
+        <v>2062</v>
       </c>
       <c r="Z320" t="s">
-        <v>2254</v>
+        <v>2263</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28405,7 +28432,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28464,7 +28491,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28523,7 +28550,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28585,7 +28612,7 @@
         <v>1720</v>
       </c>
       <c r="W324" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28647,7 +28674,7 @@
         <v>1721</v>
       </c>
       <c r="W325" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28709,7 +28736,7 @@
         <v>1722</v>
       </c>
       <c r="W326" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28771,7 +28798,7 @@
         <v>1723</v>
       </c>
       <c r="W327" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28830,7 +28857,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -28892,7 +28919,7 @@
         <v>1723</v>
       </c>
       <c r="W329" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -28954,7 +28981,7 @@
         <v>1724</v>
       </c>
       <c r="W330" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29016,7 +29043,7 @@
         <v>1725</v>
       </c>
       <c r="W331" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29078,7 +29105,7 @@
         <v>1725</v>
       </c>
       <c r="W332" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29140,7 +29167,7 @@
         <v>1726</v>
       </c>
       <c r="W333" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29202,7 +29229,7 @@
         <v>1727</v>
       </c>
       <c r="W334" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29264,7 +29291,7 @@
         <v>1728</v>
       </c>
       <c r="W335" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29323,13 +29350,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X336" t="s">
-        <v>2054</v>
+        <v>2063</v>
       </c>
       <c r="Z336" t="s">
-        <v>2255</v>
+        <v>2264</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29391,7 +29418,7 @@
         <v>1729</v>
       </c>
       <c r="W337" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29453,13 +29480,13 @@
         <v>1730</v>
       </c>
       <c r="W338" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X338" t="s">
-        <v>2055</v>
+        <v>2064</v>
       </c>
       <c r="Z338" t="s">
-        <v>2256</v>
+        <v>2265</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29521,13 +29548,13 @@
         <v>1731</v>
       </c>
       <c r="W339" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X339" t="s">
-        <v>2056</v>
+        <v>2065</v>
       </c>
       <c r="Z339" t="s">
-        <v>2257</v>
+        <v>2266</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29589,7 +29616,7 @@
         <v>1732</v>
       </c>
       <c r="W340" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29651,7 +29678,7 @@
         <v>1733</v>
       </c>
       <c r="W341" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29713,10 +29740,10 @@
         <v>1734</v>
       </c>
       <c r="W342" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X342" t="s">
-        <v>2057</v>
+        <v>2066</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29778,7 +29805,7 @@
         <v>1735</v>
       </c>
       <c r="W343" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29840,7 +29867,7 @@
         <v>1736</v>
       </c>
       <c r="W344" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -29902,13 +29929,13 @@
         <v>1737</v>
       </c>
       <c r="W345" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X345" t="s">
-        <v>2058</v>
+        <v>2067</v>
       </c>
       <c r="Z345" t="s">
-        <v>2258</v>
+        <v>2267</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -29970,7 +29997,7 @@
         <v>1701</v>
       </c>
       <c r="W346" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30032,7 +30059,7 @@
         <v>1738</v>
       </c>
       <c r="W347" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30094,16 +30121,16 @@
         <v>1739</v>
       </c>
       <c r="W348" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X348" t="s">
-        <v>2059</v>
+        <v>2068</v>
       </c>
       <c r="Y348" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z348" t="s">
-        <v>2259</v>
+        <v>2268</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30168,13 +30195,13 @@
         <v>1740</v>
       </c>
       <c r="W349" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X349" t="s">
-        <v>2060</v>
+        <v>2069</v>
       </c>
       <c r="Z349" t="s">
-        <v>2260</v>
+        <v>2269</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30236,7 +30263,7 @@
         <v>1741</v>
       </c>
       <c r="W350" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30298,16 +30325,16 @@
         <v>1742</v>
       </c>
       <c r="W351" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X351" t="s">
-        <v>2061</v>
+        <v>2070</v>
       </c>
       <c r="Y351" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z351" t="s">
-        <v>2261</v>
+        <v>2270</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30369,13 +30396,13 @@
         <v>1743</v>
       </c>
       <c r="W352" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X352" t="s">
         <v>1743</v>
       </c>
       <c r="Z352" t="s">
-        <v>2262</v>
+        <v>2271</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30437,16 +30464,16 @@
         <v>1744</v>
       </c>
       <c r="W353" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X353" t="s">
-        <v>2062</v>
+        <v>2071</v>
       </c>
       <c r="Y353" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z353" t="s">
-        <v>2263</v>
+        <v>2272</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30508,7 +30535,7 @@
         <v>1745</v>
       </c>
       <c r="W354" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30570,7 +30597,7 @@
         <v>1746</v>
       </c>
       <c r="W355" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30629,7 +30656,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30688,7 +30715,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30747,7 +30774,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30809,7 +30836,7 @@
         <v>1747</v>
       </c>
       <c r="W359" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30874,7 +30901,7 @@
         <v>1748</v>
       </c>
       <c r="W360" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -30939,7 +30966,7 @@
         <v>1749</v>
       </c>
       <c r="W361" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31001,16 +31028,16 @@
         <v>1750</v>
       </c>
       <c r="W362" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X362" t="s">
-        <v>2063</v>
+        <v>2072</v>
       </c>
       <c r="Y362" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z362" t="s">
-        <v>2264</v>
+        <v>2273</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31072,16 +31099,16 @@
         <v>1751</v>
       </c>
       <c r="W363" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X363" t="s">
-        <v>2064</v>
+        <v>2073</v>
       </c>
       <c r="Y363" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z363" t="s">
-        <v>2265</v>
+        <v>2274</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31143,7 +31170,7 @@
         <v>1752</v>
       </c>
       <c r="W364" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31205,7 +31232,7 @@
         <v>1753</v>
       </c>
       <c r="W365" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31270,7 +31297,7 @@
         <v>1754</v>
       </c>
       <c r="W366" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31332,7 +31359,7 @@
         <v>1755</v>
       </c>
       <c r="W367" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31394,7 +31421,7 @@
         <v>1756</v>
       </c>
       <c r="W368" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31459,13 +31486,13 @@
         <v>1757</v>
       </c>
       <c r="W369" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X369" t="s">
-        <v>2065</v>
+        <v>2074</v>
       </c>
       <c r="Z369" t="s">
-        <v>2266</v>
+        <v>2275</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31527,7 +31554,7 @@
         <v>1758</v>
       </c>
       <c r="W370" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31589,16 +31616,16 @@
         <v>1759</v>
       </c>
       <c r="W371" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X371" t="s">
-        <v>2066</v>
+        <v>2075</v>
       </c>
       <c r="Y371" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z371" t="s">
-        <v>2267</v>
+        <v>2276</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31663,7 +31690,7 @@
         <v>1760</v>
       </c>
       <c r="W372" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31728,16 +31755,16 @@
         <v>1761</v>
       </c>
       <c r="W373" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X373" t="s">
-        <v>2067</v>
+        <v>2076</v>
       </c>
       <c r="Y373" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z373" t="s">
-        <v>2268</v>
+        <v>2277</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31799,7 +31826,7 @@
         <v>1762</v>
       </c>
       <c r="W374" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31864,7 +31891,7 @@
         <v>1763</v>
       </c>
       <c r="W375" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -31929,7 +31956,7 @@
         <v>1764</v>
       </c>
       <c r="W376" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -31994,7 +32021,7 @@
         <v>1764</v>
       </c>
       <c r="W377" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32059,13 +32086,13 @@
         <v>1765</v>
       </c>
       <c r="W378" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X378" t="s">
-        <v>2065</v>
+        <v>2074</v>
       </c>
       <c r="Z378" t="s">
-        <v>2269</v>
+        <v>2278</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32127,16 +32154,16 @@
         <v>1766</v>
       </c>
       <c r="W379" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X379" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="Y379" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z379" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32201,7 +32228,7 @@
         <v>1767</v>
       </c>
       <c r="W380" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32263,7 +32290,7 @@
         <v>1768</v>
       </c>
       <c r="W381" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32328,7 +32355,7 @@
         <v>1769</v>
       </c>
       <c r="W382" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32390,7 +32417,7 @@
         <v>1770</v>
       </c>
       <c r="W383" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32455,7 +32482,7 @@
         <v>1769</v>
       </c>
       <c r="W384" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32517,16 +32544,16 @@
         <v>1771</v>
       </c>
       <c r="W385" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X385" t="s">
-        <v>2068</v>
+        <v>2077</v>
       </c>
       <c r="Y385" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z385" t="s">
-        <v>2270</v>
+        <v>2279</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32594,7 +32621,7 @@
         <v>1772</v>
       </c>
       <c r="W386" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32656,7 +32683,7 @@
         <v>1773</v>
       </c>
       <c r="W387" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32718,7 +32745,7 @@
         <v>1774</v>
       </c>
       <c r="W388" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32780,16 +32807,16 @@
         <v>1775</v>
       </c>
       <c r="W389" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X389" t="s">
-        <v>2069</v>
+        <v>2078</v>
       </c>
       <c r="Y389" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z389" t="s">
-        <v>2271</v>
+        <v>2280</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32854,16 +32881,16 @@
         <v>1776</v>
       </c>
       <c r="W390" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X390" t="s">
-        <v>2070</v>
+        <v>2079</v>
       </c>
       <c r="Y390" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z390" t="s">
-        <v>2272</v>
+        <v>2281</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -32928,7 +32955,7 @@
         <v>1777</v>
       </c>
       <c r="W391" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -32990,7 +33017,7 @@
         <v>1778</v>
       </c>
       <c r="W392" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33052,16 +33079,16 @@
         <v>1779</v>
       </c>
       <c r="W393" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X393" t="s">
-        <v>2071</v>
+        <v>2080</v>
       </c>
       <c r="Y393" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z393" t="s">
-        <v>2273</v>
+        <v>2282</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33123,7 +33150,7 @@
         <v>1780</v>
       </c>
       <c r="W394" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33188,16 +33215,16 @@
         <v>1781</v>
       </c>
       <c r="W395" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X395" t="s">
-        <v>2072</v>
+        <v>2081</v>
       </c>
       <c r="Y395" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z395" t="s">
-        <v>2274</v>
+        <v>2283</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33262,13 +33289,13 @@
         <v>1782</v>
       </c>
       <c r="W396" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X396" t="s">
-        <v>2073</v>
+        <v>2082</v>
       </c>
       <c r="Y396" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33330,7 +33357,7 @@
         <v>1783</v>
       </c>
       <c r="W397" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33392,7 +33419,7 @@
         <v>1784</v>
       </c>
       <c r="W398" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33457,7 +33484,7 @@
         <v>1785</v>
       </c>
       <c r="W399" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33522,16 +33549,16 @@
         <v>1786</v>
       </c>
       <c r="W400" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X400" t="s">
-        <v>2074</v>
+        <v>2083</v>
       </c>
       <c r="Y400" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z400" t="s">
-        <v>2275</v>
+        <v>2284</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33596,7 +33623,7 @@
         <v>1787</v>
       </c>
       <c r="W401" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33661,7 +33688,7 @@
         <v>1788</v>
       </c>
       <c r="W402" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33726,16 +33753,16 @@
         <v>1789</v>
       </c>
       <c r="W403" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X403" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="Y403" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z403" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33800,7 +33827,7 @@
         <v>1790</v>
       </c>
       <c r="W404" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33865,7 +33892,7 @@
         <v>1791</v>
       </c>
       <c r="W405" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -33894,10 +33921,10 @@
         <v>2730</v>
       </c>
       <c r="H406" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="I406" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="J406" s="1">
         <v>46076</v>
@@ -33912,16 +33939,16 @@
         <v>1260</v>
       </c>
       <c r="N406" s="1">
-        <v>46091</v>
+        <v>46111</v>
       </c>
       <c r="O406" s="1">
         <v>46248</v>
       </c>
       <c r="Q406">
-        <v>155</v>
+        <v>-46111</v>
       </c>
       <c r="R406">
-        <v>166</v>
+        <v>-46080</v>
       </c>
       <c r="S406" t="s">
         <v>1493</v>
@@ -33933,13 +33960,13 @@
         <v>1792</v>
       </c>
       <c r="V406" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="W406" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA406" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407" spans="1:27">
@@ -33998,16 +34025,16 @@
         <v>1793</v>
       </c>
       <c r="W407" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X407" t="s">
-        <v>2075</v>
+        <v>2084</v>
       </c>
       <c r="Y407" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z407" t="s">
-        <v>2276</v>
+        <v>2285</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34072,13 +34099,13 @@
         <v>1794</v>
       </c>
       <c r="W408" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X408" t="s">
-        <v>2076</v>
+        <v>2085</v>
       </c>
       <c r="Z408" t="s">
-        <v>2076</v>
+        <v>2085</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34143,7 +34170,7 @@
         <v>1795</v>
       </c>
       <c r="W409" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34208,7 +34235,7 @@
         <v>1796</v>
       </c>
       <c r="W410" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34273,7 +34300,7 @@
         <v>1797</v>
       </c>
       <c r="W411" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34338,7 +34365,7 @@
         <v>1798</v>
       </c>
       <c r="W412" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34403,7 +34430,7 @@
         <v>1799</v>
       </c>
       <c r="W413" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34468,7 +34495,7 @@
         <v>1799</v>
       </c>
       <c r="W414" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34533,7 +34560,7 @@
         <v>1800</v>
       </c>
       <c r="W415" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34598,7 +34625,7 @@
         <v>1801</v>
       </c>
       <c r="W416" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34663,7 +34690,7 @@
         <v>1799</v>
       </c>
       <c r="W417" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34728,7 +34755,7 @@
         <v>1802</v>
       </c>
       <c r="W418" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34793,7 +34820,7 @@
         <v>1803</v>
       </c>
       <c r="W419" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34858,16 +34885,16 @@
         <v>1804</v>
       </c>
       <c r="W420" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X420" t="s">
-        <v>2077</v>
+        <v>2086</v>
       </c>
       <c r="Y420" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z420" t="s">
-        <v>2277</v>
+        <v>2286</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -34932,7 +34959,7 @@
         <v>1805</v>
       </c>
       <c r="W421" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -34997,7 +35024,7 @@
         <v>1806</v>
       </c>
       <c r="W422" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35062,7 +35089,7 @@
         <v>1807</v>
       </c>
       <c r="W423" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35127,16 +35154,16 @@
         <v>1808</v>
       </c>
       <c r="W424" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X424" t="s">
-        <v>2078</v>
+        <v>2087</v>
       </c>
       <c r="Y424" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z424" t="s">
-        <v>2278</v>
+        <v>2287</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35201,7 +35228,7 @@
         <v>1807</v>
       </c>
       <c r="W425" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35266,7 +35293,7 @@
         <v>1809</v>
       </c>
       <c r="W426" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35331,7 +35358,7 @@
         <v>1810</v>
       </c>
       <c r="W427" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35396,13 +35423,13 @@
         <v>1811</v>
       </c>
       <c r="W428" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X428" t="s">
-        <v>2079</v>
+        <v>2088</v>
       </c>
       <c r="Y428" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35467,16 +35494,16 @@
         <v>1812</v>
       </c>
       <c r="W429" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X429" t="s">
-        <v>2080</v>
+        <v>2089</v>
       </c>
       <c r="Y429" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z429" t="s">
-        <v>2279</v>
+        <v>2288</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35541,7 +35568,7 @@
         <v>1813</v>
       </c>
       <c r="W430" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35606,16 +35633,16 @@
         <v>1814</v>
       </c>
       <c r="W431" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X431" t="s">
-        <v>2081</v>
+        <v>2090</v>
       </c>
       <c r="Y431" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z431" t="s">
-        <v>2280</v>
+        <v>2289</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35680,7 +35707,7 @@
         <v>1815</v>
       </c>
       <c r="W432" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35745,7 +35772,7 @@
         <v>1816</v>
       </c>
       <c r="W433" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35810,7 +35837,7 @@
         <v>1817</v>
       </c>
       <c r="W434" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35875,7 +35902,7 @@
         <v>1818</v>
       </c>
       <c r="W435" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -35940,7 +35967,7 @@
         <v>1819</v>
       </c>
       <c r="W436" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36005,7 +36032,7 @@
         <v>1820</v>
       </c>
       <c r="W437" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36070,7 +36097,7 @@
         <v>1821</v>
       </c>
       <c r="W438" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36135,7 +36162,7 @@
         <v>1822</v>
       </c>
       <c r="W439" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36200,16 +36227,16 @@
         <v>1823</v>
       </c>
       <c r="W440" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X440" t="s">
-        <v>2082</v>
+        <v>2091</v>
       </c>
       <c r="Y440" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z440" t="s">
-        <v>2281</v>
+        <v>2290</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36274,16 +36301,16 @@
         <v>1824</v>
       </c>
       <c r="W441" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X441" t="s">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="Y441" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z441" t="s">
-        <v>2282</v>
+        <v>2291</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36348,16 +36375,16 @@
         <v>1825</v>
       </c>
       <c r="W442" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X442" t="s">
-        <v>2084</v>
+        <v>2093</v>
       </c>
       <c r="Y442" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z442" t="s">
-        <v>2283</v>
+        <v>2292</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36422,7 +36449,7 @@
         <v>1826</v>
       </c>
       <c r="W443" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36487,7 +36514,7 @@
         <v>1827</v>
       </c>
       <c r="W444" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36552,16 +36579,16 @@
         <v>1824</v>
       </c>
       <c r="W445" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X445" t="s">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="Y445" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z445" t="s">
-        <v>2284</v>
+        <v>2293</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36626,16 +36653,16 @@
         <v>1824</v>
       </c>
       <c r="W446" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X446" t="s">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="Y446" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z446" t="s">
-        <v>2285</v>
+        <v>2294</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36700,16 +36727,16 @@
         <v>1828</v>
       </c>
       <c r="W447" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X447" t="s">
-        <v>2085</v>
+        <v>2094</v>
       </c>
       <c r="Y447" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z447" t="s">
-        <v>2286</v>
+        <v>2295</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36774,16 +36801,16 @@
         <v>1824</v>
       </c>
       <c r="W448" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X448" t="s">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="Y448" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z448" t="s">
-        <v>2287</v>
+        <v>2296</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36848,16 +36875,16 @@
         <v>1824</v>
       </c>
       <c r="W449" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X449" t="s">
-        <v>2083</v>
+        <v>2092</v>
       </c>
       <c r="Y449" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z449" t="s">
-        <v>2288</v>
+        <v>2297</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -36922,16 +36949,16 @@
         <v>1829</v>
       </c>
       <c r="W450" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X450" t="s">
-        <v>2080</v>
+        <v>2089</v>
       </c>
       <c r="Y450" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z450" t="s">
-        <v>2289</v>
+        <v>2298</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -36996,16 +37023,16 @@
         <v>1830</v>
       </c>
       <c r="W451" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X451" t="s">
-        <v>2086</v>
+        <v>2095</v>
       </c>
       <c r="Y451" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z451" t="s">
-        <v>2290</v>
+        <v>2299</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37070,7 +37097,7 @@
         <v>1831</v>
       </c>
       <c r="W452" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37135,16 +37162,16 @@
         <v>1832</v>
       </c>
       <c r="W453" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X453" t="s">
-        <v>2087</v>
+        <v>2096</v>
       </c>
       <c r="Y453" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z453" t="s">
-        <v>2291</v>
+        <v>2300</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37209,16 +37236,16 @@
         <v>1833</v>
       </c>
       <c r="W454" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X454" t="s">
-        <v>2088</v>
+        <v>2097</v>
       </c>
       <c r="Y454" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z454" t="s">
-        <v>2292</v>
+        <v>2301</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37283,16 +37310,16 @@
         <v>1834</v>
       </c>
       <c r="W455" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X455" t="s">
-        <v>2089</v>
+        <v>2098</v>
       </c>
       <c r="Y455" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z455" t="s">
-        <v>2293</v>
+        <v>2302</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37357,16 +37384,16 @@
         <v>1835</v>
       </c>
       <c r="W456" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X456" t="s">
-        <v>2088</v>
+        <v>2097</v>
       </c>
       <c r="Y456" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z456" t="s">
-        <v>2294</v>
+        <v>2303</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37431,7 +37458,7 @@
         <v>1836</v>
       </c>
       <c r="W457" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37496,7 +37523,7 @@
         <v>1836</v>
       </c>
       <c r="W458" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37561,16 +37588,16 @@
         <v>1834</v>
       </c>
       <c r="W459" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X459" t="s">
-        <v>2089</v>
+        <v>2098</v>
       </c>
       <c r="Y459" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z459" t="s">
-        <v>2295</v>
+        <v>2304</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37635,16 +37662,16 @@
         <v>1837</v>
       </c>
       <c r="W460" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X460" t="s">
-        <v>2090</v>
+        <v>2099</v>
       </c>
       <c r="Y460" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z460" t="s">
-        <v>2296</v>
+        <v>2305</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37709,16 +37736,16 @@
         <v>1838</v>
       </c>
       <c r="W461" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X461" t="s">
-        <v>2091</v>
+        <v>2100</v>
       </c>
       <c r="Y461" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z461" t="s">
-        <v>2297</v>
+        <v>2306</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37783,7 +37810,7 @@
         <v>1839</v>
       </c>
       <c r="W462" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37848,16 +37875,16 @@
         <v>1840</v>
       </c>
       <c r="W463" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X463" t="s">
-        <v>2092</v>
+        <v>2101</v>
       </c>
       <c r="Y463" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z463" t="s">
-        <v>2298</v>
+        <v>2307</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -37922,16 +37949,16 @@
         <v>1841</v>
       </c>
       <c r="W464" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X464" t="s">
-        <v>2093</v>
+        <v>2102</v>
       </c>
       <c r="Y464" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z464" t="s">
-        <v>2299</v>
+        <v>2308</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -37996,16 +38023,16 @@
         <v>1842</v>
       </c>
       <c r="W465" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X465" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="Y465" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z465" t="s">
-        <v>2300</v>
+        <v>2309</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38070,7 +38097,7 @@
         <v>1843</v>
       </c>
       <c r="W466" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38135,16 +38162,16 @@
         <v>1844</v>
       </c>
       <c r="W467" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X467" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
       <c r="Y467" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z467" t="s">
-        <v>2301</v>
+        <v>2310</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38209,16 +38236,16 @@
         <v>1845</v>
       </c>
       <c r="W468" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X468" t="s">
-        <v>2096</v>
+        <v>2105</v>
       </c>
       <c r="Y468" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z468" t="s">
-        <v>2302</v>
+        <v>2311</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38283,16 +38310,16 @@
         <v>1846</v>
       </c>
       <c r="W469" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X469" t="s">
-        <v>2096</v>
+        <v>2105</v>
       </c>
       <c r="Y469" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z469" t="s">
-        <v>2303</v>
+        <v>2312</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38357,16 +38384,16 @@
         <v>1847</v>
       </c>
       <c r="W470" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X470" t="s">
-        <v>2097</v>
+        <v>2106</v>
       </c>
       <c r="Y470" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z470" t="s">
-        <v>2304</v>
+        <v>2313</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38431,7 +38458,7 @@
         <v>1848</v>
       </c>
       <c r="W471" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38496,16 +38523,16 @@
         <v>1849</v>
       </c>
       <c r="W472" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X472" t="s">
-        <v>2098</v>
+        <v>2107</v>
       </c>
       <c r="Y472" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z472" t="s">
-        <v>2305</v>
+        <v>2314</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38570,16 +38597,16 @@
         <v>1849</v>
       </c>
       <c r="W473" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X473" t="s">
-        <v>2098</v>
+        <v>2107</v>
       </c>
       <c r="Y473" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z473" t="s">
-        <v>2306</v>
+        <v>2315</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38644,7 +38671,7 @@
         <v>1850</v>
       </c>
       <c r="W474" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38709,16 +38736,16 @@
         <v>1851</v>
       </c>
       <c r="W475" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X475" t="s">
-        <v>2099</v>
+        <v>2108</v>
       </c>
       <c r="Y475" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z475" t="s">
-        <v>2307</v>
+        <v>2316</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38783,16 +38810,16 @@
         <v>1852</v>
       </c>
       <c r="W476" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X476" t="s">
-        <v>2100</v>
+        <v>2109</v>
       </c>
       <c r="Y476" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z476" t="s">
-        <v>2308</v>
+        <v>2317</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38857,7 +38884,7 @@
         <v>1853</v>
       </c>
       <c r="W477" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -38922,7 +38949,7 @@
         <v>1854</v>
       </c>
       <c r="W478" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -38987,16 +39014,16 @@
         <v>1855</v>
       </c>
       <c r="W479" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X479" t="s">
-        <v>2101</v>
+        <v>2110</v>
       </c>
       <c r="Y479" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z479" t="s">
-        <v>2309</v>
+        <v>2318</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39061,16 +39088,16 @@
         <v>1856</v>
       </c>
       <c r="W480" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X480" t="s">
-        <v>2102</v>
+        <v>2111</v>
       </c>
       <c r="Y480" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z480" t="s">
-        <v>2310</v>
+        <v>2319</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39135,16 +39162,16 @@
         <v>1857</v>
       </c>
       <c r="W481" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X481" t="s">
-        <v>2103</v>
+        <v>2112</v>
       </c>
       <c r="Y481" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z481" t="s">
-        <v>2311</v>
+        <v>2320</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39209,7 +39236,7 @@
         <v>1858</v>
       </c>
       <c r="W482" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39274,7 +39301,7 @@
         <v>1859</v>
       </c>
       <c r="W483" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39342,13 +39369,13 @@
         <v>1860</v>
       </c>
       <c r="W484" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2312</v>
+        <v>2321</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39413,7 +39440,7 @@
         <v>1861</v>
       </c>
       <c r="W485" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39481,13 +39508,13 @@
         <v>1862</v>
       </c>
       <c r="W486" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2313</v>
+        <v>2322</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39552,7 +39579,7 @@
         <v>1863</v>
       </c>
       <c r="W487" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39617,16 +39644,16 @@
         <v>1864</v>
       </c>
       <c r="W488" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X488" t="s">
-        <v>2104</v>
+        <v>2113</v>
       </c>
       <c r="Y488" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z488" t="s">
-        <v>2314</v>
+        <v>2323</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39691,7 +39718,7 @@
         <v>1865</v>
       </c>
       <c r="W489" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39759,13 +39786,13 @@
         <v>1866</v>
       </c>
       <c r="W490" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2315</v>
+        <v>2324</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39830,16 +39857,16 @@
         <v>1867</v>
       </c>
       <c r="W491" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X491" t="s">
-        <v>2105</v>
+        <v>2114</v>
       </c>
       <c r="Y491" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z491" t="s">
-        <v>2316</v>
+        <v>2325</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -39904,16 +39931,16 @@
         <v>1868</v>
       </c>
       <c r="W492" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X492" t="s">
-        <v>2106</v>
+        <v>2115</v>
       </c>
       <c r="Y492" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z492" t="s">
-        <v>2317</v>
+        <v>2326</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -39978,16 +40005,16 @@
         <v>1869</v>
       </c>
       <c r="W493" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X493" t="s">
-        <v>2107</v>
+        <v>2116</v>
       </c>
       <c r="Y493" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z493" t="s">
-        <v>2318</v>
+        <v>2327</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40052,13 +40079,13 @@
         <v>1870</v>
       </c>
       <c r="W494" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X494" t="s">
-        <v>2108</v>
+        <v>2117</v>
       </c>
       <c r="Y494" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40123,16 +40150,16 @@
         <v>1871</v>
       </c>
       <c r="W495" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X495" t="s">
-        <v>2109</v>
+        <v>2118</v>
       </c>
       <c r="Y495" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z495" t="s">
-        <v>2319</v>
+        <v>2328</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40197,7 +40224,7 @@
         <v>1872</v>
       </c>
       <c r="W496" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40265,7 +40292,7 @@
         <v>1873</v>
       </c>
       <c r="W497" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40330,7 +40357,7 @@
         <v>1874</v>
       </c>
       <c r="W498" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40398,7 +40425,7 @@
         <v>1875</v>
       </c>
       <c r="W499" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40463,16 +40490,16 @@
         <v>1876</v>
       </c>
       <c r="W500" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X500" t="s">
-        <v>2107</v>
+        <v>2116</v>
       </c>
       <c r="Y500" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z500" t="s">
-        <v>2320</v>
+        <v>2329</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40537,16 +40564,16 @@
         <v>1877</v>
       </c>
       <c r="W501" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X501" t="s">
-        <v>2110</v>
+        <v>2119</v>
       </c>
       <c r="Y501" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z501" t="s">
-        <v>2321</v>
+        <v>2330</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40611,7 +40638,7 @@
         <v>1878</v>
       </c>
       <c r="W502" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40679,7 +40706,7 @@
         <v>1879</v>
       </c>
       <c r="W503" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40747,16 +40774,16 @@
         <v>1880</v>
       </c>
       <c r="W504" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X504" t="s">
-        <v>2111</v>
+        <v>2120</v>
       </c>
       <c r="Y504" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z504" t="s">
-        <v>2322</v>
+        <v>2331</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40821,7 +40848,7 @@
         <v>1881</v>
       </c>
       <c r="W505" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40886,16 +40913,16 @@
         <v>1882</v>
       </c>
       <c r="W506" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X506" t="s">
-        <v>2112</v>
+        <v>2121</v>
       </c>
       <c r="Y506" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z506" t="s">
-        <v>2323</v>
+        <v>2332</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -40960,7 +40987,7 @@
         <v>1883</v>
       </c>
       <c r="W507" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41025,7 +41052,7 @@
         <v>1884</v>
       </c>
       <c r="W508" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41090,16 +41117,16 @@
         <v>1885</v>
       </c>
       <c r="W509" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X509" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="Y509" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z509" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41164,16 +41191,16 @@
         <v>1886</v>
       </c>
       <c r="W510" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X510" t="s">
-        <v>2113</v>
+        <v>2122</v>
       </c>
       <c r="Y510" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z510" t="s">
-        <v>2324</v>
+        <v>2333</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41241,7 +41268,7 @@
         <v>1887</v>
       </c>
       <c r="W511" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41309,7 +41336,7 @@
         <v>1888</v>
       </c>
       <c r="W512" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41377,7 +41404,7 @@
         <v>1889</v>
       </c>
       <c r="W513" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41445,7 +41472,7 @@
         <v>1889</v>
       </c>
       <c r="W514" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41513,7 +41540,7 @@
         <v>1889</v>
       </c>
       <c r="W515" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41581,13 +41608,13 @@
         <v>1890</v>
       </c>
       <c r="W516" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2325</v>
+        <v>2334</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41655,13 +41682,13 @@
         <v>1891</v>
       </c>
       <c r="W517" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2326</v>
+        <v>2335</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41729,16 +41756,16 @@
         <v>1892</v>
       </c>
       <c r="W518" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X518" t="s">
-        <v>2114</v>
+        <v>2123</v>
       </c>
       <c r="Y518" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z518" t="s">
-        <v>2327</v>
+        <v>2336</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41806,16 +41833,16 @@
         <v>1893</v>
       </c>
       <c r="W519" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X519" t="s">
-        <v>2115</v>
+        <v>2124</v>
       </c>
       <c r="Y519" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z519" t="s">
-        <v>2328</v>
+        <v>2337</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41880,7 +41907,7 @@
         <v>1496</v>
       </c>
       <c r="W520" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -41948,7 +41975,7 @@
         <v>1894</v>
       </c>
       <c r="W521" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42016,7 +42043,7 @@
         <v>1894</v>
       </c>
       <c r="W522" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42084,7 +42111,7 @@
         <v>1895</v>
       </c>
       <c r="W523" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42152,7 +42179,7 @@
         <v>1896</v>
       </c>
       <c r="W524" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42220,7 +42247,7 @@
         <v>1897</v>
       </c>
       <c r="W525" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42288,7 +42315,7 @@
         <v>1898</v>
       </c>
       <c r="W526" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42356,7 +42383,7 @@
         <v>1899</v>
       </c>
       <c r="W527" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42421,7 +42448,7 @@
         <v>1900</v>
       </c>
       <c r="W528" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42489,7 +42516,7 @@
         <v>1901</v>
       </c>
       <c r="W529" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42557,16 +42584,16 @@
         <v>1902</v>
       </c>
       <c r="W530" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X530" t="s">
-        <v>2116</v>
+        <v>2125</v>
       </c>
       <c r="Y530" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z530" t="s">
-        <v>2329</v>
+        <v>2338</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42634,7 +42661,7 @@
         <v>1903</v>
       </c>
       <c r="W531" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42699,7 +42726,7 @@
         <v>1904</v>
       </c>
       <c r="W532" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42767,16 +42794,16 @@
         <v>1905</v>
       </c>
       <c r="W533" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X533" t="s">
-        <v>2117</v>
+        <v>2126</v>
       </c>
       <c r="Y533" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z533" t="s">
-        <v>2330</v>
+        <v>2339</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42844,13 +42871,13 @@
         <v>1906</v>
       </c>
       <c r="W534" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2331</v>
+        <v>2340</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -42918,7 +42945,7 @@
         <v>1907</v>
       </c>
       <c r="W535" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -42986,7 +43013,7 @@
         <v>1908</v>
       </c>
       <c r="W536" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43054,16 +43081,16 @@
         <v>1909</v>
       </c>
       <c r="W537" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X537" t="s">
-        <v>2118</v>
+        <v>2127</v>
       </c>
       <c r="Y537" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z537" t="s">
-        <v>2332</v>
+        <v>2341</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43131,7 +43158,7 @@
         <v>1910</v>
       </c>
       <c r="W538" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43199,7 +43226,7 @@
         <v>1911</v>
       </c>
       <c r="W539" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43267,7 +43294,7 @@
         <v>1912</v>
       </c>
       <c r="W540" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43335,7 +43362,7 @@
         <v>1913</v>
       </c>
       <c r="W541" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43403,16 +43430,16 @@
         <v>1914</v>
       </c>
       <c r="W542" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X542" t="s">
-        <v>2119</v>
+        <v>2128</v>
       </c>
       <c r="Y542" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z542" t="s">
-        <v>2333</v>
+        <v>2342</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43480,7 +43507,7 @@
         <v>1915</v>
       </c>
       <c r="W543" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43548,16 +43575,16 @@
         <v>1916</v>
       </c>
       <c r="W544" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="X544" t="s">
-        <v>2120</v>
+        <v>2129</v>
       </c>
       <c r="Y544" t="s">
-        <v>2121</v>
+        <v>2130</v>
       </c>
       <c r="Z544" t="s">
-        <v>2334</v>
+        <v>2343</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43625,7 +43652,7 @@
         <v>1917</v>
       </c>
       <c r="W545" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43693,7 +43720,7 @@
         <v>1918</v>
       </c>
       <c r="W546" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43761,7 +43788,7 @@
         <v>1919</v>
       </c>
       <c r="W547" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43829,7 +43856,7 @@
         <v>1920</v>
       </c>
       <c r="W548" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -43897,7 +43924,7 @@
         <v>1920</v>
       </c>
       <c r="W549" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -43965,7 +43992,7 @@
         <v>1921</v>
       </c>
       <c r="W550" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44030,7 +44057,7 @@
         <v>1922</v>
       </c>
       <c r="W551" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44098,7 +44125,7 @@
         <v>1923</v>
       </c>
       <c r="W552" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44163,7 +44190,7 @@
         <v>1924</v>
       </c>
       <c r="W553" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44231,7 +44258,7 @@
         <v>1925</v>
       </c>
       <c r="W554" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44299,7 +44326,7 @@
         <v>1926</v>
       </c>
       <c r="W555" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44367,7 +44394,7 @@
         <v>1927</v>
       </c>
       <c r="W556" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44432,7 +44459,7 @@
         <v>1928</v>
       </c>
       <c r="W557" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44500,7 +44527,7 @@
         <v>1929</v>
       </c>
       <c r="W558" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44568,7 +44595,7 @@
         <v>1930</v>
       </c>
       <c r="W559" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44633,7 +44660,7 @@
         <v>1931</v>
       </c>
       <c r="W560" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44701,7 +44728,7 @@
         <v>1932</v>
       </c>
       <c r="W561" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44754,10 +44781,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R562">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S562" t="s">
         <v>1493</v>
@@ -44766,10 +44793,10 @@
         <v>1494</v>
       </c>
       <c r="V562" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="W562" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44834,7 +44861,7 @@
         <v>1933</v>
       </c>
       <c r="W563" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -44863,7 +44890,7 @@
         <v>2736</v>
       </c>
       <c r="H564" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="I564" t="s">
         <v>1257</v>
@@ -44887,10 +44914,10 @@
         <v>46248</v>
       </c>
       <c r="Q564">
-        <v>-2</v>
+        <v>-46248</v>
       </c>
       <c r="R564">
-        <v>29</v>
+        <v>-46217</v>
       </c>
       <c r="S564" t="s">
         <v>1493</v>
@@ -44898,14 +44925,17 @@
       <c r="T564" t="s">
         <v>1494</v>
       </c>
+      <c r="U564" t="s">
+        <v>1934</v>
+      </c>
       <c r="V564" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="W564" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA564" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565" spans="1:27">
@@ -44967,10 +44997,10 @@
         <v>1494</v>
       </c>
       <c r="U565" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="W565" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45035,10 +45065,10 @@
         <v>1493</v>
       </c>
       <c r="U566" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="W566" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45103,10 +45133,10 @@
         <v>1494</v>
       </c>
       <c r="U567" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="W567" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45159,10 +45189,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R568">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S568" t="s">
         <v>1493</v>
@@ -45171,13 +45201,13 @@
         <v>1494</v>
       </c>
       <c r="U568" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="V568" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="W568" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA568" t="b">
         <v>1</v>
@@ -45242,10 +45272,10 @@
         <v>1494</v>
       </c>
       <c r="U569" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="W569" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45307,10 +45337,10 @@
         <v>1494</v>
       </c>
       <c r="U570" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="W570" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45372,10 +45402,10 @@
         <v>1494</v>
       </c>
       <c r="U571" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="W571" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45440,10 +45470,10 @@
         <v>1494</v>
       </c>
       <c r="U572" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="W572" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45508,10 +45538,10 @@
         <v>1494</v>
       </c>
       <c r="U573" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="W573" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45576,10 +45606,10 @@
         <v>1494</v>
       </c>
       <c r="U574" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="W574" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45632,10 +45662,10 @@
         <v>46244</v>
       </c>
       <c r="Q575">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R575">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S575" t="s">
         <v>1493</v>
@@ -45644,13 +45674,13 @@
         <v>1493</v>
       </c>
       <c r="U575" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="V575" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="W575" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA575" t="b">
         <v>1</v>
@@ -45715,10 +45745,10 @@
         <v>1493</v>
       </c>
       <c r="U576" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="W576" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45783,10 +45813,10 @@
         <v>1493</v>
       </c>
       <c r="U577" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="W577" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45851,10 +45881,10 @@
         <v>1493</v>
       </c>
       <c r="U578" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="W578" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -45919,10 +45949,10 @@
         <v>1493</v>
       </c>
       <c r="U579" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="W579" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -45987,10 +46017,10 @@
         <v>1494</v>
       </c>
       <c r="U580" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="W580" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46055,10 +46085,10 @@
         <v>1494</v>
       </c>
       <c r="U581" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="W581" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46111,10 +46141,10 @@
         <v>46240</v>
       </c>
       <c r="Q582">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="R582">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S582" t="s">
         <v>1493</v>
@@ -46123,13 +46153,13 @@
         <v>1494</v>
       </c>
       <c r="U582" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="V582" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="W582" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA582" t="b">
         <v>1</v>
@@ -46178,11 +46208,14 @@
       <c r="N583" s="1">
         <v>46265</v>
       </c>
+      <c r="O583" s="1">
+        <v>46265</v>
+      </c>
       <c r="Q583">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="R583">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S583" t="s">
         <v>1493</v>
@@ -46190,8 +46223,11 @@
       <c r="T583" t="s">
         <v>1494</v>
       </c>
+      <c r="V583" t="s">
+        <v>1963</v>
+      </c>
       <c r="W583" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA583" t="b">
         <v>1</v>
@@ -46256,10 +46292,10 @@
         <v>1493</v>
       </c>
       <c r="U584" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="W584" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46324,10 +46360,10 @@
         <v>1493</v>
       </c>
       <c r="U585" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="W585" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46376,11 +46412,14 @@
       <c r="N586" s="1">
         <v>46269</v>
       </c>
+      <c r="O586" s="1">
+        <v>46269</v>
+      </c>
       <c r="Q586">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="R586">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S586" t="s">
         <v>1493</v>
@@ -46388,8 +46427,11 @@
       <c r="T586" t="s">
         <v>1494</v>
       </c>
+      <c r="V586" t="s">
+        <v>1964</v>
+      </c>
       <c r="W586" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46439,19 +46481,19 @@
         <v>46248</v>
       </c>
       <c r="Q587">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R587">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S587" t="s">
         <v>1493</v>
       </c>
       <c r="V587" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="W587" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA587" t="b">
         <v>1</v>
@@ -46500,11 +46542,14 @@
       <c r="N588" s="1">
         <v>46255</v>
       </c>
+      <c r="O588" s="1">
+        <v>46255</v>
+      </c>
       <c r="Q588">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="R588">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S588" t="s">
         <v>1494</v>
@@ -46513,10 +46558,13 @@
         <v>1494</v>
       </c>
       <c r="U588" t="s">
-        <v>1952</v>
+        <v>1953</v>
+      </c>
+      <c r="V588" t="s">
+        <v>1966</v>
       </c>
       <c r="W588" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46566,10 +46614,10 @@
         <v>46277</v>
       </c>
       <c r="Q589">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R589">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S589" t="s">
         <v>1494</v>
@@ -46578,10 +46626,13 @@
         <v>1493</v>
       </c>
       <c r="U589" t="s">
-        <v>1953</v>
+        <v>1954</v>
+      </c>
+      <c r="V589" t="s">
+        <v>1967</v>
       </c>
       <c r="W589" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA589" t="b">
         <v>1</v>
@@ -46631,10 +46682,10 @@
         <v>46257</v>
       </c>
       <c r="Q590">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R590">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S590" t="s">
         <v>1493</v>
@@ -46642,8 +46693,14 @@
       <c r="T590" t="s">
         <v>1494</v>
       </c>
+      <c r="U590" t="s">
+        <v>1955</v>
+      </c>
+      <c r="V590" t="s">
+        <v>1968</v>
+      </c>
       <c r="W590" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA590" t="b">
         <v>1</v>
@@ -46693,10 +46750,10 @@
         <v>46257</v>
       </c>
       <c r="Q591">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="R591">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S591" t="s">
         <v>1493</v>
@@ -46704,8 +46761,11 @@
       <c r="T591" t="s">
         <v>1493</v>
       </c>
+      <c r="V591" t="s">
+        <v>1969</v>
+      </c>
       <c r="W591" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA591" t="b">
         <v>1</v>
@@ -46755,10 +46815,10 @@
         <v>46277</v>
       </c>
       <c r="Q592">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R592">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S592" t="s">
         <v>1493</v>
@@ -46766,8 +46826,11 @@
       <c r="T592" t="s">
         <v>1493</v>
       </c>
+      <c r="V592" t="s">
+        <v>1970</v>
+      </c>
       <c r="W592" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA592" t="b">
         <v>1</v>
@@ -46817,10 +46880,10 @@
         <v>46277</v>
       </c>
       <c r="Q593">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R593">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S593" t="s">
         <v>1494</v>
@@ -46829,10 +46892,13 @@
         <v>1493</v>
       </c>
       <c r="U593" t="s">
-        <v>1954</v>
+        <v>1956</v>
+      </c>
+      <c r="V593" t="s">
+        <v>1967</v>
       </c>
       <c r="W593" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="AA593" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7459" uniqueCount="2348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7456" uniqueCount="2346">
   <si>
     <t>om_emg</t>
   </si>
@@ -5899,46 +5899,40 @@
     <t>Estoque no alternado 285K4. Caso use do estoque, verificar validade que consta no item. Ramon 12/08/26. Item em pane, anv autorizada a voar por 3 dias pela MMEL a contar de 12/08. Ramon 13/08/26</t>
   </si>
   <si>
-    <t>Foi solicitado via email no dia 02-03-2 o atendimento do item com estoque FAB. Claudio -02-03-26 - Em resposta, a coordenadoria disse que o estque seria insuficiente. Foi verificado que na T.O da ANV o QPA para esse item são 2 EA, solicitei confirmação. - Cláudio -02-03-2026. Solicitado o cancelamento da emergência em função da quantidade cedida ao 2733 ter sido de 01ea. Considerando o QPA 02 ea. Encontra-se em tratativa junto a fiscalização e o gestor do contrato conforme mensagem de e-mail de 05/03. - SOLICITAÇÃO E-C98-26047.Colocado pedido AOG Textron J17626242 - previsão de entrega em Miami 05/08 AWB4238 em desembaraço no GIGRJ em 06/8/2026, previsao de CANAL hoje às 18 horas ATZ Marcio 6/8/2026 - MATERIAL EM RECEBIMENTO VEE ONE 07/08/2026 16:31, SERÁ ENVIADO NA SEGUNDA FEIRA - AWB 12752106375 dpe 14/08/2026</t>
-  </si>
-  <si>
     <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Consolidando embarque próximo voo para o GIG</t>
   </si>
   <si>
-    <t>Colocado pedido Textron IJ17575583 - entregue em Miami 15/07. Carga rercepcionada GIG 19/07 - Aguardando liberação do SEFAZ. ATZ 21/07 - material em processo de expedição RC 23/07/2026 - MATERIAL ENVIADO PELO RECIBO 639/FAB/26 - AWB 12750389603 DPE 13/08/2026</t>
-  </si>
-  <si>
-    <t>Item em bancada porem em pessimo estado, foi solicitado recolhimento de mais unidades para envio a oficina para tentativa de reparo ATZ Marcio 17/7/26. Solicitado abertura de O.S. para 3EA do item no dia 16-07-26 via Email para a Coordenadoria - CLA-21-07-26- SERÁ ENTREGUE PELA WILLIAM DPE DIA 12-08-26 - CLA-11-08</t>
-  </si>
-  <si>
-    <t>Pedido I816822 entregue em Miami 27/07. Previsão de chegada GIG 30/07 (voo 4208). Previsão de canal 31/07 - MATERIAL RECEBIDO NA VEE ONE, EM PROCESSO DE EXPEDIÇÃO 04/08/2026 - ATZ RC - MATERIAL ENVIADO VIA RECIBO 650/FAB/26 - AWB 12750991113 DPE 06/08/2026, ESTÁ DISPONÍVEL PARA RETIRADA DESDE 04/08/2026 - retirado na Gollog dia 10/08/2026</t>
+    <t>Item em bancada porem em pessimo estado, foi solicitado recolhimento de mais unidades para envio a oficina para tentativa de reparo ATZ Marcio 17/7/26. Solicitado abertura de O.S. para 3EA do item no dia 16-07-26 via Email para a Coordenadoria - CLA-21-07-26- SERÁ ENTREGUE PELA WILLIAM DPE DIA 14-08-26 - CLA-13-08</t>
   </si>
   <si>
     <t>Enviado para o Operador(02 EA), atendimento parcial, em 31/07/2026 -AWB 127-5041 6833- REZ - o outro 1 EA será atendido pelo estoque FAB. conforme solicitado por Email- CLA-03-08 - AWB 127-5082 1282 -1 EA ENVIADO ESTOQUE FAB - Material entregue dia 06/08/2026</t>
   </si>
   <si>
-    <t>Temos 4 EA em manutenção na William, será pedido prioridade. CLA-03-08</t>
+    <t>Temos 4 EA em manutenção na William, será pedido prioridade. CLA-03-08 - DPE DIA 14-08 - CLA 13-08</t>
   </si>
   <si>
     <t>PEDIDO NO EPM E-C98-26060 - CLA-05-08 , por gentileza, me confirme se está correto a data da informação e prazo de entrega do item.O item solicitado não atende a pane do sistema ARCOND,pôs a pane é de 18/11/2024, anterior ao contrato vigente ,desta forma deve ser feito toda analise do sistema ,devido muito tempo inoperante e sem o item. SO R1 Bispo VEE-ONE-BE em 06/08/26</t>
   </si>
   <si>
-    <t>Foi solicitado abertura de O.S. no dia 7 -08-26 de 6 EA. As OSs foram abertas e aguardando recolhimento para reparo. CLA-10-08 - ITEM FOI RECOLHIDO PELA WILLIAM- CLA-11-08</t>
-  </si>
-  <si>
-    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08</t>
-  </si>
-  <si>
-    <t>TEM ESTOQUE NA VEEONE</t>
-  </si>
-  <si>
-    <t>Em estoque na V1 JPA 12/8/26 Marcio 13:23</t>
+    <t>Foi solicitado abertura de O.S. no dia 7 -08-26 de 6 EA. As OSs foram abertas e aguardando recolhimento para reparo. CLA-10-08 - ITEM FOI RECOLHIDO PELA WILLIAM- CLA-11-08 - DPE 14-08</t>
+  </si>
+  <si>
+    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08- ITEM AGUARDANDO DEFINIÇÃO DA COORDENADORIA QUANTO A EFETIVIDADE PARA APLICAÇÃO NA REFERIDA ANV.- CLA-13-08</t>
+  </si>
+  <si>
+    <t>Temos somente 03 ea em STK, favor utilizar o estoque FAB para posterior devolução. ATZ RC 13/08 - FOI SOLICITADO O ATENDIMENTO COM ESTOQUE FAB -CLA-13-08</t>
+  </si>
+  <si>
+    <t>Estoque veeone da base pamals- AWB 12752567745 - DPE 14/08/2026 - recibo 680/FAB/26</t>
   </si>
   <si>
     <t>Previsao de entrega da oficina do RJ na V1 JPA 13/8/2026 durante o dia, horario comercial, ATZ Marcio 12/8 13:22hs</t>
   </si>
   <si>
-    <t>1 Unidade na oficina em BH William, solicitado prioridade na entrega DPE 14/8, aguardando orçamento final ATZ Marcio 12/8 13:24hs</t>
+    <t>1 Unidade na oficina em BH William, solicitado prioridade na entrega DPE 14/8, aguardando orçamento final ATZ Marcio 12/8 13:24hs- DPE 14-08</t>
+  </si>
+  <si>
+    <t>Temos no STK V1, material em separação, recibo 682/FAB/26 - atz rc 13/08</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7535,7 +7529,7 @@
         <v>1500</v>
       </c>
       <c r="W2" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7597,16 +7591,16 @@
         <v>1501</v>
       </c>
       <c r="W3" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X3" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="Y3" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z3" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7668,7 +7662,7 @@
         <v>1500</v>
       </c>
       <c r="W4" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7730,7 +7724,7 @@
         <v>1502</v>
       </c>
       <c r="W5" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7792,7 +7786,7 @@
         <v>1503</v>
       </c>
       <c r="W6" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7854,7 +7848,7 @@
         <v>1504</v>
       </c>
       <c r="W7" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7916,7 +7910,7 @@
         <v>1505</v>
       </c>
       <c r="W8" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7978,7 +7972,7 @@
         <v>1506</v>
       </c>
       <c r="W9" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8040,7 +8034,7 @@
         <v>1507</v>
       </c>
       <c r="W10" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8102,7 +8096,7 @@
         <v>1508</v>
       </c>
       <c r="W11" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8164,7 +8158,7 @@
         <v>1509</v>
       </c>
       <c r="W12" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8226,7 +8220,7 @@
         <v>1505</v>
       </c>
       <c r="W13" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8288,16 +8282,16 @@
         <v>1510</v>
       </c>
       <c r="W14" t="s">
+        <v>1973</v>
+      </c>
+      <c r="X14" t="s">
         <v>1975</v>
       </c>
-      <c r="X14" t="s">
-        <v>1977</v>
-      </c>
       <c r="Y14" t="s">
+        <v>2132</v>
+      </c>
+      <c r="Z14" t="s">
         <v>2134</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>2136</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8356,7 +8350,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8421,7 +8415,7 @@
         <v>1511</v>
       </c>
       <c r="W16" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8483,7 +8477,7 @@
         <v>1512</v>
       </c>
       <c r="W17" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8545,7 +8539,7 @@
         <v>1503</v>
       </c>
       <c r="W18" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8607,7 +8601,7 @@
         <v>1503</v>
       </c>
       <c r="W19" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8669,7 +8663,7 @@
         <v>1513</v>
       </c>
       <c r="W20" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8731,7 +8725,7 @@
         <v>1514</v>
       </c>
       <c r="W21" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8793,7 +8787,7 @@
         <v>1514</v>
       </c>
       <c r="W22" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8855,7 +8849,7 @@
         <v>1515</v>
       </c>
       <c r="W23" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8914,7 +8908,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -8973,7 +8967,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9035,7 +9029,7 @@
         <v>1503</v>
       </c>
       <c r="W26" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9094,7 +9088,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9153,7 +9147,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9215,7 +9209,7 @@
         <v>1516</v>
       </c>
       <c r="W29" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9274,7 +9268,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9336,7 +9330,7 @@
         <v>1517</v>
       </c>
       <c r="W31" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9398,7 +9392,7 @@
         <v>1518</v>
       </c>
       <c r="W32" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9460,7 +9454,7 @@
         <v>1519</v>
       </c>
       <c r="W33" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9522,7 +9516,7 @@
         <v>1520</v>
       </c>
       <c r="W34" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9584,7 +9578,7 @@
         <v>1521</v>
       </c>
       <c r="W35" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9646,7 +9640,7 @@
         <v>1517</v>
       </c>
       <c r="W36" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9708,7 +9702,7 @@
         <v>1522</v>
       </c>
       <c r="W37" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9770,7 +9764,7 @@
         <v>1500</v>
       </c>
       <c r="W38" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9832,7 +9826,7 @@
         <v>1519</v>
       </c>
       <c r="W39" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9894,7 +9888,7 @@
         <v>1523</v>
       </c>
       <c r="W40" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -9956,7 +9950,7 @@
         <v>1524</v>
       </c>
       <c r="W41" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10018,16 +10012,16 @@
         <v>1525</v>
       </c>
       <c r="W42" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X42" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="Y42" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z42" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10089,7 +10083,7 @@
         <v>1519</v>
       </c>
       <c r="W43" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10151,7 +10145,7 @@
         <v>1526</v>
       </c>
       <c r="W44" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10213,7 +10207,7 @@
         <v>1519</v>
       </c>
       <c r="W45" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10275,7 +10269,7 @@
         <v>1519</v>
       </c>
       <c r="W46" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10337,7 +10331,7 @@
         <v>1527</v>
       </c>
       <c r="W47" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10399,7 +10393,7 @@
         <v>1528</v>
       </c>
       <c r="W48" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10461,7 +10455,7 @@
         <v>1529</v>
       </c>
       <c r="W49" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10523,7 +10517,7 @@
         <v>1530</v>
       </c>
       <c r="W50" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10585,7 +10579,7 @@
         <v>1531</v>
       </c>
       <c r="W51" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10647,7 +10641,7 @@
         <v>1520</v>
       </c>
       <c r="W52" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10709,7 +10703,7 @@
         <v>1514</v>
       </c>
       <c r="W53" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10771,7 +10765,7 @@
         <v>1514</v>
       </c>
       <c r="W54" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10833,7 +10827,7 @@
         <v>1514</v>
       </c>
       <c r="W55" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10895,7 +10889,7 @@
         <v>1532</v>
       </c>
       <c r="W56" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -10957,7 +10951,7 @@
         <v>1533</v>
       </c>
       <c r="W57" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11019,16 +11013,16 @@
         <v>1534</v>
       </c>
       <c r="W58" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X58" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="Y58" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z58" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11090,7 +11084,7 @@
         <v>1535</v>
       </c>
       <c r="W59" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11152,7 +11146,7 @@
         <v>1536</v>
       </c>
       <c r="W60" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11214,7 +11208,7 @@
         <v>1514</v>
       </c>
       <c r="W61" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11276,7 +11270,7 @@
         <v>1537</v>
       </c>
       <c r="W62" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11335,7 +11329,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11394,7 +11388,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11453,7 +11447,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11512,7 +11506,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11571,7 +11565,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11630,7 +11624,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11692,7 +11686,7 @@
         <v>1538</v>
       </c>
       <c r="W69" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11754,7 +11748,7 @@
         <v>1536</v>
       </c>
       <c r="W70" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11816,7 +11810,7 @@
         <v>1521</v>
       </c>
       <c r="W71" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11878,7 +11872,7 @@
         <v>1539</v>
       </c>
       <c r="W72" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -11940,7 +11934,7 @@
         <v>1540</v>
       </c>
       <c r="W73" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12002,16 +11996,16 @@
         <v>1541</v>
       </c>
       <c r="W74" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X74" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="Y74" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z74" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12073,16 +12067,16 @@
         <v>1542</v>
       </c>
       <c r="W75" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X75" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="Y75" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z75" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12144,7 +12138,7 @@
         <v>1521</v>
       </c>
       <c r="W76" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12206,7 +12200,7 @@
         <v>1521</v>
       </c>
       <c r="W77" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12268,10 +12262,10 @@
         <v>1543</v>
       </c>
       <c r="W78" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="Z78" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12336,7 +12330,7 @@
         <v>1544</v>
       </c>
       <c r="W79" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12395,7 +12389,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12454,7 +12448,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12516,7 +12510,7 @@
         <v>1545</v>
       </c>
       <c r="W82" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12578,7 +12572,7 @@
         <v>1546</v>
       </c>
       <c r="W83" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12640,7 +12634,7 @@
         <v>1547</v>
       </c>
       <c r="W84" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12699,7 +12693,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12761,7 +12755,7 @@
         <v>1548</v>
       </c>
       <c r="W86" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12823,7 +12817,7 @@
         <v>1549</v>
       </c>
       <c r="W87" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12885,7 +12879,7 @@
         <v>1549</v>
       </c>
       <c r="W88" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -12947,7 +12941,7 @@
         <v>1514</v>
       </c>
       <c r="W89" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13009,16 +13003,16 @@
         <v>1550</v>
       </c>
       <c r="W90" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X90" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="Y90" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z90" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13080,16 +13074,16 @@
         <v>1551</v>
       </c>
       <c r="W91" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X91" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="Y91" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z91" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13151,7 +13145,7 @@
         <v>1552</v>
       </c>
       <c r="W92" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13213,7 +13207,7 @@
         <v>1553</v>
       </c>
       <c r="W93" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13275,7 +13269,7 @@
         <v>1553</v>
       </c>
       <c r="W94" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13337,7 +13331,7 @@
         <v>1554</v>
       </c>
       <c r="W95" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13399,16 +13393,16 @@
         <v>1555</v>
       </c>
       <c r="W96" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X96" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="Y96" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z96" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13470,7 +13464,7 @@
         <v>1556</v>
       </c>
       <c r="W97" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13532,7 +13526,7 @@
         <v>1557</v>
       </c>
       <c r="W98" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13594,7 +13588,7 @@
         <v>1558</v>
       </c>
       <c r="W99" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13656,7 +13650,7 @@
         <v>1559</v>
       </c>
       <c r="W100" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13718,16 +13712,16 @@
         <v>1560</v>
       </c>
       <c r="W101" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X101" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="Y101" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z101" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13789,7 +13783,7 @@
         <v>1561</v>
       </c>
       <c r="W102" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13851,7 +13845,7 @@
         <v>1561</v>
       </c>
       <c r="W103" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13913,7 +13907,7 @@
         <v>1562</v>
       </c>
       <c r="W104" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -13975,16 +13969,16 @@
         <v>1563</v>
       </c>
       <c r="W105" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X105" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="Y105" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z105" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14046,16 +14040,16 @@
         <v>1564</v>
       </c>
       <c r="W106" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X106" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="Y106" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z106" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14117,7 +14111,7 @@
         <v>1565</v>
       </c>
       <c r="W107" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14179,16 +14173,16 @@
         <v>1566</v>
       </c>
       <c r="W108" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X108" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="Y108" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z108" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14250,16 +14244,16 @@
         <v>1567</v>
       </c>
       <c r="W109" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X109" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="Y109" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z109" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14318,7 +14312,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14380,16 +14374,16 @@
         <v>1568</v>
       </c>
       <c r="W111" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X111" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="Y111" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z111" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14451,16 +14445,16 @@
         <v>1569</v>
       </c>
       <c r="W112" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X112" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="Y112" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z112" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14522,16 +14516,16 @@
         <v>1570</v>
       </c>
       <c r="W113" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X113" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="Y113" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z113" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14593,16 +14587,16 @@
         <v>1571</v>
       </c>
       <c r="W114" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X114" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="Y114" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z114" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14664,16 +14658,16 @@
         <v>1567</v>
       </c>
       <c r="W115" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X115" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="Y115" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z115" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14735,16 +14729,16 @@
         <v>1567</v>
       </c>
       <c r="W116" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X116" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="Y116" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z116" t="s">
-        <v>2155</v>
+        <v>2153</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14806,16 +14800,16 @@
         <v>1572</v>
       </c>
       <c r="W117" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X117" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="Y117" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z117" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14877,16 +14871,16 @@
         <v>1573</v>
       </c>
       <c r="W118" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X118" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="Y118" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z118" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -14948,7 +14942,7 @@
         <v>1574</v>
       </c>
       <c r="W119" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15010,16 +15004,16 @@
         <v>1575</v>
       </c>
       <c r="W120" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X120" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y120" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z120" t="s">
-        <v>2158</v>
+        <v>2156</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15081,16 +15075,16 @@
         <v>1575</v>
       </c>
       <c r="W121" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X121" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y121" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z121" t="s">
-        <v>2159</v>
+        <v>2157</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15152,16 +15146,16 @@
         <v>1575</v>
       </c>
       <c r="W122" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X122" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y122" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z122" t="s">
-        <v>2160</v>
+        <v>2158</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15223,16 +15217,16 @@
         <v>1575</v>
       </c>
       <c r="W123" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X123" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y123" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z123" t="s">
-        <v>2161</v>
+        <v>2159</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15294,16 +15288,16 @@
         <v>1575</v>
       </c>
       <c r="W124" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X124" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y124" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z124" t="s">
-        <v>2162</v>
+        <v>2160</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15365,16 +15359,16 @@
         <v>1575</v>
       </c>
       <c r="W125" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X125" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y125" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z125" t="s">
-        <v>2163</v>
+        <v>2161</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15436,16 +15430,16 @@
         <v>1575</v>
       </c>
       <c r="W126" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X126" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y126" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z126" t="s">
-        <v>2164</v>
+        <v>2162</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15507,16 +15501,16 @@
         <v>1576</v>
       </c>
       <c r="W127" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X127" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="Y127" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z127" t="s">
-        <v>2165</v>
+        <v>2163</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15578,16 +15572,16 @@
         <v>1577</v>
       </c>
       <c r="W128" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X128" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="Y128" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z128" t="s">
-        <v>2166</v>
+        <v>2164</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15649,16 +15643,16 @@
         <v>1575</v>
       </c>
       <c r="W129" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X129" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y129" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z129" t="s">
-        <v>2167</v>
+        <v>2165</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15720,16 +15714,16 @@
         <v>1575</v>
       </c>
       <c r="W130" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X130" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y130" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z130" t="s">
-        <v>2168</v>
+        <v>2166</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15791,7 +15785,7 @@
         <v>1578</v>
       </c>
       <c r="W131" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15850,7 +15844,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15909,7 +15903,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -15971,16 +15965,16 @@
         <v>1575</v>
       </c>
       <c r="W134" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X134" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y134" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z134" t="s">
-        <v>2169</v>
+        <v>2167</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16042,16 +16036,16 @@
         <v>1575</v>
       </c>
       <c r="W135" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X135" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y135" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z135" t="s">
-        <v>2170</v>
+        <v>2168</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16113,7 +16107,7 @@
         <v>1574</v>
       </c>
       <c r="W136" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16172,7 +16166,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16234,16 +16228,16 @@
         <v>1579</v>
       </c>
       <c r="W138" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X138" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="Y138" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z138" t="s">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16305,16 +16299,16 @@
         <v>1567</v>
       </c>
       <c r="W139" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X139" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="Y139" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z139" t="s">
-        <v>2172</v>
+        <v>2170</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16376,16 +16370,16 @@
         <v>1575</v>
       </c>
       <c r="W140" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X140" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y140" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z140" t="s">
-        <v>2173</v>
+        <v>2171</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16444,7 +16438,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16503,7 +16497,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16565,16 +16559,16 @@
         <v>1580</v>
       </c>
       <c r="W143" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X143" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="Y143" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z143" t="s">
-        <v>2174</v>
+        <v>2172</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16636,16 +16630,16 @@
         <v>1581</v>
       </c>
       <c r="W144" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X144" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="Y144" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z144" t="s">
-        <v>2175</v>
+        <v>2173</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16707,16 +16701,16 @@
         <v>1582</v>
       </c>
       <c r="W145" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X145" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="Y145" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z145" t="s">
-        <v>2176</v>
+        <v>2174</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16778,16 +16772,16 @@
         <v>1583</v>
       </c>
       <c r="W146" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X146" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="Y146" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z146" t="s">
-        <v>2177</v>
+        <v>2175</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16846,7 +16840,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16908,7 +16902,7 @@
         <v>1584</v>
       </c>
       <c r="W148" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -16970,16 +16964,16 @@
         <v>1585</v>
       </c>
       <c r="W149" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X149" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="Y149" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z149" t="s">
-        <v>2178</v>
+        <v>2176</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17041,7 +17035,7 @@
         <v>1586</v>
       </c>
       <c r="W150" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17103,16 +17097,16 @@
         <v>1587</v>
       </c>
       <c r="W151" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X151" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="Y151" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z151" t="s">
-        <v>2179</v>
+        <v>2177</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17174,7 +17168,7 @@
         <v>1586</v>
       </c>
       <c r="W152" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17236,7 +17230,7 @@
         <v>1584</v>
       </c>
       <c r="W153" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17298,7 +17292,7 @@
         <v>1586</v>
       </c>
       <c r="W154" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17360,7 +17354,7 @@
         <v>1586</v>
       </c>
       <c r="W155" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17422,16 +17416,16 @@
         <v>1588</v>
       </c>
       <c r="W156" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X156" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="Y156" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z156" t="s">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17493,7 +17487,7 @@
         <v>1584</v>
       </c>
       <c r="W157" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17555,16 +17549,16 @@
         <v>1589</v>
       </c>
       <c r="W158" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X158" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="Y158" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z158" t="s">
-        <v>2181</v>
+        <v>2179</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17626,16 +17620,16 @@
         <v>1590</v>
       </c>
       <c r="W159" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X159" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="Y159" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z159" t="s">
-        <v>2182</v>
+        <v>2180</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17697,16 +17691,16 @@
         <v>1589</v>
       </c>
       <c r="W160" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X160" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="Y160" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z160" t="s">
-        <v>2183</v>
+        <v>2181</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17768,16 +17762,16 @@
         <v>1589</v>
       </c>
       <c r="W161" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X161" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="Y161" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z161" t="s">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17839,16 +17833,16 @@
         <v>1589</v>
       </c>
       <c r="W162" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X162" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="Y162" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z162" t="s">
-        <v>2185</v>
+        <v>2183</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17910,16 +17904,16 @@
         <v>1591</v>
       </c>
       <c r="W163" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X163" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="Y163" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z163" t="s">
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -17981,16 +17975,16 @@
         <v>1592</v>
       </c>
       <c r="W164" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X164" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="Y164" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z164" t="s">
-        <v>2187</v>
+        <v>2185</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18052,16 +18046,16 @@
         <v>1593</v>
       </c>
       <c r="W165" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X165" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="Y165" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z165" t="s">
-        <v>2188</v>
+        <v>2186</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18123,16 +18117,16 @@
         <v>1594</v>
       </c>
       <c r="W166" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X166" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="Y166" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z166" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18194,16 +18188,16 @@
         <v>1572</v>
       </c>
       <c r="W167" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X167" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="Y167" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z167" t="s">
-        <v>2190</v>
+        <v>2188</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18265,16 +18259,16 @@
         <v>1575</v>
       </c>
       <c r="W168" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X168" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y168" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z168" t="s">
-        <v>2191</v>
+        <v>2189</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18336,7 +18330,7 @@
         <v>1595</v>
       </c>
       <c r="W169" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18398,16 +18392,16 @@
         <v>1575</v>
       </c>
       <c r="W170" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X170" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="Y170" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z170" t="s">
-        <v>2192</v>
+        <v>2190</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18469,16 +18463,16 @@
         <v>1596</v>
       </c>
       <c r="W171" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X171" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="Y171" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z171" t="s">
-        <v>2193</v>
+        <v>2191</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18540,16 +18534,16 @@
         <v>1597</v>
       </c>
       <c r="W172" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X172" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="Y172" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z172" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18611,16 +18605,16 @@
         <v>1598</v>
       </c>
       <c r="W173" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X173" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="Y173" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z173" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18682,16 +18676,16 @@
         <v>1599</v>
       </c>
       <c r="W174" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X174" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="Y174" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z174" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18753,16 +18747,16 @@
         <v>1600</v>
       </c>
       <c r="W175" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X175" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="Y175" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z175" t="s">
-        <v>2197</v>
+        <v>2195</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18824,16 +18818,16 @@
         <v>1601</v>
       </c>
       <c r="W176" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X176" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="Y176" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z176" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18895,7 +18889,7 @@
         <v>1595</v>
       </c>
       <c r="W177" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -18957,16 +18951,16 @@
         <v>1602</v>
       </c>
       <c r="W178" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X178" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="Y178" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z178" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19028,16 +19022,16 @@
         <v>1603</v>
       </c>
       <c r="W179" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X179" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="Y179" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z179" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19099,7 +19093,7 @@
         <v>1604</v>
       </c>
       <c r="W180" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19161,16 +19155,16 @@
         <v>1605</v>
       </c>
       <c r="W181" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X181" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="Y181" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z181" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19232,16 +19226,16 @@
         <v>1605</v>
       </c>
       <c r="W182" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X182" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="Y182" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z182" t="s">
-        <v>2202</v>
+        <v>2200</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19303,16 +19297,16 @@
         <v>1606</v>
       </c>
       <c r="W183" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X183" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="Y183" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z183" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19374,16 +19368,16 @@
         <v>1607</v>
       </c>
       <c r="W184" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X184" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="Y184" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z184" t="s">
-        <v>2204</v>
+        <v>2202</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19445,16 +19439,16 @@
         <v>1608</v>
       </c>
       <c r="W185" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X185" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="Y185" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z185" t="s">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19516,7 +19510,7 @@
         <v>1609</v>
       </c>
       <c r="W186" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19578,7 +19572,7 @@
         <v>1610</v>
       </c>
       <c r="W187" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19640,7 +19634,7 @@
         <v>1611</v>
       </c>
       <c r="W188" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19702,7 +19696,7 @@
         <v>1612</v>
       </c>
       <c r="W189" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19764,16 +19758,16 @@
         <v>1613</v>
       </c>
       <c r="W190" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X190" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="Y190" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z190" t="s">
-        <v>2206</v>
+        <v>2204</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19835,16 +19829,16 @@
         <v>1614</v>
       </c>
       <c r="W191" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X191" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="Y191" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z191" t="s">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19906,7 +19900,7 @@
         <v>1615</v>
       </c>
       <c r="W192" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -19968,7 +19962,7 @@
         <v>1615</v>
       </c>
       <c r="W193" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20030,16 +20024,16 @@
         <v>1616</v>
       </c>
       <c r="W194" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X194" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="Y194" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z194" t="s">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20101,16 +20095,16 @@
         <v>1617</v>
       </c>
       <c r="W195" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X195" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="Y195" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z195" t="s">
-        <v>2209</v>
+        <v>2207</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20172,16 +20166,16 @@
         <v>1618</v>
       </c>
       <c r="W196" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X196" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="Y196" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z196" t="s">
-        <v>2210</v>
+        <v>2208</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20243,16 +20237,16 @@
         <v>1614</v>
       </c>
       <c r="W197" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X197" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="Y197" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z197" t="s">
-        <v>2211</v>
+        <v>2209</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20314,7 +20308,7 @@
         <v>1619</v>
       </c>
       <c r="W198" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20376,7 +20370,7 @@
         <v>1620</v>
       </c>
       <c r="W199" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20438,16 +20432,16 @@
         <v>1621</v>
       </c>
       <c r="W200" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X200" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Y200" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z200" t="s">
-        <v>2212</v>
+        <v>2210</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20509,16 +20503,16 @@
         <v>1621</v>
       </c>
       <c r="W201" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X201" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="Y201" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z201" t="s">
-        <v>2213</v>
+        <v>2211</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20580,16 +20574,16 @@
         <v>1622</v>
       </c>
       <c r="W202" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X202" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="Y202" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z202" t="s">
-        <v>2214</v>
+        <v>2212</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20651,16 +20645,16 @@
         <v>1623</v>
       </c>
       <c r="W203" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X203" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="Y203" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z203" t="s">
-        <v>2215</v>
+        <v>2213</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20722,16 +20716,16 @@
         <v>1624</v>
       </c>
       <c r="W204" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X204" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="Y204" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z204" t="s">
-        <v>2216</v>
+        <v>2214</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20793,16 +20787,16 @@
         <v>1625</v>
       </c>
       <c r="W205" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X205" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="Y205" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z205" t="s">
-        <v>2217</v>
+        <v>2215</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20864,16 +20858,16 @@
         <v>1626</v>
       </c>
       <c r="W206" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X206" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="Y206" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z206" t="s">
-        <v>2218</v>
+        <v>2216</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -20935,16 +20929,16 @@
         <v>1627</v>
       </c>
       <c r="W207" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X207" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="Y207" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z207" t="s">
-        <v>2219</v>
+        <v>2217</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21006,16 +21000,16 @@
         <v>1628</v>
       </c>
       <c r="W208" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X208" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="Y208" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z208" t="s">
-        <v>2220</v>
+        <v>2218</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21077,7 +21071,7 @@
         <v>1629</v>
       </c>
       <c r="W209" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21139,16 +21133,16 @@
         <v>1630</v>
       </c>
       <c r="W210" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X210" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="Y210" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z210" t="s">
-        <v>2221</v>
+        <v>2219</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21210,16 +21204,16 @@
         <v>1631</v>
       </c>
       <c r="W211" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X211" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="Y211" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z211" t="s">
-        <v>2222</v>
+        <v>2220</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21281,16 +21275,16 @@
         <v>1632</v>
       </c>
       <c r="W212" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X212" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="Y212" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z212" t="s">
-        <v>2223</v>
+        <v>2221</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21352,16 +21346,16 @@
         <v>1633</v>
       </c>
       <c r="W213" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X213" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="Y213" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z213" t="s">
-        <v>2224</v>
+        <v>2222</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21423,7 +21417,7 @@
         <v>1634</v>
       </c>
       <c r="W214" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21485,16 +21479,16 @@
         <v>1599</v>
       </c>
       <c r="W215" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X215" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="Y215" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z215" t="s">
-        <v>2225</v>
+        <v>2223</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21556,16 +21550,16 @@
         <v>1635</v>
       </c>
       <c r="W216" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X216" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="Y216" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z216" t="s">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21627,7 +21621,7 @@
         <v>1636</v>
       </c>
       <c r="W217" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21689,16 +21683,16 @@
         <v>1637</v>
       </c>
       <c r="W218" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X218" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="Y218" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z218" t="s">
-        <v>2227</v>
+        <v>2225</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21760,16 +21754,16 @@
         <v>1638</v>
       </c>
       <c r="W219" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X219" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="Y219" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z219" t="s">
-        <v>2228</v>
+        <v>2226</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21831,7 +21825,7 @@
         <v>1639</v>
       </c>
       <c r="W220" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21893,7 +21887,7 @@
         <v>1640</v>
       </c>
       <c r="W221" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -21955,7 +21949,7 @@
         <v>1639</v>
       </c>
       <c r="W222" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22017,7 +22011,7 @@
         <v>1640</v>
       </c>
       <c r="W223" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22079,16 +22073,16 @@
         <v>1641</v>
       </c>
       <c r="W224" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X224" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="Y224" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z224" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22150,16 +22144,16 @@
         <v>1642</v>
       </c>
       <c r="W225" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X225" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="Y225" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z225" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22221,7 +22215,7 @@
         <v>1643</v>
       </c>
       <c r="W226" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22283,7 +22277,7 @@
         <v>1644</v>
       </c>
       <c r="W227" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22345,7 +22339,7 @@
         <v>1645</v>
       </c>
       <c r="W228" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22407,16 +22401,16 @@
         <v>1646</v>
       </c>
       <c r="W229" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X229" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="Y229" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z229" t="s">
-        <v>2231</v>
+        <v>2229</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22478,16 +22472,16 @@
         <v>1647</v>
       </c>
       <c r="W230" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X230" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="Y230" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z230" t="s">
-        <v>2232</v>
+        <v>2230</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22549,16 +22543,16 @@
         <v>1648</v>
       </c>
       <c r="W231" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X231" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="Y231" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z231" t="s">
-        <v>2233</v>
+        <v>2231</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22623,16 +22617,16 @@
         <v>1649</v>
       </c>
       <c r="W232" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X232" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="Y232" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z232" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22694,16 +22688,16 @@
         <v>1650</v>
       </c>
       <c r="W233" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X233" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="Y233" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z233" t="s">
-        <v>2234</v>
+        <v>2232</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22765,16 +22759,16 @@
         <v>1651</v>
       </c>
       <c r="W234" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X234" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="Y234" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z234" t="s">
-        <v>2235</v>
+        <v>2233</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22836,16 +22830,16 @@
         <v>1651</v>
       </c>
       <c r="W235" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X235" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="Y235" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z235" t="s">
-        <v>2236</v>
+        <v>2234</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22907,16 +22901,16 @@
         <v>1652</v>
       </c>
       <c r="W236" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X236" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="Y236" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z236" t="s">
-        <v>2237</v>
+        <v>2235</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -22978,7 +22972,7 @@
         <v>1653</v>
       </c>
       <c r="W237" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23040,7 +23034,7 @@
         <v>1654</v>
       </c>
       <c r="W238" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23102,16 +23096,16 @@
         <v>1655</v>
       </c>
       <c r="W239" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X239" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Y239" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z239" t="s">
-        <v>2238</v>
+        <v>2236</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23173,16 +23167,16 @@
         <v>1656</v>
       </c>
       <c r="W240" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X240" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="Y240" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z240" t="s">
-        <v>2239</v>
+        <v>2237</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23244,7 +23238,7 @@
         <v>1657</v>
       </c>
       <c r="W241" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23306,16 +23300,16 @@
         <v>1658</v>
       </c>
       <c r="W242" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X242" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="Y242" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z242" t="s">
-        <v>2240</v>
+        <v>2238</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23377,16 +23371,16 @@
         <v>1659</v>
       </c>
       <c r="W243" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X243" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="Y243" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z243" t="s">
-        <v>2241</v>
+        <v>2239</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23448,16 +23442,16 @@
         <v>1658</v>
       </c>
       <c r="W244" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X244" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="Y244" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z244" t="s">
-        <v>2242</v>
+        <v>2240</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23519,16 +23513,16 @@
         <v>1660</v>
       </c>
       <c r="W245" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X245" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="Y245" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z245" t="s">
-        <v>2243</v>
+        <v>2241</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23590,16 +23584,16 @@
         <v>1659</v>
       </c>
       <c r="W246" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X246" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="Y246" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z246" t="s">
-        <v>2244</v>
+        <v>2242</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23661,16 +23655,16 @@
         <v>1660</v>
       </c>
       <c r="W247" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X247" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="Y247" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z247" t="s">
-        <v>2245</v>
+        <v>2243</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23732,16 +23726,16 @@
         <v>1661</v>
       </c>
       <c r="W248" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X248" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="Y248" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z248" t="s">
-        <v>2246</v>
+        <v>2244</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23803,16 +23797,16 @@
         <v>1651</v>
       </c>
       <c r="W249" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X249" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="Y249" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z249" t="s">
-        <v>2247</v>
+        <v>2245</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23874,7 +23868,7 @@
         <v>1662</v>
       </c>
       <c r="W250" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -23936,7 +23930,7 @@
         <v>1663</v>
       </c>
       <c r="W251" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -23998,16 +23992,16 @@
         <v>1664</v>
       </c>
       <c r="W252" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X252" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="Y252" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z252" t="s">
-        <v>2248</v>
+        <v>2246</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24069,16 +24063,16 @@
         <v>1665</v>
       </c>
       <c r="W253" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X253" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="Y253" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z253" t="s">
-        <v>2249</v>
+        <v>2247</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24140,7 +24134,7 @@
         <v>1666</v>
       </c>
       <c r="W254" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24202,16 +24196,16 @@
         <v>1667</v>
       </c>
       <c r="W255" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X255" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="Y255" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z255" t="s">
-        <v>2250</v>
+        <v>2248</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24273,7 +24267,7 @@
         <v>1668</v>
       </c>
       <c r="W256" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24338,7 +24332,7 @@
         <v>1669</v>
       </c>
       <c r="W257" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24400,7 +24394,7 @@
         <v>1670</v>
       </c>
       <c r="W258" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24462,7 +24456,7 @@
         <v>1670</v>
       </c>
       <c r="W259" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24524,7 +24518,7 @@
         <v>1671</v>
       </c>
       <c r="W260" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24586,16 +24580,16 @@
         <v>1672</v>
       </c>
       <c r="W261" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X261" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="Y261" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z261" t="s">
-        <v>2251</v>
+        <v>2249</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24657,13 +24651,13 @@
         <v>1673</v>
       </c>
       <c r="W262" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X262" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="Y262" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24725,16 +24719,16 @@
         <v>1674</v>
       </c>
       <c r="W263" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X263" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="Y263" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z263" t="s">
-        <v>2252</v>
+        <v>2250</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24796,7 +24790,7 @@
         <v>1675</v>
       </c>
       <c r="W264" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24858,7 +24852,7 @@
         <v>1675</v>
       </c>
       <c r="W265" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24920,7 +24914,7 @@
         <v>1676</v>
       </c>
       <c r="W266" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -24982,16 +24976,16 @@
         <v>1677</v>
       </c>
       <c r="W267" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X267" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="Y267" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z267" t="s">
-        <v>2253</v>
+        <v>2251</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25053,16 +25047,16 @@
         <v>1678</v>
       </c>
       <c r="W268" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X268" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="Y268" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z268" t="s">
-        <v>2254</v>
+        <v>2252</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25124,7 +25118,7 @@
         <v>1519</v>
       </c>
       <c r="W269" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25186,7 +25180,7 @@
         <v>1679</v>
       </c>
       <c r="W270" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25248,7 +25242,7 @@
         <v>1680</v>
       </c>
       <c r="W271" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25310,16 +25304,16 @@
         <v>1681</v>
       </c>
       <c r="W272" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X272" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="Y272" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z272" t="s">
-        <v>2255</v>
+        <v>2253</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25378,7 +25372,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25440,7 +25434,7 @@
         <v>1682</v>
       </c>
       <c r="W274" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25499,7 +25493,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25561,7 +25555,7 @@
         <v>1683</v>
       </c>
       <c r="W276" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25623,7 +25617,7 @@
         <v>1684</v>
       </c>
       <c r="W277" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25685,16 +25679,16 @@
         <v>1685</v>
       </c>
       <c r="W278" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X278" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="Y278" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z278" t="s">
-        <v>2256</v>
+        <v>2254</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25756,16 +25750,16 @@
         <v>1686</v>
       </c>
       <c r="W279" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X279" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="Y279" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z279" t="s">
-        <v>2257</v>
+        <v>2255</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25827,16 +25821,16 @@
         <v>1686</v>
       </c>
       <c r="W280" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X280" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="Y280" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z280" t="s">
-        <v>2258</v>
+        <v>2256</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25898,16 +25892,16 @@
         <v>1687</v>
       </c>
       <c r="W281" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X281" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="Y281" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z281" t="s">
-        <v>2259</v>
+        <v>2257</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -25969,7 +25963,7 @@
         <v>1688</v>
       </c>
       <c r="W282" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26031,7 +26025,7 @@
         <v>1689</v>
       </c>
       <c r="W283" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26093,7 +26087,7 @@
         <v>1690</v>
       </c>
       <c r="W284" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26155,16 +26149,16 @@
         <v>1691</v>
       </c>
       <c r="W285" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X285" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="Y285" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z285" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26226,7 +26220,7 @@
         <v>1692</v>
       </c>
       <c r="W286" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26288,16 +26282,16 @@
         <v>1686</v>
       </c>
       <c r="W287" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X287" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="Y287" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z287" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26359,16 +26353,16 @@
         <v>1693</v>
       </c>
       <c r="W288" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X288" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="Y288" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z288" t="s">
-        <v>2262</v>
+        <v>2260</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26430,7 +26424,7 @@
         <v>1694</v>
       </c>
       <c r="W289" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26492,16 +26486,16 @@
         <v>1695</v>
       </c>
       <c r="W290" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X290" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="Y290" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z290" t="s">
-        <v>2263</v>
+        <v>2261</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26563,16 +26557,16 @@
         <v>1696</v>
       </c>
       <c r="W291" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X291" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="Y291" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z291" t="s">
-        <v>2264</v>
+        <v>2262</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26634,7 +26628,7 @@
         <v>1697</v>
       </c>
       <c r="W292" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26693,7 +26687,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26755,7 +26749,7 @@
         <v>1698</v>
       </c>
       <c r="W294" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26817,7 +26811,7 @@
         <v>1699</v>
       </c>
       <c r="W295" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26879,7 +26873,7 @@
         <v>1700</v>
       </c>
       <c r="W296" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -26941,13 +26935,13 @@
         <v>1701</v>
       </c>
       <c r="W297" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X297" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="Z297" t="s">
-        <v>2265</v>
+        <v>2263</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27009,7 +27003,7 @@
         <v>1702</v>
       </c>
       <c r="W298" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27071,7 +27065,7 @@
         <v>1703</v>
       </c>
       <c r="W299" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27133,7 +27127,7 @@
         <v>1704</v>
       </c>
       <c r="W300" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27195,7 +27189,7 @@
         <v>1705</v>
       </c>
       <c r="W301" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27257,7 +27251,7 @@
         <v>1706</v>
       </c>
       <c r="W302" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27319,16 +27313,16 @@
         <v>1707</v>
       </c>
       <c r="W303" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X303" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="Y303" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z303" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27390,7 +27384,7 @@
         <v>1708</v>
       </c>
       <c r="W304" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27452,7 +27446,7 @@
         <v>1709</v>
       </c>
       <c r="W305" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27514,7 +27508,7 @@
         <v>1710</v>
       </c>
       <c r="W306" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27576,7 +27570,7 @@
         <v>1711</v>
       </c>
       <c r="W307" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27638,7 +27632,7 @@
         <v>1704</v>
       </c>
       <c r="W308" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27700,7 +27694,7 @@
         <v>1712</v>
       </c>
       <c r="W309" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27762,7 +27756,7 @@
         <v>1713</v>
       </c>
       <c r="W310" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27824,7 +27818,7 @@
         <v>1714</v>
       </c>
       <c r="W311" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27886,7 +27880,7 @@
         <v>1715</v>
       </c>
       <c r="W312" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -27948,7 +27942,7 @@
         <v>1716</v>
       </c>
       <c r="W313" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28010,7 +28004,7 @@
         <v>1717</v>
       </c>
       <c r="W314" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28072,7 +28066,7 @@
         <v>1718</v>
       </c>
       <c r="W315" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28134,7 +28128,7 @@
         <v>1719</v>
       </c>
       <c r="W316" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28196,7 +28190,7 @@
         <v>1720</v>
       </c>
       <c r="W317" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28258,7 +28252,7 @@
         <v>1721</v>
       </c>
       <c r="W318" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28320,7 +28314,7 @@
         <v>1722</v>
       </c>
       <c r="W319" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28379,13 +28373,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X320" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="Z320" t="s">
-        <v>2267</v>
+        <v>2265</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28444,7 +28438,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28503,7 +28497,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28562,7 +28556,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28624,7 +28618,7 @@
         <v>1723</v>
       </c>
       <c r="W324" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28686,7 +28680,7 @@
         <v>1724</v>
       </c>
       <c r="W325" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28748,7 +28742,7 @@
         <v>1725</v>
       </c>
       <c r="W326" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28810,7 +28804,7 @@
         <v>1726</v>
       </c>
       <c r="W327" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28869,7 +28863,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -28931,7 +28925,7 @@
         <v>1726</v>
       </c>
       <c r="W329" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -28993,7 +28987,7 @@
         <v>1727</v>
       </c>
       <c r="W330" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29055,7 +29049,7 @@
         <v>1728</v>
       </c>
       <c r="W331" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29117,7 +29111,7 @@
         <v>1728</v>
       </c>
       <c r="W332" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29179,7 +29173,7 @@
         <v>1729</v>
       </c>
       <c r="W333" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29241,7 +29235,7 @@
         <v>1730</v>
       </c>
       <c r="W334" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29303,7 +29297,7 @@
         <v>1731</v>
       </c>
       <c r="W335" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29362,13 +29356,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X336" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="Z336" t="s">
-        <v>2268</v>
+        <v>2266</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29430,7 +29424,7 @@
         <v>1732</v>
       </c>
       <c r="W337" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29492,13 +29486,13 @@
         <v>1733</v>
       </c>
       <c r="W338" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X338" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="Z338" t="s">
-        <v>2269</v>
+        <v>2267</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29560,13 +29554,13 @@
         <v>1734</v>
       </c>
       <c r="W339" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X339" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="Z339" t="s">
-        <v>2270</v>
+        <v>2268</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29628,7 +29622,7 @@
         <v>1735</v>
       </c>
       <c r="W340" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29690,7 +29684,7 @@
         <v>1736</v>
       </c>
       <c r="W341" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29752,10 +29746,10 @@
         <v>1737</v>
       </c>
       <c r="W342" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X342" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29817,7 +29811,7 @@
         <v>1738</v>
       </c>
       <c r="W343" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29879,7 +29873,7 @@
         <v>1739</v>
       </c>
       <c r="W344" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -29941,13 +29935,13 @@
         <v>1740</v>
       </c>
       <c r="W345" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X345" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="Z345" t="s">
-        <v>2271</v>
+        <v>2269</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30009,7 +30003,7 @@
         <v>1704</v>
       </c>
       <c r="W346" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30071,7 +30065,7 @@
         <v>1741</v>
       </c>
       <c r="W347" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30133,16 +30127,16 @@
         <v>1742</v>
       </c>
       <c r="W348" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X348" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="Y348" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z348" t="s">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30207,13 +30201,13 @@
         <v>1743</v>
       </c>
       <c r="W349" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X349" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="Z349" t="s">
-        <v>2273</v>
+        <v>2271</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30275,7 +30269,7 @@
         <v>1744</v>
       </c>
       <c r="W350" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30337,16 +30331,16 @@
         <v>1745</v>
       </c>
       <c r="W351" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X351" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="Y351" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z351" t="s">
-        <v>2274</v>
+        <v>2272</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30408,13 +30402,13 @@
         <v>1746</v>
       </c>
       <c r="W352" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X352" t="s">
         <v>1746</v>
       </c>
       <c r="Z352" t="s">
-        <v>2275</v>
+        <v>2273</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30476,16 +30470,16 @@
         <v>1747</v>
       </c>
       <c r="W353" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X353" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="Y353" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z353" t="s">
-        <v>2276</v>
+        <v>2274</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30547,7 +30541,7 @@
         <v>1748</v>
       </c>
       <c r="W354" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30609,7 +30603,7 @@
         <v>1749</v>
       </c>
       <c r="W355" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30668,7 +30662,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30727,7 +30721,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30786,7 +30780,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30848,7 +30842,7 @@
         <v>1750</v>
       </c>
       <c r="W359" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30913,7 +30907,7 @@
         <v>1751</v>
       </c>
       <c r="W360" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -30978,7 +30972,7 @@
         <v>1752</v>
       </c>
       <c r="W361" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31040,16 +31034,16 @@
         <v>1753</v>
       </c>
       <c r="W362" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X362" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="Y362" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z362" t="s">
-        <v>2277</v>
+        <v>2275</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31111,16 +31105,16 @@
         <v>1754</v>
       </c>
       <c r="W363" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X363" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="Y363" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z363" t="s">
-        <v>2278</v>
+        <v>2276</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31182,7 +31176,7 @@
         <v>1755</v>
       </c>
       <c r="W364" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31244,7 +31238,7 @@
         <v>1756</v>
       </c>
       <c r="W365" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31309,7 +31303,7 @@
         <v>1757</v>
       </c>
       <c r="W366" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31371,7 +31365,7 @@
         <v>1758</v>
       </c>
       <c r="W367" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31433,7 +31427,7 @@
         <v>1759</v>
       </c>
       <c r="W368" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31498,13 +31492,13 @@
         <v>1760</v>
       </c>
       <c r="W369" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X369" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="Z369" t="s">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31566,7 +31560,7 @@
         <v>1761</v>
       </c>
       <c r="W370" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31628,16 +31622,16 @@
         <v>1762</v>
       </c>
       <c r="W371" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X371" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="Y371" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z371" t="s">
-        <v>2280</v>
+        <v>2278</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31702,7 +31696,7 @@
         <v>1763</v>
       </c>
       <c r="W372" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31767,16 +31761,16 @@
         <v>1764</v>
       </c>
       <c r="W373" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X373" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="Y373" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z373" t="s">
-        <v>2281</v>
+        <v>2279</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31838,7 +31832,7 @@
         <v>1765</v>
       </c>
       <c r="W374" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31903,7 +31897,7 @@
         <v>1766</v>
       </c>
       <c r="W375" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -31968,7 +31962,7 @@
         <v>1767</v>
       </c>
       <c r="W376" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32033,7 +32027,7 @@
         <v>1767</v>
       </c>
       <c r="W377" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32098,13 +32092,13 @@
         <v>1768</v>
       </c>
       <c r="W378" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X378" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="Z378" t="s">
-        <v>2282</v>
+        <v>2280</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32166,16 +32160,16 @@
         <v>1769</v>
       </c>
       <c r="W379" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X379" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="Y379" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z379" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32240,7 +32234,7 @@
         <v>1770</v>
       </c>
       <c r="W380" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32302,7 +32296,7 @@
         <v>1771</v>
       </c>
       <c r="W381" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32367,7 +32361,7 @@
         <v>1772</v>
       </c>
       <c r="W382" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32429,7 +32423,7 @@
         <v>1773</v>
       </c>
       <c r="W383" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32494,7 +32488,7 @@
         <v>1772</v>
       </c>
       <c r="W384" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32556,16 +32550,16 @@
         <v>1774</v>
       </c>
       <c r="W385" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X385" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="Y385" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z385" t="s">
-        <v>2283</v>
+        <v>2281</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32633,7 +32627,7 @@
         <v>1775</v>
       </c>
       <c r="W386" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32695,7 +32689,7 @@
         <v>1776</v>
       </c>
       <c r="W387" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32757,7 +32751,7 @@
         <v>1777</v>
       </c>
       <c r="W388" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32819,16 +32813,16 @@
         <v>1778</v>
       </c>
       <c r="W389" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X389" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="Y389" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z389" t="s">
-        <v>2284</v>
+        <v>2282</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32893,16 +32887,16 @@
         <v>1779</v>
       </c>
       <c r="W390" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X390" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="Y390" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z390" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -32967,7 +32961,7 @@
         <v>1780</v>
       </c>
       <c r="W391" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33029,7 +33023,7 @@
         <v>1781</v>
       </c>
       <c r="W392" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33091,16 +33085,16 @@
         <v>1782</v>
       </c>
       <c r="W393" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X393" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="Y393" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z393" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33162,7 +33156,7 @@
         <v>1783</v>
       </c>
       <c r="W394" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33227,16 +33221,16 @@
         <v>1784</v>
       </c>
       <c r="W395" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X395" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="Y395" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z395" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33301,13 +33295,13 @@
         <v>1785</v>
       </c>
       <c r="W396" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X396" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="Y396" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33369,7 +33363,7 @@
         <v>1786</v>
       </c>
       <c r="W397" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33431,7 +33425,7 @@
         <v>1787</v>
       </c>
       <c r="W398" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33496,7 +33490,7 @@
         <v>1788</v>
       </c>
       <c r="W399" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33561,16 +33555,16 @@
         <v>1789</v>
       </c>
       <c r="W400" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X400" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="Y400" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z400" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33635,7 +33629,7 @@
         <v>1790</v>
       </c>
       <c r="W401" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33700,7 +33694,7 @@
         <v>1791</v>
       </c>
       <c r="W402" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33765,16 +33759,16 @@
         <v>1792</v>
       </c>
       <c r="W403" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X403" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="Y403" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z403" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33839,7 +33833,7 @@
         <v>1793</v>
       </c>
       <c r="W404" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33904,7 +33898,7 @@
         <v>1794</v>
       </c>
       <c r="W405" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -33953,9 +33947,6 @@
       <c r="N406" s="1">
         <v>46111</v>
       </c>
-      <c r="O406" s="1">
-        <v>46248</v>
-      </c>
       <c r="Q406">
         <v>-46111</v>
       </c>
@@ -33971,11 +33962,8 @@
       <c r="U406" t="s">
         <v>1795</v>
       </c>
-      <c r="V406" t="s">
-        <v>1961</v>
-      </c>
       <c r="W406" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34037,16 +34025,16 @@
         <v>1796</v>
       </c>
       <c r="W407" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X407" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="Y407" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z407" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34111,13 +34099,13 @@
         <v>1797</v>
       </c>
       <c r="W408" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X408" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="Z408" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34182,7 +34170,7 @@
         <v>1798</v>
       </c>
       <c r="W409" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34247,7 +34235,7 @@
         <v>1799</v>
       </c>
       <c r="W410" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34312,7 +34300,7 @@
         <v>1800</v>
       </c>
       <c r="W411" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34377,7 +34365,7 @@
         <v>1801</v>
       </c>
       <c r="W412" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34442,7 +34430,7 @@
         <v>1802</v>
       </c>
       <c r="W413" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34507,7 +34495,7 @@
         <v>1802</v>
       </c>
       <c r="W414" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34572,7 +34560,7 @@
         <v>1803</v>
       </c>
       <c r="W415" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34637,7 +34625,7 @@
         <v>1804</v>
       </c>
       <c r="W416" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34702,7 +34690,7 @@
         <v>1802</v>
       </c>
       <c r="W417" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34767,7 +34755,7 @@
         <v>1805</v>
       </c>
       <c r="W418" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34832,7 +34820,7 @@
         <v>1806</v>
       </c>
       <c r="W419" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34897,16 +34885,16 @@
         <v>1807</v>
       </c>
       <c r="W420" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X420" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="Y420" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z420" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -34971,7 +34959,7 @@
         <v>1808</v>
       </c>
       <c r="W421" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35036,7 +35024,7 @@
         <v>1809</v>
       </c>
       <c r="W422" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35101,7 +35089,7 @@
         <v>1810</v>
       </c>
       <c r="W423" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35166,16 +35154,16 @@
         <v>1811</v>
       </c>
       <c r="W424" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X424" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="Y424" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z424" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35240,7 +35228,7 @@
         <v>1810</v>
       </c>
       <c r="W425" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35305,7 +35293,7 @@
         <v>1812</v>
       </c>
       <c r="W426" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35370,7 +35358,7 @@
         <v>1813</v>
       </c>
       <c r="W427" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35435,13 +35423,13 @@
         <v>1814</v>
       </c>
       <c r="W428" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X428" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="Y428" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35506,16 +35494,16 @@
         <v>1815</v>
       </c>
       <c r="W429" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X429" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="Y429" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z429" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35580,7 +35568,7 @@
         <v>1816</v>
       </c>
       <c r="W430" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35645,16 +35633,16 @@
         <v>1817</v>
       </c>
       <c r="W431" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X431" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="Y431" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z431" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35719,7 +35707,7 @@
         <v>1818</v>
       </c>
       <c r="W432" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35784,7 +35772,7 @@
         <v>1819</v>
       </c>
       <c r="W433" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35849,7 +35837,7 @@
         <v>1820</v>
       </c>
       <c r="W434" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35914,7 +35902,7 @@
         <v>1821</v>
       </c>
       <c r="W435" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -35979,7 +35967,7 @@
         <v>1822</v>
       </c>
       <c r="W436" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36044,7 +36032,7 @@
         <v>1823</v>
       </c>
       <c r="W437" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36109,7 +36097,7 @@
         <v>1824</v>
       </c>
       <c r="W438" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36174,7 +36162,7 @@
         <v>1825</v>
       </c>
       <c r="W439" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36239,16 +36227,16 @@
         <v>1826</v>
       </c>
       <c r="W440" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X440" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="Y440" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z440" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36313,16 +36301,16 @@
         <v>1827</v>
       </c>
       <c r="W441" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X441" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="Y441" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z441" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36387,16 +36375,16 @@
         <v>1828</v>
       </c>
       <c r="W442" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X442" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="Y442" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z442" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36461,7 +36449,7 @@
         <v>1829</v>
       </c>
       <c r="W443" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36526,7 +36514,7 @@
         <v>1830</v>
       </c>
       <c r="W444" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36591,16 +36579,16 @@
         <v>1827</v>
       </c>
       <c r="W445" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X445" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="Y445" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z445" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36665,16 +36653,16 @@
         <v>1827</v>
       </c>
       <c r="W446" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X446" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="Y446" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z446" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36739,16 +36727,16 @@
         <v>1831</v>
       </c>
       <c r="W447" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X447" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="Y447" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z447" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36813,16 +36801,16 @@
         <v>1827</v>
       </c>
       <c r="W448" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X448" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="Y448" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z448" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36887,16 +36875,16 @@
         <v>1827</v>
       </c>
       <c r="W449" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X449" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="Y449" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z449" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -36961,16 +36949,16 @@
         <v>1832</v>
       </c>
       <c r="W450" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X450" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="Y450" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z450" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37035,16 +37023,16 @@
         <v>1833</v>
       </c>
       <c r="W451" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X451" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="Y451" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z451" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37109,7 +37097,7 @@
         <v>1834</v>
       </c>
       <c r="W452" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37174,16 +37162,16 @@
         <v>1835</v>
       </c>
       <c r="W453" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X453" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="Y453" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z453" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37248,16 +37236,16 @@
         <v>1836</v>
       </c>
       <c r="W454" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X454" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="Y454" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z454" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37322,16 +37310,16 @@
         <v>1837</v>
       </c>
       <c r="W455" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X455" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="Y455" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z455" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37396,16 +37384,16 @@
         <v>1838</v>
       </c>
       <c r="W456" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X456" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="Y456" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z456" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37470,7 +37458,7 @@
         <v>1839</v>
       </c>
       <c r="W457" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37535,7 +37523,7 @@
         <v>1839</v>
       </c>
       <c r="W458" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37600,16 +37588,16 @@
         <v>1837</v>
       </c>
       <c r="W459" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X459" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="Y459" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z459" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37674,16 +37662,16 @@
         <v>1840</v>
       </c>
       <c r="W460" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X460" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="Y460" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z460" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37748,16 +37736,16 @@
         <v>1841</v>
       </c>
       <c r="W461" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X461" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="Y461" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z461" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37822,7 +37810,7 @@
         <v>1842</v>
       </c>
       <c r="W462" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37887,16 +37875,16 @@
         <v>1843</v>
       </c>
       <c r="W463" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X463" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="Y463" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z463" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -37961,16 +37949,16 @@
         <v>1844</v>
       </c>
       <c r="W464" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X464" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="Y464" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z464" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38035,16 +38023,16 @@
         <v>1845</v>
       </c>
       <c r="W465" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X465" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="Y465" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z465" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38109,7 +38097,7 @@
         <v>1846</v>
       </c>
       <c r="W466" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38174,16 +38162,16 @@
         <v>1847</v>
       </c>
       <c r="W467" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X467" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="Y467" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z467" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38248,16 +38236,16 @@
         <v>1848</v>
       </c>
       <c r="W468" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X468" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="Y468" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z468" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38322,16 +38310,16 @@
         <v>1849</v>
       </c>
       <c r="W469" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X469" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="Y469" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z469" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38396,16 +38384,16 @@
         <v>1850</v>
       </c>
       <c r="W470" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X470" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="Y470" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z470" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38470,7 +38458,7 @@
         <v>1851</v>
       </c>
       <c r="W471" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38535,16 +38523,16 @@
         <v>1852</v>
       </c>
       <c r="W472" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X472" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="Y472" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z472" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38609,16 +38597,16 @@
         <v>1852</v>
       </c>
       <c r="W473" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X473" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="Y473" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z473" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38683,7 +38671,7 @@
         <v>1853</v>
       </c>
       <c r="W474" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38748,16 +38736,16 @@
         <v>1854</v>
       </c>
       <c r="W475" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X475" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="Y475" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z475" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38822,16 +38810,16 @@
         <v>1855</v>
       </c>
       <c r="W476" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X476" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="Y476" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z476" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38896,7 +38884,7 @@
         <v>1856</v>
       </c>
       <c r="W477" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -38961,7 +38949,7 @@
         <v>1857</v>
       </c>
       <c r="W478" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39026,16 +39014,16 @@
         <v>1858</v>
       </c>
       <c r="W479" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X479" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
       <c r="Y479" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z479" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39100,16 +39088,16 @@
         <v>1859</v>
       </c>
       <c r="W480" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X480" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="Y480" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z480" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39174,16 +39162,16 @@
         <v>1860</v>
       </c>
       <c r="W481" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X481" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
       <c r="Y481" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z481" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39248,7 +39236,7 @@
         <v>1861</v>
       </c>
       <c r="W482" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39313,7 +39301,7 @@
         <v>1862</v>
       </c>
       <c r="W483" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39381,13 +39369,13 @@
         <v>1863</v>
       </c>
       <c r="W484" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39452,7 +39440,7 @@
         <v>1864</v>
       </c>
       <c r="W485" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39520,13 +39508,13 @@
         <v>1865</v>
       </c>
       <c r="W486" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39591,7 +39579,7 @@
         <v>1866</v>
       </c>
       <c r="W487" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39656,16 +39644,16 @@
         <v>1867</v>
       </c>
       <c r="W488" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X488" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="Y488" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z488" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39730,7 +39718,7 @@
         <v>1868</v>
       </c>
       <c r="W489" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39798,13 +39786,13 @@
         <v>1869</v>
       </c>
       <c r="W490" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39869,16 +39857,16 @@
         <v>1870</v>
       </c>
       <c r="W491" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X491" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
       <c r="Y491" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z491" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -39943,16 +39931,16 @@
         <v>1871</v>
       </c>
       <c r="W492" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X492" t="s">
-        <v>2119</v>
+        <v>2117</v>
       </c>
       <c r="Y492" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z492" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40017,16 +40005,16 @@
         <v>1872</v>
       </c>
       <c r="W493" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X493" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="Y493" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z493" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40091,13 +40079,13 @@
         <v>1873</v>
       </c>
       <c r="W494" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X494" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
       <c r="Y494" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40162,16 +40150,16 @@
         <v>1874</v>
       </c>
       <c r="W495" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X495" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
       <c r="Y495" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z495" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40236,7 +40224,7 @@
         <v>1875</v>
       </c>
       <c r="W496" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40304,7 +40292,7 @@
         <v>1876</v>
       </c>
       <c r="W497" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40369,7 +40357,7 @@
         <v>1877</v>
       </c>
       <c r="W498" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40437,7 +40425,7 @@
         <v>1878</v>
       </c>
       <c r="W499" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40502,16 +40490,16 @@
         <v>1879</v>
       </c>
       <c r="W500" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X500" t="s">
-        <v>2120</v>
+        <v>2118</v>
       </c>
       <c r="Y500" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z500" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40576,16 +40564,16 @@
         <v>1880</v>
       </c>
       <c r="W501" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X501" t="s">
-        <v>2123</v>
+        <v>2121</v>
       </c>
       <c r="Y501" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z501" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40650,7 +40638,7 @@
         <v>1881</v>
       </c>
       <c r="W502" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40718,7 +40706,7 @@
         <v>1882</v>
       </c>
       <c r="W503" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40786,16 +40774,16 @@
         <v>1883</v>
       </c>
       <c r="W504" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X504" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
       <c r="Y504" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z504" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40860,7 +40848,7 @@
         <v>1884</v>
       </c>
       <c r="W505" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40925,16 +40913,16 @@
         <v>1885</v>
       </c>
       <c r="W506" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X506" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
       <c r="Y506" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z506" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -40999,7 +40987,7 @@
         <v>1886</v>
       </c>
       <c r="W507" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41064,7 +41052,7 @@
         <v>1887</v>
       </c>
       <c r="W508" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41129,16 +41117,16 @@
         <v>1888</v>
       </c>
       <c r="W509" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X509" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="Y509" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z509" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41203,16 +41191,16 @@
         <v>1889</v>
       </c>
       <c r="W510" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X510" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="Y510" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z510" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41280,7 +41268,7 @@
         <v>1890</v>
       </c>
       <c r="W511" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41348,7 +41336,7 @@
         <v>1891</v>
       </c>
       <c r="W512" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41416,7 +41404,7 @@
         <v>1892</v>
       </c>
       <c r="W513" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41484,7 +41472,7 @@
         <v>1892</v>
       </c>
       <c r="W514" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41552,7 +41540,7 @@
         <v>1892</v>
       </c>
       <c r="W515" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41620,13 +41608,13 @@
         <v>1893</v>
       </c>
       <c r="W516" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41694,13 +41682,13 @@
         <v>1894</v>
       </c>
       <c r="W517" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41768,16 +41756,16 @@
         <v>1895</v>
       </c>
       <c r="W518" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X518" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="Y518" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z518" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41845,16 +41833,16 @@
         <v>1896</v>
       </c>
       <c r="W519" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X519" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
       <c r="Y519" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z519" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41919,7 +41907,7 @@
         <v>1499</v>
       </c>
       <c r="W520" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -41987,7 +41975,7 @@
         <v>1897</v>
       </c>
       <c r="W521" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42055,7 +42043,7 @@
         <v>1897</v>
       </c>
       <c r="W522" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42123,7 +42111,7 @@
         <v>1898</v>
       </c>
       <c r="W523" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42191,7 +42179,7 @@
         <v>1899</v>
       </c>
       <c r="W524" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42259,7 +42247,7 @@
         <v>1900</v>
       </c>
       <c r="W525" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42327,7 +42315,7 @@
         <v>1901</v>
       </c>
       <c r="W526" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42395,7 +42383,7 @@
         <v>1902</v>
       </c>
       <c r="W527" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42460,7 +42448,7 @@
         <v>1903</v>
       </c>
       <c r="W528" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42528,7 +42516,7 @@
         <v>1904</v>
       </c>
       <c r="W529" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42596,16 +42584,16 @@
         <v>1905</v>
       </c>
       <c r="W530" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X530" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
       <c r="Y530" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z530" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42673,7 +42661,7 @@
         <v>1906</v>
       </c>
       <c r="W531" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42738,7 +42726,7 @@
         <v>1907</v>
       </c>
       <c r="W532" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42806,16 +42794,16 @@
         <v>1908</v>
       </c>
       <c r="W533" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X533" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
       <c r="Y533" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z533" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42883,13 +42871,13 @@
         <v>1909</v>
       </c>
       <c r="W534" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -42957,7 +42945,7 @@
         <v>1910</v>
       </c>
       <c r="W535" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43025,7 +43013,7 @@
         <v>1911</v>
       </c>
       <c r="W536" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43093,16 +43081,16 @@
         <v>1912</v>
       </c>
       <c r="W537" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X537" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
       <c r="Y537" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z537" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43170,7 +43158,7 @@
         <v>1913</v>
       </c>
       <c r="W538" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43238,7 +43226,7 @@
         <v>1914</v>
       </c>
       <c r="W539" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43306,7 +43294,7 @@
         <v>1915</v>
       </c>
       <c r="W540" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43374,7 +43362,7 @@
         <v>1916</v>
       </c>
       <c r="W541" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43442,16 +43430,16 @@
         <v>1917</v>
       </c>
       <c r="W542" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X542" t="s">
+        <v>2130</v>
+      </c>
+      <c r="Y542" t="s">
         <v>2132</v>
       </c>
-      <c r="Y542" t="s">
-        <v>2134</v>
-      </c>
       <c r="Z542" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43519,7 +43507,7 @@
         <v>1918</v>
       </c>
       <c r="W543" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43587,16 +43575,16 @@
         <v>1919</v>
       </c>
       <c r="W544" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="X544" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
       <c r="Y544" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
       <c r="Z544" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43664,7 +43652,7 @@
         <v>1920</v>
       </c>
       <c r="W545" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43732,7 +43720,7 @@
         <v>1921</v>
       </c>
       <c r="W546" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43800,7 +43788,7 @@
         <v>1922</v>
       </c>
       <c r="W547" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43868,7 +43856,7 @@
         <v>1923</v>
       </c>
       <c r="W548" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -43936,7 +43924,7 @@
         <v>1923</v>
       </c>
       <c r="W549" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44004,7 +43992,7 @@
         <v>1924</v>
       </c>
       <c r="W550" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44069,7 +44057,7 @@
         <v>1925</v>
       </c>
       <c r="W551" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44137,7 +44125,7 @@
         <v>1926</v>
       </c>
       <c r="W552" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44202,7 +44190,7 @@
         <v>1927</v>
       </c>
       <c r="W553" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44270,7 +44258,7 @@
         <v>1928</v>
       </c>
       <c r="W554" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44338,7 +44326,7 @@
         <v>1929</v>
       </c>
       <c r="W555" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44406,7 +44394,7 @@
         <v>1930</v>
       </c>
       <c r="W556" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44471,7 +44459,7 @@
         <v>1931</v>
       </c>
       <c r="W557" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44539,7 +44527,7 @@
         <v>1932</v>
       </c>
       <c r="W558" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44607,7 +44595,7 @@
         <v>1933</v>
       </c>
       <c r="W559" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44672,7 +44660,7 @@
         <v>1934</v>
       </c>
       <c r="W560" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44740,7 +44728,7 @@
         <v>1935</v>
       </c>
       <c r="W561" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44805,10 +44793,10 @@
         <v>1497</v>
       </c>
       <c r="V562" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="W562" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44873,7 +44861,7 @@
         <v>1936</v>
       </c>
       <c r="W563" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -44922,9 +44910,6 @@
       <c r="N564" s="1">
         <v>46248</v>
       </c>
-      <c r="O564" s="1">
-        <v>46248</v>
-      </c>
       <c r="Q564">
         <v>-46248</v>
       </c>
@@ -44940,11 +44925,8 @@
       <c r="U564" t="s">
         <v>1937</v>
       </c>
-      <c r="V564" t="s">
-        <v>1963</v>
-      </c>
       <c r="W564" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45012,7 +44994,7 @@
         <v>1938</v>
       </c>
       <c r="W565" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45080,7 +45062,7 @@
         <v>1939</v>
       </c>
       <c r="W566" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45148,7 +45130,7 @@
         <v>1940</v>
       </c>
       <c r="W567" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45216,10 +45198,10 @@
         <v>1941</v>
       </c>
       <c r="V568" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="W568" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA568" t="b">
         <v>1</v>
@@ -45287,7 +45269,7 @@
         <v>1942</v>
       </c>
       <c r="W569" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45352,7 +45334,7 @@
         <v>1943</v>
       </c>
       <c r="W570" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45417,7 +45399,7 @@
         <v>1944</v>
       </c>
       <c r="W571" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45485,7 +45467,7 @@
         <v>1945</v>
       </c>
       <c r="W572" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45553,7 +45535,7 @@
         <v>1946</v>
       </c>
       <c r="W573" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45621,7 +45603,7 @@
         <v>1947</v>
       </c>
       <c r="W574" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45670,9 +45652,6 @@
       <c r="N575" s="1">
         <v>46255</v>
       </c>
-      <c r="O575" s="1">
-        <v>46244</v>
-      </c>
       <c r="P575" t="s">
         <v>1491</v>
       </c>
@@ -45691,11 +45670,8 @@
       <c r="U575" t="s">
         <v>1948</v>
       </c>
-      <c r="V575" t="s">
-        <v>1965</v>
-      </c>
       <c r="W575" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -45763,7 +45739,7 @@
         <v>1949</v>
       </c>
       <c r="W576" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45831,7 +45807,7 @@
         <v>1949</v>
       </c>
       <c r="W577" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45899,7 +45875,7 @@
         <v>1950</v>
       </c>
       <c r="W578" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -45967,7 +45943,7 @@
         <v>1951</v>
       </c>
       <c r="W579" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46035,7 +46011,7 @@
         <v>1952</v>
       </c>
       <c r="W580" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46103,7 +46079,7 @@
         <v>1953</v>
       </c>
       <c r="W581" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46171,10 +46147,10 @@
         <v>1954</v>
       </c>
       <c r="V582" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="W582" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA582" t="b">
         <v>1</v>
@@ -46239,10 +46215,10 @@
         <v>1497</v>
       </c>
       <c r="V583" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="W583" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA583" t="b">
         <v>1</v>
@@ -46310,7 +46286,7 @@
         <v>1955</v>
       </c>
       <c r="W584" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46378,7 +46354,7 @@
         <v>1955</v>
       </c>
       <c r="W585" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46443,10 +46419,10 @@
         <v>1497</v>
       </c>
       <c r="V586" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="W586" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46505,10 +46481,10 @@
         <v>1496</v>
       </c>
       <c r="V587" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="W587" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA587" t="b">
         <v>1</v>
@@ -46576,10 +46552,10 @@
         <v>1956</v>
       </c>
       <c r="V588" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="W588" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46647,10 +46623,10 @@
         <v>1957</v>
       </c>
       <c r="V589" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="W589" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA589" t="b">
         <v>1</v>
@@ -46718,10 +46694,10 @@
         <v>1958</v>
       </c>
       <c r="V590" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="W590" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA590" t="b">
         <v>1</v>
@@ -46786,10 +46762,10 @@
         <v>1496</v>
       </c>
       <c r="V591" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="W591" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA591" t="b">
         <v>1</v>
@@ -46857,10 +46833,10 @@
         <v>1959</v>
       </c>
       <c r="V592" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="W592" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA592" t="b">
         <v>1</v>
@@ -46928,10 +46904,10 @@
         <v>1960</v>
       </c>
       <c r="V593" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="W593" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA593" t="b">
         <v>1</v>
@@ -46996,7 +46972,7 @@
         <v>1959</v>
       </c>
       <c r="W594" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="AA594" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44781,10 +44781,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R562">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S562" t="s">
         <v>1496</v>
@@ -45183,10 +45183,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R568">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S568" t="s">
         <v>1496</v>
@@ -46132,10 +46132,10 @@
         <v>46240</v>
       </c>
       <c r="Q582">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="R582">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S582" t="s">
         <v>1496</v>
@@ -46203,10 +46203,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="R583">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S583" t="s">
         <v>1496</v>
@@ -46407,10 +46407,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="R586">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S586" t="s">
         <v>1496</v>
@@ -46472,10 +46472,10 @@
         <v>46248</v>
       </c>
       <c r="Q587">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R587">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S587" t="s">
         <v>1496</v>
@@ -46537,10 +46537,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="R588">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S588" t="s">
         <v>1497</v>
@@ -46608,10 +46608,10 @@
         <v>46254</v>
       </c>
       <c r="Q589">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R589">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S589" t="s">
         <v>1497</v>
@@ -46679,10 +46679,10 @@
         <v>46248</v>
       </c>
       <c r="Q590">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R590">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S590" t="s">
         <v>1496</v>
@@ -46750,10 +46750,10 @@
         <v>46257</v>
       </c>
       <c r="Q591">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R591">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S591" t="s">
         <v>1496</v>
@@ -46818,10 +46818,10 @@
         <v>46254</v>
       </c>
       <c r="Q592">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R592">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S592" t="s">
         <v>1496</v>
@@ -46889,10 +46889,10 @@
         <v>46254</v>
       </c>
       <c r="Q593">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R593">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S593" t="s">
         <v>1497</v>
@@ -46957,10 +46957,10 @@
         <v>46278</v>
       </c>
       <c r="Q594">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R594">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S594" t="s">
         <v>1496</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -5890,7 +5890,7 @@
     <t>Estoque com 12 EA do Pn LM600-9 (Alternado). Godoy 12/08/26. Atendido com estoque local em 13/08. Ramon 13/08/26</t>
   </si>
   <si>
-    <t>AWB 127-5256 7745 com previsão de entrega em 14/08. Ramon 13/08/26</t>
+    <t>AWB 127-5256 7745 com previsão de entrega em 14/08. Ramon 13/08/26. Recibo 680/FAB/26 (NF 2082) assinados em 13/08. Ramon 14/08/26</t>
   </si>
   <si>
     <t>Item em pane, anv autorizada a voar por 3 dias pela MMEL a contar de 12/08. Ramon 13/08/26</t>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44799,10 +44799,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R562">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="S562" t="s">
         <v>1502</v>
@@ -45201,10 +45201,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="R568">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S568" t="s">
         <v>1502</v>
@@ -46150,10 +46150,10 @@
         <v>46240</v>
       </c>
       <c r="Q582">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="R582">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S582" t="s">
         <v>1502</v>
@@ -46221,10 +46221,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="R583">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S583" t="s">
         <v>1502</v>
@@ -46425,10 +46425,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-21</v>
+        <v>-18</v>
       </c>
       <c r="R586">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S586" t="s">
         <v>1502</v>
@@ -46490,10 +46490,10 @@
         <v>46248</v>
       </c>
       <c r="Q587">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R587">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S587" t="s">
         <v>1502</v>
@@ -46555,10 +46555,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R588">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S588" t="s">
         <v>1503</v>
@@ -46626,10 +46626,10 @@
         <v>46254</v>
       </c>
       <c r="Q589">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R589">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S589" t="s">
         <v>1503</v>
@@ -46768,10 +46768,10 @@
         <v>46257</v>
       </c>
       <c r="Q591">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="R591">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S591" t="s">
         <v>1502</v>
@@ -46836,10 +46836,10 @@
         <v>46254</v>
       </c>
       <c r="Q592">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R592">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S592" t="s">
         <v>1502</v>
@@ -46907,10 +46907,10 @@
         <v>46254</v>
       </c>
       <c r="Q593">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R593">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S593" t="s">
         <v>1503</v>
@@ -46975,10 +46975,10 @@
         <v>46278</v>
       </c>
       <c r="Q594">
-        <v>-30</v>
+        <v>-27</v>
       </c>
       <c r="R594">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S594" t="s">
         <v>1502</v>
@@ -47040,10 +47040,10 @@
         <v>46279</v>
       </c>
       <c r="Q595">
-        <v>-31</v>
+        <v>-28</v>
       </c>
       <c r="R595">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S595" t="s">
         <v>1503</v>
@@ -47102,10 +47102,10 @@
         <v>46259</v>
       </c>
       <c r="Q596">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R596">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S596" t="s">
         <v>1503</v>
@@ -47164,10 +47164,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R597">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S597" t="s">
         <v>1502</v>
@@ -47226,10 +47226,10 @@
         <v>46259</v>
       </c>
       <c r="Q598">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R598">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S598" t="s">
         <v>1502</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -5941,9 +5941,6 @@
     <t>Temos somente 03 ea em STK, favor utilizar o estoque FAB para posterior devolução. ATZ RC 13/08 - FOI SOLICITADO O ATENDIMENTO COM ESTOQUE FAB -CLA-13-08</t>
   </si>
   <si>
-    <t>Estoque veeone da base pamals- AWB 12752567745 - DPE 14/08/2026 - recibo 680/FAB/26</t>
-  </si>
-  <si>
     <t>Previsao de entrega da oficina do RJ na V1 JPA 13/8/2026 durante o dia, horario comercial, ATZ Marcio 12/8 13:22hs</t>
   </si>
   <si>
@@ -5951,6 +5948,9 @@
   </si>
   <si>
     <t>Temos no STK V1, material em separação, recibo 682/FAB/26 - atz rc 13/08</t>
+  </si>
+  <si>
+    <t>será enviado o pn 9910592-2 do estoque da VeeOne base PAMALS. -CLA -14-08</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -46693,9 +46693,6 @@
       <c r="N590" s="1">
         <v>46257</v>
       </c>
-      <c r="O590" s="1">
-        <v>46248</v>
-      </c>
       <c r="Q590">
         <v>-46257</v>
       </c>
@@ -46710,9 +46707,6 @@
       </c>
       <c r="U590" t="s">
         <v>1964</v>
-      </c>
-      <c r="V590" t="s">
-        <v>1975</v>
       </c>
       <c r="W590" t="s">
         <v>1979</v>
@@ -46780,7 +46774,7 @@
         <v>1502</v>
       </c>
       <c r="V591" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="W591" t="s">
         <v>1979</v>
@@ -46851,7 +46845,7 @@
         <v>1965</v>
       </c>
       <c r="V592" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="W592" t="s">
         <v>1979</v>
@@ -46922,7 +46916,7 @@
         <v>1966</v>
       </c>
       <c r="V593" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="W593" t="s">
         <v>1979</v>
@@ -46988,6 +46982,9 @@
       </c>
       <c r="U594" t="s">
         <v>1965</v>
+      </c>
+      <c r="V594" t="s">
+        <v>1978</v>
       </c>
       <c r="W594" t="s">
         <v>1979</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7503" uniqueCount="2355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7504" uniqueCount="2356">
   <si>
     <t>om_emg</t>
   </si>
@@ -5921,6 +5921,9 @@
   </si>
   <si>
     <t>item será atendido com o estoque local pedido 18216324. Godoy 17/08.</t>
+  </si>
+  <si>
+    <t>Estoque alterado de "Nao" para "SIM"  daremos prioridade para movimentar o item.  Godoy 17/08/226</t>
   </si>
   <si>
     <t>Emerg Cancelada por 3S JACQUELINEJSRG em 14/08/2026 motivo: será refeito - Godoy 17/08/2026.</t>
@@ -7556,7 +7559,7 @@
         <v>1507</v>
       </c>
       <c r="W2" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7618,16 +7621,16 @@
         <v>1508</v>
       </c>
       <c r="W3" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X3" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="Y3" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z3" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7689,7 +7692,7 @@
         <v>1507</v>
       </c>
       <c r="W4" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7751,7 +7754,7 @@
         <v>1509</v>
       </c>
       <c r="W5" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7813,7 +7816,7 @@
         <v>1510</v>
       </c>
       <c r="W6" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7875,7 +7878,7 @@
         <v>1511</v>
       </c>
       <c r="W7" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7937,7 +7940,7 @@
         <v>1512</v>
       </c>
       <c r="W8" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7999,7 +8002,7 @@
         <v>1513</v>
       </c>
       <c r="W9" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8061,7 +8064,7 @@
         <v>1514</v>
       </c>
       <c r="W10" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8123,7 +8126,7 @@
         <v>1515</v>
       </c>
       <c r="W11" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8185,7 +8188,7 @@
         <v>1516</v>
       </c>
       <c r="W12" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8247,7 +8250,7 @@
         <v>1512</v>
       </c>
       <c r="W13" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8309,16 +8312,16 @@
         <v>1517</v>
       </c>
       <c r="W14" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X14" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="Y14" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z14" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8377,7 +8380,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8442,7 +8445,7 @@
         <v>1518</v>
       </c>
       <c r="W16" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8504,7 +8507,7 @@
         <v>1519</v>
       </c>
       <c r="W17" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8566,7 +8569,7 @@
         <v>1510</v>
       </c>
       <c r="W18" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8628,7 +8631,7 @@
         <v>1510</v>
       </c>
       <c r="W19" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8690,7 +8693,7 @@
         <v>1520</v>
       </c>
       <c r="W20" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8752,7 +8755,7 @@
         <v>1521</v>
       </c>
       <c r="W21" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8814,7 +8817,7 @@
         <v>1521</v>
       </c>
       <c r="W22" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8876,7 +8879,7 @@
         <v>1522</v>
       </c>
       <c r="W23" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8935,7 +8938,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -8994,7 +8997,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9056,7 +9059,7 @@
         <v>1510</v>
       </c>
       <c r="W26" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9115,7 +9118,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9174,7 +9177,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9236,7 +9239,7 @@
         <v>1523</v>
       </c>
       <c r="W29" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9295,7 +9298,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9357,7 +9360,7 @@
         <v>1524</v>
       </c>
       <c r="W31" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9419,7 +9422,7 @@
         <v>1525</v>
       </c>
       <c r="W32" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9481,7 +9484,7 @@
         <v>1526</v>
       </c>
       <c r="W33" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9543,7 +9546,7 @@
         <v>1527</v>
       </c>
       <c r="W34" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9605,7 +9608,7 @@
         <v>1528</v>
       </c>
       <c r="W35" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9667,7 +9670,7 @@
         <v>1524</v>
       </c>
       <c r="W36" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9729,7 +9732,7 @@
         <v>1529</v>
       </c>
       <c r="W37" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9791,7 +9794,7 @@
         <v>1507</v>
       </c>
       <c r="W38" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9853,7 +9856,7 @@
         <v>1526</v>
       </c>
       <c r="W39" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9915,7 +9918,7 @@
         <v>1530</v>
       </c>
       <c r="W40" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -9977,7 +9980,7 @@
         <v>1531</v>
       </c>
       <c r="W41" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10039,16 +10042,16 @@
         <v>1532</v>
       </c>
       <c r="W42" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X42" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="Y42" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z42" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10110,7 +10113,7 @@
         <v>1526</v>
       </c>
       <c r="W43" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10172,7 +10175,7 @@
         <v>1533</v>
       </c>
       <c r="W44" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10234,7 +10237,7 @@
         <v>1526</v>
       </c>
       <c r="W45" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10296,7 +10299,7 @@
         <v>1526</v>
       </c>
       <c r="W46" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10358,7 +10361,7 @@
         <v>1534</v>
       </c>
       <c r="W47" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10420,7 +10423,7 @@
         <v>1535</v>
       </c>
       <c r="W48" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10482,7 +10485,7 @@
         <v>1536</v>
       </c>
       <c r="W49" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10544,7 +10547,7 @@
         <v>1537</v>
       </c>
       <c r="W50" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10606,7 +10609,7 @@
         <v>1538</v>
       </c>
       <c r="W51" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10668,7 +10671,7 @@
         <v>1527</v>
       </c>
       <c r="W52" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10730,7 +10733,7 @@
         <v>1521</v>
       </c>
       <c r="W53" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10792,7 +10795,7 @@
         <v>1521</v>
       </c>
       <c r="W54" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10854,7 +10857,7 @@
         <v>1521</v>
       </c>
       <c r="W55" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10916,7 +10919,7 @@
         <v>1539</v>
       </c>
       <c r="W56" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -10978,7 +10981,7 @@
         <v>1540</v>
       </c>
       <c r="W57" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11040,16 +11043,16 @@
         <v>1541</v>
       </c>
       <c r="W58" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X58" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="Y58" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z58" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11111,7 +11114,7 @@
         <v>1542</v>
       </c>
       <c r="W59" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11173,7 +11176,7 @@
         <v>1543</v>
       </c>
       <c r="W60" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11235,7 +11238,7 @@
         <v>1521</v>
       </c>
       <c r="W61" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11297,7 +11300,7 @@
         <v>1544</v>
       </c>
       <c r="W62" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11356,7 +11359,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11415,7 +11418,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11474,7 +11477,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11533,7 +11536,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11592,7 +11595,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11651,7 +11654,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11713,7 +11716,7 @@
         <v>1545</v>
       </c>
       <c r="W69" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11775,7 +11778,7 @@
         <v>1543</v>
       </c>
       <c r="W70" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11837,7 +11840,7 @@
         <v>1528</v>
       </c>
       <c r="W71" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11899,7 +11902,7 @@
         <v>1546</v>
       </c>
       <c r="W72" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -11961,7 +11964,7 @@
         <v>1547</v>
       </c>
       <c r="W73" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12023,16 +12026,16 @@
         <v>1548</v>
       </c>
       <c r="W74" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X74" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="Y74" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z74" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12094,16 +12097,16 @@
         <v>1549</v>
       </c>
       <c r="W75" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X75" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="Y75" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z75" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12165,7 +12168,7 @@
         <v>1528</v>
       </c>
       <c r="W76" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12227,7 +12230,7 @@
         <v>1528</v>
       </c>
       <c r="W77" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12289,10 +12292,10 @@
         <v>1550</v>
       </c>
       <c r="W78" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="Z78" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12357,7 +12360,7 @@
         <v>1551</v>
       </c>
       <c r="W79" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12416,7 +12419,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12475,7 +12478,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12537,7 +12540,7 @@
         <v>1552</v>
       </c>
       <c r="W82" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12599,7 +12602,7 @@
         <v>1553</v>
       </c>
       <c r="W83" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12661,7 +12664,7 @@
         <v>1554</v>
       </c>
       <c r="W84" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12720,7 +12723,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12782,7 +12785,7 @@
         <v>1555</v>
       </c>
       <c r="W86" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12844,7 +12847,7 @@
         <v>1556</v>
       </c>
       <c r="W87" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12906,7 +12909,7 @@
         <v>1556</v>
       </c>
       <c r="W88" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -12968,7 +12971,7 @@
         <v>1521</v>
       </c>
       <c r="W89" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13030,16 +13033,16 @@
         <v>1557</v>
       </c>
       <c r="W90" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X90" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="Y90" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z90" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13101,16 +13104,16 @@
         <v>1558</v>
       </c>
       <c r="W91" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X91" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="Y91" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z91" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13172,7 +13175,7 @@
         <v>1559</v>
       </c>
       <c r="W92" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13234,7 +13237,7 @@
         <v>1560</v>
       </c>
       <c r="W93" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13296,7 +13299,7 @@
         <v>1560</v>
       </c>
       <c r="W94" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13358,7 +13361,7 @@
         <v>1561</v>
       </c>
       <c r="W95" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13420,16 +13423,16 @@
         <v>1562</v>
       </c>
       <c r="W96" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X96" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="Y96" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z96" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13491,7 +13494,7 @@
         <v>1563</v>
       </c>
       <c r="W97" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13553,7 +13556,7 @@
         <v>1564</v>
       </c>
       <c r="W98" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13615,7 +13618,7 @@
         <v>1565</v>
       </c>
       <c r="W99" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13677,7 +13680,7 @@
         <v>1566</v>
       </c>
       <c r="W100" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13739,16 +13742,16 @@
         <v>1567</v>
       </c>
       <c r="W101" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X101" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="Y101" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z101" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13810,7 +13813,7 @@
         <v>1568</v>
       </c>
       <c r="W102" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13872,7 +13875,7 @@
         <v>1568</v>
       </c>
       <c r="W103" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13934,7 +13937,7 @@
         <v>1569</v>
       </c>
       <c r="W104" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -13996,16 +13999,16 @@
         <v>1570</v>
       </c>
       <c r="W105" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X105" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="Y105" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z105" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14067,16 +14070,16 @@
         <v>1571</v>
       </c>
       <c r="W106" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X106" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="Y106" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z106" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14138,7 +14141,7 @@
         <v>1572</v>
       </c>
       <c r="W107" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14200,16 +14203,16 @@
         <v>1573</v>
       </c>
       <c r="W108" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X108" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="Y108" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z108" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14271,16 +14274,16 @@
         <v>1574</v>
       </c>
       <c r="W109" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X109" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="Y109" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z109" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14339,7 +14342,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14401,16 +14404,16 @@
         <v>1575</v>
       </c>
       <c r="W111" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X111" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y111" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z111" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14472,16 +14475,16 @@
         <v>1576</v>
       </c>
       <c r="W112" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X112" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="Y112" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z112" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14543,16 +14546,16 @@
         <v>1577</v>
       </c>
       <c r="W113" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X113" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="Y113" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z113" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14614,16 +14617,16 @@
         <v>1578</v>
       </c>
       <c r="W114" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X114" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="Y114" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z114" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14685,16 +14688,16 @@
         <v>1574</v>
       </c>
       <c r="W115" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X115" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="Y115" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z115" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14756,16 +14759,16 @@
         <v>1574</v>
       </c>
       <c r="W116" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X116" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="Y116" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z116" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14827,16 +14830,16 @@
         <v>1579</v>
       </c>
       <c r="W117" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X117" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="Y117" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z117" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14898,16 +14901,16 @@
         <v>1580</v>
       </c>
       <c r="W118" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X118" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="Y118" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z118" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -14969,7 +14972,7 @@
         <v>1581</v>
       </c>
       <c r="W119" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15031,16 +15034,16 @@
         <v>1582</v>
       </c>
       <c r="W120" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X120" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y120" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z120" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15102,16 +15105,16 @@
         <v>1582</v>
       </c>
       <c r="W121" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X121" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y121" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z121" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15173,16 +15176,16 @@
         <v>1582</v>
       </c>
       <c r="W122" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X122" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y122" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z122" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15244,16 +15247,16 @@
         <v>1582</v>
       </c>
       <c r="W123" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X123" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y123" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z123" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15315,16 +15318,16 @@
         <v>1582</v>
       </c>
       <c r="W124" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X124" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y124" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z124" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15386,16 +15389,16 @@
         <v>1582</v>
       </c>
       <c r="W125" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X125" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y125" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z125" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15457,16 +15460,16 @@
         <v>1582</v>
       </c>
       <c r="W126" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X126" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y126" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z126" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15528,16 +15531,16 @@
         <v>1583</v>
       </c>
       <c r="W127" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X127" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="Y127" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z127" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15599,16 +15602,16 @@
         <v>1584</v>
       </c>
       <c r="W128" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X128" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="Y128" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z128" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15670,16 +15673,16 @@
         <v>1582</v>
       </c>
       <c r="W129" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X129" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y129" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z129" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15741,16 +15744,16 @@
         <v>1582</v>
       </c>
       <c r="W130" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X130" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y130" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z130" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15812,7 +15815,7 @@
         <v>1585</v>
       </c>
       <c r="W131" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15871,7 +15874,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15930,7 +15933,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -15992,16 +15995,16 @@
         <v>1582</v>
       </c>
       <c r="W134" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X134" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y134" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z134" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16063,16 +16066,16 @@
         <v>1582</v>
       </c>
       <c r="W135" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X135" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y135" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z135" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16134,7 +16137,7 @@
         <v>1581</v>
       </c>
       <c r="W136" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16193,7 +16196,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16255,16 +16258,16 @@
         <v>1586</v>
       </c>
       <c r="W138" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X138" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Y138" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z138" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16326,16 +16329,16 @@
         <v>1574</v>
       </c>
       <c r="W139" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X139" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="Y139" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z139" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16397,16 +16400,16 @@
         <v>1582</v>
       </c>
       <c r="W140" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X140" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y140" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z140" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16465,7 +16468,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16524,7 +16527,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16586,16 +16589,16 @@
         <v>1587</v>
       </c>
       <c r="W143" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X143" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="Y143" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z143" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16657,16 +16660,16 @@
         <v>1588</v>
       </c>
       <c r="W144" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X144" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="Y144" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z144" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16728,16 +16731,16 @@
         <v>1589</v>
       </c>
       <c r="W145" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X145" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="Y145" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z145" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16799,16 +16802,16 @@
         <v>1590</v>
       </c>
       <c r="W146" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X146" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="Y146" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z146" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16867,7 +16870,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16929,7 +16932,7 @@
         <v>1591</v>
       </c>
       <c r="W148" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -16991,16 +16994,16 @@
         <v>1592</v>
       </c>
       <c r="W149" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X149" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="Y149" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z149" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17062,7 +17065,7 @@
         <v>1593</v>
       </c>
       <c r="W150" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17124,16 +17127,16 @@
         <v>1594</v>
       </c>
       <c r="W151" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X151" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="Y151" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z151" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17195,7 +17198,7 @@
         <v>1593</v>
       </c>
       <c r="W152" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17257,7 +17260,7 @@
         <v>1591</v>
       </c>
       <c r="W153" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17319,7 +17322,7 @@
         <v>1593</v>
       </c>
       <c r="W154" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17381,7 +17384,7 @@
         <v>1593</v>
       </c>
       <c r="W155" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17443,16 +17446,16 @@
         <v>1595</v>
       </c>
       <c r="W156" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X156" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="Y156" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z156" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17514,7 +17517,7 @@
         <v>1591</v>
       </c>
       <c r="W157" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17576,16 +17579,16 @@
         <v>1596</v>
       </c>
       <c r="W158" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X158" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y158" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z158" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17647,16 +17650,16 @@
         <v>1597</v>
       </c>
       <c r="W159" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X159" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="Y159" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z159" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17718,16 +17721,16 @@
         <v>1596</v>
       </c>
       <c r="W160" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X160" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y160" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z160" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17789,16 +17792,16 @@
         <v>1596</v>
       </c>
       <c r="W161" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X161" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y161" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z161" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17860,16 +17863,16 @@
         <v>1596</v>
       </c>
       <c r="W162" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X162" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y162" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z162" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17931,16 +17934,16 @@
         <v>1598</v>
       </c>
       <c r="W163" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X163" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="Y163" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z163" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -18002,16 +18005,16 @@
         <v>1599</v>
       </c>
       <c r="W164" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X164" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="Y164" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z164" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18073,16 +18076,16 @@
         <v>1600</v>
       </c>
       <c r="W165" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X165" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="Y165" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z165" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18144,16 +18147,16 @@
         <v>1601</v>
       </c>
       <c r="W166" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X166" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Y166" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z166" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18215,16 +18218,16 @@
         <v>1579</v>
       </c>
       <c r="W167" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X167" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="Y167" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z167" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18286,16 +18289,16 @@
         <v>1582</v>
       </c>
       <c r="W168" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X168" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y168" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z168" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18357,7 +18360,7 @@
         <v>1602</v>
       </c>
       <c r="W169" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18419,16 +18422,16 @@
         <v>1582</v>
       </c>
       <c r="W170" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X170" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="Y170" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z170" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18490,16 +18493,16 @@
         <v>1603</v>
       </c>
       <c r="W171" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X171" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y171" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z171" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18561,16 +18564,16 @@
         <v>1604</v>
       </c>
       <c r="W172" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X172" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Y172" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z172" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18632,16 +18635,16 @@
         <v>1605</v>
       </c>
       <c r="W173" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X173" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="Y173" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z173" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18703,16 +18706,16 @@
         <v>1606</v>
       </c>
       <c r="W174" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X174" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="Y174" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z174" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18774,16 +18777,16 @@
         <v>1607</v>
       </c>
       <c r="W175" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X175" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="Y175" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z175" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18845,16 +18848,16 @@
         <v>1608</v>
       </c>
       <c r="W176" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X176" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Y176" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z176" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18916,7 +18919,7 @@
         <v>1602</v>
       </c>
       <c r="W177" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -18978,16 +18981,16 @@
         <v>1609</v>
       </c>
       <c r="W178" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X178" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y178" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z178" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19049,16 +19052,16 @@
         <v>1610</v>
       </c>
       <c r="W179" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X179" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y179" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z179" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19120,7 +19123,7 @@
         <v>1611</v>
       </c>
       <c r="W180" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19182,16 +19185,16 @@
         <v>1612</v>
       </c>
       <c r="W181" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X181" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Y181" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z181" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19253,16 +19256,16 @@
         <v>1612</v>
       </c>
       <c r="W182" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X182" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Y182" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z182" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19324,16 +19327,16 @@
         <v>1613</v>
       </c>
       <c r="W183" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X183" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="Y183" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z183" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19395,16 +19398,16 @@
         <v>1614</v>
       </c>
       <c r="W184" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X184" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="Y184" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z184" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19466,16 +19469,16 @@
         <v>1615</v>
       </c>
       <c r="W185" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X185" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="Y185" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z185" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19537,7 +19540,7 @@
         <v>1616</v>
       </c>
       <c r="W186" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19599,7 +19602,7 @@
         <v>1617</v>
       </c>
       <c r="W187" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19661,7 +19664,7 @@
         <v>1618</v>
       </c>
       <c r="W188" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19723,7 +19726,7 @@
         <v>1619</v>
       </c>
       <c r="W189" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19785,16 +19788,16 @@
         <v>1620</v>
       </c>
       <c r="W190" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X190" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="Y190" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z190" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19856,16 +19859,16 @@
         <v>1621</v>
       </c>
       <c r="W191" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X191" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="Y191" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z191" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19927,7 +19930,7 @@
         <v>1622</v>
       </c>
       <c r="W192" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -19989,7 +19992,7 @@
         <v>1622</v>
       </c>
       <c r="W193" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20051,16 +20054,16 @@
         <v>1623</v>
       </c>
       <c r="W194" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X194" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="Y194" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z194" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20122,16 +20125,16 @@
         <v>1624</v>
       </c>
       <c r="W195" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X195" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="Y195" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z195" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20193,16 +20196,16 @@
         <v>1625</v>
       </c>
       <c r="W196" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X196" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="Y196" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z196" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20264,16 +20267,16 @@
         <v>1621</v>
       </c>
       <c r="W197" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X197" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="Y197" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z197" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20335,7 +20338,7 @@
         <v>1626</v>
       </c>
       <c r="W198" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20397,7 +20400,7 @@
         <v>1627</v>
       </c>
       <c r="W199" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20459,16 +20462,16 @@
         <v>1628</v>
       </c>
       <c r="W200" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X200" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Y200" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z200" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20530,16 +20533,16 @@
         <v>1628</v>
       </c>
       <c r="W201" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X201" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Y201" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z201" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20601,16 +20604,16 @@
         <v>1629</v>
       </c>
       <c r="W202" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X202" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="Y202" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z202" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20672,16 +20675,16 @@
         <v>1630</v>
       </c>
       <c r="W203" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X203" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y203" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z203" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20743,16 +20746,16 @@
         <v>1631</v>
       </c>
       <c r="W204" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X204" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="Y204" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z204" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20814,16 +20817,16 @@
         <v>1632</v>
       </c>
       <c r="W205" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X205" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="Y205" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z205" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20885,16 +20888,16 @@
         <v>1633</v>
       </c>
       <c r="W206" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X206" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="Y206" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z206" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -20956,16 +20959,16 @@
         <v>1634</v>
       </c>
       <c r="W207" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X207" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="Y207" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z207" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21027,16 +21030,16 @@
         <v>1635</v>
       </c>
       <c r="W208" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X208" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="Y208" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z208" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21098,7 +21101,7 @@
         <v>1636</v>
       </c>
       <c r="W209" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21160,16 +21163,16 @@
         <v>1637</v>
       </c>
       <c r="W210" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X210" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y210" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z210" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21231,16 +21234,16 @@
         <v>1638</v>
       </c>
       <c r="W211" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X211" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Y211" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z211" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21302,16 +21305,16 @@
         <v>1639</v>
       </c>
       <c r="W212" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X212" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="Y212" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z212" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21373,16 +21376,16 @@
         <v>1640</v>
       </c>
       <c r="W213" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X213" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="Y213" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z213" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21444,7 +21447,7 @@
         <v>1641</v>
       </c>
       <c r="W214" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21506,16 +21509,16 @@
         <v>1606</v>
       </c>
       <c r="W215" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X215" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="Y215" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z215" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21577,16 +21580,16 @@
         <v>1642</v>
       </c>
       <c r="W216" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X216" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="Y216" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z216" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21648,7 +21651,7 @@
         <v>1643</v>
       </c>
       <c r="W217" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21710,16 +21713,16 @@
         <v>1644</v>
       </c>
       <c r="W218" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X218" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="Y218" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z218" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21781,16 +21784,16 @@
         <v>1645</v>
       </c>
       <c r="W219" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X219" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="Y219" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z219" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21852,7 +21855,7 @@
         <v>1646</v>
       </c>
       <c r="W220" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21914,7 +21917,7 @@
         <v>1647</v>
       </c>
       <c r="W221" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -21976,7 +21979,7 @@
         <v>1646</v>
       </c>
       <c r="W222" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22038,7 +22041,7 @@
         <v>1647</v>
       </c>
       <c r="W223" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22100,16 +22103,16 @@
         <v>1648</v>
       </c>
       <c r="W224" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X224" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Y224" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z224" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22171,16 +22174,16 @@
         <v>1649</v>
       </c>
       <c r="W225" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X225" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y225" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z225" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22242,7 +22245,7 @@
         <v>1650</v>
       </c>
       <c r="W226" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22304,7 +22307,7 @@
         <v>1651</v>
       </c>
       <c r="W227" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22366,7 +22369,7 @@
         <v>1652</v>
       </c>
       <c r="W228" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22428,16 +22431,16 @@
         <v>1653</v>
       </c>
       <c r="W229" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X229" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="Y229" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z229" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22499,16 +22502,16 @@
         <v>1654</v>
       </c>
       <c r="W230" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X230" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="Y230" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z230" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22570,16 +22573,16 @@
         <v>1655</v>
       </c>
       <c r="W231" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X231" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="Y231" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z231" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22644,16 +22647,16 @@
         <v>1656</v>
       </c>
       <c r="W232" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X232" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="Y232" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z232" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22715,16 +22718,16 @@
         <v>1657</v>
       </c>
       <c r="W233" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X233" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="Y233" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z233" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22786,16 +22789,16 @@
         <v>1658</v>
       </c>
       <c r="W234" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X234" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y234" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z234" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22857,16 +22860,16 @@
         <v>1658</v>
       </c>
       <c r="W235" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X235" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y235" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z235" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22928,16 +22931,16 @@
         <v>1659</v>
       </c>
       <c r="W236" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X236" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y236" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z236" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -22999,7 +23002,7 @@
         <v>1660</v>
       </c>
       <c r="W237" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23061,7 +23064,7 @@
         <v>1661</v>
       </c>
       <c r="W238" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23123,16 +23126,16 @@
         <v>1662</v>
       </c>
       <c r="W239" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X239" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="Y239" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z239" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23194,16 +23197,16 @@
         <v>1663</v>
       </c>
       <c r="W240" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X240" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="Y240" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z240" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23265,7 +23268,7 @@
         <v>1664</v>
       </c>
       <c r="W241" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23327,16 +23330,16 @@
         <v>1665</v>
       </c>
       <c r="W242" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X242" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y242" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z242" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23398,16 +23401,16 @@
         <v>1666</v>
       </c>
       <c r="W243" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X243" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="Y243" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z243" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23469,16 +23472,16 @@
         <v>1665</v>
       </c>
       <c r="W244" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X244" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y244" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z244" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23540,16 +23543,16 @@
         <v>1667</v>
       </c>
       <c r="W245" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X245" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="Y245" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z245" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23611,16 +23614,16 @@
         <v>1666</v>
       </c>
       <c r="W246" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X246" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="Y246" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z246" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23682,16 +23685,16 @@
         <v>1667</v>
       </c>
       <c r="W247" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X247" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="Y247" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z247" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23753,16 +23756,16 @@
         <v>1668</v>
       </c>
       <c r="W248" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X248" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="Y248" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z248" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23824,16 +23827,16 @@
         <v>1658</v>
       </c>
       <c r="W249" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X249" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y249" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z249" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23895,7 +23898,7 @@
         <v>1669</v>
       </c>
       <c r="W250" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -23957,7 +23960,7 @@
         <v>1670</v>
       </c>
       <c r="W251" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -24019,16 +24022,16 @@
         <v>1671</v>
       </c>
       <c r="W252" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X252" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="Y252" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z252" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24090,16 +24093,16 @@
         <v>1672</v>
       </c>
       <c r="W253" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X253" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="Y253" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z253" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24161,7 +24164,7 @@
         <v>1673</v>
       </c>
       <c r="W254" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24223,16 +24226,16 @@
         <v>1674</v>
       </c>
       <c r="W255" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X255" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y255" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z255" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24294,7 +24297,7 @@
         <v>1675</v>
       </c>
       <c r="W256" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24359,7 +24362,7 @@
         <v>1676</v>
       </c>
       <c r="W257" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24421,7 +24424,7 @@
         <v>1677</v>
       </c>
       <c r="W258" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24483,7 +24486,7 @@
         <v>1677</v>
       </c>
       <c r="W259" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24545,7 +24548,7 @@
         <v>1678</v>
       </c>
       <c r="W260" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24607,16 +24610,16 @@
         <v>1679</v>
       </c>
       <c r="W261" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X261" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="Y261" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z261" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24678,13 +24681,13 @@
         <v>1680</v>
       </c>
       <c r="W262" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X262" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="Y262" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24746,16 +24749,16 @@
         <v>1681</v>
       </c>
       <c r="W263" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X263" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y263" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z263" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24817,7 +24820,7 @@
         <v>1682</v>
       </c>
       <c r="W264" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24879,7 +24882,7 @@
         <v>1682</v>
       </c>
       <c r="W265" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24941,7 +24944,7 @@
         <v>1683</v>
       </c>
       <c r="W266" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -25003,16 +25006,16 @@
         <v>1684</v>
       </c>
       <c r="W267" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X267" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="Y267" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z267" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25074,16 +25077,16 @@
         <v>1685</v>
       </c>
       <c r="W268" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X268" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="Y268" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z268" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25145,7 +25148,7 @@
         <v>1526</v>
       </c>
       <c r="W269" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25207,7 +25210,7 @@
         <v>1686</v>
       </c>
       <c r="W270" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25269,7 +25272,7 @@
         <v>1687</v>
       </c>
       <c r="W271" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25331,16 +25334,16 @@
         <v>1688</v>
       </c>
       <c r="W272" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X272" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="Y272" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z272" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25399,7 +25402,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25461,7 +25464,7 @@
         <v>1689</v>
       </c>
       <c r="W274" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25520,7 +25523,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25582,7 +25585,7 @@
         <v>1690</v>
       </c>
       <c r="W276" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25644,7 +25647,7 @@
         <v>1691</v>
       </c>
       <c r="W277" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25706,16 +25709,16 @@
         <v>1692</v>
       </c>
       <c r="W278" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X278" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="Y278" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z278" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25777,16 +25780,16 @@
         <v>1693</v>
       </c>
       <c r="W279" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X279" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="Y279" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z279" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25848,16 +25851,16 @@
         <v>1693</v>
       </c>
       <c r="W280" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X280" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="Y280" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z280" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25919,16 +25922,16 @@
         <v>1694</v>
       </c>
       <c r="W281" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X281" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="Y281" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z281" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -25990,7 +25993,7 @@
         <v>1695</v>
       </c>
       <c r="W282" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26052,7 +26055,7 @@
         <v>1696</v>
       </c>
       <c r="W283" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26114,7 +26117,7 @@
         <v>1697</v>
       </c>
       <c r="W284" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26176,16 +26179,16 @@
         <v>1698</v>
       </c>
       <c r="W285" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X285" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="Y285" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z285" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26247,7 +26250,7 @@
         <v>1699</v>
       </c>
       <c r="W286" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26309,16 +26312,16 @@
         <v>1693</v>
       </c>
       <c r="W287" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X287" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="Y287" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z287" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26380,16 +26383,16 @@
         <v>1700</v>
       </c>
       <c r="W288" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X288" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="Y288" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z288" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26451,7 +26454,7 @@
         <v>1701</v>
       </c>
       <c r="W289" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26513,16 +26516,16 @@
         <v>1702</v>
       </c>
       <c r="W290" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X290" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="Y290" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z290" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26584,16 +26587,16 @@
         <v>1703</v>
       </c>
       <c r="W291" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X291" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="Y291" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z291" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26655,7 +26658,7 @@
         <v>1704</v>
       </c>
       <c r="W292" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26714,7 +26717,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26776,7 +26779,7 @@
         <v>1705</v>
       </c>
       <c r="W294" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26838,7 +26841,7 @@
         <v>1706</v>
       </c>
       <c r="W295" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26900,7 +26903,7 @@
         <v>1707</v>
       </c>
       <c r="W296" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -26962,13 +26965,13 @@
         <v>1708</v>
       </c>
       <c r="W297" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X297" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="Z297" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27030,7 +27033,7 @@
         <v>1709</v>
       </c>
       <c r="W298" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27092,7 +27095,7 @@
         <v>1710</v>
       </c>
       <c r="W299" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27154,7 +27157,7 @@
         <v>1711</v>
       </c>
       <c r="W300" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27216,7 +27219,7 @@
         <v>1712</v>
       </c>
       <c r="W301" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27278,7 +27281,7 @@
         <v>1713</v>
       </c>
       <c r="W302" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27340,16 +27343,16 @@
         <v>1714</v>
       </c>
       <c r="W303" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X303" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="Y303" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z303" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27411,7 +27414,7 @@
         <v>1715</v>
       </c>
       <c r="W304" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27473,7 +27476,7 @@
         <v>1716</v>
       </c>
       <c r="W305" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27535,7 +27538,7 @@
         <v>1717</v>
       </c>
       <c r="W306" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27597,7 +27600,7 @@
         <v>1718</v>
       </c>
       <c r="W307" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27659,7 +27662,7 @@
         <v>1711</v>
       </c>
       <c r="W308" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27721,7 +27724,7 @@
         <v>1719</v>
       </c>
       <c r="W309" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27783,7 +27786,7 @@
         <v>1720</v>
       </c>
       <c r="W310" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27845,7 +27848,7 @@
         <v>1721</v>
       </c>
       <c r="W311" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27907,7 +27910,7 @@
         <v>1722</v>
       </c>
       <c r="W312" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -27969,7 +27972,7 @@
         <v>1723</v>
       </c>
       <c r="W313" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28031,7 +28034,7 @@
         <v>1724</v>
       </c>
       <c r="W314" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28093,7 +28096,7 @@
         <v>1725</v>
       </c>
       <c r="W315" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28155,7 +28158,7 @@
         <v>1726</v>
       </c>
       <c r="W316" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28217,7 +28220,7 @@
         <v>1727</v>
       </c>
       <c r="W317" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28279,7 +28282,7 @@
         <v>1728</v>
       </c>
       <c r="W318" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28341,7 +28344,7 @@
         <v>1729</v>
       </c>
       <c r="W319" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28400,13 +28403,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X320" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="Z320" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28465,7 +28468,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28524,7 +28527,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28583,7 +28586,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28645,7 +28648,7 @@
         <v>1730</v>
       </c>
       <c r="W324" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28707,7 +28710,7 @@
         <v>1731</v>
       </c>
       <c r="W325" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28769,7 +28772,7 @@
         <v>1732</v>
       </c>
       <c r="W326" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28831,7 +28834,7 @@
         <v>1733</v>
       </c>
       <c r="W327" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28890,7 +28893,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -28952,7 +28955,7 @@
         <v>1733</v>
       </c>
       <c r="W329" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -29014,7 +29017,7 @@
         <v>1734</v>
       </c>
       <c r="W330" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29076,7 +29079,7 @@
         <v>1735</v>
       </c>
       <c r="W331" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29138,7 +29141,7 @@
         <v>1735</v>
       </c>
       <c r="W332" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29200,7 +29203,7 @@
         <v>1736</v>
       </c>
       <c r="W333" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29262,7 +29265,7 @@
         <v>1737</v>
       </c>
       <c r="W334" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29324,7 +29327,7 @@
         <v>1738</v>
       </c>
       <c r="W335" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29383,13 +29386,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X336" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Z336" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29451,7 +29454,7 @@
         <v>1739</v>
       </c>
       <c r="W337" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29513,13 +29516,13 @@
         <v>1740</v>
       </c>
       <c r="W338" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X338" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="Z338" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29581,13 +29584,13 @@
         <v>1741</v>
       </c>
       <c r="W339" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X339" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Z339" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29649,7 +29652,7 @@
         <v>1742</v>
       </c>
       <c r="W340" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29711,7 +29714,7 @@
         <v>1743</v>
       </c>
       <c r="W341" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29773,10 +29776,10 @@
         <v>1744</v>
       </c>
       <c r="W342" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X342" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29838,7 +29841,7 @@
         <v>1745</v>
       </c>
       <c r="W343" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29900,7 +29903,7 @@
         <v>1746</v>
       </c>
       <c r="W344" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -29962,13 +29965,13 @@
         <v>1747</v>
       </c>
       <c r="W345" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X345" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="Z345" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30030,7 +30033,7 @@
         <v>1711</v>
       </c>
       <c r="W346" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30092,7 +30095,7 @@
         <v>1748</v>
       </c>
       <c r="W347" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30154,16 +30157,16 @@
         <v>1749</v>
       </c>
       <c r="W348" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X348" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="Y348" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z348" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30228,13 +30231,13 @@
         <v>1750</v>
       </c>
       <c r="W349" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X349" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="Z349" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30296,7 +30299,7 @@
         <v>1751</v>
       </c>
       <c r="W350" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30358,16 +30361,16 @@
         <v>1752</v>
       </c>
       <c r="W351" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X351" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="Y351" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z351" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30429,13 +30432,13 @@
         <v>1753</v>
       </c>
       <c r="W352" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X352" t="s">
         <v>1753</v>
       </c>
       <c r="Z352" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30497,16 +30500,16 @@
         <v>1754</v>
       </c>
       <c r="W353" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X353" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="Y353" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z353" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30568,7 +30571,7 @@
         <v>1755</v>
       </c>
       <c r="W354" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30630,7 +30633,7 @@
         <v>1756</v>
       </c>
       <c r="W355" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30689,7 +30692,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30748,7 +30751,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30807,7 +30810,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30869,7 +30872,7 @@
         <v>1757</v>
       </c>
       <c r="W359" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30934,7 +30937,7 @@
         <v>1758</v>
       </c>
       <c r="W360" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -30999,7 +31002,7 @@
         <v>1759</v>
       </c>
       <c r="W361" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31061,16 +31064,16 @@
         <v>1760</v>
       </c>
       <c r="W362" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X362" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="Y362" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z362" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31132,16 +31135,16 @@
         <v>1761</v>
       </c>
       <c r="W363" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X363" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="Y363" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z363" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31203,7 +31206,7 @@
         <v>1762</v>
       </c>
       <c r="W364" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31265,7 +31268,7 @@
         <v>1763</v>
       </c>
       <c r="W365" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31330,7 +31333,7 @@
         <v>1764</v>
       </c>
       <c r="W366" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31392,7 +31395,7 @@
         <v>1765</v>
       </c>
       <c r="W367" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31454,7 +31457,7 @@
         <v>1766</v>
       </c>
       <c r="W368" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31519,13 +31522,13 @@
         <v>1767</v>
       </c>
       <c r="W369" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X369" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z369" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31587,7 +31590,7 @@
         <v>1768</v>
       </c>
       <c r="W370" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31649,16 +31652,16 @@
         <v>1769</v>
       </c>
       <c r="W371" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X371" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="Y371" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z371" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31723,7 +31726,7 @@
         <v>1770</v>
       </c>
       <c r="W372" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31788,16 +31791,16 @@
         <v>1771</v>
       </c>
       <c r="W373" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X373" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="Y373" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z373" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31859,7 +31862,7 @@
         <v>1772</v>
       </c>
       <c r="W374" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31924,7 +31927,7 @@
         <v>1773</v>
       </c>
       <c r="W375" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -31989,7 +31992,7 @@
         <v>1774</v>
       </c>
       <c r="W376" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32054,7 +32057,7 @@
         <v>1774</v>
       </c>
       <c r="W377" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32119,13 +32122,13 @@
         <v>1775</v>
       </c>
       <c r="W378" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X378" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Z378" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32187,16 +32190,16 @@
         <v>1776</v>
       </c>
       <c r="W379" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X379" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="Y379" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z379" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32261,7 +32264,7 @@
         <v>1777</v>
       </c>
       <c r="W380" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32323,7 +32326,7 @@
         <v>1778</v>
       </c>
       <c r="W381" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32388,7 +32391,7 @@
         <v>1779</v>
       </c>
       <c r="W382" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32450,7 +32453,7 @@
         <v>1780</v>
       </c>
       <c r="W383" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32515,7 +32518,7 @@
         <v>1779</v>
       </c>
       <c r="W384" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32577,16 +32580,16 @@
         <v>1781</v>
       </c>
       <c r="W385" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X385" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="Y385" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z385" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32654,7 +32657,7 @@
         <v>1782</v>
       </c>
       <c r="W386" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32716,7 +32719,7 @@
         <v>1783</v>
       </c>
       <c r="W387" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32778,7 +32781,7 @@
         <v>1784</v>
       </c>
       <c r="W388" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32840,16 +32843,16 @@
         <v>1785</v>
       </c>
       <c r="W389" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X389" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="Y389" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z389" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32914,16 +32917,16 @@
         <v>1786</v>
       </c>
       <c r="W390" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X390" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="Y390" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z390" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -32988,7 +32991,7 @@
         <v>1787</v>
       </c>
       <c r="W391" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33050,7 +33053,7 @@
         <v>1788</v>
       </c>
       <c r="W392" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33112,16 +33115,16 @@
         <v>1789</v>
       </c>
       <c r="W393" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X393" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="Y393" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z393" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33183,7 +33186,7 @@
         <v>1790</v>
       </c>
       <c r="W394" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33248,16 +33251,16 @@
         <v>1791</v>
       </c>
       <c r="W395" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X395" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="Y395" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z395" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33322,13 +33325,13 @@
         <v>1792</v>
       </c>
       <c r="W396" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X396" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Y396" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33390,7 +33393,7 @@
         <v>1793</v>
       </c>
       <c r="W397" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33452,7 +33455,7 @@
         <v>1794</v>
       </c>
       <c r="W398" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33517,7 +33520,7 @@
         <v>1795</v>
       </c>
       <c r="W399" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33582,16 +33585,16 @@
         <v>1796</v>
       </c>
       <c r="W400" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X400" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="Y400" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z400" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33656,7 +33659,7 @@
         <v>1797</v>
       </c>
       <c r="W401" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33721,7 +33724,7 @@
         <v>1798</v>
       </c>
       <c r="W402" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33786,16 +33789,16 @@
         <v>1799</v>
       </c>
       <c r="W403" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X403" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="Y403" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z403" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33860,7 +33863,7 @@
         <v>1800</v>
       </c>
       <c r="W404" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33925,7 +33928,7 @@
         <v>1801</v>
       </c>
       <c r="W405" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -33990,7 +33993,7 @@
         <v>1802</v>
       </c>
       <c r="W406" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34052,16 +34055,16 @@
         <v>1803</v>
       </c>
       <c r="W407" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X407" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="Y407" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z407" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34126,13 +34129,13 @@
         <v>1804</v>
       </c>
       <c r="W408" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X408" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="Z408" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34197,7 +34200,7 @@
         <v>1805</v>
       </c>
       <c r="W409" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34262,7 +34265,7 @@
         <v>1806</v>
       </c>
       <c r="W410" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34327,7 +34330,7 @@
         <v>1807</v>
       </c>
       <c r="W411" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34392,7 +34395,7 @@
         <v>1808</v>
       </c>
       <c r="W412" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34457,7 +34460,7 @@
         <v>1809</v>
       </c>
       <c r="W413" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34522,7 +34525,7 @@
         <v>1809</v>
       </c>
       <c r="W414" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34587,7 +34590,7 @@
         <v>1810</v>
       </c>
       <c r="W415" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34652,7 +34655,7 @@
         <v>1811</v>
       </c>
       <c r="W416" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34717,7 +34720,7 @@
         <v>1809</v>
       </c>
       <c r="W417" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34782,7 +34785,7 @@
         <v>1812</v>
       </c>
       <c r="W418" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34847,7 +34850,7 @@
         <v>1813</v>
       </c>
       <c r="W419" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34912,16 +34915,16 @@
         <v>1814</v>
       </c>
       <c r="W420" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X420" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="Y420" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z420" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -34986,7 +34989,7 @@
         <v>1815</v>
       </c>
       <c r="W421" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35051,7 +35054,7 @@
         <v>1816</v>
       </c>
       <c r="W422" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35116,7 +35119,7 @@
         <v>1817</v>
       </c>
       <c r="W423" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35181,16 +35184,16 @@
         <v>1818</v>
       </c>
       <c r="W424" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X424" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="Y424" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z424" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35255,7 +35258,7 @@
         <v>1817</v>
       </c>
       <c r="W425" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35320,7 +35323,7 @@
         <v>1819</v>
       </c>
       <c r="W426" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35385,7 +35388,7 @@
         <v>1820</v>
       </c>
       <c r="W427" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35450,13 +35453,13 @@
         <v>1821</v>
       </c>
       <c r="W428" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X428" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="Y428" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35521,16 +35524,16 @@
         <v>1822</v>
       </c>
       <c r="W429" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X429" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="Y429" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z429" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35595,7 +35598,7 @@
         <v>1823</v>
       </c>
       <c r="W430" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35660,16 +35663,16 @@
         <v>1824</v>
       </c>
       <c r="W431" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X431" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="Y431" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z431" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35734,7 +35737,7 @@
         <v>1825</v>
       </c>
       <c r="W432" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35799,7 +35802,7 @@
         <v>1826</v>
       </c>
       <c r="W433" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35864,7 +35867,7 @@
         <v>1827</v>
       </c>
       <c r="W434" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35929,7 +35932,7 @@
         <v>1828</v>
       </c>
       <c r="W435" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -35994,7 +35997,7 @@
         <v>1829</v>
       </c>
       <c r="W436" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36059,7 +36062,7 @@
         <v>1830</v>
       </c>
       <c r="W437" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36124,7 +36127,7 @@
         <v>1831</v>
       </c>
       <c r="W438" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36189,7 +36192,7 @@
         <v>1832</v>
       </c>
       <c r="W439" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36254,16 +36257,16 @@
         <v>1833</v>
       </c>
       <c r="W440" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X440" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="Y440" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z440" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36328,16 +36331,16 @@
         <v>1834</v>
       </c>
       <c r="W441" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X441" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Y441" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z441" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36402,16 +36405,16 @@
         <v>1835</v>
       </c>
       <c r="W442" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X442" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="Y442" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z442" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36476,7 +36479,7 @@
         <v>1836</v>
       </c>
       <c r="W443" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36541,7 +36544,7 @@
         <v>1837</v>
       </c>
       <c r="W444" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36606,16 +36609,16 @@
         <v>1834</v>
       </c>
       <c r="W445" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X445" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Y445" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z445" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36680,16 +36683,16 @@
         <v>1834</v>
       </c>
       <c r="W446" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X446" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Y446" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z446" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36754,16 +36757,16 @@
         <v>1838</v>
       </c>
       <c r="W447" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X447" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="Y447" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z447" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36828,16 +36831,16 @@
         <v>1834</v>
       </c>
       <c r="W448" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X448" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Y448" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z448" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36902,16 +36905,16 @@
         <v>1834</v>
       </c>
       <c r="W449" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X449" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Y449" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z449" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -36976,16 +36979,16 @@
         <v>1839</v>
       </c>
       <c r="W450" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X450" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="Y450" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z450" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37050,16 +37053,16 @@
         <v>1840</v>
       </c>
       <c r="W451" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X451" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="Y451" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z451" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37124,7 +37127,7 @@
         <v>1841</v>
       </c>
       <c r="W452" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37189,16 +37192,16 @@
         <v>1842</v>
       </c>
       <c r="W453" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X453" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="Y453" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z453" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37263,16 +37266,16 @@
         <v>1843</v>
       </c>
       <c r="W454" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X454" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="Y454" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z454" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37337,16 +37340,16 @@
         <v>1844</v>
       </c>
       <c r="W455" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X455" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="Y455" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z455" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37411,16 +37414,16 @@
         <v>1845</v>
       </c>
       <c r="W456" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X456" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="Y456" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z456" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37485,7 +37488,7 @@
         <v>1846</v>
       </c>
       <c r="W457" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37550,7 +37553,7 @@
         <v>1846</v>
       </c>
       <c r="W458" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37615,16 +37618,16 @@
         <v>1844</v>
       </c>
       <c r="W459" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X459" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="Y459" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z459" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37689,16 +37692,16 @@
         <v>1847</v>
       </c>
       <c r="W460" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X460" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="Y460" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z460" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37763,16 +37766,16 @@
         <v>1848</v>
       </c>
       <c r="W461" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X461" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="Y461" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z461" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37837,7 +37840,7 @@
         <v>1849</v>
       </c>
       <c r="W462" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37902,16 +37905,16 @@
         <v>1850</v>
       </c>
       <c r="W463" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X463" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="Y463" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z463" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -37976,16 +37979,16 @@
         <v>1851</v>
       </c>
       <c r="W464" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X464" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="Y464" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z464" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38050,16 +38053,16 @@
         <v>1852</v>
       </c>
       <c r="W465" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X465" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="Y465" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z465" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38124,7 +38127,7 @@
         <v>1853</v>
       </c>
       <c r="W466" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38189,16 +38192,16 @@
         <v>1854</v>
       </c>
       <c r="W467" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X467" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="Y467" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z467" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38263,16 +38266,16 @@
         <v>1855</v>
       </c>
       <c r="W468" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X468" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="Y468" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z468" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38337,16 +38340,16 @@
         <v>1856</v>
       </c>
       <c r="W469" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X469" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="Y469" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z469" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38411,16 +38414,16 @@
         <v>1857</v>
       </c>
       <c r="W470" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X470" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="Y470" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z470" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38485,7 +38488,7 @@
         <v>1858</v>
       </c>
       <c r="W471" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38550,16 +38553,16 @@
         <v>1859</v>
       </c>
       <c r="W472" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X472" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="Y472" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z472" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38624,16 +38627,16 @@
         <v>1859</v>
       </c>
       <c r="W473" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X473" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="Y473" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z473" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38698,7 +38701,7 @@
         <v>1860</v>
       </c>
       <c r="W474" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38763,16 +38766,16 @@
         <v>1861</v>
       </c>
       <c r="W475" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X475" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="Y475" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z475" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38837,16 +38840,16 @@
         <v>1862</v>
       </c>
       <c r="W476" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X476" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="Y476" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z476" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38911,7 +38914,7 @@
         <v>1863</v>
       </c>
       <c r="W477" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -38976,7 +38979,7 @@
         <v>1864</v>
       </c>
       <c r="W478" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39041,16 +39044,16 @@
         <v>1865</v>
       </c>
       <c r="W479" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X479" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="Y479" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z479" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39115,16 +39118,16 @@
         <v>1866</v>
       </c>
       <c r="W480" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X480" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="Y480" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z480" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39189,16 +39192,16 @@
         <v>1867</v>
       </c>
       <c r="W481" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X481" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="Y481" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z481" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39263,7 +39266,7 @@
         <v>1868</v>
       </c>
       <c r="W482" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39328,7 +39331,7 @@
         <v>1869</v>
       </c>
       <c r="W483" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39396,13 +39399,13 @@
         <v>1870</v>
       </c>
       <c r="W484" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39467,7 +39470,7 @@
         <v>1871</v>
       </c>
       <c r="W485" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39535,13 +39538,13 @@
         <v>1872</v>
       </c>
       <c r="W486" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39606,7 +39609,7 @@
         <v>1873</v>
       </c>
       <c r="W487" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39671,16 +39674,16 @@
         <v>1874</v>
       </c>
       <c r="W488" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X488" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="Y488" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z488" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39745,7 +39748,7 @@
         <v>1875</v>
       </c>
       <c r="W489" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39813,13 +39816,13 @@
         <v>1876</v>
       </c>
       <c r="W490" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39884,16 +39887,16 @@
         <v>1877</v>
       </c>
       <c r="W491" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X491" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="Y491" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z491" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -39958,16 +39961,16 @@
         <v>1878</v>
       </c>
       <c r="W492" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X492" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="Y492" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z492" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40032,16 +40035,16 @@
         <v>1879</v>
       </c>
       <c r="W493" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X493" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="Y493" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z493" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40106,13 +40109,13 @@
         <v>1880</v>
       </c>
       <c r="W494" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X494" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="Y494" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40177,16 +40180,16 @@
         <v>1881</v>
       </c>
       <c r="W495" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X495" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="Y495" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z495" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40251,7 +40254,7 @@
         <v>1882</v>
       </c>
       <c r="W496" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40319,7 +40322,7 @@
         <v>1883</v>
       </c>
       <c r="W497" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40384,7 +40387,7 @@
         <v>1884</v>
       </c>
       <c r="W498" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40452,7 +40455,7 @@
         <v>1885</v>
       </c>
       <c r="W499" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40517,16 +40520,16 @@
         <v>1886</v>
       </c>
       <c r="W500" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X500" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="Y500" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z500" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40591,16 +40594,16 @@
         <v>1887</v>
       </c>
       <c r="W501" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X501" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="Y501" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z501" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40665,7 +40668,7 @@
         <v>1888</v>
       </c>
       <c r="W502" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40733,7 +40736,7 @@
         <v>1889</v>
       </c>
       <c r="W503" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40801,16 +40804,16 @@
         <v>1890</v>
       </c>
       <c r="W504" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X504" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="Y504" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z504" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40875,7 +40878,7 @@
         <v>1891</v>
       </c>
       <c r="W505" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40940,16 +40943,16 @@
         <v>1892</v>
       </c>
       <c r="W506" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X506" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="Y506" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z506" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -41014,7 +41017,7 @@
         <v>1893</v>
       </c>
       <c r="W507" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41079,7 +41082,7 @@
         <v>1894</v>
       </c>
       <c r="W508" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41144,16 +41147,16 @@
         <v>1895</v>
       </c>
       <c r="W509" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X509" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="Y509" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z509" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41218,16 +41221,16 @@
         <v>1896</v>
       </c>
       <c r="W510" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X510" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="Y510" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z510" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41295,7 +41298,7 @@
         <v>1897</v>
       </c>
       <c r="W511" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41363,7 +41366,7 @@
         <v>1898</v>
       </c>
       <c r="W512" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41431,7 +41434,7 @@
         <v>1899</v>
       </c>
       <c r="W513" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41499,7 +41502,7 @@
         <v>1899</v>
       </c>
       <c r="W514" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41567,7 +41570,7 @@
         <v>1899</v>
       </c>
       <c r="W515" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41635,13 +41638,13 @@
         <v>1900</v>
       </c>
       <c r="W516" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41709,13 +41712,13 @@
         <v>1901</v>
       </c>
       <c r="W517" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41783,16 +41786,16 @@
         <v>1902</v>
       </c>
       <c r="W518" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X518" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="Y518" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z518" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41860,16 +41863,16 @@
         <v>1903</v>
       </c>
       <c r="W519" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X519" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="Y519" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z519" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41934,7 +41937,7 @@
         <v>1506</v>
       </c>
       <c r="W520" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -42002,7 +42005,7 @@
         <v>1904</v>
       </c>
       <c r="W521" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42070,7 +42073,7 @@
         <v>1904</v>
       </c>
       <c r="W522" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42138,7 +42141,7 @@
         <v>1905</v>
       </c>
       <c r="W523" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42206,7 +42209,7 @@
         <v>1906</v>
       </c>
       <c r="W524" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42274,7 +42277,7 @@
         <v>1907</v>
       </c>
       <c r="W525" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42342,7 +42345,7 @@
         <v>1908</v>
       </c>
       <c r="W526" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42410,7 +42413,7 @@
         <v>1909</v>
       </c>
       <c r="W527" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42475,7 +42478,7 @@
         <v>1910</v>
       </c>
       <c r="W528" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42543,7 +42546,7 @@
         <v>1911</v>
       </c>
       <c r="W529" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42611,16 +42614,16 @@
         <v>1912</v>
       </c>
       <c r="W530" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X530" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="Y530" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z530" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42688,7 +42691,7 @@
         <v>1913</v>
       </c>
       <c r="W531" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42753,7 +42756,7 @@
         <v>1914</v>
       </c>
       <c r="W532" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42821,16 +42824,16 @@
         <v>1915</v>
       </c>
       <c r="W533" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X533" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="Y533" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z533" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42898,13 +42901,13 @@
         <v>1916</v>
       </c>
       <c r="W534" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -42972,7 +42975,7 @@
         <v>1917</v>
       </c>
       <c r="W535" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43040,7 +43043,7 @@
         <v>1918</v>
       </c>
       <c r="W536" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43108,16 +43111,16 @@
         <v>1919</v>
       </c>
       <c r="W537" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X537" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="Y537" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z537" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43185,7 +43188,7 @@
         <v>1920</v>
       </c>
       <c r="W538" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43253,7 +43256,7 @@
         <v>1921</v>
       </c>
       <c r="W539" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43321,7 +43324,7 @@
         <v>1922</v>
       </c>
       <c r="W540" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43389,7 +43392,7 @@
         <v>1923</v>
       </c>
       <c r="W541" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43457,16 +43460,16 @@
         <v>1924</v>
       </c>
       <c r="W542" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X542" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="Y542" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z542" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43534,7 +43537,7 @@
         <v>1925</v>
       </c>
       <c r="W543" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43602,16 +43605,16 @@
         <v>1926</v>
       </c>
       <c r="W544" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="X544" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="Y544" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Z544" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43679,7 +43682,7 @@
         <v>1927</v>
       </c>
       <c r="W545" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43747,7 +43750,7 @@
         <v>1928</v>
       </c>
       <c r="W546" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43815,7 +43818,7 @@
         <v>1929</v>
       </c>
       <c r="W547" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43883,7 +43886,7 @@
         <v>1930</v>
       </c>
       <c r="W548" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -43951,7 +43954,7 @@
         <v>1930</v>
       </c>
       <c r="W549" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44019,7 +44022,7 @@
         <v>1931</v>
       </c>
       <c r="W550" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44084,7 +44087,7 @@
         <v>1932</v>
       </c>
       <c r="W551" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44152,7 +44155,7 @@
         <v>1933</v>
       </c>
       <c r="W552" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44217,7 +44220,7 @@
         <v>1934</v>
       </c>
       <c r="W553" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44285,7 +44288,7 @@
         <v>1935</v>
       </c>
       <c r="W554" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44353,7 +44356,7 @@
         <v>1936</v>
       </c>
       <c r="W555" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44421,7 +44424,7 @@
         <v>1937</v>
       </c>
       <c r="W556" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44486,7 +44489,7 @@
         <v>1938</v>
       </c>
       <c r="W557" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44554,7 +44557,7 @@
         <v>1939</v>
       </c>
       <c r="W558" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44622,7 +44625,7 @@
         <v>1940</v>
       </c>
       <c r="W559" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44687,7 +44690,7 @@
         <v>1941</v>
       </c>
       <c r="W560" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44755,7 +44758,7 @@
         <v>1942</v>
       </c>
       <c r="W561" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44820,10 +44823,10 @@
         <v>1504</v>
       </c>
       <c r="V562" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="W562" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44888,7 +44891,7 @@
         <v>1943</v>
       </c>
       <c r="W563" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -44953,7 +44956,7 @@
         <v>1944</v>
       </c>
       <c r="W564" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45021,7 +45024,7 @@
         <v>1945</v>
       </c>
       <c r="W565" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45089,7 +45092,7 @@
         <v>1946</v>
       </c>
       <c r="W566" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45157,7 +45160,7 @@
         <v>1947</v>
       </c>
       <c r="W567" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45225,10 +45228,10 @@
         <v>1948</v>
       </c>
       <c r="V568" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="W568" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA568" t="b">
         <v>1</v>
@@ -45296,7 +45299,7 @@
         <v>1949</v>
       </c>
       <c r="W569" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45361,7 +45364,7 @@
         <v>1950</v>
       </c>
       <c r="W570" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45426,7 +45429,7 @@
         <v>1951</v>
       </c>
       <c r="W571" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45494,7 +45497,7 @@
         <v>1952</v>
       </c>
       <c r="W572" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45562,7 +45565,7 @@
         <v>1953</v>
       </c>
       <c r="W573" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45630,7 +45633,7 @@
         <v>1954</v>
       </c>
       <c r="W574" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45698,7 +45701,7 @@
         <v>1955</v>
       </c>
       <c r="W575" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -45766,7 +45769,7 @@
         <v>1956</v>
       </c>
       <c r="W576" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45834,7 +45837,7 @@
         <v>1956</v>
       </c>
       <c r="W577" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45902,7 +45905,7 @@
         <v>1957</v>
       </c>
       <c r="W578" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -45970,7 +45973,7 @@
         <v>1958</v>
       </c>
       <c r="W579" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46038,7 +46041,7 @@
         <v>1959</v>
       </c>
       <c r="W580" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46106,7 +46109,7 @@
         <v>1960</v>
       </c>
       <c r="W581" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46174,10 +46177,10 @@
         <v>1961</v>
       </c>
       <c r="V582" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="W582" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA582" t="b">
         <v>1</v>
@@ -46242,10 +46245,10 @@
         <v>1504</v>
       </c>
       <c r="V583" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="W583" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA583" t="b">
         <v>1</v>
@@ -46313,7 +46316,7 @@
         <v>1962</v>
       </c>
       <c r="W584" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46381,7 +46384,7 @@
         <v>1962</v>
       </c>
       <c r="W585" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46446,10 +46449,10 @@
         <v>1504</v>
       </c>
       <c r="V586" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="W586" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46508,10 +46511,10 @@
         <v>1503</v>
       </c>
       <c r="V587" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="W587" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA587" t="b">
         <v>1</v>
@@ -46579,10 +46582,10 @@
         <v>1963</v>
       </c>
       <c r="V588" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="W588" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46650,10 +46653,10 @@
         <v>1964</v>
       </c>
       <c r="V589" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="W589" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA589" t="b">
         <v>1</v>
@@ -46718,7 +46721,7 @@
         <v>1965</v>
       </c>
       <c r="W590" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA590" t="b">
         <v>0</v>
@@ -46783,10 +46786,10 @@
         <v>1503</v>
       </c>
       <c r="V591" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="W591" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA591" t="b">
         <v>1</v>
@@ -46854,10 +46857,10 @@
         <v>1966</v>
       </c>
       <c r="V592" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="W592" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA592" t="b">
         <v>1</v>
@@ -46925,10 +46928,10 @@
         <v>1967</v>
       </c>
       <c r="V593" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="W593" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA593" t="b">
         <v>1</v>
@@ -46993,10 +46996,10 @@
         <v>1966</v>
       </c>
       <c r="V594" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="W594" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA594" t="b">
         <v>1</v>
@@ -47058,7 +47061,7 @@
         <v>1503</v>
       </c>
       <c r="W595" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA595" t="b">
         <v>1</v>
@@ -47123,7 +47126,7 @@
         <v>1968</v>
       </c>
       <c r="W596" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA596" t="b">
         <v>1</v>
@@ -47179,13 +47182,16 @@
         <v>3</v>
       </c>
       <c r="S597" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="T597" t="s">
         <v>1504</v>
       </c>
+      <c r="U597" t="s">
+        <v>1969</v>
+      </c>
       <c r="W597" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA597" t="b">
         <v>1</v>
@@ -47250,10 +47256,10 @@
         <v>1504</v>
       </c>
       <c r="U598" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="W598" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AA598" t="b">
         <v>0</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44811,10 +44811,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R562">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S562" t="s">
         <v>1503</v>
@@ -45213,10 +45213,10 @@
         <v>46249</v>
       </c>
       <c r="Q568">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R568">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S568" t="s">
         <v>1503</v>
@@ -46162,10 +46162,10 @@
         <v>46240</v>
       </c>
       <c r="Q582">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="R582">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S582" t="s">
         <v>1503</v>
@@ -46233,10 +46233,10 @@
         <v>46265</v>
       </c>
       <c r="Q583">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="R583">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S583" t="s">
         <v>1503</v>
@@ -46437,10 +46437,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="R586">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S586" t="s">
         <v>1503</v>
@@ -46502,10 +46502,10 @@
         <v>46248</v>
       </c>
       <c r="Q587">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R587">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S587" t="s">
         <v>1503</v>
@@ -46567,10 +46567,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="R588">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S588" t="s">
         <v>1504</v>
@@ -46638,10 +46638,10 @@
         <v>46254</v>
       </c>
       <c r="Q589">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R589">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S589" t="s">
         <v>1504</v>
@@ -46774,10 +46774,10 @@
         <v>46257</v>
       </c>
       <c r="Q591">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R591">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S591" t="s">
         <v>1503</v>
@@ -46842,10 +46842,10 @@
         <v>46254</v>
       </c>
       <c r="Q592">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R592">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S592" t="s">
         <v>1503</v>
@@ -46913,10 +46913,10 @@
         <v>46254</v>
       </c>
       <c r="Q593">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R593">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S593" t="s">
         <v>1504</v>
@@ -46981,10 +46981,10 @@
         <v>46278</v>
       </c>
       <c r="Q594">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R594">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S594" t="s">
         <v>1503</v>
@@ -47049,10 +47049,10 @@
         <v>46279</v>
       </c>
       <c r="Q595">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="R595">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S595" t="s">
         <v>1504</v>
@@ -47111,10 +47111,10 @@
         <v>46259</v>
       </c>
       <c r="Q596">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="R596">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S596" t="s">
         <v>1504</v>
@@ -47176,10 +47176,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="R597">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S597" t="s">
         <v>1504</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44841,10 +44841,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R562">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S562" t="s">
         <v>1507</v>
@@ -46479,10 +46479,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="R586">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S586" t="s">
         <v>1507</v>
@@ -46615,10 +46615,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R588">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S588" t="s">
         <v>1508</v>
@@ -46686,10 +46686,10 @@
         <v>46254</v>
       </c>
       <c r="Q589">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R589">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S589" t="s">
         <v>1508</v>
@@ -46822,10 +46822,10 @@
         <v>46251</v>
       </c>
       <c r="Q591">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R591">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S591" t="s">
         <v>1507</v>
@@ -46964,10 +46964,10 @@
         <v>46254</v>
       </c>
       <c r="Q593">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R593">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S593" t="s">
         <v>1508</v>
@@ -47103,10 +47103,10 @@
         <v>46279</v>
       </c>
       <c r="Q595">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R595">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S595" t="s">
         <v>1508</v>
@@ -47168,10 +47168,10 @@
         <v>46259</v>
       </c>
       <c r="Q596">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R596">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S596" t="s">
         <v>1508</v>
@@ -47236,10 +47236,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R597">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S597" t="s">
         <v>1508</v>
@@ -47372,10 +47372,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="R599">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S599" t="s">
         <v>1507</v>
@@ -47434,10 +47434,10 @@
         <v>46282</v>
       </c>
       <c r="Q600">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R600">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S600" t="s">
         <v>1507</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44856,10 +44856,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R562">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S562" t="s">
         <v>1512</v>
@@ -46488,10 +46488,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="R586">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S586" t="s">
         <v>1512</v>
@@ -46621,10 +46621,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R588">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S588" t="s">
         <v>1513</v>
@@ -46692,10 +46692,10 @@
         <v>46254</v>
       </c>
       <c r="Q589">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R589">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S589" t="s">
         <v>1513</v>
@@ -46973,10 +46973,10 @@
         <v>46254</v>
       </c>
       <c r="Q593">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R593">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S593" t="s">
         <v>1513</v>
@@ -47112,10 +47112,10 @@
         <v>46279</v>
       </c>
       <c r="Q595">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R595">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S595" t="s">
         <v>1513</v>
@@ -47177,10 +47177,10 @@
         <v>46259</v>
       </c>
       <c r="Q596">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R596">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S596" t="s">
         <v>1513</v>
@@ -47245,10 +47245,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R597">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S597" t="s">
         <v>1513</v>
@@ -47381,10 +47381,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R599">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S599" t="s">
         <v>1512</v>
@@ -47446,10 +47446,10 @@
         <v>46282</v>
       </c>
       <c r="Q600">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R600">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S600" t="s">
         <v>1512</v>
@@ -47511,10 +47511,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R601">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S601" t="s">
         <v>1512</v>
@@ -47573,10 +47573,10 @@
         <v>46260</v>
       </c>
       <c r="Q602">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R602">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S602" t="s">
         <v>1512</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -47224,7 +47224,7 @@
         <v>2729</v>
       </c>
       <c r="H597" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="I597" t="s">
         <v>1273</v>
@@ -47552,7 +47552,7 @@
         <v>2731</v>
       </c>
       <c r="H602" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="I602" t="s">
         <v>1272</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7570" uniqueCount="2372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7567" uniqueCount="2369">
   <si>
     <t>om_emg</t>
   </si>
@@ -5971,34 +5971,19 @@
     <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08</t>
   </si>
   <si>
-    <t>Enviado para o Operador(02 EA), atendimento parcial, em 31/07/2026 -AWB 127-5041 6833- REZ - o outro 1 EA será atendido pelo estoque FAB. conforme solicitado por Email- CLA-03-08 - AWB 127-5082 1282 -1 EA ENVIADO ESTOQUE FAB - Material entregue dia 06/08/2026</t>
-  </si>
-  <si>
-    <t>Temos 4 EA em manutenção na William, será pedido prioridade. CLA-03-08 - DPE DIA 14-08 - CLA 13-08 - AWB 127-5299 2505 DPE 18/08/2026</t>
-  </si>
-  <si>
     <t>PEDIDO NO EPM E-C98-26060 - CLA-05-08 , por gentileza, me confirme se está correto a data da informação e prazo de entrega do item.O item solicitado não atende a pane do sistema ARCOND,pôs a pane é de 18/11/2024, anterior ao contrato vigente ,desta forma deve ser feito toda analise do sistema ,devido muito tempo inoperante e sem o item. SO R1 Bispo VEE-ONE-BE em 06/08/26</t>
   </si>
   <si>
-    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08- ITEM AGUARDANDO DEFINIÇÃO DA COORDENADORIA QUANTO A EFETIVIDADE PARA APLICAÇÃO NA REFERIDA ANV.- CLA-13-08</t>
-  </si>
-  <si>
-    <t>Temos somente 03 ea em STK, favor utilizar o estoque FAB para posterior devolução. ATZ RC 13/08 - FOI SOLICITADO O ATENDIMENTO COM ESTOQUE FAB -CLA-13-08 - AWB 127-5299 0173 DPE 18/08/2026</t>
-  </si>
-  <si>
-    <t>Previsao de entrega da oficina do RJ na V1 JPA 13/8/2026 durante o dia, horario comercial, ATZ Marcio 12/8 13:22hs - Material entregue dia 17/08/2026 - Retirado pelo TEN Goncalves</t>
-  </si>
-  <si>
-    <t>1 Unidade na oficina em BH William, solicitado prioridade na entrega DPE 14/8, aguardando orçamento final ATZ Marcio 12/8 13:24hs- DPE 14-08 - AWB 127-5299 0604 DPE 15-08-26 CLA-17-08</t>
-  </si>
-  <si>
-    <t>Temos no STK V1, material em separação, recibo 682/FAB/26 - atz rc 13/08 - MATERIAL ENVIADO VIA AWB 12752709016 - DPE 18/08/2026</t>
-  </si>
-  <si>
-    <t>será enviado o pn 9910592-2 do estoque da VeeOne base PAMALS. -CLA -14-08- AWB 127-5299 0604 DPE 15-08-26 CLA-17-08</t>
-  </si>
-  <si>
-    <t>foi solicitoado o atendimento com o estoque FAB. CLA-17-08 - o item PN superado 069-1025-25 não serve na ANV 2721 - temos 4ea na wiliam para reparo, já foi solicitado o DPE.</t>
+    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08- ITEM AGUARDANDO DEFINIÇÃO DA COORDENADORIA QUANTO A EFETIVIDADE PARA APLICAÇÃO NA REFERIDA ANV.- CLA-13-08 - AT 685000002258</t>
+  </si>
+  <si>
+    <t>Temos somente 03 ea em STK, favor utilizar o estoque FAB para posterior devolução. ATZ RC 13/08 - FOI SOLICITADO O ATENDIMENTO COM ESTOQUE FAB -CLA-13-08 - AWB 127-5299 0173 DPE 18/08/2026 - ENTREGUE DIA 18/08/2026</t>
+  </si>
+  <si>
+    <t>Temos no STK V1, material em separação, recibo 682/FAB/26 - atz rc 13/08 - MATERIAL ENVIADO VIA AWB 12752709016 - DPE 18/08/2026 - ENTREGUE DIA 18/08/2026</t>
+  </si>
+  <si>
+    <t>foi solicitoado o atendimento com o estoque FAB. CLA-17-08 - o item PN superado 069-1025-25 não serve na ANV 2721 - temos 4ea na wiliam para reparo, já foi solicitado o DPE - OS 4 ITENS ESTÃO COM PROBLEMAS NO DISPAY. -FOI ENVIADO PARA O WIILIAM MAIS 3 UNS PARA REPARO - AINDA SEM DPE -CLA-20-08</t>
   </si>
   <si>
     <t>Enviado para o Operador dia 17/08/26, AWB 127-5332-5834 - REZ</t>
@@ -6007,10 +5992,16 @@
     <t>ITEM FOI ENTREGUE PARA A FAB VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUECLA-17-08</t>
   </si>
   <si>
-    <t>pedido no EPM E-C98-26061 -CLA-18-08</t>
-  </si>
-  <si>
-    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08</t>
+    <t>pedido no EPM E-C98-26061 -CLA-18-08 - em cotação no mercado. Validar se os alternados PN A-7512-24 ou MS25309-7512 ou M6363/2-2 atendem</t>
+  </si>
+  <si>
+    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08</t>
+  </si>
+  <si>
+    <t>Colocado pedido Textron WB0003128625 - direto para o Brasil</t>
+  </si>
+  <si>
+    <t>Colocado pedido no fornecedor - validando entrega em Miami</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7607,7 +7598,7 @@
         <v>1517</v>
       </c>
       <c r="W2" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7669,16 +7660,16 @@
         <v>1518</v>
       </c>
       <c r="W3" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X3" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="Y3" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z3" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7740,7 +7731,7 @@
         <v>1517</v>
       </c>
       <c r="W4" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7802,7 +7793,7 @@
         <v>1519</v>
       </c>
       <c r="W5" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7864,7 +7855,7 @@
         <v>1520</v>
       </c>
       <c r="W6" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7926,7 +7917,7 @@
         <v>1521</v>
       </c>
       <c r="W7" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7988,7 +7979,7 @@
         <v>1522</v>
       </c>
       <c r="W8" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -8050,7 +8041,7 @@
         <v>1523</v>
       </c>
       <c r="W9" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8112,7 +8103,7 @@
         <v>1524</v>
       </c>
       <c r="W10" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8174,7 +8165,7 @@
         <v>1525</v>
       </c>
       <c r="W11" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8236,7 +8227,7 @@
         <v>1526</v>
       </c>
       <c r="W12" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8298,7 +8289,7 @@
         <v>1522</v>
       </c>
       <c r="W13" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8360,16 +8351,16 @@
         <v>1527</v>
       </c>
       <c r="W14" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X14" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="Y14" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z14" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8428,7 +8419,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8493,7 +8484,7 @@
         <v>1528</v>
       </c>
       <c r="W16" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8555,7 +8546,7 @@
         <v>1529</v>
       </c>
       <c r="W17" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8617,7 +8608,7 @@
         <v>1520</v>
       </c>
       <c r="W18" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8679,7 +8670,7 @@
         <v>1520</v>
       </c>
       <c r="W19" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8741,7 +8732,7 @@
         <v>1530</v>
       </c>
       <c r="W20" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8803,7 +8794,7 @@
         <v>1531</v>
       </c>
       <c r="W21" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8865,7 +8856,7 @@
         <v>1531</v>
       </c>
       <c r="W22" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8927,7 +8918,7 @@
         <v>1532</v>
       </c>
       <c r="W23" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8986,7 +8977,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -9045,7 +9036,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9107,7 +9098,7 @@
         <v>1520</v>
       </c>
       <c r="W26" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9166,7 +9157,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9225,7 +9216,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9287,7 +9278,7 @@
         <v>1533</v>
       </c>
       <c r="W29" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9346,7 +9337,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9408,7 +9399,7 @@
         <v>1534</v>
       </c>
       <c r="W31" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9470,7 +9461,7 @@
         <v>1535</v>
       </c>
       <c r="W32" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9532,7 +9523,7 @@
         <v>1536</v>
       </c>
       <c r="W33" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9594,7 +9585,7 @@
         <v>1537</v>
       </c>
       <c r="W34" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9656,7 +9647,7 @@
         <v>1538</v>
       </c>
       <c r="W35" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9718,7 +9709,7 @@
         <v>1534</v>
       </c>
       <c r="W36" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9780,7 +9771,7 @@
         <v>1539</v>
       </c>
       <c r="W37" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9842,7 +9833,7 @@
         <v>1517</v>
       </c>
       <c r="W38" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9904,7 +9895,7 @@
         <v>1536</v>
       </c>
       <c r="W39" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9966,7 +9957,7 @@
         <v>1540</v>
       </c>
       <c r="W40" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -10028,7 +10019,7 @@
         <v>1541</v>
       </c>
       <c r="W41" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10090,16 +10081,16 @@
         <v>1542</v>
       </c>
       <c r="W42" t="s">
+        <v>1996</v>
+      </c>
+      <c r="X42" t="s">
         <v>1999</v>
       </c>
-      <c r="X42" t="s">
-        <v>2002</v>
-      </c>
       <c r="Y42" t="s">
+        <v>2155</v>
+      </c>
+      <c r="Z42" t="s">
         <v>2158</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>2161</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10161,7 +10152,7 @@
         <v>1536</v>
       </c>
       <c r="W43" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10223,7 +10214,7 @@
         <v>1543</v>
       </c>
       <c r="W44" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10285,7 +10276,7 @@
         <v>1536</v>
       </c>
       <c r="W45" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10347,7 +10338,7 @@
         <v>1536</v>
       </c>
       <c r="W46" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10409,7 +10400,7 @@
         <v>1544</v>
       </c>
       <c r="W47" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10471,7 +10462,7 @@
         <v>1545</v>
       </c>
       <c r="W48" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10533,7 +10524,7 @@
         <v>1546</v>
       </c>
       <c r="W49" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10595,7 +10586,7 @@
         <v>1547</v>
       </c>
       <c r="W50" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10657,7 +10648,7 @@
         <v>1548</v>
       </c>
       <c r="W51" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10719,7 +10710,7 @@
         <v>1537</v>
       </c>
       <c r="W52" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10781,7 +10772,7 @@
         <v>1531</v>
       </c>
       <c r="W53" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10843,7 +10834,7 @@
         <v>1531</v>
       </c>
       <c r="W54" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10905,7 +10896,7 @@
         <v>1531</v>
       </c>
       <c r="W55" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10967,7 +10958,7 @@
         <v>1549</v>
       </c>
       <c r="W56" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -11029,7 +11020,7 @@
         <v>1550</v>
       </c>
       <c r="W57" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11091,16 +11082,16 @@
         <v>1551</v>
       </c>
       <c r="W58" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X58" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="Y58" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z58" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11162,7 +11153,7 @@
         <v>1552</v>
       </c>
       <c r="W59" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11224,7 +11215,7 @@
         <v>1553</v>
       </c>
       <c r="W60" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11286,7 +11277,7 @@
         <v>1531</v>
       </c>
       <c r="W61" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11348,7 +11339,7 @@
         <v>1554</v>
       </c>
       <c r="W62" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11407,7 +11398,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11466,7 +11457,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11525,7 +11516,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11584,7 +11575,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11643,7 +11634,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11702,7 +11693,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11764,7 +11755,7 @@
         <v>1555</v>
       </c>
       <c r="W69" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11826,7 +11817,7 @@
         <v>1553</v>
       </c>
       <c r="W70" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11888,7 +11879,7 @@
         <v>1538</v>
       </c>
       <c r="W71" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11950,7 +11941,7 @@
         <v>1556</v>
       </c>
       <c r="W72" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -12012,7 +12003,7 @@
         <v>1557</v>
       </c>
       <c r="W73" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12074,16 +12065,16 @@
         <v>1558</v>
       </c>
       <c r="W74" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X74" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="Y74" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z74" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12145,16 +12136,16 @@
         <v>1559</v>
       </c>
       <c r="W75" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X75" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="Y75" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z75" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12216,7 +12207,7 @@
         <v>1538</v>
       </c>
       <c r="W76" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12278,7 +12269,7 @@
         <v>1538</v>
       </c>
       <c r="W77" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12340,10 +12331,10 @@
         <v>1560</v>
       </c>
       <c r="W78" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="Z78" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12408,7 +12399,7 @@
         <v>1561</v>
       </c>
       <c r="W79" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12467,7 +12458,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12526,7 +12517,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12588,7 +12579,7 @@
         <v>1562</v>
       </c>
       <c r="W82" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12650,7 +12641,7 @@
         <v>1563</v>
       </c>
       <c r="W83" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12712,7 +12703,7 @@
         <v>1564</v>
       </c>
       <c r="W84" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12771,7 +12762,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12833,7 +12824,7 @@
         <v>1565</v>
       </c>
       <c r="W86" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12895,7 +12886,7 @@
         <v>1566</v>
       </c>
       <c r="W87" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12957,7 +12948,7 @@
         <v>1566</v>
       </c>
       <c r="W88" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -13019,7 +13010,7 @@
         <v>1531</v>
       </c>
       <c r="W89" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13081,16 +13072,16 @@
         <v>1567</v>
       </c>
       <c r="W90" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X90" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="Y90" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z90" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13152,16 +13143,16 @@
         <v>1568</v>
       </c>
       <c r="W91" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X91" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="Y91" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z91" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13223,7 +13214,7 @@
         <v>1569</v>
       </c>
       <c r="W92" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13285,7 +13276,7 @@
         <v>1570</v>
       </c>
       <c r="W93" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13347,7 +13338,7 @@
         <v>1570</v>
       </c>
       <c r="W94" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13409,7 +13400,7 @@
         <v>1571</v>
       </c>
       <c r="W95" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13471,16 +13462,16 @@
         <v>1572</v>
       </c>
       <c r="W96" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X96" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="Y96" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z96" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13542,7 +13533,7 @@
         <v>1573</v>
       </c>
       <c r="W97" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13604,7 +13595,7 @@
         <v>1574</v>
       </c>
       <c r="W98" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13666,7 +13657,7 @@
         <v>1575</v>
       </c>
       <c r="W99" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13728,7 +13719,7 @@
         <v>1576</v>
       </c>
       <c r="W100" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13790,16 +13781,16 @@
         <v>1577</v>
       </c>
       <c r="W101" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X101" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="Y101" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z101" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13861,7 +13852,7 @@
         <v>1578</v>
       </c>
       <c r="W102" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13923,7 +13914,7 @@
         <v>1578</v>
       </c>
       <c r="W103" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13985,7 +13976,7 @@
         <v>1579</v>
       </c>
       <c r="W104" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -14047,16 +14038,16 @@
         <v>1580</v>
       </c>
       <c r="W105" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X105" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="Y105" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z105" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14118,16 +14109,16 @@
         <v>1581</v>
       </c>
       <c r="W106" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X106" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="Y106" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z106" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14189,7 +14180,7 @@
         <v>1582</v>
       </c>
       <c r="W107" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14251,16 +14242,16 @@
         <v>1583</v>
       </c>
       <c r="W108" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X108" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="Y108" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z108" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14322,16 +14313,16 @@
         <v>1584</v>
       </c>
       <c r="W109" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X109" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="Y109" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z109" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14390,7 +14381,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14452,16 +14443,16 @@
         <v>1585</v>
       </c>
       <c r="W111" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X111" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="Y111" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z111" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14523,16 +14514,16 @@
         <v>1586</v>
       </c>
       <c r="W112" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X112" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="Y112" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z112" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14594,16 +14585,16 @@
         <v>1587</v>
       </c>
       <c r="W113" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X113" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="Y113" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z113" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14665,16 +14656,16 @@
         <v>1588</v>
       </c>
       <c r="W114" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X114" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="Y114" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z114" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14736,16 +14727,16 @@
         <v>1584</v>
       </c>
       <c r="W115" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X115" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="Y115" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z115" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14807,16 +14798,16 @@
         <v>1584</v>
       </c>
       <c r="W116" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X116" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="Y116" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z116" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14878,16 +14869,16 @@
         <v>1589</v>
       </c>
       <c r="W117" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X117" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="Y117" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z117" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14949,16 +14940,16 @@
         <v>1590</v>
       </c>
       <c r="W118" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X118" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="Y118" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z118" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -15020,7 +15011,7 @@
         <v>1591</v>
       </c>
       <c r="W119" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15082,16 +15073,16 @@
         <v>1592</v>
       </c>
       <c r="W120" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X120" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y120" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z120" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15153,16 +15144,16 @@
         <v>1592</v>
       </c>
       <c r="W121" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X121" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y121" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z121" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15224,16 +15215,16 @@
         <v>1592</v>
       </c>
       <c r="W122" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X122" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y122" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z122" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15295,16 +15286,16 @@
         <v>1592</v>
       </c>
       <c r="W123" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X123" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y123" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z123" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15366,16 +15357,16 @@
         <v>1592</v>
       </c>
       <c r="W124" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X124" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y124" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z124" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15437,16 +15428,16 @@
         <v>1592</v>
       </c>
       <c r="W125" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X125" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y125" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z125" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15508,16 +15499,16 @@
         <v>1592</v>
       </c>
       <c r="W126" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X126" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y126" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z126" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15579,16 +15570,16 @@
         <v>1593</v>
       </c>
       <c r="W127" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X127" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="Y127" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z127" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15650,16 +15641,16 @@
         <v>1594</v>
       </c>
       <c r="W128" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X128" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="Y128" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z128" t="s">
-        <v>2190</v>
+        <v>2187</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15721,16 +15712,16 @@
         <v>1592</v>
       </c>
       <c r="W129" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X129" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y129" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z129" t="s">
-        <v>2191</v>
+        <v>2188</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15792,16 +15783,16 @@
         <v>1592</v>
       </c>
       <c r="W130" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X130" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y130" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z130" t="s">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15863,7 +15854,7 @@
         <v>1595</v>
       </c>
       <c r="W131" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15922,7 +15913,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15981,7 +15972,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -16043,16 +16034,16 @@
         <v>1592</v>
       </c>
       <c r="W134" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X134" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y134" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z134" t="s">
-        <v>2193</v>
+        <v>2190</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16114,16 +16105,16 @@
         <v>1592</v>
       </c>
       <c r="W135" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X135" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y135" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z135" t="s">
-        <v>2194</v>
+        <v>2191</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16185,7 +16176,7 @@
         <v>1591</v>
       </c>
       <c r="W136" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16244,7 +16235,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16306,16 +16297,16 @@
         <v>1596</v>
       </c>
       <c r="W138" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X138" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="Y138" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z138" t="s">
-        <v>2195</v>
+        <v>2192</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16377,16 +16368,16 @@
         <v>1584</v>
       </c>
       <c r="W139" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X139" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="Y139" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z139" t="s">
-        <v>2196</v>
+        <v>2193</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16448,16 +16439,16 @@
         <v>1592</v>
       </c>
       <c r="W140" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X140" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y140" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z140" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16516,7 +16507,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16575,7 +16566,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16637,16 +16628,16 @@
         <v>1597</v>
       </c>
       <c r="W143" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X143" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="Y143" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z143" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16708,16 +16699,16 @@
         <v>1598</v>
       </c>
       <c r="W144" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X144" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="Y144" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z144" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16779,16 +16770,16 @@
         <v>1599</v>
       </c>
       <c r="W145" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X145" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="Y145" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z145" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16850,16 +16841,16 @@
         <v>1600</v>
       </c>
       <c r="W146" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X146" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="Y146" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z146" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16918,7 +16909,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16980,7 +16971,7 @@
         <v>1601</v>
       </c>
       <c r="W148" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -17042,16 +17033,16 @@
         <v>1602</v>
       </c>
       <c r="W149" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X149" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="Y149" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z149" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17113,7 +17104,7 @@
         <v>1603</v>
       </c>
       <c r="W150" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17175,16 +17166,16 @@
         <v>1604</v>
       </c>
       <c r="W151" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X151" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="Y151" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z151" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17246,7 +17237,7 @@
         <v>1603</v>
       </c>
       <c r="W152" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17308,7 +17299,7 @@
         <v>1601</v>
       </c>
       <c r="W153" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17370,7 +17361,7 @@
         <v>1603</v>
       </c>
       <c r="W154" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17432,7 +17423,7 @@
         <v>1603</v>
       </c>
       <c r="W155" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17494,16 +17485,16 @@
         <v>1605</v>
       </c>
       <c r="W156" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X156" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="Y156" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z156" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17565,7 +17556,7 @@
         <v>1601</v>
       </c>
       <c r="W157" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17627,16 +17618,16 @@
         <v>1606</v>
       </c>
       <c r="W158" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X158" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="Y158" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z158" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17698,16 +17689,16 @@
         <v>1607</v>
       </c>
       <c r="W159" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X159" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
       <c r="Y159" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z159" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17769,16 +17760,16 @@
         <v>1606</v>
       </c>
       <c r="W160" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X160" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="Y160" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z160" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17840,16 +17831,16 @@
         <v>1606</v>
       </c>
       <c r="W161" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X161" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="Y161" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z161" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17911,16 +17902,16 @@
         <v>1606</v>
       </c>
       <c r="W162" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X162" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="Y162" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z162" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17982,16 +17973,16 @@
         <v>1608</v>
       </c>
       <c r="W163" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X163" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
       <c r="Y163" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z163" t="s">
-        <v>2210</v>
+        <v>2207</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -18053,16 +18044,16 @@
         <v>1609</v>
       </c>
       <c r="W164" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X164" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="Y164" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z164" t="s">
-        <v>2211</v>
+        <v>2208</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18124,16 +18115,16 @@
         <v>1610</v>
       </c>
       <c r="W165" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X165" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
       <c r="Y165" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z165" t="s">
-        <v>2212</v>
+        <v>2209</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18195,16 +18186,16 @@
         <v>1611</v>
       </c>
       <c r="W166" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X166" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="Y166" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z166" t="s">
-        <v>2213</v>
+        <v>2210</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18266,16 +18257,16 @@
         <v>1589</v>
       </c>
       <c r="W167" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X167" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="Y167" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z167" t="s">
-        <v>2214</v>
+        <v>2211</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18337,16 +18328,16 @@
         <v>1592</v>
       </c>
       <c r="W168" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X168" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y168" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z168" t="s">
-        <v>2215</v>
+        <v>2212</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18408,7 +18399,7 @@
         <v>1612</v>
       </c>
       <c r="W169" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18470,16 +18461,16 @@
         <v>1592</v>
       </c>
       <c r="W170" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X170" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="Y170" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z170" t="s">
-        <v>2216</v>
+        <v>2213</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18541,16 +18532,16 @@
         <v>1613</v>
       </c>
       <c r="W171" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X171" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="Y171" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z171" t="s">
-        <v>2217</v>
+        <v>2214</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18612,16 +18603,16 @@
         <v>1614</v>
       </c>
       <c r="W172" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X172" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="Y172" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z172" t="s">
-        <v>2218</v>
+        <v>2215</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18683,16 +18674,16 @@
         <v>1615</v>
       </c>
       <c r="W173" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X173" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
       <c r="Y173" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z173" t="s">
-        <v>2219</v>
+        <v>2216</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18754,16 +18745,16 @@
         <v>1616</v>
       </c>
       <c r="W174" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X174" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="Y174" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z174" t="s">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18825,16 +18816,16 @@
         <v>1617</v>
       </c>
       <c r="W175" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X175" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="Y175" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z175" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18896,16 +18887,16 @@
         <v>1618</v>
       </c>
       <c r="W176" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X176" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="Y176" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z176" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18967,7 +18958,7 @@
         <v>1612</v>
       </c>
       <c r="W177" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -19029,16 +19020,16 @@
         <v>1619</v>
       </c>
       <c r="W178" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X178" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
       <c r="Y178" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z178" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19100,16 +19091,16 @@
         <v>1620</v>
       </c>
       <c r="W179" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X179" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="Y179" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z179" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19171,7 +19162,7 @@
         <v>1621</v>
       </c>
       <c r="W180" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19233,16 +19224,16 @@
         <v>1622</v>
       </c>
       <c r="W181" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X181" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="Y181" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z181" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19304,16 +19295,16 @@
         <v>1622</v>
       </c>
       <c r="W182" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X182" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
       <c r="Y182" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z182" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19375,16 +19366,16 @@
         <v>1623</v>
       </c>
       <c r="W183" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X183" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="Y183" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z183" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19446,16 +19437,16 @@
         <v>1624</v>
       </c>
       <c r="W184" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X184" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="Y184" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z184" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19517,16 +19508,16 @@
         <v>1625</v>
       </c>
       <c r="W185" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X185" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
       <c r="Y185" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z185" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19588,7 +19579,7 @@
         <v>1626</v>
       </c>
       <c r="W186" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19650,7 +19641,7 @@
         <v>1627</v>
       </c>
       <c r="W187" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19712,7 +19703,7 @@
         <v>1628</v>
       </c>
       <c r="W188" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19774,7 +19765,7 @@
         <v>1629</v>
       </c>
       <c r="W189" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19836,16 +19827,16 @@
         <v>1630</v>
       </c>
       <c r="W190" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X190" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
       <c r="Y190" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z190" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19907,16 +19898,16 @@
         <v>1631</v>
       </c>
       <c r="W191" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X191" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
       <c r="Y191" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z191" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19978,7 +19969,7 @@
         <v>1632</v>
       </c>
       <c r="W192" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -20040,7 +20031,7 @@
         <v>1632</v>
       </c>
       <c r="W193" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20102,16 +20093,16 @@
         <v>1633</v>
       </c>
       <c r="W194" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X194" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="Y194" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z194" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20173,16 +20164,16 @@
         <v>1634</v>
       </c>
       <c r="W195" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X195" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="Y195" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z195" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20244,16 +20235,16 @@
         <v>1635</v>
       </c>
       <c r="W196" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X196" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
       <c r="Y196" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z196" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20315,16 +20306,16 @@
         <v>1631</v>
       </c>
       <c r="W197" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X197" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
       <c r="Y197" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z197" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20386,7 +20377,7 @@
         <v>1636</v>
       </c>
       <c r="W198" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20448,7 +20439,7 @@
         <v>1637</v>
       </c>
       <c r="W199" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20510,16 +20501,16 @@
         <v>1638</v>
       </c>
       <c r="W200" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X200" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
       <c r="Y200" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z200" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20581,16 +20572,16 @@
         <v>1638</v>
       </c>
       <c r="W201" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X201" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
       <c r="Y201" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z201" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20652,16 +20643,16 @@
         <v>1639</v>
       </c>
       <c r="W202" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X202" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
       <c r="Y202" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z202" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20723,16 +20714,16 @@
         <v>1640</v>
       </c>
       <c r="W203" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X203" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="Y203" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z203" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20794,16 +20785,16 @@
         <v>1641</v>
       </c>
       <c r="W204" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X204" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
       <c r="Y204" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z204" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20865,16 +20856,16 @@
         <v>1642</v>
       </c>
       <c r="W205" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X205" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
       <c r="Y205" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z205" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20936,16 +20927,16 @@
         <v>1643</v>
       </c>
       <c r="W206" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X206" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
       <c r="Y206" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z206" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -21007,16 +20998,16 @@
         <v>1644</v>
       </c>
       <c r="W207" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X207" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
       <c r="Y207" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z207" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21078,16 +21069,16 @@
         <v>1645</v>
       </c>
       <c r="W208" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X208" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="Y208" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z208" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21149,7 +21140,7 @@
         <v>1646</v>
       </c>
       <c r="W209" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21211,16 +21202,16 @@
         <v>1647</v>
       </c>
       <c r="W210" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X210" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
       <c r="Y210" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z210" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21282,16 +21273,16 @@
         <v>1648</v>
       </c>
       <c r="W211" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X211" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="Y211" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z211" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21353,16 +21344,16 @@
         <v>1649</v>
       </c>
       <c r="W212" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X212" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="Y212" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z212" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21424,16 +21415,16 @@
         <v>1650</v>
       </c>
       <c r="W213" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X213" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="Y213" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z213" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21495,7 +21486,7 @@
         <v>1651</v>
       </c>
       <c r="W214" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21557,16 +21548,16 @@
         <v>1616</v>
       </c>
       <c r="W215" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X215" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
       <c r="Y215" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z215" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21628,16 +21619,16 @@
         <v>1652</v>
       </c>
       <c r="W216" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X216" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="Y216" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z216" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21699,7 +21690,7 @@
         <v>1653</v>
       </c>
       <c r="W217" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21761,16 +21752,16 @@
         <v>1654</v>
       </c>
       <c r="W218" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X218" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="Y218" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z218" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21832,16 +21823,16 @@
         <v>1655</v>
       </c>
       <c r="W219" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X219" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="Y219" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z219" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21903,7 +21894,7 @@
         <v>1656</v>
       </c>
       <c r="W220" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21965,7 +21956,7 @@
         <v>1657</v>
       </c>
       <c r="W221" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -22027,7 +22018,7 @@
         <v>1656</v>
       </c>
       <c r="W222" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22089,7 +22080,7 @@
         <v>1657</v>
       </c>
       <c r="W223" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22151,16 +22142,16 @@
         <v>1658</v>
       </c>
       <c r="W224" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X224" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
       <c r="Y224" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z224" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22222,16 +22213,16 @@
         <v>1659</v>
       </c>
       <c r="W225" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X225" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
       <c r="Y225" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z225" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22293,7 +22284,7 @@
         <v>1660</v>
       </c>
       <c r="W226" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22355,7 +22346,7 @@
         <v>1661</v>
       </c>
       <c r="W227" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22417,7 +22408,7 @@
         <v>1662</v>
       </c>
       <c r="W228" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22479,16 +22470,16 @@
         <v>1663</v>
       </c>
       <c r="W229" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X229" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="Y229" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z229" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22550,16 +22541,16 @@
         <v>1664</v>
       </c>
       <c r="W230" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X230" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="Y230" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z230" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22621,16 +22612,16 @@
         <v>1665</v>
       </c>
       <c r="W231" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X231" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
       <c r="Y231" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z231" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22695,16 +22686,16 @@
         <v>1666</v>
       </c>
       <c r="W232" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X232" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="Y232" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z232" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22766,16 +22757,16 @@
         <v>1667</v>
       </c>
       <c r="W233" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X233" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
       <c r="Y233" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z233" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22837,16 +22828,16 @@
         <v>1668</v>
       </c>
       <c r="W234" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X234" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="Y234" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z234" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22908,16 +22899,16 @@
         <v>1668</v>
       </c>
       <c r="W235" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X235" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="Y235" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z235" t="s">
-        <v>2260</v>
+        <v>2257</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22979,16 +22970,16 @@
         <v>1669</v>
       </c>
       <c r="W236" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X236" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="Y236" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z236" t="s">
-        <v>2261</v>
+        <v>2258</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -23050,7 +23041,7 @@
         <v>1670</v>
       </c>
       <c r="W237" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23112,7 +23103,7 @@
         <v>1671</v>
       </c>
       <c r="W238" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23174,16 +23165,16 @@
         <v>1672</v>
       </c>
       <c r="W239" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X239" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="Y239" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z239" t="s">
-        <v>2262</v>
+        <v>2259</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23245,16 +23236,16 @@
         <v>1673</v>
       </c>
       <c r="W240" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X240" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="Y240" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z240" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23316,7 +23307,7 @@
         <v>1674</v>
       </c>
       <c r="W241" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23378,16 +23369,16 @@
         <v>1675</v>
       </c>
       <c r="W242" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X242" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="Y242" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z242" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23449,16 +23440,16 @@
         <v>1676</v>
       </c>
       <c r="W243" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X243" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="Y243" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z243" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23520,16 +23511,16 @@
         <v>1675</v>
       </c>
       <c r="W244" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X244" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="Y244" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z244" t="s">
-        <v>2266</v>
+        <v>2263</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23591,16 +23582,16 @@
         <v>1677</v>
       </c>
       <c r="W245" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X245" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="Y245" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z245" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23662,16 +23653,16 @@
         <v>1676</v>
       </c>
       <c r="W246" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X246" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="Y246" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z246" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23733,16 +23724,16 @@
         <v>1677</v>
       </c>
       <c r="W247" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X247" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="Y247" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z247" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23804,16 +23795,16 @@
         <v>1678</v>
       </c>
       <c r="W248" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X248" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
       <c r="Y248" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z248" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23875,16 +23866,16 @@
         <v>1668</v>
       </c>
       <c r="W249" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X249" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="Y249" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z249" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23946,7 +23937,7 @@
         <v>1679</v>
       </c>
       <c r="W250" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -24008,7 +23999,7 @@
         <v>1680</v>
       </c>
       <c r="W251" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -24070,16 +24061,16 @@
         <v>1681</v>
       </c>
       <c r="W252" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X252" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="Y252" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z252" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24141,16 +24132,16 @@
         <v>1682</v>
       </c>
       <c r="W253" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X253" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="Y253" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z253" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24212,7 +24203,7 @@
         <v>1683</v>
       </c>
       <c r="W254" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24274,16 +24265,16 @@
         <v>1684</v>
       </c>
       <c r="W255" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X255" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="Y255" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z255" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24345,7 +24336,7 @@
         <v>1685</v>
       </c>
       <c r="W256" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24410,7 +24401,7 @@
         <v>1686</v>
       </c>
       <c r="W257" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24472,7 +24463,7 @@
         <v>1687</v>
       </c>
       <c r="W258" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24534,7 +24525,7 @@
         <v>1687</v>
       </c>
       <c r="W259" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24596,7 +24587,7 @@
         <v>1688</v>
       </c>
       <c r="W260" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24658,16 +24649,16 @@
         <v>1689</v>
       </c>
       <c r="W261" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X261" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
       <c r="Y261" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z261" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24729,13 +24720,13 @@
         <v>1690</v>
       </c>
       <c r="W262" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X262" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
       <c r="Y262" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24797,16 +24788,16 @@
         <v>1691</v>
       </c>
       <c r="W263" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X263" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="Y263" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z263" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24868,7 +24859,7 @@
         <v>1692</v>
       </c>
       <c r="W264" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24930,7 +24921,7 @@
         <v>1692</v>
       </c>
       <c r="W265" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24992,7 +24983,7 @@
         <v>1693</v>
       </c>
       <c r="W266" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -25054,16 +25045,16 @@
         <v>1694</v>
       </c>
       <c r="W267" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X267" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="Y267" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z267" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25125,16 +25116,16 @@
         <v>1695</v>
       </c>
       <c r="W268" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X268" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="Y268" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z268" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25196,7 +25187,7 @@
         <v>1536</v>
       </c>
       <c r="W269" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25258,7 +25249,7 @@
         <v>1696</v>
       </c>
       <c r="W270" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25320,7 +25311,7 @@
         <v>1697</v>
       </c>
       <c r="W271" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25382,16 +25373,16 @@
         <v>1698</v>
       </c>
       <c r="W272" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X272" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="Y272" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z272" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25450,7 +25441,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25512,7 +25503,7 @@
         <v>1699</v>
       </c>
       <c r="W274" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25571,7 +25562,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25633,7 +25624,7 @@
         <v>1700</v>
       </c>
       <c r="W276" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25695,7 +25686,7 @@
         <v>1701</v>
       </c>
       <c r="W277" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25757,16 +25748,16 @@
         <v>1702</v>
       </c>
       <c r="W278" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X278" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="Y278" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z278" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25828,16 +25819,16 @@
         <v>1703</v>
       </c>
       <c r="W279" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X279" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="Y279" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z279" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25899,16 +25890,16 @@
         <v>1703</v>
       </c>
       <c r="W280" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X280" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="Y280" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z280" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25970,16 +25961,16 @@
         <v>1704</v>
       </c>
       <c r="W281" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X281" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="Y281" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z281" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -26041,7 +26032,7 @@
         <v>1705</v>
       </c>
       <c r="W282" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26103,7 +26094,7 @@
         <v>1706</v>
       </c>
       <c r="W283" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26165,7 +26156,7 @@
         <v>1707</v>
       </c>
       <c r="W284" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26227,16 +26218,16 @@
         <v>1708</v>
       </c>
       <c r="W285" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X285" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="Y285" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z285" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26298,7 +26289,7 @@
         <v>1709</v>
       </c>
       <c r="W286" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26360,16 +26351,16 @@
         <v>1703</v>
       </c>
       <c r="W287" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X287" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
       <c r="Y287" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z287" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26431,16 +26422,16 @@
         <v>1710</v>
       </c>
       <c r="W288" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X288" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="Y288" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z288" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26502,7 +26493,7 @@
         <v>1711</v>
       </c>
       <c r="W289" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26564,16 +26555,16 @@
         <v>1712</v>
       </c>
       <c r="W290" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X290" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="Y290" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z290" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26635,16 +26626,16 @@
         <v>1713</v>
       </c>
       <c r="W291" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X291" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="Y291" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z291" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26706,7 +26697,7 @@
         <v>1714</v>
       </c>
       <c r="W292" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26765,7 +26756,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26827,7 +26818,7 @@
         <v>1715</v>
       </c>
       <c r="W294" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26889,7 +26880,7 @@
         <v>1716</v>
       </c>
       <c r="W295" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26951,7 +26942,7 @@
         <v>1717</v>
       </c>
       <c r="W296" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -27013,13 +27004,13 @@
         <v>1718</v>
       </c>
       <c r="W297" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X297" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
       <c r="Z297" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27081,7 +27072,7 @@
         <v>1719</v>
       </c>
       <c r="W298" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27143,7 +27134,7 @@
         <v>1720</v>
       </c>
       <c r="W299" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27205,7 +27196,7 @@
         <v>1721</v>
       </c>
       <c r="W300" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27267,7 +27258,7 @@
         <v>1722</v>
       </c>
       <c r="W301" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27329,7 +27320,7 @@
         <v>1723</v>
       </c>
       <c r="W302" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27391,16 +27382,16 @@
         <v>1724</v>
       </c>
       <c r="W303" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X303" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="Y303" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z303" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27462,7 +27453,7 @@
         <v>1725</v>
       </c>
       <c r="W304" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27524,7 +27515,7 @@
         <v>1726</v>
       </c>
       <c r="W305" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27586,7 +27577,7 @@
         <v>1727</v>
       </c>
       <c r="W306" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27648,7 +27639,7 @@
         <v>1728</v>
       </c>
       <c r="W307" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27710,7 +27701,7 @@
         <v>1721</v>
       </c>
       <c r="W308" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27772,7 +27763,7 @@
         <v>1729</v>
       </c>
       <c r="W309" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27834,7 +27825,7 @@
         <v>1730</v>
       </c>
       <c r="W310" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27896,7 +27887,7 @@
         <v>1731</v>
       </c>
       <c r="W311" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27958,7 +27949,7 @@
         <v>1732</v>
       </c>
       <c r="W312" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -28020,7 +28011,7 @@
         <v>1733</v>
       </c>
       <c r="W313" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28082,7 +28073,7 @@
         <v>1734</v>
       </c>
       <c r="W314" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28144,7 +28135,7 @@
         <v>1735</v>
       </c>
       <c r="W315" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28206,7 +28197,7 @@
         <v>1736</v>
       </c>
       <c r="W316" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28268,7 +28259,7 @@
         <v>1737</v>
       </c>
       <c r="W317" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28330,7 +28321,7 @@
         <v>1738</v>
       </c>
       <c r="W318" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28392,7 +28383,7 @@
         <v>1739</v>
       </c>
       <c r="W319" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28451,13 +28442,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X320" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
       <c r="Z320" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28516,7 +28507,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28575,7 +28566,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28634,7 +28625,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28696,7 +28687,7 @@
         <v>1740</v>
       </c>
       <c r="W324" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28758,7 +28749,7 @@
         <v>1741</v>
       </c>
       <c r="W325" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28820,7 +28811,7 @@
         <v>1742</v>
       </c>
       <c r="W326" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28882,7 +28873,7 @@
         <v>1743</v>
       </c>
       <c r="W327" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28941,7 +28932,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -29003,7 +28994,7 @@
         <v>1743</v>
       </c>
       <c r="W329" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -29065,7 +29056,7 @@
         <v>1744</v>
       </c>
       <c r="W330" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29127,7 +29118,7 @@
         <v>1745</v>
       </c>
       <c r="W331" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29189,7 +29180,7 @@
         <v>1745</v>
       </c>
       <c r="W332" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29251,7 +29242,7 @@
         <v>1746</v>
       </c>
       <c r="W333" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29313,7 +29304,7 @@
         <v>1747</v>
       </c>
       <c r="W334" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29375,7 +29366,7 @@
         <v>1748</v>
       </c>
       <c r="W335" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29434,13 +29425,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X336" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="Z336" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29502,7 +29493,7 @@
         <v>1749</v>
       </c>
       <c r="W337" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29564,13 +29555,13 @@
         <v>1750</v>
       </c>
       <c r="W338" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X338" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
       <c r="Z338" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29632,13 +29623,13 @@
         <v>1751</v>
       </c>
       <c r="W339" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X339" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
       <c r="Z339" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29700,7 +29691,7 @@
         <v>1752</v>
       </c>
       <c r="W340" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29762,7 +29753,7 @@
         <v>1753</v>
       </c>
       <c r="W341" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29824,10 +29815,10 @@
         <v>1754</v>
       </c>
       <c r="W342" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X342" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29889,7 +29880,7 @@
         <v>1755</v>
       </c>
       <c r="W343" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29951,7 +29942,7 @@
         <v>1756</v>
       </c>
       <c r="W344" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -30013,13 +30004,13 @@
         <v>1757</v>
       </c>
       <c r="W345" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X345" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
       <c r="Z345" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30081,7 +30072,7 @@
         <v>1721</v>
       </c>
       <c r="W346" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30143,7 +30134,7 @@
         <v>1758</v>
       </c>
       <c r="W347" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30205,16 +30196,16 @@
         <v>1759</v>
       </c>
       <c r="W348" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X348" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="Y348" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z348" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30279,13 +30270,13 @@
         <v>1760</v>
       </c>
       <c r="W349" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X349" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
       <c r="Z349" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30347,7 +30338,7 @@
         <v>1761</v>
       </c>
       <c r="W350" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30409,16 +30400,16 @@
         <v>1762</v>
       </c>
       <c r="W351" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X351" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="Y351" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z351" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30480,13 +30471,13 @@
         <v>1763</v>
       </c>
       <c r="W352" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X352" t="s">
         <v>1763</v>
       </c>
       <c r="Z352" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30548,16 +30539,16 @@
         <v>1764</v>
       </c>
       <c r="W353" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X353" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
       <c r="Y353" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z353" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30619,7 +30610,7 @@
         <v>1765</v>
       </c>
       <c r="W354" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30681,7 +30672,7 @@
         <v>1766</v>
       </c>
       <c r="W355" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30740,7 +30731,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30799,7 +30790,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30858,7 +30849,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30920,7 +30911,7 @@
         <v>1767</v>
       </c>
       <c r="W359" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30985,7 +30976,7 @@
         <v>1768</v>
       </c>
       <c r="W360" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -31050,7 +31041,7 @@
         <v>1769</v>
       </c>
       <c r="W361" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31112,16 +31103,16 @@
         <v>1770</v>
       </c>
       <c r="W362" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X362" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="Y362" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z362" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31183,16 +31174,16 @@
         <v>1771</v>
       </c>
       <c r="W363" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X363" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="Y363" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z363" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31254,7 +31245,7 @@
         <v>1772</v>
       </c>
       <c r="W364" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31316,7 +31307,7 @@
         <v>1773</v>
       </c>
       <c r="W365" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31381,7 +31372,7 @@
         <v>1774</v>
       </c>
       <c r="W366" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31443,7 +31434,7 @@
         <v>1775</v>
       </c>
       <c r="W367" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31505,7 +31496,7 @@
         <v>1776</v>
       </c>
       <c r="W368" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31570,13 +31561,13 @@
         <v>1777</v>
       </c>
       <c r="W369" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X369" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="Z369" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31638,7 +31629,7 @@
         <v>1778</v>
       </c>
       <c r="W370" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31700,16 +31691,16 @@
         <v>1779</v>
       </c>
       <c r="W371" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X371" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="Y371" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z371" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31774,7 +31765,7 @@
         <v>1780</v>
       </c>
       <c r="W372" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31839,16 +31830,16 @@
         <v>1781</v>
       </c>
       <c r="W373" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X373" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
       <c r="Y373" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z373" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31910,7 +31901,7 @@
         <v>1782</v>
       </c>
       <c r="W374" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31975,7 +31966,7 @@
         <v>1783</v>
       </c>
       <c r="W375" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -32040,7 +32031,7 @@
         <v>1784</v>
       </c>
       <c r="W376" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32105,7 +32096,7 @@
         <v>1784</v>
       </c>
       <c r="W377" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32170,13 +32161,13 @@
         <v>1785</v>
       </c>
       <c r="W378" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X378" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
       <c r="Z378" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32238,16 +32229,16 @@
         <v>1786</v>
       </c>
       <c r="W379" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X379" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="Y379" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z379" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32312,7 +32303,7 @@
         <v>1787</v>
       </c>
       <c r="W380" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32374,7 +32365,7 @@
         <v>1788</v>
       </c>
       <c r="W381" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32439,7 +32430,7 @@
         <v>1789</v>
       </c>
       <c r="W382" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32501,7 +32492,7 @@
         <v>1790</v>
       </c>
       <c r="W383" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32566,7 +32557,7 @@
         <v>1789</v>
       </c>
       <c r="W384" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32628,16 +32619,16 @@
         <v>1791</v>
       </c>
       <c r="W385" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X385" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
       <c r="Y385" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z385" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32705,7 +32696,7 @@
         <v>1792</v>
       </c>
       <c r="W386" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32767,7 +32758,7 @@
         <v>1793</v>
       </c>
       <c r="W387" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32829,7 +32820,7 @@
         <v>1794</v>
       </c>
       <c r="W388" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32891,16 +32882,16 @@
         <v>1795</v>
       </c>
       <c r="W389" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X389" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
       <c r="Y389" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z389" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32965,16 +32956,16 @@
         <v>1796</v>
       </c>
       <c r="W390" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X390" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
       <c r="Y390" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z390" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -33039,7 +33030,7 @@
         <v>1797</v>
       </c>
       <c r="W391" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33101,7 +33092,7 @@
         <v>1798</v>
       </c>
       <c r="W392" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33163,16 +33154,16 @@
         <v>1799</v>
       </c>
       <c r="W393" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X393" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
       <c r="Y393" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z393" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33234,7 +33225,7 @@
         <v>1800</v>
       </c>
       <c r="W394" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33299,16 +33290,16 @@
         <v>1801</v>
       </c>
       <c r="W395" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X395" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
       <c r="Y395" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z395" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33373,13 +33364,13 @@
         <v>1802</v>
       </c>
       <c r="W396" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X396" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="Y396" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33441,7 +33432,7 @@
         <v>1803</v>
       </c>
       <c r="W397" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33503,7 +33494,7 @@
         <v>1804</v>
       </c>
       <c r="W398" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33568,7 +33559,7 @@
         <v>1805</v>
       </c>
       <c r="W399" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33633,16 +33624,16 @@
         <v>1806</v>
       </c>
       <c r="W400" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X400" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
       <c r="Y400" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z400" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33707,7 +33698,7 @@
         <v>1807</v>
       </c>
       <c r="W401" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33772,7 +33763,7 @@
         <v>1808</v>
       </c>
       <c r="W402" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33837,16 +33828,16 @@
         <v>1809</v>
       </c>
       <c r="W403" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X403" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="Y403" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z403" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33911,7 +33902,7 @@
         <v>1810</v>
       </c>
       <c r="W404" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33976,7 +33967,7 @@
         <v>1811</v>
       </c>
       <c r="W405" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -34041,7 +34032,7 @@
         <v>1812</v>
       </c>
       <c r="W406" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34103,16 +34094,16 @@
         <v>1813</v>
       </c>
       <c r="W407" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X407" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
       <c r="Y407" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z407" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34177,13 +34168,13 @@
         <v>1814</v>
       </c>
       <c r="W408" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X408" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="Z408" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34248,7 +34239,7 @@
         <v>1815</v>
       </c>
       <c r="W409" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34313,7 +34304,7 @@
         <v>1816</v>
       </c>
       <c r="W410" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34378,7 +34369,7 @@
         <v>1817</v>
       </c>
       <c r="W411" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34443,7 +34434,7 @@
         <v>1818</v>
       </c>
       <c r="W412" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34508,7 +34499,7 @@
         <v>1819</v>
       </c>
       <c r="W413" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34573,7 +34564,7 @@
         <v>1819</v>
       </c>
       <c r="W414" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34638,7 +34629,7 @@
         <v>1820</v>
       </c>
       <c r="W415" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34703,7 +34694,7 @@
         <v>1821</v>
       </c>
       <c r="W416" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34768,7 +34759,7 @@
         <v>1819</v>
       </c>
       <c r="W417" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34833,7 +34824,7 @@
         <v>1822</v>
       </c>
       <c r="W418" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34898,7 +34889,7 @@
         <v>1823</v>
       </c>
       <c r="W419" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34963,16 +34954,16 @@
         <v>1824</v>
       </c>
       <c r="W420" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X420" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
       <c r="Y420" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z420" t="s">
-        <v>2314</v>
+        <v>2311</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -35037,7 +35028,7 @@
         <v>1825</v>
       </c>
       <c r="W421" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35102,7 +35093,7 @@
         <v>1826</v>
       </c>
       <c r="W422" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35167,7 +35158,7 @@
         <v>1827</v>
       </c>
       <c r="W423" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35232,16 +35223,16 @@
         <v>1828</v>
       </c>
       <c r="W424" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X424" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
       <c r="Y424" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z424" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35306,7 +35297,7 @@
         <v>1827</v>
       </c>
       <c r="W425" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35371,7 +35362,7 @@
         <v>1829</v>
       </c>
       <c r="W426" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35436,7 +35427,7 @@
         <v>1830</v>
       </c>
       <c r="W427" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35501,13 +35492,13 @@
         <v>1831</v>
       </c>
       <c r="W428" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X428" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
       <c r="Y428" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35572,16 +35563,16 @@
         <v>1832</v>
       </c>
       <c r="W429" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X429" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="Y429" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z429" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35646,7 +35637,7 @@
         <v>1833</v>
       </c>
       <c r="W430" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35711,16 +35702,16 @@
         <v>1834</v>
       </c>
       <c r="W431" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X431" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
       <c r="Y431" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z431" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35785,7 +35776,7 @@
         <v>1835</v>
       </c>
       <c r="W432" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35850,7 +35841,7 @@
         <v>1836</v>
       </c>
       <c r="W433" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35915,7 +35906,7 @@
         <v>1837</v>
       </c>
       <c r="W434" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35980,7 +35971,7 @@
         <v>1838</v>
       </c>
       <c r="W435" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -36045,7 +36036,7 @@
         <v>1839</v>
       </c>
       <c r="W436" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36110,7 +36101,7 @@
         <v>1840</v>
       </c>
       <c r="W437" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36175,7 +36166,7 @@
         <v>1841</v>
       </c>
       <c r="W438" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36240,7 +36231,7 @@
         <v>1842</v>
       </c>
       <c r="W439" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36305,16 +36296,16 @@
         <v>1843</v>
       </c>
       <c r="W440" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X440" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
       <c r="Y440" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z440" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36379,16 +36370,16 @@
         <v>1844</v>
       </c>
       <c r="W441" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X441" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="Y441" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z441" t="s">
-        <v>2319</v>
+        <v>2316</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36453,16 +36444,16 @@
         <v>1845</v>
       </c>
       <c r="W442" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X442" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
       <c r="Y442" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z442" t="s">
-        <v>2320</v>
+        <v>2317</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36527,7 +36518,7 @@
         <v>1846</v>
       </c>
       <c r="W443" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36592,7 +36583,7 @@
         <v>1847</v>
       </c>
       <c r="W444" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36657,16 +36648,16 @@
         <v>1844</v>
       </c>
       <c r="W445" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X445" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="Y445" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z445" t="s">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36731,16 +36722,16 @@
         <v>1844</v>
       </c>
       <c r="W446" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X446" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="Y446" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z446" t="s">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36805,16 +36796,16 @@
         <v>1848</v>
       </c>
       <c r="W447" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X447" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
       <c r="Y447" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z447" t="s">
-        <v>2323</v>
+        <v>2320</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36879,16 +36870,16 @@
         <v>1844</v>
       </c>
       <c r="W448" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X448" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="Y448" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z448" t="s">
-        <v>2324</v>
+        <v>2321</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36953,16 +36944,16 @@
         <v>1844</v>
       </c>
       <c r="W449" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X449" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
       <c r="Y449" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z449" t="s">
-        <v>2325</v>
+        <v>2322</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -37027,16 +37018,16 @@
         <v>1849</v>
       </c>
       <c r="W450" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X450" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
       <c r="Y450" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z450" t="s">
-        <v>2326</v>
+        <v>2323</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37101,16 +37092,16 @@
         <v>1850</v>
       </c>
       <c r="W451" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X451" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
       <c r="Y451" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z451" t="s">
-        <v>2327</v>
+        <v>2324</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37175,7 +37166,7 @@
         <v>1851</v>
       </c>
       <c r="W452" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37240,16 +37231,16 @@
         <v>1852</v>
       </c>
       <c r="W453" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X453" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
       <c r="Y453" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z453" t="s">
-        <v>2328</v>
+        <v>2325</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37314,16 +37305,16 @@
         <v>1853</v>
       </c>
       <c r="W454" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X454" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
       <c r="Y454" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z454" t="s">
-        <v>2329</v>
+        <v>2326</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37388,16 +37379,16 @@
         <v>1854</v>
       </c>
       <c r="W455" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X455" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="Y455" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z455" t="s">
-        <v>2330</v>
+        <v>2327</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37462,16 +37453,16 @@
         <v>1855</v>
       </c>
       <c r="W456" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X456" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
       <c r="Y456" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z456" t="s">
-        <v>2331</v>
+        <v>2328</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37536,7 +37527,7 @@
         <v>1856</v>
       </c>
       <c r="W457" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37601,7 +37592,7 @@
         <v>1856</v>
       </c>
       <c r="W458" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37666,16 +37657,16 @@
         <v>1854</v>
       </c>
       <c r="W459" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X459" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
       <c r="Y459" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z459" t="s">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37740,16 +37731,16 @@
         <v>1857</v>
       </c>
       <c r="W460" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X460" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
       <c r="Y460" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z460" t="s">
-        <v>2333</v>
+        <v>2330</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37814,16 +37805,16 @@
         <v>1858</v>
       </c>
       <c r="W461" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X461" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
       <c r="Y461" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z461" t="s">
-        <v>2334</v>
+        <v>2331</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37888,7 +37879,7 @@
         <v>1859</v>
       </c>
       <c r="W462" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37953,16 +37944,16 @@
         <v>1860</v>
       </c>
       <c r="W463" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X463" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
       <c r="Y463" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z463" t="s">
-        <v>2335</v>
+        <v>2332</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -38027,16 +38018,16 @@
         <v>1861</v>
       </c>
       <c r="W464" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X464" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
       <c r="Y464" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z464" t="s">
-        <v>2336</v>
+        <v>2333</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38101,16 +38092,16 @@
         <v>1862</v>
       </c>
       <c r="W465" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X465" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="Y465" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z465" t="s">
-        <v>2337</v>
+        <v>2334</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38175,7 +38166,7 @@
         <v>1863</v>
       </c>
       <c r="W466" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38240,16 +38231,16 @@
         <v>1864</v>
       </c>
       <c r="W467" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X467" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="Y467" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z467" t="s">
-        <v>2338</v>
+        <v>2335</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38314,16 +38305,16 @@
         <v>1865</v>
       </c>
       <c r="W468" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X468" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="Y468" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z468" t="s">
-        <v>2339</v>
+        <v>2336</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38388,16 +38379,16 @@
         <v>1866</v>
       </c>
       <c r="W469" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X469" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
       <c r="Y469" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z469" t="s">
-        <v>2340</v>
+        <v>2337</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38462,16 +38453,16 @@
         <v>1867</v>
       </c>
       <c r="W470" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X470" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="Y470" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z470" t="s">
-        <v>2341</v>
+        <v>2338</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38536,7 +38527,7 @@
         <v>1868</v>
       </c>
       <c r="W471" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38601,16 +38592,16 @@
         <v>1869</v>
       </c>
       <c r="W472" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X472" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="Y472" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z472" t="s">
-        <v>2342</v>
+        <v>2339</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38675,16 +38666,16 @@
         <v>1869</v>
       </c>
       <c r="W473" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X473" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="Y473" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z473" t="s">
-        <v>2343</v>
+        <v>2340</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38749,7 +38740,7 @@
         <v>1870</v>
       </c>
       <c r="W474" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38814,16 +38805,16 @@
         <v>1871</v>
       </c>
       <c r="W475" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X475" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
       <c r="Y475" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z475" t="s">
-        <v>2344</v>
+        <v>2341</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38888,16 +38879,16 @@
         <v>1872</v>
       </c>
       <c r="W476" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X476" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="Y476" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z476" t="s">
-        <v>2345</v>
+        <v>2342</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38962,7 +38953,7 @@
         <v>1873</v>
       </c>
       <c r="W477" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -39027,7 +39018,7 @@
         <v>1874</v>
       </c>
       <c r="W478" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39092,16 +39083,16 @@
         <v>1875</v>
       </c>
       <c r="W479" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X479" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="Y479" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z479" t="s">
-        <v>2346</v>
+        <v>2343</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39166,16 +39157,16 @@
         <v>1876</v>
       </c>
       <c r="W480" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X480" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
       <c r="Y480" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z480" t="s">
-        <v>2347</v>
+        <v>2344</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39240,16 +39231,16 @@
         <v>1877</v>
       </c>
       <c r="W481" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X481" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
       <c r="Y481" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z481" t="s">
-        <v>2348</v>
+        <v>2345</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39314,7 +39305,7 @@
         <v>1878</v>
       </c>
       <c r="W482" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39379,7 +39370,7 @@
         <v>1879</v>
       </c>
       <c r="W483" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39447,13 +39438,13 @@
         <v>1880</v>
       </c>
       <c r="W484" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2349</v>
+        <v>2346</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39518,7 +39509,7 @@
         <v>1881</v>
       </c>
       <c r="W485" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39586,13 +39577,13 @@
         <v>1882</v>
       </c>
       <c r="W486" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2350</v>
+        <v>2347</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39657,7 +39648,7 @@
         <v>1883</v>
       </c>
       <c r="W487" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39722,16 +39713,16 @@
         <v>1884</v>
       </c>
       <c r="W488" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X488" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="Y488" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z488" t="s">
-        <v>2351</v>
+        <v>2348</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39796,7 +39787,7 @@
         <v>1885</v>
       </c>
       <c r="W489" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39864,13 +39855,13 @@
         <v>1886</v>
       </c>
       <c r="W490" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2352</v>
+        <v>2349</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39935,16 +39926,16 @@
         <v>1887</v>
       </c>
       <c r="W491" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X491" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
       <c r="Y491" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z491" t="s">
-        <v>2353</v>
+        <v>2350</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -40009,16 +40000,16 @@
         <v>1888</v>
       </c>
       <c r="W492" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X492" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
       <c r="Y492" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z492" t="s">
-        <v>2354</v>
+        <v>2351</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40083,16 +40074,16 @@
         <v>1889</v>
       </c>
       <c r="W493" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X493" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="Y493" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z493" t="s">
-        <v>2355</v>
+        <v>2352</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40157,13 +40148,13 @@
         <v>1890</v>
       </c>
       <c r="W494" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X494" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="Y494" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40228,16 +40219,16 @@
         <v>1891</v>
       </c>
       <c r="W495" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X495" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="Y495" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z495" t="s">
-        <v>2356</v>
+        <v>2353</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40302,7 +40293,7 @@
         <v>1892</v>
       </c>
       <c r="W496" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40370,7 +40361,7 @@
         <v>1893</v>
       </c>
       <c r="W497" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40435,7 +40426,7 @@
         <v>1894</v>
       </c>
       <c r="W498" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40503,7 +40494,7 @@
         <v>1895</v>
       </c>
       <c r="W499" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40568,16 +40559,16 @@
         <v>1896</v>
       </c>
       <c r="W500" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X500" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
       <c r="Y500" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z500" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40642,16 +40633,16 @@
         <v>1897</v>
       </c>
       <c r="W501" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X501" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
       <c r="Y501" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z501" t="s">
-        <v>2358</v>
+        <v>2355</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40716,7 +40707,7 @@
         <v>1898</v>
       </c>
       <c r="W502" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40784,7 +40775,7 @@
         <v>1899</v>
       </c>
       <c r="W503" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40852,16 +40843,16 @@
         <v>1900</v>
       </c>
       <c r="W504" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X504" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="Y504" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z504" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40926,7 +40917,7 @@
         <v>1901</v>
       </c>
       <c r="W505" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40991,16 +40982,16 @@
         <v>1902</v>
       </c>
       <c r="W506" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X506" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="Y506" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z506" t="s">
-        <v>2360</v>
+        <v>2357</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -41065,7 +41056,7 @@
         <v>1903</v>
       </c>
       <c r="W507" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41130,7 +41121,7 @@
         <v>1904</v>
       </c>
       <c r="W508" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41195,16 +41186,16 @@
         <v>1905</v>
       </c>
       <c r="W509" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X509" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="Y509" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z509" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41269,16 +41260,16 @@
         <v>1906</v>
       </c>
       <c r="W510" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X510" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
       <c r="Y510" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z510" t="s">
-        <v>2361</v>
+        <v>2358</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41346,7 +41337,7 @@
         <v>1907</v>
       </c>
       <c r="W511" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41414,7 +41405,7 @@
         <v>1908</v>
       </c>
       <c r="W512" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41482,7 +41473,7 @@
         <v>1909</v>
       </c>
       <c r="W513" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41550,7 +41541,7 @@
         <v>1909</v>
       </c>
       <c r="W514" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41618,7 +41609,7 @@
         <v>1909</v>
       </c>
       <c r="W515" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41686,13 +41677,13 @@
         <v>1910</v>
       </c>
       <c r="W516" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2362</v>
+        <v>2359</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41760,13 +41751,13 @@
         <v>1911</v>
       </c>
       <c r="W517" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2363</v>
+        <v>2360</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41834,16 +41825,16 @@
         <v>1912</v>
       </c>
       <c r="W518" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X518" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="Y518" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z518" t="s">
-        <v>2364</v>
+        <v>2361</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41911,16 +41902,16 @@
         <v>1913</v>
       </c>
       <c r="W519" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X519" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="Y519" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z519" t="s">
-        <v>2365</v>
+        <v>2362</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41985,7 +41976,7 @@
         <v>1516</v>
       </c>
       <c r="W520" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -42053,7 +42044,7 @@
         <v>1914</v>
       </c>
       <c r="W521" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42121,7 +42112,7 @@
         <v>1914</v>
       </c>
       <c r="W522" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42189,7 +42180,7 @@
         <v>1915</v>
       </c>
       <c r="W523" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42257,7 +42248,7 @@
         <v>1916</v>
       </c>
       <c r="W524" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42325,7 +42316,7 @@
         <v>1917</v>
       </c>
       <c r="W525" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42393,7 +42384,7 @@
         <v>1918</v>
       </c>
       <c r="W526" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42461,7 +42452,7 @@
         <v>1919</v>
       </c>
       <c r="W527" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42526,7 +42517,7 @@
         <v>1920</v>
       </c>
       <c r="W528" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42594,7 +42585,7 @@
         <v>1921</v>
       </c>
       <c r="W529" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42662,16 +42653,16 @@
         <v>1922</v>
       </c>
       <c r="W530" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X530" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
       <c r="Y530" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z530" t="s">
-        <v>2366</v>
+        <v>2363</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42739,7 +42730,7 @@
         <v>1923</v>
       </c>
       <c r="W531" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42804,7 +42795,7 @@
         <v>1924</v>
       </c>
       <c r="W532" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42872,16 +42863,16 @@
         <v>1925</v>
       </c>
       <c r="W533" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X533" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="Y533" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z533" t="s">
-        <v>2367</v>
+        <v>2364</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42949,13 +42940,13 @@
         <v>1926</v>
       </c>
       <c r="W534" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -43023,7 +43014,7 @@
         <v>1927</v>
       </c>
       <c r="W535" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43091,7 +43082,7 @@
         <v>1928</v>
       </c>
       <c r="W536" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43159,16 +43150,16 @@
         <v>1929</v>
       </c>
       <c r="W537" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X537" t="s">
+        <v>2152</v>
+      </c>
+      <c r="Y537" t="s">
         <v>2155</v>
       </c>
-      <c r="Y537" t="s">
-        <v>2158</v>
-      </c>
       <c r="Z537" t="s">
-        <v>2369</v>
+        <v>2366</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43236,7 +43227,7 @@
         <v>1930</v>
       </c>
       <c r="W538" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43304,7 +43295,7 @@
         <v>1931</v>
       </c>
       <c r="W539" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43372,7 +43363,7 @@
         <v>1932</v>
       </c>
       <c r="W540" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43440,7 +43431,7 @@
         <v>1933</v>
       </c>
       <c r="W541" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43508,16 +43499,16 @@
         <v>1934</v>
       </c>
       <c r="W542" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X542" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
       <c r="Y542" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z542" t="s">
-        <v>2370</v>
+        <v>2367</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43585,7 +43576,7 @@
         <v>1935</v>
       </c>
       <c r="W543" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43653,16 +43644,16 @@
         <v>1936</v>
       </c>
       <c r="W544" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="X544" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
       <c r="Y544" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
       <c r="Z544" t="s">
-        <v>2371</v>
+        <v>2368</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43730,7 +43721,7 @@
         <v>1937</v>
       </c>
       <c r="W545" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43798,7 +43789,7 @@
         <v>1938</v>
       </c>
       <c r="W546" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43866,7 +43857,7 @@
         <v>1939</v>
       </c>
       <c r="W547" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43934,7 +43925,7 @@
         <v>1940</v>
       </c>
       <c r="W548" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -44002,7 +43993,7 @@
         <v>1940</v>
       </c>
       <c r="W549" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44070,7 +44061,7 @@
         <v>1941</v>
       </c>
       <c r="W550" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44135,7 +44126,7 @@
         <v>1942</v>
       </c>
       <c r="W551" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44203,7 +44194,7 @@
         <v>1943</v>
       </c>
       <c r="W552" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44268,7 +44259,7 @@
         <v>1944</v>
       </c>
       <c r="W553" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44336,7 +44327,7 @@
         <v>1945</v>
       </c>
       <c r="W554" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44404,7 +44395,7 @@
         <v>1946</v>
       </c>
       <c r="W555" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44472,7 +44463,7 @@
         <v>1947</v>
       </c>
       <c r="W556" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44537,7 +44528,7 @@
         <v>1948</v>
       </c>
       <c r="W557" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44605,7 +44596,7 @@
         <v>1949</v>
       </c>
       <c r="W558" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44673,7 +44664,7 @@
         <v>1950</v>
       </c>
       <c r="W559" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44738,7 +44729,7 @@
         <v>1951</v>
       </c>
       <c r="W560" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44806,7 +44797,7 @@
         <v>1952</v>
       </c>
       <c r="W561" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44859,10 +44850,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R562">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S562" t="s">
         <v>1513</v>
@@ -44874,7 +44865,7 @@
         <v>1984</v>
       </c>
       <c r="W562" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44939,7 +44930,7 @@
         <v>1953</v>
       </c>
       <c r="W563" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -45004,7 +44995,7 @@
         <v>1954</v>
       </c>
       <c r="W564" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45072,7 +45063,7 @@
         <v>1955</v>
       </c>
       <c r="W565" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45140,7 +45131,7 @@
         <v>1956</v>
       </c>
       <c r="W566" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45208,7 +45199,7 @@
         <v>1957</v>
       </c>
       <c r="W567" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45276,7 +45267,7 @@
         <v>1958</v>
       </c>
       <c r="W568" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA568" t="b">
         <v>0</v>
@@ -45344,7 +45335,7 @@
         <v>1959</v>
       </c>
       <c r="W569" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45409,7 +45400,7 @@
         <v>1960</v>
       </c>
       <c r="W570" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45474,7 +45465,7 @@
         <v>1961</v>
       </c>
       <c r="W571" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45542,7 +45533,7 @@
         <v>1962</v>
       </c>
       <c r="W572" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45610,7 +45601,7 @@
         <v>1963</v>
       </c>
       <c r="W573" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45678,7 +45669,7 @@
         <v>1964</v>
       </c>
       <c r="W574" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45746,7 +45737,7 @@
         <v>1965</v>
       </c>
       <c r="W575" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -45814,7 +45805,7 @@
         <v>1966</v>
       </c>
       <c r="W576" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45882,7 +45873,7 @@
         <v>1966</v>
       </c>
       <c r="W577" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45950,7 +45941,7 @@
         <v>1967</v>
       </c>
       <c r="W578" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -46018,7 +46009,7 @@
         <v>1968</v>
       </c>
       <c r="W579" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46086,7 +46077,7 @@
         <v>1969</v>
       </c>
       <c r="W580" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46154,7 +46145,7 @@
         <v>1970</v>
       </c>
       <c r="W581" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46203,9 +46194,6 @@
       <c r="N582" s="1">
         <v>46265</v>
       </c>
-      <c r="O582" s="1">
-        <v>46240</v>
-      </c>
       <c r="P582" t="s">
         <v>1509</v>
       </c>
@@ -46224,11 +46212,8 @@
       <c r="U582" t="s">
         <v>1971</v>
       </c>
-      <c r="V582" t="s">
-        <v>1985</v>
-      </c>
       <c r="W582" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA582" t="b">
         <v>0</v>
@@ -46277,9 +46262,6 @@
       <c r="N583" s="1">
         <v>46265</v>
       </c>
-      <c r="O583" s="1">
-        <v>46252</v>
-      </c>
       <c r="P583" t="s">
         <v>1510</v>
       </c>
@@ -46298,11 +46280,8 @@
       <c r="U583" t="s">
         <v>1972</v>
       </c>
-      <c r="V583" t="s">
-        <v>1986</v>
-      </c>
       <c r="W583" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA583" t="b">
         <v>0</v>
@@ -46370,7 +46349,7 @@
         <v>1973</v>
       </c>
       <c r="W584" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46438,7 +46417,7 @@
         <v>1973</v>
       </c>
       <c r="W585" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46491,10 +46470,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="R586">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S586" t="s">
         <v>1513</v>
@@ -46503,10 +46482,10 @@
         <v>1514</v>
       </c>
       <c r="V586" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="W586" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46571,7 +46550,7 @@
         <v>1974</v>
       </c>
       <c r="W587" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA587" t="b">
         <v>0</v>
@@ -46624,10 +46603,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R588">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S588" t="s">
         <v>1514</v>
@@ -46639,10 +46618,10 @@
         <v>1975</v>
       </c>
       <c r="V588" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="W588" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46692,13 +46671,13 @@
         <v>46277</v>
       </c>
       <c r="O589" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="Q589">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="R589">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S589" t="s">
         <v>1514</v>
@@ -46710,10 +46689,10 @@
         <v>1976</v>
       </c>
       <c r="V589" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="W589" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA589" t="b">
         <v>1</v>
@@ -46778,7 +46757,7 @@
         <v>1977</v>
       </c>
       <c r="W590" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA590" t="b">
         <v>0</v>
@@ -46827,9 +46806,6 @@
       <c r="N591" s="1">
         <v>46257</v>
       </c>
-      <c r="O591" s="1">
-        <v>46251</v>
-      </c>
       <c r="P591" t="s">
         <v>1503</v>
       </c>
@@ -46848,11 +46824,8 @@
       <c r="U591" t="s">
         <v>1978</v>
       </c>
-      <c r="V591" t="s">
-        <v>1990</v>
-      </c>
       <c r="W591" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA591" t="b">
         <v>0</v>
@@ -46901,9 +46874,6 @@
       <c r="N592" s="1">
         <v>46277</v>
       </c>
-      <c r="O592" s="1">
-        <v>46254</v>
-      </c>
       <c r="Q592">
         <v>-46277</v>
       </c>
@@ -46919,11 +46889,8 @@
       <c r="U592" t="s">
         <v>1979</v>
       </c>
-      <c r="V592" t="s">
-        <v>1991</v>
-      </c>
       <c r="W592" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA592" t="b">
         <v>0</v>
@@ -46973,13 +46940,13 @@
         <v>46277</v>
       </c>
       <c r="O593" s="1">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="Q593">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="R593">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S593" t="s">
         <v>1514</v>
@@ -46991,10 +46958,10 @@
         <v>1980</v>
       </c>
       <c r="V593" t="s">
-        <v>1992</v>
+        <v>1988</v>
       </c>
       <c r="W593" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA593" t="b">
         <v>1</v>
@@ -47043,9 +47010,6 @@
       <c r="N594" s="1">
         <v>46278</v>
       </c>
-      <c r="O594" s="1">
-        <v>46249</v>
-      </c>
       <c r="Q594">
         <v>-46278</v>
       </c>
@@ -47061,11 +47025,8 @@
       <c r="U594" t="s">
         <v>1979</v>
       </c>
-      <c r="V594" t="s">
-        <v>1993</v>
-      </c>
       <c r="W594" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA594" t="b">
         <v>0</v>
@@ -47115,10 +47076,10 @@
         <v>46279</v>
       </c>
       <c r="Q595">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R595">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S595" t="s">
         <v>1514</v>
@@ -47127,10 +47088,10 @@
         <v>1513</v>
       </c>
       <c r="V595" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="W595" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA595" t="b">
         <v>1</v>
@@ -47180,10 +47141,10 @@
         <v>46259</v>
       </c>
       <c r="Q596">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R596">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S596" t="s">
         <v>1514</v>
@@ -47195,10 +47156,10 @@
         <v>1981</v>
       </c>
       <c r="V596" t="s">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="W596" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA596" t="b">
         <v>1</v>
@@ -47248,10 +47209,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R597">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S597" t="s">
         <v>1514</v>
@@ -47263,10 +47224,10 @@
         <v>1982</v>
       </c>
       <c r="V597" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="W597" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA597" t="b">
         <v>1</v>
@@ -47334,7 +47295,7 @@
         <v>1983</v>
       </c>
       <c r="W598" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA598" t="b">
         <v>0</v>
@@ -47384,10 +47345,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="R599">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S599" t="s">
         <v>1513</v>
@@ -47396,10 +47357,10 @@
         <v>1514</v>
       </c>
       <c r="V599" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="W599" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA599" t="b">
         <v>1</v>
@@ -47449,10 +47410,10 @@
         <v>46282</v>
       </c>
       <c r="Q600">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="R600">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S600" t="s">
         <v>1513</v>
@@ -47461,10 +47422,10 @@
         <v>1514</v>
       </c>
       <c r="V600" t="s">
-        <v>1998</v>
+        <v>1993</v>
       </c>
       <c r="W600" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA600" t="b">
         <v>1</v>
@@ -47514,10 +47475,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R601">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S601" t="s">
         <v>1513</v>
@@ -47526,7 +47487,7 @@
         <v>1514</v>
       </c>
       <c r="W601" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA601" t="b">
         <v>1</v>
@@ -47576,10 +47537,10 @@
         <v>46260</v>
       </c>
       <c r="Q602">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R602">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S602" t="s">
         <v>1513</v>
@@ -47587,8 +47548,11 @@
       <c r="T602" t="s">
         <v>1514</v>
       </c>
+      <c r="V602" t="s">
+        <v>1994</v>
+      </c>
       <c r="W602" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA602" t="b">
         <v>1</v>
@@ -47638,10 +47602,10 @@
         <v>46266</v>
       </c>
       <c r="Q603">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="R603">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S603" t="s">
         <v>1513</v>
@@ -47649,8 +47613,11 @@
       <c r="T603" t="s">
         <v>1514</v>
       </c>
+      <c r="V603" t="s">
+        <v>1995</v>
+      </c>
       <c r="W603" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="AA603" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7580" uniqueCount="2371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7579" uniqueCount="2370">
   <si>
     <t>om_emg</t>
   </si>
@@ -5983,31 +5983,28 @@
     <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08- ITEM AGUARDANDO DEFINIÇÃO DA COORDENADORIA QUANTO A EFETIVIDADE PARA APLICAÇÃO NA REFERIDA ANV.- CLA-13-08 - AT 685000002258</t>
   </si>
   <si>
-    <t>Temos somente 03 ea em STK, favor utilizar o estoque FAB para posterior devolução. ATZ RC 13/08 - FOI SOLICITADO O ATENDIMENTO COM ESTOQUE FAB -CLA-13-08 - AWB 127-5299 0173 DPE 18/08/2026 - ENTREGUE DIA 18/08/2026</t>
-  </si>
-  <si>
     <t>Temos no STK V1, material em separação, recibo 682/FAB/26 - atz rc 13/08 - MATERIAL ENVIADO VIA AWB 12752709016 - DPE 18/08/2026 - ENTREGUE DIA 18/08/2026</t>
   </si>
   <si>
     <t>foi solicitoado o atendimento com o estoque FAB. CLA-17-08 - o item PN superado 069-1025-25 não serve na ANV 2721 - temos 4ea na wiliam para reparo, já foi solicitado o DPE - OS 4 ITENS ESTÃO COM PROBLEMAS NO DISPAY. -FOI ENVIADO PARA O WIILIAM MAIS 3 UNS PARA REPARO - AINDA SEM DPE -CLA-20-08</t>
   </si>
   <si>
-    <t>Enviado para o Operador dia 17/08/26, AWB 127-5332-5834 - REZ</t>
-  </si>
-  <si>
     <t>ITEM FOI ENTREGUE PARA A FAB VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUECLA-17-08</t>
   </si>
   <si>
     <t>pedido no EPM E-C98-26061 -CLA-18-08 - em cotação no mercado. Validar se os alternados PN A-7512-24 ou MS25309-7512 ou M6363/2-2 atendem</t>
   </si>
   <si>
-    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08</t>
-  </si>
-  <si>
-    <t>Colocado pedido Textron WB0003128625 - direto para o Brasil</t>
-  </si>
-  <si>
-    <t>Colocado pedido no fornecedor - validando entrega em Miami</t>
+    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08 - AWB127-5408 8775- CLA-21-08</t>
+  </si>
+  <si>
+    <t>Colocado pedido Textron WB0003128625 - tracking 535477333011 - previsão de entrega 24/08</t>
+  </si>
+  <si>
+    <t>Colocado pedido no fornecedor S624333 - validando entrega em Miami - TEMOS 3 EA NO ESTOQUE DA BANT</t>
+  </si>
+  <si>
+    <t>Será atendido via estoque V1 JPA. Em processo de envio. ATZ 21/08</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7604,7 +7601,7 @@
         <v>1519</v>
       </c>
       <c r="W2" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7666,16 +7663,16 @@
         <v>1520</v>
       </c>
       <c r="W3" t="s">
+        <v>1997</v>
+      </c>
+      <c r="X3" t="s">
         <v>1998</v>
       </c>
-      <c r="X3" t="s">
-        <v>1999</v>
-      </c>
       <c r="Y3" t="s">
+        <v>2156</v>
+      </c>
+      <c r="Z3" t="s">
         <v>2157</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>2158</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7737,7 +7734,7 @@
         <v>1519</v>
       </c>
       <c r="W4" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7799,7 +7796,7 @@
         <v>1521</v>
       </c>
       <c r="W5" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7861,7 +7858,7 @@
         <v>1522</v>
       </c>
       <c r="W6" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7923,7 +7920,7 @@
         <v>1523</v>
       </c>
       <c r="W7" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -7985,7 +7982,7 @@
         <v>1524</v>
       </c>
       <c r="W8" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -8047,7 +8044,7 @@
         <v>1525</v>
       </c>
       <c r="W9" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8109,7 +8106,7 @@
         <v>1526</v>
       </c>
       <c r="W10" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8171,7 +8168,7 @@
         <v>1527</v>
       </c>
       <c r="W11" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8233,7 +8230,7 @@
         <v>1528</v>
       </c>
       <c r="W12" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8295,7 +8292,7 @@
         <v>1524</v>
       </c>
       <c r="W13" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8357,16 +8354,16 @@
         <v>1529</v>
       </c>
       <c r="W14" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X14" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="Y14" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z14" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8425,7 +8422,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8490,7 +8487,7 @@
         <v>1530</v>
       </c>
       <c r="W16" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8552,7 +8549,7 @@
         <v>1531</v>
       </c>
       <c r="W17" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8614,7 +8611,7 @@
         <v>1522</v>
       </c>
       <c r="W18" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8676,7 +8673,7 @@
         <v>1522</v>
       </c>
       <c r="W19" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8738,7 +8735,7 @@
         <v>1532</v>
       </c>
       <c r="W20" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8800,7 +8797,7 @@
         <v>1533</v>
       </c>
       <c r="W21" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8862,7 +8859,7 @@
         <v>1533</v>
       </c>
       <c r="W22" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8924,7 +8921,7 @@
         <v>1534</v>
       </c>
       <c r="W23" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -8983,7 +8980,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -9042,7 +9039,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9104,7 +9101,7 @@
         <v>1522</v>
       </c>
       <c r="W26" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9163,7 +9160,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9222,7 +9219,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9284,7 +9281,7 @@
         <v>1535</v>
       </c>
       <c r="W29" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9343,7 +9340,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9405,7 +9402,7 @@
         <v>1536</v>
       </c>
       <c r="W31" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9467,7 +9464,7 @@
         <v>1537</v>
       </c>
       <c r="W32" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9529,7 +9526,7 @@
         <v>1538</v>
       </c>
       <c r="W33" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9591,7 +9588,7 @@
         <v>1539</v>
       </c>
       <c r="W34" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9653,7 +9650,7 @@
         <v>1540</v>
       </c>
       <c r="W35" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9715,7 +9712,7 @@
         <v>1536</v>
       </c>
       <c r="W36" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9777,7 +9774,7 @@
         <v>1541</v>
       </c>
       <c r="W37" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9839,7 +9836,7 @@
         <v>1519</v>
       </c>
       <c r="W38" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9901,7 +9898,7 @@
         <v>1538</v>
       </c>
       <c r="W39" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9963,7 +9960,7 @@
         <v>1542</v>
       </c>
       <c r="W40" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -10025,7 +10022,7 @@
         <v>1543</v>
       </c>
       <c r="W41" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10087,16 +10084,16 @@
         <v>1544</v>
       </c>
       <c r="W42" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X42" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="Y42" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z42" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10158,7 +10155,7 @@
         <v>1538</v>
       </c>
       <c r="W43" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10220,7 +10217,7 @@
         <v>1545</v>
       </c>
       <c r="W44" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10282,7 +10279,7 @@
         <v>1538</v>
       </c>
       <c r="W45" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10344,7 +10341,7 @@
         <v>1538</v>
       </c>
       <c r="W46" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10406,7 +10403,7 @@
         <v>1546</v>
       </c>
       <c r="W47" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10468,7 +10465,7 @@
         <v>1547</v>
       </c>
       <c r="W48" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10530,7 +10527,7 @@
         <v>1548</v>
       </c>
       <c r="W49" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10592,7 +10589,7 @@
         <v>1549</v>
       </c>
       <c r="W50" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10654,7 +10651,7 @@
         <v>1550</v>
       </c>
       <c r="W51" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10716,7 +10713,7 @@
         <v>1539</v>
       </c>
       <c r="W52" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10778,7 +10775,7 @@
         <v>1533</v>
       </c>
       <c r="W53" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10840,7 +10837,7 @@
         <v>1533</v>
       </c>
       <c r="W54" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10902,7 +10899,7 @@
         <v>1533</v>
       </c>
       <c r="W55" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10964,7 +10961,7 @@
         <v>1551</v>
       </c>
       <c r="W56" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -11026,7 +11023,7 @@
         <v>1552</v>
       </c>
       <c r="W57" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11088,16 +11085,16 @@
         <v>1553</v>
       </c>
       <c r="W58" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X58" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="Y58" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z58" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11159,7 +11156,7 @@
         <v>1554</v>
       </c>
       <c r="W59" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11221,7 +11218,7 @@
         <v>1555</v>
       </c>
       <c r="W60" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11283,7 +11280,7 @@
         <v>1533</v>
       </c>
       <c r="W61" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11345,7 +11342,7 @@
         <v>1556</v>
       </c>
       <c r="W62" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11404,7 +11401,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11463,7 +11460,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11522,7 +11519,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11581,7 +11578,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11640,7 +11637,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11699,7 +11696,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11761,7 +11758,7 @@
         <v>1557</v>
       </c>
       <c r="W69" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11823,7 +11820,7 @@
         <v>1555</v>
       </c>
       <c r="W70" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11885,7 +11882,7 @@
         <v>1540</v>
       </c>
       <c r="W71" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11947,7 +11944,7 @@
         <v>1558</v>
       </c>
       <c r="W72" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -12009,7 +12006,7 @@
         <v>1559</v>
       </c>
       <c r="W73" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12071,16 +12068,16 @@
         <v>1560</v>
       </c>
       <c r="W74" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X74" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="Y74" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z74" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12142,16 +12139,16 @@
         <v>1561</v>
       </c>
       <c r="W75" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X75" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="Y75" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z75" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12213,7 +12210,7 @@
         <v>1540</v>
       </c>
       <c r="W76" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12275,7 +12272,7 @@
         <v>1540</v>
       </c>
       <c r="W77" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12337,10 +12334,10 @@
         <v>1562</v>
       </c>
       <c r="W78" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="Z78" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12405,7 +12402,7 @@
         <v>1563</v>
       </c>
       <c r="W79" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12464,7 +12461,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12523,7 +12520,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12585,7 +12582,7 @@
         <v>1564</v>
       </c>
       <c r="W82" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12647,7 +12644,7 @@
         <v>1565</v>
       </c>
       <c r="W83" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12709,7 +12706,7 @@
         <v>1566</v>
       </c>
       <c r="W84" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12768,7 +12765,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12830,7 +12827,7 @@
         <v>1567</v>
       </c>
       <c r="W86" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12892,7 +12889,7 @@
         <v>1568</v>
       </c>
       <c r="W87" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12954,7 +12951,7 @@
         <v>1568</v>
       </c>
       <c r="W88" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -13016,7 +13013,7 @@
         <v>1533</v>
       </c>
       <c r="W89" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13078,16 +13075,16 @@
         <v>1569</v>
       </c>
       <c r="W90" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X90" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="Y90" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z90" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13149,16 +13146,16 @@
         <v>1570</v>
       </c>
       <c r="W91" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X91" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="Y91" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z91" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13220,7 +13217,7 @@
         <v>1571</v>
       </c>
       <c r="W92" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13282,7 +13279,7 @@
         <v>1572</v>
       </c>
       <c r="W93" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13344,7 +13341,7 @@
         <v>1572</v>
       </c>
       <c r="W94" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13406,7 +13403,7 @@
         <v>1573</v>
       </c>
       <c r="W95" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13468,16 +13465,16 @@
         <v>1574</v>
       </c>
       <c r="W96" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X96" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="Y96" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z96" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13539,7 +13536,7 @@
         <v>1575</v>
       </c>
       <c r="W97" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13601,7 +13598,7 @@
         <v>1576</v>
       </c>
       <c r="W98" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13663,7 +13660,7 @@
         <v>1577</v>
       </c>
       <c r="W99" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13725,7 +13722,7 @@
         <v>1578</v>
       </c>
       <c r="W100" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13787,16 +13784,16 @@
         <v>1579</v>
       </c>
       <c r="W101" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X101" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="Y101" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z101" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13858,7 +13855,7 @@
         <v>1580</v>
       </c>
       <c r="W102" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13920,7 +13917,7 @@
         <v>1580</v>
       </c>
       <c r="W103" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -13982,7 +13979,7 @@
         <v>1581</v>
       </c>
       <c r="W104" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -14044,16 +14041,16 @@
         <v>1582</v>
       </c>
       <c r="W105" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X105" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="Y105" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z105" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14115,16 +14112,16 @@
         <v>1583</v>
       </c>
       <c r="W106" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X106" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="Y106" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z106" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14186,7 +14183,7 @@
         <v>1584</v>
       </c>
       <c r="W107" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14248,16 +14245,16 @@
         <v>1585</v>
       </c>
       <c r="W108" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X108" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="Y108" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z108" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14319,16 +14316,16 @@
         <v>1586</v>
       </c>
       <c r="W109" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X109" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="Y109" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z109" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14387,7 +14384,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14449,16 +14446,16 @@
         <v>1587</v>
       </c>
       <c r="W111" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X111" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="Y111" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z111" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14520,16 +14517,16 @@
         <v>1588</v>
       </c>
       <c r="W112" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X112" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="Y112" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z112" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14591,16 +14588,16 @@
         <v>1589</v>
       </c>
       <c r="W113" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X113" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="Y113" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z113" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14662,16 +14659,16 @@
         <v>1590</v>
       </c>
       <c r="W114" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X114" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="Y114" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z114" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14733,16 +14730,16 @@
         <v>1586</v>
       </c>
       <c r="W115" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X115" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="Y115" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z115" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14804,16 +14801,16 @@
         <v>1586</v>
       </c>
       <c r="W116" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X116" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="Y116" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z116" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14875,16 +14872,16 @@
         <v>1591</v>
       </c>
       <c r="W117" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X117" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="Y117" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z117" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14946,16 +14943,16 @@
         <v>1592</v>
       </c>
       <c r="W118" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X118" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="Y118" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z118" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -15017,7 +15014,7 @@
         <v>1593</v>
       </c>
       <c r="W119" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15079,16 +15076,16 @@
         <v>1594</v>
       </c>
       <c r="W120" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X120" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y120" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z120" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15150,16 +15147,16 @@
         <v>1594</v>
       </c>
       <c r="W121" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X121" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y121" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z121" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15221,16 +15218,16 @@
         <v>1594</v>
       </c>
       <c r="W122" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X122" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y122" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z122" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15292,16 +15289,16 @@
         <v>1594</v>
       </c>
       <c r="W123" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X123" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y123" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z123" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15363,16 +15360,16 @@
         <v>1594</v>
       </c>
       <c r="W124" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X124" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y124" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z124" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15434,16 +15431,16 @@
         <v>1594</v>
       </c>
       <c r="W125" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X125" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y125" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z125" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15505,16 +15502,16 @@
         <v>1594</v>
       </c>
       <c r="W126" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X126" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y126" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z126" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15576,16 +15573,16 @@
         <v>1595</v>
       </c>
       <c r="W127" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X127" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="Y127" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z127" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15647,16 +15644,16 @@
         <v>1596</v>
       </c>
       <c r="W128" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X128" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="Y128" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z128" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15718,16 +15715,16 @@
         <v>1594</v>
       </c>
       <c r="W129" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X129" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y129" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z129" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15789,16 +15786,16 @@
         <v>1594</v>
       </c>
       <c r="W130" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X130" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y130" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z130" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15860,7 +15857,7 @@
         <v>1597</v>
       </c>
       <c r="W131" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15919,7 +15916,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15978,7 +15975,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -16040,16 +16037,16 @@
         <v>1594</v>
       </c>
       <c r="W134" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X134" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y134" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z134" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16111,16 +16108,16 @@
         <v>1594</v>
       </c>
       <c r="W135" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X135" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y135" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z135" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16182,7 +16179,7 @@
         <v>1593</v>
       </c>
       <c r="W136" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16241,7 +16238,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16303,16 +16300,16 @@
         <v>1598</v>
       </c>
       <c r="W138" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X138" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="Y138" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z138" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16374,16 +16371,16 @@
         <v>1586</v>
       </c>
       <c r="W139" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X139" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="Y139" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z139" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16445,16 +16442,16 @@
         <v>1594</v>
       </c>
       <c r="W140" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X140" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y140" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z140" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16513,7 +16510,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16572,7 +16569,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16634,16 +16631,16 @@
         <v>1599</v>
       </c>
       <c r="W143" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X143" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="Y143" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z143" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16705,16 +16702,16 @@
         <v>1600</v>
       </c>
       <c r="W144" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X144" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="Y144" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z144" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16776,16 +16773,16 @@
         <v>1601</v>
       </c>
       <c r="W145" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X145" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Y145" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z145" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16847,16 +16844,16 @@
         <v>1602</v>
       </c>
       <c r="W146" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X146" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y146" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z146" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16915,7 +16912,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16977,7 +16974,7 @@
         <v>1603</v>
       </c>
       <c r="W148" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -17039,16 +17036,16 @@
         <v>1604</v>
       </c>
       <c r="W149" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X149" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="Y149" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z149" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17110,7 +17107,7 @@
         <v>1605</v>
       </c>
       <c r="W150" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17172,16 +17169,16 @@
         <v>1606</v>
       </c>
       <c r="W151" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X151" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="Y151" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z151" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17243,7 +17240,7 @@
         <v>1605</v>
       </c>
       <c r="W152" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17305,7 +17302,7 @@
         <v>1603</v>
       </c>
       <c r="W153" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17367,7 +17364,7 @@
         <v>1605</v>
       </c>
       <c r="W154" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17429,7 +17426,7 @@
         <v>1605</v>
       </c>
       <c r="W155" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17491,16 +17488,16 @@
         <v>1607</v>
       </c>
       <c r="W156" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X156" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="Y156" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z156" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17562,7 +17559,7 @@
         <v>1603</v>
       </c>
       <c r="W157" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17624,16 +17621,16 @@
         <v>1608</v>
       </c>
       <c r="W158" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X158" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y158" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z158" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17695,16 +17692,16 @@
         <v>1609</v>
       </c>
       <c r="W159" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X159" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="Y159" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z159" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17766,16 +17763,16 @@
         <v>1608</v>
       </c>
       <c r="W160" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X160" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y160" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z160" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17837,16 +17834,16 @@
         <v>1608</v>
       </c>
       <c r="W161" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X161" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y161" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z161" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17908,16 +17905,16 @@
         <v>1608</v>
       </c>
       <c r="W162" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X162" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y162" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z162" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17979,16 +17976,16 @@
         <v>1610</v>
       </c>
       <c r="W163" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X163" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="Y163" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z163" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -18050,16 +18047,16 @@
         <v>1611</v>
       </c>
       <c r="W164" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X164" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="Y164" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z164" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18121,16 +18118,16 @@
         <v>1612</v>
       </c>
       <c r="W165" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X165" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="Y165" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z165" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18192,16 +18189,16 @@
         <v>1613</v>
       </c>
       <c r="W166" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X166" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="Y166" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z166" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18263,16 +18260,16 @@
         <v>1591</v>
       </c>
       <c r="W167" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X167" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="Y167" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z167" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18334,16 +18331,16 @@
         <v>1594</v>
       </c>
       <c r="W168" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X168" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y168" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z168" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18405,7 +18402,7 @@
         <v>1614</v>
       </c>
       <c r="W169" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18467,16 +18464,16 @@
         <v>1594</v>
       </c>
       <c r="W170" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X170" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y170" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z170" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18538,16 +18535,16 @@
         <v>1615</v>
       </c>
       <c r="W171" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X171" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y171" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z171" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18609,16 +18606,16 @@
         <v>1616</v>
       </c>
       <c r="W172" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X172" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="Y172" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z172" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18680,16 +18677,16 @@
         <v>1617</v>
       </c>
       <c r="W173" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X173" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="Y173" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z173" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18751,16 +18748,16 @@
         <v>1618</v>
       </c>
       <c r="W174" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X174" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="Y174" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z174" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18822,16 +18819,16 @@
         <v>1619</v>
       </c>
       <c r="W175" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X175" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="Y175" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z175" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18893,16 +18890,16 @@
         <v>1620</v>
       </c>
       <c r="W176" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X176" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="Y176" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z176" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18964,7 +18961,7 @@
         <v>1614</v>
       </c>
       <c r="W177" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -19026,16 +19023,16 @@
         <v>1621</v>
       </c>
       <c r="W178" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X178" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="Y178" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z178" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19097,16 +19094,16 @@
         <v>1622</v>
       </c>
       <c r="W179" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X179" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y179" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z179" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19168,7 +19165,7 @@
         <v>1623</v>
       </c>
       <c r="W180" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19230,16 +19227,16 @@
         <v>1624</v>
       </c>
       <c r="W181" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X181" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="Y181" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z181" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19301,16 +19298,16 @@
         <v>1624</v>
       </c>
       <c r="W182" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X182" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="Y182" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z182" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19372,16 +19369,16 @@
         <v>1625</v>
       </c>
       <c r="W183" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X183" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="Y183" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z183" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19443,16 +19440,16 @@
         <v>1626</v>
       </c>
       <c r="W184" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X184" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="Y184" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z184" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19514,16 +19511,16 @@
         <v>1627</v>
       </c>
       <c r="W185" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X185" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="Y185" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z185" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19585,7 +19582,7 @@
         <v>1628</v>
       </c>
       <c r="W186" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19647,7 +19644,7 @@
         <v>1629</v>
       </c>
       <c r="W187" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19709,7 +19706,7 @@
         <v>1630</v>
       </c>
       <c r="W188" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19771,7 +19768,7 @@
         <v>1631</v>
       </c>
       <c r="W189" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19833,16 +19830,16 @@
         <v>1632</v>
       </c>
       <c r="W190" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X190" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="Y190" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z190" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19904,16 +19901,16 @@
         <v>1633</v>
       </c>
       <c r="W191" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X191" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="Y191" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z191" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19975,7 +19972,7 @@
         <v>1634</v>
       </c>
       <c r="W192" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -20037,7 +20034,7 @@
         <v>1634</v>
       </c>
       <c r="W193" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20099,16 +20096,16 @@
         <v>1635</v>
       </c>
       <c r="W194" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X194" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="Y194" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z194" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20170,16 +20167,16 @@
         <v>1636</v>
       </c>
       <c r="W195" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X195" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y195" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z195" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20241,16 +20238,16 @@
         <v>1637</v>
       </c>
       <c r="W196" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X196" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="Y196" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z196" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20312,16 +20309,16 @@
         <v>1633</v>
       </c>
       <c r="W197" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X197" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="Y197" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z197" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20383,7 +20380,7 @@
         <v>1638</v>
       </c>
       <c r="W198" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20445,7 +20442,7 @@
         <v>1639</v>
       </c>
       <c r="W199" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20507,16 +20504,16 @@
         <v>1640</v>
       </c>
       <c r="W200" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X200" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="Y200" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z200" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20578,16 +20575,16 @@
         <v>1640</v>
       </c>
       <c r="W201" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X201" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="Y201" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z201" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20649,16 +20646,16 @@
         <v>1641</v>
       </c>
       <c r="W202" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X202" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="Y202" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z202" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20720,16 +20717,16 @@
         <v>1642</v>
       </c>
       <c r="W203" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X203" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="Y203" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z203" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20791,16 +20788,16 @@
         <v>1643</v>
       </c>
       <c r="W204" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X204" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="Y204" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z204" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20862,16 +20859,16 @@
         <v>1644</v>
       </c>
       <c r="W205" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X205" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="Y205" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z205" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20933,16 +20930,16 @@
         <v>1645</v>
       </c>
       <c r="W206" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X206" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="Y206" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z206" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -21004,16 +21001,16 @@
         <v>1646</v>
       </c>
       <c r="W207" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X207" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="Y207" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z207" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21075,16 +21072,16 @@
         <v>1647</v>
       </c>
       <c r="W208" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X208" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="Y208" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z208" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21146,7 +21143,7 @@
         <v>1648</v>
       </c>
       <c r="W209" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21208,16 +21205,16 @@
         <v>1649</v>
       </c>
       <c r="W210" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X210" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="Y210" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z210" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21279,16 +21276,16 @@
         <v>1650</v>
       </c>
       <c r="W211" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X211" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="Y211" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z211" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21350,16 +21347,16 @@
         <v>1651</v>
       </c>
       <c r="W212" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X212" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="Y212" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z212" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21421,16 +21418,16 @@
         <v>1652</v>
       </c>
       <c r="W213" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X213" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="Y213" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z213" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21492,7 +21489,7 @@
         <v>1653</v>
       </c>
       <c r="W214" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21554,16 +21551,16 @@
         <v>1618</v>
       </c>
       <c r="W215" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X215" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="Y215" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z215" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21625,16 +21622,16 @@
         <v>1654</v>
       </c>
       <c r="W216" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X216" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="Y216" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z216" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21696,7 +21693,7 @@
         <v>1655</v>
       </c>
       <c r="W217" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21758,16 +21755,16 @@
         <v>1656</v>
       </c>
       <c r="W218" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X218" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="Y218" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z218" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21829,16 +21826,16 @@
         <v>1657</v>
       </c>
       <c r="W219" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X219" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="Y219" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z219" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21900,7 +21897,7 @@
         <v>1658</v>
       </c>
       <c r="W220" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21962,7 +21959,7 @@
         <v>1659</v>
       </c>
       <c r="W221" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -22024,7 +22021,7 @@
         <v>1658</v>
       </c>
       <c r="W222" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22086,7 +22083,7 @@
         <v>1659</v>
       </c>
       <c r="W223" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22148,16 +22145,16 @@
         <v>1660</v>
       </c>
       <c r="W224" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X224" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="Y224" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z224" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22219,16 +22216,16 @@
         <v>1661</v>
       </c>
       <c r="W225" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X225" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="Y225" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z225" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22290,7 +22287,7 @@
         <v>1662</v>
       </c>
       <c r="W226" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22352,7 +22349,7 @@
         <v>1663</v>
       </c>
       <c r="W227" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22414,7 +22411,7 @@
         <v>1664</v>
       </c>
       <c r="W228" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22476,16 +22473,16 @@
         <v>1665</v>
       </c>
       <c r="W229" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X229" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="Y229" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z229" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22547,16 +22544,16 @@
         <v>1666</v>
       </c>
       <c r="W230" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X230" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="Y230" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z230" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22618,16 +22615,16 @@
         <v>1667</v>
       </c>
       <c r="W231" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X231" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="Y231" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z231" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22692,16 +22689,16 @@
         <v>1668</v>
       </c>
       <c r="W232" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X232" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="Y232" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z232" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22763,16 +22760,16 @@
         <v>1669</v>
       </c>
       <c r="W233" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X233" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="Y233" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z233" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22834,16 +22831,16 @@
         <v>1670</v>
       </c>
       <c r="W234" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X234" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="Y234" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z234" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22905,16 +22902,16 @@
         <v>1670</v>
       </c>
       <c r="W235" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X235" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="Y235" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z235" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22976,16 +22973,16 @@
         <v>1671</v>
       </c>
       <c r="W236" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X236" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="Y236" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z236" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -23047,7 +23044,7 @@
         <v>1672</v>
       </c>
       <c r="W237" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23109,7 +23106,7 @@
         <v>1673</v>
       </c>
       <c r="W238" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23171,16 +23168,16 @@
         <v>1674</v>
       </c>
       <c r="W239" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X239" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="Y239" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z239" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23242,16 +23239,16 @@
         <v>1675</v>
       </c>
       <c r="W240" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X240" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="Y240" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z240" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23313,7 +23310,7 @@
         <v>1676</v>
       </c>
       <c r="W241" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23375,16 +23372,16 @@
         <v>1677</v>
       </c>
       <c r="W242" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X242" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="Y242" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z242" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23446,16 +23443,16 @@
         <v>1678</v>
       </c>
       <c r="W243" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X243" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="Y243" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z243" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23517,16 +23514,16 @@
         <v>1677</v>
       </c>
       <c r="W244" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X244" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="Y244" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z244" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23588,16 +23585,16 @@
         <v>1679</v>
       </c>
       <c r="W245" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X245" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="Y245" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z245" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23659,16 +23656,16 @@
         <v>1678</v>
       </c>
       <c r="W246" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X246" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="Y246" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z246" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23730,16 +23727,16 @@
         <v>1679</v>
       </c>
       <c r="W247" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X247" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="Y247" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z247" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23801,16 +23798,16 @@
         <v>1680</v>
       </c>
       <c r="W248" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X248" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="Y248" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z248" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23872,16 +23869,16 @@
         <v>1670</v>
       </c>
       <c r="W249" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X249" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="Y249" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z249" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23943,7 +23940,7 @@
         <v>1681</v>
       </c>
       <c r="W250" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -24005,7 +24002,7 @@
         <v>1682</v>
       </c>
       <c r="W251" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -24067,16 +24064,16 @@
         <v>1683</v>
       </c>
       <c r="W252" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X252" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y252" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z252" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24138,16 +24135,16 @@
         <v>1684</v>
       </c>
       <c r="W253" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X253" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="Y253" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z253" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24209,7 +24206,7 @@
         <v>1685</v>
       </c>
       <c r="W254" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24271,16 +24268,16 @@
         <v>1686</v>
       </c>
       <c r="W255" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X255" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Y255" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z255" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24342,7 +24339,7 @@
         <v>1687</v>
       </c>
       <c r="W256" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24407,7 +24404,7 @@
         <v>1688</v>
       </c>
       <c r="W257" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24469,7 +24466,7 @@
         <v>1689</v>
       </c>
       <c r="W258" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24531,7 +24528,7 @@
         <v>1689</v>
       </c>
       <c r="W259" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24593,7 +24590,7 @@
         <v>1690</v>
       </c>
       <c r="W260" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24655,16 +24652,16 @@
         <v>1691</v>
       </c>
       <c r="W261" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X261" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y261" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z261" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24726,13 +24723,13 @@
         <v>1692</v>
       </c>
       <c r="W262" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X262" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="Y262" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24794,16 +24791,16 @@
         <v>1693</v>
       </c>
       <c r="W263" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X263" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="Y263" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z263" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24865,7 +24862,7 @@
         <v>1694</v>
       </c>
       <c r="W264" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24927,7 +24924,7 @@
         <v>1694</v>
       </c>
       <c r="W265" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -24989,7 +24986,7 @@
         <v>1695</v>
       </c>
       <c r="W266" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -25051,16 +25048,16 @@
         <v>1696</v>
       </c>
       <c r="W267" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X267" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="Y267" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z267" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25122,16 +25119,16 @@
         <v>1697</v>
       </c>
       <c r="W268" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X268" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="Y268" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z268" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25193,7 +25190,7 @@
         <v>1538</v>
       </c>
       <c r="W269" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25255,7 +25252,7 @@
         <v>1698</v>
       </c>
       <c r="W270" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25317,7 +25314,7 @@
         <v>1699</v>
       </c>
       <c r="W271" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25379,16 +25376,16 @@
         <v>1700</v>
       </c>
       <c r="W272" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X272" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="Y272" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z272" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25447,7 +25444,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25509,7 +25506,7 @@
         <v>1701</v>
       </c>
       <c r="W274" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25568,7 +25565,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25630,7 +25627,7 @@
         <v>1702</v>
       </c>
       <c r="W276" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25692,7 +25689,7 @@
         <v>1703</v>
       </c>
       <c r="W277" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25754,16 +25751,16 @@
         <v>1704</v>
       </c>
       <c r="W278" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X278" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="Y278" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z278" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25825,16 +25822,16 @@
         <v>1705</v>
       </c>
       <c r="W279" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X279" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="Y279" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z279" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25896,16 +25893,16 @@
         <v>1705</v>
       </c>
       <c r="W280" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X280" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="Y280" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z280" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25967,16 +25964,16 @@
         <v>1706</v>
       </c>
       <c r="W281" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X281" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="Y281" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z281" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -26038,7 +26035,7 @@
         <v>1707</v>
       </c>
       <c r="W282" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26100,7 +26097,7 @@
         <v>1708</v>
       </c>
       <c r="W283" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26162,7 +26159,7 @@
         <v>1709</v>
       </c>
       <c r="W284" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26224,16 +26221,16 @@
         <v>1710</v>
       </c>
       <c r="W285" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X285" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="Y285" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z285" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26295,7 +26292,7 @@
         <v>1711</v>
       </c>
       <c r="W286" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26357,16 +26354,16 @@
         <v>1705</v>
       </c>
       <c r="W287" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X287" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="Y287" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z287" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26428,16 +26425,16 @@
         <v>1712</v>
       </c>
       <c r="W288" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X288" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="Y288" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z288" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26499,7 +26496,7 @@
         <v>1713</v>
       </c>
       <c r="W289" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26561,16 +26558,16 @@
         <v>1714</v>
       </c>
       <c r="W290" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X290" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="Y290" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z290" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26632,16 +26629,16 @@
         <v>1715</v>
       </c>
       <c r="W291" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X291" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="Y291" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z291" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26703,7 +26700,7 @@
         <v>1716</v>
       </c>
       <c r="W292" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26762,7 +26759,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26824,7 +26821,7 @@
         <v>1717</v>
       </c>
       <c r="W294" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26886,7 +26883,7 @@
         <v>1718</v>
       </c>
       <c r="W295" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26948,7 +26945,7 @@
         <v>1719</v>
       </c>
       <c r="W296" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -27010,13 +27007,13 @@
         <v>1720</v>
       </c>
       <c r="W297" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X297" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="Z297" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27078,7 +27075,7 @@
         <v>1721</v>
       </c>
       <c r="W298" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27140,7 +27137,7 @@
         <v>1722</v>
       </c>
       <c r="W299" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27202,7 +27199,7 @@
         <v>1723</v>
       </c>
       <c r="W300" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27264,7 +27261,7 @@
         <v>1724</v>
       </c>
       <c r="W301" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27326,7 +27323,7 @@
         <v>1725</v>
       </c>
       <c r="W302" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27388,16 +27385,16 @@
         <v>1726</v>
       </c>
       <c r="W303" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X303" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="Y303" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z303" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27459,7 +27456,7 @@
         <v>1727</v>
       </c>
       <c r="W304" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27521,7 +27518,7 @@
         <v>1728</v>
       </c>
       <c r="W305" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27583,7 +27580,7 @@
         <v>1729</v>
       </c>
       <c r="W306" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27645,7 +27642,7 @@
         <v>1730</v>
       </c>
       <c r="W307" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27707,7 +27704,7 @@
         <v>1723</v>
       </c>
       <c r="W308" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27769,7 +27766,7 @@
         <v>1731</v>
       </c>
       <c r="W309" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27831,7 +27828,7 @@
         <v>1732</v>
       </c>
       <c r="W310" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27893,7 +27890,7 @@
         <v>1733</v>
       </c>
       <c r="W311" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27955,7 +27952,7 @@
         <v>1734</v>
       </c>
       <c r="W312" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -28017,7 +28014,7 @@
         <v>1735</v>
       </c>
       <c r="W313" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28079,7 +28076,7 @@
         <v>1736</v>
       </c>
       <c r="W314" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28141,7 +28138,7 @@
         <v>1737</v>
       </c>
       <c r="W315" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28203,7 +28200,7 @@
         <v>1738</v>
       </c>
       <c r="W316" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28265,7 +28262,7 @@
         <v>1739</v>
       </c>
       <c r="W317" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28327,7 +28324,7 @@
         <v>1740</v>
       </c>
       <c r="W318" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28389,7 +28386,7 @@
         <v>1741</v>
       </c>
       <c r="W319" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28448,13 +28445,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X320" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="Z320" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28513,7 +28510,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28572,7 +28569,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28631,7 +28628,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28693,7 +28690,7 @@
         <v>1742</v>
       </c>
       <c r="W324" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28755,7 +28752,7 @@
         <v>1743</v>
       </c>
       <c r="W325" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28817,7 +28814,7 @@
         <v>1744</v>
       </c>
       <c r="W326" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28879,7 +28876,7 @@
         <v>1745</v>
       </c>
       <c r="W327" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28938,7 +28935,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -29000,7 +28997,7 @@
         <v>1745</v>
       </c>
       <c r="W329" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -29062,7 +29059,7 @@
         <v>1746</v>
       </c>
       <c r="W330" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29124,7 +29121,7 @@
         <v>1747</v>
       </c>
       <c r="W331" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29186,7 +29183,7 @@
         <v>1747</v>
       </c>
       <c r="W332" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29248,7 +29245,7 @@
         <v>1748</v>
       </c>
       <c r="W333" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29310,7 +29307,7 @@
         <v>1749</v>
       </c>
       <c r="W334" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29372,7 +29369,7 @@
         <v>1750</v>
       </c>
       <c r="W335" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29431,13 +29428,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X336" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="Z336" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29499,7 +29496,7 @@
         <v>1751</v>
       </c>
       <c r="W337" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29561,13 +29558,13 @@
         <v>1752</v>
       </c>
       <c r="W338" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X338" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="Z338" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29629,13 +29626,13 @@
         <v>1753</v>
       </c>
       <c r="W339" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X339" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="Z339" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29697,7 +29694,7 @@
         <v>1754</v>
       </c>
       <c r="W340" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29759,7 +29756,7 @@
         <v>1755</v>
       </c>
       <c r="W341" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29821,10 +29818,10 @@
         <v>1756</v>
       </c>
       <c r="W342" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X342" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29886,7 +29883,7 @@
         <v>1757</v>
       </c>
       <c r="W343" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29948,7 +29945,7 @@
         <v>1758</v>
       </c>
       <c r="W344" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -30010,13 +30007,13 @@
         <v>1759</v>
       </c>
       <c r="W345" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X345" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="Z345" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30078,7 +30075,7 @@
         <v>1723</v>
       </c>
       <c r="W346" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30140,7 +30137,7 @@
         <v>1760</v>
       </c>
       <c r="W347" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30202,16 +30199,16 @@
         <v>1761</v>
       </c>
       <c r="W348" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X348" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="Y348" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z348" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30276,13 +30273,13 @@
         <v>1762</v>
       </c>
       <c r="W349" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X349" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="Z349" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30344,7 +30341,7 @@
         <v>1763</v>
       </c>
       <c r="W350" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30406,16 +30403,16 @@
         <v>1764</v>
       </c>
       <c r="W351" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X351" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="Y351" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z351" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30477,13 +30474,13 @@
         <v>1765</v>
       </c>
       <c r="W352" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X352" t="s">
         <v>1765</v>
       </c>
       <c r="Z352" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30545,16 +30542,16 @@
         <v>1766</v>
       </c>
       <c r="W353" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X353" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Y353" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z353" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30616,7 +30613,7 @@
         <v>1767</v>
       </c>
       <c r="W354" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30678,7 +30675,7 @@
         <v>1768</v>
       </c>
       <c r="W355" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30737,7 +30734,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30796,7 +30793,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30855,7 +30852,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30917,7 +30914,7 @@
         <v>1769</v>
       </c>
       <c r="W359" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -30982,7 +30979,7 @@
         <v>1770</v>
       </c>
       <c r="W360" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -31047,7 +31044,7 @@
         <v>1771</v>
       </c>
       <c r="W361" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31109,16 +31106,16 @@
         <v>1772</v>
       </c>
       <c r="W362" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X362" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="Y362" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z362" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31180,16 +31177,16 @@
         <v>1773</v>
       </c>
       <c r="W363" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X363" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="Y363" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z363" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31251,7 +31248,7 @@
         <v>1774</v>
       </c>
       <c r="W364" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31313,7 +31310,7 @@
         <v>1775</v>
       </c>
       <c r="W365" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31378,7 +31375,7 @@
         <v>1776</v>
       </c>
       <c r="W366" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31440,7 +31437,7 @@
         <v>1777</v>
       </c>
       <c r="W367" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31502,7 +31499,7 @@
         <v>1778</v>
       </c>
       <c r="W368" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31567,13 +31564,13 @@
         <v>1779</v>
       </c>
       <c r="W369" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X369" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="Z369" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31635,7 +31632,7 @@
         <v>1780</v>
       </c>
       <c r="W370" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31697,16 +31694,16 @@
         <v>1781</v>
       </c>
       <c r="W371" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X371" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="Y371" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z371" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31771,7 +31768,7 @@
         <v>1782</v>
       </c>
       <c r="W372" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31836,16 +31833,16 @@
         <v>1783</v>
       </c>
       <c r="W373" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X373" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="Y373" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z373" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31907,7 +31904,7 @@
         <v>1784</v>
       </c>
       <c r="W374" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31972,7 +31969,7 @@
         <v>1785</v>
       </c>
       <c r="W375" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -32037,7 +32034,7 @@
         <v>1786</v>
       </c>
       <c r="W376" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32102,7 +32099,7 @@
         <v>1786</v>
       </c>
       <c r="W377" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32167,13 +32164,13 @@
         <v>1787</v>
       </c>
       <c r="W378" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X378" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="Z378" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32235,16 +32232,16 @@
         <v>1788</v>
       </c>
       <c r="W379" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X379" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="Y379" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z379" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32309,7 +32306,7 @@
         <v>1789</v>
       </c>
       <c r="W380" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32371,7 +32368,7 @@
         <v>1790</v>
       </c>
       <c r="W381" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32436,7 +32433,7 @@
         <v>1791</v>
       </c>
       <c r="W382" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32498,7 +32495,7 @@
         <v>1792</v>
       </c>
       <c r="W383" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32563,7 +32560,7 @@
         <v>1791</v>
       </c>
       <c r="W384" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32625,16 +32622,16 @@
         <v>1793</v>
       </c>
       <c r="W385" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X385" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="Y385" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z385" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32702,7 +32699,7 @@
         <v>1794</v>
       </c>
       <c r="W386" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32764,7 +32761,7 @@
         <v>1795</v>
       </c>
       <c r="W387" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32826,7 +32823,7 @@
         <v>1796</v>
       </c>
       <c r="W388" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32888,16 +32885,16 @@
         <v>1797</v>
       </c>
       <c r="W389" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X389" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="Y389" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z389" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32962,16 +32959,16 @@
         <v>1798</v>
       </c>
       <c r="W390" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X390" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="Y390" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z390" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -33036,7 +33033,7 @@
         <v>1799</v>
       </c>
       <c r="W391" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33098,7 +33095,7 @@
         <v>1800</v>
       </c>
       <c r="W392" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33160,16 +33157,16 @@
         <v>1801</v>
       </c>
       <c r="W393" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X393" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="Y393" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z393" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33231,7 +33228,7 @@
         <v>1802</v>
       </c>
       <c r="W394" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33296,16 +33293,16 @@
         <v>1803</v>
       </c>
       <c r="W395" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X395" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="Y395" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z395" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33370,13 +33367,13 @@
         <v>1804</v>
       </c>
       <c r="W396" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X396" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="Y396" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33438,7 +33435,7 @@
         <v>1805</v>
       </c>
       <c r="W397" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33500,7 +33497,7 @@
         <v>1806</v>
       </c>
       <c r="W398" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33565,7 +33562,7 @@
         <v>1807</v>
       </c>
       <c r="W399" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33630,16 +33627,16 @@
         <v>1808</v>
       </c>
       <c r="W400" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X400" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="Y400" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z400" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33704,7 +33701,7 @@
         <v>1809</v>
       </c>
       <c r="W401" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33769,7 +33766,7 @@
         <v>1810</v>
       </c>
       <c r="W402" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33834,16 +33831,16 @@
         <v>1811</v>
       </c>
       <c r="W403" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X403" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="Y403" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z403" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33908,7 +33905,7 @@
         <v>1812</v>
       </c>
       <c r="W404" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33973,7 +33970,7 @@
         <v>1813</v>
       </c>
       <c r="W405" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -34038,7 +34035,7 @@
         <v>1814</v>
       </c>
       <c r="W406" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34100,16 +34097,16 @@
         <v>1815</v>
       </c>
       <c r="W407" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X407" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="Y407" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z407" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34174,13 +34171,13 @@
         <v>1816</v>
       </c>
       <c r="W408" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X408" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="Z408" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34245,7 +34242,7 @@
         <v>1817</v>
       </c>
       <c r="W409" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34310,7 +34307,7 @@
         <v>1818</v>
       </c>
       <c r="W410" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34375,7 +34372,7 @@
         <v>1819</v>
       </c>
       <c r="W411" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34440,7 +34437,7 @@
         <v>1820</v>
       </c>
       <c r="W412" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34505,7 +34502,7 @@
         <v>1821</v>
       </c>
       <c r="W413" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34570,7 +34567,7 @@
         <v>1821</v>
       </c>
       <c r="W414" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34635,7 +34632,7 @@
         <v>1822</v>
       </c>
       <c r="W415" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34700,7 +34697,7 @@
         <v>1823</v>
       </c>
       <c r="W416" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34765,7 +34762,7 @@
         <v>1821</v>
       </c>
       <c r="W417" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34830,7 +34827,7 @@
         <v>1824</v>
       </c>
       <c r="W418" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34895,7 +34892,7 @@
         <v>1825</v>
       </c>
       <c r="W419" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34960,16 +34957,16 @@
         <v>1826</v>
       </c>
       <c r="W420" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X420" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="Y420" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z420" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -35034,7 +35031,7 @@
         <v>1827</v>
       </c>
       <c r="W421" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35099,7 +35096,7 @@
         <v>1828</v>
       </c>
       <c r="W422" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35164,7 +35161,7 @@
         <v>1829</v>
       </c>
       <c r="W423" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35229,16 +35226,16 @@
         <v>1830</v>
       </c>
       <c r="W424" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X424" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="Y424" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z424" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35303,7 +35300,7 @@
         <v>1829</v>
       </c>
       <c r="W425" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35368,7 +35365,7 @@
         <v>1831</v>
       </c>
       <c r="W426" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35433,7 +35430,7 @@
         <v>1832</v>
       </c>
       <c r="W427" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35498,13 +35495,13 @@
         <v>1833</v>
       </c>
       <c r="W428" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X428" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="Y428" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35569,16 +35566,16 @@
         <v>1834</v>
       </c>
       <c r="W429" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X429" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="Y429" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z429" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35643,7 +35640,7 @@
         <v>1835</v>
       </c>
       <c r="W430" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35708,16 +35705,16 @@
         <v>1836</v>
       </c>
       <c r="W431" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X431" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="Y431" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z431" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35782,7 +35779,7 @@
         <v>1837</v>
       </c>
       <c r="W432" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35847,7 +35844,7 @@
         <v>1838</v>
       </c>
       <c r="W433" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35912,7 +35909,7 @@
         <v>1839</v>
       </c>
       <c r="W434" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35977,7 +35974,7 @@
         <v>1840</v>
       </c>
       <c r="W435" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -36042,7 +36039,7 @@
         <v>1841</v>
       </c>
       <c r="W436" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36107,7 +36104,7 @@
         <v>1842</v>
       </c>
       <c r="W437" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36172,7 +36169,7 @@
         <v>1843</v>
       </c>
       <c r="W438" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36237,7 +36234,7 @@
         <v>1844</v>
       </c>
       <c r="W439" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36302,16 +36299,16 @@
         <v>1845</v>
       </c>
       <c r="W440" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X440" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="Y440" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z440" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36376,16 +36373,16 @@
         <v>1846</v>
       </c>
       <c r="W441" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X441" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Y441" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z441" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36450,16 +36447,16 @@
         <v>1847</v>
       </c>
       <c r="W442" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X442" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="Y442" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z442" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36524,7 +36521,7 @@
         <v>1848</v>
       </c>
       <c r="W443" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36589,7 +36586,7 @@
         <v>1849</v>
       </c>
       <c r="W444" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36654,16 +36651,16 @@
         <v>1846</v>
       </c>
       <c r="W445" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X445" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Y445" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z445" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36728,16 +36725,16 @@
         <v>1846</v>
       </c>
       <c r="W446" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X446" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Y446" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z446" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36802,16 +36799,16 @@
         <v>1850</v>
       </c>
       <c r="W447" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X447" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="Y447" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z447" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36876,16 +36873,16 @@
         <v>1846</v>
       </c>
       <c r="W448" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X448" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Y448" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z448" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36950,16 +36947,16 @@
         <v>1846</v>
       </c>
       <c r="W449" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X449" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Y449" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z449" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -37024,16 +37021,16 @@
         <v>1851</v>
       </c>
       <c r="W450" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X450" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="Y450" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z450" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37098,16 +37095,16 @@
         <v>1852</v>
       </c>
       <c r="W451" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X451" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="Y451" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z451" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37172,7 +37169,7 @@
         <v>1853</v>
       </c>
       <c r="W452" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37237,16 +37234,16 @@
         <v>1854</v>
       </c>
       <c r="W453" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X453" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="Y453" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z453" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37311,16 +37308,16 @@
         <v>1855</v>
       </c>
       <c r="W454" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X454" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="Y454" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z454" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37385,16 +37382,16 @@
         <v>1856</v>
       </c>
       <c r="W455" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X455" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="Y455" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z455" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37459,16 +37456,16 @@
         <v>1857</v>
       </c>
       <c r="W456" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X456" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="Y456" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z456" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37533,7 +37530,7 @@
         <v>1858</v>
       </c>
       <c r="W457" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37598,7 +37595,7 @@
         <v>1858</v>
       </c>
       <c r="W458" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37663,16 +37660,16 @@
         <v>1856</v>
       </c>
       <c r="W459" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X459" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="Y459" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z459" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37737,16 +37734,16 @@
         <v>1859</v>
       </c>
       <c r="W460" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X460" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="Y460" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z460" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37811,16 +37808,16 @@
         <v>1860</v>
       </c>
       <c r="W461" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X461" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="Y461" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z461" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37885,7 +37882,7 @@
         <v>1861</v>
       </c>
       <c r="W462" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37950,16 +37947,16 @@
         <v>1862</v>
       </c>
       <c r="W463" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X463" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="Y463" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z463" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -38024,16 +38021,16 @@
         <v>1863</v>
       </c>
       <c r="W464" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X464" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="Y464" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z464" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38098,16 +38095,16 @@
         <v>1864</v>
       </c>
       <c r="W465" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X465" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="Y465" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z465" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38172,7 +38169,7 @@
         <v>1865</v>
       </c>
       <c r="W466" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38237,16 +38234,16 @@
         <v>1866</v>
       </c>
       <c r="W467" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X467" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="Y467" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z467" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38311,16 +38308,16 @@
         <v>1867</v>
       </c>
       <c r="W468" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X468" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Y468" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z468" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38385,16 +38382,16 @@
         <v>1868</v>
       </c>
       <c r="W469" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X469" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Y469" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z469" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38459,16 +38456,16 @@
         <v>1869</v>
       </c>
       <c r="W470" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X470" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="Y470" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z470" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38533,7 +38530,7 @@
         <v>1870</v>
       </c>
       <c r="W471" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38598,16 +38595,16 @@
         <v>1871</v>
       </c>
       <c r="W472" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X472" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="Y472" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z472" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38672,16 +38669,16 @@
         <v>1871</v>
       </c>
       <c r="W473" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X473" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="Y473" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z473" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38746,7 +38743,7 @@
         <v>1872</v>
       </c>
       <c r="W474" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38811,16 +38808,16 @@
         <v>1873</v>
       </c>
       <c r="W475" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X475" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="Y475" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z475" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38885,16 +38882,16 @@
         <v>1874</v>
       </c>
       <c r="W476" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X476" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="Y476" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z476" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38959,7 +38956,7 @@
         <v>1875</v>
       </c>
       <c r="W477" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -39024,7 +39021,7 @@
         <v>1876</v>
       </c>
       <c r="W478" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39089,16 +39086,16 @@
         <v>1877</v>
       </c>
       <c r="W479" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X479" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="Y479" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z479" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39163,16 +39160,16 @@
         <v>1878</v>
       </c>
       <c r="W480" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X480" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="Y480" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z480" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39237,16 +39234,16 @@
         <v>1879</v>
       </c>
       <c r="W481" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X481" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="Y481" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z481" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39311,7 +39308,7 @@
         <v>1880</v>
       </c>
       <c r="W482" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39376,7 +39373,7 @@
         <v>1881</v>
       </c>
       <c r="W483" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39444,13 +39441,13 @@
         <v>1882</v>
       </c>
       <c r="W484" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39515,7 +39512,7 @@
         <v>1883</v>
       </c>
       <c r="W485" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39583,13 +39580,13 @@
         <v>1884</v>
       </c>
       <c r="W486" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39654,7 +39651,7 @@
         <v>1885</v>
       </c>
       <c r="W487" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39719,16 +39716,16 @@
         <v>1886</v>
       </c>
       <c r="W488" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X488" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="Y488" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z488" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39793,7 +39790,7 @@
         <v>1887</v>
       </c>
       <c r="W489" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39861,13 +39858,13 @@
         <v>1888</v>
       </c>
       <c r="W490" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39932,16 +39929,16 @@
         <v>1889</v>
       </c>
       <c r="W491" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X491" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="Y491" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z491" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -40006,16 +40003,16 @@
         <v>1890</v>
       </c>
       <c r="W492" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X492" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="Y492" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z492" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40080,16 +40077,16 @@
         <v>1891</v>
       </c>
       <c r="W493" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X493" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="Y493" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z493" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40154,13 +40151,13 @@
         <v>1892</v>
       </c>
       <c r="W494" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X494" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="Y494" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40225,16 +40222,16 @@
         <v>1893</v>
       </c>
       <c r="W495" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X495" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="Y495" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z495" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40299,7 +40296,7 @@
         <v>1894</v>
       </c>
       <c r="W496" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40367,7 +40364,7 @@
         <v>1895</v>
       </c>
       <c r="W497" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40432,7 +40429,7 @@
         <v>1896</v>
       </c>
       <c r="W498" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40500,7 +40497,7 @@
         <v>1897</v>
       </c>
       <c r="W499" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40565,16 +40562,16 @@
         <v>1898</v>
       </c>
       <c r="W500" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X500" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="Y500" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z500" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40639,16 +40636,16 @@
         <v>1899</v>
       </c>
       <c r="W501" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X501" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="Y501" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z501" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40713,7 +40710,7 @@
         <v>1900</v>
       </c>
       <c r="W502" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40781,7 +40778,7 @@
         <v>1901</v>
       </c>
       <c r="W503" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40849,16 +40846,16 @@
         <v>1902</v>
       </c>
       <c r="W504" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X504" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="Y504" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z504" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40923,7 +40920,7 @@
         <v>1903</v>
       </c>
       <c r="W505" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -40988,16 +40985,16 @@
         <v>1904</v>
       </c>
       <c r="W506" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X506" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="Y506" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z506" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -41062,7 +41059,7 @@
         <v>1905</v>
       </c>
       <c r="W507" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41127,7 +41124,7 @@
         <v>1906</v>
       </c>
       <c r="W508" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41192,16 +41189,16 @@
         <v>1907</v>
       </c>
       <c r="W509" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X509" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="Y509" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z509" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41266,16 +41263,16 @@
         <v>1908</v>
       </c>
       <c r="W510" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X510" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="Y510" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z510" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41343,7 +41340,7 @@
         <v>1909</v>
       </c>
       <c r="W511" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41411,7 +41408,7 @@
         <v>1910</v>
       </c>
       <c r="W512" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41479,7 +41476,7 @@
         <v>1911</v>
       </c>
       <c r="W513" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41547,7 +41544,7 @@
         <v>1911</v>
       </c>
       <c r="W514" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41615,7 +41612,7 @@
         <v>1911</v>
       </c>
       <c r="W515" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41683,13 +41680,13 @@
         <v>1912</v>
       </c>
       <c r="W516" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41757,13 +41754,13 @@
         <v>1913</v>
       </c>
       <c r="W517" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41831,16 +41828,16 @@
         <v>1914</v>
       </c>
       <c r="W518" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X518" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="Y518" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z518" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41908,16 +41905,16 @@
         <v>1915</v>
       </c>
       <c r="W519" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X519" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="Y519" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z519" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -41982,7 +41979,7 @@
         <v>1518</v>
       </c>
       <c r="W520" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -42050,7 +42047,7 @@
         <v>1916</v>
       </c>
       <c r="W521" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42118,7 +42115,7 @@
         <v>1916</v>
       </c>
       <c r="W522" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42186,7 +42183,7 @@
         <v>1917</v>
       </c>
       <c r="W523" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42254,7 +42251,7 @@
         <v>1918</v>
       </c>
       <c r="W524" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42322,7 +42319,7 @@
         <v>1919</v>
       </c>
       <c r="W525" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42390,7 +42387,7 @@
         <v>1920</v>
       </c>
       <c r="W526" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42458,7 +42455,7 @@
         <v>1921</v>
       </c>
       <c r="W527" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42523,7 +42520,7 @@
         <v>1922</v>
       </c>
       <c r="W528" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42591,7 +42588,7 @@
         <v>1923</v>
       </c>
       <c r="W529" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42659,16 +42656,16 @@
         <v>1924</v>
       </c>
       <c r="W530" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X530" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="Y530" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z530" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42736,7 +42733,7 @@
         <v>1925</v>
       </c>
       <c r="W531" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42801,7 +42798,7 @@
         <v>1926</v>
       </c>
       <c r="W532" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42869,16 +42866,16 @@
         <v>1927</v>
       </c>
       <c r="W533" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X533" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="Y533" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z533" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42946,13 +42943,13 @@
         <v>1928</v>
       </c>
       <c r="W534" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -43020,7 +43017,7 @@
         <v>1929</v>
       </c>
       <c r="W535" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43088,7 +43085,7 @@
         <v>1930</v>
       </c>
       <c r="W536" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43156,16 +43153,16 @@
         <v>1931</v>
       </c>
       <c r="W537" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X537" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="Y537" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z537" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43233,7 +43230,7 @@
         <v>1932</v>
       </c>
       <c r="W538" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43301,7 +43298,7 @@
         <v>1933</v>
       </c>
       <c r="W539" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43369,7 +43366,7 @@
         <v>1934</v>
       </c>
       <c r="W540" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43437,7 +43434,7 @@
         <v>1935</v>
       </c>
       <c r="W541" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43505,16 +43502,16 @@
         <v>1936</v>
       </c>
       <c r="W542" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X542" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="Y542" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Z542" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43582,7 +43579,7 @@
         <v>1937</v>
       </c>
       <c r="W543" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43650,16 +43647,16 @@
         <v>1938</v>
       </c>
       <c r="W544" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="X544" t="s">
+        <v>2155</v>
+      </c>
+      <c r="Y544" t="s">
         <v>2156</v>
       </c>
-      <c r="Y544" t="s">
-        <v>2157</v>
-      </c>
       <c r="Z544" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43727,7 +43724,7 @@
         <v>1939</v>
       </c>
       <c r="W545" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43795,7 +43792,7 @@
         <v>1940</v>
       </c>
       <c r="W546" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43863,7 +43860,7 @@
         <v>1941</v>
       </c>
       <c r="W547" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43931,7 +43928,7 @@
         <v>1942</v>
       </c>
       <c r="W548" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -43999,7 +43996,7 @@
         <v>1942</v>
       </c>
       <c r="W549" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44067,7 +44064,7 @@
         <v>1943</v>
       </c>
       <c r="W550" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44132,7 +44129,7 @@
         <v>1944</v>
       </c>
       <c r="W551" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44200,7 +44197,7 @@
         <v>1945</v>
       </c>
       <c r="W552" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44265,7 +44262,7 @@
         <v>1946</v>
       </c>
       <c r="W553" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44333,7 +44330,7 @@
         <v>1947</v>
       </c>
       <c r="W554" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44401,7 +44398,7 @@
         <v>1948</v>
       </c>
       <c r="W555" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44469,7 +44466,7 @@
         <v>1949</v>
       </c>
       <c r="W556" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44534,7 +44531,7 @@
         <v>1950</v>
       </c>
       <c r="W557" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44602,7 +44599,7 @@
         <v>1951</v>
       </c>
       <c r="W558" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44670,7 +44667,7 @@
         <v>1952</v>
       </c>
       <c r="W559" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44735,7 +44732,7 @@
         <v>1953</v>
       </c>
       <c r="W560" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44803,7 +44800,7 @@
         <v>1954</v>
       </c>
       <c r="W561" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44856,10 +44853,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R562">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S562" t="s">
         <v>1515</v>
@@ -44871,7 +44868,7 @@
         <v>1986</v>
       </c>
       <c r="W562" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44936,7 +44933,7 @@
         <v>1955</v>
       </c>
       <c r="W563" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -45001,7 +44998,7 @@
         <v>1956</v>
       </c>
       <c r="W564" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45069,7 +45066,7 @@
         <v>1957</v>
       </c>
       <c r="W565" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45137,7 +45134,7 @@
         <v>1958</v>
       </c>
       <c r="W566" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45205,7 +45202,7 @@
         <v>1959</v>
       </c>
       <c r="W567" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45273,7 +45270,7 @@
         <v>1960</v>
       </c>
       <c r="W568" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA568" t="b">
         <v>0</v>
@@ -45341,7 +45338,7 @@
         <v>1961</v>
       </c>
       <c r="W569" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45406,7 +45403,7 @@
         <v>1962</v>
       </c>
       <c r="W570" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45471,7 +45468,7 @@
         <v>1963</v>
       </c>
       <c r="W571" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45539,7 +45536,7 @@
         <v>1964</v>
       </c>
       <c r="W572" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45607,7 +45604,7 @@
         <v>1965</v>
       </c>
       <c r="W573" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45675,7 +45672,7 @@
         <v>1966</v>
       </c>
       <c r="W574" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45743,7 +45740,7 @@
         <v>1967</v>
       </c>
       <c r="W575" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -45811,7 +45808,7 @@
         <v>1968</v>
       </c>
       <c r="W576" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45879,7 +45876,7 @@
         <v>1968</v>
       </c>
       <c r="W577" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45947,7 +45944,7 @@
         <v>1969</v>
       </c>
       <c r="W578" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -46015,7 +46012,7 @@
         <v>1970</v>
       </c>
       <c r="W579" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46083,7 +46080,7 @@
         <v>1971</v>
       </c>
       <c r="W580" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46151,7 +46148,7 @@
         <v>1972</v>
       </c>
       <c r="W581" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46219,7 +46216,7 @@
         <v>1973</v>
       </c>
       <c r="W582" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA582" t="b">
         <v>0</v>
@@ -46287,7 +46284,7 @@
         <v>1974</v>
       </c>
       <c r="W583" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA583" t="b">
         <v>0</v>
@@ -46355,7 +46352,7 @@
         <v>1975</v>
       </c>
       <c r="W584" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46423,7 +46420,7 @@
         <v>1975</v>
       </c>
       <c r="W585" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46476,10 +46473,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="R586">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S586" t="s">
         <v>1515</v>
@@ -46491,7 +46488,7 @@
         <v>1987</v>
       </c>
       <c r="W586" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46556,7 +46553,7 @@
         <v>1976</v>
       </c>
       <c r="W587" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA587" t="b">
         <v>0</v>
@@ -46609,10 +46606,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R588">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S588" t="s">
         <v>1516</v>
@@ -46627,7 +46624,7 @@
         <v>1988</v>
       </c>
       <c r="W588" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46676,17 +46673,14 @@
       <c r="N589" s="1">
         <v>46277</v>
       </c>
-      <c r="O589" s="1">
-        <v>46252</v>
-      </c>
       <c r="P589" t="s">
         <v>1511</v>
       </c>
       <c r="Q589">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="R589">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S589" t="s">
         <v>1516</v>
@@ -46697,11 +46691,8 @@
       <c r="U589" t="s">
         <v>1978</v>
       </c>
-      <c r="V589" t="s">
-        <v>1989</v>
-      </c>
       <c r="W589" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA589" t="b">
         <v>0</v>
@@ -46766,7 +46757,7 @@
         <v>1979</v>
       </c>
       <c r="W590" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA590" t="b">
         <v>0</v>
@@ -46834,7 +46825,7 @@
         <v>1980</v>
       </c>
       <c r="W591" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA591" t="b">
         <v>0</v>
@@ -46899,7 +46890,7 @@
         <v>1981</v>
       </c>
       <c r="W592" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA592" t="b">
         <v>0</v>
@@ -46952,10 +46943,10 @@
         <v>46252</v>
       </c>
       <c r="Q593">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="R593">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S593" t="s">
         <v>1516</v>
@@ -46967,10 +46958,10 @@
         <v>1982</v>
       </c>
       <c r="V593" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="W593" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA593" t="b">
         <v>1</v>
@@ -47035,7 +47026,7 @@
         <v>1981</v>
       </c>
       <c r="W594" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA594" t="b">
         <v>0</v>
@@ -47085,10 +47076,10 @@
         <v>46279</v>
       </c>
       <c r="Q595">
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="R595">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S595" t="s">
         <v>1516</v>
@@ -47097,10 +47088,10 @@
         <v>1515</v>
       </c>
       <c r="V595" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="W595" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA595" t="b">
         <v>1</v>
@@ -47167,11 +47158,8 @@
       <c r="U596" t="s">
         <v>1983</v>
       </c>
-      <c r="V596" t="s">
-        <v>1992</v>
-      </c>
       <c r="W596" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA596" t="b">
         <v>0</v>
@@ -47221,10 +47209,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="R597">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S597" t="s">
         <v>1516</v>
@@ -47236,10 +47224,10 @@
         <v>1984</v>
       </c>
       <c r="V597" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="W597" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA597" t="b">
         <v>1</v>
@@ -47307,7 +47295,7 @@
         <v>1985</v>
       </c>
       <c r="W598" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA598" t="b">
         <v>0</v>
@@ -47357,10 +47345,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-25</v>
+        <v>-22</v>
       </c>
       <c r="R599">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S599" t="s">
         <v>1515</v>
@@ -47369,10 +47357,10 @@
         <v>1516</v>
       </c>
       <c r="V599" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="W599" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA599" t="b">
         <v>1</v>
@@ -47421,11 +47409,14 @@
       <c r="N600" s="1">
         <v>46282</v>
       </c>
+      <c r="O600" s="1">
+        <v>46255</v>
+      </c>
       <c r="Q600">
-        <v>-27</v>
+        <v>-24</v>
       </c>
       <c r="R600">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S600" t="s">
         <v>1515</v>
@@ -47434,10 +47425,10 @@
         <v>1516</v>
       </c>
       <c r="V600" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="W600" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA600" t="b">
         <v>1</v>
@@ -47487,10 +47478,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="R601">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S601" t="s">
         <v>1515</v>
@@ -47499,7 +47490,7 @@
         <v>1516</v>
       </c>
       <c r="W601" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA601" t="b">
         <v>1</v>
@@ -47549,10 +47540,10 @@
         <v>46284</v>
       </c>
       <c r="Q602">
-        <v>-29</v>
+        <v>-26</v>
       </c>
       <c r="R602">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S602" t="s">
         <v>1515</v>
@@ -47561,10 +47552,10 @@
         <v>1516</v>
       </c>
       <c r="V602" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="W602" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA602" t="b">
         <v>1</v>
@@ -47614,10 +47605,10 @@
         <v>46266</v>
       </c>
       <c r="Q603">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R603">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S603" t="s">
         <v>1515</v>
@@ -47626,10 +47617,10 @@
         <v>1516</v>
       </c>
       <c r="V603" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="W603" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA603" t="b">
         <v>1</v>
@@ -47679,10 +47670,10 @@
         <v>46264</v>
       </c>
       <c r="Q604">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="R604">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S604" t="s">
         <v>1515</v>
@@ -47690,8 +47681,11 @@
       <c r="T604" t="s">
         <v>1516</v>
       </c>
+      <c r="V604" t="s">
+        <v>1996</v>
+      </c>
       <c r="W604" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="AA604" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7598" uniqueCount="2377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7599" uniqueCount="2377">
   <si>
     <t>om_emg</t>
   </si>
@@ -4567,15 +4567,15 @@
     <t>2026-08-15 00:00:00</t>
   </si>
   <si>
+    <t>2026-08-24 00:00:00</t>
+  </si>
+  <si>
     <t>2026-08-20 00:00:00</t>
   </si>
   <si>
     <t>2026-08-14 00:00:00</t>
   </si>
   <si>
-    <t>2026-08-24 00:00:00</t>
-  </si>
-  <si>
     <t>Não</t>
   </si>
   <si>
@@ -5977,7 +5977,7 @@
     <t>Item em pane, anv autorizada a voar por 3 dias pela MMEL a contar de 12/08. Ramon 13/08/26. AWB 12752990604 - volume retirado na loja GOLLOG - CWB por RAFAEL MAIA DE LIMA em 15/08. Godoy 18/08/26.</t>
   </si>
   <si>
-    <t>Estoque no alternado 285K4. Caso use do estoque, verificar validade que consta no item. Ramon 12/08/26. Item em pane, anv autorizada a voar por 3 dias pela MMEL a contar de 12/08. Ramon 13/08/26</t>
+    <t>Estoque no alternado 285K4. Caso use do estoque, verificar validade que consta no item. Ramon 12/08/26. Item em pane, anv autorizada a voar por 3 dias pela MMEL a contar de 12/08. Ramon 13/08/26 NF 2083 assinada em 21/08. Ramon 24/08/26.</t>
   </si>
   <si>
     <t>item será atendido com o estoque local pedido 18216324. Godoy 17/08. 20/08. AWB 12753325834 - volume retirado na loja GOLLOG - BSB por MATHEUS PINHO em 20/08. Godoy 21/08/26.</t>
@@ -46683,7 +46683,7 @@
         <v>2743</v>
       </c>
       <c r="H589" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="I589" t="s">
         <v>1275</v>
@@ -46707,10 +46707,10 @@
         <v>1514</v>
       </c>
       <c r="Q589">
-        <v>-19</v>
+        <v>-25</v>
       </c>
       <c r="R589">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="S589" t="s">
         <v>1521</v>
@@ -46955,7 +46955,7 @@
         <v>2742</v>
       </c>
       <c r="H593" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="I593" t="s">
         <v>1275</v>
@@ -46978,6 +46978,9 @@
       <c r="O593" s="1">
         <v>46252</v>
       </c>
+      <c r="P593" t="s">
+        <v>1517</v>
+      </c>
       <c r="Q593">
         <v>-19</v>
       </c>
@@ -47000,7 +47003,7 @@
         <v>2004</v>
       </c>
       <c r="AA593" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="594" spans="1:27">
@@ -47180,7 +47183,7 @@
         <v>46259</v>
       </c>
       <c r="P596" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="Q596">
         <v>-5</v>
@@ -47316,7 +47319,7 @@
         <v>46259</v>
       </c>
       <c r="P598" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="Q598">
         <v>-11</v>
@@ -47712,7 +47715,7 @@
         <v>46264</v>
       </c>
       <c r="P604" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="Q604">
         <v>-6</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7599" uniqueCount="2377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7601" uniqueCount="2378">
   <si>
     <t>om_emg</t>
   </si>
@@ -5989,13 +5989,16 @@
     <t>Emerg Cancelada por 3S JACQUELINEJSRG em 14/08/2026 motivo: será refeito - Godoy 17/08/2026.</t>
   </si>
   <si>
+    <t>AWB 12754088775 - volume retirado na loja GOLLOG - NAT por Teodoro silva em 22/08. Godoy 25/08/26.</t>
+  </si>
+  <si>
     <t>Emergência transformada em ANCE em 24/08. Aguardaremos atendimento com item da Vee One. Ramon 24/08/26.</t>
   </si>
   <si>
     <t>Recibo 719/FAB/26 assinado em 24/08. Ramon 24/08/26</t>
   </si>
   <si>
-    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08</t>
+    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08 - MATERIAL EM TRANSITO - RECIBO 722/FAB/26 DPE 24/08/2026</t>
   </si>
   <si>
     <t>PEDIDO NO EPM E-C98-26060 - CLA-05-08 , por gentileza, me confirme se está correto a data da informação e prazo de entrega do item.O item solicitado não atende a pane do sistema ARCOND,pôs a pane é de 18/11/2024, anterior ao contrato vigente ,desta forma deve ser feito toda analise do sistema ,devido muito tempo inoperante e sem o item. SO R1 Bispo VEE-ONE-BE em 06/08/26</t>
@@ -6007,25 +6010,25 @@
     <t>Temos no STK V1, material em separação, recibo 682/FAB/26 - atz rc 13/08 - MATERIAL ENVIADO VIA AWB 12752709016 - DPE 18/08/2026 - ENTREGUE DIA 18/08/2026</t>
   </si>
   <si>
-    <t>foi solicitoado o atendimento com o estoque FAB. CLA-17-08 - o item PN superado 069-1025-25 não serve na ANV 2721 - temos 4ea na wiliam para reparo, já foi solicitado o DPE - OS 4 ITENS ESTÃO COM PROBLEMAS NO DISPAY. -FOI ENVIADO PARA O WIILIAM MAIS 3 UNS PARA REPARO - AINDA SEM DPE -CLA-20-08</t>
-  </si>
-  <si>
-    <t>ITEM FOI ENTREGUE PARA A FAB VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUECLA-17-08</t>
-  </si>
-  <si>
-    <t>pedido no EPM E-C98-26061 -CLA-18-08 - em cotação no mercado. Validar se os alternados PN A-7512-24 ou MS25309-7512 ou M6363/2-2 atendem</t>
-  </si>
-  <si>
-    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08 - AWB127-5408 8775- CLA-21-08</t>
-  </si>
-  <si>
-    <t>Colocado pedido Textron WB0003128625 - tracking 535477333011 - previsão de entrega 24/08</t>
+    <t>Enviado para o Operador em 24/08/26 - AWB 127-5459 2764 - REZ 24/08/26</t>
+  </si>
+  <si>
+    <t>ITEM FOI ENTREGUE PARA A FAB VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUECLA-17-08 - material enviado via awb 12754592764, DPE 25/08/2026</t>
+  </si>
+  <si>
+    <t>Colocado pedido no fornecedor WAGA INTERNATIONAL - aguardando proforma invoice para pagamento. ATZ 21/08</t>
+  </si>
+  <si>
+    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08 - AWB 12754088775 - CLA-21-08</t>
+  </si>
+  <si>
+    <t>Colocado pedido Textron WB0003128625 - tracking 535477333011 - previsão de entrega 24/08 V1 JPA</t>
   </si>
   <si>
     <t>Colocado pedido no fornecedor S624333 - validando entrega em Miami - TEMOS 3 EA NO ESTOQUE DA BANT</t>
   </si>
   <si>
-    <t>Será atendido via estoque V1 JPA. Em processo de envio. ATZ 21/08</t>
+    <t>Material enviado via recibo 720/FAB/26 DPE 24/08/2026</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7622,7 +7625,7 @@
         <v>1524</v>
       </c>
       <c r="W2" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7684,16 +7687,16 @@
         <v>1525</v>
       </c>
       <c r="W3" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X3" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="Y3" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z3" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7755,7 +7758,7 @@
         <v>1524</v>
       </c>
       <c r="W4" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7817,7 +7820,7 @@
         <v>1526</v>
       </c>
       <c r="W5" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7879,7 +7882,7 @@
         <v>1527</v>
       </c>
       <c r="W6" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7941,7 +7944,7 @@
         <v>1528</v>
       </c>
       <c r="W7" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -8003,7 +8006,7 @@
         <v>1529</v>
       </c>
       <c r="W8" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -8065,7 +8068,7 @@
         <v>1530</v>
       </c>
       <c r="W9" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8127,7 +8130,7 @@
         <v>1531</v>
       </c>
       <c r="W10" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8189,7 +8192,7 @@
         <v>1532</v>
       </c>
       <c r="W11" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8251,7 +8254,7 @@
         <v>1533</v>
       </c>
       <c r="W12" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8313,7 +8316,7 @@
         <v>1529</v>
       </c>
       <c r="W13" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8375,16 +8378,16 @@
         <v>1534</v>
       </c>
       <c r="W14" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X14" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="Y14" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z14" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8443,7 +8446,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8508,7 +8511,7 @@
         <v>1535</v>
       </c>
       <c r="W16" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8570,7 +8573,7 @@
         <v>1536</v>
       </c>
       <c r="W17" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8632,7 +8635,7 @@
         <v>1527</v>
       </c>
       <c r="W18" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8694,7 +8697,7 @@
         <v>1527</v>
       </c>
       <c r="W19" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8756,7 +8759,7 @@
         <v>1537</v>
       </c>
       <c r="W20" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8818,7 +8821,7 @@
         <v>1538</v>
       </c>
       <c r="W21" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8880,7 +8883,7 @@
         <v>1538</v>
       </c>
       <c r="W22" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8942,7 +8945,7 @@
         <v>1539</v>
       </c>
       <c r="W23" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -9001,7 +9004,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -9060,7 +9063,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9122,7 +9125,7 @@
         <v>1527</v>
       </c>
       <c r="W26" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9181,7 +9184,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9240,7 +9243,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9302,7 +9305,7 @@
         <v>1540</v>
       </c>
       <c r="W29" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9361,7 +9364,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9423,7 +9426,7 @@
         <v>1541</v>
       </c>
       <c r="W31" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9485,7 +9488,7 @@
         <v>1542</v>
       </c>
       <c r="W32" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9547,7 +9550,7 @@
         <v>1543</v>
       </c>
       <c r="W33" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9609,7 +9612,7 @@
         <v>1544</v>
       </c>
       <c r="W34" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9671,7 +9674,7 @@
         <v>1545</v>
       </c>
       <c r="W35" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9733,7 +9736,7 @@
         <v>1541</v>
       </c>
       <c r="W36" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9795,7 +9798,7 @@
         <v>1546</v>
       </c>
       <c r="W37" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9857,7 +9860,7 @@
         <v>1524</v>
       </c>
       <c r="W38" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9919,7 +9922,7 @@
         <v>1543</v>
       </c>
       <c r="W39" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9981,7 +9984,7 @@
         <v>1547</v>
       </c>
       <c r="W40" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -10043,7 +10046,7 @@
         <v>1548</v>
       </c>
       <c r="W41" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10105,16 +10108,16 @@
         <v>1549</v>
       </c>
       <c r="W42" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X42" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="Y42" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z42" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10176,7 +10179,7 @@
         <v>1543</v>
       </c>
       <c r="W43" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10238,7 +10241,7 @@
         <v>1550</v>
       </c>
       <c r="W44" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10300,7 +10303,7 @@
         <v>1543</v>
       </c>
       <c r="W45" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10362,7 +10365,7 @@
         <v>1543</v>
       </c>
       <c r="W46" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10424,7 +10427,7 @@
         <v>1551</v>
       </c>
       <c r="W47" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10486,7 +10489,7 @@
         <v>1552</v>
       </c>
       <c r="W48" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10548,7 +10551,7 @@
         <v>1553</v>
       </c>
       <c r="W49" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10610,7 +10613,7 @@
         <v>1554</v>
       </c>
       <c r="W50" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10672,7 +10675,7 @@
         <v>1555</v>
       </c>
       <c r="W51" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10734,7 +10737,7 @@
         <v>1544</v>
       </c>
       <c r="W52" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10796,7 +10799,7 @@
         <v>1538</v>
       </c>
       <c r="W53" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10858,7 +10861,7 @@
         <v>1538</v>
       </c>
       <c r="W54" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10920,7 +10923,7 @@
         <v>1538</v>
       </c>
       <c r="W55" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10982,7 +10985,7 @@
         <v>1556</v>
       </c>
       <c r="W56" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -11044,7 +11047,7 @@
         <v>1557</v>
       </c>
       <c r="W57" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11106,16 +11109,16 @@
         <v>1558</v>
       </c>
       <c r="W58" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X58" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="Y58" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z58" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11177,7 +11180,7 @@
         <v>1559</v>
       </c>
       <c r="W59" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11239,7 +11242,7 @@
         <v>1560</v>
       </c>
       <c r="W60" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11301,7 +11304,7 @@
         <v>1538</v>
       </c>
       <c r="W61" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11363,7 +11366,7 @@
         <v>1561</v>
       </c>
       <c r="W62" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11422,7 +11425,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11481,7 +11484,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11540,7 +11543,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11599,7 +11602,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11658,7 +11661,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11717,7 +11720,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11779,7 +11782,7 @@
         <v>1562</v>
       </c>
       <c r="W69" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11841,7 +11844,7 @@
         <v>1560</v>
       </c>
       <c r="W70" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11903,7 +11906,7 @@
         <v>1545</v>
       </c>
       <c r="W71" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11965,7 +11968,7 @@
         <v>1563</v>
       </c>
       <c r="W72" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -12027,7 +12030,7 @@
         <v>1564</v>
       </c>
       <c r="W73" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12089,16 +12092,16 @@
         <v>1565</v>
       </c>
       <c r="W74" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X74" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="Y74" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z74" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12160,16 +12163,16 @@
         <v>1566</v>
       </c>
       <c r="W75" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X75" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="Y75" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z75" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12231,7 +12234,7 @@
         <v>1545</v>
       </c>
       <c r="W76" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12293,7 +12296,7 @@
         <v>1545</v>
       </c>
       <c r="W77" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12355,10 +12358,10 @@
         <v>1567</v>
       </c>
       <c r="W78" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="Z78" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12423,7 +12426,7 @@
         <v>1568</v>
       </c>
       <c r="W79" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12482,7 +12485,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12541,7 +12544,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12603,7 +12606,7 @@
         <v>1569</v>
       </c>
       <c r="W82" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12665,7 +12668,7 @@
         <v>1570</v>
       </c>
       <c r="W83" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12727,7 +12730,7 @@
         <v>1571</v>
       </c>
       <c r="W84" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12786,7 +12789,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12848,7 +12851,7 @@
         <v>1572</v>
       </c>
       <c r="W86" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12910,7 +12913,7 @@
         <v>1573</v>
       </c>
       <c r="W87" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12972,7 +12975,7 @@
         <v>1573</v>
       </c>
       <c r="W88" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -13034,7 +13037,7 @@
         <v>1538</v>
       </c>
       <c r="W89" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13096,16 +13099,16 @@
         <v>1574</v>
       </c>
       <c r="W90" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X90" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="Y90" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z90" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13167,16 +13170,16 @@
         <v>1575</v>
       </c>
       <c r="W91" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X91" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="Y91" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z91" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13238,7 +13241,7 @@
         <v>1576</v>
       </c>
       <c r="W92" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13300,7 +13303,7 @@
         <v>1577</v>
       </c>
       <c r="W93" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13362,7 +13365,7 @@
         <v>1577</v>
       </c>
       <c r="W94" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13424,7 +13427,7 @@
         <v>1578</v>
       </c>
       <c r="W95" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13486,16 +13489,16 @@
         <v>1579</v>
       </c>
       <c r="W96" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X96" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="Y96" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z96" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13557,7 +13560,7 @@
         <v>1580</v>
       </c>
       <c r="W97" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13619,7 +13622,7 @@
         <v>1581</v>
       </c>
       <c r="W98" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13681,7 +13684,7 @@
         <v>1582</v>
       </c>
       <c r="W99" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13743,7 +13746,7 @@
         <v>1583</v>
       </c>
       <c r="W100" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13805,16 +13808,16 @@
         <v>1584</v>
       </c>
       <c r="W101" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X101" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="Y101" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z101" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13876,7 +13879,7 @@
         <v>1585</v>
       </c>
       <c r="W102" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13938,7 +13941,7 @@
         <v>1585</v>
       </c>
       <c r="W103" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -14000,7 +14003,7 @@
         <v>1586</v>
       </c>
       <c r="W104" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -14062,16 +14065,16 @@
         <v>1587</v>
       </c>
       <c r="W105" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X105" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="Y105" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z105" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14133,16 +14136,16 @@
         <v>1588</v>
       </c>
       <c r="W106" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X106" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="Y106" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z106" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14204,7 +14207,7 @@
         <v>1589</v>
       </c>
       <c r="W107" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14266,16 +14269,16 @@
         <v>1590</v>
       </c>
       <c r="W108" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X108" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="Y108" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z108" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14337,16 +14340,16 @@
         <v>1591</v>
       </c>
       <c r="W109" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X109" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Y109" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z109" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14405,7 +14408,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14467,16 +14470,16 @@
         <v>1592</v>
       </c>
       <c r="W111" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X111" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Y111" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z111" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14538,16 +14541,16 @@
         <v>1593</v>
       </c>
       <c r="W112" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X112" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="Y112" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z112" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14609,16 +14612,16 @@
         <v>1594</v>
       </c>
       <c r="W113" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X113" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="Y113" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z113" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14680,16 +14683,16 @@
         <v>1595</v>
       </c>
       <c r="W114" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X114" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="Y114" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z114" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14751,16 +14754,16 @@
         <v>1591</v>
       </c>
       <c r="W115" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X115" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Y115" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z115" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14822,16 +14825,16 @@
         <v>1591</v>
       </c>
       <c r="W116" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X116" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Y116" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z116" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14893,16 +14896,16 @@
         <v>1596</v>
       </c>
       <c r="W117" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X117" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="Y117" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z117" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14964,16 +14967,16 @@
         <v>1597</v>
       </c>
       <c r="W118" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X118" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="Y118" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z118" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -15035,7 +15038,7 @@
         <v>1598</v>
       </c>
       <c r="W119" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15097,16 +15100,16 @@
         <v>1599</v>
       </c>
       <c r="W120" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X120" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y120" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z120" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15168,16 +15171,16 @@
         <v>1599</v>
       </c>
       <c r="W121" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X121" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y121" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z121" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15239,16 +15242,16 @@
         <v>1599</v>
       </c>
       <c r="W122" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X122" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y122" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z122" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15310,16 +15313,16 @@
         <v>1599</v>
       </c>
       <c r="W123" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X123" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y123" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z123" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15381,16 +15384,16 @@
         <v>1599</v>
       </c>
       <c r="W124" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X124" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y124" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z124" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15452,16 +15455,16 @@
         <v>1599</v>
       </c>
       <c r="W125" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X125" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y125" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z125" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15523,16 +15526,16 @@
         <v>1599</v>
       </c>
       <c r="W126" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X126" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y126" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z126" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15594,16 +15597,16 @@
         <v>1600</v>
       </c>
       <c r="W127" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X127" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Y127" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z127" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15665,16 +15668,16 @@
         <v>1601</v>
       </c>
       <c r="W128" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X128" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="Y128" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z128" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15736,16 +15739,16 @@
         <v>1599</v>
       </c>
       <c r="W129" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X129" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y129" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z129" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15807,16 +15810,16 @@
         <v>1599</v>
       </c>
       <c r="W130" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X130" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y130" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z130" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15878,7 +15881,7 @@
         <v>1602</v>
       </c>
       <c r="W131" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15937,7 +15940,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15996,7 +15999,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -16058,16 +16061,16 @@
         <v>1599</v>
       </c>
       <c r="W134" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X134" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y134" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z134" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16129,16 +16132,16 @@
         <v>1599</v>
       </c>
       <c r="W135" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X135" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y135" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z135" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16200,7 +16203,7 @@
         <v>1598</v>
       </c>
       <c r="W136" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16259,7 +16262,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16321,16 +16324,16 @@
         <v>1603</v>
       </c>
       <c r="W138" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X138" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="Y138" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z138" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16392,16 +16395,16 @@
         <v>1591</v>
       </c>
       <c r="W139" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X139" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="Y139" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z139" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16463,16 +16466,16 @@
         <v>1599</v>
       </c>
       <c r="W140" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X140" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y140" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z140" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16531,7 +16534,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16590,7 +16593,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16652,16 +16655,16 @@
         <v>1604</v>
       </c>
       <c r="W143" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X143" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="Y143" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z143" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16723,16 +16726,16 @@
         <v>1605</v>
       </c>
       <c r="W144" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X144" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="Y144" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z144" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16794,16 +16797,16 @@
         <v>1606</v>
       </c>
       <c r="W145" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X145" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="Y145" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z145" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16865,16 +16868,16 @@
         <v>1607</v>
       </c>
       <c r="W146" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X146" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="Y146" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z146" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16933,7 +16936,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16995,7 +16998,7 @@
         <v>1608</v>
       </c>
       <c r="W148" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -17057,16 +17060,16 @@
         <v>1609</v>
       </c>
       <c r="W149" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X149" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="Y149" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z149" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17128,7 +17131,7 @@
         <v>1610</v>
       </c>
       <c r="W150" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17190,16 +17193,16 @@
         <v>1611</v>
       </c>
       <c r="W151" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X151" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="Y151" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z151" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17261,7 +17264,7 @@
         <v>1610</v>
       </c>
       <c r="W152" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17323,7 +17326,7 @@
         <v>1608</v>
       </c>
       <c r="W153" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17385,7 +17388,7 @@
         <v>1610</v>
       </c>
       <c r="W154" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17447,7 +17450,7 @@
         <v>1610</v>
       </c>
       <c r="W155" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17509,16 +17512,16 @@
         <v>1612</v>
       </c>
       <c r="W156" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X156" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="Y156" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z156" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17580,7 +17583,7 @@
         <v>1608</v>
       </c>
       <c r="W157" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17642,16 +17645,16 @@
         <v>1613</v>
       </c>
       <c r="W158" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X158" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y158" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z158" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17713,16 +17716,16 @@
         <v>1614</v>
       </c>
       <c r="W159" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X159" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="Y159" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z159" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17784,16 +17787,16 @@
         <v>1613</v>
       </c>
       <c r="W160" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X160" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y160" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z160" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17855,16 +17858,16 @@
         <v>1613</v>
       </c>
       <c r="W161" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X161" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y161" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z161" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17926,16 +17929,16 @@
         <v>1613</v>
       </c>
       <c r="W162" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X162" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y162" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z162" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -17997,16 +18000,16 @@
         <v>1615</v>
       </c>
       <c r="W163" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X163" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="Y163" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z163" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -18068,16 +18071,16 @@
         <v>1616</v>
       </c>
       <c r="W164" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X164" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="Y164" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z164" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18139,16 +18142,16 @@
         <v>1617</v>
       </c>
       <c r="W165" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X165" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="Y165" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z165" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18210,16 +18213,16 @@
         <v>1618</v>
       </c>
       <c r="W166" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X166" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="Y166" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z166" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18281,16 +18284,16 @@
         <v>1596</v>
       </c>
       <c r="W167" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X167" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="Y167" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z167" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18352,16 +18355,16 @@
         <v>1599</v>
       </c>
       <c r="W168" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X168" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y168" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z168" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18423,7 +18426,7 @@
         <v>1619</v>
       </c>
       <c r="W169" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18485,16 +18488,16 @@
         <v>1599</v>
       </c>
       <c r="W170" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X170" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="Y170" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z170" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18556,16 +18559,16 @@
         <v>1620</v>
       </c>
       <c r="W171" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X171" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y171" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z171" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18627,16 +18630,16 @@
         <v>1621</v>
       </c>
       <c r="W172" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X172" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="Y172" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z172" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18698,16 +18701,16 @@
         <v>1622</v>
       </c>
       <c r="W173" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X173" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="Y173" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z173" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18769,16 +18772,16 @@
         <v>1623</v>
       </c>
       <c r="W174" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X174" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="Y174" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z174" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18840,16 +18843,16 @@
         <v>1624</v>
       </c>
       <c r="W175" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X175" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="Y175" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z175" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18911,16 +18914,16 @@
         <v>1625</v>
       </c>
       <c r="W176" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X176" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="Y176" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z176" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18982,7 +18985,7 @@
         <v>1619</v>
       </c>
       <c r="W177" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -19044,16 +19047,16 @@
         <v>1626</v>
       </c>
       <c r="W178" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X178" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="Y178" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z178" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19115,16 +19118,16 @@
         <v>1627</v>
       </c>
       <c r="W179" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X179" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="Y179" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z179" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19186,7 +19189,7 @@
         <v>1628</v>
       </c>
       <c r="W180" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19248,16 +19251,16 @@
         <v>1629</v>
       </c>
       <c r="W181" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X181" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Y181" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z181" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19319,16 +19322,16 @@
         <v>1629</v>
       </c>
       <c r="W182" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X182" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="Y182" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z182" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19390,16 +19393,16 @@
         <v>1630</v>
       </c>
       <c r="W183" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X183" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="Y183" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z183" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19461,16 +19464,16 @@
         <v>1631</v>
       </c>
       <c r="W184" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X184" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="Y184" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z184" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19532,16 +19535,16 @@
         <v>1632</v>
       </c>
       <c r="W185" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X185" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="Y185" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z185" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19603,7 +19606,7 @@
         <v>1633</v>
       </c>
       <c r="W186" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19665,7 +19668,7 @@
         <v>1634</v>
       </c>
       <c r="W187" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19727,7 +19730,7 @@
         <v>1635</v>
       </c>
       <c r="W188" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19789,7 +19792,7 @@
         <v>1636</v>
       </c>
       <c r="W189" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19851,16 +19854,16 @@
         <v>1637</v>
       </c>
       <c r="W190" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X190" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="Y190" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z190" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19922,16 +19925,16 @@
         <v>1638</v>
       </c>
       <c r="W191" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X191" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="Y191" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z191" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19993,7 +19996,7 @@
         <v>1639</v>
       </c>
       <c r="W192" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -20055,7 +20058,7 @@
         <v>1639</v>
       </c>
       <c r="W193" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20117,16 +20120,16 @@
         <v>1640</v>
       </c>
       <c r="W194" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X194" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="Y194" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z194" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20188,16 +20191,16 @@
         <v>1641</v>
       </c>
       <c r="W195" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X195" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="Y195" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z195" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20259,16 +20262,16 @@
         <v>1642</v>
       </c>
       <c r="W196" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X196" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="Y196" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z196" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20330,16 +20333,16 @@
         <v>1638</v>
       </c>
       <c r="W197" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X197" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="Y197" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z197" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20401,7 +20404,7 @@
         <v>1643</v>
       </c>
       <c r="W198" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20463,7 +20466,7 @@
         <v>1644</v>
       </c>
       <c r="W199" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20525,16 +20528,16 @@
         <v>1645</v>
       </c>
       <c r="W200" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X200" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="Y200" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z200" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20596,16 +20599,16 @@
         <v>1645</v>
       </c>
       <c r="W201" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X201" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="Y201" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z201" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20667,16 +20670,16 @@
         <v>1646</v>
       </c>
       <c r="W202" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X202" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="Y202" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z202" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20738,16 +20741,16 @@
         <v>1647</v>
       </c>
       <c r="W203" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X203" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="Y203" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z203" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20809,16 +20812,16 @@
         <v>1648</v>
       </c>
       <c r="W204" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X204" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="Y204" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z204" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20880,16 +20883,16 @@
         <v>1649</v>
       </c>
       <c r="W205" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X205" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="Y205" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z205" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20951,16 +20954,16 @@
         <v>1650</v>
       </c>
       <c r="W206" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X206" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="Y206" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z206" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -21022,16 +21025,16 @@
         <v>1651</v>
       </c>
       <c r="W207" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X207" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="Y207" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z207" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21093,16 +21096,16 @@
         <v>1652</v>
       </c>
       <c r="W208" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X208" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y208" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z208" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21164,7 +21167,7 @@
         <v>1653</v>
       </c>
       <c r="W209" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21226,16 +21229,16 @@
         <v>1654</v>
       </c>
       <c r="W210" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X210" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="Y210" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z210" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21297,16 +21300,16 @@
         <v>1655</v>
       </c>
       <c r="W211" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X211" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="Y211" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z211" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21368,16 +21371,16 @@
         <v>1656</v>
       </c>
       <c r="W212" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X212" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="Y212" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z212" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21439,16 +21442,16 @@
         <v>1657</v>
       </c>
       <c r="W213" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X213" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y213" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z213" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21510,7 +21513,7 @@
         <v>1658</v>
       </c>
       <c r="W214" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21572,16 +21575,16 @@
         <v>1623</v>
       </c>
       <c r="W215" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X215" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="Y215" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z215" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21643,16 +21646,16 @@
         <v>1659</v>
       </c>
       <c r="W216" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X216" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="Y216" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z216" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21714,7 +21717,7 @@
         <v>1660</v>
       </c>
       <c r="W217" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21776,16 +21779,16 @@
         <v>1661</v>
       </c>
       <c r="W218" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X218" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="Y218" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z218" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21847,16 +21850,16 @@
         <v>1662</v>
       </c>
       <c r="W219" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X219" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="Y219" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z219" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21918,7 +21921,7 @@
         <v>1663</v>
       </c>
       <c r="W220" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21980,7 +21983,7 @@
         <v>1664</v>
       </c>
       <c r="W221" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -22042,7 +22045,7 @@
         <v>1663</v>
       </c>
       <c r="W222" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22104,7 +22107,7 @@
         <v>1664</v>
       </c>
       <c r="W223" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22166,16 +22169,16 @@
         <v>1665</v>
       </c>
       <c r="W224" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X224" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="Y224" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z224" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22237,16 +22240,16 @@
         <v>1666</v>
       </c>
       <c r="W225" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X225" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="Y225" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z225" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22308,7 +22311,7 @@
         <v>1667</v>
       </c>
       <c r="W226" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22370,7 +22373,7 @@
         <v>1668</v>
       </c>
       <c r="W227" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22432,7 +22435,7 @@
         <v>1669</v>
       </c>
       <c r="W228" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22494,16 +22497,16 @@
         <v>1670</v>
       </c>
       <c r="W229" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X229" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="Y229" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z229" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22565,16 +22568,16 @@
         <v>1671</v>
       </c>
       <c r="W230" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X230" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="Y230" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z230" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22636,16 +22639,16 @@
         <v>1672</v>
       </c>
       <c r="W231" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X231" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="Y231" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z231" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22710,16 +22713,16 @@
         <v>1673</v>
       </c>
       <c r="W232" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X232" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="Y232" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z232" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22781,16 +22784,16 @@
         <v>1674</v>
       </c>
       <c r="W233" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X233" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="Y233" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z233" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22852,16 +22855,16 @@
         <v>1675</v>
       </c>
       <c r="W234" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X234" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Y234" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z234" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22923,16 +22926,16 @@
         <v>1675</v>
       </c>
       <c r="W235" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X235" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Y235" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z235" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22994,16 +22997,16 @@
         <v>1676</v>
       </c>
       <c r="W236" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X236" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Y236" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z236" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -23065,7 +23068,7 @@
         <v>1677</v>
       </c>
       <c r="W237" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23127,7 +23130,7 @@
         <v>1678</v>
       </c>
       <c r="W238" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23189,16 +23192,16 @@
         <v>1679</v>
       </c>
       <c r="W239" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X239" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="Y239" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z239" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23260,16 +23263,16 @@
         <v>1680</v>
       </c>
       <c r="W240" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X240" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="Y240" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z240" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23331,7 +23334,7 @@
         <v>1681</v>
       </c>
       <c r="W241" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23393,16 +23396,16 @@
         <v>1682</v>
       </c>
       <c r="W242" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X242" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="Y242" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z242" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23464,16 +23467,16 @@
         <v>1683</v>
       </c>
       <c r="W243" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X243" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="Y243" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z243" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23535,16 +23538,16 @@
         <v>1682</v>
       </c>
       <c r="W244" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X244" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="Y244" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z244" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23606,16 +23609,16 @@
         <v>1684</v>
       </c>
       <c r="W245" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X245" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="Y245" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z245" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23677,16 +23680,16 @@
         <v>1683</v>
       </c>
       <c r="W246" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X246" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="Y246" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z246" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23748,16 +23751,16 @@
         <v>1684</v>
       </c>
       <c r="W247" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X247" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="Y247" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z247" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23819,16 +23822,16 @@
         <v>1685</v>
       </c>
       <c r="W248" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X248" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="Y248" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z248" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23890,16 +23893,16 @@
         <v>1675</v>
       </c>
       <c r="W249" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X249" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Y249" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z249" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23961,7 +23964,7 @@
         <v>1686</v>
       </c>
       <c r="W250" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -24023,7 +24026,7 @@
         <v>1687</v>
       </c>
       <c r="W251" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -24085,16 +24088,16 @@
         <v>1688</v>
       </c>
       <c r="W252" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X252" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="Y252" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z252" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24156,16 +24159,16 @@
         <v>1689</v>
       </c>
       <c r="W253" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X253" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="Y253" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z253" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24227,7 +24230,7 @@
         <v>1690</v>
       </c>
       <c r="W254" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24289,16 +24292,16 @@
         <v>1691</v>
       </c>
       <c r="W255" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X255" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="Y255" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z255" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24360,7 +24363,7 @@
         <v>1692</v>
       </c>
       <c r="W256" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24425,7 +24428,7 @@
         <v>1693</v>
       </c>
       <c r="W257" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24487,7 +24490,7 @@
         <v>1694</v>
       </c>
       <c r="W258" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24549,7 +24552,7 @@
         <v>1694</v>
       </c>
       <c r="W259" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24611,7 +24614,7 @@
         <v>1695</v>
       </c>
       <c r="W260" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24673,16 +24676,16 @@
         <v>1696</v>
       </c>
       <c r="W261" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X261" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="Y261" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z261" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24744,13 +24747,13 @@
         <v>1697</v>
       </c>
       <c r="W262" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X262" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="Y262" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24812,16 +24815,16 @@
         <v>1698</v>
       </c>
       <c r="W263" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X263" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="Y263" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z263" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24883,7 +24886,7 @@
         <v>1699</v>
       </c>
       <c r="W264" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24945,7 +24948,7 @@
         <v>1699</v>
       </c>
       <c r="W265" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -25007,7 +25010,7 @@
         <v>1700</v>
       </c>
       <c r="W266" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -25069,16 +25072,16 @@
         <v>1701</v>
       </c>
       <c r="W267" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X267" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="Y267" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z267" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25140,16 +25143,16 @@
         <v>1702</v>
       </c>
       <c r="W268" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X268" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="Y268" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z268" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25211,7 +25214,7 @@
         <v>1543</v>
       </c>
       <c r="W269" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25273,7 +25276,7 @@
         <v>1703</v>
       </c>
       <c r="W270" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25335,7 +25338,7 @@
         <v>1704</v>
       </c>
       <c r="W271" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25397,16 +25400,16 @@
         <v>1705</v>
       </c>
       <c r="W272" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X272" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="Y272" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z272" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25465,7 +25468,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25527,7 +25530,7 @@
         <v>1706</v>
       </c>
       <c r="W274" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25586,7 +25589,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25648,7 +25651,7 @@
         <v>1707</v>
       </c>
       <c r="W276" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25710,7 +25713,7 @@
         <v>1708</v>
       </c>
       <c r="W277" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25772,16 +25775,16 @@
         <v>1709</v>
       </c>
       <c r="W278" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X278" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="Y278" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z278" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25843,16 +25846,16 @@
         <v>1710</v>
       </c>
       <c r="W279" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X279" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="Y279" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z279" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25914,16 +25917,16 @@
         <v>1710</v>
       </c>
       <c r="W280" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X280" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="Y280" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z280" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25985,16 +25988,16 @@
         <v>1711</v>
       </c>
       <c r="W281" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X281" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="Y281" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z281" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -26056,7 +26059,7 @@
         <v>1712</v>
       </c>
       <c r="W282" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26118,7 +26121,7 @@
         <v>1713</v>
       </c>
       <c r="W283" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26180,7 +26183,7 @@
         <v>1714</v>
       </c>
       <c r="W284" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26242,16 +26245,16 @@
         <v>1715</v>
       </c>
       <c r="W285" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X285" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="Y285" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z285" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26313,7 +26316,7 @@
         <v>1716</v>
       </c>
       <c r="W286" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26375,16 +26378,16 @@
         <v>1710</v>
       </c>
       <c r="W287" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X287" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="Y287" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z287" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26446,16 +26449,16 @@
         <v>1717</v>
       </c>
       <c r="W288" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X288" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="Y288" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z288" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26517,7 +26520,7 @@
         <v>1718</v>
       </c>
       <c r="W289" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26579,16 +26582,16 @@
         <v>1719</v>
       </c>
       <c r="W290" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X290" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="Y290" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z290" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26650,16 +26653,16 @@
         <v>1720</v>
       </c>
       <c r="W291" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X291" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="Y291" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z291" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26721,7 +26724,7 @@
         <v>1721</v>
       </c>
       <c r="W292" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26780,7 +26783,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26842,7 +26845,7 @@
         <v>1722</v>
       </c>
       <c r="W294" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26904,7 +26907,7 @@
         <v>1723</v>
       </c>
       <c r="W295" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26966,7 +26969,7 @@
         <v>1724</v>
       </c>
       <c r="W296" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -27028,13 +27031,13 @@
         <v>1725</v>
       </c>
       <c r="W297" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X297" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="Z297" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27096,7 +27099,7 @@
         <v>1726</v>
       </c>
       <c r="W298" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27158,7 +27161,7 @@
         <v>1727</v>
       </c>
       <c r="W299" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27220,7 +27223,7 @@
         <v>1728</v>
       </c>
       <c r="W300" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27282,7 +27285,7 @@
         <v>1729</v>
       </c>
       <c r="W301" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27344,7 +27347,7 @@
         <v>1730</v>
       </c>
       <c r="W302" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27406,16 +27409,16 @@
         <v>1731</v>
       </c>
       <c r="W303" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X303" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="Y303" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z303" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27477,7 +27480,7 @@
         <v>1732</v>
       </c>
       <c r="W304" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27539,7 +27542,7 @@
         <v>1733</v>
       </c>
       <c r="W305" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27601,7 +27604,7 @@
         <v>1734</v>
       </c>
       <c r="W306" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27663,7 +27666,7 @@
         <v>1735</v>
       </c>
       <c r="W307" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27725,7 +27728,7 @@
         <v>1728</v>
       </c>
       <c r="W308" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27787,7 +27790,7 @@
         <v>1736</v>
       </c>
       <c r="W309" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27849,7 +27852,7 @@
         <v>1737</v>
       </c>
       <c r="W310" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27911,7 +27914,7 @@
         <v>1738</v>
       </c>
       <c r="W311" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27973,7 +27976,7 @@
         <v>1739</v>
       </c>
       <c r="W312" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -28035,7 +28038,7 @@
         <v>1740</v>
       </c>
       <c r="W313" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28097,7 +28100,7 @@
         <v>1741</v>
       </c>
       <c r="W314" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28159,7 +28162,7 @@
         <v>1742</v>
       </c>
       <c r="W315" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28221,7 +28224,7 @@
         <v>1743</v>
       </c>
       <c r="W316" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28283,7 +28286,7 @@
         <v>1744</v>
       </c>
       <c r="W317" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28345,7 +28348,7 @@
         <v>1745</v>
       </c>
       <c r="W318" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28407,7 +28410,7 @@
         <v>1746</v>
       </c>
       <c r="W319" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28466,13 +28469,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X320" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="Z320" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28531,7 +28534,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28590,7 +28593,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28649,7 +28652,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28711,7 +28714,7 @@
         <v>1747</v>
       </c>
       <c r="W324" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28773,7 +28776,7 @@
         <v>1748</v>
       </c>
       <c r="W325" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28835,7 +28838,7 @@
         <v>1749</v>
       </c>
       <c r="W326" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28897,7 +28900,7 @@
         <v>1750</v>
       </c>
       <c r="W327" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28956,7 +28959,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -29018,7 +29021,7 @@
         <v>1750</v>
       </c>
       <c r="W329" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -29080,7 +29083,7 @@
         <v>1751</v>
       </c>
       <c r="W330" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29142,7 +29145,7 @@
         <v>1752</v>
       </c>
       <c r="W331" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29204,7 +29207,7 @@
         <v>1752</v>
       </c>
       <c r="W332" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29266,7 +29269,7 @@
         <v>1753</v>
       </c>
       <c r="W333" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29328,7 +29331,7 @@
         <v>1754</v>
       </c>
       <c r="W334" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29390,7 +29393,7 @@
         <v>1755</v>
       </c>
       <c r="W335" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29449,13 +29452,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X336" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="Z336" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29517,7 +29520,7 @@
         <v>1756</v>
       </c>
       <c r="W337" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29579,13 +29582,13 @@
         <v>1757</v>
       </c>
       <c r="W338" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X338" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="Z338" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29647,13 +29650,13 @@
         <v>1758</v>
       </c>
       <c r="W339" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X339" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="Z339" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29715,7 +29718,7 @@
         <v>1759</v>
       </c>
       <c r="W340" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29777,7 +29780,7 @@
         <v>1760</v>
       </c>
       <c r="W341" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29839,10 +29842,10 @@
         <v>1761</v>
       </c>
       <c r="W342" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X342" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29904,7 +29907,7 @@
         <v>1762</v>
       </c>
       <c r="W343" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29966,7 +29969,7 @@
         <v>1763</v>
       </c>
       <c r="W344" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -30028,13 +30031,13 @@
         <v>1764</v>
       </c>
       <c r="W345" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X345" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="Z345" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30096,7 +30099,7 @@
         <v>1728</v>
       </c>
       <c r="W346" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30158,7 +30161,7 @@
         <v>1765</v>
       </c>
       <c r="W347" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30220,16 +30223,16 @@
         <v>1766</v>
       </c>
       <c r="W348" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X348" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="Y348" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z348" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30294,13 +30297,13 @@
         <v>1767</v>
       </c>
       <c r="W349" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X349" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="Z349" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30362,7 +30365,7 @@
         <v>1768</v>
       </c>
       <c r="W350" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30424,16 +30427,16 @@
         <v>1769</v>
       </c>
       <c r="W351" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X351" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="Y351" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z351" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30495,13 +30498,13 @@
         <v>1770</v>
       </c>
       <c r="W352" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X352" t="s">
         <v>1770</v>
       </c>
       <c r="Z352" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30563,16 +30566,16 @@
         <v>1771</v>
       </c>
       <c r="W353" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X353" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="Y353" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z353" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30634,7 +30637,7 @@
         <v>1772</v>
       </c>
       <c r="W354" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30696,7 +30699,7 @@
         <v>1773</v>
       </c>
       <c r="W355" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30755,7 +30758,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30814,7 +30817,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30873,7 +30876,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30935,7 +30938,7 @@
         <v>1774</v>
       </c>
       <c r="W359" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -31000,7 +31003,7 @@
         <v>1775</v>
       </c>
       <c r="W360" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -31065,7 +31068,7 @@
         <v>1776</v>
       </c>
       <c r="W361" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31127,16 +31130,16 @@
         <v>1777</v>
       </c>
       <c r="W362" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X362" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="Y362" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z362" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31198,16 +31201,16 @@
         <v>1778</v>
       </c>
       <c r="W363" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X363" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="Y363" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z363" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31269,7 +31272,7 @@
         <v>1779</v>
       </c>
       <c r="W364" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31331,7 +31334,7 @@
         <v>1780</v>
       </c>
       <c r="W365" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31396,7 +31399,7 @@
         <v>1781</v>
       </c>
       <c r="W366" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31458,7 +31461,7 @@
         <v>1782</v>
       </c>
       <c r="W367" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31520,7 +31523,7 @@
         <v>1783</v>
       </c>
       <c r="W368" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31585,13 +31588,13 @@
         <v>1784</v>
       </c>
       <c r="W369" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X369" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="Z369" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31653,7 +31656,7 @@
         <v>1785</v>
       </c>
       <c r="W370" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31715,16 +31718,16 @@
         <v>1786</v>
       </c>
       <c r="W371" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X371" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="Y371" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z371" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31789,7 +31792,7 @@
         <v>1787</v>
       </c>
       <c r="W372" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31854,16 +31857,16 @@
         <v>1788</v>
       </c>
       <c r="W373" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X373" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="Y373" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z373" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31925,7 +31928,7 @@
         <v>1789</v>
       </c>
       <c r="W374" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31990,7 +31993,7 @@
         <v>1790</v>
       </c>
       <c r="W375" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -32055,7 +32058,7 @@
         <v>1791</v>
       </c>
       <c r="W376" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32120,7 +32123,7 @@
         <v>1791</v>
       </c>
       <c r="W377" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32185,13 +32188,13 @@
         <v>1792</v>
       </c>
       <c r="W378" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X378" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="Z378" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32253,16 +32256,16 @@
         <v>1793</v>
       </c>
       <c r="W379" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X379" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="Y379" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z379" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32327,7 +32330,7 @@
         <v>1794</v>
       </c>
       <c r="W380" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32389,7 +32392,7 @@
         <v>1795</v>
       </c>
       <c r="W381" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32454,7 +32457,7 @@
         <v>1796</v>
       </c>
       <c r="W382" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32516,7 +32519,7 @@
         <v>1797</v>
       </c>
       <c r="W383" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32581,7 +32584,7 @@
         <v>1796</v>
       </c>
       <c r="W384" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32643,16 +32646,16 @@
         <v>1798</v>
       </c>
       <c r="W385" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X385" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="Y385" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z385" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32720,7 +32723,7 @@
         <v>1799</v>
       </c>
       <c r="W386" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32782,7 +32785,7 @@
         <v>1800</v>
       </c>
       <c r="W387" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32844,7 +32847,7 @@
         <v>1801</v>
       </c>
       <c r="W388" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32906,16 +32909,16 @@
         <v>1802</v>
       </c>
       <c r="W389" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X389" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="Y389" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z389" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32980,16 +32983,16 @@
         <v>1803</v>
       </c>
       <c r="W390" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X390" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="Y390" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z390" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -33054,7 +33057,7 @@
         <v>1804</v>
       </c>
       <c r="W391" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33116,7 +33119,7 @@
         <v>1805</v>
       </c>
       <c r="W392" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33178,16 +33181,16 @@
         <v>1806</v>
       </c>
       <c r="W393" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X393" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="Y393" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z393" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33249,7 +33252,7 @@
         <v>1807</v>
       </c>
       <c r="W394" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33314,16 +33317,16 @@
         <v>1808</v>
       </c>
       <c r="W395" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X395" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="Y395" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z395" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33388,13 +33391,13 @@
         <v>1809</v>
       </c>
       <c r="W396" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X396" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="Y396" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33456,7 +33459,7 @@
         <v>1810</v>
       </c>
       <c r="W397" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33518,7 +33521,7 @@
         <v>1811</v>
       </c>
       <c r="W398" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33583,7 +33586,7 @@
         <v>1812</v>
       </c>
       <c r="W399" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33648,16 +33651,16 @@
         <v>1813</v>
       </c>
       <c r="W400" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X400" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="Y400" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z400" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33722,7 +33725,7 @@
         <v>1814</v>
       </c>
       <c r="W401" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33787,7 +33790,7 @@
         <v>1815</v>
       </c>
       <c r="W402" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33852,16 +33855,16 @@
         <v>1816</v>
       </c>
       <c r="W403" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X403" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="Y403" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z403" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33926,7 +33929,7 @@
         <v>1817</v>
       </c>
       <c r="W404" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33991,7 +33994,7 @@
         <v>1818</v>
       </c>
       <c r="W405" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -34059,7 +34062,7 @@
         <v>1819</v>
       </c>
       <c r="W406" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34121,16 +34124,16 @@
         <v>1820</v>
       </c>
       <c r="W407" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X407" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="Y407" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z407" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34195,13 +34198,13 @@
         <v>1821</v>
       </c>
       <c r="W408" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X408" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="Z408" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34266,7 +34269,7 @@
         <v>1822</v>
       </c>
       <c r="W409" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34331,7 +34334,7 @@
         <v>1823</v>
       </c>
       <c r="W410" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34396,7 +34399,7 @@
         <v>1824</v>
       </c>
       <c r="W411" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34461,7 +34464,7 @@
         <v>1825</v>
       </c>
       <c r="W412" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34526,7 +34529,7 @@
         <v>1826</v>
       </c>
       <c r="W413" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34591,7 +34594,7 @@
         <v>1826</v>
       </c>
       <c r="W414" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34656,7 +34659,7 @@
         <v>1827</v>
       </c>
       <c r="W415" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34721,7 +34724,7 @@
         <v>1828</v>
       </c>
       <c r="W416" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34786,7 +34789,7 @@
         <v>1826</v>
       </c>
       <c r="W417" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34851,7 +34854,7 @@
         <v>1829</v>
       </c>
       <c r="W418" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34916,7 +34919,7 @@
         <v>1830</v>
       </c>
       <c r="W419" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34981,16 +34984,16 @@
         <v>1831</v>
       </c>
       <c r="W420" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X420" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="Y420" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z420" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -35055,7 +35058,7 @@
         <v>1832</v>
       </c>
       <c r="W421" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35120,7 +35123,7 @@
         <v>1833</v>
       </c>
       <c r="W422" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35185,7 +35188,7 @@
         <v>1834</v>
       </c>
       <c r="W423" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35250,16 +35253,16 @@
         <v>1835</v>
       </c>
       <c r="W424" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X424" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="Y424" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z424" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35324,7 +35327,7 @@
         <v>1834</v>
       </c>
       <c r="W425" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35389,7 +35392,7 @@
         <v>1836</v>
       </c>
       <c r="W426" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35454,7 +35457,7 @@
         <v>1837</v>
       </c>
       <c r="W427" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35519,13 +35522,13 @@
         <v>1838</v>
       </c>
       <c r="W428" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X428" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="Y428" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35590,16 +35593,16 @@
         <v>1839</v>
       </c>
       <c r="W429" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X429" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="Y429" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z429" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35664,7 +35667,7 @@
         <v>1840</v>
       </c>
       <c r="W430" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35729,16 +35732,16 @@
         <v>1841</v>
       </c>
       <c r="W431" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X431" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="Y431" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z431" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35803,7 +35806,7 @@
         <v>1842</v>
       </c>
       <c r="W432" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35868,7 +35871,7 @@
         <v>1843</v>
       </c>
       <c r="W433" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35933,7 +35936,7 @@
         <v>1844</v>
       </c>
       <c r="W434" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -35998,7 +36001,7 @@
         <v>1845</v>
       </c>
       <c r="W435" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -36063,7 +36066,7 @@
         <v>1846</v>
       </c>
       <c r="W436" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36128,7 +36131,7 @@
         <v>1847</v>
       </c>
       <c r="W437" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36193,7 +36196,7 @@
         <v>1848</v>
       </c>
       <c r="W438" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36258,7 +36261,7 @@
         <v>1849</v>
       </c>
       <c r="W439" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36323,16 +36326,16 @@
         <v>1850</v>
       </c>
       <c r="W440" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X440" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="Y440" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z440" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36397,16 +36400,16 @@
         <v>1851</v>
       </c>
       <c r="W441" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X441" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="Y441" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z441" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36471,16 +36474,16 @@
         <v>1852</v>
       </c>
       <c r="W442" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X442" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="Y442" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z442" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36545,7 +36548,7 @@
         <v>1853</v>
       </c>
       <c r="W443" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36610,7 +36613,7 @@
         <v>1854</v>
       </c>
       <c r="W444" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36675,16 +36678,16 @@
         <v>1851</v>
       </c>
       <c r="W445" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X445" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="Y445" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z445" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36749,16 +36752,16 @@
         <v>1851</v>
       </c>
       <c r="W446" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X446" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="Y446" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z446" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36823,16 +36826,16 @@
         <v>1855</v>
       </c>
       <c r="W447" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X447" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="Y447" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z447" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36897,16 +36900,16 @@
         <v>1851</v>
       </c>
       <c r="W448" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X448" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="Y448" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z448" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36971,16 +36974,16 @@
         <v>1851</v>
       </c>
       <c r="W449" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X449" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="Y449" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z449" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -37045,16 +37048,16 @@
         <v>1856</v>
       </c>
       <c r="W450" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X450" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="Y450" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z450" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37119,16 +37122,16 @@
         <v>1857</v>
       </c>
       <c r="W451" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X451" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="Y451" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z451" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37193,7 +37196,7 @@
         <v>1858</v>
       </c>
       <c r="W452" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37258,16 +37261,16 @@
         <v>1859</v>
       </c>
       <c r="W453" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X453" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="Y453" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z453" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37332,16 +37335,16 @@
         <v>1860</v>
       </c>
       <c r="W454" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X454" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="Y454" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z454" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37406,16 +37409,16 @@
         <v>1861</v>
       </c>
       <c r="W455" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X455" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="Y455" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z455" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37480,16 +37483,16 @@
         <v>1862</v>
       </c>
       <c r="W456" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X456" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="Y456" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z456" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37554,7 +37557,7 @@
         <v>1863</v>
       </c>
       <c r="W457" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37619,7 +37622,7 @@
         <v>1863</v>
       </c>
       <c r="W458" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37684,16 +37687,16 @@
         <v>1861</v>
       </c>
       <c r="W459" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X459" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="Y459" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z459" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37758,16 +37761,16 @@
         <v>1864</v>
       </c>
       <c r="W460" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X460" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="Y460" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z460" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37832,16 +37835,16 @@
         <v>1865</v>
       </c>
       <c r="W461" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X461" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="Y461" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z461" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37906,7 +37909,7 @@
         <v>1866</v>
       </c>
       <c r="W462" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37971,16 +37974,16 @@
         <v>1867</v>
       </c>
       <c r="W463" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X463" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="Y463" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z463" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -38045,16 +38048,16 @@
         <v>1868</v>
       </c>
       <c r="W464" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X464" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="Y464" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z464" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38119,16 +38122,16 @@
         <v>1869</v>
       </c>
       <c r="W465" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X465" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="Y465" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z465" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38193,7 +38196,7 @@
         <v>1870</v>
       </c>
       <c r="W466" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38258,16 +38261,16 @@
         <v>1871</v>
       </c>
       <c r="W467" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X467" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="Y467" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z467" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38332,16 +38335,16 @@
         <v>1872</v>
       </c>
       <c r="W468" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X468" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="Y468" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z468" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38406,16 +38409,16 @@
         <v>1873</v>
       </c>
       <c r="W469" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X469" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="Y469" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z469" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38480,16 +38483,16 @@
         <v>1874</v>
       </c>
       <c r="W470" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X470" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="Y470" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z470" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38554,7 +38557,7 @@
         <v>1875</v>
       </c>
       <c r="W471" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38619,16 +38622,16 @@
         <v>1876</v>
       </c>
       <c r="W472" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X472" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="Y472" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z472" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38693,16 +38696,16 @@
         <v>1876</v>
       </c>
       <c r="W473" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X473" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="Y473" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z473" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38767,7 +38770,7 @@
         <v>1877</v>
       </c>
       <c r="W474" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38832,16 +38835,16 @@
         <v>1878</v>
       </c>
       <c r="W475" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X475" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="Y475" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z475" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38906,16 +38909,16 @@
         <v>1879</v>
       </c>
       <c r="W476" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X476" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="Y476" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z476" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38980,7 +38983,7 @@
         <v>1880</v>
       </c>
       <c r="W477" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -39045,7 +39048,7 @@
         <v>1881</v>
       </c>
       <c r="W478" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39110,16 +39113,16 @@
         <v>1882</v>
       </c>
       <c r="W479" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X479" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="Y479" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z479" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39184,16 +39187,16 @@
         <v>1883</v>
       </c>
       <c r="W480" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X480" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="Y480" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z480" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39258,16 +39261,16 @@
         <v>1884</v>
       </c>
       <c r="W481" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X481" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="Y481" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z481" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39332,7 +39335,7 @@
         <v>1885</v>
       </c>
       <c r="W482" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39397,7 +39400,7 @@
         <v>1886</v>
       </c>
       <c r="W483" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39465,13 +39468,13 @@
         <v>1887</v>
       </c>
       <c r="W484" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39536,7 +39539,7 @@
         <v>1888</v>
       </c>
       <c r="W485" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39604,13 +39607,13 @@
         <v>1889</v>
       </c>
       <c r="W486" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39675,7 +39678,7 @@
         <v>1890</v>
       </c>
       <c r="W487" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39740,16 +39743,16 @@
         <v>1891</v>
       </c>
       <c r="W488" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X488" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="Y488" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z488" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39814,7 +39817,7 @@
         <v>1892</v>
       </c>
       <c r="W489" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39882,13 +39885,13 @@
         <v>1893</v>
       </c>
       <c r="W490" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39953,16 +39956,16 @@
         <v>1894</v>
       </c>
       <c r="W491" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X491" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="Y491" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z491" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -40027,16 +40030,16 @@
         <v>1895</v>
       </c>
       <c r="W492" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X492" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="Y492" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z492" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40101,16 +40104,16 @@
         <v>1896</v>
       </c>
       <c r="W493" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X493" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="Y493" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z493" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40175,13 +40178,13 @@
         <v>1897</v>
       </c>
       <c r="W494" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X494" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="Y494" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40246,16 +40249,16 @@
         <v>1898</v>
       </c>
       <c r="W495" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X495" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="Y495" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z495" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40320,7 +40323,7 @@
         <v>1899</v>
       </c>
       <c r="W496" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40388,7 +40391,7 @@
         <v>1900</v>
       </c>
       <c r="W497" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40453,7 +40456,7 @@
         <v>1901</v>
       </c>
       <c r="W498" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40521,7 +40524,7 @@
         <v>1902</v>
       </c>
       <c r="W499" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40586,16 +40589,16 @@
         <v>1903</v>
       </c>
       <c r="W500" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X500" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="Y500" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z500" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40660,16 +40663,16 @@
         <v>1904</v>
       </c>
       <c r="W501" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X501" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="Y501" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z501" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40734,7 +40737,7 @@
         <v>1905</v>
       </c>
       <c r="W502" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40802,7 +40805,7 @@
         <v>1906</v>
       </c>
       <c r="W503" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40870,16 +40873,16 @@
         <v>1907</v>
       </c>
       <c r="W504" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X504" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="Y504" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z504" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40944,7 +40947,7 @@
         <v>1908</v>
       </c>
       <c r="W505" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -41009,16 +41012,16 @@
         <v>1909</v>
       </c>
       <c r="W506" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X506" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="Y506" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z506" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -41083,7 +41086,7 @@
         <v>1910</v>
       </c>
       <c r="W507" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41148,7 +41151,7 @@
         <v>1911</v>
       </c>
       <c r="W508" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41213,16 +41216,16 @@
         <v>1912</v>
       </c>
       <c r="W509" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X509" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="Y509" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z509" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41287,16 +41290,16 @@
         <v>1913</v>
       </c>
       <c r="W510" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X510" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="Y510" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z510" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41364,7 +41367,7 @@
         <v>1914</v>
       </c>
       <c r="W511" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41432,7 +41435,7 @@
         <v>1915</v>
       </c>
       <c r="W512" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41500,7 +41503,7 @@
         <v>1916</v>
       </c>
       <c r="W513" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41568,7 +41571,7 @@
         <v>1916</v>
       </c>
       <c r="W514" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41636,7 +41639,7 @@
         <v>1916</v>
       </c>
       <c r="W515" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41704,13 +41707,13 @@
         <v>1917</v>
       </c>
       <c r="W516" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41778,13 +41781,13 @@
         <v>1918</v>
       </c>
       <c r="W517" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41852,16 +41855,16 @@
         <v>1919</v>
       </c>
       <c r="W518" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X518" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="Y518" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z518" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41929,16 +41932,16 @@
         <v>1920</v>
       </c>
       <c r="W519" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X519" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="Y519" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z519" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -42003,7 +42006,7 @@
         <v>1523</v>
       </c>
       <c r="W520" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -42071,7 +42074,7 @@
         <v>1921</v>
       </c>
       <c r="W521" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42139,7 +42142,7 @@
         <v>1921</v>
       </c>
       <c r="W522" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42207,7 +42210,7 @@
         <v>1922</v>
       </c>
       <c r="W523" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42275,7 +42278,7 @@
         <v>1923</v>
       </c>
       <c r="W524" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42343,7 +42346,7 @@
         <v>1924</v>
       </c>
       <c r="W525" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42411,7 +42414,7 @@
         <v>1925</v>
       </c>
       <c r="W526" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42479,7 +42482,7 @@
         <v>1926</v>
       </c>
       <c r="W527" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42544,7 +42547,7 @@
         <v>1927</v>
       </c>
       <c r="W528" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42612,7 +42615,7 @@
         <v>1928</v>
       </c>
       <c r="W529" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42680,16 +42683,16 @@
         <v>1929</v>
       </c>
       <c r="W530" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X530" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="Y530" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z530" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42757,7 +42760,7 @@
         <v>1930</v>
       </c>
       <c r="W531" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42822,7 +42825,7 @@
         <v>1931</v>
       </c>
       <c r="W532" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42890,16 +42893,16 @@
         <v>1932</v>
       </c>
       <c r="W533" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X533" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="Y533" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z533" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42967,13 +42970,13 @@
         <v>1933</v>
       </c>
       <c r="W534" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -43041,7 +43044,7 @@
         <v>1934</v>
       </c>
       <c r="W535" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43109,7 +43112,7 @@
         <v>1935</v>
       </c>
       <c r="W536" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43177,16 +43180,16 @@
         <v>1936</v>
       </c>
       <c r="W537" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X537" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="Y537" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z537" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43254,7 +43257,7 @@
         <v>1937</v>
       </c>
       <c r="W538" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43322,7 +43325,7 @@
         <v>1938</v>
       </c>
       <c r="W539" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43390,7 +43393,7 @@
         <v>1939</v>
       </c>
       <c r="W540" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43458,7 +43461,7 @@
         <v>1940</v>
       </c>
       <c r="W541" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43526,16 +43529,16 @@
         <v>1941</v>
       </c>
       <c r="W542" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X542" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="Y542" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z542" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43603,7 +43606,7 @@
         <v>1942</v>
       </c>
       <c r="W543" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43671,16 +43674,16 @@
         <v>1943</v>
       </c>
       <c r="W544" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="X544" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="Y544" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="Z544" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43748,7 +43751,7 @@
         <v>1944</v>
       </c>
       <c r="W545" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43816,7 +43819,7 @@
         <v>1945</v>
       </c>
       <c r="W546" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43884,7 +43887,7 @@
         <v>1946</v>
       </c>
       <c r="W547" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43952,7 +43955,7 @@
         <v>1947</v>
       </c>
       <c r="W548" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -44020,7 +44023,7 @@
         <v>1947</v>
       </c>
       <c r="W549" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44088,7 +44091,7 @@
         <v>1948</v>
       </c>
       <c r="W550" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44153,7 +44156,7 @@
         <v>1949</v>
       </c>
       <c r="W551" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44221,7 +44224,7 @@
         <v>1950</v>
       </c>
       <c r="W552" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44286,7 +44289,7 @@
         <v>1951</v>
       </c>
       <c r="W553" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44354,7 +44357,7 @@
         <v>1952</v>
       </c>
       <c r="W554" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44422,7 +44425,7 @@
         <v>1953</v>
       </c>
       <c r="W555" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44490,7 +44493,7 @@
         <v>1954</v>
       </c>
       <c r="W556" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44555,7 +44558,7 @@
         <v>1955</v>
       </c>
       <c r="W557" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44623,7 +44626,7 @@
         <v>1956</v>
       </c>
       <c r="W558" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44691,7 +44694,7 @@
         <v>1957</v>
       </c>
       <c r="W559" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44756,7 +44759,7 @@
         <v>1958</v>
       </c>
       <c r="W560" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44824,7 +44827,7 @@
         <v>1959</v>
       </c>
       <c r="W561" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44889,10 +44892,10 @@
         <v>1521</v>
       </c>
       <c r="V562" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="W562" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44957,7 +44960,7 @@
         <v>1960</v>
       </c>
       <c r="W563" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -45025,7 +45028,7 @@
         <v>1961</v>
       </c>
       <c r="W564" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45093,7 +45096,7 @@
         <v>1962</v>
       </c>
       <c r="W565" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45161,7 +45164,7 @@
         <v>1963</v>
       </c>
       <c r="W566" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45229,7 +45232,7 @@
         <v>1964</v>
       </c>
       <c r="W567" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45297,7 +45300,7 @@
         <v>1965</v>
       </c>
       <c r="W568" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA568" t="b">
         <v>0</v>
@@ -45365,7 +45368,7 @@
         <v>1966</v>
       </c>
       <c r="W569" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45430,7 +45433,7 @@
         <v>1967</v>
       </c>
       <c r="W570" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45495,7 +45498,7 @@
         <v>1968</v>
       </c>
       <c r="W571" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45563,7 +45566,7 @@
         <v>1969</v>
       </c>
       <c r="W572" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45631,7 +45634,7 @@
         <v>1970</v>
       </c>
       <c r="W573" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45699,7 +45702,7 @@
         <v>1971</v>
       </c>
       <c r="W574" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45767,7 +45770,7 @@
         <v>1972</v>
       </c>
       <c r="W575" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -45835,7 +45838,7 @@
         <v>1973</v>
       </c>
       <c r="W576" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45903,7 +45906,7 @@
         <v>1973</v>
       </c>
       <c r="W577" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45971,7 +45974,7 @@
         <v>1974</v>
       </c>
       <c r="W578" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -46039,7 +46042,7 @@
         <v>1975</v>
       </c>
       <c r="W579" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46107,7 +46110,7 @@
         <v>1976</v>
       </c>
       <c r="W580" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46175,7 +46178,7 @@
         <v>1977</v>
       </c>
       <c r="W581" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46243,7 +46246,7 @@
         <v>1978</v>
       </c>
       <c r="W582" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA582" t="b">
         <v>0</v>
@@ -46311,7 +46314,7 @@
         <v>1979</v>
       </c>
       <c r="W583" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA583" t="b">
         <v>0</v>
@@ -46379,7 +46382,7 @@
         <v>1980</v>
       </c>
       <c r="W584" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46447,7 +46450,7 @@
         <v>1980</v>
       </c>
       <c r="W585" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46512,10 +46515,10 @@
         <v>1521</v>
       </c>
       <c r="V586" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="W586" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46583,7 +46586,7 @@
         <v>1981</v>
       </c>
       <c r="W587" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA587" t="b">
         <v>0</v>
@@ -46651,10 +46654,10 @@
         <v>1982</v>
       </c>
       <c r="V588" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="W588" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46722,7 +46725,7 @@
         <v>1983</v>
       </c>
       <c r="W589" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA589" t="b">
         <v>0</v>
@@ -46790,7 +46793,7 @@
         <v>1984</v>
       </c>
       <c r="W590" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA590" t="b">
         <v>0</v>
@@ -46858,7 +46861,7 @@
         <v>1985</v>
       </c>
       <c r="W591" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA591" t="b">
         <v>0</v>
@@ -46926,7 +46929,7 @@
         <v>1986</v>
       </c>
       <c r="W592" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA592" t="b">
         <v>0</v>
@@ -46997,10 +47000,10 @@
         <v>1987</v>
       </c>
       <c r="V593" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="W593" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA593" t="b">
         <v>0</v>
@@ -47068,7 +47071,7 @@
         <v>1986</v>
       </c>
       <c r="W594" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA594" t="b">
         <v>0</v>
@@ -47130,10 +47133,10 @@
         <v>1520</v>
       </c>
       <c r="V595" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="W595" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA595" t="b">
         <v>1</v>
@@ -47201,7 +47204,7 @@
         <v>1988</v>
       </c>
       <c r="W596" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA596" t="b">
         <v>0</v>
@@ -47250,6 +47253,9 @@
       <c r="N597" s="1">
         <v>46259</v>
       </c>
+      <c r="O597" s="1">
+        <v>46259</v>
+      </c>
       <c r="Q597">
         <v>0</v>
       </c>
@@ -47266,10 +47272,10 @@
         <v>1989</v>
       </c>
       <c r="V597" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="W597" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA597" t="b">
         <v>1</v>
@@ -47337,7 +47343,7 @@
         <v>1990</v>
       </c>
       <c r="W598" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA598" t="b">
         <v>0</v>
@@ -47399,10 +47405,10 @@
         <v>1521</v>
       </c>
       <c r="V599" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="W599" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA599" t="b">
         <v>1</v>
@@ -47466,11 +47472,14 @@
       <c r="T600" t="s">
         <v>1521</v>
       </c>
+      <c r="U600" t="s">
+        <v>1991</v>
+      </c>
       <c r="V600" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="W600" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA600" t="b">
         <v>1</v>
@@ -47532,7 +47541,7 @@
         <v>1521</v>
       </c>
       <c r="W601" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA601" t="b">
         <v>1</v>
@@ -47594,10 +47603,10 @@
         <v>1521</v>
       </c>
       <c r="V602" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="W602" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA602" t="b">
         <v>1</v>
@@ -47659,13 +47668,13 @@
         <v>1521</v>
       </c>
       <c r="U603" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="V603" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="W603" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA603" t="b">
         <v>1</v>
@@ -47730,13 +47739,10 @@
         <v>1521</v>
       </c>
       <c r="U604" t="s">
-        <v>1992</v>
-      </c>
-      <c r="V604" t="s">
-        <v>2003</v>
+        <v>1993</v>
       </c>
       <c r="W604" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA604" t="b">
         <v>0</v>
@@ -47785,17 +47791,26 @@
       <c r="N605" s="1">
         <v>46289</v>
       </c>
+      <c r="O605" s="1">
+        <v>46258</v>
+      </c>
       <c r="Q605">
         <v>-30</v>
       </c>
       <c r="R605">
         <v>1</v>
       </c>
+      <c r="S605" t="s">
+        <v>1521</v>
+      </c>
       <c r="T605" t="s">
         <v>1520</v>
       </c>
+      <c r="V605" t="s">
+        <v>2004</v>
+      </c>
       <c r="W605" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="AA605" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7601" uniqueCount="2378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7600" uniqueCount="2377">
   <si>
     <t>om_emg</t>
   </si>
@@ -5998,37 +5998,34 @@
     <t>Recibo 719/FAB/26 assinado em 24/08. Ramon 24/08/26</t>
   </si>
   <si>
-    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08 - MATERIAL EM TRANSITO - RECIBO 722/FAB/26 DPE 24/08/2026</t>
+    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08 - MATERIAL EM TRANSITO - RECIBO 722/FAB/26</t>
   </si>
   <si>
     <t>PEDIDO NO EPM E-C98-26060 - CLA-05-08 , por gentileza, me confirme se está correto a data da informação e prazo de entrega do item.O item solicitado não atende a pane do sistema ARCOND,pôs a pane é de 18/11/2024, anterior ao contrato vigente ,desta forma deve ser feito toda analise do sistema ,devido muito tempo inoperante e sem o item. SO R1 Bispo VEE-ONE-BE em 06/08/26</t>
   </si>
   <si>
-    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08- ITEM AGUARDANDO DEFINIÇÃO DA COORDENADORIA QUANTO A EFETIVIDADE PARA APLICAÇÃO NA REFERIDA ANV.- CLA-13-08 - AT 685000002258</t>
-  </si>
-  <si>
-    <t>Temos no STK V1, material em separação, recibo 682/FAB/26 - atz rc 13/08 - MATERIAL ENVIADO VIA AWB 12752709016 - DPE 18/08/2026 - ENTREGUE DIA 18/08/2026</t>
+    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08- ITEM AGUARDANDO DEFINIÇÃO DA COORDENADORIA QUANTO A EFETIVIDADE PARA APLICAÇÃO NA REFERIDA ANV.- CLA-13-08 - AT 685000002258. Conforme relatado pela Coordenadoria, foi enviado, via CAN, um item novo, PN 2641010-3. Dessa forma, o item que atualmente se encontra em poder da VeeOne deverá ser estornado ao estoque.CLA-25-08</t>
   </si>
   <si>
     <t>Enviado para o Operador em 24/08/26 - AWB 127-5459 2764 - REZ 24/08/26</t>
   </si>
   <si>
-    <t>ITEM FOI ENTREGUE PARA A FAB VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUECLA-17-08 - material enviado via awb 12754592764, DPE 25/08/2026</t>
-  </si>
-  <si>
-    <t>Colocado pedido no fornecedor WAGA INTERNATIONAL - aguardando proforma invoice para pagamento. ATZ 21/08</t>
-  </si>
-  <si>
-    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08 - AWB 12754088775 - CLA-21-08</t>
-  </si>
-  <si>
-    <t>Colocado pedido Textron WB0003128625 - tracking 535477333011 - previsão de entrega 24/08 V1 JPA</t>
-  </si>
-  <si>
-    <t>Colocado pedido no fornecedor S624333 - validando entrega em Miami - TEMOS 3 EA NO ESTOQUE DA BANT</t>
-  </si>
-  <si>
-    <t>Material enviado via recibo 720/FAB/26 DPE 24/08/2026</t>
+    <t>ITEM FOI ENTREGUE PARA A FAB PAMALS VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUE CLA-17-08 - Aguardando autorização para movimentação a BANT 25/08/2026</t>
+  </si>
+  <si>
+    <t>Colocado pedido no fornecedor WAGA INTERNATIONAL - validando previsão de entrega em Miami. ATZ 25/08</t>
+  </si>
+  <si>
+    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08 - AWB 12754088775 - CLA-21-08 - recebido dia 22/08/2026</t>
+  </si>
+  <si>
+    <t>Colocado pedido Textron WB0003128625 - tracking 535477333011 - previsão de entrega 25/08 V1 JPA - MATERIAL ENVIADO VIA RECIBO 726/FAB/26, AWB A SER GERADA PELA GOLLOG RC 25/08/2026</t>
+  </si>
+  <si>
+    <t>Colocado pedido no fornecedor I823285 - entregue em Miami 21/08 - TEMOS 3 EA NO ESTOQUE DA BANT. Material seguiu via awb 12754249845. Recebido por Kleyton em 24/08. Atl Ges.</t>
+  </si>
+  <si>
+    <t>Material enviado via recibo 720/FAB/26 DPE 24/08/2026 - Retirado dia 24/08/2026 por Paula Pereira id 569968</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -7625,7 +7622,7 @@
         <v>1524</v>
       </c>
       <c r="W2" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7687,16 +7684,16 @@
         <v>1525</v>
       </c>
       <c r="W3" t="s">
+        <v>2004</v>
+      </c>
+      <c r="X3" t="s">
         <v>2005</v>
       </c>
-      <c r="X3" t="s">
-        <v>2006</v>
-      </c>
       <c r="Y3" t="s">
+        <v>2163</v>
+      </c>
+      <c r="Z3" t="s">
         <v>2164</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>2165</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7758,7 +7755,7 @@
         <v>1524</v>
       </c>
       <c r="W4" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7820,7 +7817,7 @@
         <v>1526</v>
       </c>
       <c r="W5" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7882,7 +7879,7 @@
         <v>1527</v>
       </c>
       <c r="W6" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7944,7 +7941,7 @@
         <v>1528</v>
       </c>
       <c r="W7" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -8006,7 +8003,7 @@
         <v>1529</v>
       </c>
       <c r="W8" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -8068,7 +8065,7 @@
         <v>1530</v>
       </c>
       <c r="W9" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8130,7 +8127,7 @@
         <v>1531</v>
       </c>
       <c r="W10" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8192,7 +8189,7 @@
         <v>1532</v>
       </c>
       <c r="W11" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8254,7 +8251,7 @@
         <v>1533</v>
       </c>
       <c r="W12" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8316,7 +8313,7 @@
         <v>1529</v>
       </c>
       <c r="W13" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8378,16 +8375,16 @@
         <v>1534</v>
       </c>
       <c r="W14" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X14" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="Y14" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z14" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8446,7 +8443,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8511,7 +8508,7 @@
         <v>1535</v>
       </c>
       <c r="W16" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8573,7 +8570,7 @@
         <v>1536</v>
       </c>
       <c r="W17" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8635,7 +8632,7 @@
         <v>1527</v>
       </c>
       <c r="W18" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8697,7 +8694,7 @@
         <v>1527</v>
       </c>
       <c r="W19" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8759,7 +8756,7 @@
         <v>1537</v>
       </c>
       <c r="W20" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8821,7 +8818,7 @@
         <v>1538</v>
       </c>
       <c r="W21" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8883,7 +8880,7 @@
         <v>1538</v>
       </c>
       <c r="W22" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8945,7 +8942,7 @@
         <v>1539</v>
       </c>
       <c r="W23" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -9004,7 +9001,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -9063,7 +9060,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9125,7 +9122,7 @@
         <v>1527</v>
       </c>
       <c r="W26" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9184,7 +9181,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9243,7 +9240,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9305,7 +9302,7 @@
         <v>1540</v>
       </c>
       <c r="W29" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9364,7 +9361,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9426,7 +9423,7 @@
         <v>1541</v>
       </c>
       <c r="W31" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9488,7 +9485,7 @@
         <v>1542</v>
       </c>
       <c r="W32" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9550,7 +9547,7 @@
         <v>1543</v>
       </c>
       <c r="W33" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9612,7 +9609,7 @@
         <v>1544</v>
       </c>
       <c r="W34" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9674,7 +9671,7 @@
         <v>1545</v>
       </c>
       <c r="W35" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9736,7 +9733,7 @@
         <v>1541</v>
       </c>
       <c r="W36" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9798,7 +9795,7 @@
         <v>1546</v>
       </c>
       <c r="W37" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9860,7 +9857,7 @@
         <v>1524</v>
       </c>
       <c r="W38" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9922,7 +9919,7 @@
         <v>1543</v>
       </c>
       <c r="W39" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9984,7 +9981,7 @@
         <v>1547</v>
       </c>
       <c r="W40" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -10046,7 +10043,7 @@
         <v>1548</v>
       </c>
       <c r="W41" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10108,16 +10105,16 @@
         <v>1549</v>
       </c>
       <c r="W42" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X42" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="Y42" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z42" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10179,7 +10176,7 @@
         <v>1543</v>
       </c>
       <c r="W43" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10241,7 +10238,7 @@
         <v>1550</v>
       </c>
       <c r="W44" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10303,7 +10300,7 @@
         <v>1543</v>
       </c>
       <c r="W45" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10365,7 +10362,7 @@
         <v>1543</v>
       </c>
       <c r="W46" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10427,7 +10424,7 @@
         <v>1551</v>
       </c>
       <c r="W47" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10489,7 +10486,7 @@
         <v>1552</v>
       </c>
       <c r="W48" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10551,7 +10548,7 @@
         <v>1553</v>
       </c>
       <c r="W49" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10613,7 +10610,7 @@
         <v>1554</v>
       </c>
       <c r="W50" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10675,7 +10672,7 @@
         <v>1555</v>
       </c>
       <c r="W51" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10737,7 +10734,7 @@
         <v>1544</v>
       </c>
       <c r="W52" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10799,7 +10796,7 @@
         <v>1538</v>
       </c>
       <c r="W53" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10861,7 +10858,7 @@
         <v>1538</v>
       </c>
       <c r="W54" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10923,7 +10920,7 @@
         <v>1538</v>
       </c>
       <c r="W55" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10985,7 +10982,7 @@
         <v>1556</v>
       </c>
       <c r="W56" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -11047,7 +11044,7 @@
         <v>1557</v>
       </c>
       <c r="W57" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11109,16 +11106,16 @@
         <v>1558</v>
       </c>
       <c r="W58" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X58" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="Y58" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z58" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11180,7 +11177,7 @@
         <v>1559</v>
       </c>
       <c r="W59" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11242,7 +11239,7 @@
         <v>1560</v>
       </c>
       <c r="W60" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11304,7 +11301,7 @@
         <v>1538</v>
       </c>
       <c r="W61" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11366,7 +11363,7 @@
         <v>1561</v>
       </c>
       <c r="W62" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11425,7 +11422,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11484,7 +11481,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11543,7 +11540,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11602,7 +11599,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11661,7 +11658,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11720,7 +11717,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11782,7 +11779,7 @@
         <v>1562</v>
       </c>
       <c r="W69" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11844,7 +11841,7 @@
         <v>1560</v>
       </c>
       <c r="W70" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11906,7 +11903,7 @@
         <v>1545</v>
       </c>
       <c r="W71" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11968,7 +11965,7 @@
         <v>1563</v>
       </c>
       <c r="W72" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -12030,7 +12027,7 @@
         <v>1564</v>
       </c>
       <c r="W73" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12092,16 +12089,16 @@
         <v>1565</v>
       </c>
       <c r="W74" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X74" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="Y74" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z74" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12163,16 +12160,16 @@
         <v>1566</v>
       </c>
       <c r="W75" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X75" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="Y75" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z75" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12234,7 +12231,7 @@
         <v>1545</v>
       </c>
       <c r="W76" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12296,7 +12293,7 @@
         <v>1545</v>
       </c>
       <c r="W77" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12358,10 +12355,10 @@
         <v>1567</v>
       </c>
       <c r="W78" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="Z78" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12426,7 +12423,7 @@
         <v>1568</v>
       </c>
       <c r="W79" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12485,7 +12482,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12544,7 +12541,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12606,7 +12603,7 @@
         <v>1569</v>
       </c>
       <c r="W82" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12668,7 +12665,7 @@
         <v>1570</v>
       </c>
       <c r="W83" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12730,7 +12727,7 @@
         <v>1571</v>
       </c>
       <c r="W84" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12789,7 +12786,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12851,7 +12848,7 @@
         <v>1572</v>
       </c>
       <c r="W86" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12913,7 +12910,7 @@
         <v>1573</v>
       </c>
       <c r="W87" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12975,7 +12972,7 @@
         <v>1573</v>
       </c>
       <c r="W88" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -13037,7 +13034,7 @@
         <v>1538</v>
       </c>
       <c r="W89" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13099,16 +13096,16 @@
         <v>1574</v>
       </c>
       <c r="W90" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X90" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="Y90" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z90" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13170,16 +13167,16 @@
         <v>1575</v>
       </c>
       <c r="W91" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X91" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="Y91" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z91" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13241,7 +13238,7 @@
         <v>1576</v>
       </c>
       <c r="W92" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13303,7 +13300,7 @@
         <v>1577</v>
       </c>
       <c r="W93" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13365,7 +13362,7 @@
         <v>1577</v>
       </c>
       <c r="W94" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13427,7 +13424,7 @@
         <v>1578</v>
       </c>
       <c r="W95" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13489,16 +13486,16 @@
         <v>1579</v>
       </c>
       <c r="W96" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X96" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="Y96" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z96" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13560,7 +13557,7 @@
         <v>1580</v>
       </c>
       <c r="W97" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13622,7 +13619,7 @@
         <v>1581</v>
       </c>
       <c r="W98" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13684,7 +13681,7 @@
         <v>1582</v>
       </c>
       <c r="W99" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13746,7 +13743,7 @@
         <v>1583</v>
       </c>
       <c r="W100" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13808,16 +13805,16 @@
         <v>1584</v>
       </c>
       <c r="W101" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X101" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="Y101" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z101" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13879,7 +13876,7 @@
         <v>1585</v>
       </c>
       <c r="W102" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13941,7 +13938,7 @@
         <v>1585</v>
       </c>
       <c r="W103" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -14003,7 +14000,7 @@
         <v>1586</v>
       </c>
       <c r="W104" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -14065,16 +14062,16 @@
         <v>1587</v>
       </c>
       <c r="W105" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X105" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="Y105" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z105" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14136,16 +14133,16 @@
         <v>1588</v>
       </c>
       <c r="W106" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X106" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="Y106" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z106" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14207,7 +14204,7 @@
         <v>1589</v>
       </c>
       <c r="W107" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14269,16 +14266,16 @@
         <v>1590</v>
       </c>
       <c r="W108" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X108" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="Y108" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z108" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14340,16 +14337,16 @@
         <v>1591</v>
       </c>
       <c r="W109" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X109" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="Y109" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z109" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14408,7 +14405,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14470,16 +14467,16 @@
         <v>1592</v>
       </c>
       <c r="W111" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X111" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="Y111" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z111" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14541,16 +14538,16 @@
         <v>1593</v>
       </c>
       <c r="W112" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X112" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="Y112" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z112" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14612,16 +14609,16 @@
         <v>1594</v>
       </c>
       <c r="W113" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X113" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="Y113" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z113" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14683,16 +14680,16 @@
         <v>1595</v>
       </c>
       <c r="W114" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X114" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="Y114" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z114" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14754,16 +14751,16 @@
         <v>1591</v>
       </c>
       <c r="W115" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X115" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="Y115" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z115" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14825,16 +14822,16 @@
         <v>1591</v>
       </c>
       <c r="W116" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X116" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="Y116" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z116" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14896,16 +14893,16 @@
         <v>1596</v>
       </c>
       <c r="W117" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X117" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="Y117" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z117" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14967,16 +14964,16 @@
         <v>1597</v>
       </c>
       <c r="W118" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X118" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="Y118" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z118" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -15038,7 +15035,7 @@
         <v>1598</v>
       </c>
       <c r="W119" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15100,16 +15097,16 @@
         <v>1599</v>
       </c>
       <c r="W120" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X120" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y120" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z120" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15171,16 +15168,16 @@
         <v>1599</v>
       </c>
       <c r="W121" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X121" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y121" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z121" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15242,16 +15239,16 @@
         <v>1599</v>
       </c>
       <c r="W122" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X122" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y122" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z122" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15313,16 +15310,16 @@
         <v>1599</v>
       </c>
       <c r="W123" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X123" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y123" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z123" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15384,16 +15381,16 @@
         <v>1599</v>
       </c>
       <c r="W124" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X124" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y124" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z124" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15455,16 +15452,16 @@
         <v>1599</v>
       </c>
       <c r="W125" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X125" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y125" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z125" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15526,16 +15523,16 @@
         <v>1599</v>
       </c>
       <c r="W126" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X126" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y126" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z126" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15597,16 +15594,16 @@
         <v>1600</v>
       </c>
       <c r="W127" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X127" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="Y127" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z127" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15668,16 +15665,16 @@
         <v>1601</v>
       </c>
       <c r="W128" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X128" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="Y128" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z128" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15739,16 +15736,16 @@
         <v>1599</v>
       </c>
       <c r="W129" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X129" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y129" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z129" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15810,16 +15807,16 @@
         <v>1599</v>
       </c>
       <c r="W130" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X130" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y130" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z130" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15881,7 +15878,7 @@
         <v>1602</v>
       </c>
       <c r="W131" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15940,7 +15937,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -15999,7 +15996,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -16061,16 +16058,16 @@
         <v>1599</v>
       </c>
       <c r="W134" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X134" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y134" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z134" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16132,16 +16129,16 @@
         <v>1599</v>
       </c>
       <c r="W135" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X135" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y135" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z135" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16203,7 +16200,7 @@
         <v>1598</v>
       </c>
       <c r="W136" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16262,7 +16259,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16324,16 +16321,16 @@
         <v>1603</v>
       </c>
       <c r="W138" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X138" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="Y138" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z138" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16395,16 +16392,16 @@
         <v>1591</v>
       </c>
       <c r="W139" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X139" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="Y139" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z139" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16466,16 +16463,16 @@
         <v>1599</v>
       </c>
       <c r="W140" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X140" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y140" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z140" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16534,7 +16531,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16593,7 +16590,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16655,16 +16652,16 @@
         <v>1604</v>
       </c>
       <c r="W143" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X143" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="Y143" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z143" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16726,16 +16723,16 @@
         <v>1605</v>
       </c>
       <c r="W144" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X144" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="Y144" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z144" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16797,16 +16794,16 @@
         <v>1606</v>
       </c>
       <c r="W145" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X145" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="Y145" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z145" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16868,16 +16865,16 @@
         <v>1607</v>
       </c>
       <c r="W146" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X146" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="Y146" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z146" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16936,7 +16933,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -16998,7 +16995,7 @@
         <v>1608</v>
       </c>
       <c r="W148" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -17060,16 +17057,16 @@
         <v>1609</v>
       </c>
       <c r="W149" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X149" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="Y149" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z149" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17131,7 +17128,7 @@
         <v>1610</v>
       </c>
       <c r="W150" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17193,16 +17190,16 @@
         <v>1611</v>
       </c>
       <c r="W151" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X151" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="Y151" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z151" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17264,7 +17261,7 @@
         <v>1610</v>
       </c>
       <c r="W152" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17326,7 +17323,7 @@
         <v>1608</v>
       </c>
       <c r="W153" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17388,7 +17385,7 @@
         <v>1610</v>
       </c>
       <c r="W154" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17450,7 +17447,7 @@
         <v>1610</v>
       </c>
       <c r="W155" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17512,16 +17509,16 @@
         <v>1612</v>
       </c>
       <c r="W156" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X156" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="Y156" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z156" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17583,7 +17580,7 @@
         <v>1608</v>
       </c>
       <c r="W157" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17645,16 +17642,16 @@
         <v>1613</v>
       </c>
       <c r="W158" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X158" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="Y158" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z158" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17716,16 +17713,16 @@
         <v>1614</v>
       </c>
       <c r="W159" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X159" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="Y159" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z159" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17787,16 +17784,16 @@
         <v>1613</v>
       </c>
       <c r="W160" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X160" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="Y160" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z160" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17858,16 +17855,16 @@
         <v>1613</v>
       </c>
       <c r="W161" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X161" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="Y161" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z161" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17929,16 +17926,16 @@
         <v>1613</v>
       </c>
       <c r="W162" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X162" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="Y162" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z162" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -18000,16 +17997,16 @@
         <v>1615</v>
       </c>
       <c r="W163" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X163" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="Y163" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z163" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -18071,16 +18068,16 @@
         <v>1616</v>
       </c>
       <c r="W164" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X164" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="Y164" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z164" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18142,16 +18139,16 @@
         <v>1617</v>
       </c>
       <c r="W165" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X165" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="Y165" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z165" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18213,16 +18210,16 @@
         <v>1618</v>
       </c>
       <c r="W166" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X166" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="Y166" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z166" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18284,16 +18281,16 @@
         <v>1596</v>
       </c>
       <c r="W167" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X167" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="Y167" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z167" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18355,16 +18352,16 @@
         <v>1599</v>
       </c>
       <c r="W168" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X168" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y168" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z168" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18426,7 +18423,7 @@
         <v>1619</v>
       </c>
       <c r="W169" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18488,16 +18485,16 @@
         <v>1599</v>
       </c>
       <c r="W170" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X170" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="Y170" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z170" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18559,16 +18556,16 @@
         <v>1620</v>
       </c>
       <c r="W171" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X171" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="Y171" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z171" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18630,16 +18627,16 @@
         <v>1621</v>
       </c>
       <c r="W172" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X172" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="Y172" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z172" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18701,16 +18698,16 @@
         <v>1622</v>
       </c>
       <c r="W173" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X173" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="Y173" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z173" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18772,16 +18769,16 @@
         <v>1623</v>
       </c>
       <c r="W174" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X174" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="Y174" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z174" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18843,16 +18840,16 @@
         <v>1624</v>
       </c>
       <c r="W175" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X175" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="Y175" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z175" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18914,16 +18911,16 @@
         <v>1625</v>
       </c>
       <c r="W176" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X176" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="Y176" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z176" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18985,7 +18982,7 @@
         <v>1619</v>
       </c>
       <c r="W177" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -19047,16 +19044,16 @@
         <v>1626</v>
       </c>
       <c r="W178" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X178" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="Y178" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z178" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19118,16 +19115,16 @@
         <v>1627</v>
       </c>
       <c r="W179" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X179" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="Y179" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z179" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19189,7 +19186,7 @@
         <v>1628</v>
       </c>
       <c r="W180" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19251,16 +19248,16 @@
         <v>1629</v>
       </c>
       <c r="W181" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X181" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="Y181" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z181" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19322,16 +19319,16 @@
         <v>1629</v>
       </c>
       <c r="W182" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X182" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="Y182" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z182" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19393,16 +19390,16 @@
         <v>1630</v>
       </c>
       <c r="W183" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X183" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="Y183" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z183" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19464,16 +19461,16 @@
         <v>1631</v>
       </c>
       <c r="W184" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X184" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="Y184" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z184" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19535,16 +19532,16 @@
         <v>1632</v>
       </c>
       <c r="W185" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X185" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="Y185" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z185" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19606,7 +19603,7 @@
         <v>1633</v>
       </c>
       <c r="W186" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19668,7 +19665,7 @@
         <v>1634</v>
       </c>
       <c r="W187" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19730,7 +19727,7 @@
         <v>1635</v>
       </c>
       <c r="W188" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19792,7 +19789,7 @@
         <v>1636</v>
       </c>
       <c r="W189" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19854,16 +19851,16 @@
         <v>1637</v>
       </c>
       <c r="W190" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X190" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="Y190" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z190" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19925,16 +19922,16 @@
         <v>1638</v>
       </c>
       <c r="W191" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X191" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="Y191" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z191" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -19996,7 +19993,7 @@
         <v>1639</v>
       </c>
       <c r="W192" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -20058,7 +20055,7 @@
         <v>1639</v>
       </c>
       <c r="W193" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20120,16 +20117,16 @@
         <v>1640</v>
       </c>
       <c r="W194" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X194" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="Y194" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z194" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20191,16 +20188,16 @@
         <v>1641</v>
       </c>
       <c r="W195" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X195" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="Y195" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z195" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20262,16 +20259,16 @@
         <v>1642</v>
       </c>
       <c r="W196" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X196" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="Y196" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z196" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20333,16 +20330,16 @@
         <v>1638</v>
       </c>
       <c r="W197" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X197" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="Y197" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z197" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20404,7 +20401,7 @@
         <v>1643</v>
       </c>
       <c r="W198" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20466,7 +20463,7 @@
         <v>1644</v>
       </c>
       <c r="W199" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20528,16 +20525,16 @@
         <v>1645</v>
       </c>
       <c r="W200" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X200" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="Y200" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z200" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20599,16 +20596,16 @@
         <v>1645</v>
       </c>
       <c r="W201" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X201" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="Y201" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z201" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20670,16 +20667,16 @@
         <v>1646</v>
       </c>
       <c r="W202" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X202" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="Y202" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z202" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20741,16 +20738,16 @@
         <v>1647</v>
       </c>
       <c r="W203" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X203" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="Y203" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z203" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20812,16 +20809,16 @@
         <v>1648</v>
       </c>
       <c r="W204" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X204" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="Y204" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z204" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20883,16 +20880,16 @@
         <v>1649</v>
       </c>
       <c r="W205" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X205" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="Y205" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z205" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20954,16 +20951,16 @@
         <v>1650</v>
       </c>
       <c r="W206" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X206" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="Y206" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z206" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -21025,16 +21022,16 @@
         <v>1651</v>
       </c>
       <c r="W207" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X207" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="Y207" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z207" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21096,16 +21093,16 @@
         <v>1652</v>
       </c>
       <c r="W208" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X208" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="Y208" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z208" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21167,7 +21164,7 @@
         <v>1653</v>
       </c>
       <c r="W209" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21229,16 +21226,16 @@
         <v>1654</v>
       </c>
       <c r="W210" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X210" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="Y210" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z210" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21300,16 +21297,16 @@
         <v>1655</v>
       </c>
       <c r="W211" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X211" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="Y211" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z211" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21371,16 +21368,16 @@
         <v>1656</v>
       </c>
       <c r="W212" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X212" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="Y212" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z212" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21442,16 +21439,16 @@
         <v>1657</v>
       </c>
       <c r="W213" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X213" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="Y213" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z213" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21513,7 +21510,7 @@
         <v>1658</v>
       </c>
       <c r="W214" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21575,16 +21572,16 @@
         <v>1623</v>
       </c>
       <c r="W215" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X215" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="Y215" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z215" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21646,16 +21643,16 @@
         <v>1659</v>
       </c>
       <c r="W216" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X216" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="Y216" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z216" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21717,7 +21714,7 @@
         <v>1660</v>
       </c>
       <c r="W217" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21779,16 +21776,16 @@
         <v>1661</v>
       </c>
       <c r="W218" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X218" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="Y218" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z218" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21850,16 +21847,16 @@
         <v>1662</v>
       </c>
       <c r="W219" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X219" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="Y219" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z219" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21921,7 +21918,7 @@
         <v>1663</v>
       </c>
       <c r="W220" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21983,7 +21980,7 @@
         <v>1664</v>
       </c>
       <c r="W221" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -22045,7 +22042,7 @@
         <v>1663</v>
       </c>
       <c r="W222" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22107,7 +22104,7 @@
         <v>1664</v>
       </c>
       <c r="W223" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22169,16 +22166,16 @@
         <v>1665</v>
       </c>
       <c r="W224" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X224" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="Y224" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z224" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22240,16 +22237,16 @@
         <v>1666</v>
       </c>
       <c r="W225" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X225" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="Y225" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z225" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22311,7 +22308,7 @@
         <v>1667</v>
       </c>
       <c r="W226" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22373,7 +22370,7 @@
         <v>1668</v>
       </c>
       <c r="W227" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22435,7 +22432,7 @@
         <v>1669</v>
       </c>
       <c r="W228" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22497,16 +22494,16 @@
         <v>1670</v>
       </c>
       <c r="W229" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X229" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="Y229" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z229" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22568,16 +22565,16 @@
         <v>1671</v>
       </c>
       <c r="W230" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X230" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="Y230" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z230" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22639,16 +22636,16 @@
         <v>1672</v>
       </c>
       <c r="W231" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X231" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="Y231" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z231" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22713,16 +22710,16 @@
         <v>1673</v>
       </c>
       <c r="W232" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X232" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="Y232" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z232" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22784,16 +22781,16 @@
         <v>1674</v>
       </c>
       <c r="W233" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X233" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="Y233" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z233" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22855,16 +22852,16 @@
         <v>1675</v>
       </c>
       <c r="W234" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X234" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y234" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z234" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22926,16 +22923,16 @@
         <v>1675</v>
       </c>
       <c r="W235" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X235" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y235" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z235" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -22997,16 +22994,16 @@
         <v>1676</v>
       </c>
       <c r="W236" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X236" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y236" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z236" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -23068,7 +23065,7 @@
         <v>1677</v>
       </c>
       <c r="W237" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23130,7 +23127,7 @@
         <v>1678</v>
       </c>
       <c r="W238" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23192,16 +23189,16 @@
         <v>1679</v>
       </c>
       <c r="W239" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X239" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="Y239" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z239" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23263,16 +23260,16 @@
         <v>1680</v>
       </c>
       <c r="W240" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X240" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="Y240" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z240" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23334,7 +23331,7 @@
         <v>1681</v>
       </c>
       <c r="W241" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23396,16 +23393,16 @@
         <v>1682</v>
       </c>
       <c r="W242" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X242" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="Y242" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z242" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23467,16 +23464,16 @@
         <v>1683</v>
       </c>
       <c r="W243" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X243" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="Y243" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z243" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23538,16 +23535,16 @@
         <v>1682</v>
       </c>
       <c r="W244" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X244" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="Y244" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z244" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23609,16 +23606,16 @@
         <v>1684</v>
       </c>
       <c r="W245" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X245" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="Y245" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z245" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23680,16 +23677,16 @@
         <v>1683</v>
       </c>
       <c r="W246" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X246" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="Y246" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z246" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23751,16 +23748,16 @@
         <v>1684</v>
       </c>
       <c r="W247" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X247" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="Y247" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z247" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23822,16 +23819,16 @@
         <v>1685</v>
       </c>
       <c r="W248" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X248" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="Y248" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z248" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23893,16 +23890,16 @@
         <v>1675</v>
       </c>
       <c r="W249" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X249" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y249" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z249" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23964,7 +23961,7 @@
         <v>1686</v>
       </c>
       <c r="W250" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -24026,7 +24023,7 @@
         <v>1687</v>
       </c>
       <c r="W251" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -24088,16 +24085,16 @@
         <v>1688</v>
       </c>
       <c r="W252" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X252" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="Y252" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z252" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24159,16 +24156,16 @@
         <v>1689</v>
       </c>
       <c r="W253" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X253" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="Y253" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z253" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24230,7 +24227,7 @@
         <v>1690</v>
       </c>
       <c r="W254" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24292,16 +24289,16 @@
         <v>1691</v>
       </c>
       <c r="W255" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X255" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="Y255" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z255" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24363,7 +24360,7 @@
         <v>1692</v>
       </c>
       <c r="W256" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24428,7 +24425,7 @@
         <v>1693</v>
       </c>
       <c r="W257" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24490,7 +24487,7 @@
         <v>1694</v>
       </c>
       <c r="W258" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24552,7 +24549,7 @@
         <v>1694</v>
       </c>
       <c r="W259" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24614,7 +24611,7 @@
         <v>1695</v>
       </c>
       <c r="W260" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24676,16 +24673,16 @@
         <v>1696</v>
       </c>
       <c r="W261" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X261" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="Y261" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z261" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24747,13 +24744,13 @@
         <v>1697</v>
       </c>
       <c r="W262" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X262" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="Y262" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24815,16 +24812,16 @@
         <v>1698</v>
       </c>
       <c r="W263" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X263" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="Y263" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z263" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24886,7 +24883,7 @@
         <v>1699</v>
       </c>
       <c r="W264" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24948,7 +24945,7 @@
         <v>1699</v>
       </c>
       <c r="W265" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -25010,7 +25007,7 @@
         <v>1700</v>
       </c>
       <c r="W266" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -25072,16 +25069,16 @@
         <v>1701</v>
       </c>
       <c r="W267" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X267" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="Y267" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z267" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25143,16 +25140,16 @@
         <v>1702</v>
       </c>
       <c r="W268" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X268" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="Y268" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z268" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25214,7 +25211,7 @@
         <v>1543</v>
       </c>
       <c r="W269" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25276,7 +25273,7 @@
         <v>1703</v>
       </c>
       <c r="W270" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25338,7 +25335,7 @@
         <v>1704</v>
       </c>
       <c r="W271" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25400,16 +25397,16 @@
         <v>1705</v>
       </c>
       <c r="W272" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X272" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="Y272" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z272" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25468,7 +25465,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25530,7 +25527,7 @@
         <v>1706</v>
       </c>
       <c r="W274" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25589,7 +25586,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25651,7 +25648,7 @@
         <v>1707</v>
       </c>
       <c r="W276" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25713,7 +25710,7 @@
         <v>1708</v>
       </c>
       <c r="W277" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25775,16 +25772,16 @@
         <v>1709</v>
       </c>
       <c r="W278" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X278" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="Y278" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z278" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25846,16 +25843,16 @@
         <v>1710</v>
       </c>
       <c r="W279" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X279" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="Y279" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z279" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25917,16 +25914,16 @@
         <v>1710</v>
       </c>
       <c r="W280" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X280" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="Y280" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z280" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -25988,16 +25985,16 @@
         <v>1711</v>
       </c>
       <c r="W281" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X281" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="Y281" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z281" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -26059,7 +26056,7 @@
         <v>1712</v>
       </c>
       <c r="W282" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26121,7 +26118,7 @@
         <v>1713</v>
       </c>
       <c r="W283" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26183,7 +26180,7 @@
         <v>1714</v>
       </c>
       <c r="W284" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26245,16 +26242,16 @@
         <v>1715</v>
       </c>
       <c r="W285" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X285" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="Y285" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z285" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26316,7 +26313,7 @@
         <v>1716</v>
       </c>
       <c r="W286" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26378,16 +26375,16 @@
         <v>1710</v>
       </c>
       <c r="W287" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X287" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="Y287" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z287" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26449,16 +26446,16 @@
         <v>1717</v>
       </c>
       <c r="W288" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X288" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="Y288" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z288" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26520,7 +26517,7 @@
         <v>1718</v>
       </c>
       <c r="W289" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26582,16 +26579,16 @@
         <v>1719</v>
       </c>
       <c r="W290" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X290" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="Y290" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z290" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26653,16 +26650,16 @@
         <v>1720</v>
       </c>
       <c r="W291" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X291" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="Y291" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z291" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26724,7 +26721,7 @@
         <v>1721</v>
       </c>
       <c r="W292" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26783,7 +26780,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26845,7 +26842,7 @@
         <v>1722</v>
       </c>
       <c r="W294" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26907,7 +26904,7 @@
         <v>1723</v>
       </c>
       <c r="W295" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26969,7 +26966,7 @@
         <v>1724</v>
       </c>
       <c r="W296" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -27031,13 +27028,13 @@
         <v>1725</v>
       </c>
       <c r="W297" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X297" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="Z297" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27099,7 +27096,7 @@
         <v>1726</v>
       </c>
       <c r="W298" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27161,7 +27158,7 @@
         <v>1727</v>
       </c>
       <c r="W299" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27223,7 +27220,7 @@
         <v>1728</v>
       </c>
       <c r="W300" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27285,7 +27282,7 @@
         <v>1729</v>
       </c>
       <c r="W301" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27347,7 +27344,7 @@
         <v>1730</v>
       </c>
       <c r="W302" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27409,16 +27406,16 @@
         <v>1731</v>
       </c>
       <c r="W303" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X303" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="Y303" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z303" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27480,7 +27477,7 @@
         <v>1732</v>
       </c>
       <c r="W304" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27542,7 +27539,7 @@
         <v>1733</v>
       </c>
       <c r="W305" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27604,7 +27601,7 @@
         <v>1734</v>
       </c>
       <c r="W306" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27666,7 +27663,7 @@
         <v>1735</v>
       </c>
       <c r="W307" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27728,7 +27725,7 @@
         <v>1728</v>
       </c>
       <c r="W308" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27790,7 +27787,7 @@
         <v>1736</v>
       </c>
       <c r="W309" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27852,7 +27849,7 @@
         <v>1737</v>
       </c>
       <c r="W310" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27914,7 +27911,7 @@
         <v>1738</v>
       </c>
       <c r="W311" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27976,7 +27973,7 @@
         <v>1739</v>
       </c>
       <c r="W312" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -28038,7 +28035,7 @@
         <v>1740</v>
       </c>
       <c r="W313" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28100,7 +28097,7 @@
         <v>1741</v>
       </c>
       <c r="W314" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28162,7 +28159,7 @@
         <v>1742</v>
       </c>
       <c r="W315" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28224,7 +28221,7 @@
         <v>1743</v>
       </c>
       <c r="W316" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28286,7 +28283,7 @@
         <v>1744</v>
       </c>
       <c r="W317" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28348,7 +28345,7 @@
         <v>1745</v>
       </c>
       <c r="W318" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28410,7 +28407,7 @@
         <v>1746</v>
       </c>
       <c r="W319" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28469,13 +28466,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X320" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="Z320" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28534,7 +28531,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28593,7 +28590,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28652,7 +28649,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28714,7 +28711,7 @@
         <v>1747</v>
       </c>
       <c r="W324" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28776,7 +28773,7 @@
         <v>1748</v>
       </c>
       <c r="W325" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28838,7 +28835,7 @@
         <v>1749</v>
       </c>
       <c r="W326" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28900,7 +28897,7 @@
         <v>1750</v>
       </c>
       <c r="W327" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28959,7 +28956,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -29021,7 +29018,7 @@
         <v>1750</v>
       </c>
       <c r="W329" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -29083,7 +29080,7 @@
         <v>1751</v>
       </c>
       <c r="W330" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29145,7 +29142,7 @@
         <v>1752</v>
       </c>
       <c r="W331" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29207,7 +29204,7 @@
         <v>1752</v>
       </c>
       <c r="W332" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29269,7 +29266,7 @@
         <v>1753</v>
       </c>
       <c r="W333" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29331,7 +29328,7 @@
         <v>1754</v>
       </c>
       <c r="W334" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29393,7 +29390,7 @@
         <v>1755</v>
       </c>
       <c r="W335" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29452,13 +29449,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X336" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="Z336" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29520,7 +29517,7 @@
         <v>1756</v>
       </c>
       <c r="W337" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29582,13 +29579,13 @@
         <v>1757</v>
       </c>
       <c r="W338" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X338" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Z338" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29650,13 +29647,13 @@
         <v>1758</v>
       </c>
       <c r="W339" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X339" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="Z339" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29718,7 +29715,7 @@
         <v>1759</v>
       </c>
       <c r="W340" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29780,7 +29777,7 @@
         <v>1760</v>
       </c>
       <c r="W341" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29842,10 +29839,10 @@
         <v>1761</v>
       </c>
       <c r="W342" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X342" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29907,7 +29904,7 @@
         <v>1762</v>
       </c>
       <c r="W343" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29969,7 +29966,7 @@
         <v>1763</v>
       </c>
       <c r="W344" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -30031,13 +30028,13 @@
         <v>1764</v>
       </c>
       <c r="W345" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X345" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="Z345" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30099,7 +30096,7 @@
         <v>1728</v>
       </c>
       <c r="W346" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30161,7 +30158,7 @@
         <v>1765</v>
       </c>
       <c r="W347" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30223,16 +30220,16 @@
         <v>1766</v>
       </c>
       <c r="W348" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X348" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="Y348" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z348" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30297,13 +30294,13 @@
         <v>1767</v>
       </c>
       <c r="W349" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X349" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="Z349" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30365,7 +30362,7 @@
         <v>1768</v>
       </c>
       <c r="W350" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30427,16 +30424,16 @@
         <v>1769</v>
       </c>
       <c r="W351" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X351" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="Y351" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z351" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30498,13 +30495,13 @@
         <v>1770</v>
       </c>
       <c r="W352" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X352" t="s">
         <v>1770</v>
       </c>
       <c r="Z352" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30566,16 +30563,16 @@
         <v>1771</v>
       </c>
       <c r="W353" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X353" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="Y353" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z353" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30637,7 +30634,7 @@
         <v>1772</v>
       </c>
       <c r="W354" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30699,7 +30696,7 @@
         <v>1773</v>
       </c>
       <c r="W355" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30758,7 +30755,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30817,7 +30814,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30876,7 +30873,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30938,7 +30935,7 @@
         <v>1774</v>
       </c>
       <c r="W359" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -31003,7 +31000,7 @@
         <v>1775</v>
       </c>
       <c r="W360" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -31068,7 +31065,7 @@
         <v>1776</v>
       </c>
       <c r="W361" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31130,16 +31127,16 @@
         <v>1777</v>
       </c>
       <c r="W362" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X362" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="Y362" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z362" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31201,16 +31198,16 @@
         <v>1778</v>
       </c>
       <c r="W363" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X363" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="Y363" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z363" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31272,7 +31269,7 @@
         <v>1779</v>
       </c>
       <c r="W364" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31334,7 +31331,7 @@
         <v>1780</v>
       </c>
       <c r="W365" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31399,7 +31396,7 @@
         <v>1781</v>
       </c>
       <c r="W366" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31461,7 +31458,7 @@
         <v>1782</v>
       </c>
       <c r="W367" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31523,7 +31520,7 @@
         <v>1783</v>
       </c>
       <c r="W368" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31588,13 +31585,13 @@
         <v>1784</v>
       </c>
       <c r="W369" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X369" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="Z369" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31656,7 +31653,7 @@
         <v>1785</v>
       </c>
       <c r="W370" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31718,16 +31715,16 @@
         <v>1786</v>
       </c>
       <c r="W371" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X371" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="Y371" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z371" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31792,7 +31789,7 @@
         <v>1787</v>
       </c>
       <c r="W372" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31857,16 +31854,16 @@
         <v>1788</v>
       </c>
       <c r="W373" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X373" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="Y373" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z373" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31928,7 +31925,7 @@
         <v>1789</v>
       </c>
       <c r="W374" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -31993,7 +31990,7 @@
         <v>1790</v>
       </c>
       <c r="W375" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -32058,7 +32055,7 @@
         <v>1791</v>
       </c>
       <c r="W376" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32123,7 +32120,7 @@
         <v>1791</v>
       </c>
       <c r="W377" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32188,13 +32185,13 @@
         <v>1792</v>
       </c>
       <c r="W378" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X378" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="Z378" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32256,16 +32253,16 @@
         <v>1793</v>
       </c>
       <c r="W379" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X379" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="Y379" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z379" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32330,7 +32327,7 @@
         <v>1794</v>
       </c>
       <c r="W380" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32392,7 +32389,7 @@
         <v>1795</v>
       </c>
       <c r="W381" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32457,7 +32454,7 @@
         <v>1796</v>
       </c>
       <c r="W382" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32519,7 +32516,7 @@
         <v>1797</v>
       </c>
       <c r="W383" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32584,7 +32581,7 @@
         <v>1796</v>
       </c>
       <c r="W384" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32646,16 +32643,16 @@
         <v>1798</v>
       </c>
       <c r="W385" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X385" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="Y385" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z385" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32723,7 +32720,7 @@
         <v>1799</v>
       </c>
       <c r="W386" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32785,7 +32782,7 @@
         <v>1800</v>
       </c>
       <c r="W387" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32847,7 +32844,7 @@
         <v>1801</v>
       </c>
       <c r="W388" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32909,16 +32906,16 @@
         <v>1802</v>
       </c>
       <c r="W389" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X389" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="Y389" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z389" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32983,16 +32980,16 @@
         <v>1803</v>
       </c>
       <c r="W390" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X390" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="Y390" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z390" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -33057,7 +33054,7 @@
         <v>1804</v>
       </c>
       <c r="W391" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33119,7 +33116,7 @@
         <v>1805</v>
       </c>
       <c r="W392" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33181,16 +33178,16 @@
         <v>1806</v>
       </c>
       <c r="W393" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X393" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="Y393" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z393" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33252,7 +33249,7 @@
         <v>1807</v>
       </c>
       <c r="W394" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33317,16 +33314,16 @@
         <v>1808</v>
       </c>
       <c r="W395" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X395" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="Y395" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z395" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33391,13 +33388,13 @@
         <v>1809</v>
       </c>
       <c r="W396" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X396" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="Y396" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33459,7 +33456,7 @@
         <v>1810</v>
       </c>
       <c r="W397" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33521,7 +33518,7 @@
         <v>1811</v>
       </c>
       <c r="W398" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33586,7 +33583,7 @@
         <v>1812</v>
       </c>
       <c r="W399" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33651,16 +33648,16 @@
         <v>1813</v>
       </c>
       <c r="W400" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X400" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="Y400" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z400" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33725,7 +33722,7 @@
         <v>1814</v>
       </c>
       <c r="W401" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33790,7 +33787,7 @@
         <v>1815</v>
       </c>
       <c r="W402" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33855,16 +33852,16 @@
         <v>1816</v>
       </c>
       <c r="W403" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X403" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="Y403" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z403" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33929,7 +33926,7 @@
         <v>1817</v>
       </c>
       <c r="W404" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -33994,7 +33991,7 @@
         <v>1818</v>
       </c>
       <c r="W405" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -34062,7 +34059,7 @@
         <v>1819</v>
       </c>
       <c r="W406" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34124,16 +34121,16 @@
         <v>1820</v>
       </c>
       <c r="W407" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X407" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="Y407" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z407" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34198,13 +34195,13 @@
         <v>1821</v>
       </c>
       <c r="W408" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X408" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Z408" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34269,7 +34266,7 @@
         <v>1822</v>
       </c>
       <c r="W409" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34334,7 +34331,7 @@
         <v>1823</v>
       </c>
       <c r="W410" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34399,7 +34396,7 @@
         <v>1824</v>
       </c>
       <c r="W411" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34464,7 +34461,7 @@
         <v>1825</v>
       </c>
       <c r="W412" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34529,7 +34526,7 @@
         <v>1826</v>
       </c>
       <c r="W413" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34594,7 +34591,7 @@
         <v>1826</v>
       </c>
       <c r="W414" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34659,7 +34656,7 @@
         <v>1827</v>
       </c>
       <c r="W415" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34724,7 +34721,7 @@
         <v>1828</v>
       </c>
       <c r="W416" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34789,7 +34786,7 @@
         <v>1826</v>
       </c>
       <c r="W417" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34854,7 +34851,7 @@
         <v>1829</v>
       </c>
       <c r="W418" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34919,7 +34916,7 @@
         <v>1830</v>
       </c>
       <c r="W419" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34984,16 +34981,16 @@
         <v>1831</v>
       </c>
       <c r="W420" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X420" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="Y420" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z420" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -35058,7 +35055,7 @@
         <v>1832</v>
       </c>
       <c r="W421" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35123,7 +35120,7 @@
         <v>1833</v>
       </c>
       <c r="W422" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35188,7 +35185,7 @@
         <v>1834</v>
       </c>
       <c r="W423" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35253,16 +35250,16 @@
         <v>1835</v>
       </c>
       <c r="W424" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X424" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="Y424" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z424" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35327,7 +35324,7 @@
         <v>1834</v>
       </c>
       <c r="W425" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35392,7 +35389,7 @@
         <v>1836</v>
       </c>
       <c r="W426" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35457,7 +35454,7 @@
         <v>1837</v>
       </c>
       <c r="W427" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35522,13 +35519,13 @@
         <v>1838</v>
       </c>
       <c r="W428" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X428" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="Y428" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35593,16 +35590,16 @@
         <v>1839</v>
       </c>
       <c r="W429" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X429" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="Y429" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z429" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35667,7 +35664,7 @@
         <v>1840</v>
       </c>
       <c r="W430" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35732,16 +35729,16 @@
         <v>1841</v>
       </c>
       <c r="W431" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X431" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="Y431" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z431" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35806,7 +35803,7 @@
         <v>1842</v>
       </c>
       <c r="W432" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35871,7 +35868,7 @@
         <v>1843</v>
       </c>
       <c r="W433" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35936,7 +35933,7 @@
         <v>1844</v>
       </c>
       <c r="W434" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -36001,7 +35998,7 @@
         <v>1845</v>
       </c>
       <c r="W435" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -36066,7 +36063,7 @@
         <v>1846</v>
       </c>
       <c r="W436" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36131,7 +36128,7 @@
         <v>1847</v>
       </c>
       <c r="W437" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36196,7 +36193,7 @@
         <v>1848</v>
       </c>
       <c r="W438" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36261,7 +36258,7 @@
         <v>1849</v>
       </c>
       <c r="W439" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36326,16 +36323,16 @@
         <v>1850</v>
       </c>
       <c r="W440" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X440" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="Y440" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z440" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36400,16 +36397,16 @@
         <v>1851</v>
       </c>
       <c r="W441" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X441" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="Y441" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z441" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36474,16 +36471,16 @@
         <v>1852</v>
       </c>
       <c r="W442" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X442" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="Y442" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z442" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36548,7 +36545,7 @@
         <v>1853</v>
       </c>
       <c r="W443" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36613,7 +36610,7 @@
         <v>1854</v>
       </c>
       <c r="W444" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36678,16 +36675,16 @@
         <v>1851</v>
       </c>
       <c r="W445" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X445" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="Y445" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z445" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36752,16 +36749,16 @@
         <v>1851</v>
       </c>
       <c r="W446" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X446" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="Y446" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z446" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36826,16 +36823,16 @@
         <v>1855</v>
       </c>
       <c r="W447" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X447" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="Y447" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z447" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36900,16 +36897,16 @@
         <v>1851</v>
       </c>
       <c r="W448" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X448" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="Y448" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z448" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36974,16 +36971,16 @@
         <v>1851</v>
       </c>
       <c r="W449" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X449" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="Y449" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z449" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -37048,16 +37045,16 @@
         <v>1856</v>
       </c>
       <c r="W450" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X450" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="Y450" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z450" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37122,16 +37119,16 @@
         <v>1857</v>
       </c>
       <c r="W451" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X451" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="Y451" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z451" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37196,7 +37193,7 @@
         <v>1858</v>
       </c>
       <c r="W452" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37261,16 +37258,16 @@
         <v>1859</v>
       </c>
       <c r="W453" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X453" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="Y453" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z453" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37335,16 +37332,16 @@
         <v>1860</v>
       </c>
       <c r="W454" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X454" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="Y454" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z454" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37409,16 +37406,16 @@
         <v>1861</v>
       </c>
       <c r="W455" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X455" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Y455" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z455" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37483,16 +37480,16 @@
         <v>1862</v>
       </c>
       <c r="W456" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X456" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="Y456" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z456" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37557,7 +37554,7 @@
         <v>1863</v>
       </c>
       <c r="W457" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37622,7 +37619,7 @@
         <v>1863</v>
       </c>
       <c r="W458" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37687,16 +37684,16 @@
         <v>1861</v>
       </c>
       <c r="W459" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X459" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Y459" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z459" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37761,16 +37758,16 @@
         <v>1864</v>
       </c>
       <c r="W460" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X460" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="Y460" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z460" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37835,16 +37832,16 @@
         <v>1865</v>
       </c>
       <c r="W461" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X461" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="Y461" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z461" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37909,7 +37906,7 @@
         <v>1866</v>
       </c>
       <c r="W462" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37974,16 +37971,16 @@
         <v>1867</v>
       </c>
       <c r="W463" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X463" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="Y463" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z463" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -38048,16 +38045,16 @@
         <v>1868</v>
       </c>
       <c r="W464" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X464" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="Y464" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z464" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38122,16 +38119,16 @@
         <v>1869</v>
       </c>
       <c r="W465" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X465" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="Y465" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z465" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38196,7 +38193,7 @@
         <v>1870</v>
       </c>
       <c r="W466" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38261,16 +38258,16 @@
         <v>1871</v>
       </c>
       <c r="W467" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X467" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="Y467" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z467" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38335,16 +38332,16 @@
         <v>1872</v>
       </c>
       <c r="W468" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X468" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="Y468" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z468" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38409,16 +38406,16 @@
         <v>1873</v>
       </c>
       <c r="W469" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X469" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="Y469" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z469" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38483,16 +38480,16 @@
         <v>1874</v>
       </c>
       <c r="W470" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X470" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="Y470" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z470" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38557,7 +38554,7 @@
         <v>1875</v>
       </c>
       <c r="W471" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38622,16 +38619,16 @@
         <v>1876</v>
       </c>
       <c r="W472" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X472" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="Y472" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z472" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38696,16 +38693,16 @@
         <v>1876</v>
       </c>
       <c r="W473" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X473" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="Y473" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z473" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38770,7 +38767,7 @@
         <v>1877</v>
       </c>
       <c r="W474" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38835,16 +38832,16 @@
         <v>1878</v>
       </c>
       <c r="W475" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X475" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="Y475" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z475" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38909,16 +38906,16 @@
         <v>1879</v>
       </c>
       <c r="W476" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X476" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="Y476" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z476" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38983,7 +38980,7 @@
         <v>1880</v>
       </c>
       <c r="W477" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -39048,7 +39045,7 @@
         <v>1881</v>
       </c>
       <c r="W478" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39113,16 +39110,16 @@
         <v>1882</v>
       </c>
       <c r="W479" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X479" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="Y479" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z479" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39187,16 +39184,16 @@
         <v>1883</v>
       </c>
       <c r="W480" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X480" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="Y480" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z480" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39261,16 +39258,16 @@
         <v>1884</v>
       </c>
       <c r="W481" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X481" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="Y481" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z481" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39335,7 +39332,7 @@
         <v>1885</v>
       </c>
       <c r="W482" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39400,7 +39397,7 @@
         <v>1886</v>
       </c>
       <c r="W483" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39468,13 +39465,13 @@
         <v>1887</v>
       </c>
       <c r="W484" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39539,7 +39536,7 @@
         <v>1888</v>
       </c>
       <c r="W485" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39607,13 +39604,13 @@
         <v>1889</v>
       </c>
       <c r="W486" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39678,7 +39675,7 @@
         <v>1890</v>
       </c>
       <c r="W487" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39743,16 +39740,16 @@
         <v>1891</v>
       </c>
       <c r="W488" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X488" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="Y488" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z488" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39817,7 +39814,7 @@
         <v>1892</v>
       </c>
       <c r="W489" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39885,13 +39882,13 @@
         <v>1893</v>
       </c>
       <c r="W490" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39956,16 +39953,16 @@
         <v>1894</v>
       </c>
       <c r="W491" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X491" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="Y491" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z491" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -40030,16 +40027,16 @@
         <v>1895</v>
       </c>
       <c r="W492" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X492" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="Y492" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z492" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40104,16 +40101,16 @@
         <v>1896</v>
       </c>
       <c r="W493" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X493" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="Y493" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z493" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40178,13 +40175,13 @@
         <v>1897</v>
       </c>
       <c r="W494" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X494" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="Y494" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40249,16 +40246,16 @@
         <v>1898</v>
       </c>
       <c r="W495" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X495" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="Y495" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z495" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40323,7 +40320,7 @@
         <v>1899</v>
       </c>
       <c r="W496" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40391,7 +40388,7 @@
         <v>1900</v>
       </c>
       <c r="W497" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40456,7 +40453,7 @@
         <v>1901</v>
       </c>
       <c r="W498" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40524,7 +40521,7 @@
         <v>1902</v>
       </c>
       <c r="W499" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40589,16 +40586,16 @@
         <v>1903</v>
       </c>
       <c r="W500" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X500" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="Y500" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z500" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40663,16 +40660,16 @@
         <v>1904</v>
       </c>
       <c r="W501" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X501" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="Y501" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z501" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40737,7 +40734,7 @@
         <v>1905</v>
       </c>
       <c r="W502" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40805,7 +40802,7 @@
         <v>1906</v>
       </c>
       <c r="W503" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40873,16 +40870,16 @@
         <v>1907</v>
       </c>
       <c r="W504" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X504" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="Y504" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z504" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40947,7 +40944,7 @@
         <v>1908</v>
       </c>
       <c r="W505" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -41012,16 +41009,16 @@
         <v>1909</v>
       </c>
       <c r="W506" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X506" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="Y506" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z506" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -41086,7 +41083,7 @@
         <v>1910</v>
       </c>
       <c r="W507" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41151,7 +41148,7 @@
         <v>1911</v>
       </c>
       <c r="W508" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41216,16 +41213,16 @@
         <v>1912</v>
       </c>
       <c r="W509" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X509" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="Y509" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z509" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41290,16 +41287,16 @@
         <v>1913</v>
       </c>
       <c r="W510" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X510" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="Y510" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z510" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41367,7 +41364,7 @@
         <v>1914</v>
       </c>
       <c r="W511" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41435,7 +41432,7 @@
         <v>1915</v>
       </c>
       <c r="W512" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41503,7 +41500,7 @@
         <v>1916</v>
       </c>
       <c r="W513" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41571,7 +41568,7 @@
         <v>1916</v>
       </c>
       <c r="W514" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41639,7 +41636,7 @@
         <v>1916</v>
       </c>
       <c r="W515" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41707,13 +41704,13 @@
         <v>1917</v>
       </c>
       <c r="W516" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41781,13 +41778,13 @@
         <v>1918</v>
       </c>
       <c r="W517" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41855,16 +41852,16 @@
         <v>1919</v>
       </c>
       <c r="W518" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X518" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Y518" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z518" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41932,16 +41929,16 @@
         <v>1920</v>
       </c>
       <c r="W519" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X519" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="Y519" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z519" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -42006,7 +42003,7 @@
         <v>1523</v>
       </c>
       <c r="W520" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -42074,7 +42071,7 @@
         <v>1921</v>
       </c>
       <c r="W521" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42142,7 +42139,7 @@
         <v>1921</v>
       </c>
       <c r="W522" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42210,7 +42207,7 @@
         <v>1922</v>
       </c>
       <c r="W523" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42278,7 +42275,7 @@
         <v>1923</v>
       </c>
       <c r="W524" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42346,7 +42343,7 @@
         <v>1924</v>
       </c>
       <c r="W525" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42414,7 +42411,7 @@
         <v>1925</v>
       </c>
       <c r="W526" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42482,7 +42479,7 @@
         <v>1926</v>
       </c>
       <c r="W527" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42547,7 +42544,7 @@
         <v>1927</v>
       </c>
       <c r="W528" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42615,7 +42612,7 @@
         <v>1928</v>
       </c>
       <c r="W529" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42683,16 +42680,16 @@
         <v>1929</v>
       </c>
       <c r="W530" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X530" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="Y530" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z530" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42760,7 +42757,7 @@
         <v>1930</v>
       </c>
       <c r="W531" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42825,7 +42822,7 @@
         <v>1931</v>
       </c>
       <c r="W532" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42893,16 +42890,16 @@
         <v>1932</v>
       </c>
       <c r="W533" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X533" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="Y533" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z533" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42970,13 +42967,13 @@
         <v>1933</v>
       </c>
       <c r="W534" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -43044,7 +43041,7 @@
         <v>1934</v>
       </c>
       <c r="W535" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43112,7 +43109,7 @@
         <v>1935</v>
       </c>
       <c r="W536" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43180,16 +43177,16 @@
         <v>1936</v>
       </c>
       <c r="W537" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X537" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="Y537" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z537" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43257,7 +43254,7 @@
         <v>1937</v>
       </c>
       <c r="W538" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43325,7 +43322,7 @@
         <v>1938</v>
       </c>
       <c r="W539" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43393,7 +43390,7 @@
         <v>1939</v>
       </c>
       <c r="W540" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43461,7 +43458,7 @@
         <v>1940</v>
       </c>
       <c r="W541" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43529,16 +43526,16 @@
         <v>1941</v>
       </c>
       <c r="W542" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X542" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Y542" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Z542" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43606,7 +43603,7 @@
         <v>1942</v>
       </c>
       <c r="W543" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43674,16 +43671,16 @@
         <v>1943</v>
       </c>
       <c r="W544" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="X544" t="s">
+        <v>2162</v>
+      </c>
+      <c r="Y544" t="s">
         <v>2163</v>
       </c>
-      <c r="Y544" t="s">
-        <v>2164</v>
-      </c>
       <c r="Z544" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43751,7 +43748,7 @@
         <v>1944</v>
       </c>
       <c r="W545" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43819,7 +43816,7 @@
         <v>1945</v>
       </c>
       <c r="W546" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43887,7 +43884,7 @@
         <v>1946</v>
       </c>
       <c r="W547" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43955,7 +43952,7 @@
         <v>1947</v>
       </c>
       <c r="W548" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -44023,7 +44020,7 @@
         <v>1947</v>
       </c>
       <c r="W549" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44091,7 +44088,7 @@
         <v>1948</v>
       </c>
       <c r="W550" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44156,7 +44153,7 @@
         <v>1949</v>
       </c>
       <c r="W551" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44224,7 +44221,7 @@
         <v>1950</v>
       </c>
       <c r="W552" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44289,7 +44286,7 @@
         <v>1951</v>
       </c>
       <c r="W553" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44357,7 +44354,7 @@
         <v>1952</v>
       </c>
       <c r="W554" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44425,7 +44422,7 @@
         <v>1953</v>
       </c>
       <c r="W555" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44493,7 +44490,7 @@
         <v>1954</v>
       </c>
       <c r="W556" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44558,7 +44555,7 @@
         <v>1955</v>
       </c>
       <c r="W557" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44626,7 +44623,7 @@
         <v>1956</v>
       </c>
       <c r="W558" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44694,7 +44691,7 @@
         <v>1957</v>
       </c>
       <c r="W559" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44759,7 +44756,7 @@
         <v>1958</v>
       </c>
       <c r="W560" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44827,7 +44824,7 @@
         <v>1959</v>
       </c>
       <c r="W561" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44880,10 +44877,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R562">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S562" t="s">
         <v>1520</v>
@@ -44895,7 +44892,7 @@
         <v>1994</v>
       </c>
       <c r="W562" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44960,7 +44957,7 @@
         <v>1960</v>
       </c>
       <c r="W563" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -45028,7 +45025,7 @@
         <v>1961</v>
       </c>
       <c r="W564" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45096,7 +45093,7 @@
         <v>1962</v>
       </c>
       <c r="W565" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45164,7 +45161,7 @@
         <v>1963</v>
       </c>
       <c r="W566" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45232,7 +45229,7 @@
         <v>1964</v>
       </c>
       <c r="W567" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45300,7 +45297,7 @@
         <v>1965</v>
       </c>
       <c r="W568" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA568" t="b">
         <v>0</v>
@@ -45368,7 +45365,7 @@
         <v>1966</v>
       </c>
       <c r="W569" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45433,7 +45430,7 @@
         <v>1967</v>
       </c>
       <c r="W570" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45498,7 +45495,7 @@
         <v>1968</v>
       </c>
       <c r="W571" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45566,7 +45563,7 @@
         <v>1969</v>
       </c>
       <c r="W572" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45634,7 +45631,7 @@
         <v>1970</v>
       </c>
       <c r="W573" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45702,7 +45699,7 @@
         <v>1971</v>
       </c>
       <c r="W574" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45770,7 +45767,7 @@
         <v>1972</v>
       </c>
       <c r="W575" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -45838,7 +45835,7 @@
         <v>1973</v>
       </c>
       <c r="W576" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45906,7 +45903,7 @@
         <v>1973</v>
       </c>
       <c r="W577" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45974,7 +45971,7 @@
         <v>1974</v>
       </c>
       <c r="W578" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -46042,7 +46039,7 @@
         <v>1975</v>
       </c>
       <c r="W579" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46110,7 +46107,7 @@
         <v>1976</v>
       </c>
       <c r="W580" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46178,7 +46175,7 @@
         <v>1977</v>
       </c>
       <c r="W581" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46246,7 +46243,7 @@
         <v>1978</v>
       </c>
       <c r="W582" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA582" t="b">
         <v>0</v>
@@ -46314,7 +46311,7 @@
         <v>1979</v>
       </c>
       <c r="W583" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA583" t="b">
         <v>0</v>
@@ -46382,7 +46379,7 @@
         <v>1980</v>
       </c>
       <c r="W584" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46450,7 +46447,7 @@
         <v>1980</v>
       </c>
       <c r="W585" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46503,10 +46500,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="R586">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S586" t="s">
         <v>1520</v>
@@ -46518,7 +46515,7 @@
         <v>1995</v>
       </c>
       <c r="W586" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46586,7 +46583,7 @@
         <v>1981</v>
       </c>
       <c r="W587" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA587" t="b">
         <v>0</v>
@@ -46639,10 +46636,10 @@
         <v>46255</v>
       </c>
       <c r="Q588">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R588">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S588" t="s">
         <v>1521</v>
@@ -46657,7 +46654,7 @@
         <v>1996</v>
       </c>
       <c r="W588" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46725,7 +46722,7 @@
         <v>1983</v>
       </c>
       <c r="W589" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA589" t="b">
         <v>0</v>
@@ -46793,7 +46790,7 @@
         <v>1984</v>
       </c>
       <c r="W590" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA590" t="b">
         <v>0</v>
@@ -46861,7 +46858,7 @@
         <v>1985</v>
       </c>
       <c r="W591" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA591" t="b">
         <v>0</v>
@@ -46929,7 +46926,7 @@
         <v>1986</v>
       </c>
       <c r="W592" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA592" t="b">
         <v>0</v>
@@ -46978,9 +46975,6 @@
       <c r="N593" s="1">
         <v>46277</v>
       </c>
-      <c r="O593" s="1">
-        <v>46252</v>
-      </c>
       <c r="P593" t="s">
         <v>1517</v>
       </c>
@@ -46999,11 +46993,8 @@
       <c r="U593" t="s">
         <v>1987</v>
       </c>
-      <c r="V593" t="s">
-        <v>1997</v>
-      </c>
       <c r="W593" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA593" t="b">
         <v>0</v>
@@ -47071,7 +47062,7 @@
         <v>1986</v>
       </c>
       <c r="W594" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA594" t="b">
         <v>0</v>
@@ -47121,10 +47112,10 @@
         <v>46279</v>
       </c>
       <c r="Q595">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="R595">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S595" t="s">
         <v>1521</v>
@@ -47133,10 +47124,10 @@
         <v>1520</v>
       </c>
       <c r="V595" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="W595" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA595" t="b">
         <v>1</v>
@@ -47204,7 +47195,7 @@
         <v>1988</v>
       </c>
       <c r="W596" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA596" t="b">
         <v>0</v>
@@ -47257,10 +47248,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R597">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S597" t="s">
         <v>1521</v>
@@ -47272,10 +47263,10 @@
         <v>1989</v>
       </c>
       <c r="V597" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="W597" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA597" t="b">
         <v>1</v>
@@ -47343,7 +47334,7 @@
         <v>1990</v>
       </c>
       <c r="W598" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA598" t="b">
         <v>0</v>
@@ -47393,10 +47384,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="R599">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S599" t="s">
         <v>1520</v>
@@ -47405,10 +47396,10 @@
         <v>1521</v>
       </c>
       <c r="V599" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="W599" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA599" t="b">
         <v>1</v>
@@ -47461,10 +47452,10 @@
         <v>46255</v>
       </c>
       <c r="Q600">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="R600">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S600" t="s">
         <v>1520</v>
@@ -47476,10 +47467,10 @@
         <v>1991</v>
       </c>
       <c r="V600" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="W600" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA600" t="b">
         <v>1</v>
@@ -47529,10 +47520,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R601">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S601" t="s">
         <v>1520</v>
@@ -47541,7 +47532,7 @@
         <v>1521</v>
       </c>
       <c r="W601" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA601" t="b">
         <v>1</v>
@@ -47590,11 +47581,14 @@
       <c r="N602" s="1">
         <v>46284</v>
       </c>
+      <c r="O602" s="1">
+        <v>46262</v>
+      </c>
       <c r="Q602">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R602">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S602" t="s">
         <v>1520</v>
@@ -47603,10 +47597,10 @@
         <v>1521</v>
       </c>
       <c r="V602" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="W602" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA602" t="b">
         <v>1</v>
@@ -47655,11 +47649,14 @@
       <c r="N603" s="1">
         <v>46286</v>
       </c>
+      <c r="O603" s="1">
+        <v>46258</v>
+      </c>
       <c r="Q603">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R603">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S603" t="s">
         <v>1520</v>
@@ -47671,10 +47668,10 @@
         <v>1992</v>
       </c>
       <c r="V603" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="W603" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA603" t="b">
         <v>1</v>
@@ -47742,7 +47739,7 @@
         <v>1993</v>
       </c>
       <c r="W604" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA604" t="b">
         <v>0</v>
@@ -47795,10 +47792,10 @@
         <v>46258</v>
       </c>
       <c r="Q605">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R605">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S605" t="s">
         <v>1521</v>
@@ -47807,10 +47804,10 @@
         <v>1520</v>
       </c>
       <c r="V605" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="W605" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="AA605" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -6007,7 +6007,7 @@
     <t>AWB 12754088775 - volume retirado na loja GOLLOG - NAT por Teodoro silva em 22/08. Godoy 25/08/26.</t>
   </si>
   <si>
-    <t>Emergência transformada em ANCE em 24/08. Aguardaremos atendimento com item da Vee One. Ramon 24/08/26. Emerg. cancelada pelo operador - 2S ARINALDO em 25/08. Godoy 26/08/26.</t>
+    <t>Emergência transformada em ANCE em 24/08. Aguardaremos atendimento com item da Vee One. Ramon 24/08/26.</t>
   </si>
   <si>
     <t>Recibo 719/FAB/26 assinado em 24/08. Ramon 24/08/26</t>
@@ -47650,7 +47650,7 @@
         <v>2737</v>
       </c>
       <c r="H603" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="I603" t="s">
         <v>1278</v>
@@ -47677,10 +47677,10 @@
         <v>1521</v>
       </c>
       <c r="Q603">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R603">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S603" t="s">
         <v>1524</v>
@@ -47869,7 +47869,7 @@
         <v>46259</v>
       </c>
       <c r="K606" s="1">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="L606">
         <v>1</v>
@@ -47878,13 +47878,13 @@
         <v>1281</v>
       </c>
       <c r="N606" s="1">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="Q606">
-        <v>-32</v>
+        <v>-31</v>
       </c>
       <c r="R606">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S606" t="s">
         <v>1525</v>
@@ -47931,7 +47931,7 @@
         <v>46259</v>
       </c>
       <c r="K607" s="1">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="L607">
         <v>1</v>
@@ -47940,13 +47940,13 @@
         <v>1281</v>
       </c>
       <c r="N607" s="1">
-        <v>46293</v>
+        <v>46291</v>
       </c>
       <c r="Q607">
-        <v>-33</v>
+        <v>-31</v>
       </c>
       <c r="R607">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S607" t="s">
         <v>1525</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7625" uniqueCount="2382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7627" uniqueCount="2384">
   <si>
     <t>om_emg</t>
   </si>
@@ -6011,6 +6011,12 @@
   </si>
   <si>
     <t>Recibo 719/FAB/26 assinado em 24/08. Ramon 24/08/26</t>
+  </si>
+  <si>
+    <t>item será atendido com o estoque local pedido 18294676. Godoy 26/08.</t>
+  </si>
+  <si>
+    <t>item será atendido com o estoque local pedido 18295192. Godoy 26/08.</t>
   </si>
   <si>
     <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08 - MATERIAL EM TRANSITO - RECIBO 722/FAB/26</t>
@@ -7637,7 +7643,7 @@
         <v>1528</v>
       </c>
       <c r="W2" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
@@ -7699,16 +7705,16 @@
         <v>1529</v>
       </c>
       <c r="W3" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X3" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="Y3" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z3" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
@@ -7770,7 +7776,7 @@
         <v>1528</v>
       </c>
       <c r="W4" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -7832,7 +7838,7 @@
         <v>1530</v>
       </c>
       <c r="W5" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -7894,7 +7900,7 @@
         <v>1531</v>
       </c>
       <c r="W6" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
@@ -7956,7 +7962,7 @@
         <v>1532</v>
       </c>
       <c r="W7" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -8018,7 +8024,7 @@
         <v>1533</v>
       </c>
       <c r="W8" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -8080,7 +8086,7 @@
         <v>1534</v>
       </c>
       <c r="W9" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -8142,7 +8148,7 @@
         <v>1535</v>
       </c>
       <c r="W10" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
@@ -8204,7 +8210,7 @@
         <v>1536</v>
       </c>
       <c r="W11" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -8266,7 +8272,7 @@
         <v>1537</v>
       </c>
       <c r="W12" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA12" t="b">
         <v>0</v>
@@ -8328,7 +8334,7 @@
         <v>1533</v>
       </c>
       <c r="W13" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -8390,16 +8396,16 @@
         <v>1538</v>
       </c>
       <c r="W14" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X14" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="Y14" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z14" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -8458,7 +8464,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -8523,7 +8529,7 @@
         <v>1539</v>
       </c>
       <c r="W16" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -8585,7 +8591,7 @@
         <v>1540</v>
       </c>
       <c r="W17" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -8647,7 +8653,7 @@
         <v>1531</v>
       </c>
       <c r="W18" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -8709,7 +8715,7 @@
         <v>1531</v>
       </c>
       <c r="W19" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -8771,7 +8777,7 @@
         <v>1541</v>
       </c>
       <c r="W20" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -8833,7 +8839,7 @@
         <v>1542</v>
       </c>
       <c r="W21" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -8895,7 +8901,7 @@
         <v>1542</v>
       </c>
       <c r="W22" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA22" t="b">
         <v>0</v>
@@ -8957,7 +8963,7 @@
         <v>1543</v>
       </c>
       <c r="W23" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -9016,7 +9022,7 @@
         <v>58</v>
       </c>
       <c r="W24" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -9075,7 +9081,7 @@
         <v>53</v>
       </c>
       <c r="W25" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA25" t="b">
         <v>0</v>
@@ -9137,7 +9143,7 @@
         <v>1531</v>
       </c>
       <c r="W26" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -9196,7 +9202,7 @@
         <v>42</v>
       </c>
       <c r="W27" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA27" t="b">
         <v>0</v>
@@ -9255,7 +9261,7 @@
         <v>45</v>
       </c>
       <c r="W28" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -9317,7 +9323,7 @@
         <v>1544</v>
       </c>
       <c r="W29" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -9376,7 +9382,7 @@
         <v>34</v>
       </c>
       <c r="W30" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA30" t="b">
         <v>0</v>
@@ -9438,7 +9444,7 @@
         <v>1545</v>
       </c>
       <c r="W31" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -9500,7 +9506,7 @@
         <v>1546</v>
       </c>
       <c r="W32" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA32" t="b">
         <v>0</v>
@@ -9562,7 +9568,7 @@
         <v>1547</v>
       </c>
       <c r="W33" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -9624,7 +9630,7 @@
         <v>1548</v>
       </c>
       <c r="W34" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -9686,7 +9692,7 @@
         <v>1549</v>
       </c>
       <c r="W35" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -9748,7 +9754,7 @@
         <v>1545</v>
       </c>
       <c r="W36" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -9810,7 +9816,7 @@
         <v>1550</v>
       </c>
       <c r="W37" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -9872,7 +9878,7 @@
         <v>1528</v>
       </c>
       <c r="W38" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -9934,7 +9940,7 @@
         <v>1547</v>
       </c>
       <c r="W39" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -9996,7 +10002,7 @@
         <v>1551</v>
       </c>
       <c r="W40" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -10058,7 +10064,7 @@
         <v>1552</v>
       </c>
       <c r="W41" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -10120,16 +10126,16 @@
         <v>1553</v>
       </c>
       <c r="W42" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X42" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="Y42" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z42" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -10191,7 +10197,7 @@
         <v>1547</v>
       </c>
       <c r="W43" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -10253,7 +10259,7 @@
         <v>1554</v>
       </c>
       <c r="W44" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -10315,7 +10321,7 @@
         <v>1547</v>
       </c>
       <c r="W45" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -10377,7 +10383,7 @@
         <v>1547</v>
       </c>
       <c r="W46" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -10439,7 +10445,7 @@
         <v>1555</v>
       </c>
       <c r="W47" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -10501,7 +10507,7 @@
         <v>1556</v>
       </c>
       <c r="W48" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -10563,7 +10569,7 @@
         <v>1557</v>
       </c>
       <c r="W49" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -10625,7 +10631,7 @@
         <v>1558</v>
       </c>
       <c r="W50" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA50" t="b">
         <v>0</v>
@@ -10687,7 +10693,7 @@
         <v>1559</v>
       </c>
       <c r="W51" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA51" t="b">
         <v>0</v>
@@ -10749,7 +10755,7 @@
         <v>1548</v>
       </c>
       <c r="W52" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA52" t="b">
         <v>0</v>
@@ -10811,7 +10817,7 @@
         <v>1542</v>
       </c>
       <c r="W53" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA53" t="b">
         <v>0</v>
@@ -10873,7 +10879,7 @@
         <v>1542</v>
       </c>
       <c r="W54" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA54" t="b">
         <v>0</v>
@@ -10935,7 +10941,7 @@
         <v>1542</v>
       </c>
       <c r="W55" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA55" t="b">
         <v>0</v>
@@ -10997,7 +11003,7 @@
         <v>1560</v>
       </c>
       <c r="W56" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA56" t="b">
         <v>0</v>
@@ -11059,7 +11065,7 @@
         <v>1561</v>
       </c>
       <c r="W57" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA57" t="b">
         <v>0</v>
@@ -11121,16 +11127,16 @@
         <v>1562</v>
       </c>
       <c r="W58" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X58" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="Y58" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z58" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="AA58" t="b">
         <v>0</v>
@@ -11192,7 +11198,7 @@
         <v>1563</v>
       </c>
       <c r="W59" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -11254,7 +11260,7 @@
         <v>1564</v>
       </c>
       <c r="W60" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA60" t="b">
         <v>0</v>
@@ -11316,7 +11322,7 @@
         <v>1542</v>
       </c>
       <c r="W61" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA61" t="b">
         <v>0</v>
@@ -11378,7 +11384,7 @@
         <v>1565</v>
       </c>
       <c r="W62" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA62" t="b">
         <v>0</v>
@@ -11437,7 +11443,7 @@
         <v>8</v>
       </c>
       <c r="W63" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA63" t="b">
         <v>0</v>
@@ -11496,7 +11502,7 @@
         <v>8</v>
       </c>
       <c r="W64" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA64" t="b">
         <v>0</v>
@@ -11555,7 +11561,7 @@
         <v>8</v>
       </c>
       <c r="W65" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA65" t="b">
         <v>0</v>
@@ -11614,7 +11620,7 @@
         <v>8</v>
       </c>
       <c r="W66" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA66" t="b">
         <v>0</v>
@@ -11673,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="W67" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA67" t="b">
         <v>0</v>
@@ -11732,7 +11738,7 @@
         <v>8</v>
       </c>
       <c r="W68" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA68" t="b">
         <v>0</v>
@@ -11794,7 +11800,7 @@
         <v>1566</v>
       </c>
       <c r="W69" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA69" t="b">
         <v>0</v>
@@ -11856,7 +11862,7 @@
         <v>1564</v>
       </c>
       <c r="W70" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA70" t="b">
         <v>0</v>
@@ -11918,7 +11924,7 @@
         <v>1549</v>
       </c>
       <c r="W71" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA71" t="b">
         <v>0</v>
@@ -11980,7 +11986,7 @@
         <v>1567</v>
       </c>
       <c r="W72" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA72" t="b">
         <v>0</v>
@@ -12042,7 +12048,7 @@
         <v>1568</v>
       </c>
       <c r="W73" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA73" t="b">
         <v>0</v>
@@ -12104,16 +12110,16 @@
         <v>1569</v>
       </c>
       <c r="W74" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X74" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="Y74" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z74" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="AA74" t="b">
         <v>0</v>
@@ -12175,16 +12181,16 @@
         <v>1570</v>
       </c>
       <c r="W75" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X75" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="Y75" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z75" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="AA75" t="b">
         <v>0</v>
@@ -12246,7 +12252,7 @@
         <v>1549</v>
       </c>
       <c r="W76" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA76" t="b">
         <v>0</v>
@@ -12308,7 +12314,7 @@
         <v>1549</v>
       </c>
       <c r="W77" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA77" t="b">
         <v>0</v>
@@ -12370,10 +12376,10 @@
         <v>1571</v>
       </c>
       <c r="W78" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="Z78" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="AA78" t="b">
         <v>0</v>
@@ -12438,7 +12444,7 @@
         <v>1572</v>
       </c>
       <c r="W79" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA79" t="b">
         <v>0</v>
@@ -12497,7 +12503,7 @@
         <v>21</v>
       </c>
       <c r="W80" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA80" t="b">
         <v>0</v>
@@ -12556,7 +12562,7 @@
         <v>21</v>
       </c>
       <c r="W81" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA81" t="b">
         <v>0</v>
@@ -12618,7 +12624,7 @@
         <v>1573</v>
       </c>
       <c r="W82" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA82" t="b">
         <v>0</v>
@@ -12680,7 +12686,7 @@
         <v>1574</v>
       </c>
       <c r="W83" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA83" t="b">
         <v>0</v>
@@ -12742,7 +12748,7 @@
         <v>1575</v>
       </c>
       <c r="W84" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA84" t="b">
         <v>0</v>
@@ -12801,7 +12807,7 @@
         <v>31</v>
       </c>
       <c r="W85" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA85" t="b">
         <v>0</v>
@@ -12863,7 +12869,7 @@
         <v>1576</v>
       </c>
       <c r="W86" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA86" t="b">
         <v>0</v>
@@ -12925,7 +12931,7 @@
         <v>1577</v>
       </c>
       <c r="W87" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA87" t="b">
         <v>0</v>
@@ -12987,7 +12993,7 @@
         <v>1577</v>
       </c>
       <c r="W88" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA88" t="b">
         <v>0</v>
@@ -13049,7 +13055,7 @@
         <v>1542</v>
       </c>
       <c r="W89" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA89" t="b">
         <v>0</v>
@@ -13111,16 +13117,16 @@
         <v>1578</v>
       </c>
       <c r="W90" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X90" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="Y90" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z90" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="AA90" t="b">
         <v>0</v>
@@ -13182,16 +13188,16 @@
         <v>1579</v>
       </c>
       <c r="W91" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X91" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="Y91" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z91" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="AA91" t="b">
         <v>0</v>
@@ -13253,7 +13259,7 @@
         <v>1580</v>
       </c>
       <c r="W92" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA92" t="b">
         <v>0</v>
@@ -13315,7 +13321,7 @@
         <v>1581</v>
       </c>
       <c r="W93" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA93" t="b">
         <v>0</v>
@@ -13377,7 +13383,7 @@
         <v>1581</v>
       </c>
       <c r="W94" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA94" t="b">
         <v>0</v>
@@ -13439,7 +13445,7 @@
         <v>1582</v>
       </c>
       <c r="W95" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA95" t="b">
         <v>0</v>
@@ -13501,16 +13507,16 @@
         <v>1583</v>
       </c>
       <c r="W96" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X96" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="Y96" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z96" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="AA96" t="b">
         <v>0</v>
@@ -13572,7 +13578,7 @@
         <v>1584</v>
       </c>
       <c r="W97" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA97" t="b">
         <v>0</v>
@@ -13634,7 +13640,7 @@
         <v>1585</v>
       </c>
       <c r="W98" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA98" t="b">
         <v>0</v>
@@ -13696,7 +13702,7 @@
         <v>1586</v>
       </c>
       <c r="W99" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA99" t="b">
         <v>0</v>
@@ -13758,7 +13764,7 @@
         <v>1587</v>
       </c>
       <c r="W100" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA100" t="b">
         <v>0</v>
@@ -13820,16 +13826,16 @@
         <v>1588</v>
       </c>
       <c r="W101" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X101" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="Y101" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z101" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="AA101" t="b">
         <v>0</v>
@@ -13891,7 +13897,7 @@
         <v>1589</v>
       </c>
       <c r="W102" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA102" t="b">
         <v>0</v>
@@ -13953,7 +13959,7 @@
         <v>1589</v>
       </c>
       <c r="W103" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA103" t="b">
         <v>0</v>
@@ -14015,7 +14021,7 @@
         <v>1590</v>
       </c>
       <c r="W104" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA104" t="b">
         <v>0</v>
@@ -14077,16 +14083,16 @@
         <v>1591</v>
       </c>
       <c r="W105" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X105" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="Y105" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z105" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="AA105" t="b">
         <v>0</v>
@@ -14148,16 +14154,16 @@
         <v>1592</v>
       </c>
       <c r="W106" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X106" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="Y106" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z106" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="AA106" t="b">
         <v>0</v>
@@ -14219,7 +14225,7 @@
         <v>1593</v>
       </c>
       <c r="W107" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA107" t="b">
         <v>0</v>
@@ -14281,16 +14287,16 @@
         <v>1594</v>
       </c>
       <c r="W108" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X108" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="Y108" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z108" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="AA108" t="b">
         <v>0</v>
@@ -14352,16 +14358,16 @@
         <v>1595</v>
       </c>
       <c r="W109" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X109" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y109" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z109" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="AA109" t="b">
         <v>0</v>
@@ -14420,7 +14426,7 @@
         <v>11</v>
       </c>
       <c r="W110" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA110" t="b">
         <v>0</v>
@@ -14482,16 +14488,16 @@
         <v>1596</v>
       </c>
       <c r="W111" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X111" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="Y111" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z111" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="AA111" t="b">
         <v>0</v>
@@ -14553,16 +14559,16 @@
         <v>1597</v>
       </c>
       <c r="W112" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X112" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="Y112" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z112" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="AA112" t="b">
         <v>0</v>
@@ -14624,16 +14630,16 @@
         <v>1598</v>
       </c>
       <c r="W113" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X113" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="Y113" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z113" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="AA113" t="b">
         <v>0</v>
@@ -14695,16 +14701,16 @@
         <v>1599</v>
       </c>
       <c r="W114" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X114" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="Y114" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z114" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="AA114" t="b">
         <v>0</v>
@@ -14766,16 +14772,16 @@
         <v>1595</v>
       </c>
       <c r="W115" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X115" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y115" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z115" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="AA115" t="b">
         <v>0</v>
@@ -14837,16 +14843,16 @@
         <v>1595</v>
       </c>
       <c r="W116" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X116" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y116" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z116" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="AA116" t="b">
         <v>0</v>
@@ -14908,16 +14914,16 @@
         <v>1600</v>
       </c>
       <c r="W117" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X117" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="Y117" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z117" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="AA117" t="b">
         <v>0</v>
@@ -14979,16 +14985,16 @@
         <v>1601</v>
       </c>
       <c r="W118" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X118" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="Y118" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z118" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="AA118" t="b">
         <v>0</v>
@@ -15050,7 +15056,7 @@
         <v>1602</v>
       </c>
       <c r="W119" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA119" t="b">
         <v>0</v>
@@ -15112,16 +15118,16 @@
         <v>1603</v>
       </c>
       <c r="W120" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X120" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y120" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z120" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="AA120" t="b">
         <v>0</v>
@@ -15183,16 +15189,16 @@
         <v>1603</v>
       </c>
       <c r="W121" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X121" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y121" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z121" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="AA121" t="b">
         <v>0</v>
@@ -15254,16 +15260,16 @@
         <v>1603</v>
       </c>
       <c r="W122" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X122" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y122" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z122" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="AA122" t="b">
         <v>0</v>
@@ -15325,16 +15331,16 @@
         <v>1603</v>
       </c>
       <c r="W123" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X123" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y123" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z123" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="AA123" t="b">
         <v>0</v>
@@ -15396,16 +15402,16 @@
         <v>1603</v>
       </c>
       <c r="W124" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X124" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y124" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z124" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="AA124" t="b">
         <v>0</v>
@@ -15467,16 +15473,16 @@
         <v>1603</v>
       </c>
       <c r="W125" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X125" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y125" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z125" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="AA125" t="b">
         <v>0</v>
@@ -15538,16 +15544,16 @@
         <v>1603</v>
       </c>
       <c r="W126" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X126" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y126" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z126" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="AA126" t="b">
         <v>0</v>
@@ -15609,16 +15615,16 @@
         <v>1604</v>
       </c>
       <c r="W127" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X127" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="Y127" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z127" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="AA127" t="b">
         <v>0</v>
@@ -15680,16 +15686,16 @@
         <v>1605</v>
       </c>
       <c r="W128" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X128" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="Y128" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z128" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="AA128" t="b">
         <v>0</v>
@@ -15751,16 +15757,16 @@
         <v>1603</v>
       </c>
       <c r="W129" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X129" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y129" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z129" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="AA129" t="b">
         <v>0</v>
@@ -15822,16 +15828,16 @@
         <v>1603</v>
       </c>
       <c r="W130" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X130" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y130" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z130" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="AA130" t="b">
         <v>0</v>
@@ -15893,7 +15899,7 @@
         <v>1606</v>
       </c>
       <c r="W131" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA131" t="b">
         <v>0</v>
@@ -15952,7 +15958,7 @@
         <v>4</v>
       </c>
       <c r="W132" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA132" t="b">
         <v>0</v>
@@ -16011,7 +16017,7 @@
         <v>4</v>
       </c>
       <c r="W133" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA133" t="b">
         <v>0</v>
@@ -16073,16 +16079,16 @@
         <v>1603</v>
       </c>
       <c r="W134" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X134" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y134" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z134" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="AA134" t="b">
         <v>0</v>
@@ -16144,16 +16150,16 @@
         <v>1603</v>
       </c>
       <c r="W135" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X135" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y135" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z135" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="AA135" t="b">
         <v>0</v>
@@ -16215,7 +16221,7 @@
         <v>1602</v>
       </c>
       <c r="W136" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA136" t="b">
         <v>0</v>
@@ -16274,7 +16280,7 @@
         <v>7</v>
       </c>
       <c r="W137" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA137" t="b">
         <v>0</v>
@@ -16336,16 +16342,16 @@
         <v>1607</v>
       </c>
       <c r="W138" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X138" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="Y138" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z138" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="AA138" t="b">
         <v>0</v>
@@ -16407,16 +16413,16 @@
         <v>1595</v>
       </c>
       <c r="W139" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X139" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="Y139" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z139" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="AA139" t="b">
         <v>0</v>
@@ -16478,16 +16484,16 @@
         <v>1603</v>
       </c>
       <c r="W140" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X140" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y140" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z140" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="AA140" t="b">
         <v>0</v>
@@ -16546,7 +16552,7 @@
         <v>5</v>
       </c>
       <c r="W141" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA141" t="b">
         <v>0</v>
@@ -16605,7 +16611,7 @@
         <v>19</v>
       </c>
       <c r="W142" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA142" t="b">
         <v>0</v>
@@ -16667,16 +16673,16 @@
         <v>1608</v>
       </c>
       <c r="W143" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X143" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="Y143" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z143" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="AA143" t="b">
         <v>0</v>
@@ -16738,16 +16744,16 @@
         <v>1609</v>
       </c>
       <c r="W144" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X144" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="Y144" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z144" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="AA144" t="b">
         <v>0</v>
@@ -16809,16 +16815,16 @@
         <v>1610</v>
       </c>
       <c r="W145" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X145" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="Y145" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z145" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="AA145" t="b">
         <v>0</v>
@@ -16880,16 +16886,16 @@
         <v>1611</v>
       </c>
       <c r="W146" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X146" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="Y146" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z146" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="AA146" t="b">
         <v>0</v>
@@ -16948,7 +16954,7 @@
         <v>18</v>
       </c>
       <c r="W147" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA147" t="b">
         <v>0</v>
@@ -17010,7 +17016,7 @@
         <v>1612</v>
       </c>
       <c r="W148" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA148" t="b">
         <v>0</v>
@@ -17072,16 +17078,16 @@
         <v>1613</v>
       </c>
       <c r="W149" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X149" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="Y149" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z149" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="AA149" t="b">
         <v>0</v>
@@ -17143,7 +17149,7 @@
         <v>1614</v>
       </c>
       <c r="W150" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA150" t="b">
         <v>0</v>
@@ -17205,16 +17211,16 @@
         <v>1615</v>
       </c>
       <c r="W151" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X151" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="Y151" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z151" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="AA151" t="b">
         <v>0</v>
@@ -17276,7 +17282,7 @@
         <v>1614</v>
       </c>
       <c r="W152" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA152" t="b">
         <v>0</v>
@@ -17338,7 +17344,7 @@
         <v>1612</v>
       </c>
       <c r="W153" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA153" t="b">
         <v>0</v>
@@ -17400,7 +17406,7 @@
         <v>1614</v>
       </c>
       <c r="W154" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA154" t="b">
         <v>0</v>
@@ -17462,7 +17468,7 @@
         <v>1614</v>
       </c>
       <c r="W155" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA155" t="b">
         <v>0</v>
@@ -17524,16 +17530,16 @@
         <v>1616</v>
       </c>
       <c r="W156" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X156" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="Y156" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z156" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="AA156" t="b">
         <v>0</v>
@@ -17595,7 +17601,7 @@
         <v>1612</v>
       </c>
       <c r="W157" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA157" t="b">
         <v>0</v>
@@ -17657,16 +17663,16 @@
         <v>1617</v>
       </c>
       <c r="W158" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X158" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y158" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z158" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="AA158" t="b">
         <v>0</v>
@@ -17728,16 +17734,16 @@
         <v>1618</v>
       </c>
       <c r="W159" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X159" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="Y159" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z159" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="AA159" t="b">
         <v>0</v>
@@ -17799,16 +17805,16 @@
         <v>1617</v>
       </c>
       <c r="W160" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X160" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y160" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z160" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="AA160" t="b">
         <v>0</v>
@@ -17870,16 +17876,16 @@
         <v>1617</v>
       </c>
       <c r="W161" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X161" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y161" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z161" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="AA161" t="b">
         <v>0</v>
@@ -17941,16 +17947,16 @@
         <v>1617</v>
       </c>
       <c r="W162" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X162" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y162" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z162" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="AA162" t="b">
         <v>0</v>
@@ -18012,16 +18018,16 @@
         <v>1619</v>
       </c>
       <c r="W163" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X163" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="Y163" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z163" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="AA163" t="b">
         <v>0</v>
@@ -18083,16 +18089,16 @@
         <v>1620</v>
       </c>
       <c r="W164" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X164" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="Y164" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z164" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="AA164" t="b">
         <v>0</v>
@@ -18154,16 +18160,16 @@
         <v>1621</v>
       </c>
       <c r="W165" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X165" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="Y165" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z165" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="AA165" t="b">
         <v>0</v>
@@ -18225,16 +18231,16 @@
         <v>1622</v>
       </c>
       <c r="W166" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X166" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="Y166" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z166" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="AA166" t="b">
         <v>0</v>
@@ -18296,16 +18302,16 @@
         <v>1600</v>
       </c>
       <c r="W167" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X167" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="Y167" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z167" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="AA167" t="b">
         <v>0</v>
@@ -18367,16 +18373,16 @@
         <v>1603</v>
       </c>
       <c r="W168" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X168" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y168" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z168" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="AA168" t="b">
         <v>0</v>
@@ -18438,7 +18444,7 @@
         <v>1623</v>
       </c>
       <c r="W169" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA169" t="b">
         <v>0</v>
@@ -18500,16 +18506,16 @@
         <v>1603</v>
       </c>
       <c r="W170" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X170" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="Y170" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z170" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="AA170" t="b">
         <v>0</v>
@@ -18571,16 +18577,16 @@
         <v>1624</v>
       </c>
       <c r="W171" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X171" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y171" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z171" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="AA171" t="b">
         <v>0</v>
@@ -18642,16 +18648,16 @@
         <v>1625</v>
       </c>
       <c r="W172" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X172" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="Y172" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z172" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="AA172" t="b">
         <v>0</v>
@@ -18713,16 +18719,16 @@
         <v>1626</v>
       </c>
       <c r="W173" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X173" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="Y173" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z173" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="AA173" t="b">
         <v>0</v>
@@ -18784,16 +18790,16 @@
         <v>1627</v>
       </c>
       <c r="W174" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X174" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="Y174" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z174" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="AA174" t="b">
         <v>0</v>
@@ -18855,16 +18861,16 @@
         <v>1628</v>
       </c>
       <c r="W175" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X175" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="Y175" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z175" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="AA175" t="b">
         <v>0</v>
@@ -18926,16 +18932,16 @@
         <v>1629</v>
       </c>
       <c r="W176" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X176" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="Y176" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z176" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="AA176" t="b">
         <v>0</v>
@@ -18997,7 +19003,7 @@
         <v>1623</v>
       </c>
       <c r="W177" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA177" t="b">
         <v>0</v>
@@ -19059,16 +19065,16 @@
         <v>1630</v>
       </c>
       <c r="W178" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X178" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="Y178" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z178" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="AA178" t="b">
         <v>0</v>
@@ -19130,16 +19136,16 @@
         <v>1631</v>
       </c>
       <c r="W179" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X179" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y179" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z179" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="AA179" t="b">
         <v>0</v>
@@ -19201,7 +19207,7 @@
         <v>1632</v>
       </c>
       <c r="W180" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA180" t="b">
         <v>0</v>
@@ -19263,16 +19269,16 @@
         <v>1633</v>
       </c>
       <c r="W181" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X181" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="Y181" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z181" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="AA181" t="b">
         <v>0</v>
@@ -19334,16 +19340,16 @@
         <v>1633</v>
       </c>
       <c r="W182" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X182" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="Y182" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z182" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="AA182" t="b">
         <v>0</v>
@@ -19405,16 +19411,16 @@
         <v>1634</v>
       </c>
       <c r="W183" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X183" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="Y183" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z183" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="AA183" t="b">
         <v>0</v>
@@ -19476,16 +19482,16 @@
         <v>1635</v>
       </c>
       <c r="W184" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X184" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="Y184" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z184" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="AA184" t="b">
         <v>0</v>
@@ -19547,16 +19553,16 @@
         <v>1636</v>
       </c>
       <c r="W185" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X185" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="Y185" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z185" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="AA185" t="b">
         <v>0</v>
@@ -19618,7 +19624,7 @@
         <v>1637</v>
       </c>
       <c r="W186" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA186" t="b">
         <v>0</v>
@@ -19680,7 +19686,7 @@
         <v>1638</v>
       </c>
       <c r="W187" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA187" t="b">
         <v>0</v>
@@ -19742,7 +19748,7 @@
         <v>1639</v>
       </c>
       <c r="W188" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA188" t="b">
         <v>0</v>
@@ -19804,7 +19810,7 @@
         <v>1640</v>
       </c>
       <c r="W189" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA189" t="b">
         <v>0</v>
@@ -19866,16 +19872,16 @@
         <v>1641</v>
       </c>
       <c r="W190" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X190" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="Y190" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z190" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="AA190" t="b">
         <v>0</v>
@@ -19937,16 +19943,16 @@
         <v>1642</v>
       </c>
       <c r="W191" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X191" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="Y191" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z191" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="AA191" t="b">
         <v>0</v>
@@ -20008,7 +20014,7 @@
         <v>1643</v>
       </c>
       <c r="W192" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA192" t="b">
         <v>0</v>
@@ -20070,7 +20076,7 @@
         <v>1643</v>
       </c>
       <c r="W193" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA193" t="b">
         <v>0</v>
@@ -20132,16 +20138,16 @@
         <v>1644</v>
       </c>
       <c r="W194" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X194" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="Y194" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z194" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="AA194" t="b">
         <v>0</v>
@@ -20203,16 +20209,16 @@
         <v>1645</v>
       </c>
       <c r="W195" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X195" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="Y195" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z195" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="AA195" t="b">
         <v>0</v>
@@ -20274,16 +20280,16 @@
         <v>1646</v>
       </c>
       <c r="W196" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X196" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="Y196" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z196" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="AA196" t="b">
         <v>0</v>
@@ -20345,16 +20351,16 @@
         <v>1642</v>
       </c>
       <c r="W197" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X197" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="Y197" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z197" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="AA197" t="b">
         <v>0</v>
@@ -20416,7 +20422,7 @@
         <v>1647</v>
       </c>
       <c r="W198" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA198" t="b">
         <v>0</v>
@@ -20478,7 +20484,7 @@
         <v>1648</v>
       </c>
       <c r="W199" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA199" t="b">
         <v>0</v>
@@ -20540,16 +20546,16 @@
         <v>1649</v>
       </c>
       <c r="W200" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X200" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="Y200" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z200" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="AA200" t="b">
         <v>0</v>
@@ -20611,16 +20617,16 @@
         <v>1649</v>
       </c>
       <c r="W201" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X201" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="Y201" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z201" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="AA201" t="b">
         <v>0</v>
@@ -20682,16 +20688,16 @@
         <v>1650</v>
       </c>
       <c r="W202" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X202" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="Y202" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z202" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="AA202" t="b">
         <v>0</v>
@@ -20753,16 +20759,16 @@
         <v>1651</v>
       </c>
       <c r="W203" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X203" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="Y203" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z203" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="AA203" t="b">
         <v>0</v>
@@ -20824,16 +20830,16 @@
         <v>1652</v>
       </c>
       <c r="W204" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X204" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="Y204" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z204" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="AA204" t="b">
         <v>0</v>
@@ -20895,16 +20901,16 @@
         <v>1653</v>
       </c>
       <c r="W205" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X205" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="Y205" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z205" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="AA205" t="b">
         <v>0</v>
@@ -20966,16 +20972,16 @@
         <v>1654</v>
       </c>
       <c r="W206" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X206" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="Y206" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z206" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="AA206" t="b">
         <v>0</v>
@@ -21037,16 +21043,16 @@
         <v>1655</v>
       </c>
       <c r="W207" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X207" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="Y207" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z207" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="AA207" t="b">
         <v>0</v>
@@ -21108,16 +21114,16 @@
         <v>1656</v>
       </c>
       <c r="W208" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X208" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="Y208" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z208" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="AA208" t="b">
         <v>0</v>
@@ -21179,7 +21185,7 @@
         <v>1657</v>
       </c>
       <c r="W209" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA209" t="b">
         <v>0</v>
@@ -21241,16 +21247,16 @@
         <v>1658</v>
       </c>
       <c r="W210" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X210" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="Y210" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z210" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="AA210" t="b">
         <v>0</v>
@@ -21312,16 +21318,16 @@
         <v>1659</v>
       </c>
       <c r="W211" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X211" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="Y211" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z211" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="AA211" t="b">
         <v>0</v>
@@ -21383,16 +21389,16 @@
         <v>1660</v>
       </c>
       <c r="W212" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X212" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="Y212" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z212" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="AA212" t="b">
         <v>0</v>
@@ -21454,16 +21460,16 @@
         <v>1661</v>
       </c>
       <c r="W213" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X213" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="Y213" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z213" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="AA213" t="b">
         <v>0</v>
@@ -21525,7 +21531,7 @@
         <v>1662</v>
       </c>
       <c r="W214" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA214" t="b">
         <v>0</v>
@@ -21587,16 +21593,16 @@
         <v>1627</v>
       </c>
       <c r="W215" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X215" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="Y215" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z215" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="AA215" t="b">
         <v>0</v>
@@ -21658,16 +21664,16 @@
         <v>1663</v>
       </c>
       <c r="W216" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X216" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="Y216" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z216" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="AA216" t="b">
         <v>0</v>
@@ -21729,7 +21735,7 @@
         <v>1664</v>
       </c>
       <c r="W217" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA217" t="b">
         <v>0</v>
@@ -21791,16 +21797,16 @@
         <v>1665</v>
       </c>
       <c r="W218" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X218" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="Y218" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z218" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="AA218" t="b">
         <v>0</v>
@@ -21862,16 +21868,16 @@
         <v>1666</v>
       </c>
       <c r="W219" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X219" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="Y219" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z219" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="AA219" t="b">
         <v>0</v>
@@ -21933,7 +21939,7 @@
         <v>1667</v>
       </c>
       <c r="W220" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA220" t="b">
         <v>0</v>
@@ -21995,7 +22001,7 @@
         <v>1668</v>
       </c>
       <c r="W221" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA221" t="b">
         <v>0</v>
@@ -22057,7 +22063,7 @@
         <v>1667</v>
       </c>
       <c r="W222" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA222" t="b">
         <v>0</v>
@@ -22119,7 +22125,7 @@
         <v>1668</v>
       </c>
       <c r="W223" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA223" t="b">
         <v>0</v>
@@ -22181,16 +22187,16 @@
         <v>1669</v>
       </c>
       <c r="W224" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X224" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="Y224" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z224" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="AA224" t="b">
         <v>0</v>
@@ -22252,16 +22258,16 @@
         <v>1670</v>
       </c>
       <c r="W225" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X225" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="Y225" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z225" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="AA225" t="b">
         <v>0</v>
@@ -22323,7 +22329,7 @@
         <v>1671</v>
       </c>
       <c r="W226" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA226" t="b">
         <v>0</v>
@@ -22385,7 +22391,7 @@
         <v>1672</v>
       </c>
       <c r="W227" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA227" t="b">
         <v>0</v>
@@ -22447,7 +22453,7 @@
         <v>1673</v>
       </c>
       <c r="W228" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA228" t="b">
         <v>0</v>
@@ -22509,16 +22515,16 @@
         <v>1674</v>
       </c>
       <c r="W229" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X229" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="Y229" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z229" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="AA229" t="b">
         <v>0</v>
@@ -22580,16 +22586,16 @@
         <v>1675</v>
       </c>
       <c r="W230" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X230" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="Y230" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z230" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="AA230" t="b">
         <v>0</v>
@@ -22651,16 +22657,16 @@
         <v>1676</v>
       </c>
       <c r="W231" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X231" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="Y231" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z231" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="AA231" t="b">
         <v>0</v>
@@ -22725,16 +22731,16 @@
         <v>1677</v>
       </c>
       <c r="W232" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X232" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="Y232" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z232" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="AA232" t="b">
         <v>0</v>
@@ -22796,16 +22802,16 @@
         <v>1678</v>
       </c>
       <c r="W233" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X233" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="Y233" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z233" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="AA233" t="b">
         <v>0</v>
@@ -22867,16 +22873,16 @@
         <v>1679</v>
       </c>
       <c r="W234" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X234" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="Y234" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z234" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="AA234" t="b">
         <v>0</v>
@@ -22938,16 +22944,16 @@
         <v>1679</v>
       </c>
       <c r="W235" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X235" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="Y235" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z235" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="AA235" t="b">
         <v>0</v>
@@ -23009,16 +23015,16 @@
         <v>1680</v>
       </c>
       <c r="W236" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X236" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="Y236" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z236" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="AA236" t="b">
         <v>0</v>
@@ -23080,7 +23086,7 @@
         <v>1681</v>
       </c>
       <c r="W237" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA237" t="b">
         <v>0</v>
@@ -23142,7 +23148,7 @@
         <v>1682</v>
       </c>
       <c r="W238" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA238" t="b">
         <v>0</v>
@@ -23204,16 +23210,16 @@
         <v>1683</v>
       </c>
       <c r="W239" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X239" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="Y239" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z239" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="AA239" t="b">
         <v>0</v>
@@ -23275,16 +23281,16 @@
         <v>1684</v>
       </c>
       <c r="W240" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X240" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="Y240" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z240" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="AA240" t="b">
         <v>0</v>
@@ -23346,7 +23352,7 @@
         <v>1685</v>
       </c>
       <c r="W241" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA241" t="b">
         <v>0</v>
@@ -23408,16 +23414,16 @@
         <v>1686</v>
       </c>
       <c r="W242" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X242" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="Y242" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z242" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="AA242" t="b">
         <v>0</v>
@@ -23479,16 +23485,16 @@
         <v>1687</v>
       </c>
       <c r="W243" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X243" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="Y243" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z243" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="AA243" t="b">
         <v>0</v>
@@ -23550,16 +23556,16 @@
         <v>1686</v>
       </c>
       <c r="W244" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X244" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="Y244" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z244" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="AA244" t="b">
         <v>0</v>
@@ -23621,16 +23627,16 @@
         <v>1688</v>
       </c>
       <c r="W245" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X245" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="Y245" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z245" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="AA245" t="b">
         <v>0</v>
@@ -23692,16 +23698,16 @@
         <v>1687</v>
       </c>
       <c r="W246" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X246" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="Y246" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z246" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="AA246" t="b">
         <v>0</v>
@@ -23763,16 +23769,16 @@
         <v>1688</v>
       </c>
       <c r="W247" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X247" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="Y247" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z247" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="AA247" t="b">
         <v>0</v>
@@ -23834,16 +23840,16 @@
         <v>1689</v>
       </c>
       <c r="W248" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X248" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="Y248" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z248" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="AA248" t="b">
         <v>0</v>
@@ -23905,16 +23911,16 @@
         <v>1679</v>
       </c>
       <c r="W249" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X249" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="Y249" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z249" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="AA249" t="b">
         <v>0</v>
@@ -23976,7 +23982,7 @@
         <v>1690</v>
       </c>
       <c r="W250" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA250" t="b">
         <v>0</v>
@@ -24038,7 +24044,7 @@
         <v>1691</v>
       </c>
       <c r="W251" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA251" t="b">
         <v>0</v>
@@ -24100,16 +24106,16 @@
         <v>1692</v>
       </c>
       <c r="W252" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X252" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="Y252" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z252" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="AA252" t="b">
         <v>0</v>
@@ -24171,16 +24177,16 @@
         <v>1693</v>
       </c>
       <c r="W253" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X253" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="Y253" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z253" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="AA253" t="b">
         <v>0</v>
@@ -24242,7 +24248,7 @@
         <v>1694</v>
       </c>
       <c r="W254" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA254" t="b">
         <v>0</v>
@@ -24304,16 +24310,16 @@
         <v>1695</v>
       </c>
       <c r="W255" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X255" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="Y255" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z255" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="AA255" t="b">
         <v>0</v>
@@ -24375,7 +24381,7 @@
         <v>1696</v>
       </c>
       <c r="W256" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA256" t="b">
         <v>0</v>
@@ -24440,7 +24446,7 @@
         <v>1697</v>
       </c>
       <c r="W257" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA257" t="b">
         <v>0</v>
@@ -24502,7 +24508,7 @@
         <v>1698</v>
       </c>
       <c r="W258" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA258" t="b">
         <v>0</v>
@@ -24564,7 +24570,7 @@
         <v>1698</v>
       </c>
       <c r="W259" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA259" t="b">
         <v>0</v>
@@ -24626,7 +24632,7 @@
         <v>1699</v>
       </c>
       <c r="W260" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA260" t="b">
         <v>0</v>
@@ -24688,16 +24694,16 @@
         <v>1700</v>
       </c>
       <c r="W261" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X261" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="Y261" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z261" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="AA261" t="b">
         <v>0</v>
@@ -24759,13 +24765,13 @@
         <v>1701</v>
       </c>
       <c r="W262" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X262" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="Y262" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="AA262" t="b">
         <v>0</v>
@@ -24827,16 +24833,16 @@
         <v>1702</v>
       </c>
       <c r="W263" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X263" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="Y263" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z263" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="AA263" t="b">
         <v>0</v>
@@ -24898,7 +24904,7 @@
         <v>1703</v>
       </c>
       <c r="W264" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA264" t="b">
         <v>0</v>
@@ -24960,7 +24966,7 @@
         <v>1703</v>
       </c>
       <c r="W265" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA265" t="b">
         <v>0</v>
@@ -25022,7 +25028,7 @@
         <v>1704</v>
       </c>
       <c r="W266" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA266" t="b">
         <v>0</v>
@@ -25084,16 +25090,16 @@
         <v>1705</v>
       </c>
       <c r="W267" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X267" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="Y267" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z267" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="AA267" t="b">
         <v>0</v>
@@ -25155,16 +25161,16 @@
         <v>1706</v>
       </c>
       <c r="W268" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X268" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="Y268" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z268" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="AA268" t="b">
         <v>0</v>
@@ -25226,7 +25232,7 @@
         <v>1547</v>
       </c>
       <c r="W269" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA269" t="b">
         <v>0</v>
@@ -25288,7 +25294,7 @@
         <v>1707</v>
       </c>
       <c r="W270" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA270" t="b">
         <v>0</v>
@@ -25350,7 +25356,7 @@
         <v>1708</v>
       </c>
       <c r="W271" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA271" t="b">
         <v>0</v>
@@ -25412,16 +25418,16 @@
         <v>1709</v>
       </c>
       <c r="W272" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X272" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="Y272" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z272" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="AA272" t="b">
         <v>0</v>
@@ -25480,7 +25486,7 @@
         <v>7</v>
       </c>
       <c r="W273" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA273" t="b">
         <v>0</v>
@@ -25542,7 +25548,7 @@
         <v>1710</v>
       </c>
       <c r="W274" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA274" t="b">
         <v>0</v>
@@ -25601,7 +25607,7 @@
         <v>7</v>
       </c>
       <c r="W275" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA275" t="b">
         <v>0</v>
@@ -25663,7 +25669,7 @@
         <v>1711</v>
       </c>
       <c r="W276" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA276" t="b">
         <v>0</v>
@@ -25725,7 +25731,7 @@
         <v>1712</v>
       </c>
       <c r="W277" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA277" t="b">
         <v>0</v>
@@ -25787,16 +25793,16 @@
         <v>1713</v>
       </c>
       <c r="W278" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X278" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="Y278" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z278" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="AA278" t="b">
         <v>0</v>
@@ -25858,16 +25864,16 @@
         <v>1714</v>
       </c>
       <c r="W279" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X279" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Y279" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z279" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="AA279" t="b">
         <v>0</v>
@@ -25929,16 +25935,16 @@
         <v>1714</v>
       </c>
       <c r="W280" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X280" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Y280" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z280" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="AA280" t="b">
         <v>0</v>
@@ -26000,16 +26006,16 @@
         <v>1715</v>
       </c>
       <c r="W281" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X281" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Y281" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z281" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="AA281" t="b">
         <v>0</v>
@@ -26071,7 +26077,7 @@
         <v>1716</v>
       </c>
       <c r="W282" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA282" t="b">
         <v>0</v>
@@ -26133,7 +26139,7 @@
         <v>1717</v>
       </c>
       <c r="W283" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA283" t="b">
         <v>0</v>
@@ -26195,7 +26201,7 @@
         <v>1718</v>
       </c>
       <c r="W284" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA284" t="b">
         <v>0</v>
@@ -26257,16 +26263,16 @@
         <v>1719</v>
       </c>
       <c r="W285" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X285" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="Y285" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z285" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="AA285" t="b">
         <v>0</v>
@@ -26328,7 +26334,7 @@
         <v>1720</v>
       </c>
       <c r="W286" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA286" t="b">
         <v>0</v>
@@ -26390,16 +26396,16 @@
         <v>1714</v>
       </c>
       <c r="W287" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X287" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="Y287" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z287" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="AA287" t="b">
         <v>0</v>
@@ -26461,16 +26467,16 @@
         <v>1721</v>
       </c>
       <c r="W288" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X288" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="Y288" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z288" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="AA288" t="b">
         <v>0</v>
@@ -26532,7 +26538,7 @@
         <v>1722</v>
       </c>
       <c r="W289" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA289" t="b">
         <v>0</v>
@@ -26594,16 +26600,16 @@
         <v>1723</v>
       </c>
       <c r="W290" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X290" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="Y290" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z290" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="AA290" t="b">
         <v>0</v>
@@ -26665,16 +26671,16 @@
         <v>1724</v>
       </c>
       <c r="W291" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X291" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="Y291" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z291" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="AA291" t="b">
         <v>0</v>
@@ -26736,7 +26742,7 @@
         <v>1725</v>
       </c>
       <c r="W292" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA292" t="b">
         <v>0</v>
@@ -26795,7 +26801,7 @@
         <v>14</v>
       </c>
       <c r="W293" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA293" t="b">
         <v>0</v>
@@ -26857,7 +26863,7 @@
         <v>1726</v>
       </c>
       <c r="W294" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA294" t="b">
         <v>0</v>
@@ -26919,7 +26925,7 @@
         <v>1727</v>
       </c>
       <c r="W295" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA295" t="b">
         <v>0</v>
@@ -26981,7 +26987,7 @@
         <v>1728</v>
       </c>
       <c r="W296" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA296" t="b">
         <v>0</v>
@@ -27043,13 +27049,13 @@
         <v>1729</v>
       </c>
       <c r="W297" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X297" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="Z297" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="AA297" t="b">
         <v>0</v>
@@ -27111,7 +27117,7 @@
         <v>1730</v>
       </c>
       <c r="W298" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA298" t="b">
         <v>0</v>
@@ -27173,7 +27179,7 @@
         <v>1731</v>
       </c>
       <c r="W299" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA299" t="b">
         <v>0</v>
@@ -27235,7 +27241,7 @@
         <v>1732</v>
       </c>
       <c r="W300" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA300" t="b">
         <v>0</v>
@@ -27297,7 +27303,7 @@
         <v>1733</v>
       </c>
       <c r="W301" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA301" t="b">
         <v>0</v>
@@ -27359,7 +27365,7 @@
         <v>1734</v>
       </c>
       <c r="W302" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA302" t="b">
         <v>0</v>
@@ -27421,16 +27427,16 @@
         <v>1735</v>
       </c>
       <c r="W303" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X303" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="Y303" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z303" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="AA303" t="b">
         <v>0</v>
@@ -27492,7 +27498,7 @@
         <v>1736</v>
       </c>
       <c r="W304" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA304" t="b">
         <v>0</v>
@@ -27554,7 +27560,7 @@
         <v>1737</v>
       </c>
       <c r="W305" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA305" t="b">
         <v>0</v>
@@ -27616,7 +27622,7 @@
         <v>1738</v>
       </c>
       <c r="W306" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA306" t="b">
         <v>0</v>
@@ -27678,7 +27684,7 @@
         <v>1739</v>
       </c>
       <c r="W307" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA307" t="b">
         <v>0</v>
@@ -27740,7 +27746,7 @@
         <v>1732</v>
       </c>
       <c r="W308" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA308" t="b">
         <v>0</v>
@@ -27802,7 +27808,7 @@
         <v>1740</v>
       </c>
       <c r="W309" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA309" t="b">
         <v>0</v>
@@ -27864,7 +27870,7 @@
         <v>1741</v>
       </c>
       <c r="W310" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA310" t="b">
         <v>0</v>
@@ -27926,7 +27932,7 @@
         <v>1742</v>
       </c>
       <c r="W311" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA311" t="b">
         <v>0</v>
@@ -27988,7 +27994,7 @@
         <v>1743</v>
       </c>
       <c r="W312" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA312" t="b">
         <v>0</v>
@@ -28050,7 +28056,7 @@
         <v>1744</v>
       </c>
       <c r="W313" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA313" t="b">
         <v>0</v>
@@ -28112,7 +28118,7 @@
         <v>1745</v>
       </c>
       <c r="W314" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA314" t="b">
         <v>0</v>
@@ -28174,7 +28180,7 @@
         <v>1746</v>
       </c>
       <c r="W315" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA315" t="b">
         <v>0</v>
@@ -28236,7 +28242,7 @@
         <v>1747</v>
       </c>
       <c r="W316" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA316" t="b">
         <v>0</v>
@@ -28298,7 +28304,7 @@
         <v>1748</v>
       </c>
       <c r="W317" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA317" t="b">
         <v>0</v>
@@ -28360,7 +28366,7 @@
         <v>1749</v>
       </c>
       <c r="W318" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA318" t="b">
         <v>0</v>
@@ -28422,7 +28428,7 @@
         <v>1750</v>
       </c>
       <c r="W319" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA319" t="b">
         <v>0</v>
@@ -28481,13 +28487,13 @@
         <v>29</v>
       </c>
       <c r="W320" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X320" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="Z320" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="AA320" t="b">
         <v>0</v>
@@ -28546,7 +28552,7 @@
         <v>29</v>
       </c>
       <c r="W321" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA321" t="b">
         <v>0</v>
@@ -28605,7 +28611,7 @@
         <v>29</v>
       </c>
       <c r="W322" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA322" t="b">
         <v>0</v>
@@ -28664,7 +28670,7 @@
         <v>0</v>
       </c>
       <c r="W323" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA323" t="b">
         <v>0</v>
@@ -28726,7 +28732,7 @@
         <v>1751</v>
       </c>
       <c r="W324" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA324" t="b">
         <v>0</v>
@@ -28788,7 +28794,7 @@
         <v>1752</v>
       </c>
       <c r="W325" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA325" t="b">
         <v>0</v>
@@ -28850,7 +28856,7 @@
         <v>1753</v>
       </c>
       <c r="W326" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA326" t="b">
         <v>0</v>
@@ -28912,7 +28918,7 @@
         <v>1754</v>
       </c>
       <c r="W327" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA327" t="b">
         <v>0</v>
@@ -28971,7 +28977,7 @@
         <v>14</v>
       </c>
       <c r="W328" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA328" t="b">
         <v>0</v>
@@ -29033,7 +29039,7 @@
         <v>1754</v>
       </c>
       <c r="W329" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA329" t="b">
         <v>0</v>
@@ -29095,7 +29101,7 @@
         <v>1755</v>
       </c>
       <c r="W330" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA330" t="b">
         <v>0</v>
@@ -29157,7 +29163,7 @@
         <v>1756</v>
       </c>
       <c r="W331" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA331" t="b">
         <v>0</v>
@@ -29219,7 +29225,7 @@
         <v>1756</v>
       </c>
       <c r="W332" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA332" t="b">
         <v>0</v>
@@ -29281,7 +29287,7 @@
         <v>1757</v>
       </c>
       <c r="W333" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA333" t="b">
         <v>0</v>
@@ -29343,7 +29349,7 @@
         <v>1758</v>
       </c>
       <c r="W334" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA334" t="b">
         <v>0</v>
@@ -29405,7 +29411,7 @@
         <v>1759</v>
       </c>
       <c r="W335" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA335" t="b">
         <v>0</v>
@@ -29464,13 +29470,13 @@
         <v>12</v>
       </c>
       <c r="W336" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X336" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="Z336" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="AA336" t="b">
         <v>0</v>
@@ -29532,7 +29538,7 @@
         <v>1760</v>
       </c>
       <c r="W337" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA337" t="b">
         <v>0</v>
@@ -29594,13 +29600,13 @@
         <v>1761</v>
       </c>
       <c r="W338" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X338" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="Z338" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="AA338" t="b">
         <v>0</v>
@@ -29662,13 +29668,13 @@
         <v>1762</v>
       </c>
       <c r="W339" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X339" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="Z339" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="AA339" t="b">
         <v>0</v>
@@ -29730,7 +29736,7 @@
         <v>1763</v>
       </c>
       <c r="W340" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA340" t="b">
         <v>0</v>
@@ -29792,7 +29798,7 @@
         <v>1764</v>
       </c>
       <c r="W341" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA341" t="b">
         <v>0</v>
@@ -29854,10 +29860,10 @@
         <v>1765</v>
       </c>
       <c r="W342" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X342" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="AA342" t="b">
         <v>0</v>
@@ -29919,7 +29925,7 @@
         <v>1766</v>
       </c>
       <c r="W343" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA343" t="b">
         <v>0</v>
@@ -29981,7 +29987,7 @@
         <v>1767</v>
       </c>
       <c r="W344" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA344" t="b">
         <v>0</v>
@@ -30043,13 +30049,13 @@
         <v>1768</v>
       </c>
       <c r="W345" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X345" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="Z345" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="AA345" t="b">
         <v>0</v>
@@ -30111,7 +30117,7 @@
         <v>1732</v>
       </c>
       <c r="W346" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA346" t="b">
         <v>0</v>
@@ -30173,7 +30179,7 @@
         <v>1769</v>
       </c>
       <c r="W347" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA347" t="b">
         <v>0</v>
@@ -30235,16 +30241,16 @@
         <v>1770</v>
       </c>
       <c r="W348" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X348" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="Y348" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z348" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="AA348" t="b">
         <v>0</v>
@@ -30309,13 +30315,13 @@
         <v>1771</v>
       </c>
       <c r="W349" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X349" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="Z349" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="AA349" t="b">
         <v>0</v>
@@ -30377,7 +30383,7 @@
         <v>1772</v>
       </c>
       <c r="W350" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA350" t="b">
         <v>0</v>
@@ -30439,16 +30445,16 @@
         <v>1773</v>
       </c>
       <c r="W351" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X351" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="Y351" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z351" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="AA351" t="b">
         <v>0</v>
@@ -30510,13 +30516,13 @@
         <v>1774</v>
       </c>
       <c r="W352" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X352" t="s">
         <v>1774</v>
       </c>
       <c r="Z352" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="AA352" t="b">
         <v>0</v>
@@ -30578,16 +30584,16 @@
         <v>1775</v>
       </c>
       <c r="W353" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X353" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="Y353" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z353" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="AA353" t="b">
         <v>0</v>
@@ -30649,7 +30655,7 @@
         <v>1776</v>
       </c>
       <c r="W354" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA354" t="b">
         <v>0</v>
@@ -30711,7 +30717,7 @@
         <v>1777</v>
       </c>
       <c r="W355" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA355" t="b">
         <v>0</v>
@@ -30770,7 +30776,7 @@
         <v>0</v>
       </c>
       <c r="W356" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA356" t="b">
         <v>0</v>
@@ -30829,7 +30835,7 @@
         <v>0</v>
       </c>
       <c r="W357" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA357" t="b">
         <v>0</v>
@@ -30888,7 +30894,7 @@
         <v>0</v>
       </c>
       <c r="W358" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA358" t="b">
         <v>0</v>
@@ -30950,7 +30956,7 @@
         <v>1778</v>
       </c>
       <c r="W359" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA359" t="b">
         <v>0</v>
@@ -31015,7 +31021,7 @@
         <v>1779</v>
       </c>
       <c r="W360" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA360" t="b">
         <v>0</v>
@@ -31080,7 +31086,7 @@
         <v>1780</v>
       </c>
       <c r="W361" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA361" t="b">
         <v>0</v>
@@ -31142,16 +31148,16 @@
         <v>1781</v>
       </c>
       <c r="W362" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X362" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="Y362" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z362" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="AA362" t="b">
         <v>0</v>
@@ -31213,16 +31219,16 @@
         <v>1782</v>
       </c>
       <c r="W363" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X363" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="Y363" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z363" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="AA363" t="b">
         <v>0</v>
@@ -31284,7 +31290,7 @@
         <v>1783</v>
       </c>
       <c r="W364" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA364" t="b">
         <v>0</v>
@@ -31346,7 +31352,7 @@
         <v>1784</v>
       </c>
       <c r="W365" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA365" t="b">
         <v>0</v>
@@ -31411,7 +31417,7 @@
         <v>1785</v>
       </c>
       <c r="W366" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA366" t="b">
         <v>0</v>
@@ -31473,7 +31479,7 @@
         <v>1786</v>
       </c>
       <c r="W367" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA367" t="b">
         <v>0</v>
@@ -31535,7 +31541,7 @@
         <v>1787</v>
       </c>
       <c r="W368" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA368" t="b">
         <v>0</v>
@@ -31600,13 +31606,13 @@
         <v>1788</v>
       </c>
       <c r="W369" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X369" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="Z369" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="AA369" t="b">
         <v>0</v>
@@ -31668,7 +31674,7 @@
         <v>1789</v>
       </c>
       <c r="W370" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA370" t="b">
         <v>0</v>
@@ -31730,16 +31736,16 @@
         <v>1790</v>
       </c>
       <c r="W371" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X371" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="Y371" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z371" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="AA371" t="b">
         <v>0</v>
@@ -31804,7 +31810,7 @@
         <v>1791</v>
       </c>
       <c r="W372" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA372" t="b">
         <v>0</v>
@@ -31869,16 +31875,16 @@
         <v>1792</v>
       </c>
       <c r="W373" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X373" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="Y373" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z373" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="AA373" t="b">
         <v>0</v>
@@ -31940,7 +31946,7 @@
         <v>1793</v>
       </c>
       <c r="W374" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA374" t="b">
         <v>0</v>
@@ -32005,7 +32011,7 @@
         <v>1794</v>
       </c>
       <c r="W375" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA375" t="b">
         <v>0</v>
@@ -32070,7 +32076,7 @@
         <v>1795</v>
       </c>
       <c r="W376" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA376" t="b">
         <v>0</v>
@@ -32135,7 +32141,7 @@
         <v>1795</v>
       </c>
       <c r="W377" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA377" t="b">
         <v>0</v>
@@ -32200,13 +32206,13 @@
         <v>1796</v>
       </c>
       <c r="W378" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X378" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="Z378" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="AA378" t="b">
         <v>0</v>
@@ -32268,16 +32274,16 @@
         <v>1797</v>
       </c>
       <c r="W379" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X379" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="Y379" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z379" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="AA379" t="b">
         <v>0</v>
@@ -32342,7 +32348,7 @@
         <v>1798</v>
       </c>
       <c r="W380" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA380" t="b">
         <v>0</v>
@@ -32404,7 +32410,7 @@
         <v>1799</v>
       </c>
       <c r="W381" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA381" t="b">
         <v>0</v>
@@ -32469,7 +32475,7 @@
         <v>1800</v>
       </c>
       <c r="W382" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA382" t="b">
         <v>0</v>
@@ -32531,7 +32537,7 @@
         <v>1801</v>
       </c>
       <c r="W383" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA383" t="b">
         <v>0</v>
@@ -32596,7 +32602,7 @@
         <v>1800</v>
       </c>
       <c r="W384" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA384" t="b">
         <v>0</v>
@@ -32658,16 +32664,16 @@
         <v>1802</v>
       </c>
       <c r="W385" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X385" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="Y385" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z385" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="AA385" t="b">
         <v>0</v>
@@ -32735,7 +32741,7 @@
         <v>1803</v>
       </c>
       <c r="W386" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA386" t="b">
         <v>0</v>
@@ -32797,7 +32803,7 @@
         <v>1804</v>
       </c>
       <c r="W387" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA387" t="b">
         <v>0</v>
@@ -32859,7 +32865,7 @@
         <v>1805</v>
       </c>
       <c r="W388" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA388" t="b">
         <v>0</v>
@@ -32921,16 +32927,16 @@
         <v>1806</v>
       </c>
       <c r="W389" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X389" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="Y389" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z389" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="AA389" t="b">
         <v>0</v>
@@ -32995,16 +33001,16 @@
         <v>1807</v>
       </c>
       <c r="W390" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X390" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="Y390" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z390" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="AA390" t="b">
         <v>0</v>
@@ -33069,7 +33075,7 @@
         <v>1808</v>
       </c>
       <c r="W391" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA391" t="b">
         <v>0</v>
@@ -33131,7 +33137,7 @@
         <v>1809</v>
       </c>
       <c r="W392" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA392" t="b">
         <v>0</v>
@@ -33193,16 +33199,16 @@
         <v>1810</v>
       </c>
       <c r="W393" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X393" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="Y393" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z393" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="AA393" t="b">
         <v>0</v>
@@ -33264,7 +33270,7 @@
         <v>1811</v>
       </c>
       <c r="W394" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA394" t="b">
         <v>0</v>
@@ -33329,16 +33335,16 @@
         <v>1812</v>
       </c>
       <c r="W395" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X395" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="Y395" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z395" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="AA395" t="b">
         <v>0</v>
@@ -33403,13 +33409,13 @@
         <v>1813</v>
       </c>
       <c r="W396" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X396" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="Y396" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="AA396" t="b">
         <v>0</v>
@@ -33471,7 +33477,7 @@
         <v>1814</v>
       </c>
       <c r="W397" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA397" t="b">
         <v>0</v>
@@ -33533,7 +33539,7 @@
         <v>1815</v>
       </c>
       <c r="W398" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA398" t="b">
         <v>0</v>
@@ -33598,7 +33604,7 @@
         <v>1816</v>
       </c>
       <c r="W399" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA399" t="b">
         <v>0</v>
@@ -33663,16 +33669,16 @@
         <v>1817</v>
       </c>
       <c r="W400" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X400" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="Y400" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z400" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="AA400" t="b">
         <v>0</v>
@@ -33737,7 +33743,7 @@
         <v>1818</v>
       </c>
       <c r="W401" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA401" t="b">
         <v>0</v>
@@ -33802,7 +33808,7 @@
         <v>1819</v>
       </c>
       <c r="W402" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA402" t="b">
         <v>0</v>
@@ -33867,16 +33873,16 @@
         <v>1820</v>
       </c>
       <c r="W403" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X403" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="Y403" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z403" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="AA403" t="b">
         <v>0</v>
@@ -33941,7 +33947,7 @@
         <v>1821</v>
       </c>
       <c r="W404" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA404" t="b">
         <v>0</v>
@@ -34006,7 +34012,7 @@
         <v>1822</v>
       </c>
       <c r="W405" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA405" t="b">
         <v>0</v>
@@ -34074,7 +34080,7 @@
         <v>1823</v>
       </c>
       <c r="W406" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA406" t="b">
         <v>0</v>
@@ -34136,16 +34142,16 @@
         <v>1824</v>
       </c>
       <c r="W407" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X407" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="Y407" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z407" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="AA407" t="b">
         <v>0</v>
@@ -34210,13 +34216,13 @@
         <v>1825</v>
       </c>
       <c r="W408" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X408" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="Z408" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="AA408" t="b">
         <v>0</v>
@@ -34281,7 +34287,7 @@
         <v>1826</v>
       </c>
       <c r="W409" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA409" t="b">
         <v>0</v>
@@ -34346,7 +34352,7 @@
         <v>1827</v>
       </c>
       <c r="W410" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA410" t="b">
         <v>0</v>
@@ -34411,7 +34417,7 @@
         <v>1828</v>
       </c>
       <c r="W411" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA411" t="b">
         <v>0</v>
@@ -34476,7 +34482,7 @@
         <v>1829</v>
       </c>
       <c r="W412" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA412" t="b">
         <v>0</v>
@@ -34541,7 +34547,7 @@
         <v>1830</v>
       </c>
       <c r="W413" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA413" t="b">
         <v>0</v>
@@ -34606,7 +34612,7 @@
         <v>1830</v>
       </c>
       <c r="W414" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA414" t="b">
         <v>0</v>
@@ -34671,7 +34677,7 @@
         <v>1831</v>
       </c>
       <c r="W415" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA415" t="b">
         <v>0</v>
@@ -34736,7 +34742,7 @@
         <v>1832</v>
       </c>
       <c r="W416" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA416" t="b">
         <v>0</v>
@@ -34801,7 +34807,7 @@
         <v>1830</v>
       </c>
       <c r="W417" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA417" t="b">
         <v>0</v>
@@ -34866,7 +34872,7 @@
         <v>1833</v>
       </c>
       <c r="W418" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA418" t="b">
         <v>0</v>
@@ -34931,7 +34937,7 @@
         <v>1834</v>
       </c>
       <c r="W419" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA419" t="b">
         <v>0</v>
@@ -34996,16 +35002,16 @@
         <v>1835</v>
       </c>
       <c r="W420" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X420" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="Y420" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z420" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="AA420" t="b">
         <v>0</v>
@@ -35070,7 +35076,7 @@
         <v>1836</v>
       </c>
       <c r="W421" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA421" t="b">
         <v>0</v>
@@ -35135,7 +35141,7 @@
         <v>1837</v>
       </c>
       <c r="W422" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA422" t="b">
         <v>0</v>
@@ -35200,7 +35206,7 @@
         <v>1838</v>
       </c>
       <c r="W423" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA423" t="b">
         <v>0</v>
@@ -35265,16 +35271,16 @@
         <v>1839</v>
       </c>
       <c r="W424" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X424" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="Y424" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z424" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="AA424" t="b">
         <v>0</v>
@@ -35339,7 +35345,7 @@
         <v>1838</v>
       </c>
       <c r="W425" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA425" t="b">
         <v>0</v>
@@ -35404,7 +35410,7 @@
         <v>1840</v>
       </c>
       <c r="W426" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA426" t="b">
         <v>0</v>
@@ -35469,7 +35475,7 @@
         <v>1841</v>
       </c>
       <c r="W427" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA427" t="b">
         <v>0</v>
@@ -35534,13 +35540,13 @@
         <v>1842</v>
       </c>
       <c r="W428" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X428" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="Y428" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="AA428" t="b">
         <v>0</v>
@@ -35605,16 +35611,16 @@
         <v>1843</v>
       </c>
       <c r="W429" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X429" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="Y429" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z429" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="AA429" t="b">
         <v>0</v>
@@ -35679,7 +35685,7 @@
         <v>1844</v>
       </c>
       <c r="W430" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA430" t="b">
         <v>0</v>
@@ -35744,16 +35750,16 @@
         <v>1845</v>
       </c>
       <c r="W431" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X431" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="Y431" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z431" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="AA431" t="b">
         <v>0</v>
@@ -35818,7 +35824,7 @@
         <v>1846</v>
       </c>
       <c r="W432" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA432" t="b">
         <v>0</v>
@@ -35883,7 +35889,7 @@
         <v>1847</v>
       </c>
       <c r="W433" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA433" t="b">
         <v>0</v>
@@ -35948,7 +35954,7 @@
         <v>1848</v>
       </c>
       <c r="W434" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA434" t="b">
         <v>0</v>
@@ -36013,7 +36019,7 @@
         <v>1849</v>
       </c>
       <c r="W435" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA435" t="b">
         <v>0</v>
@@ -36078,7 +36084,7 @@
         <v>1850</v>
       </c>
       <c r="W436" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA436" t="b">
         <v>0</v>
@@ -36143,7 +36149,7 @@
         <v>1851</v>
       </c>
       <c r="W437" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA437" t="b">
         <v>0</v>
@@ -36208,7 +36214,7 @@
         <v>1852</v>
       </c>
       <c r="W438" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA438" t="b">
         <v>0</v>
@@ -36273,7 +36279,7 @@
         <v>1853</v>
       </c>
       <c r="W439" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA439" t="b">
         <v>0</v>
@@ -36338,16 +36344,16 @@
         <v>1854</v>
       </c>
       <c r="W440" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X440" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="Y440" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z440" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="AA440" t="b">
         <v>0</v>
@@ -36412,16 +36418,16 @@
         <v>1855</v>
       </c>
       <c r="W441" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X441" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="Y441" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z441" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="AA441" t="b">
         <v>0</v>
@@ -36486,16 +36492,16 @@
         <v>1856</v>
       </c>
       <c r="W442" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X442" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="Y442" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z442" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="AA442" t="b">
         <v>0</v>
@@ -36560,7 +36566,7 @@
         <v>1857</v>
       </c>
       <c r="W443" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA443" t="b">
         <v>0</v>
@@ -36625,7 +36631,7 @@
         <v>1858</v>
       </c>
       <c r="W444" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA444" t="b">
         <v>0</v>
@@ -36690,16 +36696,16 @@
         <v>1855</v>
       </c>
       <c r="W445" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X445" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="Y445" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z445" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="AA445" t="b">
         <v>0</v>
@@ -36764,16 +36770,16 @@
         <v>1855</v>
       </c>
       <c r="W446" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X446" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="Y446" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z446" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="AA446" t="b">
         <v>0</v>
@@ -36838,16 +36844,16 @@
         <v>1859</v>
       </c>
       <c r="W447" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X447" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="Y447" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z447" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="AA447" t="b">
         <v>0</v>
@@ -36912,16 +36918,16 @@
         <v>1855</v>
       </c>
       <c r="W448" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X448" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="Y448" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z448" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="AA448" t="b">
         <v>0</v>
@@ -36986,16 +36992,16 @@
         <v>1855</v>
       </c>
       <c r="W449" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X449" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="Y449" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z449" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="AA449" t="b">
         <v>0</v>
@@ -37060,16 +37066,16 @@
         <v>1860</v>
       </c>
       <c r="W450" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X450" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="Y450" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z450" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="AA450" t="b">
         <v>0</v>
@@ -37134,16 +37140,16 @@
         <v>1861</v>
       </c>
       <c r="W451" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X451" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="Y451" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z451" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="AA451" t="b">
         <v>0</v>
@@ -37208,7 +37214,7 @@
         <v>1862</v>
       </c>
       <c r="W452" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA452" t="b">
         <v>0</v>
@@ -37273,16 +37279,16 @@
         <v>1863</v>
       </c>
       <c r="W453" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X453" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="Y453" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z453" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="AA453" t="b">
         <v>0</v>
@@ -37347,16 +37353,16 @@
         <v>1864</v>
       </c>
       <c r="W454" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X454" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="Y454" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z454" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="AA454" t="b">
         <v>0</v>
@@ -37421,16 +37427,16 @@
         <v>1865</v>
       </c>
       <c r="W455" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X455" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="Y455" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z455" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="AA455" t="b">
         <v>0</v>
@@ -37495,16 +37501,16 @@
         <v>1866</v>
       </c>
       <c r="W456" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X456" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="Y456" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z456" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="AA456" t="b">
         <v>0</v>
@@ -37569,7 +37575,7 @@
         <v>1867</v>
       </c>
       <c r="W457" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA457" t="b">
         <v>0</v>
@@ -37634,7 +37640,7 @@
         <v>1867</v>
       </c>
       <c r="W458" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA458" t="b">
         <v>0</v>
@@ -37699,16 +37705,16 @@
         <v>1865</v>
       </c>
       <c r="W459" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X459" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="Y459" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z459" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="AA459" t="b">
         <v>0</v>
@@ -37773,16 +37779,16 @@
         <v>1868</v>
       </c>
       <c r="W460" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X460" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="Y460" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z460" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="AA460" t="b">
         <v>0</v>
@@ -37847,16 +37853,16 @@
         <v>1869</v>
       </c>
       <c r="W461" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X461" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="Y461" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z461" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="AA461" t="b">
         <v>0</v>
@@ -37921,7 +37927,7 @@
         <v>1870</v>
       </c>
       <c r="W462" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA462" t="b">
         <v>0</v>
@@ -37986,16 +37992,16 @@
         <v>1871</v>
       </c>
       <c r="W463" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X463" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="Y463" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z463" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="AA463" t="b">
         <v>0</v>
@@ -38060,16 +38066,16 @@
         <v>1872</v>
       </c>
       <c r="W464" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X464" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="Y464" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z464" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="AA464" t="b">
         <v>0</v>
@@ -38134,16 +38140,16 @@
         <v>1873</v>
       </c>
       <c r="W465" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X465" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="Y465" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z465" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="AA465" t="b">
         <v>0</v>
@@ -38208,7 +38214,7 @@
         <v>1874</v>
       </c>
       <c r="W466" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA466" t="b">
         <v>0</v>
@@ -38273,16 +38279,16 @@
         <v>1875</v>
       </c>
       <c r="W467" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X467" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="Y467" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z467" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="AA467" t="b">
         <v>0</v>
@@ -38347,16 +38353,16 @@
         <v>1876</v>
       </c>
       <c r="W468" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X468" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="Y468" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z468" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="AA468" t="b">
         <v>0</v>
@@ -38421,16 +38427,16 @@
         <v>1877</v>
       </c>
       <c r="W469" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X469" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="Y469" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z469" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="AA469" t="b">
         <v>0</v>
@@ -38495,16 +38501,16 @@
         <v>1878</v>
       </c>
       <c r="W470" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X470" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="Y470" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z470" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="AA470" t="b">
         <v>0</v>
@@ -38569,7 +38575,7 @@
         <v>1879</v>
       </c>
       <c r="W471" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA471" t="b">
         <v>0</v>
@@ -38634,16 +38640,16 @@
         <v>1880</v>
       </c>
       <c r="W472" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X472" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="Y472" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z472" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="AA472" t="b">
         <v>0</v>
@@ -38708,16 +38714,16 @@
         <v>1880</v>
       </c>
       <c r="W473" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X473" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="Y473" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z473" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="AA473" t="b">
         <v>0</v>
@@ -38782,7 +38788,7 @@
         <v>1881</v>
       </c>
       <c r="W474" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA474" t="b">
         <v>0</v>
@@ -38847,16 +38853,16 @@
         <v>1882</v>
       </c>
       <c r="W475" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X475" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="Y475" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z475" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="AA475" t="b">
         <v>0</v>
@@ -38921,16 +38927,16 @@
         <v>1883</v>
       </c>
       <c r="W476" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X476" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="Y476" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z476" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="AA476" t="b">
         <v>0</v>
@@ -38995,7 +39001,7 @@
         <v>1884</v>
       </c>
       <c r="W477" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA477" t="b">
         <v>0</v>
@@ -39060,7 +39066,7 @@
         <v>1885</v>
       </c>
       <c r="W478" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA478" t="b">
         <v>0</v>
@@ -39125,16 +39131,16 @@
         <v>1886</v>
       </c>
       <c r="W479" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X479" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="Y479" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z479" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="AA479" t="b">
         <v>0</v>
@@ -39199,16 +39205,16 @@
         <v>1887</v>
       </c>
       <c r="W480" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X480" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="Y480" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z480" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="AA480" t="b">
         <v>0</v>
@@ -39273,16 +39279,16 @@
         <v>1888</v>
       </c>
       <c r="W481" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X481" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="Y481" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z481" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="AA481" t="b">
         <v>0</v>
@@ -39347,7 +39353,7 @@
         <v>1889</v>
       </c>
       <c r="W482" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA482" t="b">
         <v>0</v>
@@ -39412,7 +39418,7 @@
         <v>1890</v>
       </c>
       <c r="W483" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA483" t="b">
         <v>0</v>
@@ -39480,13 +39486,13 @@
         <v>1891</v>
       </c>
       <c r="W484" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X484">
         <v>12738616480</v>
       </c>
       <c r="Z484" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="AA484" t="b">
         <v>0</v>
@@ -39551,7 +39557,7 @@
         <v>1892</v>
       </c>
       <c r="W485" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA485" t="b">
         <v>0</v>
@@ -39619,13 +39625,13 @@
         <v>1893</v>
       </c>
       <c r="W486" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X486">
         <v>12738616480</v>
       </c>
       <c r="Z486" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="AA486" t="b">
         <v>0</v>
@@ -39690,7 +39696,7 @@
         <v>1894</v>
       </c>
       <c r="W487" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA487" t="b">
         <v>0</v>
@@ -39755,16 +39761,16 @@
         <v>1895</v>
       </c>
       <c r="W488" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X488" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="Y488" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z488" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="AA488" t="b">
         <v>0</v>
@@ -39829,7 +39835,7 @@
         <v>1896</v>
       </c>
       <c r="W489" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA489" t="b">
         <v>0</v>
@@ -39897,13 +39903,13 @@
         <v>1897</v>
       </c>
       <c r="W490" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X490">
         <v>12738926716</v>
       </c>
       <c r="Z490" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="AA490" t="b">
         <v>0</v>
@@ -39968,16 +39974,16 @@
         <v>1898</v>
       </c>
       <c r="W491" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X491" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="Y491" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z491" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="AA491" t="b">
         <v>0</v>
@@ -40042,16 +40048,16 @@
         <v>1899</v>
       </c>
       <c r="W492" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X492" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="Y492" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z492" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="AA492" t="b">
         <v>0</v>
@@ -40116,16 +40122,16 @@
         <v>1900</v>
       </c>
       <c r="W493" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X493" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="Y493" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z493" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="AA493" t="b">
         <v>0</v>
@@ -40190,13 +40196,13 @@
         <v>1901</v>
       </c>
       <c r="W494" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X494" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="Y494" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="AA494" t="b">
         <v>0</v>
@@ -40261,16 +40267,16 @@
         <v>1902</v>
       </c>
       <c r="W495" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X495" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="Y495" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z495" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="AA495" t="b">
         <v>0</v>
@@ -40335,7 +40341,7 @@
         <v>1903</v>
       </c>
       <c r="W496" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA496" t="b">
         <v>0</v>
@@ -40403,7 +40409,7 @@
         <v>1904</v>
       </c>
       <c r="W497" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA497" t="b">
         <v>0</v>
@@ -40468,7 +40474,7 @@
         <v>1905</v>
       </c>
       <c r="W498" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA498" t="b">
         <v>0</v>
@@ -40536,7 +40542,7 @@
         <v>1906</v>
       </c>
       <c r="W499" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA499" t="b">
         <v>0</v>
@@ -40601,16 +40607,16 @@
         <v>1907</v>
       </c>
       <c r="W500" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X500" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="Y500" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z500" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="AA500" t="b">
         <v>0</v>
@@ -40675,16 +40681,16 @@
         <v>1908</v>
       </c>
       <c r="W501" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X501" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="Y501" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z501" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="AA501" t="b">
         <v>0</v>
@@ -40749,7 +40755,7 @@
         <v>1909</v>
       </c>
       <c r="W502" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA502" t="b">
         <v>0</v>
@@ -40817,7 +40823,7 @@
         <v>1910</v>
       </c>
       <c r="W503" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA503" t="b">
         <v>0</v>
@@ -40885,16 +40891,16 @@
         <v>1911</v>
       </c>
       <c r="W504" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X504" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="Y504" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z504" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="AA504" t="b">
         <v>0</v>
@@ -40959,7 +40965,7 @@
         <v>1912</v>
       </c>
       <c r="W505" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA505" t="b">
         <v>0</v>
@@ -41024,16 +41030,16 @@
         <v>1913</v>
       </c>
       <c r="W506" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X506" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="Y506" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z506" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="AA506" t="b">
         <v>0</v>
@@ -41098,7 +41104,7 @@
         <v>1914</v>
       </c>
       <c r="W507" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA507" t="b">
         <v>0</v>
@@ -41163,7 +41169,7 @@
         <v>1915</v>
       </c>
       <c r="W508" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA508" t="b">
         <v>0</v>
@@ -41228,16 +41234,16 @@
         <v>1916</v>
       </c>
       <c r="W509" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X509" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="Y509" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z509" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="AA509" t="b">
         <v>0</v>
@@ -41302,16 +41308,16 @@
         <v>1917</v>
       </c>
       <c r="W510" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X510" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="Y510" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z510" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="AA510" t="b">
         <v>0</v>
@@ -41379,7 +41385,7 @@
         <v>1918</v>
       </c>
       <c r="W511" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA511" t="b">
         <v>0</v>
@@ -41447,7 +41453,7 @@
         <v>1919</v>
       </c>
       <c r="W512" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA512" t="b">
         <v>0</v>
@@ -41515,7 +41521,7 @@
         <v>1920</v>
       </c>
       <c r="W513" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA513" t="b">
         <v>0</v>
@@ -41583,7 +41589,7 @@
         <v>1920</v>
       </c>
       <c r="W514" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA514" t="b">
         <v>0</v>
@@ -41651,7 +41657,7 @@
         <v>1920</v>
       </c>
       <c r="W515" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA515" t="b">
         <v>0</v>
@@ -41719,13 +41725,13 @@
         <v>1921</v>
       </c>
       <c r="W516" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X516">
         <v>12743527212</v>
       </c>
       <c r="Z516" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="AA516" t="b">
         <v>0</v>
@@ -41793,13 +41799,13 @@
         <v>1922</v>
       </c>
       <c r="W517" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X517">
         <v>12743529135</v>
       </c>
       <c r="Z517" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="AA517" t="b">
         <v>0</v>
@@ -41867,16 +41873,16 @@
         <v>1923</v>
       </c>
       <c r="W518" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X518" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="Y518" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z518" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="AA518" t="b">
         <v>0</v>
@@ -41944,16 +41950,16 @@
         <v>1924</v>
       </c>
       <c r="W519" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X519" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="Y519" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z519" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="AA519" t="b">
         <v>0</v>
@@ -42018,7 +42024,7 @@
         <v>1527</v>
       </c>
       <c r="W520" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA520" t="b">
         <v>0</v>
@@ -42086,7 +42092,7 @@
         <v>1925</v>
       </c>
       <c r="W521" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA521" t="b">
         <v>0</v>
@@ -42154,7 +42160,7 @@
         <v>1925</v>
       </c>
       <c r="W522" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA522" t="b">
         <v>0</v>
@@ -42222,7 +42228,7 @@
         <v>1926</v>
       </c>
       <c r="W523" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA523" t="b">
         <v>0</v>
@@ -42290,7 +42296,7 @@
         <v>1927</v>
       </c>
       <c r="W524" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA524" t="b">
         <v>0</v>
@@ -42358,7 +42364,7 @@
         <v>1928</v>
       </c>
       <c r="W525" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA525" t="b">
         <v>0</v>
@@ -42426,7 +42432,7 @@
         <v>1929</v>
       </c>
       <c r="W526" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA526" t="b">
         <v>0</v>
@@ -42494,7 +42500,7 @@
         <v>1930</v>
       </c>
       <c r="W527" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA527" t="b">
         <v>0</v>
@@ -42559,7 +42565,7 @@
         <v>1931</v>
       </c>
       <c r="W528" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA528" t="b">
         <v>0</v>
@@ -42627,7 +42633,7 @@
         <v>1932</v>
       </c>
       <c r="W529" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA529" t="b">
         <v>0</v>
@@ -42695,16 +42701,16 @@
         <v>1933</v>
       </c>
       <c r="W530" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X530" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="Y530" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z530" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="AA530" t="b">
         <v>0</v>
@@ -42772,7 +42778,7 @@
         <v>1934</v>
       </c>
       <c r="W531" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA531" t="b">
         <v>0</v>
@@ -42837,7 +42843,7 @@
         <v>1935</v>
       </c>
       <c r="W532" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA532" t="b">
         <v>0</v>
@@ -42905,16 +42911,16 @@
         <v>1936</v>
       </c>
       <c r="W533" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X533" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="Y533" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z533" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="AA533" t="b">
         <v>0</v>
@@ -42982,13 +42988,13 @@
         <v>1937</v>
       </c>
       <c r="W534" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X534">
         <v>12743527212</v>
       </c>
       <c r="Z534" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="AA534" t="b">
         <v>0</v>
@@ -43056,7 +43062,7 @@
         <v>1938</v>
       </c>
       <c r="W535" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA535" t="b">
         <v>0</v>
@@ -43124,7 +43130,7 @@
         <v>1939</v>
       </c>
       <c r="W536" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA536" t="b">
         <v>0</v>
@@ -43192,16 +43198,16 @@
         <v>1940</v>
       </c>
       <c r="W537" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X537" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="Y537" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z537" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="AA537" t="b">
         <v>0</v>
@@ -43269,7 +43275,7 @@
         <v>1941</v>
       </c>
       <c r="W538" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA538" t="b">
         <v>0</v>
@@ -43337,7 +43343,7 @@
         <v>1942</v>
       </c>
       <c r="W539" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA539" t="b">
         <v>0</v>
@@ -43405,7 +43411,7 @@
         <v>1943</v>
       </c>
       <c r="W540" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA540" t="b">
         <v>0</v>
@@ -43473,7 +43479,7 @@
         <v>1944</v>
       </c>
       <c r="W541" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA541" t="b">
         <v>0</v>
@@ -43541,16 +43547,16 @@
         <v>1945</v>
       </c>
       <c r="W542" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X542" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="Y542" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z542" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="AA542" t="b">
         <v>0</v>
@@ -43618,7 +43624,7 @@
         <v>1946</v>
       </c>
       <c r="W543" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA543" t="b">
         <v>0</v>
@@ -43686,16 +43692,16 @@
         <v>1947</v>
       </c>
       <c r="W544" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="X544" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="Y544" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="Z544" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="AA544" t="b">
         <v>0</v>
@@ -43763,7 +43769,7 @@
         <v>1948</v>
       </c>
       <c r="W545" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA545" t="b">
         <v>0</v>
@@ -43831,7 +43837,7 @@
         <v>1949</v>
       </c>
       <c r="W546" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA546" t="b">
         <v>0</v>
@@ -43899,7 +43905,7 @@
         <v>1950</v>
       </c>
       <c r="W547" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA547" t="b">
         <v>0</v>
@@ -43967,7 +43973,7 @@
         <v>1951</v>
       </c>
       <c r="W548" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA548" t="b">
         <v>0</v>
@@ -44035,7 +44041,7 @@
         <v>1951</v>
       </c>
       <c r="W549" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA549" t="b">
         <v>0</v>
@@ -44103,7 +44109,7 @@
         <v>1952</v>
       </c>
       <c r="W550" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA550" t="b">
         <v>0</v>
@@ -44168,7 +44174,7 @@
         <v>1953</v>
       </c>
       <c r="W551" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA551" t="b">
         <v>0</v>
@@ -44236,7 +44242,7 @@
         <v>1954</v>
       </c>
       <c r="W552" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA552" t="b">
         <v>0</v>
@@ -44301,7 +44307,7 @@
         <v>1955</v>
       </c>
       <c r="W553" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA553" t="b">
         <v>0</v>
@@ -44369,7 +44375,7 @@
         <v>1956</v>
       </c>
       <c r="W554" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA554" t="b">
         <v>0</v>
@@ -44437,7 +44443,7 @@
         <v>1957</v>
       </c>
       <c r="W555" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA555" t="b">
         <v>0</v>
@@ -44505,7 +44511,7 @@
         <v>1958</v>
       </c>
       <c r="W556" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA556" t="b">
         <v>0</v>
@@ -44570,7 +44576,7 @@
         <v>1959</v>
       </c>
       <c r="W557" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA557" t="b">
         <v>0</v>
@@ -44638,7 +44644,7 @@
         <v>1960</v>
       </c>
       <c r="W558" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA558" t="b">
         <v>0</v>
@@ -44706,7 +44712,7 @@
         <v>1961</v>
       </c>
       <c r="W559" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA559" t="b">
         <v>0</v>
@@ -44771,7 +44777,7 @@
         <v>1962</v>
       </c>
       <c r="W560" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA560" t="b">
         <v>0</v>
@@ -44839,7 +44845,7 @@
         <v>1963</v>
       </c>
       <c r="W561" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA561" t="b">
         <v>0</v>
@@ -44904,10 +44910,10 @@
         <v>1525</v>
       </c>
       <c r="V562" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="W562" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA562" t="b">
         <v>1</v>
@@ -44972,7 +44978,7 @@
         <v>1964</v>
       </c>
       <c r="W563" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA563" t="b">
         <v>0</v>
@@ -45040,7 +45046,7 @@
         <v>1965</v>
       </c>
       <c r="W564" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA564" t="b">
         <v>0</v>
@@ -45108,7 +45114,7 @@
         <v>1966</v>
       </c>
       <c r="W565" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA565" t="b">
         <v>0</v>
@@ -45176,7 +45182,7 @@
         <v>1967</v>
       </c>
       <c r="W566" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA566" t="b">
         <v>0</v>
@@ -45244,7 +45250,7 @@
         <v>1968</v>
       </c>
       <c r="W567" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA567" t="b">
         <v>0</v>
@@ -45312,7 +45318,7 @@
         <v>1969</v>
       </c>
       <c r="W568" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA568" t="b">
         <v>0</v>
@@ -45380,7 +45386,7 @@
         <v>1970</v>
       </c>
       <c r="W569" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA569" t="b">
         <v>0</v>
@@ -45445,7 +45451,7 @@
         <v>1971</v>
       </c>
       <c r="W570" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA570" t="b">
         <v>0</v>
@@ -45510,7 +45516,7 @@
         <v>1972</v>
       </c>
       <c r="W571" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA571" t="b">
         <v>0</v>
@@ -45578,7 +45584,7 @@
         <v>1973</v>
       </c>
       <c r="W572" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA572" t="b">
         <v>0</v>
@@ -45646,7 +45652,7 @@
         <v>1974</v>
       </c>
       <c r="W573" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA573" t="b">
         <v>0</v>
@@ -45714,7 +45720,7 @@
         <v>1975</v>
       </c>
       <c r="W574" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA574" t="b">
         <v>0</v>
@@ -45782,7 +45788,7 @@
         <v>1976</v>
       </c>
       <c r="W575" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA575" t="b">
         <v>0</v>
@@ -45850,7 +45856,7 @@
         <v>1977</v>
       </c>
       <c r="W576" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA576" t="b">
         <v>0</v>
@@ -45918,7 +45924,7 @@
         <v>1977</v>
       </c>
       <c r="W577" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA577" t="b">
         <v>0</v>
@@ -45986,7 +45992,7 @@
         <v>1978</v>
       </c>
       <c r="W578" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA578" t="b">
         <v>0</v>
@@ -46054,7 +46060,7 @@
         <v>1979</v>
       </c>
       <c r="W579" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA579" t="b">
         <v>0</v>
@@ -46122,7 +46128,7 @@
         <v>1980</v>
       </c>
       <c r="W580" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA580" t="b">
         <v>0</v>
@@ -46190,7 +46196,7 @@
         <v>1981</v>
       </c>
       <c r="W581" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA581" t="b">
         <v>0</v>
@@ -46258,7 +46264,7 @@
         <v>1982</v>
       </c>
       <c r="W582" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA582" t="b">
         <v>0</v>
@@ -46326,7 +46332,7 @@
         <v>1983</v>
       </c>
       <c r="W583" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA583" t="b">
         <v>0</v>
@@ -46394,7 +46400,7 @@
         <v>1984</v>
       </c>
       <c r="W584" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA584" t="b">
         <v>0</v>
@@ -46462,7 +46468,7 @@
         <v>1984</v>
       </c>
       <c r="W585" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA585" t="b">
         <v>0</v>
@@ -46527,10 +46533,10 @@
         <v>1525</v>
       </c>
       <c r="V586" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="W586" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA586" t="b">
         <v>1</v>
@@ -46598,7 +46604,7 @@
         <v>1985</v>
       </c>
       <c r="W587" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA587" t="b">
         <v>0</v>
@@ -46666,10 +46672,10 @@
         <v>1986</v>
       </c>
       <c r="V588" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="W588" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA588" t="b">
         <v>1</v>
@@ -46737,7 +46743,7 @@
         <v>1987</v>
       </c>
       <c r="W589" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA589" t="b">
         <v>0</v>
@@ -46805,7 +46811,7 @@
         <v>1988</v>
       </c>
       <c r="W590" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA590" t="b">
         <v>0</v>
@@ -46873,7 +46879,7 @@
         <v>1989</v>
       </c>
       <c r="W591" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA591" t="b">
         <v>0</v>
@@ -46941,7 +46947,7 @@
         <v>1990</v>
       </c>
       <c r="W592" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA592" t="b">
         <v>0</v>
@@ -47009,7 +47015,7 @@
         <v>1991</v>
       </c>
       <c r="W593" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA593" t="b">
         <v>0</v>
@@ -47077,7 +47083,7 @@
         <v>1990</v>
       </c>
       <c r="W594" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA594" t="b">
         <v>0</v>
@@ -47145,10 +47151,10 @@
         <v>1992</v>
       </c>
       <c r="V595" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="W595" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA595" t="b">
         <v>0</v>
@@ -47216,7 +47222,7 @@
         <v>1993</v>
       </c>
       <c r="W596" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA596" t="b">
         <v>0</v>
@@ -47284,10 +47290,10 @@
         <v>1994</v>
       </c>
       <c r="V597" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="W597" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA597" t="b">
         <v>1</v>
@@ -47355,7 +47361,7 @@
         <v>1995</v>
       </c>
       <c r="W598" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA598" t="b">
         <v>0</v>
@@ -47417,10 +47423,10 @@
         <v>1525</v>
       </c>
       <c r="V599" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="W599" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA599" t="b">
         <v>1</v>
@@ -47488,10 +47494,10 @@
         <v>1996</v>
       </c>
       <c r="V600" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="W600" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA600" t="b">
         <v>1</v>
@@ -47553,7 +47559,7 @@
         <v>1525</v>
       </c>
       <c r="W601" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA601" t="b">
         <v>1</v>
@@ -47618,10 +47624,10 @@
         <v>1525</v>
       </c>
       <c r="V602" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="W602" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA602" t="b">
         <v>1</v>
@@ -47692,10 +47698,10 @@
         <v>1997</v>
       </c>
       <c r="V603" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="W603" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA603" t="b">
         <v>0</v>
@@ -47763,7 +47769,7 @@
         <v>1998</v>
       </c>
       <c r="W604" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA604" t="b">
         <v>0</v>
@@ -47828,10 +47834,10 @@
         <v>1524</v>
       </c>
       <c r="V605" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="W605" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA605" t="b">
         <v>1</v>
@@ -47892,8 +47898,11 @@
       <c r="T606" t="s">
         <v>1524</v>
       </c>
+      <c r="U606" t="s">
+        <v>1999</v>
+      </c>
       <c r="W606" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA606" t="b">
         <v>1</v>
@@ -47954,8 +47963,11 @@
       <c r="T607" t="s">
         <v>1525</v>
       </c>
+      <c r="U607" t="s">
+        <v>2000</v>
+      </c>
       <c r="W607" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="AA607" t="b">
         <v>1</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44901,10 +44901,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R562">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S562" t="s">
         <v>1524</v>
@@ -46524,10 +46524,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="R586">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S586" t="s">
         <v>1524</v>
@@ -46663,10 +46663,10 @@
         <v>1518</v>
       </c>
       <c r="Q588">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R588">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S588" t="s">
         <v>1525</v>
@@ -47281,10 +47281,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R597">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S597" t="s">
         <v>1525</v>
@@ -47417,10 +47417,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="R599">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S599" t="s">
         <v>1524</v>
@@ -47485,10 +47485,10 @@
         <v>46255</v>
       </c>
       <c r="Q600">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="R600">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S600" t="s">
         <v>1524</v>
@@ -47553,10 +47553,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="R601">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S601" t="s">
         <v>1524</v>
@@ -47618,10 +47618,10 @@
         <v>46262</v>
       </c>
       <c r="Q602">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="R602">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S602" t="s">
         <v>1524</v>
@@ -47686,10 +47686,10 @@
         <v>46258</v>
       </c>
       <c r="Q603">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="R603">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S603" t="s">
         <v>1524</v>
@@ -47825,10 +47825,10 @@
         <v>46258</v>
       </c>
       <c r="Q605">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="R605">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S605" t="s">
         <v>1525</v>
@@ -47893,10 +47893,10 @@
         <v>46267</v>
       </c>
       <c r="Q606">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="R606">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S606" t="s">
         <v>1525</v>
@@ -47958,10 +47958,10 @@
         <v>46291</v>
       </c>
       <c r="Q607">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="R607">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S607" t="s">
         <v>1525</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44910,10 +44910,10 @@
         <v>46251</v>
       </c>
       <c r="Q562">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R562">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S562" t="s">
         <v>1527</v>
@@ -46533,10 +46533,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R586">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S586" t="s">
         <v>1527</v>
@@ -47287,10 +47287,10 @@
         <v>46259</v>
       </c>
       <c r="Q597">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R597">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S597" t="s">
         <v>1528</v>
@@ -47423,10 +47423,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="R599">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S599" t="s">
         <v>1527</v>
@@ -47562,10 +47562,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="R601">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S601" t="s">
         <v>1527</v>
@@ -47627,10 +47627,10 @@
         <v>46262</v>
       </c>
       <c r="Q602">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="R602">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S602" t="s">
         <v>1527</v>
@@ -47695,10 +47695,10 @@
         <v>46258</v>
       </c>
       <c r="Q603">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="R603">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S603" t="s">
         <v>1527</v>
@@ -47834,10 +47834,10 @@
         <v>46258</v>
       </c>
       <c r="Q605">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="R605">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S605" t="s">
         <v>1528</v>
@@ -47902,10 +47902,10 @@
         <v>46267</v>
       </c>
       <c r="Q606">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="R606">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S606" t="s">
         <v>1528</v>
@@ -47967,10 +47967,10 @@
         <v>46291</v>
       </c>
       <c r="Q607">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="R607">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S607" t="s">
         <v>1528</v>
@@ -48035,10 +48035,10 @@
         <v>46269</v>
       </c>
       <c r="Q608">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R608">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S608" t="s">
         <v>1527</v>
@@ -48097,10 +48097,10 @@
         <v>46293</v>
       </c>
       <c r="Q609">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="R609">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S609" t="s">
         <v>1527</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -6007,7 +6007,7 @@
     <t>item será atendido com o estoque local pedido 18216324. Godoy 17/08. 20/08. AWB 12753325834 - volume retirado na loja GOLLOG - BSB por MATHEUS PINHO em 20/08. Godoy 21/08/26.</t>
   </si>
   <si>
-    <t>Estoque alterado de "Nao" para "SIM"  daremos prioridade para movimentar o item. Godoy 17/08/226</t>
+    <t>Estoque alterado de "Nao" para "SIM"  daremos prioridade para movimentar o item. Godoy 17/08/26. AWB 12755178874 -  volume retirado na loja GOLLOG - NAT por Teodoro silva em 29/08. Godoy 31/08/26.</t>
   </si>
   <si>
     <t>Emerg Cancelada por 3S JACQUELINEJSRG em 14/08/2026 motivo: será refeito - Godoy 17/08/2026.</t>
@@ -6016,7 +6016,7 @@
     <t>AWB 12754088775 - volume retirado na loja GOLLOG - NAT por Teodoro silva em 22/08. Godoy 25/08/26. TCTR - item atendido pela empresa Vee One através do recibo 709/FAB/26 em 25/08/2026. Godoy 28/08/26.</t>
   </si>
   <si>
-    <t>Emergência transformada em ANCE em 24/08. Aguardaremos atendimento com item da Vee One. Ramon 24/08/26.</t>
+    <t>Emergência transformada em ANCE em 24/08. Aguardaremos atendimento com item da Vee One. Ramon 24/08/26. AWB 12754249845 - volume retirado na loja GOLLOG - QMA por Kleyton em 24/08. Godoy 31/08/26.</t>
   </si>
   <si>
     <t>Recibo 719/FAB/26 assinado em 24/08. Ramon 24/08/26</t>
@@ -6031,25 +6031,19 @@
     <t>item será atendido com o estoque local pedido 18295192. Godoy 26/08.</t>
   </si>
   <si>
-    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08 - MATERIAL EM TRANSITO - RECIBO 722/FAB/26</t>
+    <t>Colocado pedido junto ao fornecedor LEGACY PARTS - tracking 1ZY85G530324002115 - entregue em Miami 11/08. Chegada GIG dia 15-08 (voo 4273). Entregue V1 JPA 17/08 - MATERIAL EM TRANSITO - RECIBO 722/FAB/26 awb 12754830370 DPE 28/08/2026</t>
   </si>
   <si>
     <t>PEDIDO NO EPM E-C98-26060 - CLA-05-08 , por gentileza, me confirme se está correto a data da informação e prazo de entrega do item.O item solicitado não atende a pane do sistema ARCOND,pôs a pane é de 18/11/2024, anterior ao contrato vigente ,desta forma deve ser feito toda analise do sistema ,devido muito tempo inoperante e sem o item. SO R1 Bispo VEE-ONE-BE em 06/08/26</t>
   </si>
   <si>
-    <t>Foi solicitado atendimento com estoque FAB - CLA- 10-08, ITEM PRONTO PARA EMBARQUE, AGUARDANDO NOTA FISCAL - CLA-11-08- ITEM AGUARDANDO DEFINIÇÃO DA COORDENADORIA QUANTO A EFETIVIDADE PARA APLICAÇÃO NA REFERIDA ANV.- CLA-13-08 - AT 685000002258. Conforme relatado pela Coordenadoria, foi enviado, via CAN, um item novo, PN 2641010-3. Dessa forma, o item que atualmente se encontra em poder da VeeOne deverá ser estornado ao estoque.CLA-25-08 - ITEM ENVIADO DIA 25-08-2026-AWB 127-5484 2314 DPE 26-08-26 -CLA-26-08</t>
-  </si>
-  <si>
-    <t>ITEM FOI ENTREGUE PARA A FAB PAMALS VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUE CLA-17-08 - Aguardando autorização para movimentação a BANT 25/08/2026</t>
-  </si>
-  <si>
-    <t>Colocado pedido no fornecedor WAGA INTERNATIONAL - validando previsão de entrega em Miami. ATZ 25/08</t>
-  </si>
-  <si>
-    <t>DPE DA WILLIAM DIA 20-08-2026 -CLA-18-08 -ENTREGUE NA BASE DO PAMALS 1 EA , SERÁ ENVIAO AO OPERADOR- CLA-20-08 - AWB 12754088775 - CLA-21-08 - recebido dia 22/08/2026</t>
-  </si>
-  <si>
-    <t>Colocado pedido Textron WB0003128625 - tracking 535477333011 - previsão de entrega 25/08 V1 JPA - MATERIAL ENVIADO VIA RECIBO 726/FAB/26, AWB A SER GERADA PELA GOLLOG RC 25/08/2026</t>
+    <t>ITEM FOI ENTREGUE PARA A FAB PAMALS VIA RECIBO 598/FAB/26 31-07-26 - AINDA NÃO FOI PARA O ESTOQUE CLA-17-08 -Enviado para o Operador em 27/08/26 - AWB 12755178874 - REZ DPE 29/08/2026</t>
+  </si>
+  <si>
+    <t>Colocado pedido no fornecedor WAGA INTERNATIONAL INV26-00008 - tracking 876324334524 - previsão de entrega em Miami 31/08</t>
+  </si>
+  <si>
+    <t>Colocado pedido Textron WB0003128625 - tracking 535477333011 - previsão de entrega 25/08 V1 JPA - MATERIAL ENVIADO VIA RECIBO 726/FAB/26, AWB A SER GERADA PELA GOLLOG RC 25/08/2026 - AWB 12754866615 DPE 28/08/2026</t>
   </si>
   <si>
     <t>Colocado pedido no fornecedor I823285 - entregue em Miami 21/08 - TEMOS 3 EA NO ESTOQUE DA BANT. Material seguiu via awb 12754249845. Recebido por Kleyton em 24/08. Atl Ges.</t>
@@ -6058,7 +6052,13 @@
     <t>Material enviado via recibo 720/FAB/26 DPE 24/08/2026 - Retirado dia 24/08/2026 por Paula Pereira id 569968</t>
   </si>
   <si>
-    <t>Será atendido via estoque Vee One</t>
+    <t>Enviado para o Operador em 27/08/26- AWB 127-5516 5121 - REZ - MATERIAL DISPONIVEL PRA RETIRADA DIA 28/08/2026</t>
+  </si>
+  <si>
+    <t>Enviado para o Operador em 27/08/26- AWB 12755165585 - REZ DPE 01/09/2026</t>
+  </si>
+  <si>
+    <t>em cotação no mercado. ATZ 28/08</t>
   </si>
   <si>
     <t>VEE ONE</t>
@@ -44907,13 +44907,13 @@
         <v>46243</v>
       </c>
       <c r="O562" s="1">
-        <v>46251</v>
+        <v>46262</v>
       </c>
       <c r="Q562">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R562">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="S562" t="s">
         <v>1527</v>
@@ -46533,10 +46533,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="R586">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="S586" t="s">
         <v>1527</v>
@@ -46665,9 +46665,6 @@
       <c r="N588" s="1">
         <v>46255</v>
       </c>
-      <c r="O588" s="1">
-        <v>46260</v>
-      </c>
       <c r="P588" t="s">
         <v>1521</v>
       </c>
@@ -46685,9 +46682,6 @@
       </c>
       <c r="U588" t="s">
         <v>1989</v>
-      </c>
-      <c r="V588" t="s">
-        <v>2007</v>
       </c>
       <c r="W588" t="s">
         <v>2015</v>
@@ -47284,13 +47278,13 @@
         <v>46259</v>
       </c>
       <c r="O597" s="1">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="Q597">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R597">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S597" t="s">
         <v>1528</v>
@@ -47302,7 +47296,7 @@
         <v>1997</v>
       </c>
       <c r="V597" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="W597" t="s">
         <v>2015</v>
@@ -47422,11 +47416,14 @@
       <c r="N599" s="1">
         <v>46280</v>
       </c>
+      <c r="O599" s="1">
+        <v>46280</v>
+      </c>
       <c r="Q599">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="R599">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S599" t="s">
         <v>1527</v>
@@ -47435,7 +47432,7 @@
         <v>1528</v>
       </c>
       <c r="V599" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="W599" t="s">
         <v>2015</v>
@@ -47487,9 +47484,6 @@
       <c r="N600" s="1">
         <v>46282</v>
       </c>
-      <c r="O600" s="1">
-        <v>46255</v>
-      </c>
       <c r="P600" t="s">
         <v>1524</v>
       </c>
@@ -47507,9 +47501,6 @@
       </c>
       <c r="U600" t="s">
         <v>1999</v>
-      </c>
-      <c r="V600" t="s">
-        <v>2010</v>
       </c>
       <c r="W600" t="s">
         <v>2015</v>
@@ -47562,10 +47553,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="R601">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S601" t="s">
         <v>1527</v>
@@ -47627,10 +47618,10 @@
         <v>46262</v>
       </c>
       <c r="Q602">
-        <v>-21</v>
+        <v>-19</v>
       </c>
       <c r="R602">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S602" t="s">
         <v>1527</v>
@@ -47639,7 +47630,7 @@
         <v>1528</v>
       </c>
       <c r="V602" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="W602" t="s">
         <v>2015</v>
@@ -47695,10 +47686,10 @@
         <v>46258</v>
       </c>
       <c r="Q603">
-        <v>-23</v>
+        <v>-21</v>
       </c>
       <c r="R603">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S603" t="s">
         <v>1527</v>
@@ -47710,7 +47701,7 @@
         <v>2000</v>
       </c>
       <c r="V603" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="W603" t="s">
         <v>2015</v>
@@ -47751,7 +47742,7 @@
         <v>46254</v>
       </c>
       <c r="K604" s="1">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="L604">
         <v>2</v>
@@ -47760,16 +47751,16 @@
         <v>1283</v>
       </c>
       <c r="N604" s="1">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="P604" t="s">
         <v>1523</v>
       </c>
       <c r="Q604">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R604">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S604" t="s">
         <v>1527</v>
@@ -47834,10 +47825,10 @@
         <v>46258</v>
       </c>
       <c r="Q605">
-        <v>-26</v>
+        <v>-24</v>
       </c>
       <c r="R605">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S605" t="s">
         <v>1528</v>
@@ -47849,7 +47840,7 @@
         <v>2002</v>
       </c>
       <c r="V605" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="W605" t="s">
         <v>2015</v>
@@ -47901,11 +47892,14 @@
       <c r="N606" s="1">
         <v>46267</v>
       </c>
+      <c r="O606" s="1">
+        <v>46262</v>
+      </c>
       <c r="Q606">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="R606">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S606" t="s">
         <v>1528</v>
@@ -47915,6 +47909,9 @@
       </c>
       <c r="U606" t="s">
         <v>2003</v>
+      </c>
+      <c r="V606" t="s">
+        <v>2012</v>
       </c>
       <c r="W606" t="s">
         <v>2015</v>
@@ -47966,11 +47963,14 @@
       <c r="N607" s="1">
         <v>46291</v>
       </c>
+      <c r="O607" s="1">
+        <v>46266</v>
+      </c>
       <c r="Q607">
-        <v>-28</v>
+        <v>-26</v>
       </c>
       <c r="R607">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S607" t="s">
         <v>1528</v>
@@ -47982,7 +47982,7 @@
         <v>2004</v>
       </c>
       <c r="V607" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="W607" t="s">
         <v>2015</v>
@@ -48014,7 +48014,7 @@
         <v>2721</v>
       </c>
       <c r="H608" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I608" t="s">
         <v>1281</v>
@@ -48035,10 +48035,10 @@
         <v>46269</v>
       </c>
       <c r="Q608">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="R608">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S608" t="s">
         <v>1527</v>
@@ -48097,16 +48097,19 @@
         <v>46293</v>
       </c>
       <c r="Q609">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="R609">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S609" t="s">
         <v>1527</v>
       </c>
       <c r="T609" t="s">
         <v>1528</v>
+      </c>
+      <c r="V609" t="s">
+        <v>2014</v>
       </c>
       <c r="W609" t="s">
         <v>2015</v>

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7651" uniqueCount="2388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7652" uniqueCount="2388">
   <si>
     <t>om_emg</t>
   </si>
@@ -6022,7 +6022,7 @@
     <t>Recibo 719/FAB/26 assinado em 24/08. Ramon 24/08/26</t>
   </si>
   <si>
-    <t>Possui AWB ou recibo assinado? Ramon 28/08/26.</t>
+    <t>Possui AWB ou recibo assinado? Ramon 28/08/26. AWB 127-5428 0726 recebido por Paula em 24/08. Ramon31/08/26.</t>
   </si>
   <si>
     <t>item será atendido com o estoque local pedido 18294676. Godoy 26/08. Emg é na verdade AIFP, corrigido na planilha de 28/08. Ramon 28/08/26.</t>
@@ -47824,6 +47824,9 @@
       <c r="O605" s="1">
         <v>46258</v>
       </c>
+      <c r="P605" t="s">
+        <v>1523</v>
+      </c>
       <c r="Q605">
         <v>-24</v>
       </c>
@@ -47846,7 +47849,7 @@
         <v>2015</v>
       </c>
       <c r="AA605" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606" spans="1:27">

--- a/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
+++ b/Contrato 005/Dashboard/02_Dados_Tratados/historico_completo_emergencias.xlsx
@@ -44943,10 +44943,10 @@
         <v>46263</v>
       </c>
       <c r="Q562">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R562">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S562" t="s">
         <v>1534</v>
@@ -46569,10 +46569,10 @@
         <v>46269</v>
       </c>
       <c r="Q586">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R586">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="S586" t="s">
         <v>1534</v>
@@ -47453,10 +47453,10 @@
         <v>46280</v>
       </c>
       <c r="Q599">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R599">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S599" t="s">
         <v>1534</v>
@@ -47586,10 +47586,10 @@
         <v>46283</v>
       </c>
       <c r="Q601">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="R601">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S601" t="s">
         <v>1534</v>
@@ -47651,10 +47651,10 @@
         <v>46265</v>
       </c>
       <c r="Q602">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="R602">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S602" t="s">
         <v>1534</v>
@@ -47722,10 +47722,10 @@
         <v>46258</v>
       </c>
       <c r="Q603">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="R603">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S603" t="s">
         <v>1534</v>
@@ -48062,10 +48062,10 @@
         <v>46269</v>
       </c>
       <c r="Q608">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R608">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S608" t="s">
         <v>1534</v>
@@ -48130,10 +48130,10 @@
         <v>46293</v>
       </c>
       <c r="Q609">
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="R609">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S609" t="s">
         <v>1534</v>
@@ -48340,10 +48340,10 @@
         <v>46297</v>
       </c>
       <c r="Q612">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="R612">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S612" t="s">
         <v>1535</v>
